--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1115,15 +1115,15 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$B$5:$B$17,"TI",Planejado!$C$5:$C$17,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$B$5:$B$16,"TI",Planejado!$C$5:$C$16,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$B$6:$B$18,"TI",Comparativo!$C$6:$C$18,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$B$6:$B$18,"TI",Comparativo!$C$6:$C$18,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1139,7 +1139,7 @@
         <v/>
       </c>
       <c r="I6" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$18,"&gt;0",Comparativo!$B$6:$B$18,"TI",Comparativo!$C$6:$C$18,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$18,"?*",Comparativo!$B$6:$B$18,"TI",Comparativo!$C$6:$C$18,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$17,"&gt;0",Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$17,"?*",Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1155,15 +1155,15 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$B$5:$B$17,"TI",Planejado!$C$5:$C$17,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$B$5:$B$16,"TI",Planejado!$C$5:$C$16,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$B$6:$B$18,"TI",Comparativo!$C$6:$C$18,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$B$6:$B$18,"TI",Comparativo!$C$6:$C$18,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$18,"&gt;0",Comparativo!$B$6:$B$18,"TI",Comparativo!$C$6:$C$18,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$18,"?*",Comparativo!$B$6:$B$18,"TI",Comparativo!$C$6:$C$18,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$17,"&gt;0",Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$17,"?*",Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="12">
@@ -1219,7 +1219,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$18,"&gt;0",Comparativo!$B$6:$B$18,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$18,"?*",Comparativo!$B$6:$B$18,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$17,"&gt;0",Comparativo!$B$6:$B$17,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$17,"?*",Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1273,23 +1273,23 @@
         <v>1</v>
       </c>
       <c r="B13" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A13),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A13),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A13),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A13),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A13),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="G13" s="19">
@@ -1302,23 +1302,23 @@
         <v>2</v>
       </c>
       <c r="B14" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A14),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A14),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A14),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A14),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="F14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A14),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="G14" s="19">
@@ -1331,23 +1331,23 @@
         <v>3</v>
       </c>
       <c r="B15" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A15),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A15),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A15),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A15),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="F15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A15),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="G15" s="19">
@@ -1360,23 +1360,23 @@
         <v>4</v>
       </c>
       <c r="B16" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A16),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A16),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A16),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A16),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="F16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A16),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="G16" s="19">
@@ -1389,23 +1389,23 @@
         <v>5</v>
       </c>
       <c r="B17" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A17),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A17),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A17),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A17),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="F17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$18,MATCH(LARGE(Comparativo!$O$6:$O$18,A17),Comparativo!$O$6:$O$18,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
         <v/>
       </c>
       <c r="G17" s="19">
@@ -1429,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2359,123 +2359,57 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="24">
-        <f>Planejado!A17</f>
-        <v/>
-      </c>
-      <c r="B18" s="24">
-        <f>Planejado!B17</f>
-        <v/>
-      </c>
-      <c r="C18" s="24">
-        <f>Planejado!C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="25">
-        <f>Planejado!D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>Planejado!G17</f>
-        <v/>
-      </c>
-      <c r="F18" s="26">
-        <f>INDEX(Planejado!$H17:$S17,$D$3)</f>
-        <v/>
-      </c>
-      <c r="G18" s="26">
-        <f>INDEX(Realizado!$H17:$S17,$D$3)</f>
-        <v/>
-      </c>
-      <c r="H18" s="26">
-        <f>G18-F18</f>
-        <v/>
-      </c>
-      <c r="I18" s="26">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H17:$S17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="26">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H17:$S17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="26">
-        <f>J18-I18</f>
-        <v/>
-      </c>
-      <c r="L18" s="27">
-        <f>IFERROR(K18/I18,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="27">
-        <f>IFERROR(J18/I18,"")</f>
-        <v/>
-      </c>
-      <c r="N18" s="28">
-        <f>IF(P18=0,"Sem lançamento",IF(AND(I18=0,J18=0),"—",IF(I18=0,"Não orçado",IF(K18&gt;0.05*I18,"Acima do orçado",IF(K18&lt;-0.05*I18,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O18" s="23">
-        <f>IF(K18&gt;1,K18+ROW()/1000000,"")</f>
-        <v/>
-      </c>
-      <c r="P18" s="29">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H17:$S17&lt;&gt;""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n"/>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="31">
-        <f>SUM(F6:F18)</f>
-        <v/>
-      </c>
-      <c r="G29" s="31">
-        <f>SUM(G6:G18)</f>
-        <v/>
-      </c>
-      <c r="H29" s="31">
-        <f>SUM(H6:H18)</f>
-        <v/>
-      </c>
-      <c r="I29" s="31">
-        <f>SUM(I6:I18)</f>
-        <v/>
-      </c>
-      <c r="J29" s="31">
-        <f>SUM(J6:J18)</f>
-        <v/>
-      </c>
-      <c r="K29" s="31">
-        <f>SUM(K6:K18)</f>
-        <v/>
-      </c>
-      <c r="L29" s="32">
-        <f>IFERROR(K29/I29,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="32">
-        <f>IFERROR(J29/I29,"")</f>
-        <v/>
-      </c>
-      <c r="N29" s="30" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="30" t="n"/>
+      <c r="F27" s="31">
+        <f>SUM(F6:F17)</f>
+        <v/>
+      </c>
+      <c r="G27" s="31">
+        <f>SUM(G6:G17)</f>
+        <v/>
+      </c>
+      <c r="H27" s="31">
+        <f>SUM(H6:H17)</f>
+        <v/>
+      </c>
+      <c r="I27" s="31">
+        <f>SUM(I6:I17)</f>
+        <v/>
+      </c>
+      <c r="J27" s="31">
+        <f>SUM(J6:J17)</f>
+        <v/>
+      </c>
+      <c r="K27" s="31">
+        <f>SUM(K6:K17)</f>
+        <v/>
+      </c>
+      <c r="L27" s="32">
+        <f>IFERROR(K27/I27,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="32">
+        <f>IFERROR(J27/I27,"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="30" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N18"/>
+  <autoFilter ref="A5:N17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H18">
+  <conditionalFormatting sqref="H6:H17">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2483,7 +2417,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K18">
+  <conditionalFormatting sqref="K6:K17">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2506,7 +2440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2665,12 +2599,12 @@
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>Vinicius Di Franco — salário bruto</t>
+          <t>Vinicius Di Franco</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>Analista Administrativo — aumento de R$ 2.570,52 para R$ 3.070,52 a partir de 05/08/26, absorvido pela folga do envelope orçado (custo total segue R$ 5.416,525/mês)</t>
+          <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
@@ -2684,40 +2618,40 @@
         </is>
       </c>
       <c r="H5" s="26" t="n">
-        <v>2570.52</v>
+        <v>5416.525</v>
       </c>
       <c r="I5" s="26" t="n">
-        <v>2570.52</v>
+        <v>5416.525</v>
       </c>
       <c r="J5" s="26" t="n">
-        <v>2570.52</v>
+        <v>5416.525</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>2570.52</v>
+        <v>5416.525</v>
       </c>
       <c r="L5" s="26" t="n">
-        <v>2570.52</v>
+        <v>5416.525</v>
       </c>
       <c r="M5" s="26" t="n">
-        <v>2570.52</v>
+        <v>5416.525</v>
       </c>
       <c r="N5" s="26" t="n">
-        <v>2570.52</v>
+        <v>5416.525</v>
       </c>
       <c r="O5" s="26" t="n">
-        <v>3070.52</v>
+        <v>5416.525</v>
       </c>
       <c r="P5" s="26" t="n">
-        <v>3070.52</v>
+        <v>5416.525</v>
       </c>
       <c r="Q5" s="26" t="n">
-        <v>3070.52</v>
+        <v>5416.525</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>3070.52</v>
+        <v>5416.525</v>
       </c>
       <c r="S5" s="26" t="n">
-        <v>3070.52</v>
+        <v>5416.525</v>
       </c>
       <c r="T5" s="33">
         <f>SUM(H5:S5)</f>
@@ -2727,7 +2661,7 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>TI-E01B</t>
+          <t>TI-E02</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
@@ -2742,59 +2676,59 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Vinicius Di Franco — encargos e benefícios</t>
+          <t>Elias Benedito</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER. Planejado = resíduo do envelope de R$ 5.416,525/mês, que já previa o aumento. A folga não é economia estrutural: com o bruto de agosto ela quase se esgota.</t>
+          <t>Suporte Técnico Terceirizado</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>Encargos e Benefícios - CLT</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H6" s="26" t="n">
-        <v>2846.005</v>
+        <v>1065</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>2846.005</v>
+        <v>1065</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>2846.005</v>
+        <v>1065</v>
       </c>
       <c r="K6" s="26" t="n">
-        <v>2846.005</v>
+        <v>1065</v>
       </c>
       <c r="L6" s="26" t="n">
-        <v>2846.005</v>
+        <v>1065</v>
       </c>
       <c r="M6" s="26" t="n">
-        <v>2846.005</v>
+        <v>1065</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>2846.005</v>
+        <v>1065</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>2346.005</v>
+        <v>1065</v>
       </c>
       <c r="P6" s="26" t="n">
-        <v>2346.005</v>
+        <v>1065</v>
       </c>
       <c r="Q6" s="26" t="n">
-        <v>2346.005</v>
+        <v>1065</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>2346.005</v>
+        <v>1065</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>2346.005</v>
+        <v>1065</v>
       </c>
       <c r="T6" s="33">
         <f>SUM(H6:S6)</f>
@@ -2804,7 +2738,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>TI-E02</t>
+          <t>TI-E03</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
@@ -2819,12 +2753,12 @@
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>Elias Benedito</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>Suporte Técnico Terceirizado</t>
+          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -2838,40 +2772,40 @@
         </is>
       </c>
       <c r="H7" s="26" t="n">
-        <v>1065</v>
+        <v>0</v>
       </c>
       <c r="I7" s="26" t="n">
-        <v>1065</v>
+        <v>0</v>
       </c>
       <c r="J7" s="26" t="n">
-        <v>1065</v>
+        <v>0</v>
       </c>
       <c r="K7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="L7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="M7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="Q7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="S7" s="26" t="n">
-        <v>1065</v>
+        <v>10000</v>
       </c>
       <c r="T7" s="33">
         <f>SUM(H7:S7)</f>
@@ -2881,7 +2815,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>TI-E03</t>
+          <t>TI-D01</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
@@ -2891,64 +2825,60 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Peças de Manutenção</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
+          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr"/>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="J8" s="26" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="K8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="L8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="M8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="O8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="P8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="Q8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="S8" s="26" t="n">
-        <v>10000</v>
+        <v>810</v>
       </c>
       <c r="T8" s="33">
         <f>SUM(H8:S8)</f>
@@ -2958,7 +2888,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>TI-D01</t>
+          <t>TI-D02</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
@@ -2973,55 +2903,55 @@
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>Peças de Manutenção</t>
+          <t>Backup em Nuvem</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
+          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr"/>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos Diversos</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="I9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="J9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="K9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="L9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="M9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="N9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="O9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="P9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="Q9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="S9" s="26" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="T9" s="33">
         <f>SUM(H9:S9)</f>
@@ -3031,7 +2961,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>TI-D02</t>
+          <t>TI-D03</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
@@ -3046,12 +2976,12 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Backup em Nuvem</t>
+          <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
+          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr"/>
@@ -3061,40 +2991,40 @@
         </is>
       </c>
       <c r="H10" s="26" t="n">
-        <v>825</v>
+        <v>1300</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>825</v>
+        <v>1300</v>
       </c>
       <c r="J10" s="26" t="n">
-        <v>825</v>
+        <v>1300</v>
       </c>
       <c r="K10" s="26" t="n">
-        <v>825</v>
+        <v>1300</v>
       </c>
       <c r="L10" s="26" t="n">
-        <v>825</v>
+        <v>1300</v>
       </c>
       <c r="M10" s="26" t="n">
-        <v>825</v>
+        <v>1300</v>
       </c>
       <c r="N10" s="26" t="n">
-        <v>825</v>
+        <v>1600</v>
       </c>
       <c r="O10" s="26" t="n">
-        <v>825</v>
+        <v>1600</v>
       </c>
       <c r="P10" s="26" t="n">
-        <v>825</v>
+        <v>1600</v>
       </c>
       <c r="Q10" s="26" t="n">
-        <v>825</v>
+        <v>1600</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>825</v>
+        <v>1600</v>
       </c>
       <c r="S10" s="26" t="n">
-        <v>825</v>
+        <v>1600</v>
       </c>
       <c r="T10" s="33">
         <f>SUM(H10:S10)</f>
@@ -3104,7 +3034,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>TI-D03</t>
+          <t>TI-D04</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
@@ -3119,12 +3049,12 @@
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>Inteligência Artificial (Adapta)</t>
+          <t>Antivírus</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
+          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr"/>
@@ -3134,40 +3064,40 @@
         </is>
       </c>
       <c r="H11" s="26" t="n">
-        <v>1300</v>
+        <v>240</v>
       </c>
       <c r="I11" s="26" t="n">
-        <v>1300</v>
+        <v>240</v>
       </c>
       <c r="J11" s="26" t="n">
-        <v>1300</v>
+        <v>240</v>
       </c>
       <c r="K11" s="26" t="n">
-        <v>1300</v>
+        <v>240</v>
       </c>
       <c r="L11" s="26" t="n">
-        <v>1300</v>
+        <v>240</v>
       </c>
       <c r="M11" s="26" t="n">
-        <v>1300</v>
+        <v>240</v>
       </c>
       <c r="N11" s="26" t="n">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="O11" s="26" t="n">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="P11" s="26" t="n">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="Q11" s="26" t="n">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="S11" s="26" t="n">
-        <v>1600</v>
+        <v>240</v>
       </c>
       <c r="T11" s="33">
         <f>SUM(H11:S11)</f>
@@ -3177,7 +3107,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>TI-D04</t>
+          <t>TI-D05</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
@@ -3192,12 +3122,12 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Antivírus</t>
+          <t>Pacote Office 365</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
+          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr"/>
@@ -3207,40 +3137,40 @@
         </is>
       </c>
       <c r="H12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="J12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="K12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="L12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="M12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="O12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="P12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="Q12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="S12" s="26" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="T12" s="33">
         <f>SUM(H12:S12)</f>
@@ -3250,7 +3180,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>TI-D05</t>
+          <t>TI-D06</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
@@ -3265,55 +3195,55 @@
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>Pacote Office 365</t>
+          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
+          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr"/>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Móveis e Utensílios</t>
         </is>
       </c>
       <c r="H13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="I13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="J13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="K13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="L13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="M13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="P13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="Q13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="S13" s="26" t="n">
-        <v>375</v>
+        <v>2800</v>
       </c>
       <c r="T13" s="33">
         <f>SUM(H13:S13)</f>
@@ -3323,7 +3253,7 @@
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>TI-D06</t>
+          <t>TI-D07</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
@@ -3338,55 +3268,51 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
-        </is>
-      </c>
+          <t>Cursos e Treinamentos</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr"/>
       <c r="F14" s="24" t="inlineStr"/>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Móveis e Utensílios</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="J14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="L14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="M14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="N14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="O14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="P14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="Q14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="S14" s="26" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="T14" s="33">
         <f>SUM(H14:S14)</f>
@@ -3396,7 +3322,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>TI-D07</t>
+          <t>TI-D08</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
@@ -3411,51 +3337,51 @@
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>Cursos e Treinamentos</t>
+          <t>Aplicativo de Gravação de Reunião</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr"/>
       <c r="F15" s="24" t="inlineStr"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="I15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="J15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="L15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="M15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="N15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="O15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="P15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="Q15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="S15" s="26" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="T15" s="33">
         <f>SUM(H15:S15)</f>
@@ -3465,7 +3391,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>TI-D08</t>
+          <t>TI-D09</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
@@ -3480,197 +3406,128 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>Aplicativo de Gravação de Reunião</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr"/>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
       <c r="F16" s="24" t="inlineStr"/>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Prêmios</t>
         </is>
       </c>
       <c r="H16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="K16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="L16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="M16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="N16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="O16" s="26" t="n">
-        <v>220</v>
+        <v>2400</v>
       </c>
       <c r="P16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="S16" s="26" t="n">
-        <v>220</v>
+        <v>3600</v>
       </c>
       <c r="T16" s="33">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>TI-D09</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>TI</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>Despesas</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>Bonificação do time</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr"/>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>Prêmios</t>
-        </is>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="26" t="n">
-        <v>2400</v>
-      </c>
-      <c r="P17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="26" t="n">
-        <v>3600</v>
-      </c>
-      <c r="T17" s="33">
-        <f>SUM(H17:S17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="31">
-        <f>SUM(H5:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="31">
-        <f>SUM(I5:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="31">
-        <f>SUM(J5:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="31">
-        <f>SUM(K5:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="31">
-        <f>SUM(L5:L17)</f>
-        <v/>
-      </c>
-      <c r="M18" s="31">
-        <f>SUM(M5:M17)</f>
-        <v/>
-      </c>
-      <c r="N18" s="31">
-        <f>SUM(N5:N17)</f>
-        <v/>
-      </c>
-      <c r="O18" s="31">
-        <f>SUM(O5:O17)</f>
-        <v/>
-      </c>
-      <c r="P18" s="31">
-        <f>SUM(P5:P17)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="31">
-        <f>SUM(Q5:Q17)</f>
-        <v/>
-      </c>
-      <c r="R18" s="31">
-        <f>SUM(R5:R17)</f>
-        <v/>
-      </c>
-      <c r="S18" s="31">
-        <f>SUM(S5:S17)</f>
-        <v/>
-      </c>
-      <c r="T18" s="31">
-        <f>SUM(T5:T17)</f>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+      <c r="H17" s="31">
+        <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="31">
+        <f>SUM(I5:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="31">
+        <f>SUM(J5:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="31">
+        <f>SUM(K5:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="31">
+        <f>SUM(L5:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="31">
+        <f>SUM(M5:M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="31">
+        <f>SUM(N5:N16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="31">
+        <f>SUM(O5:O16)</f>
+        <v/>
+      </c>
+      <c r="P17" s="31">
+        <f>SUM(P5:P16)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="31">
+        <f>SUM(Q5:Q16)</f>
+        <v/>
+      </c>
+      <c r="R17" s="31">
+        <f>SUM(R5:R16)</f>
+        <v/>
+      </c>
+      <c r="S17" s="31">
+        <f>SUM(S5:S16)</f>
+        <v/>
+      </c>
+      <c r="T17" s="31">
+        <f>SUM(T5:T16)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T17"/>
+  <autoFilter ref="A4:T16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -3685,7 +3542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3871,28 +3728,18 @@
       <c r="I5" s="37" t="n"/>
       <c r="J5" s="37" t="n"/>
       <c r="K5" s="37" t="n"/>
-      <c r="L5" s="37" t="n">
-        <v>2570.52</v>
-      </c>
-      <c r="M5" s="37" t="n">
-        <v>2570.52</v>
-      </c>
-      <c r="N5" s="37" t="n">
-        <v>2570.52</v>
-      </c>
+      <c r="L5" s="37" t="n"/>
+      <c r="M5" s="37" t="n"/>
+      <c r="N5" s="37" t="n"/>
       <c r="O5" s="37" t="n"/>
       <c r="T5" s="33">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
-      <c r="U5" s="38" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
+      <c r="U5" s="38" t="n"/>
       <c r="V5" s="38" t="inlineStr">
         <is>
-          <t>Salário bruto vigente até jul; sobe para R$ 3.070,52 em ago</t>
+          <t>PREENCHER com o CUSTO TOTAL. Bruto: R$ 2.570,52/mês até jul e R$ 3.070,52 de ago — faltam encargos e benefícios</t>
         </is>
       </c>
     </row>
@@ -3929,18 +3776,28 @@
       <c r="I6" s="37" t="n"/>
       <c r="J6" s="37" t="n"/>
       <c r="K6" s="37" t="n"/>
-      <c r="L6" s="37" t="n"/>
-      <c r="M6" s="37" t="n"/>
-      <c r="N6" s="37" t="n"/>
+      <c r="L6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="O6" s="37" t="n"/>
       <c r="T6" s="33">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
-      <c r="U6" s="38" t="n"/>
+      <c r="U6" s="38" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
       <c r="V6" s="38" t="inlineStr">
         <is>
-          <t>PREENCHER — encargos e benefícios sobre o bruto</t>
+          <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
         </is>
       </c>
     </row>
@@ -3978,13 +3835,13 @@
       <c r="J7" s="37" t="n"/>
       <c r="K7" s="37" t="n"/>
       <c r="L7" s="37" t="n">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="M7" s="37" t="n">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="N7" s="37" t="n">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="O7" s="37" t="n"/>
       <c r="T7" s="33">
@@ -3998,7 +3855,7 @@
       </c>
       <c r="V7" s="38" t="inlineStr">
         <is>
-          <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
+          <t>R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
         </is>
       </c>
     </row>
@@ -4035,30 +3892,16 @@
       <c r="I8" s="37" t="n"/>
       <c r="J8" s="37" t="n"/>
       <c r="K8" s="37" t="n"/>
-      <c r="L8" s="37" t="n">
-        <v>6300</v>
-      </c>
-      <c r="M8" s="37" t="n">
-        <v>6300</v>
-      </c>
-      <c r="N8" s="37" t="n">
-        <v>6300</v>
-      </c>
+      <c r="L8" s="37" t="n"/>
+      <c r="M8" s="37" t="n"/>
+      <c r="N8" s="37" t="n"/>
       <c r="O8" s="37" t="n"/>
       <c r="T8" s="33">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
-      <c r="U8" s="38" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
-      <c r="V8" s="38" t="inlineStr">
-        <is>
-          <t>R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
-        </is>
-      </c>
+      <c r="U8" s="38" t="n"/>
+      <c r="V8" s="38" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="35">
@@ -4412,116 +4255,72 @@
       <c r="U16" s="38" t="n"/>
       <c r="V16" s="38" t="n"/>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="35">
-        <f>Planejado!A17</f>
-        <v/>
-      </c>
-      <c r="B17" s="35">
-        <f>Planejado!B17</f>
-        <v/>
-      </c>
-      <c r="C17" s="35">
-        <f>Planejado!C17</f>
-        <v/>
-      </c>
-      <c r="D17" s="36">
-        <f>Planejado!D17</f>
-        <v/>
-      </c>
-      <c r="E17" s="36">
-        <f>Planejado!E17</f>
-        <v/>
-      </c>
-      <c r="F17" s="35">
-        <f>Planejado!F17</f>
-        <v/>
-      </c>
-      <c r="G17" s="35">
-        <f>Planejado!G17</f>
-        <v/>
-      </c>
-      <c r="H17" s="37" t="n"/>
-      <c r="I17" s="37" t="n"/>
-      <c r="J17" s="37" t="n"/>
-      <c r="K17" s="37" t="n"/>
-      <c r="L17" s="37" t="n"/>
-      <c r="M17" s="37" t="n"/>
-      <c r="N17" s="37" t="n"/>
-      <c r="O17" s="37" t="n"/>
-      <c r="T17" s="33">
-        <f>SUM(H17:S17)</f>
-        <v/>
-      </c>
-      <c r="U17" s="38" t="n"/>
-      <c r="V17" s="38" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B18" s="39" t="n"/>
-      <c r="C18" s="39" t="n"/>
-      <c r="D18" s="39" t="n"/>
-      <c r="E18" s="39" t="n"/>
-      <c r="F18" s="39" t="n"/>
-      <c r="G18" s="39" t="n"/>
-      <c r="H18" s="40">
-        <f>SUM(H5:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="40">
-        <f>SUM(I5:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="40">
-        <f>SUM(J5:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="40">
-        <f>SUM(K5:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="40">
-        <f>SUM(L5:L17)</f>
-        <v/>
-      </c>
-      <c r="M18" s="40">
-        <f>SUM(M5:M17)</f>
-        <v/>
-      </c>
-      <c r="N18" s="40">
-        <f>SUM(N5:N17)</f>
-        <v/>
-      </c>
-      <c r="O18" s="40">
-        <f>SUM(O5:O17)</f>
-        <v/>
-      </c>
-      <c r="P18" s="40">
-        <f>SUM(P5:P17)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="40">
-        <f>SUM(Q5:Q17)</f>
-        <v/>
-      </c>
-      <c r="R18" s="40">
-        <f>SUM(R5:R17)</f>
-        <v/>
-      </c>
-      <c r="S18" s="40">
-        <f>SUM(S5:S17)</f>
-        <v/>
-      </c>
-      <c r="T18" s="40">
-        <f>SUM(T5:T17)</f>
-        <v/>
-      </c>
-      <c r="U18" s="39" t="n"/>
-      <c r="V18" s="39" t="n"/>
+      <c r="B17" s="39" t="n"/>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
+      <c r="H17" s="40">
+        <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="40">
+        <f>SUM(I5:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="40">
+        <f>SUM(J5:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="40">
+        <f>SUM(K5:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="40">
+        <f>SUM(L5:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="40">
+        <f>SUM(M5:M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="40">
+        <f>SUM(N5:N16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="40">
+        <f>SUM(O5:O16)</f>
+        <v/>
+      </c>
+      <c r="P17" s="40">
+        <f>SUM(P5:P16)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="40">
+        <f>SUM(Q5:Q16)</f>
+        <v/>
+      </c>
+      <c r="R17" s="40">
+        <f>SUM(R5:R16)</f>
+        <v/>
+      </c>
+      <c r="S17" s="40">
+        <f>SUM(S5:S16)</f>
+        <v/>
+      </c>
+      <c r="T17" s="40">
+        <f>SUM(T5:T16)</f>
+        <v/>
+      </c>
+      <c r="U17" s="39" t="n"/>
+      <c r="V17" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4614,11 +4413,11 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D5" s="42">
@@ -4649,11 +4448,11 @@
         </is>
       </c>
       <c r="B6" s="26">
-        <f>SUMIFS(Planejado!$I$5:$I$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C6" s="26">
-        <f>SUMIFS(Realizado!$I$5:$I$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D6" s="26">
@@ -4684,11 +4483,11 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D7" s="42">
@@ -4719,11 +4518,11 @@
         </is>
       </c>
       <c r="B8" s="26">
-        <f>SUMIFS(Planejado!$K$5:$K$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>SUMIFS(Realizado!$K$5:$K$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="26">
@@ -4754,11 +4553,11 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D9" s="42">
@@ -4789,11 +4588,11 @@
         </is>
       </c>
       <c r="B10" s="26">
-        <f>SUMIFS(Planejado!$M$5:$M$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C10" s="26">
-        <f>SUMIFS(Realizado!$M$5:$M$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D10" s="26">
@@ -4824,11 +4623,11 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="42">
@@ -4859,11 +4658,11 @@
         </is>
       </c>
       <c r="B12" s="26">
-        <f>SUMIFS(Planejado!$O$5:$O$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C12" s="26">
-        <f>SUMIFS(Realizado!$O$5:$O$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D12" s="26">
@@ -4894,11 +4693,11 @@
         </is>
       </c>
       <c r="B13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D13" s="42">
@@ -4929,11 +4728,11 @@
         </is>
       </c>
       <c r="B14" s="26">
-        <f>SUMIFS(Planejado!$Q$5:$Q$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C14" s="26">
-        <f>SUMIFS(Realizado!$Q$5:$Q$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D14" s="26">
@@ -4964,11 +4763,11 @@
         </is>
       </c>
       <c r="B15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D15" s="42">
@@ -4999,11 +4798,11 @@
         </is>
       </c>
       <c r="B16" s="26">
-        <f>SUMIFS(Planejado!$S$5:$S$17,Planejado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="C16" s="26">
-        <f>SUMIFS(Realizado!$S$5:$S$17,Realizado!$B$5:$B$17,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
       <c r="D16" s="26">
@@ -5080,7 +4879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5156,11 +4955,11 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$E$6:$E$18,$A5,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A5,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$E$6:$E$18,$A5,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A5,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="D5" s="42">
@@ -5180,22 +4979,22 @@
         <v/>
       </c>
       <c r="H5" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$G$5:$G$17,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="46" t="inlineStr">
         <is>
-          <t>Encargos e Benefícios - CLT</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="B6" s="26">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$E$6:$E$18,$A6,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A6,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="C6" s="26">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$E$6:$E$18,$A6,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A6,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="D6" s="26">
@@ -5215,22 +5014,22 @@
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$G$5:$G$17,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$E$6:$E$18,$A7,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A7,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$E$6:$E$18,$A7,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A7,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="D7" s="42">
@@ -5250,22 +5049,22 @@
         <v/>
       </c>
       <c r="H7" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$G$5:$G$17,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="46" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="B8" s="26">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$E$6:$E$18,$A8,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A8,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$E$6:$E$18,$A8,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A8,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="26">
@@ -5285,22 +5084,22 @@
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$G$5:$G$17,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Prêmios</t>
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$E$6:$E$18,$A9,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A9,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$E$6:$E$18,$A9,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A9,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="D9" s="42">
@@ -5320,22 +5119,22 @@
         <v/>
       </c>
       <c r="H9" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$G$5:$G$17,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="46" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
       <c r="B10" s="26">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$E$6:$E$18,$A10,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A10,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="C10" s="26">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$E$6:$E$18,$A10,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A10,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="D10" s="26">
@@ -5355,22 +5154,22 @@
         <v/>
       </c>
       <c r="H10" s="26">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$G$5:$G$17,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos Diversos</t>
+          <t>Móveis e Utensílios</t>
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$E$6:$E$18,$A11,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A11,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$E$6:$E$18,$A11,Comparativo!$B$6:$B$18,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A11,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="42">
@@ -5390,77 +5189,42 @@
         <v/>
       </c>
       <c r="H11" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$G$5:$G$17,$A11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
-        <is>
-          <t>Móveis e Utensílios</t>
-        </is>
-      </c>
-      <c r="B12" s="26">
-        <f>SUMIFS(Comparativo!$I$6:$I$18,Comparativo!$E$6:$E$18,$A12,Comparativo!$B$6:$B$18,"TI")</f>
-        <v/>
-      </c>
-      <c r="C12" s="26">
-        <f>SUMIFS(Comparativo!$J$6:$J$18,Comparativo!$E$6:$E$18,$A12,Comparativo!$B$6:$B$18,"TI")</f>
-        <v/>
-      </c>
-      <c r="D12" s="26">
-        <f>B12</f>
-        <v/>
-      </c>
-      <c r="E12" s="26">
-        <f>C12</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
-        <f>E12-D12</f>
-        <v/>
-      </c>
-      <c r="G12" s="47">
+        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="31">
+        <f>SUM(B5:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="31">
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="31">
+        <f>SUM(D5:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="31">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="31">
+        <f>SUM(F5:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="48">
         <f>IFERROR(F12/D12,"")</f>
         <v/>
       </c>
-      <c r="H12" s="26">
-        <f>SUMIFS(Planejado!$T$5:$T$17,Planejado!$G$5:$G$17,$A12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="31">
-        <f>SUM(B5:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="31">
-        <f>SUM(C5:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="31">
-        <f>SUM(D5:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="31">
-        <f>SUM(E5:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="31">
-        <f>SUM(F5:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="48">
-        <f>IFERROR(F13/D13,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="31">
-        <f>SUM(H5:H12)</f>
+      <c r="H12" s="31">
+        <f>SUM(H5:H11)</f>
         <v/>
       </c>
     </row>
@@ -5469,7 +5233,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F12">
+  <conditionalFormatting sqref="F5:F11">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5552,17 +5316,17 @@
       </c>
       <c r="B5" s="50" t="inlineStr">
         <is>
-          <t>Encargos do Vinicius — CAMPO A PREENCHER</t>
+          <t>Custo total do Vinicius — A LANÇAR</t>
         </is>
       </c>
       <c r="C5" s="50" t="inlineStr">
         <is>
-          <t>A linha TI-E01B recebe os encargos e benefícios sobre o salário bruto, mesmo tratamento dado à Geovanna. Hoje está em branco. Brutos confirmados pela gestora: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26. O envelope orçado permanece em R$ 5.416,525/mês — o aumento foi absorvido pela folga, não somado ao orçamento.</t>
+          <t>Mesmo caso da Geovanna. O planejado é R$ 5.416,525/mês (custo total). Brutos confirmados: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26 — o aumento é absorvido pela folga do envelope, que já previa reajuste, então o orçado não muda. O realizado está em branco.</t>
         </is>
       </c>
       <c r="D5" s="50" t="inlineStr">
         <is>
-          <t>A folga do orçado NÃO é economia estrutural: o custo total foi dimensionado prevendo um aumento maior, ainda não concedido. Com o bruto de agosto, o orçado de encargos (R$ 2.346,01) equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar.</t>
+          <t>A folga do orçado NÃO é economia estrutural. Com o bruto de agosto, sobram R$ 2.346,01 para encargos, o que equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar. Só o custo total real vai dizer.</t>
         </is>
       </c>
       <c r="E5" s="50" t="inlineStr">
@@ -5572,7 +5336,7 @@
       </c>
       <c r="F5" s="51" t="inlineStr">
         <is>
-          <t>PREENCHER</t>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -3772,10 +3772,18 @@
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="H6" s="37" t="n"/>
-      <c r="I6" s="37" t="n"/>
-      <c r="J6" s="37" t="n"/>
-      <c r="K6" s="37" t="n"/>
+      <c r="H6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="37" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="37" t="n">
         <v>0</v>
       </c>
@@ -3830,10 +3838,18 @@
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="37" t="n"/>
-      <c r="I7" s="37" t="n"/>
-      <c r="J7" s="37" t="n"/>
-      <c r="K7" s="37" t="n"/>
+      <c r="H7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="37" t="n">
+        <v>6300</v>
+      </c>
       <c r="L7" s="37" t="n">
         <v>6300</v>
       </c>
@@ -3855,7 +3871,7 @@
       </c>
       <c r="V7" s="38" t="inlineStr">
         <is>
-          <t>R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
+          <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -5332,7 +5332,7 @@
       </c>
       <c r="B5" s="50" t="inlineStr">
         <is>
-          <t>Custo total do Vinicius — A LANÇAR</t>
+          <t>Vinicius — custo total A LANÇAR</t>
         </is>
       </c>
       <c r="C5" s="50" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,13 +106,42 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B3A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B3A"/>
+      <sz val="9"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +185,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001E6B3A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
@@ -167,11 +206,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -201,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -233,7 +267,30 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,7 +298,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -262,6 +323,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -305,7 +367,7 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -314,19 +376,19 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1012,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1223,201 +1285,528 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
+          <t>ECONOMIA GERADA — acumulado de janeiro até o mês de referência</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Economia bruta</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="17">
+        <f>-SUMIF(Comparativo!$Q$6:$Q$17,"&lt;0")</f>
+        <v/>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Soma de tudo que ficou abaixo do orçado</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>(−) Gastos acima do orçado</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="17">
+        <f>-SUMIF(Comparativo!$Q$6:$Q$17,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Estouros que consomem parte da economia</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="19">
+        <f> ECONOMIA LÍQUIDA</f>
+        <v/>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="20">
+        <f>-SUM(Comparativo!$Q$6:$Q$17)</f>
+        <v/>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>O número defensável: só linhas comparáveis</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Projeção para o ano</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="17">
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$17)/Comparativo!$D$3*12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Extrapolação linear, se o padrão dos meses fechados se mantiver</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>% sobre o orçado do período</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="22">
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$17)/SUM(Comparativo!$S$6:$S$17),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Economia líquida ÷ planejado das linhas que entram na conta</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Fora desta conta: linhas sem nenhum lançamento. Só entra o que foi efetivamente lançado e é comparável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>DE ONDE VEIO A ECONOMIA (top 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Planejado acum.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Realizado acum.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Economia (R$)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>% da linha</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="28">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="29">
+        <f>IFERROR(F21/D21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="29">
+        <f>IFERROR(F22/D22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="28">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>IFERROR(F23/D23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="28">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="29">
+        <f>IFERROR(F24/D24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="28">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>IFERROR(F25/D25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
           <t>MAIORES DESVIOS DO ACUMULADO (top 5 acima do orçado)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="H29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C13" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A13),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="19">
-        <f>IFERROR(F13/D13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="B30" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="27">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="29">
+        <f>IFERROR(F30/D30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C14" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A14),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="19">
-        <f>IFERROR(F14/D14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="B31" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="27">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="29">
+        <f>IFERROR(F31/D31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A15),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="19">
-        <f>IFERROR(F15/D15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="B32" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="27">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="29">
+        <f>IFERROR(F32/D32,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A16),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="19">
-        <f>IFERROR(F16/D16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="B33" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="27">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="29">
+        <f>IFERROR(F33/D33,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="17">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="17">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A17),Comparativo!$O$6:$O$17,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="19">
-        <f>IFERROR(F17/D17,"")</f>
+      <c r="B34" s="26">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="26">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="27">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="27">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="27">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="29">
+        <f>IFERROR(F34/D34,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="16">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1429,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1448,6 +1837,9 @@
     <col width="17" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="10" customWidth="1" min="15" max="15"/>
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1470,17 +1862,17 @@
           <t>Mês de referência:</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Mês nº:</t>
         </is>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="33">
         <f>MATCH($B$3,Planejado!$H$4:$S$4,0)</f>
         <v/>
       </c>
@@ -1556,852 +1948,1011 @@
           <t>Situação</t>
         </is>
       </c>
-      <c r="O5" s="23" t="inlineStr">
+      <c r="O5" s="34" t="inlineStr">
         <is>
           <t>(aux ranking)</t>
         </is>
       </c>
-      <c r="P5" s="23" t="inlineStr">
+      <c r="P5" s="34" t="inlineStr">
         <is>
           <t>(aux meses lançados)</t>
         </is>
       </c>
+      <c r="Q5" s="34" t="inlineStr">
+        <is>
+          <t>(aux desvio comparável)</t>
+        </is>
+      </c>
+      <c r="R5" s="34" t="inlineStr">
+        <is>
+          <t>(aux ranking economia)</t>
+        </is>
+      </c>
+      <c r="S5" s="34" t="inlineStr">
+        <is>
+          <t>(aux planejado comparável)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="24">
+      <c r="A6" s="35">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="35">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="35">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="36">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="35">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="37">
         <f>INDEX(Planejado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="37">
         <f>INDEX(Realizado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="37">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="37">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="27">
+      <c r="L6" s="38">
         <f>IFERROR(K6/I6,"")</f>
         <v/>
       </c>
-      <c r="M6" s="27">
+      <c r="M6" s="38">
         <f>IFERROR(J6/I6,"")</f>
         <v/>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="39">
         <f>IF(P6=0,"Sem lançamento",IF(AND(I6=0,J6=0),"—",IF(I6=0,"Não orçado",IF(K6&gt;0.05*I6,"Acima do orçado",IF(K6&lt;-0.05*I6,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O6" s="23">
+      <c r="O6" s="34">
         <f>IF(K6&gt;1,K6+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H5:$S5&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q6" s="41">
+        <f>IF(P6=0,"",K6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="41">
+        <f>IF(AND(Q6&lt;&gt;"",Q6&lt;-1),-Q6+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S6" s="41">
+        <f>IF(Q6="","",I6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="24">
+      <c r="A7" s="35">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="35">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="35">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="36">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="35">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="37">
         <f>INDEX(Planejado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="37">
         <f>INDEX(Realizado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="37">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="37">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="38">
         <f>IFERROR(K7/I7,"")</f>
         <v/>
       </c>
-      <c r="M7" s="27">
+      <c r="M7" s="38">
         <f>IFERROR(J7/I7,"")</f>
         <v/>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="39">
         <f>IF(P7=0,"Sem lançamento",IF(AND(I7=0,J7=0),"—",IF(I7=0,"Não orçado",IF(K7&gt;0.05*I7,"Acima do orçado",IF(K7&lt;-0.05*I7,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="34">
         <f>IF(K7&gt;1,K7+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H6:$S6&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q7" s="41">
+        <f>IF(P7=0,"",K7)</f>
+        <v/>
+      </c>
+      <c r="R7" s="41">
+        <f>IF(AND(Q7&lt;&gt;"",Q7&lt;-1),-Q7+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S7" s="41">
+        <f>IF(Q7="","",I7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="24">
+      <c r="A8" s="35">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="35">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="35">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="36">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="35">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="37">
         <f>INDEX(Planejado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="37">
         <f>INDEX(Realizado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="37">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="37">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="38">
         <f>IFERROR(K8/I8,"")</f>
         <v/>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="38">
         <f>IFERROR(J8/I8,"")</f>
         <v/>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="39">
         <f>IF(P8=0,"Sem lançamento",IF(AND(I8=0,J8=0),"—",IF(I8=0,"Não orçado",IF(K8&gt;0.05*I8,"Acima do orçado",IF(K8&lt;-0.05*I8,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="34">
         <f>IF(K8&gt;1,K8+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P8" s="29">
+      <c r="P8" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H7:$S7&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q8" s="41">
+        <f>IF(P8=0,"",K8)</f>
+        <v/>
+      </c>
+      <c r="R8" s="41">
+        <f>IF(AND(Q8&lt;&gt;"",Q8&lt;-1),-Q8+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S8" s="41">
+        <f>IF(Q8="","",I8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="24">
+      <c r="A9" s="35">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="35">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="35">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="36">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="35">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="37">
         <f>INDEX(Planejado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="37">
         <f>INDEX(Realizado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="37">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="37">
         <f>J9-I9</f>
         <v/>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="38">
         <f>IFERROR(K9/I9,"")</f>
         <v/>
       </c>
-      <c r="M9" s="27">
+      <c r="M9" s="38">
         <f>IFERROR(J9/I9,"")</f>
         <v/>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="39">
         <f>IF(P9=0,"Sem lançamento",IF(AND(I9=0,J9=0),"—",IF(I9=0,"Não orçado",IF(K9&gt;0.05*I9,"Acima do orçado",IF(K9&lt;-0.05*I9,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O9" s="23">
+      <c r="O9" s="34">
         <f>IF(K9&gt;1,K9+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P9" s="29">
+      <c r="P9" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H8:$S8&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q9" s="41">
+        <f>IF(P9=0,"",K9)</f>
+        <v/>
+      </c>
+      <c r="R9" s="41">
+        <f>IF(AND(Q9&lt;&gt;"",Q9&lt;-1),-Q9+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S9" s="41">
+        <f>IF(Q9="","",I9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="24">
+      <c r="A10" s="35">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="35">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="35">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="36">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="35">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="37">
         <f>INDEX(Planejado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="37">
         <f>INDEX(Realizado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="37">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="37">
         <f>J10-I10</f>
         <v/>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="38">
         <f>IFERROR(K10/I10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="27">
+      <c r="M10" s="38">
         <f>IFERROR(J10/I10,"")</f>
         <v/>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="39">
         <f>IF(P10=0,"Sem lançamento",IF(AND(I10=0,J10=0),"—",IF(I10=0,"Não orçado",IF(K10&gt;0.05*I10,"Acima do orçado",IF(K10&lt;-0.05*I10,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="34">
         <f>IF(K10&gt;1,K10+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P10" s="29">
+      <c r="P10" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H9:$S9&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q10" s="41">
+        <f>IF(P10=0,"",K10)</f>
+        <v/>
+      </c>
+      <c r="R10" s="41">
+        <f>IF(AND(Q10&lt;&gt;"",Q10&lt;-1),-Q10+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S10" s="41">
+        <f>IF(Q10="","",I10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="24">
+      <c r="A11" s="35">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="35">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="35">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="36">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="35">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="37">
         <f>INDEX(Planejado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="37">
         <f>INDEX(Realizado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="37">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="37">
         <f>J11-I11</f>
         <v/>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="38">
         <f>IFERROR(K11/I11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="38">
         <f>IFERROR(J11/I11,"")</f>
         <v/>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="39">
         <f>IF(P11=0,"Sem lançamento",IF(AND(I11=0,J11=0),"—",IF(I11=0,"Não orçado",IF(K11&gt;0.05*I11,"Acima do orçado",IF(K11&lt;-0.05*I11,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O11" s="23">
+      <c r="O11" s="34">
         <f>IF(K11&gt;1,K11+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P11" s="29">
+      <c r="P11" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H10:$S10&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q11" s="41">
+        <f>IF(P11=0,"",K11)</f>
+        <v/>
+      </c>
+      <c r="R11" s="41">
+        <f>IF(AND(Q11&lt;&gt;"",Q11&lt;-1),-Q11+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S11" s="41">
+        <f>IF(Q11="","",I11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="24">
+      <c r="A12" s="35">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="35">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="35">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="36">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="35">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="37">
         <f>INDEX(Planejado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="37">
         <f>INDEX(Realizado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="37">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="37">
         <f>J12-I12</f>
         <v/>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="38">
         <f>IFERROR(K12/I12,"")</f>
         <v/>
       </c>
-      <c r="M12" s="27">
+      <c r="M12" s="38">
         <f>IFERROR(J12/I12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="39">
         <f>IF(P12=0,"Sem lançamento",IF(AND(I12=0,J12=0),"—",IF(I12=0,"Não orçado",IF(K12&gt;0.05*I12,"Acima do orçado",IF(K12&lt;-0.05*I12,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O12" s="23">
+      <c r="O12" s="34">
         <f>IF(K12&gt;1,K12+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P12" s="29">
+      <c r="P12" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H11:$S11&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q12" s="41">
+        <f>IF(P12=0,"",K12)</f>
+        <v/>
+      </c>
+      <c r="R12" s="41">
+        <f>IF(AND(Q12&lt;&gt;"",Q12&lt;-1),-Q12+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S12" s="41">
+        <f>IF(Q12="","",I12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="24">
+      <c r="A13" s="35">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="35">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="35">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="36">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="35">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="37">
         <f>INDEX(Planejado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="37">
         <f>INDEX(Realizado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="37">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="37">
         <f>J13-I13</f>
         <v/>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="38">
         <f>IFERROR(K13/I13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="38">
         <f>IFERROR(J13/I13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="39">
         <f>IF(P13=0,"Sem lançamento",IF(AND(I13=0,J13=0),"—",IF(I13=0,"Não orçado",IF(K13&gt;0.05*I13,"Acima do orçado",IF(K13&lt;-0.05*I13,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O13" s="23">
+      <c r="O13" s="34">
         <f>IF(K13&gt;1,K13+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P13" s="29">
+      <c r="P13" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H12:$S12&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q13" s="41">
+        <f>IF(P13=0,"",K13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="41">
+        <f>IF(AND(Q13&lt;&gt;"",Q13&lt;-1),-Q13+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S13" s="41">
+        <f>IF(Q13="","",I13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="24">
+      <c r="A14" s="35">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="35">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="35">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="36">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="35">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="37">
         <f>INDEX(Planejado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="37">
         <f>INDEX(Realizado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="37">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="37">
         <f>J14-I14</f>
         <v/>
       </c>
-      <c r="L14" s="27">
+      <c r="L14" s="38">
         <f>IFERROR(K14/I14,"")</f>
         <v/>
       </c>
-      <c r="M14" s="27">
+      <c r="M14" s="38">
         <f>IFERROR(J14/I14,"")</f>
         <v/>
       </c>
-      <c r="N14" s="28">
+      <c r="N14" s="39">
         <f>IF(P14=0,"Sem lançamento",IF(AND(I14=0,J14=0),"—",IF(I14=0,"Não orçado",IF(K14&gt;0.05*I14,"Acima do orçado",IF(K14&lt;-0.05*I14,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O14" s="23">
+      <c r="O14" s="34">
         <f>IF(K14&gt;1,K14+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P14" s="29">
+      <c r="P14" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H13:$S13&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q14" s="41">
+        <f>IF(P14=0,"",K14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="41">
+        <f>IF(AND(Q14&lt;&gt;"",Q14&lt;-1),-Q14+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S14" s="41">
+        <f>IF(Q14="","",I14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="24">
+      <c r="A15" s="35">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="35">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="35">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="36">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="35">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="37">
         <f>INDEX(Planejado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="37">
         <f>INDEX(Realizado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="37">
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="37">
         <f>J15-I15</f>
         <v/>
       </c>
-      <c r="L15" s="27">
+      <c r="L15" s="38">
         <f>IFERROR(K15/I15,"")</f>
         <v/>
       </c>
-      <c r="M15" s="27">
+      <c r="M15" s="38">
         <f>IFERROR(J15/I15,"")</f>
         <v/>
       </c>
-      <c r="N15" s="28">
+      <c r="N15" s="39">
         <f>IF(P15=0,"Sem lançamento",IF(AND(I15=0,J15=0),"—",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O15" s="23">
+      <c r="O15" s="34">
         <f>IF(K15&gt;1,K15+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P15" s="29">
+      <c r="P15" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$S14&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q15" s="41">
+        <f>IF(P15=0,"",K15)</f>
+        <v/>
+      </c>
+      <c r="R15" s="41">
+        <f>IF(AND(Q15&lt;&gt;"",Q15&lt;-1),-Q15+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S15" s="41">
+        <f>IF(Q15="","",I15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="24">
+      <c r="A16" s="35">
         <f>Planejado!A15</f>
         <v/>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="35">
         <f>Planejado!B15</f>
         <v/>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="35">
         <f>Planejado!C15</f>
         <v/>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="36">
         <f>Planejado!D15</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="35">
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="37">
         <f>INDEX(Planejado!$H15:$S15,$D$3)</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="37">
         <f>INDEX(Realizado!$H15:$S15,$D$3)</f>
         <v/>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="37">
         <f>G16-F16</f>
         <v/>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H15:$S15)</f>
         <v/>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H15:$S15)</f>
         <v/>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="37">
         <f>J16-I16</f>
         <v/>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="38">
         <f>IFERROR(K16/I16,"")</f>
         <v/>
       </c>
-      <c r="M16" s="27">
+      <c r="M16" s="38">
         <f>IFERROR(J16/I16,"")</f>
         <v/>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="39">
         <f>IF(P16=0,"Sem lançamento",IF(AND(I16=0,J16=0),"—",IF(I16=0,"Não orçado",IF(K16&gt;0.05*I16,"Acima do orçado",IF(K16&lt;-0.05*I16,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O16" s="23">
+      <c r="O16" s="34">
         <f>IF(K16&gt;1,K16+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P16" s="29">
+      <c r="P16" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H15:$S15&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q16" s="41">
+        <f>IF(P16=0,"",K16)</f>
+        <v/>
+      </c>
+      <c r="R16" s="41">
+        <f>IF(AND(Q16&lt;&gt;"",Q16&lt;-1),-Q16+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S16" s="41">
+        <f>IF(Q16="","",I16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="24">
+      <c r="A17" s="35">
         <f>Planejado!A16</f>
         <v/>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="35">
         <f>Planejado!B16</f>
         <v/>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="35">
         <f>Planejado!C16</f>
         <v/>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="36">
         <f>Planejado!D16</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="35">
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="37">
         <f>INDEX(Planejado!$H16:$S16,$D$3)</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="37">
         <f>INDEX(Realizado!$H16:$S16,$D$3)</f>
         <v/>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="37">
         <f>G17-F17</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H16:$S16)</f>
         <v/>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H16:$S16)</f>
         <v/>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="37">
         <f>J17-I17</f>
         <v/>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="38">
         <f>IFERROR(K17/I17,"")</f>
         <v/>
       </c>
-      <c r="M17" s="27">
+      <c r="M17" s="38">
         <f>IFERROR(J17/I17,"")</f>
         <v/>
       </c>
-      <c r="N17" s="28">
+      <c r="N17" s="39">
         <f>IF(P17=0,"Sem lançamento",IF(AND(I17=0,J17=0),"—",IF(I17=0,"Não orçado",IF(K17&gt;0.05*I17,"Acima do orçado",IF(K17&lt;-0.05*I17,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O17" s="23">
+      <c r="O17" s="34">
         <f>IF(K17&gt;1,K17+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P17" s="29">
+      <c r="P17" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H16:$S16&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q17" s="41">
+        <f>IF(P17=0,"",K17)</f>
+        <v/>
+      </c>
+      <c r="R17" s="41">
+        <f>IF(AND(Q17&lt;&gt;"",Q17&lt;-1),-Q17+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S17" s="41">
+        <f>IF(Q17="","",I17)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="31">
+      <c r="B27" s="42" t="n"/>
+      <c r="C27" s="42" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="43">
         <f>SUM(F6:F17)</f>
         <v/>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="43">
         <f>SUM(G6:G17)</f>
         <v/>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="43">
         <f>SUM(H6:H17)</f>
         <v/>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="43">
         <f>SUM(I6:I17)</f>
         <v/>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="43">
         <f>SUM(J6:J17)</f>
         <v/>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="43">
         <f>SUM(K6:K17)</f>
         <v/>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="44">
         <f>IFERROR(K27/I27,"")</f>
         <v/>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="44">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
-      <c r="N27" s="30" t="n"/>
+      <c r="N27" s="42" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:N17"/>
@@ -2582,946 +3133,946 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>TI-E01</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>Vinicius Di Franco</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H5" s="26" t="n">
+      <c r="H5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="I5" s="26" t="n">
+      <c r="I5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="J5" s="26" t="n">
+      <c r="J5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="K5" s="26" t="n">
+      <c r="K5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="L5" s="26" t="n">
+      <c r="L5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="M5" s="26" t="n">
+      <c r="M5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="N5" s="26" t="n">
+      <c r="N5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="O5" s="26" t="n">
+      <c r="O5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="P5" s="26" t="n">
+      <c r="P5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="Q5" s="26" t="n">
+      <c r="Q5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="R5" s="26" t="n">
+      <c r="R5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="S5" s="26" t="n">
+      <c r="S5" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="T5" s="33">
+      <c r="T5" s="45">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>TI-E02</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Elias Benedito</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>Suporte Técnico Terceirizado</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="K6" s="26" t="n">
+      <c r="K6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="L6" s="26" t="n">
+      <c r="L6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="M6" s="26" t="n">
+      <c r="M6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="N6" s="26" t="n">
+      <c r="N6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="O6" s="26" t="n">
+      <c r="O6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="P6" s="26" t="n">
+      <c r="P6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="Q6" s="26" t="n">
+      <c r="Q6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="R6" s="26" t="n">
+      <c r="R6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="S6" s="26" t="n">
+      <c r="S6" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="T6" s="33">
+      <c r="T6" s="45">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>TI-E03</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Jonathan</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H7" s="26" t="n">
+      <c r="H7" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="26" t="n">
+      <c r="J7" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="26" t="n">
+      <c r="K7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="L7" s="26" t="n">
+      <c r="L7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="M7" s="26" t="n">
+      <c r="M7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="N7" s="26" t="n">
+      <c r="N7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="O7" s="26" t="n">
+      <c r="O7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="P7" s="26" t="n">
+      <c r="P7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="Q7" s="26" t="n">
+      <c r="Q7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="R7" s="26" t="n">
+      <c r="R7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="S7" s="26" t="n">
+      <c r="S7" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="T7" s="33">
+      <c r="T7" s="45">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>TI-D01</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Peças de Manutenção</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr"/>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr"/>
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="K8" s="26" t="n">
+      <c r="K8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="L8" s="26" t="n">
+      <c r="L8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="M8" s="26" t="n">
+      <c r="M8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="N8" s="26" t="n">
+      <c r="N8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="O8" s="26" t="n">
+      <c r="O8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="P8" s="26" t="n">
+      <c r="P8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="Q8" s="26" t="n">
+      <c r="Q8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="R8" s="26" t="n">
+      <c r="R8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="S8" s="26" t="n">
+      <c r="S8" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="T8" s="33">
+      <c r="T8" s="45">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>TI-D02</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Backup em Nuvem</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr"/>
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="J9" s="26" t="n">
+      <c r="J9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="K9" s="26" t="n">
+      <c r="K9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="L9" s="26" t="n">
+      <c r="L9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="M9" s="26" t="n">
+      <c r="M9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="N9" s="26" t="n">
+      <c r="N9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="O9" s="26" t="n">
+      <c r="O9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="P9" s="26" t="n">
+      <c r="P9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="Q9" s="26" t="n">
+      <c r="Q9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="R9" s="26" t="n">
+      <c r="R9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="S9" s="26" t="n">
+      <c r="S9" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="T9" s="33">
+      <c r="T9" s="45">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>TI-D03</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr"/>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr"/>
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H10" s="26" t="n">
+      <c r="H10" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="K10" s="26" t="n">
+      <c r="K10" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="L10" s="26" t="n">
+      <c r="L10" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="M10" s="26" t="n">
+      <c r="M10" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="N10" s="26" t="n">
+      <c r="N10" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="O10" s="26" t="n">
+      <c r="O10" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="P10" s="26" t="n">
+      <c r="P10" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="Q10" s="26" t="n">
+      <c r="Q10" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="R10" s="26" t="n">
+      <c r="R10" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="S10" s="26" t="n">
+      <c r="S10" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10" s="45">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>TI-D04</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>Antivírus</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr"/>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr"/>
+      <c r="G11" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="I11" s="26" t="n">
+      <c r="I11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="J11" s="26" t="n">
+      <c r="J11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="K11" s="26" t="n">
+      <c r="K11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="L11" s="26" t="n">
+      <c r="L11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="M11" s="26" t="n">
+      <c r="M11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="N11" s="26" t="n">
+      <c r="N11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="O11" s="26" t="n">
+      <c r="O11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="P11" s="26" t="n">
+      <c r="P11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="Q11" s="26" t="n">
+      <c r="Q11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="R11" s="26" t="n">
+      <c r="R11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="S11" s="26" t="n">
+      <c r="S11" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="T11" s="33">
+      <c r="T11" s="45">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>TI-D05</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>Pacote Office 365</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr"/>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr"/>
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="J12" s="26" t="n">
+      <c r="J12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="K12" s="26" t="n">
+      <c r="K12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="L12" s="26" t="n">
+      <c r="L12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="M12" s="26" t="n">
+      <c r="M12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="N12" s="26" t="n">
+      <c r="N12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="O12" s="26" t="n">
+      <c r="O12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="P12" s="26" t="n">
+      <c r="P12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="Q12" s="26" t="n">
+      <c r="Q12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="R12" s="26" t="n">
+      <c r="R12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="S12" s="26" t="n">
+      <c r="S12" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="T12" s="33">
+      <c r="T12" s="45">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>TI-D06</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr"/>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr"/>
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>Móveis e Utensílios</t>
         </is>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="J13" s="26" t="n">
+      <c r="J13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="K13" s="26" t="n">
+      <c r="K13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="L13" s="26" t="n">
+      <c r="L13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="M13" s="26" t="n">
+      <c r="M13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="N13" s="26" t="n">
+      <c r="N13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="O13" s="26" t="n">
+      <c r="O13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="P13" s="26" t="n">
+      <c r="P13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="Q13" s="26" t="n">
+      <c r="Q13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="R13" s="26" t="n">
+      <c r="R13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="S13" s="26" t="n">
+      <c r="S13" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="T13" s="33">
+      <c r="T13" s="45">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>TI-D07</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Cursos e Treinamentos</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr"/>
-      <c r="F14" s="24" t="inlineStr"/>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr"/>
+      <c r="F14" s="35" t="inlineStr"/>
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H14" s="26" t="n">
+      <c r="H14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="I14" s="26" t="n">
+      <c r="I14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="J14" s="26" t="n">
+      <c r="J14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="K14" s="26" t="n">
+      <c r="K14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="L14" s="26" t="n">
+      <c r="L14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="M14" s="26" t="n">
+      <c r="M14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="N14" s="26" t="n">
+      <c r="N14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="O14" s="26" t="n">
+      <c r="O14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="P14" s="26" t="n">
+      <c r="P14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="Q14" s="26" t="n">
+      <c r="Q14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="R14" s="26" t="n">
+      <c r="R14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="S14" s="26" t="n">
+      <c r="S14" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="T14" s="33">
+      <c r="T14" s="45">
         <f>SUM(H14:S14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>TI-D08</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Aplicativo de Gravação de Reunião</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr"/>
-      <c r="F15" s="24" t="inlineStr"/>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr"/>
+      <c r="F15" s="35" t="inlineStr"/>
+      <c r="G15" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H15" s="26" t="n">
+      <c r="H15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="I15" s="26" t="n">
+      <c r="I15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="J15" s="26" t="n">
+      <c r="J15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="K15" s="26" t="n">
+      <c r="K15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="L15" s="26" t="n">
+      <c r="L15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="M15" s="26" t="n">
+      <c r="M15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="N15" s="26" t="n">
+      <c r="N15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="O15" s="26" t="n">
+      <c r="O15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="P15" s="26" t="n">
+      <c r="P15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="Q15" s="26" t="n">
+      <c r="Q15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="R15" s="26" t="n">
+      <c r="R15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="S15" s="26" t="n">
+      <c r="S15" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="T15" s="33">
+      <c r="T15" s="45">
         <f>SUM(H15:S15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>TI-D09</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Bonificação do time</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr"/>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr"/>
+      <c r="G16" s="35" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H16" s="26" t="n">
+      <c r="H16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="26" t="n">
+      <c r="J16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="26" t="n">
+      <c r="K16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="26" t="n">
+      <c r="L16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="26" t="n">
+      <c r="M16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="26" t="n">
+      <c r="N16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="26" t="n">
+      <c r="O16" s="37" t="n">
         <v>2400</v>
       </c>
-      <c r="P16" s="26" t="n">
+      <c r="P16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="26" t="n">
+      <c r="Q16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="R16" s="26" t="n">
+      <c r="R16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="26" t="n">
+      <c r="S16" s="37" t="n">
         <v>3600</v>
       </c>
-      <c r="T16" s="33">
+      <c r="T16" s="45">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="31">
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="43">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="43">
         <f>SUM(I5:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="43">
         <f>SUM(J5:J16)</f>
         <v/>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="43">
         <f>SUM(K5:K16)</f>
         <v/>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="43">
         <f>SUM(L5:L16)</f>
         <v/>
       </c>
-      <c r="M17" s="31">
+      <c r="M17" s="43">
         <f>SUM(M5:M16)</f>
         <v/>
       </c>
-      <c r="N17" s="31">
+      <c r="N17" s="43">
         <f>SUM(N5:N16)</f>
         <v/>
       </c>
-      <c r="O17" s="31">
+      <c r="O17" s="43">
         <f>SUM(O5:O16)</f>
         <v/>
       </c>
-      <c r="P17" s="31">
+      <c r="P17" s="43">
         <f>SUM(P5:P16)</f>
         <v/>
       </c>
-      <c r="Q17" s="31">
+      <c r="Q17" s="43">
         <f>SUM(Q5:Q16)</f>
         <v/>
       </c>
-      <c r="R17" s="31">
+      <c r="R17" s="43">
         <f>SUM(R5:R16)</f>
         <v/>
       </c>
-      <c r="S17" s="31">
+      <c r="S17" s="43">
         <f>SUM(S5:S16)</f>
         <v/>
       </c>
-      <c r="T17" s="31">
+      <c r="T17" s="43">
         <f>SUM(T5:T16)</f>
         <v/>
       </c>
@@ -3584,759 +4135,759 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>Detalhe / Observação</t>
         </is>
       </c>
-      <c r="F4" s="34" t="inlineStr">
+      <c r="F4" s="46" t="inlineStr">
         <is>
           <t>Vínculo</t>
         </is>
       </c>
-      <c r="G4" s="34" t="inlineStr">
+      <c r="G4" s="46" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="H4" s="34" t="inlineStr">
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="I4" s="34" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="J4" s="34" t="inlineStr">
+      <c r="J4" s="46" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="K4" s="34" t="inlineStr">
+      <c r="K4" s="46" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="L4" s="34" t="inlineStr">
+      <c r="L4" s="46" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="M4" s="34" t="inlineStr">
+      <c r="M4" s="46" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="N4" s="34" t="inlineStr">
+      <c r="N4" s="46" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="O4" s="34" t="inlineStr">
+      <c r="O4" s="46" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="P4" s="34" t="inlineStr">
+      <c r="P4" s="46" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="Q4" s="34" t="inlineStr">
+      <c r="Q4" s="46" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="R4" s="34" t="inlineStr">
+      <c r="R4" s="46" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="S4" s="34" t="inlineStr">
+      <c r="S4" s="46" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="T4" s="34" t="inlineStr">
+      <c r="T4" s="46" t="inlineStr">
         <is>
           <t>TOTAL REALIZADO</t>
         </is>
       </c>
-      <c r="U4" s="34" t="inlineStr">
+      <c r="U4" s="46" t="inlineStr">
         <is>
           <t>Fonte do dado</t>
         </is>
       </c>
-      <c r="V4" s="34" t="inlineStr">
+      <c r="V4" s="46" t="inlineStr">
         <is>
           <t>Observações do mês</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="35">
+      <c r="A5" s="47">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="47">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="47">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="48">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="48">
         <f>Planejado!E5</f>
         <v/>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="47">
         <f>Planejado!F5</f>
         <v/>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="47">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="37" t="n"/>
-      <c r="I5" s="37" t="n"/>
-      <c r="J5" s="37" t="n"/>
-      <c r="K5" s="37" t="n"/>
-      <c r="L5" s="37" t="n"/>
-      <c r="M5" s="37" t="n"/>
-      <c r="N5" s="37" t="n"/>
-      <c r="O5" s="37" t="n"/>
-      <c r="T5" s="33">
+      <c r="H5" s="49" t="n"/>
+      <c r="I5" s="49" t="n"/>
+      <c r="J5" s="49" t="n"/>
+      <c r="K5" s="49" t="n"/>
+      <c r="L5" s="49" t="n"/>
+      <c r="M5" s="49" t="n"/>
+      <c r="N5" s="49" t="n"/>
+      <c r="O5" s="49" t="n"/>
+      <c r="T5" s="45">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
-      <c r="U5" s="38" t="n"/>
-      <c r="V5" s="38" t="inlineStr">
+      <c r="U5" s="50" t="n"/>
+      <c r="V5" s="50" t="inlineStr">
         <is>
           <t>PREENCHER com o CUSTO TOTAL. Bruto: R$ 2.570,52/mês até jul e R$ 3.070,52 de ago — faltam encargos e benefícios</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="35">
+      <c r="A6" s="47">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="47">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="47">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="48">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="48">
         <f>Planejado!E6</f>
         <v/>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="47">
         <f>Planejado!F6</f>
         <v/>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="47">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="H6" s="37" t="n">
+      <c r="H6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="37" t="n">
+      <c r="I6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="37" t="n">
+      <c r="J6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="37" t="n">
+      <c r="K6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="37" t="n">
+      <c r="L6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="37" t="n">
+      <c r="M6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="37" t="n">
+      <c r="N6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="37" t="n"/>
-      <c r="T6" s="33">
+      <c r="O6" s="49" t="n"/>
+      <c r="T6" s="45">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
-      <c r="U6" s="38" t="inlineStr">
+      <c r="U6" s="50" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V6" s="38" t="inlineStr">
+      <c r="V6" s="50" t="inlineStr">
         <is>
           <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="35">
+      <c r="A7" s="47">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="47">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="47">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="48">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="48">
         <f>Planejado!E7</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="47">
         <f>Planejado!F7</f>
         <v/>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="47">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="37" t="n">
+      <c r="H7" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I7" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="37" t="n">
+      <c r="J7" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="37" t="n">
+      <c r="K7" s="49" t="n">
         <v>6300</v>
       </c>
-      <c r="L7" s="37" t="n">
+      <c r="L7" s="49" t="n">
         <v>6300</v>
       </c>
-      <c r="M7" s="37" t="n">
+      <c r="M7" s="49" t="n">
         <v>6300</v>
       </c>
-      <c r="N7" s="37" t="n">
+      <c r="N7" s="49" t="n">
         <v>6300</v>
       </c>
-      <c r="O7" s="37" t="n"/>
-      <c r="T7" s="33">
+      <c r="O7" s="49" t="n"/>
+      <c r="T7" s="45">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
-      <c r="U7" s="38" t="inlineStr">
+      <c r="U7" s="50" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V7" s="38" t="inlineStr">
+      <c r="V7" s="50" t="inlineStr">
         <is>
           <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="35">
+      <c r="A8" s="47">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="47">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="47">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="48">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="48">
         <f>Planejado!E8</f>
         <v/>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="47">
         <f>Planejado!F8</f>
         <v/>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="47">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="37" t="n"/>
-      <c r="I8" s="37" t="n"/>
-      <c r="J8" s="37" t="n"/>
-      <c r="K8" s="37" t="n"/>
-      <c r="L8" s="37" t="n"/>
-      <c r="M8" s="37" t="n"/>
-      <c r="N8" s="37" t="n"/>
-      <c r="O8" s="37" t="n"/>
-      <c r="T8" s="33">
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+      <c r="M8" s="49" t="n"/>
+      <c r="N8" s="49" t="n"/>
+      <c r="O8" s="49" t="n"/>
+      <c r="T8" s="45">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
-      <c r="U8" s="38" t="n"/>
-      <c r="V8" s="38" t="n"/>
+      <c r="U8" s="50" t="n"/>
+      <c r="V8" s="50" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="35">
+      <c r="A9" s="47">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="47">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="47">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="48">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="48">
         <f>Planejado!E9</f>
         <v/>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="47">
         <f>Planejado!F9</f>
         <v/>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="47">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="37" t="n"/>
-      <c r="I9" s="37" t="n"/>
-      <c r="J9" s="37" t="n"/>
-      <c r="K9" s="37" t="n"/>
-      <c r="L9" s="37" t="n"/>
-      <c r="M9" s="37" t="n"/>
-      <c r="N9" s="37" t="n"/>
-      <c r="O9" s="37" t="n"/>
-      <c r="T9" s="33">
+      <c r="H9" s="49" t="n"/>
+      <c r="I9" s="49" t="n"/>
+      <c r="J9" s="49" t="n"/>
+      <c r="K9" s="49" t="n"/>
+      <c r="L9" s="49" t="n"/>
+      <c r="M9" s="49" t="n"/>
+      <c r="N9" s="49" t="n"/>
+      <c r="O9" s="49" t="n"/>
+      <c r="T9" s="45">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
-      <c r="U9" s="38" t="n"/>
-      <c r="V9" s="38" t="n"/>
+      <c r="U9" s="50" t="n"/>
+      <c r="V9" s="50" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="35">
+      <c r="A10" s="47">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="47">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="47">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="48">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="48">
         <f>Planejado!E10</f>
         <v/>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="47">
         <f>Planejado!F10</f>
         <v/>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="47">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="37" t="n"/>
-      <c r="I10" s="37" t="n"/>
-      <c r="J10" s="37" t="n"/>
-      <c r="K10" s="37" t="n"/>
-      <c r="L10" s="37" t="n"/>
-      <c r="M10" s="37" t="n"/>
-      <c r="N10" s="37" t="n"/>
-      <c r="O10" s="37" t="n"/>
-      <c r="T10" s="33">
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="49" t="n"/>
+      <c r="K10" s="49" t="n"/>
+      <c r="L10" s="49" t="n"/>
+      <c r="M10" s="49" t="n"/>
+      <c r="N10" s="49" t="n"/>
+      <c r="O10" s="49" t="n"/>
+      <c r="T10" s="45">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
-      <c r="U10" s="38" t="n"/>
-      <c r="V10" s="38" t="n"/>
+      <c r="U10" s="50" t="n"/>
+      <c r="V10" s="50" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="35">
+      <c r="A11" s="47">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="47">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="47">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="48">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="48">
         <f>Planejado!E11</f>
         <v/>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="47">
         <f>Planejado!F11</f>
         <v/>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="47">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="37" t="n"/>
-      <c r="I11" s="37" t="n"/>
-      <c r="J11" s="37" t="n"/>
-      <c r="K11" s="37" t="n"/>
-      <c r="L11" s="37" t="n"/>
-      <c r="M11" s="37" t="n"/>
-      <c r="N11" s="37" t="n"/>
-      <c r="O11" s="37" t="n"/>
-      <c r="T11" s="33">
+      <c r="H11" s="49" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="49" t="n"/>
+      <c r="K11" s="49" t="n"/>
+      <c r="L11" s="49" t="n"/>
+      <c r="M11" s="49" t="n"/>
+      <c r="N11" s="49" t="n"/>
+      <c r="O11" s="49" t="n"/>
+      <c r="T11" s="45">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
-      <c r="U11" s="38" t="n"/>
-      <c r="V11" s="38" t="n"/>
+      <c r="U11" s="50" t="n"/>
+      <c r="V11" s="50" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="35">
+      <c r="A12" s="47">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="47">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="47">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="48">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="48">
         <f>Planejado!E12</f>
         <v/>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="47">
         <f>Planejado!F12</f>
         <v/>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="47">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="37" t="n"/>
-      <c r="I12" s="37" t="n"/>
-      <c r="J12" s="37" t="n"/>
-      <c r="K12" s="37" t="n"/>
-      <c r="L12" s="37" t="n"/>
-      <c r="M12" s="37" t="n"/>
-      <c r="N12" s="37" t="n"/>
-      <c r="O12" s="37" t="n"/>
-      <c r="T12" s="33">
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="49" t="n"/>
+      <c r="K12" s="49" t="n"/>
+      <c r="L12" s="49" t="n"/>
+      <c r="M12" s="49" t="n"/>
+      <c r="N12" s="49" t="n"/>
+      <c r="O12" s="49" t="n"/>
+      <c r="T12" s="45">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
-      <c r="U12" s="38" t="n"/>
-      <c r="V12" s="38" t="n"/>
+      <c r="U12" s="50" t="n"/>
+      <c r="V12" s="50" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="35">
+      <c r="A13" s="47">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="47">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="47">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="48">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="48">
         <f>Planejado!E13</f>
         <v/>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="47">
         <f>Planejado!F13</f>
         <v/>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="47">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="37" t="n"/>
-      <c r="I13" s="37" t="n"/>
-      <c r="J13" s="37" t="n"/>
-      <c r="K13" s="37" t="n"/>
-      <c r="L13" s="37" t="n"/>
-      <c r="M13" s="37" t="n"/>
-      <c r="N13" s="37" t="n"/>
-      <c r="O13" s="37" t="n"/>
-      <c r="T13" s="33">
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="49" t="n"/>
+      <c r="K13" s="49" t="n"/>
+      <c r="L13" s="49" t="n"/>
+      <c r="M13" s="49" t="n"/>
+      <c r="N13" s="49" t="n"/>
+      <c r="O13" s="49" t="n"/>
+      <c r="T13" s="45">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="38" t="n"/>
-      <c r="V13" s="38" t="n"/>
+      <c r="U13" s="50" t="n"/>
+      <c r="V13" s="50" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="35">
+      <c r="A14" s="47">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="47">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="47">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="48">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="48">
         <f>Planejado!E14</f>
         <v/>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="47">
         <f>Planejado!F14</f>
         <v/>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="47">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="H14" s="37" t="n"/>
-      <c r="I14" s="37" t="n"/>
-      <c r="J14" s="37" t="n"/>
-      <c r="K14" s="37" t="n"/>
-      <c r="L14" s="37" t="n"/>
-      <c r="M14" s="37" t="n"/>
-      <c r="N14" s="37" t="n"/>
-      <c r="O14" s="37" t="n"/>
-      <c r="T14" s="33">
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="49" t="n"/>
+      <c r="K14" s="49" t="n"/>
+      <c r="L14" s="49" t="n"/>
+      <c r="M14" s="49" t="n"/>
+      <c r="N14" s="49" t="n"/>
+      <c r="O14" s="49" t="n"/>
+      <c r="T14" s="45">
         <f>SUM(H14:S14)</f>
         <v/>
       </c>
-      <c r="U14" s="38" t="n"/>
-      <c r="V14" s="38" t="n"/>
+      <c r="U14" s="50" t="n"/>
+      <c r="V14" s="50" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="35">
+      <c r="A15" s="47">
         <f>Planejado!A15</f>
         <v/>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="47">
         <f>Planejado!B15</f>
         <v/>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="47">
         <f>Planejado!C15</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="48">
         <f>Planejado!D15</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="48">
         <f>Planejado!E15</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="47">
         <f>Planejado!F15</f>
         <v/>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="47">
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="H15" s="37" t="n"/>
-      <c r="I15" s="37" t="n"/>
-      <c r="J15" s="37" t="n"/>
-      <c r="K15" s="37" t="n"/>
-      <c r="L15" s="37" t="n"/>
-      <c r="M15" s="37" t="n"/>
-      <c r="N15" s="37" t="n"/>
-      <c r="O15" s="37" t="n"/>
-      <c r="T15" s="33">
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="49" t="n"/>
+      <c r="K15" s="49" t="n"/>
+      <c r="L15" s="49" t="n"/>
+      <c r="M15" s="49" t="n"/>
+      <c r="N15" s="49" t="n"/>
+      <c r="O15" s="49" t="n"/>
+      <c r="T15" s="45">
         <f>SUM(H15:S15)</f>
         <v/>
       </c>
-      <c r="U15" s="38" t="n"/>
-      <c r="V15" s="38" t="n"/>
+      <c r="U15" s="50" t="n"/>
+      <c r="V15" s="50" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="35">
+      <c r="A16" s="47">
         <f>Planejado!A16</f>
         <v/>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="47">
         <f>Planejado!B16</f>
         <v/>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="47">
         <f>Planejado!C16</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="48">
         <f>Planejado!D16</f>
         <v/>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="48">
         <f>Planejado!E16</f>
         <v/>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="47">
         <f>Planejado!F16</f>
         <v/>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="47">
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="H16" s="37" t="n"/>
-      <c r="I16" s="37" t="n"/>
-      <c r="J16" s="37" t="n"/>
-      <c r="K16" s="37" t="n"/>
-      <c r="L16" s="37" t="n"/>
-      <c r="M16" s="37" t="n"/>
-      <c r="N16" s="37" t="n"/>
-      <c r="O16" s="37" t="n"/>
-      <c r="T16" s="33">
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="49" t="n"/>
+      <c r="M16" s="49" t="n"/>
+      <c r="N16" s="49" t="n"/>
+      <c r="O16" s="49" t="n"/>
+      <c r="T16" s="45">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
-      <c r="U16" s="38" t="n"/>
-      <c r="V16" s="38" t="n"/>
+      <c r="U16" s="50" t="n"/>
+      <c r="V16" s="50" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B17" s="39" t="n"/>
-      <c r="C17" s="39" t="n"/>
-      <c r="D17" s="39" t="n"/>
-      <c r="E17" s="39" t="n"/>
-      <c r="F17" s="39" t="n"/>
-      <c r="G17" s="39" t="n"/>
-      <c r="H17" s="40">
+      <c r="B17" s="51" t="n"/>
+      <c r="C17" s="51" t="n"/>
+      <c r="D17" s="51" t="n"/>
+      <c r="E17" s="51" t="n"/>
+      <c r="F17" s="51" t="n"/>
+      <c r="G17" s="51" t="n"/>
+      <c r="H17" s="52">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="40">
+      <c r="I17" s="52">
         <f>SUM(I5:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="52">
         <f>SUM(J5:J16)</f>
         <v/>
       </c>
-      <c r="K17" s="40">
+      <c r="K17" s="52">
         <f>SUM(K5:K16)</f>
         <v/>
       </c>
-      <c r="L17" s="40">
+      <c r="L17" s="52">
         <f>SUM(L5:L16)</f>
         <v/>
       </c>
-      <c r="M17" s="40">
+      <c r="M17" s="52">
         <f>SUM(M5:M16)</f>
         <v/>
       </c>
-      <c r="N17" s="40">
+      <c r="N17" s="52">
         <f>SUM(N5:N16)</f>
         <v/>
       </c>
-      <c r="O17" s="40">
+      <c r="O17" s="52">
         <f>SUM(O5:O16)</f>
         <v/>
       </c>
-      <c r="P17" s="40">
+      <c r="P17" s="52">
         <f>SUM(P5:P16)</f>
         <v/>
       </c>
-      <c r="Q17" s="40">
+      <c r="Q17" s="52">
         <f>SUM(Q5:Q16)</f>
         <v/>
       </c>
-      <c r="R17" s="40">
+      <c r="R17" s="52">
         <f>SUM(R5:R16)</f>
         <v/>
       </c>
-      <c r="S17" s="40">
+      <c r="S17" s="52">
         <f>SUM(S5:S16)</f>
         <v/>
       </c>
-      <c r="T17" s="40">
+      <c r="T17" s="52">
         <f>SUM(T5:T16)</f>
         <v/>
       </c>
-      <c r="U17" s="39" t="n"/>
-      <c r="V17" s="39" t="n"/>
+      <c r="U17" s="51" t="n"/>
+      <c r="V17" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4423,453 +4974,453 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="54">
         <f>SUMIFS(Planejado!$H$5:$H$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="54">
         <f>SUMIFS(Realizado!$H$5:$H$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="54">
         <f>B5</f>
         <v/>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="54">
         <f>C5</f>
         <v/>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="54">
         <f>E5-D5</f>
         <v/>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="54">
         <f>SUM($D$5:D5)</f>
         <v/>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="54">
         <f>SUM($E$5:E5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="37">
         <f>SUMIFS(Planejado!$I$5:$I$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="37">
         <f>SUMIFS(Realizado!$I$5:$I$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="37">
         <f>B6</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="37">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="37">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="37">
         <f>SUM($D$5:D6)</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="37">
         <f>SUM($E$5:E6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B7" s="42">
+      <c r="B7" s="54">
         <f>SUMIFS(Planejado!$J$5:$J$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="54">
         <f>SUMIFS(Realizado!$J$5:$J$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="54">
         <f>B7</f>
         <v/>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="54">
         <f>C7</f>
         <v/>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="54">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="54">
         <f>SUM($D$5:D7)</f>
         <v/>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="54">
         <f>SUM($E$5:E7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="37">
         <f>SUMIFS(Planejado!$K$5:$K$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="37">
         <f>SUMIFS(Realizado!$K$5:$K$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="37">
         <f>B8</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="37">
         <f>C8</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="37">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="37">
         <f>SUM($D$5:D8)</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="37">
         <f>SUM($E$5:E8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="54">
         <f>SUMIFS(Planejado!$L$5:$L$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="54">
         <f>SUMIFS(Realizado!$L$5:$L$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="54">
         <f>B9</f>
         <v/>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="54">
         <f>C9</f>
         <v/>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="54">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="54">
         <f>SUM($D$5:D9)</f>
         <v/>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="54">
         <f>SUM($E$5:E9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="37">
         <f>SUMIFS(Planejado!$M$5:$M$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="37">
         <f>SUMIFS(Realizado!$M$5:$M$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="37">
         <f>B10</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="37">
         <f>C10</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="37">
         <f>E10-D10</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="37">
         <f>SUM($D$5:D10)</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="37">
         <f>SUM($E$5:E10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B11" s="42">
+      <c r="B11" s="54">
         <f>SUMIFS(Planejado!$N$5:$N$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="54">
         <f>SUMIFS(Realizado!$N$5:$N$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="54">
         <f>B11</f>
         <v/>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="54">
         <f>C11</f>
         <v/>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="54">
         <f>E11-D11</f>
         <v/>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="54">
         <f>SUM($D$5:D11)</f>
         <v/>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="54">
         <f>SUM($E$5:E11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="37">
         <f>SUMIFS(Planejado!$O$5:$O$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="37">
         <f>SUMIFS(Realizado!$O$5:$O$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="37">
         <f>B12</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="37">
         <f>C12</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="37">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="37">
         <f>SUM($D$5:D12)</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="37">
         <f>SUM($E$5:E12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="B13" s="42">
+      <c r="B13" s="54">
         <f>SUMIFS(Planejado!$P$5:$P$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="54">
         <f>SUMIFS(Realizado!$P$5:$P$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="54">
         <f>B13</f>
         <v/>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="54">
         <f>C13</f>
         <v/>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="54">
         <f>E13-D13</f>
         <v/>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="54">
         <f>SUM($D$5:D13)</f>
         <v/>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="54">
         <f>SUM($E$5:E13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="37">
         <f>SUMIFS(Planejado!$Q$5:$Q$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="37">
         <f>SUMIFS(Realizado!$Q$5:$Q$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="37">
         <f>B14</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="37">
         <f>C14</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="37">
         <f>E14-D14</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="37">
         <f>SUM($D$5:D14)</f>
         <v/>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="37">
         <f>SUM($E$5:E14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="54">
         <f>SUMIFS(Planejado!$R$5:$R$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="54">
         <f>SUMIFS(Realizado!$R$5:$R$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="54">
         <f>B15</f>
         <v/>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="54">
         <f>C15</f>
         <v/>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="54">
         <f>E15-D15</f>
         <v/>
       </c>
-      <c r="G15" s="42">
+      <c r="G15" s="54">
         <f>SUM($D$5:D15)</f>
         <v/>
       </c>
-      <c r="H15" s="42">
+      <c r="H15" s="54">
         <f>SUM($E$5:E15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="55" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="37">
         <f>SUMIFS(Planejado!$S$5:$S$16,Planejado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="37">
         <f>SUMIFS(Realizado!$S$5:$S$16,Realizado!$B$5:$B$16,"TI")</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="37">
         <f>B16</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="37">
         <f>C16</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="37">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="37">
         <f>SUM($D$5:D16)</f>
         <v/>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="37">
         <f>SUM($E$5:E16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="43">
         <f>SUM(B5:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="43">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="43">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="43">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="43">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="30" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4965,281 +5516,281 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="54">
         <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A5,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="54">
         <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A5,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="54">
         <f>B5</f>
         <v/>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="54">
         <f>C5</f>
         <v/>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="54">
         <f>E5-D5</f>
         <v/>
       </c>
-      <c r="G5" s="45">
+      <c r="G5" s="57">
         <f>IFERROR(F5/D5,"")</f>
         <v/>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="54">
         <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A6,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A6,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="37">
         <f>B6</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="37">
         <f>C6</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="37">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="59">
         <f>IFERROR(F6/D6,"")</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="37">
         <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="B7" s="42">
+      <c r="B7" s="54">
         <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A7,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="54">
         <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A7,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="54">
         <f>B7</f>
         <v/>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="54">
         <f>C7</f>
         <v/>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="54">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="57">
         <f>IFERROR(F7/D7,"")</f>
         <v/>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="54">
         <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A8,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A8,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="37">
         <f>B8</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="37">
         <f>C8</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="37">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="59">
         <f>IFERROR(F8/D8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="37">
         <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="54">
         <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A9,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="54">
         <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A9,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="54">
         <f>B9</f>
         <v/>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="54">
         <f>C9</f>
         <v/>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="54">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="57">
         <f>IFERROR(F9/D9,"")</f>
         <v/>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="54">
         <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A10,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A10,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="37">
         <f>B10</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="37">
         <f>C10</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="37">
         <f>E10-D10</f>
         <v/>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="59">
         <f>IFERROR(F10/D10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="37">
         <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>Móveis e Utensílios</t>
         </is>
       </c>
-      <c r="B11" s="42">
+      <c r="B11" s="54">
         <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A11,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="54">
         <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A11,Comparativo!$B$6:$B$17,"TI")</f>
         <v/>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="54">
         <f>B11</f>
         <v/>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="54">
         <f>C11</f>
         <v/>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="54">
         <f>E11-D11</f>
         <v/>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="57">
         <f>IFERROR(F11/D11,"")</f>
         <v/>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="54">
         <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="43">
         <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="43">
         <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="43">
         <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="43">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="43">
         <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="60">
         <f>IFERROR(F12/D12,"")</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="43">
         <f>SUM(H5:H11)</f>
         <v/>
       </c>
@@ -5325,384 +5876,384 @@
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>Vinicius — custo total A LANÇAR</t>
         </is>
       </c>
-      <c r="C5" s="50" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>Mesmo caso da Geovanna. O planejado é R$ 5.416,525/mês (custo total). Brutos confirmados: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26 — o aumento é absorvido pela folga do envelope, que já previa reajuste, então o orçado não muda. O realizado está em branco.</t>
         </is>
       </c>
-      <c r="D5" s="50" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>A folga do orçado NÃO é economia estrutural. Com o bruto de agosto, sobram R$ 2.346,01 para encargos, o que equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar. Só o custo total real vai dizer.</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr">
+      <c r="E5" s="62" t="inlineStr">
         <is>
           <t>Cristiane + RH</t>
         </is>
       </c>
-      <c r="F5" s="51" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B6" s="53" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
         </is>
       </c>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
         </is>
       </c>
-      <c r="D6" s="53" t="inlineStr">
+      <c r="D6" s="65" t="inlineStr">
         <is>
           <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
         </is>
       </c>
-      <c r="E6" s="53" t="inlineStr">
+      <c r="E6" s="65" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F6" s="54" t="inlineStr">
+      <c r="F6" s="66" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="50" t="inlineStr">
+      <c r="B7" s="62" t="inlineStr">
         <is>
           <t>Elias Benedito zerado nos três meses</t>
         </is>
       </c>
-      <c r="C7" s="50" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
         </is>
       </c>
-      <c r="D7" s="50" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 12.780 a liberar no orçamento do ano.</t>
         </is>
       </c>
-      <c r="E7" s="50" t="inlineStr">
+      <c r="E7" s="62" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="54" t="inlineStr">
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="52" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B8" s="53" t="inlineStr">
+      <c r="B8" s="65" t="inlineStr">
         <is>
           <t>Planejado de jan a abr — CONFERIR</t>
         </is>
       </c>
-      <c r="C8" s="53" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
         </is>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="65" t="inlineStr">
         <is>
           <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
         </is>
       </c>
-      <c r="E8" s="53" t="inlineStr">
+      <c r="E8" s="65" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F8" s="55" t="inlineStr">
+      <c r="F8" s="67" t="inlineStr">
         <is>
           <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B9" s="50" t="inlineStr">
+      <c r="B9" s="62" t="inlineStr">
         <is>
           <t>Realizado de jan a abr — A LANÇAR</t>
         </is>
       </c>
-      <c r="C9" s="50" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
         </is>
       </c>
-      <c r="D9" s="50" t="inlineStr">
+      <c r="D9" s="62" t="inlineStr">
         <is>
           <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
         </is>
       </c>
-      <c r="E9" s="50" t="inlineStr">
+      <c r="E9" s="62" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="51" t="inlineStr">
+      <c r="F9" s="63" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="52" t="inlineStr">
+      <c r="A10" s="64" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B10" s="53" t="inlineStr">
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>Despesas do TI — A LANÇAR</t>
         </is>
       </c>
-      <c r="C10" s="53" t="inlineStr">
+      <c r="C10" s="65" t="inlineStr">
         <is>
           <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
         </is>
       </c>
-      <c r="D10" s="53" t="inlineStr">
+      <c r="D10" s="65" t="inlineStr">
         <is>
           <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
         </is>
       </c>
-      <c r="E10" s="53" t="inlineStr">
+      <c r="E10" s="65" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="51" t="inlineStr">
+      <c r="F10" s="63" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="50" t="inlineStr">
+      <c r="B11" s="62" t="inlineStr">
         <is>
           <t>Base de meses — reconciliada com a ficha original</t>
         </is>
       </c>
-      <c r="C11" s="50" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
         </is>
       </c>
-      <c r="D11" s="50" t="inlineStr">
+      <c r="D11" s="62" t="inlineStr">
         <is>
           <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
         </is>
       </c>
-      <c r="E11" s="50" t="inlineStr">
+      <c r="E11" s="62" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F11" s="56" t="inlineStr">
+      <c r="F11" s="68" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="52" t="inlineStr">
+      <c r="A12" s="64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="53" t="inlineStr">
+      <c r="B12" s="65" t="inlineStr">
         <is>
           <t>Origem do valor realizado</t>
         </is>
       </c>
-      <c r="C12" s="53" t="inlineStr">
+      <c r="C12" s="65" t="inlineStr">
         <is>
           <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
         </is>
       </c>
-      <c r="D12" s="53" t="inlineStr">
+      <c r="D12" s="65" t="inlineStr">
         <is>
           <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
         </is>
       </c>
-      <c r="E12" s="53" t="inlineStr">
+      <c r="E12" s="65" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F12" s="54" t="inlineStr">
+      <c r="F12" s="66" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B13" s="50" t="inlineStr">
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
-      <c r="C13" s="50" t="inlineStr">
+      <c r="C13" s="62" t="inlineStr">
         <is>
           <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
         </is>
       </c>
-      <c r="D13" s="50" t="inlineStr">
+      <c r="D13" s="62" t="inlineStr">
         <is>
           <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
         </is>
       </c>
-      <c r="E13" s="50" t="inlineStr">
+      <c r="E13" s="62" t="inlineStr">
         <is>
           <t>Cristiane + Controladoria</t>
         </is>
       </c>
-      <c r="F13" s="54" t="inlineStr">
+      <c r="F13" s="66" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="52" t="inlineStr">
+      <c r="A14" s="64" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B14" s="53" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>Sala de Reunião — recorrente ou pontual?</t>
         </is>
       </c>
-      <c r="C14" s="53" t="inlineStr">
+      <c r="C14" s="65" t="inlineStr">
         <is>
           <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
         </is>
       </c>
-      <c r="D14" s="53" t="inlineStr">
+      <c r="D14" s="65" t="inlineStr">
         <is>
           <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
         </is>
       </c>
-      <c r="E14" s="53" t="inlineStr">
+      <c r="E14" s="65" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F14" s="54" t="inlineStr">
+      <c r="F14" s="66" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B15" s="50" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>Office 365 — nº de licenças</t>
         </is>
       </c>
-      <c r="C15" s="50" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
         </is>
       </c>
-      <c r="D15" s="50" t="inlineStr">
+      <c r="D15" s="62" t="inlineStr">
         <is>
           <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
         </is>
       </c>
-      <c r="E15" s="50" t="inlineStr">
+      <c r="E15" s="62" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F15" s="54" t="inlineStr">
+      <c r="F15" s="66" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="52" t="inlineStr">
+      <c r="A16" s="64" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B16" s="53" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>Critério de competência x caixa</t>
         </is>
       </c>
-      <c r="C16" s="53" t="inlineStr">
+      <c r="C16" s="65" t="inlineStr">
         <is>
           <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
         </is>
       </c>
-      <c r="D16" s="53" t="inlineStr">
+      <c r="D16" s="65" t="inlineStr">
         <is>
           <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
         </is>
       </c>
-      <c r="E16" s="53" t="inlineStr">
+      <c r="E16" s="65" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="54" t="inlineStr">
+      <c r="F16" s="66" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -5746,67 +6297,67 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>ROTINA MENSAL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="58" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="57" t="inlineStr">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="70" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="57" t="inlineStr">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="70" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -5814,67 +6365,67 @@
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="70" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="58" t="inlineStr">
+      <c r="B13" s="70" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="70" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="70" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="57" t="inlineStr">
+      <c r="A16" s="69" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="58" t="inlineStr">
+      <c r="B16" s="70" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -5882,43 +6433,43 @@
     </row>
     <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>REGRAS DA PLANILHA</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="57" t="inlineStr">
+      <c r="A19" s="69" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="58" t="inlineStr">
+      <c r="B19" s="70" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="57" t="inlineStr">
+      <c r="A20" s="69" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="58" t="inlineStr">
+      <c r="B20" s="70" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="57" t="inlineStr">
+      <c r="A21" s="69" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="58" t="inlineStr">
+      <c r="B21" s="70" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -6235,17 +6235,17 @@
       </c>
       <c r="B16" s="65" t="inlineStr">
         <is>
-          <t>Critério de competência x caixa</t>
+          <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
       <c r="C16" s="65" t="inlineStr">
         <is>
-          <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
+          <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
       <c r="D16" s="65" t="inlineStr">
         <is>
-          <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
+          <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Vale conferir quais contratos pagam no mês seguinte e decidir se o comparativo passa para competência.</t>
         </is>
       </c>
       <c r="E16" s="65" t="inlineStr">
@@ -6253,9 +6253,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="66" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F16" s="67" t="inlineStr">
+        <is>
+          <t>DECIDIR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,7 +141,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -208,6 +208,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -235,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -383,6 +388,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1177,15 +1185,15 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$B$5:$B$16,"TI",Planejado!$C$5:$C$16,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$B$5:$B$20,"TI",Planejado!$C$5:$C$20,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1201,7 +1209,7 @@
         <v/>
       </c>
       <c r="I6" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$17,"&gt;0",Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$17,"?*",Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$21,"&gt;0",Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$21,"?*",Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1217,15 +1225,15 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$B$5:$B$16,"TI",Planejado!$C$5:$C$16,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$B$5:$B$20,"TI",Planejado!$C$5:$C$20,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1241,7 +1249,7 @@
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$17,"&gt;0",Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$17,"?*",Comparativo!$B$6:$B$17,"TI",Comparativo!$C$6:$C$17,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$21,"&gt;0",Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$21,"?*",Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1257,15 +1265,15 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="12">
@@ -1281,7 +1289,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$17,"&gt;0",Comparativo!$B$6:$B$17,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$17,"?*",Comparativo!$B$6:$B$17,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$21,"&gt;0",Comparativo!$B$6:$B$21,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$21,"?*",Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1300,7 +1308,7 @@
       </c>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="17">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$17,"&lt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$21,"&lt;0")</f>
         <v/>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -1322,7 +1330,7 @@
       </c>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="17">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$17,"&gt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$21,"&gt;0")</f>
         <v/>
       </c>
       <c r="D13" s="18" t="inlineStr">
@@ -1343,7 +1351,7 @@
       </c>
       <c r="B14" s="19" t="n"/>
       <c r="C14" s="20">
-        <f>-SUM(Comparativo!$Q$6:$Q$17)</f>
+        <f>-SUM(Comparativo!$Q$6:$Q$21)</f>
         <v/>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -1365,7 +1373,7 @@
       </c>
       <c r="B15" s="16" t="n"/>
       <c r="C15" s="17">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$17)/Comparativo!$D$3*12,"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$21)/Comparativo!$D$3*12,"")</f>
         <v/>
       </c>
       <c r="D15" s="18" t="inlineStr">
@@ -1387,7 +1395,7 @@
       </c>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="22">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$17)/SUM(Comparativo!$S$6:$S$17),"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$21)/SUM(Comparativo!$S$6:$S$21),"")</f>
         <v/>
       </c>
       <c r="D16" s="18" t="inlineStr">
@@ -1459,23 +1467,23 @@
         <v>1</v>
       </c>
       <c r="B21" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="C21" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A21),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),""),"")</f>
         <v/>
       </c>
       <c r="G21" s="29">
@@ -1488,23 +1496,23 @@
         <v>2</v>
       </c>
       <c r="B22" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="C22" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="F22" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A22),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),""),"")</f>
         <v/>
       </c>
       <c r="G22" s="29">
@@ -1517,23 +1525,23 @@
         <v>3</v>
       </c>
       <c r="B23" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="C23" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="F23" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A23),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),""),"")</f>
         <v/>
       </c>
       <c r="G23" s="29">
@@ -1546,23 +1554,23 @@
         <v>4</v>
       </c>
       <c r="B24" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="C24" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="F24" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A24),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),""),"")</f>
         <v/>
       </c>
       <c r="G24" s="29">
@@ -1575,23 +1583,23 @@
         <v>5</v>
       </c>
       <c r="B25" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$R$6:$R$17,A25),Comparativo!$R$6:$R$17,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),""),"")</f>
         <v/>
       </c>
       <c r="G25" s="29">
@@ -1649,23 +1657,23 @@
         <v>1</v>
       </c>
       <c r="B30" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="C30" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="F30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A30),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="G30" s="29">
@@ -1678,23 +1686,23 @@
         <v>2</v>
       </c>
       <c r="B31" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="C31" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="F31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A31),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="G31" s="29">
@@ -1707,23 +1715,23 @@
         <v>3</v>
       </c>
       <c r="B32" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="C32" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="F32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A32),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="G32" s="29">
@@ -1736,23 +1744,23 @@
         <v>4</v>
       </c>
       <c r="B33" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="C33" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="F33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A33),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="G33" s="29">
@@ -1765,23 +1773,23 @@
         <v>5</v>
       </c>
       <c r="B34" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$17,MATCH(LARGE(Comparativo!$O$6:$O$17,A34),Comparativo!$O$6:$O$17,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="29">
@@ -1818,7 +1826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2910,57 +2918,369 @@
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="42" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="35">
+        <f>Planejado!A17</f>
+        <v/>
+      </c>
+      <c r="B18" s="35">
+        <f>Planejado!B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="35">
+        <f>Planejado!C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="36">
+        <f>Planejado!D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="35">
+        <f>Planejado!G17</f>
+        <v/>
+      </c>
+      <c r="F18" s="37">
+        <f>INDEX(Planejado!$H17:$S17,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G18" s="37">
+        <f>INDEX(Realizado!$H17:$S17,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H18" s="37">
+        <f>G18-F18</f>
+        <v/>
+      </c>
+      <c r="I18" s="37">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H17:$S17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="37">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H17:$S17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="37">
+        <f>J18-I18</f>
+        <v/>
+      </c>
+      <c r="L18" s="38">
+        <f>IFERROR(K18/I18,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="38">
+        <f>IFERROR(J18/I18,"")</f>
+        <v/>
+      </c>
+      <c r="N18" s="39">
+        <f>IF(P18=0,"Sem lançamento",IF(AND(I18=0,J18=0),"—",IF(I18=0,"Não orçado",IF(K18&gt;0.05*I18,"Acima do orçado",IF(K18&lt;-0.05*I18,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O18" s="34">
+        <f>IF(K18&gt;1,K18+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="40">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H17:$S17&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="41">
+        <f>IF(P18=0,"",K18)</f>
+        <v/>
+      </c>
+      <c r="R18" s="41">
+        <f>IF(AND(Q18&lt;&gt;"",Q18&lt;-1),-Q18+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S18" s="41">
+        <f>IF(Q18="","",I18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="35">
+        <f>Planejado!A18</f>
+        <v/>
+      </c>
+      <c r="B19" s="35">
+        <f>Planejado!B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="35">
+        <f>Planejado!C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="36">
+        <f>Planejado!D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="35">
+        <f>Planejado!G18</f>
+        <v/>
+      </c>
+      <c r="F19" s="37">
+        <f>INDEX(Planejado!$H18:$S18,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G19" s="37">
+        <f>INDEX(Realizado!$H18:$S18,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H19" s="37">
+        <f>G19-F19</f>
+        <v/>
+      </c>
+      <c r="I19" s="37">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H18:$S18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="37">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H18:$S18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="37">
+        <f>J19-I19</f>
+        <v/>
+      </c>
+      <c r="L19" s="38">
+        <f>IFERROR(K19/I19,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="38">
+        <f>IFERROR(J19/I19,"")</f>
+        <v/>
+      </c>
+      <c r="N19" s="39">
+        <f>IF(P19=0,"Sem lançamento",IF(AND(I19=0,J19=0),"—",IF(I19=0,"Não orçado",IF(K19&gt;0.05*I19,"Acima do orçado",IF(K19&lt;-0.05*I19,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O19" s="34">
+        <f>IF(K19&gt;1,K19+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="40">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H18:$S18&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="41">
+        <f>IF(P19=0,"",K19)</f>
+        <v/>
+      </c>
+      <c r="R19" s="41">
+        <f>IF(AND(Q19&lt;&gt;"",Q19&lt;-1),-Q19+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="41">
+        <f>IF(Q19="","",I19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="35">
+        <f>Planejado!A19</f>
+        <v/>
+      </c>
+      <c r="B20" s="35">
+        <f>Planejado!B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="35">
+        <f>Planejado!C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="36">
+        <f>Planejado!D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="35">
+        <f>Planejado!G19</f>
+        <v/>
+      </c>
+      <c r="F20" s="37">
+        <f>INDEX(Planejado!$H19:$S19,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G20" s="37">
+        <f>INDEX(Realizado!$H19:$S19,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H20" s="37">
+        <f>G20-F20</f>
+        <v/>
+      </c>
+      <c r="I20" s="37">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H19:$S19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="37">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H19:$S19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="37">
+        <f>J20-I20</f>
+        <v/>
+      </c>
+      <c r="L20" s="38">
+        <f>IFERROR(K20/I20,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="38">
+        <f>IFERROR(J20/I20,"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="39">
+        <f>IF(P20=0,"Sem lançamento",IF(AND(I20=0,J20=0),"—",IF(I20=0,"Não orçado",IF(K20&gt;0.05*I20,"Acima do orçado",IF(K20&lt;-0.05*I20,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O20" s="34">
+        <f>IF(K20&gt;1,K20+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="40">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H19:$S19&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="41">
+        <f>IF(P20=0,"",K20)</f>
+        <v/>
+      </c>
+      <c r="R20" s="41">
+        <f>IF(AND(Q20&lt;&gt;"",Q20&lt;-1),-Q20+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="41">
+        <f>IF(Q20="","",I20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="35">
+        <f>Planejado!A20</f>
+        <v/>
+      </c>
+      <c r="B21" s="35">
+        <f>Planejado!B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="35">
+        <f>Planejado!C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="36">
+        <f>Planejado!D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="35">
+        <f>Planejado!G20</f>
+        <v/>
+      </c>
+      <c r="F21" s="37">
+        <f>INDEX(Planejado!$H20:$S20,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G21" s="37">
+        <f>INDEX(Realizado!$H20:$S20,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H21" s="37">
+        <f>G21-F21</f>
+        <v/>
+      </c>
+      <c r="I21" s="37">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H20:$S20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="37">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H20:$S20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="37">
+        <f>J21-I21</f>
+        <v/>
+      </c>
+      <c r="L21" s="38">
+        <f>IFERROR(K21/I21,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="38">
+        <f>IFERROR(J21/I21,"")</f>
+        <v/>
+      </c>
+      <c r="N21" s="39">
+        <f>IF(P21=0,"Sem lançamento",IF(AND(I21=0,J21=0),"—",IF(I21=0,"Não orçado",IF(K21&gt;0.05*I21,"Acima do orçado",IF(K21&lt;-0.05*I21,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O21" s="34">
+        <f>IF(K21&gt;1,K21+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P21" s="40">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H20:$S20&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="41">
+        <f>IF(P21=0,"",K21)</f>
+        <v/>
+      </c>
+      <c r="R21" s="41">
+        <f>IF(AND(Q21&lt;&gt;"",Q21&lt;-1),-Q21+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S21" s="41">
+        <f>IF(Q21="","",I21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="42" t="n"/>
-      <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="42" t="n"/>
-      <c r="F27" s="43">
-        <f>SUM(F6:F17)</f>
-        <v/>
-      </c>
-      <c r="G27" s="43">
-        <f>SUM(G6:G17)</f>
-        <v/>
-      </c>
-      <c r="H27" s="43">
-        <f>SUM(H6:H17)</f>
-        <v/>
-      </c>
-      <c r="I27" s="43">
-        <f>SUM(I6:I17)</f>
-        <v/>
-      </c>
-      <c r="J27" s="43">
-        <f>SUM(J6:J17)</f>
-        <v/>
-      </c>
-      <c r="K27" s="43">
-        <f>SUM(K6:K17)</f>
-        <v/>
-      </c>
-      <c r="L27" s="44">
-        <f>IFERROR(K27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="44">
-        <f>IFERROR(J27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="42" t="n"/>
+      <c r="B31" s="42" t="n"/>
+      <c r="C31" s="42" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="43">
+        <f>SUM(F6:F21)</f>
+        <v/>
+      </c>
+      <c r="G31" s="43">
+        <f>SUM(G6:G21)</f>
+        <v/>
+      </c>
+      <c r="H31" s="43">
+        <f>SUM(H6:H21)</f>
+        <v/>
+      </c>
+      <c r="I31" s="43">
+        <f>SUM(I6:I21)</f>
+        <v/>
+      </c>
+      <c r="J31" s="43">
+        <f>SUM(J6:J21)</f>
+        <v/>
+      </c>
+      <c r="K31" s="43">
+        <f>SUM(K6:K21)</f>
+        <v/>
+      </c>
+      <c r="L31" s="44">
+        <f>IFERROR(K31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="44">
+        <f>IFERROR(J31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="42" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N17"/>
+  <autoFilter ref="A5:N21"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H17">
+  <conditionalFormatting sqref="H6:H21">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2968,7 +3288,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K17">
+  <conditionalFormatting sqref="K6:K21">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2991,7 +3311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3942,7 +4262,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>TI-D09</t>
+          <t>TI-D10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
@@ -3957,18 +4277,18 @@
       </c>
       <c r="D16" s="36" t="inlineStr">
         <is>
-          <t>Bonificação do time</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="E16" s="36" t="inlineStr">
         <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
         </is>
       </c>
       <c r="F16" s="35" t="inlineStr"/>
       <c r="G16" s="35" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H16" s="37" t="n">
@@ -3993,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="37" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P16" s="37" t="n">
         <v>0</v>
@@ -4005,80 +4325,372 @@
         <v>0</v>
       </c>
       <c r="S16" s="37" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="T16" s="45">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr">
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>TI-D11</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr"/>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>Licenças de Softwares</t>
+        </is>
+      </c>
+      <c r="H17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="45">
+        <f>SUM(H17:S17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>TI-D12</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
+        <is>
+          <t>Adapta One</t>
+        </is>
+      </c>
+      <c r="E18" s="36" t="inlineStr">
+        <is>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr"/>
+      <c r="G18" s="35" t="inlineStr">
+        <is>
+          <t>Licenças de Softwares</t>
+        </is>
+      </c>
+      <c r="H18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="45">
+        <f>SUM(H18:S18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>TI-D13</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D19" s="36" t="inlineStr">
+        <is>
+          <t>Adapta Skip</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr"/>
+      <c r="G19" s="35" t="inlineStr">
+        <is>
+          <t>Licenças de Softwares</t>
+        </is>
+      </c>
+      <c r="H19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="45">
+        <f>SUM(H19:S19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>TI-D09</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D20" s="36" t="inlineStr">
+        <is>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr"/>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="37" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="37" t="n">
+        <v>3600</v>
+      </c>
+      <c r="T20" s="45">
+        <f>SUM(H20:S20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B17" s="42" t="n"/>
-      <c r="C17" s="42" t="n"/>
-      <c r="D17" s="42" t="n"/>
-      <c r="E17" s="42" t="n"/>
-      <c r="F17" s="42" t="n"/>
-      <c r="G17" s="42" t="n"/>
-      <c r="H17" s="43">
-        <f>SUM(H5:H16)</f>
-        <v/>
-      </c>
-      <c r="I17" s="43">
-        <f>SUM(I5:I16)</f>
-        <v/>
-      </c>
-      <c r="J17" s="43">
-        <f>SUM(J5:J16)</f>
-        <v/>
-      </c>
-      <c r="K17" s="43">
-        <f>SUM(K5:K16)</f>
-        <v/>
-      </c>
-      <c r="L17" s="43">
-        <f>SUM(L5:L16)</f>
-        <v/>
-      </c>
-      <c r="M17" s="43">
-        <f>SUM(M5:M16)</f>
-        <v/>
-      </c>
-      <c r="N17" s="43">
-        <f>SUM(N5:N16)</f>
-        <v/>
-      </c>
-      <c r="O17" s="43">
-        <f>SUM(O5:O16)</f>
-        <v/>
-      </c>
-      <c r="P17" s="43">
-        <f>SUM(P5:P16)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="43">
-        <f>SUM(Q5:Q16)</f>
-        <v/>
-      </c>
-      <c r="R17" s="43">
-        <f>SUM(R5:R16)</f>
-        <v/>
-      </c>
-      <c r="S17" s="43">
-        <f>SUM(S5:S16)</f>
-        <v/>
-      </c>
-      <c r="T17" s="43">
-        <f>SUM(T5:T16)</f>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="42" t="n"/>
+      <c r="E21" s="42" t="n"/>
+      <c r="F21" s="42" t="n"/>
+      <c r="G21" s="42" t="n"/>
+      <c r="H21" s="43">
+        <f>SUM(H5:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="43">
+        <f>SUM(I5:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="43">
+        <f>SUM(J5:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="43">
+        <f>SUM(K5:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="43">
+        <f>SUM(L5:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="43">
+        <f>SUM(M5:M20)</f>
+        <v/>
+      </c>
+      <c r="N21" s="43">
+        <f>SUM(N5:N20)</f>
+        <v/>
+      </c>
+      <c r="O21" s="43">
+        <f>SUM(O5:O20)</f>
+        <v/>
+      </c>
+      <c r="P21" s="43">
+        <f>SUM(P5:P20)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="43">
+        <f>SUM(Q5:Q20)</f>
+        <v/>
+      </c>
+      <c r="R21" s="43">
+        <f>SUM(R5:R20)</f>
+        <v/>
+      </c>
+      <c r="S21" s="43">
+        <f>SUM(S5:S20)</f>
+        <v/>
+      </c>
+      <c r="T21" s="43">
+        <f>SUM(T5:T20)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T16"/>
+  <autoFilter ref="A4:T20"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -4093,7 +4705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4822,72 +5434,248 @@
       <c r="U16" s="50" t="n"/>
       <c r="V16" s="50" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="47">
+        <f>Planejado!A17</f>
+        <v/>
+      </c>
+      <c r="B17" s="47">
+        <f>Planejado!B17</f>
+        <v/>
+      </c>
+      <c r="C17" s="47">
+        <f>Planejado!C17</f>
+        <v/>
+      </c>
+      <c r="D17" s="48">
+        <f>Planejado!D17</f>
+        <v/>
+      </c>
+      <c r="E17" s="48">
+        <f>Planejado!E17</f>
+        <v/>
+      </c>
+      <c r="F17" s="47">
+        <f>Planejado!F17</f>
+        <v/>
+      </c>
+      <c r="G17" s="47">
+        <f>Planejado!G17</f>
+        <v/>
+      </c>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="49" t="n"/>
+      <c r="K17" s="49" t="n"/>
+      <c r="L17" s="49" t="n"/>
+      <c r="M17" s="49" t="n"/>
+      <c r="N17" s="49" t="n"/>
+      <c r="O17" s="49" t="n"/>
+      <c r="T17" s="45">
+        <f>SUM(H17:S17)</f>
+        <v/>
+      </c>
+      <c r="U17" s="50" t="n"/>
+      <c r="V17" s="50" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="47">
+        <f>Planejado!A18</f>
+        <v/>
+      </c>
+      <c r="B18" s="47">
+        <f>Planejado!B18</f>
+        <v/>
+      </c>
+      <c r="C18" s="47">
+        <f>Planejado!C18</f>
+        <v/>
+      </c>
+      <c r="D18" s="48">
+        <f>Planejado!D18</f>
+        <v/>
+      </c>
+      <c r="E18" s="48">
+        <f>Planejado!E18</f>
+        <v/>
+      </c>
+      <c r="F18" s="47">
+        <f>Planejado!F18</f>
+        <v/>
+      </c>
+      <c r="G18" s="47">
+        <f>Planejado!G18</f>
+        <v/>
+      </c>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="49" t="n"/>
+      <c r="K18" s="49" t="n"/>
+      <c r="L18" s="49" t="n"/>
+      <c r="M18" s="49" t="n"/>
+      <c r="N18" s="49" t="n"/>
+      <c r="O18" s="49" t="n"/>
+      <c r="T18" s="45">
+        <f>SUM(H18:S18)</f>
+        <v/>
+      </c>
+      <c r="U18" s="50" t="n"/>
+      <c r="V18" s="50" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="47">
+        <f>Planejado!A19</f>
+        <v/>
+      </c>
+      <c r="B19" s="47">
+        <f>Planejado!B19</f>
+        <v/>
+      </c>
+      <c r="C19" s="47">
+        <f>Planejado!C19</f>
+        <v/>
+      </c>
+      <c r="D19" s="48">
+        <f>Planejado!D19</f>
+        <v/>
+      </c>
+      <c r="E19" s="48">
+        <f>Planejado!E19</f>
+        <v/>
+      </c>
+      <c r="F19" s="47">
+        <f>Planejado!F19</f>
+        <v/>
+      </c>
+      <c r="G19" s="47">
+        <f>Planejado!G19</f>
+        <v/>
+      </c>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="49" t="n"/>
+      <c r="K19" s="49" t="n"/>
+      <c r="L19" s="49" t="n"/>
+      <c r="M19" s="49" t="n"/>
+      <c r="N19" s="49" t="n"/>
+      <c r="O19" s="49" t="n"/>
+      <c r="T19" s="45">
+        <f>SUM(H19:S19)</f>
+        <v/>
+      </c>
+      <c r="U19" s="50" t="n"/>
+      <c r="V19" s="50" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="47">
+        <f>Planejado!A20</f>
+        <v/>
+      </c>
+      <c r="B20" s="47">
+        <f>Planejado!B20</f>
+        <v/>
+      </c>
+      <c r="C20" s="47">
+        <f>Planejado!C20</f>
+        <v/>
+      </c>
+      <c r="D20" s="48">
+        <f>Planejado!D20</f>
+        <v/>
+      </c>
+      <c r="E20" s="48">
+        <f>Planejado!E20</f>
+        <v/>
+      </c>
+      <c r="F20" s="47">
+        <f>Planejado!F20</f>
+        <v/>
+      </c>
+      <c r="G20" s="47">
+        <f>Planejado!G20</f>
+        <v/>
+      </c>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="49" t="n"/>
+      <c r="K20" s="49" t="n"/>
+      <c r="L20" s="49" t="n"/>
+      <c r="M20" s="49" t="n"/>
+      <c r="N20" s="49" t="n"/>
+      <c r="O20" s="49" t="n"/>
+      <c r="T20" s="45">
+        <f>SUM(H20:S20)</f>
+        <v/>
+      </c>
+      <c r="U20" s="50" t="n"/>
+      <c r="V20" s="50" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B17" s="51" t="n"/>
-      <c r="C17" s="51" t="n"/>
-      <c r="D17" s="51" t="n"/>
-      <c r="E17" s="51" t="n"/>
-      <c r="F17" s="51" t="n"/>
-      <c r="G17" s="51" t="n"/>
-      <c r="H17" s="52">
-        <f>SUM(H5:H16)</f>
-        <v/>
-      </c>
-      <c r="I17" s="52">
-        <f>SUM(I5:I16)</f>
-        <v/>
-      </c>
-      <c r="J17" s="52">
-        <f>SUM(J5:J16)</f>
-        <v/>
-      </c>
-      <c r="K17" s="52">
-        <f>SUM(K5:K16)</f>
-        <v/>
-      </c>
-      <c r="L17" s="52">
-        <f>SUM(L5:L16)</f>
-        <v/>
-      </c>
-      <c r="M17" s="52">
-        <f>SUM(M5:M16)</f>
-        <v/>
-      </c>
-      <c r="N17" s="52">
-        <f>SUM(N5:N16)</f>
-        <v/>
-      </c>
-      <c r="O17" s="52">
-        <f>SUM(O5:O16)</f>
-        <v/>
-      </c>
-      <c r="P17" s="52">
-        <f>SUM(P5:P16)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="52">
-        <f>SUM(Q5:Q16)</f>
-        <v/>
-      </c>
-      <c r="R17" s="52">
-        <f>SUM(R5:R16)</f>
-        <v/>
-      </c>
-      <c r="S17" s="52">
-        <f>SUM(S5:S16)</f>
-        <v/>
-      </c>
-      <c r="T17" s="52">
-        <f>SUM(T5:T16)</f>
-        <v/>
-      </c>
-      <c r="U17" s="51" t="n"/>
-      <c r="V17" s="51" t="n"/>
+      <c r="B21" s="51" t="n"/>
+      <c r="C21" s="51" t="n"/>
+      <c r="D21" s="51" t="n"/>
+      <c r="E21" s="51" t="n"/>
+      <c r="F21" s="51" t="n"/>
+      <c r="G21" s="51" t="n"/>
+      <c r="H21" s="52">
+        <f>SUM(H5:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="52">
+        <f>SUM(I5:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="52">
+        <f>SUM(J5:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="52">
+        <f>SUM(K5:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="52">
+        <f>SUM(L5:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="52">
+        <f>SUM(M5:M20)</f>
+        <v/>
+      </c>
+      <c r="N21" s="52">
+        <f>SUM(N5:N20)</f>
+        <v/>
+      </c>
+      <c r="O21" s="52">
+        <f>SUM(O5:O20)</f>
+        <v/>
+      </c>
+      <c r="P21" s="52">
+        <f>SUM(P5:P20)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="52">
+        <f>SUM(Q5:Q20)</f>
+        <v/>
+      </c>
+      <c r="R21" s="52">
+        <f>SUM(R5:R20)</f>
+        <v/>
+      </c>
+      <c r="S21" s="52">
+        <f>SUM(S5:S20)</f>
+        <v/>
+      </c>
+      <c r="T21" s="52">
+        <f>SUM(T5:T20)</f>
+        <v/>
+      </c>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4980,11 +5768,11 @@
         </is>
       </c>
       <c r="B5" s="54">
-        <f>SUMIFS(Planejado!$H$5:$H$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C5" s="54">
-        <f>SUMIFS(Realizado!$H$5:$H$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D5" s="54">
@@ -5015,11 +5803,11 @@
         </is>
       </c>
       <c r="B6" s="37">
-        <f>SUMIFS(Planejado!$I$5:$I$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C6" s="37">
-        <f>SUMIFS(Realizado!$I$5:$I$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D6" s="37">
@@ -5050,11 +5838,11 @@
         </is>
       </c>
       <c r="B7" s="54">
-        <f>SUMIFS(Planejado!$J$5:$J$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C7" s="54">
-        <f>SUMIFS(Realizado!$J$5:$J$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D7" s="54">
@@ -5085,11 +5873,11 @@
         </is>
       </c>
       <c r="B8" s="37">
-        <f>SUMIFS(Planejado!$K$5:$K$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C8" s="37">
-        <f>SUMIFS(Realizado!$K$5:$K$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="37">
@@ -5120,11 +5908,11 @@
         </is>
       </c>
       <c r="B9" s="54">
-        <f>SUMIFS(Planejado!$L$5:$L$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C9" s="54">
-        <f>SUMIFS(Realizado!$L$5:$L$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D9" s="54">
@@ -5155,11 +5943,11 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>SUMIFS(Planejado!$M$5:$M$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C10" s="37">
-        <f>SUMIFS(Realizado!$M$5:$M$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D10" s="37">
@@ -5190,11 +5978,11 @@
         </is>
       </c>
       <c r="B11" s="54">
-        <f>SUMIFS(Planejado!$N$5:$N$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C11" s="54">
-        <f>SUMIFS(Realizado!$N$5:$N$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="54">
@@ -5225,11 +6013,11 @@
         </is>
       </c>
       <c r="B12" s="37">
-        <f>SUMIFS(Planejado!$O$5:$O$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C12" s="37">
-        <f>SUMIFS(Realizado!$O$5:$O$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D12" s="37">
@@ -5260,11 +6048,11 @@
         </is>
       </c>
       <c r="B13" s="54">
-        <f>SUMIFS(Planejado!$P$5:$P$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C13" s="54">
-        <f>SUMIFS(Realizado!$P$5:$P$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D13" s="54">
@@ -5295,11 +6083,11 @@
         </is>
       </c>
       <c r="B14" s="37">
-        <f>SUMIFS(Planejado!$Q$5:$Q$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C14" s="37">
-        <f>SUMIFS(Realizado!$Q$5:$Q$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D14" s="37">
@@ -5330,11 +6118,11 @@
         </is>
       </c>
       <c r="B15" s="54">
-        <f>SUMIFS(Planejado!$R$5:$R$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C15" s="54">
-        <f>SUMIFS(Realizado!$R$5:$R$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D15" s="54">
@@ -5365,11 +6153,11 @@
         </is>
       </c>
       <c r="B16" s="37">
-        <f>SUMIFS(Planejado!$S$5:$S$16,Planejado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$20,Planejado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="C16" s="37">
-        <f>SUMIFS(Realizado!$S$5:$S$16,Realizado!$B$5:$B$16,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$20,Realizado!$B$5:$B$20,"TI")</f>
         <v/>
       </c>
       <c r="D16" s="37">
@@ -5522,11 +6310,11 @@
         </is>
       </c>
       <c r="B5" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A5,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A5,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C5" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A5,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A5,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D5" s="54">
@@ -5546,7 +6334,7 @@
         <v/>
       </c>
       <c r="H5" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A5)</f>
         <v/>
       </c>
     </row>
@@ -5557,11 +6345,11 @@
         </is>
       </c>
       <c r="B6" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A6,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A6,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C6" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A6,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A6,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D6" s="37">
@@ -5581,7 +6369,7 @@
         <v/>
       </c>
       <c r="H6" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A6)</f>
         <v/>
       </c>
     </row>
@@ -5592,11 +6380,11 @@
         </is>
       </c>
       <c r="B7" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A7,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A7,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C7" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A7,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A7,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D7" s="54">
@@ -5616,7 +6404,7 @@
         <v/>
       </c>
       <c r="H7" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A7)</f>
         <v/>
       </c>
     </row>
@@ -5627,11 +6415,11 @@
         </is>
       </c>
       <c r="B8" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A8,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A8,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C8" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A8,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A8,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="37">
@@ -5651,7 +6439,7 @@
         <v/>
       </c>
       <c r="H8" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A8)</f>
         <v/>
       </c>
     </row>
@@ -5662,11 +6450,11 @@
         </is>
       </c>
       <c r="B9" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A9,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A9,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C9" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A9,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A9,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D9" s="54">
@@ -5686,7 +6474,7 @@
         <v/>
       </c>
       <c r="H9" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A9)</f>
         <v/>
       </c>
     </row>
@@ -5697,11 +6485,11 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A10,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A10,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C10" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A10,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A10,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D10" s="37">
@@ -5721,7 +6509,7 @@
         <v/>
       </c>
       <c r="H10" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A10)</f>
         <v/>
       </c>
     </row>
@@ -5732,11 +6520,11 @@
         </is>
       </c>
       <c r="B11" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$17,Comparativo!$E$6:$E$17,$A11,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A11,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C11" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$17,Comparativo!$E$6:$E$17,$A11,Comparativo!$B$6:$B$17,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A11,Comparativo!$B$6:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="54">
@@ -5756,7 +6544,7 @@
         <v/>
       </c>
       <c r="H11" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$16,Planejado!$G$5:$G$16,$A11)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A11)</f>
         <v/>
       </c>
     </row>
@@ -5818,7 +6606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6134,59 +6922,59 @@
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B13" s="62" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
         </is>
       </c>
       <c r="C13" s="62" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
         </is>
       </c>
       <c r="D13" s="62" t="inlineStr">
         <is>
-          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
+          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E13" s="62" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F13" s="66" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F13" s="69" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" s="65" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
       <c r="C14" s="65" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
         </is>
       </c>
       <c r="D14" s="65" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
         </is>
       </c>
       <c r="E14" s="65" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F14" s="66" t="inlineStr">
@@ -6198,22 +6986,22 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" s="62" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
         </is>
       </c>
       <c r="C15" s="62" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
         </is>
       </c>
       <c r="D15" s="62" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
         </is>
       </c>
       <c r="E15" s="62" t="inlineStr">
@@ -6230,30 +7018,62 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="64" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C16" s="65" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D16" s="65" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E16" s="65" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F16" s="66" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="61" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B16" s="65" t="inlineStr">
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
-      <c r="C16" s="65" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
-      <c r="D16" s="65" t="inlineStr">
+      <c r="D17" s="62" t="inlineStr">
         <is>
           <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Vale conferir quais contratos pagam no mês seguinte e decidir se o comparativo passa para competência.</t>
         </is>
       </c>
-      <c r="E16" s="65" t="inlineStr">
+      <c r="E17" s="62" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="67" t="inlineStr">
+      <c r="F17" s="67" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>
@@ -6304,60 +7124,60 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="69" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="70" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="69" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="70" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="69" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="70" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="69" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="70" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="69" t="inlineStr">
+      <c r="A9" s="70" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="70" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -6372,60 +7192,60 @@
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="69" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="70" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="69" t="inlineStr">
+      <c r="A13" s="70" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="70" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="69" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="70" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="69" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="70" t="inlineStr">
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="69" t="inlineStr">
+      <c r="A16" s="70" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="70" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -6440,36 +7260,36 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="69" t="inlineStr">
+      <c r="A19" s="70" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="70" t="inlineStr">
+      <c r="B19" s="71" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="69" t="inlineStr">
+      <c r="A20" s="70" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="70" t="inlineStr">
+      <c r="B20" s="71" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="69" t="inlineStr">
+      <c r="A21" s="70" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="70" t="inlineStr">
+      <c r="B21" s="71" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -15,10 +15,14 @@
     <sheet name="Por Plano de Contas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Pendências" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Contas Pagas (resumo)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Contas Pagas (detalhe)" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +34,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,10 +142,15 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -213,6 +222,11 @@
         <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -240,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -396,9 +410,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1820,6 +1851,4054 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H105"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONTAS PAGAS — DETALHE  (TI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Um lançamento por linha, como veio do financeiro. Use o filtro do cabeçalho para conferir credor, empreendimento ou mês.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>Mês</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Data de Pagamento</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>Credor</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="F4" s="46" t="inlineStr">
+        <is>
+          <t>Empreendimento</t>
+        </is>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>Centro de Custo</t>
+        </is>
+      </c>
+      <c r="H4" s="46" t="inlineStr">
+        <is>
+          <t>Valor Líquido</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B5" s="79" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D5" s="79" t="inlineStr">
+        <is>
+          <t>FAT.11.25</t>
+        </is>
+      </c>
+      <c r="E5" s="79" t="inlineStr">
+        <is>
+          <t>95941/1</t>
+        </is>
+      </c>
+      <c r="F5" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G5" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H5" s="80" t="n">
+        <v>407.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B6" s="79" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D6" s="79" t="inlineStr">
+        <is>
+          <t>FAT.01.26</t>
+        </is>
+      </c>
+      <c r="E6" s="79" t="inlineStr">
+        <is>
+          <t>97478/1</t>
+        </is>
+      </c>
+      <c r="F6" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G6" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H6" s="80" t="n">
+        <v>390.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B7" s="79" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D7" s="79" t="inlineStr">
+        <is>
+          <t>FAT.184180933</t>
+        </is>
+      </c>
+      <c r="E7" s="79" t="inlineStr">
+        <is>
+          <t>97480/1</t>
+        </is>
+      </c>
+      <c r="F7" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G7" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H7" s="80" t="n">
+        <v>123.76</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B8" s="79" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="79" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="D8" s="79" t="inlineStr">
+        <is>
+          <t>NFS.347106</t>
+        </is>
+      </c>
+      <c r="E8" s="79" t="inlineStr">
+        <is>
+          <t>96534/1</t>
+        </is>
+      </c>
+      <c r="F8" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G8" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H8" s="80" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B9" s="79" t="inlineStr">
+        <is>
+          <t>19/01/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="79" t="inlineStr">
+        <is>
+          <t>J H ALVES - MONITOR REMOTO</t>
+        </is>
+      </c>
+      <c r="D9" s="79" t="inlineStr">
+        <is>
+          <t>NFS.70</t>
+        </is>
+      </c>
+      <c r="E9" s="79" t="inlineStr">
+        <is>
+          <t>96602/1</t>
+        </is>
+      </c>
+      <c r="F9" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G9" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H9" s="80" t="n">
+        <v>4311.56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="79" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="D10" s="79" t="inlineStr">
+        <is>
+          <t>AV.LIC EMAILS 01.25</t>
+        </is>
+      </c>
+      <c r="E10" s="79" t="inlineStr">
+        <is>
+          <t>96014/1</t>
+        </is>
+      </c>
+      <c r="F10" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G10" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H10" s="80" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>25/01/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="79" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="D11" s="79" t="inlineStr">
+        <is>
+          <t>BOL.13.01</t>
+        </is>
+      </c>
+      <c r="E11" s="79" t="inlineStr">
+        <is>
+          <t>96623/1</t>
+        </is>
+      </c>
+      <c r="F11" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G11" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H11" s="80" t="n">
+        <v>918.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="79" t="inlineStr">
+        <is>
+          <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="D12" s="79" t="inlineStr">
+        <is>
+          <t>FAT.2682</t>
+        </is>
+      </c>
+      <c r="E12" s="79" t="inlineStr">
+        <is>
+          <t>96458/1</t>
+        </is>
+      </c>
+      <c r="F12" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G12" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H12" s="80" t="n">
+        <v>723.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B13" s="79" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="79" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D13" s="79" t="inlineStr">
+        <is>
+          <t>FAT.2011241340</t>
+        </is>
+      </c>
+      <c r="E13" s="79" t="inlineStr">
+        <is>
+          <t>96088/1</t>
+        </is>
+      </c>
+      <c r="F13" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G13" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H13" s="80" t="n">
+        <v>51.63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="79" t="inlineStr">
+        <is>
+          <t>TIM S A</t>
+        </is>
+      </c>
+      <c r="D14" s="79" t="inlineStr">
+        <is>
+          <t>FAT.5664047504</t>
+        </is>
+      </c>
+      <c r="E14" s="79" t="inlineStr">
+        <is>
+          <t>96789/1</t>
+        </is>
+      </c>
+      <c r="F14" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G14" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H14" s="80" t="n">
+        <v>331.42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D15" s="79" t="inlineStr">
+        <is>
+          <t>CX.16.01.26</t>
+        </is>
+      </c>
+      <c r="E15" s="79" t="inlineStr">
+        <is>
+          <t>97067/1</t>
+        </is>
+      </c>
+      <c r="F15" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G15" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H15" s="80" t="n">
+        <v>39.84</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D16" s="79" t="inlineStr">
+        <is>
+          <t>SAL.Sal_122025</t>
+        </is>
+      </c>
+      <c r="E16" s="79" t="inlineStr">
+        <is>
+          <t>96252/1</t>
+        </is>
+      </c>
+      <c r="F16" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G16" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H16" s="80" t="n">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B17" s="79" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D17" s="79" t="inlineStr">
+        <is>
+          <t>SAL.VALE_ 012026</t>
+        </is>
+      </c>
+      <c r="E17" s="79" t="inlineStr">
+        <is>
+          <t>97269/1</t>
+        </is>
+      </c>
+      <c r="F17" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G17" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H17" s="80" t="n">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="79" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="79" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="D18" s="79" t="inlineStr">
+        <is>
+          <t>BOL.1</t>
+        </is>
+      </c>
+      <c r="E18" s="79" t="inlineStr">
+        <is>
+          <t>97204/1</t>
+        </is>
+      </c>
+      <c r="F18" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G18" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H18" s="80" t="n">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="79" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="D19" s="79" t="inlineStr">
+        <is>
+          <t>AV.04.02.26</t>
+        </is>
+      </c>
+      <c r="E19" s="79" t="inlineStr">
+        <is>
+          <t>98500/1</t>
+        </is>
+      </c>
+      <c r="F19" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G19" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H19" s="80" t="n">
+        <v>26.67</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B20" s="79" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="79" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="D20" s="79" t="inlineStr">
+        <is>
+          <t>AV.12.02.26 LCW</t>
+        </is>
+      </c>
+      <c r="E20" s="79" t="inlineStr">
+        <is>
+          <t>99336/1</t>
+        </is>
+      </c>
+      <c r="F20" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G20" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H20" s="80" t="n">
+        <v>72.58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B21" s="79" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="79" t="inlineStr">
+        <is>
+          <t>OPENAI BRAZIL LIMITADA</t>
+        </is>
+      </c>
+      <c r="D21" s="79" t="inlineStr">
+        <is>
+          <t>AV.CHATGPT JUR 2026</t>
+        </is>
+      </c>
+      <c r="E21" s="79" t="inlineStr">
+        <is>
+          <t>95104/2</t>
+        </is>
+      </c>
+      <c r="F21" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G21" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H21" s="80" t="n">
+        <v>234.46</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B22" s="79" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="79" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D22" s="79" t="inlineStr">
+        <is>
+          <t>FAT.3575377</t>
+        </is>
+      </c>
+      <c r="E22" s="79" t="inlineStr">
+        <is>
+          <t>100172/1</t>
+        </is>
+      </c>
+      <c r="F22" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G22" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H22" s="80" t="n">
+        <v>52.32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B23" s="79" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="79" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D23" s="79" t="inlineStr">
+        <is>
+          <t>FAT.5290953</t>
+        </is>
+      </c>
+      <c r="E23" s="79" t="inlineStr">
+        <is>
+          <t>100173/1</t>
+        </is>
+      </c>
+      <c r="F23" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G23" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H23" s="80" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B24" s="79" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="79" t="inlineStr">
+        <is>
+          <t>TIM S A</t>
+        </is>
+      </c>
+      <c r="D24" s="79" t="inlineStr">
+        <is>
+          <t>BOL.141</t>
+        </is>
+      </c>
+      <c r="E24" s="79" t="inlineStr">
+        <is>
+          <t>99947/1</t>
+        </is>
+      </c>
+      <c r="F24" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G24" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H24" s="80" t="n">
+        <v>338.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B25" s="79" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="79" t="inlineStr">
+        <is>
+          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
+        </is>
+      </c>
+      <c r="D25" s="79" t="inlineStr">
+        <is>
+          <t>BOL.26449</t>
+        </is>
+      </c>
+      <c r="E25" s="79" t="inlineStr">
+        <is>
+          <t>99484/1</t>
+        </is>
+      </c>
+      <c r="F25" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G25" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H25" s="80" t="n">
+        <v>137.94</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B26" s="79" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="79" t="inlineStr">
+        <is>
+          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
+        </is>
+      </c>
+      <c r="D26" s="79" t="inlineStr">
+        <is>
+          <t>BOL.27256</t>
+        </is>
+      </c>
+      <c r="E26" s="79" t="inlineStr">
+        <is>
+          <t>99486/1</t>
+        </is>
+      </c>
+      <c r="F26" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G26" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H26" s="80" t="n">
+        <v>137.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B27" s="79" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D27" s="79" t="inlineStr">
+        <is>
+          <t>SAL.SAL JANEIRO 2026</t>
+        </is>
+      </c>
+      <c r="E27" s="79" t="inlineStr">
+        <is>
+          <t>98811/1</t>
+        </is>
+      </c>
+      <c r="F27" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G27" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H27" s="80" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B28" s="79" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D28" s="79" t="inlineStr">
+        <is>
+          <t>SAL.VALE FEVEREIRO 26</t>
+        </is>
+      </c>
+      <c r="E28" s="79" t="inlineStr">
+        <is>
+          <t>99890/1</t>
+        </is>
+      </c>
+      <c r="F28" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G28" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H28" s="80" t="n">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B29" s="79" t="inlineStr">
+        <is>
+          <t>2026-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="C29" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D29" s="79" t="inlineStr">
+        <is>
+          <t>FGTS/INSS</t>
+        </is>
+      </c>
+      <c r="E29" s="79" t="inlineStr">
+        <is>
+          <t>113754/2</t>
+        </is>
+      </c>
+      <c r="F29" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G29" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H29" s="80" t="n">
+        <v>207.04</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B30" s="79" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C30" s="79" t="inlineStr">
+        <is>
+          <t>Vale Alimentação Vinicius</t>
+        </is>
+      </c>
+      <c r="D30" s="79" t="inlineStr"/>
+      <c r="E30" s="79" t="inlineStr"/>
+      <c r="F30" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G30" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H30" s="80" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="79" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="B31" s="79" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="79" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="D31" s="79" t="inlineStr">
+        <is>
+          <t>NFS.1430</t>
+        </is>
+      </c>
+      <c r="E31" s="79" t="inlineStr">
+        <is>
+          <t>99956/1</t>
+        </is>
+      </c>
+      <c r="F31" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G31" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H31" s="80" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B32" s="79" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D32" s="79" t="inlineStr">
+        <is>
+          <t>FAT.5042829</t>
+        </is>
+      </c>
+      <c r="E32" s="79" t="inlineStr">
+        <is>
+          <t>100503/1</t>
+        </is>
+      </c>
+      <c r="F32" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G32" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H32" s="80" t="n">
+        <v>87.69</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B33" s="79" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="C33" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D33" s="79" t="inlineStr">
+        <is>
+          <t>FAT.5042827</t>
+        </is>
+      </c>
+      <c r="E33" s="79" t="inlineStr">
+        <is>
+          <t>100504/1</t>
+        </is>
+      </c>
+      <c r="F33" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G33" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H33" s="80" t="n">
+        <v>382.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B34" s="79" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D34" s="79" t="inlineStr">
+        <is>
+          <t>FAT.8910508</t>
+        </is>
+      </c>
+      <c r="E34" s="79" t="inlineStr">
+        <is>
+          <t>102706/1</t>
+        </is>
+      </c>
+      <c r="F34" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G34" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H34" s="80" t="n">
+        <v>429.49</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B35" s="79" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C35" s="79" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="D35" s="79" t="inlineStr">
+        <is>
+          <t>NFS.351653</t>
+        </is>
+      </c>
+      <c r="E35" s="79" t="inlineStr">
+        <is>
+          <t>100083/1</t>
+        </is>
+      </c>
+      <c r="F35" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G35" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H35" s="80" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B36" s="79" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="79" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="D36" s="79" t="inlineStr">
+        <is>
+          <t>NFS.359396</t>
+        </is>
+      </c>
+      <c r="E36" s="79" t="inlineStr">
+        <is>
+          <t>102608/1</t>
+        </is>
+      </c>
+      <c r="F36" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G36" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H36" s="80" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B37" s="79" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="79" t="inlineStr">
+        <is>
+          <t>OPENAI BRAZIL LIMITADA</t>
+        </is>
+      </c>
+      <c r="D37" s="79" t="inlineStr">
+        <is>
+          <t>AV.CHATGPT JUR 2026</t>
+        </is>
+      </c>
+      <c r="E37" s="79" t="inlineStr">
+        <is>
+          <t>95104/3</t>
+        </is>
+      </c>
+      <c r="F37" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G37" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H37" s="80" t="n">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B38" s="79" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C38" s="79" t="inlineStr">
+        <is>
+          <t>OPENAI BRAZIL LIMITADA</t>
+        </is>
+      </c>
+      <c r="D38" s="79" t="inlineStr">
+        <is>
+          <t>AV.CHATGPT JUR 2026</t>
+        </is>
+      </c>
+      <c r="E38" s="79" t="inlineStr">
+        <is>
+          <t>95104/4</t>
+        </is>
+      </c>
+      <c r="F38" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G38" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H38" s="80" t="n">
+        <v>210.38</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B39" s="79" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="C39" s="79" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D39" s="79" t="inlineStr">
+        <is>
+          <t>FAT.2024588614</t>
+        </is>
+      </c>
+      <c r="E39" s="79" t="inlineStr">
+        <is>
+          <t>102316/1</t>
+        </is>
+      </c>
+      <c r="F39" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G39" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H39" s="80" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B40" s="79" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="C40" s="79" t="inlineStr">
+        <is>
+          <t>TIM S A</t>
+        </is>
+      </c>
+      <c r="D40" s="79" t="inlineStr">
+        <is>
+          <t>BOL.5708173302</t>
+        </is>
+      </c>
+      <c r="E40" s="79" t="inlineStr">
+        <is>
+          <t>102057/1</t>
+        </is>
+      </c>
+      <c r="F40" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G40" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H40" s="80" t="n">
+        <v>284.63</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B41" s="79" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="C41" s="79" t="inlineStr">
+        <is>
+          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
+        </is>
+      </c>
+      <c r="D41" s="79" t="inlineStr">
+        <is>
+          <t>BOL.28049</t>
+        </is>
+      </c>
+      <c r="E41" s="79" t="inlineStr">
+        <is>
+          <t>100887/1</t>
+        </is>
+      </c>
+      <c r="F41" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G41" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H41" s="80" t="n">
+        <v>137.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B42" s="79" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D42" s="79" t="inlineStr">
+        <is>
+          <t>SAL.SAL FEVEREIRO 26</t>
+        </is>
+      </c>
+      <c r="E42" s="79" t="inlineStr">
+        <is>
+          <t>101276/1</t>
+        </is>
+      </c>
+      <c r="F42" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G42" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H42" s="80" t="n">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B43" s="79" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="C43" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D43" s="79" t="inlineStr">
+        <is>
+          <t>SAL.VALE 032026</t>
+        </is>
+      </c>
+      <c r="E43" s="79" t="inlineStr">
+        <is>
+          <t>102295/1</t>
+        </is>
+      </c>
+      <c r="F43" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G43" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H43" s="80" t="n">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B44" s="79" t="inlineStr">
+        <is>
+          <t>2026-03-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="C44" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D44" s="79" t="inlineStr">
+        <is>
+          <t>FGTS/INSS</t>
+        </is>
+      </c>
+      <c r="E44" s="79" t="inlineStr">
+        <is>
+          <t>113754/3</t>
+        </is>
+      </c>
+      <c r="F44" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G44" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H44" s="80" t="n">
+        <v>207.04</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B45" s="79" t="inlineStr">
+        <is>
+          <t>2026-03-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="79" t="inlineStr">
+        <is>
+          <t>Vale Alimentação Vinicius</t>
+        </is>
+      </c>
+      <c r="D45" s="79" t="inlineStr"/>
+      <c r="E45" s="79" t="inlineStr"/>
+      <c r="F45" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G45" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H45" s="80" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B46" s="79" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="79" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="D46" s="79" t="inlineStr">
+        <is>
+          <t>NFS.1500</t>
+        </is>
+      </c>
+      <c r="E46" s="79" t="inlineStr">
+        <is>
+          <t>102432/1</t>
+        </is>
+      </c>
+      <c r="F46" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G46" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H46" s="80" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="79" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="B47" s="79" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="79" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="D47" s="79" t="inlineStr">
+        <is>
+          <t>NFS.1534</t>
+        </is>
+      </c>
+      <c r="E47" s="79" t="inlineStr">
+        <is>
+          <t>102434/1</t>
+        </is>
+      </c>
+      <c r="F47" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G47" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H47" s="80" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B48" s="79" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D48" s="79" t="inlineStr">
+        <is>
+          <t>FAT.8910315</t>
+        </is>
+      </c>
+      <c r="E48" s="79" t="inlineStr">
+        <is>
+          <t>105607/1</t>
+        </is>
+      </c>
+      <c r="F48" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G48" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H48" s="80" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B49" s="79" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D49" s="79" t="inlineStr">
+        <is>
+          <t>FAT.13443658</t>
+        </is>
+      </c>
+      <c r="E49" s="79" t="inlineStr">
+        <is>
+          <t>105676/1</t>
+        </is>
+      </c>
+      <c r="F49" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G49" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H49" s="80" t="n">
+        <v>557.63</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B50" s="79" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D50" s="79" t="inlineStr">
+        <is>
+          <t>FAT.13443664</t>
+        </is>
+      </c>
+      <c r="E50" s="79" t="inlineStr">
+        <is>
+          <t>105677/1</t>
+        </is>
+      </c>
+      <c r="F50" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G50" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H50" s="80" t="n">
+        <v>132.09</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B51" s="79" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C51" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D51" s="79" t="inlineStr">
+        <is>
+          <t>FAT.13443112</t>
+        </is>
+      </c>
+      <c r="E51" s="79" t="inlineStr">
+        <is>
+          <t>105792/1</t>
+        </is>
+      </c>
+      <c r="F51" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G51" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H51" s="80" t="n">
+        <v>20.23</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B52" s="79" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C52" s="79" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="D52" s="79" t="inlineStr">
+        <is>
+          <t>NFS.363799</t>
+        </is>
+      </c>
+      <c r="E52" s="79" t="inlineStr">
+        <is>
+          <t>104634/1</t>
+        </is>
+      </c>
+      <c r="F52" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G52" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H52" s="80" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B53" s="79" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="79" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="D53" s="79" t="inlineStr">
+        <is>
+          <t>BOL.04.26</t>
+        </is>
+      </c>
+      <c r="E53" s="79" t="inlineStr">
+        <is>
+          <t>104820/1</t>
+        </is>
+      </c>
+      <c r="F53" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G53" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H53" s="80" t="n">
+        <v>1024.76</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B54" s="79" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C54" s="79" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="D54" s="79" t="inlineStr">
+        <is>
+          <t>BOL.LOCAWEB 29.04.26</t>
+        </is>
+      </c>
+      <c r="E54" s="79" t="inlineStr">
+        <is>
+          <t>106325/1</t>
+        </is>
+      </c>
+      <c r="F54" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G54" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H54" s="80" t="n">
+        <v>21.76</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B55" s="79" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C55" s="79" t="inlineStr">
+        <is>
+          <t>OPENAI BRAZIL LIMITADA</t>
+        </is>
+      </c>
+      <c r="D55" s="79" t="inlineStr">
+        <is>
+          <t>FAT.CHATGPT 3 LIC</t>
+        </is>
+      </c>
+      <c r="E55" s="79" t="inlineStr">
+        <is>
+          <t>102137/1</t>
+        </is>
+      </c>
+      <c r="F55" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G55" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H55" s="80" t="n">
+        <v>5393.88</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B56" s="79" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C56" s="79" t="inlineStr">
+        <is>
+          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
+        </is>
+      </c>
+      <c r="D56" s="79" t="inlineStr">
+        <is>
+          <t>BOL.28855</t>
+        </is>
+      </c>
+      <c r="E56" s="79" t="inlineStr">
+        <is>
+          <t>103694/1</t>
+        </is>
+      </c>
+      <c r="F56" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G56" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H56" s="80" t="n">
+        <v>137.9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B57" s="79" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C57" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D57" s="79" t="inlineStr">
+        <is>
+          <t>SAL.SAL 032026</t>
+        </is>
+      </c>
+      <c r="E57" s="79" t="inlineStr">
+        <is>
+          <t>103924/1</t>
+        </is>
+      </c>
+      <c r="F57" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G57" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H57" s="80" t="n">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B58" s="79" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C58" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D58" s="79" t="inlineStr">
+        <is>
+          <t>SAL.vale 042026</t>
+        </is>
+      </c>
+      <c r="E58" s="79" t="inlineStr">
+        <is>
+          <t>105055/1</t>
+        </is>
+      </c>
+      <c r="F58" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G58" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H58" s="80" t="n">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B59" s="79" t="inlineStr">
+        <is>
+          <t>2026-04-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="C59" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D59" s="79" t="inlineStr">
+        <is>
+          <t>FGTS/INSS</t>
+        </is>
+      </c>
+      <c r="E59" s="79" t="inlineStr">
+        <is>
+          <t>113754/4</t>
+        </is>
+      </c>
+      <c r="F59" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G59" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H59" s="80" t="n">
+        <v>207.04</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B60" s="79" t="inlineStr">
+        <is>
+          <t>2026-04-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C60" s="79" t="inlineStr">
+        <is>
+          <t>Vale Alimentação Vinicius</t>
+        </is>
+      </c>
+      <c r="D60" s="79" t="inlineStr"/>
+      <c r="E60" s="79" t="inlineStr"/>
+      <c r="F60" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G60" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H60" s="80" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="79" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="B61" s="79" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="C61" s="79" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="D61" s="79" t="inlineStr">
+        <is>
+          <t>NFS.1573</t>
+        </is>
+      </c>
+      <c r="E61" s="79" t="inlineStr">
+        <is>
+          <t>105411/1</t>
+        </is>
+      </c>
+      <c r="F61" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G61" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H61" s="80" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B62" s="79" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="C62" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D62" s="79" t="inlineStr">
+        <is>
+          <t>FAT.2ªvia Claro Abril</t>
+        </is>
+      </c>
+      <c r="E62" s="79" t="inlineStr">
+        <is>
+          <t>107340/1</t>
+        </is>
+      </c>
+      <c r="F62" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G62" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H62" s="80" t="n">
+        <v>182.32</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B63" s="79" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="C63" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D63" s="79" t="inlineStr">
+        <is>
+          <t>FAT.17483469</t>
+        </is>
+      </c>
+      <c r="E63" s="79" t="inlineStr">
+        <is>
+          <t>108218/1</t>
+        </is>
+      </c>
+      <c r="F63" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G63" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H63" s="80" t="n">
+        <v>629.98</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B64" s="79" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="C64" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D64" s="79" t="inlineStr">
+        <is>
+          <t>FAT.17483469</t>
+        </is>
+      </c>
+      <c r="E64" s="79" t="inlineStr">
+        <is>
+          <t>108218/2</t>
+        </is>
+      </c>
+      <c r="F64" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G64" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H64" s="80" t="n">
+        <v>18.86</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B65" s="79" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="C65" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D65" s="79" t="inlineStr">
+        <is>
+          <t>FAT.17483469</t>
+        </is>
+      </c>
+      <c r="E65" s="79" t="inlineStr">
+        <is>
+          <t>108218/3</t>
+        </is>
+      </c>
+      <c r="F65" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G65" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H65" s="80" t="n">
+        <v>133.95</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B66" s="79" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="C66" s="79" t="inlineStr">
+        <is>
+          <t>J H ALVES - MONITOR REMOTO</t>
+        </is>
+      </c>
+      <c r="D66" s="79" t="inlineStr">
+        <is>
+          <t>NFS.76</t>
+        </is>
+      </c>
+      <c r="E66" s="79" t="inlineStr">
+        <is>
+          <t>105987/1</t>
+        </is>
+      </c>
+      <c r="F66" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G66" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H66" s="80" t="n">
+        <v>3723.62</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B67" s="79" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="C67" s="79" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="D67" s="79" t="inlineStr">
+        <is>
+          <t>BOL.LOCAWEB 11.05.26</t>
+        </is>
+      </c>
+      <c r="E67" s="79" t="inlineStr">
+        <is>
+          <t>107254/1</t>
+        </is>
+      </c>
+      <c r="F67" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G67" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H67" s="80" t="n">
+        <v>74.81</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B68" s="79" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C68" s="79" t="inlineStr">
+        <is>
+          <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="D68" s="79" t="inlineStr">
+        <is>
+          <t>NFS.5744</t>
+        </is>
+      </c>
+      <c r="E68" s="79" t="inlineStr">
+        <is>
+          <t>106664/1</t>
+        </is>
+      </c>
+      <c r="F68" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G68" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H68" s="80" t="n">
+        <v>741.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B69" s="79" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="C69" s="79" t="inlineStr">
+        <is>
+          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
+        </is>
+      </c>
+      <c r="D69" s="79" t="inlineStr">
+        <is>
+          <t>BOL.29637</t>
+        </is>
+      </c>
+      <c r="E69" s="79" t="inlineStr">
+        <is>
+          <t>108040/1</t>
+        </is>
+      </c>
+      <c r="F69" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G69" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H69" s="80" t="n">
+        <v>137.92</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B70" s="79" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C70" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D70" s="79" t="inlineStr">
+        <is>
+          <t>SAL.sal 042026</t>
+        </is>
+      </c>
+      <c r="E70" s="79" t="inlineStr">
+        <is>
+          <t>106947/1</t>
+        </is>
+      </c>
+      <c r="F70" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G70" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H70" s="80" t="n">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B71" s="79" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="C71" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D71" s="79" t="inlineStr">
+        <is>
+          <t>SAL.vale 052026</t>
+        </is>
+      </c>
+      <c r="E71" s="79" t="inlineStr">
+        <is>
+          <t>108156/1</t>
+        </is>
+      </c>
+      <c r="F71" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G71" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H71" s="80" t="n">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B72" s="79" t="inlineStr">
+        <is>
+          <t>2026-05-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="C72" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D72" s="79" t="inlineStr">
+        <is>
+          <t>FGTS/INSS</t>
+        </is>
+      </c>
+      <c r="E72" s="79" t="inlineStr">
+        <is>
+          <t>113754/5</t>
+        </is>
+      </c>
+      <c r="F72" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G72" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H72" s="80" t="n">
+        <v>207.04</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B73" s="79" t="inlineStr">
+        <is>
+          <t>2026-05-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C73" s="79" t="inlineStr">
+        <is>
+          <t>Vale Alimentação Vinicius</t>
+        </is>
+      </c>
+      <c r="D73" s="79" t="inlineStr"/>
+      <c r="E73" s="79" t="inlineStr"/>
+      <c r="F73" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G73" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H73" s="80" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="79" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="B74" s="79" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="C74" s="79" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="D74" s="79" t="inlineStr">
+        <is>
+          <t>NFS.1631</t>
+        </is>
+      </c>
+      <c r="E74" s="79" t="inlineStr">
+        <is>
+          <t>107973/1</t>
+        </is>
+      </c>
+      <c r="F74" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G74" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H74" s="80" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B75" s="79" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C75" s="79" t="inlineStr">
+        <is>
+          <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
+        </is>
+      </c>
+      <c r="D75" s="79" t="inlineStr">
+        <is>
+          <t>AV.1015392</t>
+        </is>
+      </c>
+      <c r="E75" s="79" t="inlineStr">
+        <is>
+          <t>108925/1</t>
+        </is>
+      </c>
+      <c r="F75" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G75" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H75" s="80" t="n">
+        <v>183.6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B76" s="79" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C76" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D76" s="79" t="inlineStr">
+        <is>
+          <t>FAT.21882309</t>
+        </is>
+      </c>
+      <c r="E76" s="79" t="inlineStr">
+        <is>
+          <t>111124/1</t>
+        </is>
+      </c>
+      <c r="F76" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G76" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H76" s="80" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B77" s="79" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D77" s="79" t="inlineStr">
+        <is>
+          <t>FAT.21882309</t>
+        </is>
+      </c>
+      <c r="E77" s="79" t="inlineStr">
+        <is>
+          <t>111124/3</t>
+        </is>
+      </c>
+      <c r="F77" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G77" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H77" s="80" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B78" s="79" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="79" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="D78" s="79" t="inlineStr">
+        <is>
+          <t>NFS.373725</t>
+        </is>
+      </c>
+      <c r="E78" s="79" t="inlineStr">
+        <is>
+          <t>110785/1</t>
+        </is>
+      </c>
+      <c r="F78" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G78" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H78" s="80" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B79" s="79" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="79" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="D79" s="79" t="inlineStr">
+        <is>
+          <t>NFS.0036884701</t>
+        </is>
+      </c>
+      <c r="E79" s="79" t="inlineStr">
+        <is>
+          <t>109295/1</t>
+        </is>
+      </c>
+      <c r="F79" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G79" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H79" s="80" t="n">
+        <v>84.81999999999999</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B80" s="79" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="79" t="inlineStr">
+        <is>
+          <t>J H ALVES - MONITOR REMOTO</t>
+        </is>
+      </c>
+      <c r="D80" s="79" t="inlineStr">
+        <is>
+          <t>NFS.78</t>
+        </is>
+      </c>
+      <c r="E80" s="79" t="inlineStr">
+        <is>
+          <t>108317/1</t>
+        </is>
+      </c>
+      <c r="F80" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G80" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H80" s="80" t="n">
+        <v>6173.37</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B81" s="79" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="79" t="inlineStr">
+        <is>
+          <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="D81" s="79" t="inlineStr">
+        <is>
+          <t>NFS.5832</t>
+        </is>
+      </c>
+      <c r="E81" s="79" t="inlineStr">
+        <is>
+          <t>109227/1</t>
+        </is>
+      </c>
+      <c r="F81" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G81" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H81" s="80" t="n">
+        <v>740.38</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B82" s="79" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="79" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D82" s="79" t="inlineStr">
+        <is>
+          <t>FAT.Vivo 04 2026</t>
+        </is>
+      </c>
+      <c r="E82" s="79" t="inlineStr">
+        <is>
+          <t>110752/1</t>
+        </is>
+      </c>
+      <c r="F82" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G82" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H82" s="80" t="n">
+        <v>184.86</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B83" s="79" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="79" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D83" s="79" t="inlineStr">
+        <is>
+          <t>FAT.Vivo 05 2026</t>
+        </is>
+      </c>
+      <c r="E83" s="79" t="inlineStr">
+        <is>
+          <t>110753/1</t>
+        </is>
+      </c>
+      <c r="F83" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G83" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H83" s="80" t="n">
+        <v>184.86</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B84" s="79" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="79" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D84" s="79" t="inlineStr">
+        <is>
+          <t>FAT.Vivo 06 2026</t>
+        </is>
+      </c>
+      <c r="E84" s="79" t="inlineStr">
+        <is>
+          <t>110754/1</t>
+        </is>
+      </c>
+      <c r="F84" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G84" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H84" s="80" t="n">
+        <v>184.86</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B85" s="79" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="79" t="inlineStr">
+        <is>
+          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
+        </is>
+      </c>
+      <c r="D85" s="79" t="inlineStr">
+        <is>
+          <t>BOL.1017717992</t>
+        </is>
+      </c>
+      <c r="E85" s="79" t="inlineStr">
+        <is>
+          <t>109298/1</t>
+        </is>
+      </c>
+      <c r="F85" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G85" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H85" s="80" t="n">
+        <v>137.93</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B86" s="79" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D86" s="79" t="inlineStr">
+        <is>
+          <t>CX.27.05.26</t>
+        </is>
+      </c>
+      <c r="E86" s="79" t="inlineStr">
+        <is>
+          <t>108827/1</t>
+        </is>
+      </c>
+      <c r="F86" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G86" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H86" s="80" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B87" s="79" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D87" s="79" t="inlineStr">
+        <is>
+          <t>SAL.1_ Ferias 1 VIn D 26</t>
+        </is>
+      </c>
+      <c r="E87" s="79" t="inlineStr">
+        <is>
+          <t>107780/1</t>
+        </is>
+      </c>
+      <c r="F87" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G87" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H87" s="80" t="n">
+        <v>1101.12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B88" s="79" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D88" s="79" t="inlineStr">
+        <is>
+          <t>SAL.sal 052026</t>
+        </is>
+      </c>
+      <c r="E88" s="79" t="inlineStr">
+        <is>
+          <t>109482/1</t>
+        </is>
+      </c>
+      <c r="F88" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G88" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H88" s="80" t="n">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B89" s="79" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D89" s="79" t="inlineStr">
+        <is>
+          <t>SAL.SALARIO06VINI</t>
+        </is>
+      </c>
+      <c r="E89" s="79" t="inlineStr">
+        <is>
+          <t>110700/1</t>
+        </is>
+      </c>
+      <c r="F89" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G89" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H89" s="80" t="n">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B90" s="79" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="C90" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D90" s="79" t="inlineStr">
+        <is>
+          <t>FGTS/INSS</t>
+        </is>
+      </c>
+      <c r="E90" s="79" t="inlineStr">
+        <is>
+          <t>113754/6</t>
+        </is>
+      </c>
+      <c r="F90" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G90" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H90" s="80" t="n">
+        <v>207.04</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B91" s="79" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C91" s="79" t="inlineStr">
+        <is>
+          <t>Vale Alimentação Vinicius</t>
+        </is>
+      </c>
+      <c r="D91" s="79" t="inlineStr"/>
+      <c r="E91" s="79" t="inlineStr"/>
+      <c r="F91" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G91" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H91" s="80" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="79" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="B92" s="79" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="79" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="D92" s="79" t="inlineStr">
+        <is>
+          <t>NFS.33</t>
+        </is>
+      </c>
+      <c r="E92" s="79" t="inlineStr">
+        <is>
+          <t>110902/1</t>
+        </is>
+      </c>
+      <c r="F92" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G92" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H92" s="80" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B93" s="79" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D93" s="79" t="inlineStr">
+        <is>
+          <t>FAT.Claro 07.26</t>
+        </is>
+      </c>
+      <c r="E93" s="79" t="inlineStr">
+        <is>
+          <t>113575/1</t>
+        </is>
+      </c>
+      <c r="F93" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G93" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H93" s="80" t="n">
+        <v>20.39</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B94" s="79" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D94" s="79" t="inlineStr">
+        <is>
+          <t>FAT.Claro 07.26</t>
+        </is>
+      </c>
+      <c r="E94" s="79" t="inlineStr">
+        <is>
+          <t>113575/2</t>
+        </is>
+      </c>
+      <c r="F94" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G94" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H94" s="80" t="n">
+        <v>133.73</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B95" s="79" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="79" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="D95" s="79" t="inlineStr">
+        <is>
+          <t>FAT.Claro 07.26</t>
+        </is>
+      </c>
+      <c r="E95" s="79" t="inlineStr">
+        <is>
+          <t>113575/3</t>
+        </is>
+      </c>
+      <c r="F95" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G95" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H95" s="80" t="n">
+        <v>825.28</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B96" s="79" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="79" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="D96" s="79" t="inlineStr">
+        <is>
+          <t>NFS.377682</t>
+        </is>
+      </c>
+      <c r="E96" s="79" t="inlineStr">
+        <is>
+          <t>114092/1</t>
+        </is>
+      </c>
+      <c r="F96" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G96" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H96" s="80" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B97" s="79" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="79" t="inlineStr">
+        <is>
+          <t>J H ALVES - MONITOR REMOTO</t>
+        </is>
+      </c>
+      <c r="D97" s="79" t="inlineStr">
+        <is>
+          <t>NFS.3</t>
+        </is>
+      </c>
+      <c r="E97" s="79" t="inlineStr">
+        <is>
+          <t>111371/1</t>
+        </is>
+      </c>
+      <c r="F97" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G97" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H97" s="80" t="n">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B98" s="79" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="79" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="D98" s="79" t="inlineStr">
+        <is>
+          <t>BOL.LOCAWEB 07.26</t>
+        </is>
+      </c>
+      <c r="E98" s="79" t="inlineStr">
+        <is>
+          <t>113049/1</t>
+        </is>
+      </c>
+      <c r="F98" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G98" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H98" s="80" t="n">
+        <v>1151.26</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B99" s="79" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="79" t="inlineStr">
+        <is>
+          <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="D99" s="79" t="inlineStr">
+        <is>
+          <t>NFS.66</t>
+        </is>
+      </c>
+      <c r="E99" s="79" t="inlineStr">
+        <is>
+          <t>112107/1</t>
+        </is>
+      </c>
+      <c r="F99" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G99" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H99" s="80" t="n">
+        <v>1037.38</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B100" s="79" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D100" s="79" t="inlineStr">
+        <is>
+          <t>SAL.sal 0626</t>
+        </is>
+      </c>
+      <c r="E100" s="79" t="inlineStr">
+        <is>
+          <t>112402/1</t>
+        </is>
+      </c>
+      <c r="F100" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G100" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H100" s="80" t="n">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B101" s="79" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D101" s="79" t="inlineStr">
+        <is>
+          <t>FGTS/INSS</t>
+        </is>
+      </c>
+      <c r="E101" s="79" t="inlineStr">
+        <is>
+          <t>113754/1</t>
+        </is>
+      </c>
+      <c r="F101" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G101" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H101" s="80" t="n">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B102" s="79" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="79" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="D102" s="79" t="inlineStr">
+        <is>
+          <t>FGTS/INSS</t>
+        </is>
+      </c>
+      <c r="E102" s="79" t="inlineStr">
+        <is>
+          <t>113754/7</t>
+        </is>
+      </c>
+      <c r="F102" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G102" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H102" s="80" t="n">
+        <v>207.04</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B103" s="79" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C103" s="79" t="inlineStr">
+        <is>
+          <t>Vale Alimentação Vinicius</t>
+        </is>
+      </c>
+      <c r="D103" s="79" t="inlineStr"/>
+      <c r="E103" s="79" t="inlineStr"/>
+      <c r="F103" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G103" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H103" s="80" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="79" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="B104" s="79" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="79" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="D104" s="79" t="inlineStr">
+        <is>
+          <t>NFS.84</t>
+        </is>
+      </c>
+      <c r="E104" s="79" t="inlineStr">
+        <is>
+          <t>113583/1</t>
+        </is>
+      </c>
+      <c r="F104" s="79" t="inlineStr">
+        <is>
+          <t>Tetus</t>
+        </is>
+      </c>
+      <c r="G104" s="79" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="H104" s="80" t="n">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="G105" s="81" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="H105" s="82">
+        <f>SUM(H5:H104)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H104"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7318,4 +11397,625 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONTAS PAGAS — RESUMO POR CREDOR  (TI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Extrato do financeiro, centro de custo "T.I". ABA DE APOIO: o centro de custo destes itens ainda não foi decidido, então nada aqui entra no Planejado, no Realizado nem no Painel. A coluna final aponta o que provavelmente já está no orçamento — confira e remova as duplicidades à mão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>Credor</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Centro de Custo</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>Nº lanç.</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="F4" s="46" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="H4" s="46" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="I4" s="46" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="J4" s="46" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="K4" s="46" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>Já está no orçamento?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="56" t="inlineStr">
+        <is>
+          <t>J H ALVES - MONITOR REMOTO</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C5" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="54" t="n">
+        <v>4311.56</v>
+      </c>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n">
+        <v>3723.62</v>
+      </c>
+      <c r="I5" s="54" t="n">
+        <v>6173.37</v>
+      </c>
+      <c r="J5" s="54" t="n">
+        <v>6300</v>
+      </c>
+      <c r="K5" s="72" t="n">
+        <v>20508.55</v>
+      </c>
+      <c r="L5" s="73" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="74" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C6" s="75" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="76" t="n">
+        <v>2670.84</v>
+      </c>
+      <c r="E6" s="76" t="n">
+        <v>2986.04</v>
+      </c>
+      <c r="F6" s="76" t="n">
+        <v>2778.04</v>
+      </c>
+      <c r="G6" s="76" t="n">
+        <v>2751.04</v>
+      </c>
+      <c r="H6" s="76" t="n">
+        <v>2719.04</v>
+      </c>
+      <c r="I6" s="76" t="n">
+        <v>3633.16</v>
+      </c>
+      <c r="J6" s="76" t="n">
+        <v>2461.04</v>
+      </c>
+      <c r="K6" s="77" t="n">
+        <v>19999.2</v>
+      </c>
+      <c r="L6" s="78" t="inlineStr">
+        <is>
+          <t>TI-E01 Vinicius Di Franco</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="74" t="inlineStr">
+        <is>
+          <t>OPENAI BRAZIL LIMITADA</t>
+        </is>
+      </c>
+      <c r="B7" s="74" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C7" s="75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="76" t="n"/>
+      <c r="E7" s="76" t="n">
+        <v>234.46</v>
+      </c>
+      <c r="F7" s="76" t="n">
+        <v>321.76</v>
+      </c>
+      <c r="G7" s="76" t="n">
+        <v>5393.88</v>
+      </c>
+      <c r="H7" s="76" t="n"/>
+      <c r="I7" s="76" t="n"/>
+      <c r="J7" s="76" t="n"/>
+      <c r="K7" s="77" t="n">
+        <v>5950.1</v>
+      </c>
+      <c r="L7" s="78" t="inlineStr">
+        <is>
+          <t>TI-D11 GPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C8" s="53" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" s="54" t="n">
+        <v>922.1099999999999</v>
+      </c>
+      <c r="E8" s="54" t="n"/>
+      <c r="F8" s="54" t="n">
+        <v>899.5799999999999</v>
+      </c>
+      <c r="G8" s="54" t="n">
+        <v>721.9400000000001</v>
+      </c>
+      <c r="H8" s="54" t="n">
+        <v>965.1099999999999</v>
+      </c>
+      <c r="I8" s="54" t="n">
+        <v>740</v>
+      </c>
+      <c r="J8" s="54" t="n">
+        <v>979.4</v>
+      </c>
+      <c r="K8" s="72" t="n">
+        <v>5228.139999999999</v>
+      </c>
+      <c r="L8" s="73" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="54" t="n">
+        <v>924.2800000000001</v>
+      </c>
+      <c r="E9" s="54" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="F9" s="54" t="n"/>
+      <c r="G9" s="54" t="n">
+        <v>1046.52</v>
+      </c>
+      <c r="H9" s="54" t="n">
+        <v>74.81</v>
+      </c>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n">
+        <v>1151.26</v>
+      </c>
+      <c r="K9" s="72" t="n">
+        <v>3296.12</v>
+      </c>
+      <c r="L9" s="73" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="54" t="n">
+        <v>723.75</v>
+      </c>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="n">
+        <v>741.1</v>
+      </c>
+      <c r="I10" s="54" t="n">
+        <v>740.38</v>
+      </c>
+      <c r="J10" s="54" t="n">
+        <v>1037.38</v>
+      </c>
+      <c r="K10" s="72" t="n">
+        <v>3242.61</v>
+      </c>
+      <c r="L10" s="73" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="74" t="inlineStr">
+        <is>
+          <t>Vale Alimentação Vinicius</t>
+        </is>
+      </c>
+      <c r="B11" s="74" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C11" s="75" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="76" t="n"/>
+      <c r="E11" s="76" t="n">
+        <v>485</v>
+      </c>
+      <c r="F11" s="76" t="n">
+        <v>485</v>
+      </c>
+      <c r="G11" s="76" t="n">
+        <v>485</v>
+      </c>
+      <c r="H11" s="76" t="n">
+        <v>485</v>
+      </c>
+      <c r="I11" s="76" t="n">
+        <v>485</v>
+      </c>
+      <c r="J11" s="76" t="n">
+        <v>485</v>
+      </c>
+      <c r="K11" s="77" t="n">
+        <v>2910</v>
+      </c>
+      <c r="L11" s="78" t="inlineStr">
+        <is>
+          <t>TI-E01 Vinicius (benefício)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>TIM S A</t>
+        </is>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C12" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="54" t="n">
+        <v>331.42</v>
+      </c>
+      <c r="E12" s="54" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="F12" s="54" t="n">
+        <v>284.63</v>
+      </c>
+      <c r="G12" s="54" t="n"/>
+      <c r="H12" s="54" t="n"/>
+      <c r="I12" s="54" t="n"/>
+      <c r="J12" s="54" t="n"/>
+      <c r="K12" s="72" t="n">
+        <v>954.5500000000001</v>
+      </c>
+      <c r="L12" s="73" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
+        </is>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C13" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="54" t="n"/>
+      <c r="E13" s="54" t="n">
+        <v>275.84</v>
+      </c>
+      <c r="F13" s="54" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="G13" s="54" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="H13" s="54" t="n">
+        <v>137.92</v>
+      </c>
+      <c r="I13" s="54" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="J13" s="54" t="n"/>
+      <c r="K13" s="72" t="n">
+        <v>827.49</v>
+      </c>
+      <c r="L13" s="73" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C14" s="53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="54" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="E14" s="54" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="F14" s="54" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n">
+        <v>554.58</v>
+      </c>
+      <c r="J14" s="54" t="n"/>
+      <c r="K14" s="72" t="n">
+        <v>758.53</v>
+      </c>
+      <c r="L14" s="73" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="B15" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C15" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="54" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E15" s="54" t="n">
+        <v>75</v>
+      </c>
+      <c r="F15" s="54" t="n">
+        <v>225</v>
+      </c>
+      <c r="G15" s="54" t="n">
+        <v>75</v>
+      </c>
+      <c r="H15" s="54" t="n">
+        <v>75</v>
+      </c>
+      <c r="I15" s="54" t="n">
+        <v>75</v>
+      </c>
+      <c r="J15" s="54" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="K15" s="72" t="n">
+        <v>690</v>
+      </c>
+      <c r="L15" s="73" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C16" s="53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="54" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E16" s="54" t="n"/>
+      <c r="F16" s="54" t="n">
+        <v>159.2</v>
+      </c>
+      <c r="G16" s="54" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="H16" s="54" t="n"/>
+      <c r="I16" s="54" t="n">
+        <v>164.42</v>
+      </c>
+      <c r="J16" s="54" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="K16" s="72" t="n">
+        <v>562.42</v>
+      </c>
+      <c r="L16" s="73" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C17" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="54" t="n"/>
+      <c r="F17" s="54" t="n"/>
+      <c r="G17" s="54" t="n"/>
+      <c r="H17" s="54" t="n"/>
+      <c r="I17" s="54" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="72" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="L17" s="73" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="n"/>
+      <c r="C18" s="51" t="n"/>
+      <c r="D18" s="52">
+        <f>SUM(D5:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="52">
+        <f>SUM(E5:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="52">
+        <f>SUM(F5:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="52">
+        <f>SUM(G5:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="52">
+        <f>SUM(H5:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="52">
+        <f>SUM(I5:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="52">
+        <f>SUM(J5:J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="52">
+        <f>SUM(K5:K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="51" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:L17"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -150,7 +150,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -219,6 +219,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
@@ -254,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -401,10 +406,13 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -417,13 +425,13 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1927,3964 +1935,3964 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="79" t="inlineStr">
+      <c r="A5" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="79" t="inlineStr">
+      <c r="B5" s="80" t="inlineStr">
         <is>
           <t>09/01/2026</t>
         </is>
       </c>
-      <c r="C5" s="79" t="inlineStr">
+      <c r="C5" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D5" s="79" t="inlineStr">
+      <c r="D5" s="80" t="inlineStr">
         <is>
           <t>FAT.11.25</t>
         </is>
       </c>
-      <c r="E5" s="79" t="inlineStr">
+      <c r="E5" s="80" t="inlineStr">
         <is>
           <t>95941/1</t>
         </is>
       </c>
-      <c r="F5" s="79" t="inlineStr">
+      <c r="F5" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G5" s="79" t="inlineStr">
+      <c r="G5" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H5" s="80" t="n">
+      <c r="H5" s="81" t="n">
         <v>407.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="79" t="inlineStr">
+      <c r="A6" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B6" s="79" t="inlineStr">
+      <c r="B6" s="80" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C6" s="79" t="inlineStr">
+      <c r="C6" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
+      <c r="D6" s="80" t="inlineStr">
         <is>
           <t>FAT.01.26</t>
         </is>
       </c>
-      <c r="E6" s="79" t="inlineStr">
+      <c r="E6" s="80" t="inlineStr">
         <is>
           <t>97478/1</t>
         </is>
       </c>
-      <c r="F6" s="79" t="inlineStr">
+      <c r="F6" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G6" s="79" t="inlineStr">
+      <c r="G6" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H6" s="80" t="n">
+      <c r="H6" s="81" t="n">
         <v>390.95</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="79" t="inlineStr">
+      <c r="A7" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B7" s="79" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C7" s="79" t="inlineStr">
+      <c r="C7" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D7" s="79" t="inlineStr">
+      <c r="D7" s="80" t="inlineStr">
         <is>
           <t>FAT.184180933</t>
         </is>
       </c>
-      <c r="E7" s="79" t="inlineStr">
+      <c r="E7" s="80" t="inlineStr">
         <is>
           <t>97480/1</t>
         </is>
       </c>
-      <c r="F7" s="79" t="inlineStr">
+      <c r="F7" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G7" s="79" t="inlineStr">
+      <c r="G7" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H7" s="80" t="n">
+      <c r="H7" s="81" t="n">
         <v>123.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="79" t="inlineStr">
+      <c r="A8" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C8" s="79" t="inlineStr">
+      <c r="C8" s="80" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D8" s="79" t="inlineStr">
+      <c r="D8" s="80" t="inlineStr">
         <is>
           <t>NFS.347106</t>
         </is>
       </c>
-      <c r="E8" s="79" t="inlineStr">
+      <c r="E8" s="80" t="inlineStr">
         <is>
           <t>96534/1</t>
         </is>
       </c>
-      <c r="F8" s="79" t="inlineStr">
+      <c r="F8" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G8" s="79" t="inlineStr">
+      <c r="G8" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H8" s="80" t="n">
+      <c r="H8" s="81" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="79" t="inlineStr">
+      <c r="A9" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="C9" s="79" t="inlineStr">
+      <c r="C9" s="80" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D9" s="79" t="inlineStr">
+      <c r="D9" s="80" t="inlineStr">
         <is>
           <t>NFS.70</t>
         </is>
       </c>
-      <c r="E9" s="79" t="inlineStr">
+      <c r="E9" s="80" t="inlineStr">
         <is>
           <t>96602/1</t>
         </is>
       </c>
-      <c r="F9" s="79" t="inlineStr">
+      <c r="F9" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G9" s="79" t="inlineStr">
+      <c r="G9" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H9" s="80" t="n">
+      <c r="H9" s="81" t="n">
         <v>4311.56</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="79" t="inlineStr">
+      <c r="A10" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B10" s="79" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="C10" s="79" t="inlineStr">
+      <c r="C10" s="80" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D10" s="79" t="inlineStr">
+      <c r="D10" s="80" t="inlineStr">
         <is>
           <t>AV.LIC EMAILS 01.25</t>
         </is>
       </c>
-      <c r="E10" s="79" t="inlineStr">
+      <c r="E10" s="80" t="inlineStr">
         <is>
           <t>96014/1</t>
         </is>
       </c>
-      <c r="F10" s="79" t="inlineStr">
+      <c r="F10" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G10" s="79" t="inlineStr">
+      <c r="G10" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H10" s="80" t="n">
+      <c r="H10" s="81" t="n">
         <v>6.2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="79" t="inlineStr">
+      <c r="A11" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B11" s="79" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>25/01/2026</t>
         </is>
       </c>
-      <c r="C11" s="79" t="inlineStr">
+      <c r="C11" s="80" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D11" s="79" t="inlineStr">
+      <c r="D11" s="80" t="inlineStr">
         <is>
           <t>BOL.13.01</t>
         </is>
       </c>
-      <c r="E11" s="79" t="inlineStr">
+      <c r="E11" s="80" t="inlineStr">
         <is>
           <t>96623/1</t>
         </is>
       </c>
-      <c r="F11" s="79" t="inlineStr">
+      <c r="F11" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G11" s="79" t="inlineStr">
+      <c r="G11" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H11" s="80" t="n">
+      <c r="H11" s="81" t="n">
         <v>918.08</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="79" t="inlineStr">
+      <c r="A12" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C12" s="79" t="inlineStr">
+      <c r="C12" s="80" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D12" s="79" t="inlineStr">
+      <c r="D12" s="80" t="inlineStr">
         <is>
           <t>FAT.2682</t>
         </is>
       </c>
-      <c r="E12" s="79" t="inlineStr">
+      <c r="E12" s="80" t="inlineStr">
         <is>
           <t>96458/1</t>
         </is>
       </c>
-      <c r="F12" s="79" t="inlineStr">
+      <c r="F12" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G12" s="79" t="inlineStr">
+      <c r="G12" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H12" s="80" t="n">
+      <c r="H12" s="81" t="n">
         <v>723.75</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="79" t="inlineStr">
+      <c r="A13" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B13" s="79" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="C13" s="79" t="inlineStr">
+      <c r="C13" s="80" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D13" s="79" t="inlineStr">
+      <c r="D13" s="80" t="inlineStr">
         <is>
           <t>FAT.2011241340</t>
         </is>
       </c>
-      <c r="E13" s="79" t="inlineStr">
+      <c r="E13" s="80" t="inlineStr">
         <is>
           <t>96088/1</t>
         </is>
       </c>
-      <c r="F13" s="79" t="inlineStr">
+      <c r="F13" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G13" s="79" t="inlineStr">
+      <c r="G13" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H13" s="80" t="n">
+      <c r="H13" s="81" t="n">
         <v>51.63</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="79" t="inlineStr">
+      <c r="A14" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>22/01/2026</t>
         </is>
       </c>
-      <c r="C14" s="79" t="inlineStr">
+      <c r="C14" s="80" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D14" s="79" t="inlineStr">
+      <c r="D14" s="80" t="inlineStr">
         <is>
           <t>FAT.5664047504</t>
         </is>
       </c>
-      <c r="E14" s="79" t="inlineStr">
+      <c r="E14" s="80" t="inlineStr">
         <is>
           <t>96789/1</t>
         </is>
       </c>
-      <c r="F14" s="79" t="inlineStr">
+      <c r="F14" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G14" s="79" t="inlineStr">
+      <c r="G14" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H14" s="80" t="n">
+      <c r="H14" s="81" t="n">
         <v>331.42</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="79" t="inlineStr">
+      <c r="A15" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="80" t="inlineStr">
         <is>
           <t>26/01/2026</t>
         </is>
       </c>
-      <c r="C15" s="79" t="inlineStr">
+      <c r="C15" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D15" s="79" t="inlineStr">
+      <c r="D15" s="80" t="inlineStr">
         <is>
           <t>CX.16.01.26</t>
         </is>
       </c>
-      <c r="E15" s="79" t="inlineStr">
+      <c r="E15" s="80" t="inlineStr">
         <is>
           <t>97067/1</t>
         </is>
       </c>
-      <c r="F15" s="79" t="inlineStr">
+      <c r="F15" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G15" s="79" t="inlineStr">
+      <c r="G15" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H15" s="80" t="n">
+      <c r="H15" s="81" t="n">
         <v>39.84</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="79" t="inlineStr">
+      <c r="A16" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="80" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="C16" s="79" t="inlineStr">
+      <c r="C16" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="D16" s="80" t="inlineStr">
         <is>
           <t>SAL.Sal_122025</t>
         </is>
       </c>
-      <c r="E16" s="79" t="inlineStr">
+      <c r="E16" s="80" t="inlineStr">
         <is>
           <t>96252/1</t>
         </is>
       </c>
-      <c r="F16" s="79" t="inlineStr">
+      <c r="F16" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G16" s="79" t="inlineStr">
+      <c r="G16" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H16" s="80" t="n">
+      <c r="H16" s="81" t="n">
         <v>1602</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="79" t="inlineStr">
+      <c r="A17" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B17" s="79" t="inlineStr">
+      <c r="B17" s="80" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="C17" s="79" t="inlineStr">
+      <c r="C17" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D17" s="79" t="inlineStr">
+      <c r="D17" s="80" t="inlineStr">
         <is>
           <t>SAL.VALE_ 012026</t>
         </is>
       </c>
-      <c r="E17" s="79" t="inlineStr">
+      <c r="E17" s="80" t="inlineStr">
         <is>
           <t>97269/1</t>
         </is>
       </c>
-      <c r="F17" s="79" t="inlineStr">
+      <c r="F17" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G17" s="79" t="inlineStr">
+      <c r="G17" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H17" s="80" t="n">
+      <c r="H17" s="81" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="79" t="inlineStr">
+      <c r="A18" s="80" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B18" s="79" t="inlineStr">
+      <c r="B18" s="80" t="inlineStr">
         <is>
           <t>27/01/2026</t>
         </is>
       </c>
-      <c r="C18" s="79" t="inlineStr">
+      <c r="C18" s="80" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D18" s="79" t="inlineStr">
+      <c r="D18" s="80" t="inlineStr">
         <is>
           <t>BOL.1</t>
         </is>
       </c>
-      <c r="E18" s="79" t="inlineStr">
+      <c r="E18" s="80" t="inlineStr">
         <is>
           <t>97204/1</t>
         </is>
       </c>
-      <c r="F18" s="79" t="inlineStr">
+      <c r="F18" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G18" s="79" t="inlineStr">
+      <c r="G18" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H18" s="80" t="n">
+      <c r="H18" s="81" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="79" t="inlineStr">
+      <c r="A19" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B19" s="79" t="inlineStr">
+      <c r="B19" s="80" t="inlineStr">
         <is>
           <t>04/02/2026</t>
         </is>
       </c>
-      <c r="C19" s="79" t="inlineStr">
+      <c r="C19" s="80" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D19" s="79" t="inlineStr">
+      <c r="D19" s="80" t="inlineStr">
         <is>
           <t>AV.04.02.26</t>
         </is>
       </c>
-      <c r="E19" s="79" t="inlineStr">
+      <c r="E19" s="80" t="inlineStr">
         <is>
           <t>98500/1</t>
         </is>
       </c>
-      <c r="F19" s="79" t="inlineStr">
+      <c r="F19" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G19" s="79" t="inlineStr">
+      <c r="G19" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H19" s="80" t="n">
+      <c r="H19" s="81" t="n">
         <v>26.67</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="79" t="inlineStr">
+      <c r="A20" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C20" s="79" t="inlineStr">
+      <c r="C20" s="80" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D20" s="79" t="inlineStr">
+      <c r="D20" s="80" t="inlineStr">
         <is>
           <t>AV.12.02.26 LCW</t>
         </is>
       </c>
-      <c r="E20" s="79" t="inlineStr">
+      <c r="E20" s="80" t="inlineStr">
         <is>
           <t>99336/1</t>
         </is>
       </c>
-      <c r="F20" s="79" t="inlineStr">
+      <c r="F20" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G20" s="79" t="inlineStr">
+      <c r="G20" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H20" s="80" t="n">
+      <c r="H20" s="81" t="n">
         <v>72.58</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="79" t="inlineStr">
+      <c r="A21" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B21" s="79" t="inlineStr">
+      <c r="B21" s="80" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C21" s="79" t="inlineStr">
+      <c r="C21" s="80" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D21" s="79" t="inlineStr">
+      <c r="D21" s="80" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E21" s="79" t="inlineStr">
+      <c r="E21" s="80" t="inlineStr">
         <is>
           <t>95104/2</t>
         </is>
       </c>
-      <c r="F21" s="79" t="inlineStr">
+      <c r="F21" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G21" s="79" t="inlineStr">
+      <c r="G21" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H21" s="80" t="n">
+      <c r="H21" s="81" t="n">
         <v>234.46</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="79" t="inlineStr">
+      <c r="A22" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B22" s="79" t="inlineStr">
+      <c r="B22" s="80" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C22" s="79" t="inlineStr">
+      <c r="C22" s="80" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D22" s="79" t="inlineStr">
+      <c r="D22" s="80" t="inlineStr">
         <is>
           <t>FAT.3575377</t>
         </is>
       </c>
-      <c r="E22" s="79" t="inlineStr">
+      <c r="E22" s="80" t="inlineStr">
         <is>
           <t>100172/1</t>
         </is>
       </c>
-      <c r="F22" s="79" t="inlineStr">
+      <c r="F22" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G22" s="79" t="inlineStr">
+      <c r="G22" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H22" s="80" t="n">
+      <c r="H22" s="81" t="n">
         <v>52.32</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="79" t="inlineStr">
+      <c r="A23" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B23" s="79" t="inlineStr">
+      <c r="B23" s="80" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C23" s="79" t="inlineStr">
+      <c r="C23" s="80" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D23" s="79" t="inlineStr">
+      <c r="D23" s="80" t="inlineStr">
         <is>
           <t>FAT.5290953</t>
         </is>
       </c>
-      <c r="E23" s="79" t="inlineStr">
+      <c r="E23" s="80" t="inlineStr">
         <is>
           <t>100173/1</t>
         </is>
       </c>
-      <c r="F23" s="79" t="inlineStr">
+      <c r="F23" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G23" s="79" t="inlineStr">
+      <c r="G23" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H23" s="80" t="n">
+      <c r="H23" s="81" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="79" t="inlineStr">
+      <c r="A24" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B24" s="79" t="inlineStr">
+      <c r="B24" s="80" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C24" s="79" t="inlineStr">
+      <c r="C24" s="80" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D24" s="79" t="inlineStr">
+      <c r="D24" s="80" t="inlineStr">
         <is>
           <t>BOL.141</t>
         </is>
       </c>
-      <c r="E24" s="79" t="inlineStr">
+      <c r="E24" s="80" t="inlineStr">
         <is>
           <t>99947/1</t>
         </is>
       </c>
-      <c r="F24" s="79" t="inlineStr">
+      <c r="F24" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G24" s="79" t="inlineStr">
+      <c r="G24" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H24" s="80" t="n">
+      <c r="H24" s="81" t="n">
         <v>338.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="79" t="inlineStr">
+      <c r="A25" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B25" s="79" t="inlineStr">
+      <c r="B25" s="80" t="inlineStr">
         <is>
           <t>13/02/2026</t>
         </is>
       </c>
-      <c r="C25" s="79" t="inlineStr">
+      <c r="C25" s="80" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D25" s="79" t="inlineStr">
+      <c r="D25" s="80" t="inlineStr">
         <is>
           <t>BOL.26449</t>
         </is>
       </c>
-      <c r="E25" s="79" t="inlineStr">
+      <c r="E25" s="80" t="inlineStr">
         <is>
           <t>99484/1</t>
         </is>
       </c>
-      <c r="F25" s="79" t="inlineStr">
+      <c r="F25" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G25" s="79" t="inlineStr">
+      <c r="G25" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H25" s="80" t="n">
+      <c r="H25" s="81" t="n">
         <v>137.94</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="79" t="inlineStr">
+      <c r="A26" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B26" s="79" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>19/02/2026</t>
         </is>
       </c>
-      <c r="C26" s="79" t="inlineStr">
+      <c r="C26" s="80" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D26" s="79" t="inlineStr">
+      <c r="D26" s="80" t="inlineStr">
         <is>
           <t>BOL.27256</t>
         </is>
       </c>
-      <c r="E26" s="79" t="inlineStr">
+      <c r="E26" s="80" t="inlineStr">
         <is>
           <t>99486/1</t>
         </is>
       </c>
-      <c r="F26" s="79" t="inlineStr">
+      <c r="F26" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G26" s="79" t="inlineStr">
+      <c r="G26" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H26" s="80" t="n">
+      <c r="H26" s="81" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="79" t="inlineStr">
+      <c r="A27" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B27" s="79" t="inlineStr">
+      <c r="B27" s="80" t="inlineStr">
         <is>
           <t>06/02/2026</t>
         </is>
       </c>
-      <c r="C27" s="79" t="inlineStr">
+      <c r="C27" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D27" s="79" t="inlineStr">
+      <c r="D27" s="80" t="inlineStr">
         <is>
           <t>SAL.SAL JANEIRO 2026</t>
         </is>
       </c>
-      <c r="E27" s="79" t="inlineStr">
+      <c r="E27" s="80" t="inlineStr">
         <is>
           <t>98811/1</t>
         </is>
       </c>
-      <c r="F27" s="79" t="inlineStr">
+      <c r="F27" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G27" s="79" t="inlineStr">
+      <c r="G27" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H27" s="80" t="n">
+      <c r="H27" s="81" t="n">
         <v>1750</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="79" t="inlineStr">
+      <c r="A28" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B28" s="79" t="inlineStr">
+      <c r="B28" s="80" t="inlineStr">
         <is>
           <t>20/02/2026</t>
         </is>
       </c>
-      <c r="C28" s="79" t="inlineStr">
+      <c r="C28" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D28" s="79" t="inlineStr">
+      <c r="D28" s="80" t="inlineStr">
         <is>
           <t>SAL.VALE FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E28" s="79" t="inlineStr">
+      <c r="E28" s="80" t="inlineStr">
         <is>
           <t>99890/1</t>
         </is>
       </c>
-      <c r="F28" s="79" t="inlineStr">
+      <c r="F28" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G28" s="79" t="inlineStr">
+      <c r="G28" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H28" s="80" t="n">
+      <c r="H28" s="81" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="79" t="inlineStr">
+      <c r="A29" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B29" s="79" t="inlineStr">
+      <c r="B29" s="80" t="inlineStr">
         <is>
           <t>2026-02-20 00:00:00</t>
         </is>
       </c>
-      <c r="C29" s="79" t="inlineStr">
+      <c r="C29" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D29" s="79" t="inlineStr">
+      <c r="D29" s="80" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E29" s="79" t="inlineStr">
+      <c r="E29" s="80" t="inlineStr">
         <is>
           <t>113754/2</t>
         </is>
       </c>
-      <c r="F29" s="79" t="inlineStr">
+      <c r="F29" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G29" s="79" t="inlineStr">
+      <c r="G29" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H29" s="80" t="n">
+      <c r="H29" s="81" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="79" t="inlineStr">
+      <c r="A30" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B30" s="79" t="inlineStr">
+      <c r="B30" s="80" t="inlineStr">
         <is>
           <t>2026-02-01 00:00:00</t>
         </is>
       </c>
-      <c r="C30" s="79" t="inlineStr">
+      <c r="C30" s="80" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D30" s="79" t="inlineStr"/>
-      <c r="E30" s="79" t="inlineStr"/>
-      <c r="F30" s="79" t="inlineStr">
+      <c r="D30" s="80" t="inlineStr"/>
+      <c r="E30" s="80" t="inlineStr"/>
+      <c r="F30" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G30" s="79" t="inlineStr">
+      <c r="G30" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H30" s="80" t="n">
+      <c r="H30" s="81" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="79" t="inlineStr">
+      <c r="A31" s="80" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B31" s="79" t="inlineStr">
+      <c r="B31" s="80" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C31" s="79" t="inlineStr">
+      <c r="C31" s="80" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D31" s="79" t="inlineStr">
+      <c r="D31" s="80" t="inlineStr">
         <is>
           <t>NFS.1430</t>
         </is>
       </c>
-      <c r="E31" s="79" t="inlineStr">
+      <c r="E31" s="80" t="inlineStr">
         <is>
           <t>99956/1</t>
         </is>
       </c>
-      <c r="F31" s="79" t="inlineStr">
+      <c r="F31" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G31" s="79" t="inlineStr">
+      <c r="G31" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H31" s="80" t="n">
+      <c r="H31" s="81" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="79" t="inlineStr">
+      <c r="A32" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B32" s="79" t="inlineStr">
+      <c r="B32" s="80" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C32" s="79" t="inlineStr">
+      <c r="C32" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D32" s="79" t="inlineStr">
+      <c r="D32" s="80" t="inlineStr">
         <is>
           <t>FAT.5042829</t>
         </is>
       </c>
-      <c r="E32" s="79" t="inlineStr">
+      <c r="E32" s="80" t="inlineStr">
         <is>
           <t>100503/1</t>
         </is>
       </c>
-      <c r="F32" s="79" t="inlineStr">
+      <c r="F32" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G32" s="79" t="inlineStr">
+      <c r="G32" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H32" s="80" t="n">
+      <c r="H32" s="81" t="n">
         <v>87.69</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="79" t="inlineStr">
+      <c r="A33" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B33" s="79" t="inlineStr">
+      <c r="B33" s="80" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C33" s="79" t="inlineStr">
+      <c r="C33" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D33" s="79" t="inlineStr">
+      <c r="D33" s="80" t="inlineStr">
         <is>
           <t>FAT.5042827</t>
         </is>
       </c>
-      <c r="E33" s="79" t="inlineStr">
+      <c r="E33" s="80" t="inlineStr">
         <is>
           <t>100504/1</t>
         </is>
       </c>
-      <c r="F33" s="79" t="inlineStr">
+      <c r="F33" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G33" s="79" t="inlineStr">
+      <c r="G33" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H33" s="80" t="n">
+      <c r="H33" s="81" t="n">
         <v>382.4</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="79" t="inlineStr">
+      <c r="A34" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B34" s="79" t="inlineStr">
+      <c r="B34" s="80" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="C34" s="79" t="inlineStr">
+      <c r="C34" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D34" s="79" t="inlineStr">
+      <c r="D34" s="80" t="inlineStr">
         <is>
           <t>FAT.8910508</t>
         </is>
       </c>
-      <c r="E34" s="79" t="inlineStr">
+      <c r="E34" s="80" t="inlineStr">
         <is>
           <t>102706/1</t>
         </is>
       </c>
-      <c r="F34" s="79" t="inlineStr">
+      <c r="F34" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G34" s="79" t="inlineStr">
+      <c r="G34" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H34" s="80" t="n">
+      <c r="H34" s="81" t="n">
         <v>429.49</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="79" t="inlineStr">
+      <c r="A35" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B35" s="79" t="inlineStr">
+      <c r="B35" s="80" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="C35" s="79" t="inlineStr">
+      <c r="C35" s="80" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D35" s="79" t="inlineStr">
+      <c r="D35" s="80" t="inlineStr">
         <is>
           <t>NFS.351653</t>
         </is>
       </c>
-      <c r="E35" s="79" t="inlineStr">
+      <c r="E35" s="80" t="inlineStr">
         <is>
           <t>100083/1</t>
         </is>
       </c>
-      <c r="F35" s="79" t="inlineStr">
+      <c r="F35" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G35" s="79" t="inlineStr">
+      <c r="G35" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H35" s="80" t="n">
+      <c r="H35" s="81" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="79" t="inlineStr">
+      <c r="A36" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B36" s="79" t="inlineStr">
+      <c r="B36" s="80" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="C36" s="79" t="inlineStr">
+      <c r="C36" s="80" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D36" s="79" t="inlineStr">
+      <c r="D36" s="80" t="inlineStr">
         <is>
           <t>NFS.359396</t>
         </is>
       </c>
-      <c r="E36" s="79" t="inlineStr">
+      <c r="E36" s="80" t="inlineStr">
         <is>
           <t>102608/1</t>
         </is>
       </c>
-      <c r="F36" s="79" t="inlineStr">
+      <c r="F36" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G36" s="79" t="inlineStr">
+      <c r="G36" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H36" s="80" t="n">
+      <c r="H36" s="81" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="79" t="inlineStr">
+      <c r="A37" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B37" s="79" t="inlineStr">
+      <c r="B37" s="80" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="C37" s="79" t="inlineStr">
+      <c r="C37" s="80" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D37" s="79" t="inlineStr">
+      <c r="D37" s="80" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E37" s="79" t="inlineStr">
+      <c r="E37" s="80" t="inlineStr">
         <is>
           <t>95104/3</t>
         </is>
       </c>
-      <c r="F37" s="79" t="inlineStr">
+      <c r="F37" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G37" s="79" t="inlineStr">
+      <c r="G37" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H37" s="80" t="n">
+      <c r="H37" s="81" t="n">
         <v>111.38</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="79" t="inlineStr">
+      <c r="A38" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B38" s="79" t="inlineStr">
+      <c r="B38" s="80" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C38" s="79" t="inlineStr">
+      <c r="C38" s="80" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D38" s="79" t="inlineStr">
+      <c r="D38" s="80" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E38" s="79" t="inlineStr">
+      <c r="E38" s="80" t="inlineStr">
         <is>
           <t>95104/4</t>
         </is>
       </c>
-      <c r="F38" s="79" t="inlineStr">
+      <c r="F38" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G38" s="79" t="inlineStr">
+      <c r="G38" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H38" s="80" t="n">
+      <c r="H38" s="81" t="n">
         <v>210.38</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="79" t="inlineStr">
+      <c r="A39" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B39" s="79" t="inlineStr">
+      <c r="B39" s="80" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="C39" s="79" t="inlineStr">
+      <c r="C39" s="80" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D39" s="79" t="inlineStr">
+      <c r="D39" s="80" t="inlineStr">
         <is>
           <t>FAT.2024588614</t>
         </is>
       </c>
-      <c r="E39" s="79" t="inlineStr">
+      <c r="E39" s="80" t="inlineStr">
         <is>
           <t>102316/1</t>
         </is>
       </c>
-      <c r="F39" s="79" t="inlineStr">
+      <c r="F39" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G39" s="79" t="inlineStr">
+      <c r="G39" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H39" s="80" t="n">
+      <c r="H39" s="81" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="79" t="inlineStr">
+      <c r="A40" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B40" s="79" t="inlineStr">
+      <c r="B40" s="80" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C40" s="79" t="inlineStr">
+      <c r="C40" s="80" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D40" s="79" t="inlineStr">
+      <c r="D40" s="80" t="inlineStr">
         <is>
           <t>BOL.5708173302</t>
         </is>
       </c>
-      <c r="E40" s="79" t="inlineStr">
+      <c r="E40" s="80" t="inlineStr">
         <is>
           <t>102057/1</t>
         </is>
       </c>
-      <c r="F40" s="79" t="inlineStr">
+      <c r="F40" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G40" s="79" t="inlineStr">
+      <c r="G40" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H40" s="80" t="n">
+      <c r="H40" s="81" t="n">
         <v>284.63</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="79" t="inlineStr">
+      <c r="A41" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B41" s="79" t="inlineStr">
+      <c r="B41" s="80" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="C41" s="79" t="inlineStr">
+      <c r="C41" s="80" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D41" s="79" t="inlineStr">
+      <c r="D41" s="80" t="inlineStr">
         <is>
           <t>BOL.28049</t>
         </is>
       </c>
-      <c r="E41" s="79" t="inlineStr">
+      <c r="E41" s="80" t="inlineStr">
         <is>
           <t>100887/1</t>
         </is>
       </c>
-      <c r="F41" s="79" t="inlineStr">
+      <c r="F41" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G41" s="79" t="inlineStr">
+      <c r="G41" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H41" s="80" t="n">
+      <c r="H41" s="81" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="79" t="inlineStr">
+      <c r="A42" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B42" s="79" t="inlineStr">
+      <c r="B42" s="80" t="inlineStr">
         <is>
           <t>06/03/2026</t>
         </is>
       </c>
-      <c r="C42" s="79" t="inlineStr">
+      <c r="C42" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D42" s="79" t="inlineStr">
+      <c r="D42" s="80" t="inlineStr">
         <is>
           <t>SAL.SAL FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E42" s="79" t="inlineStr">
+      <c r="E42" s="80" t="inlineStr">
         <is>
           <t>101276/1</t>
         </is>
       </c>
-      <c r="F42" s="79" t="inlineStr">
+      <c r="F42" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G42" s="79" t="inlineStr">
+      <c r="G42" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H42" s="80" t="n">
+      <c r="H42" s="81" t="n">
         <v>1542</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="79" t="inlineStr">
+      <c r="A43" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B43" s="79" t="inlineStr">
+      <c r="B43" s="80" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C43" s="79" t="inlineStr">
+      <c r="C43" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D43" s="79" t="inlineStr">
+      <c r="D43" s="80" t="inlineStr">
         <is>
           <t>SAL.VALE 032026</t>
         </is>
       </c>
-      <c r="E43" s="79" t="inlineStr">
+      <c r="E43" s="80" t="inlineStr">
         <is>
           <t>102295/1</t>
         </is>
       </c>
-      <c r="F43" s="79" t="inlineStr">
+      <c r="F43" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G43" s="79" t="inlineStr">
+      <c r="G43" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H43" s="80" t="n">
+      <c r="H43" s="81" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="79" t="inlineStr">
+      <c r="A44" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B44" s="79" t="inlineStr">
+      <c r="B44" s="80" t="inlineStr">
         <is>
           <t>2026-03-20 00:00:00</t>
         </is>
       </c>
-      <c r="C44" s="79" t="inlineStr">
+      <c r="C44" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D44" s="79" t="inlineStr">
+      <c r="D44" s="80" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E44" s="79" t="inlineStr">
+      <c r="E44" s="80" t="inlineStr">
         <is>
           <t>113754/3</t>
         </is>
       </c>
-      <c r="F44" s="79" t="inlineStr">
+      <c r="F44" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G44" s="79" t="inlineStr">
+      <c r="G44" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H44" s="80" t="n">
+      <c r="H44" s="81" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="79" t="inlineStr">
+      <c r="A45" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B45" s="79" t="inlineStr">
+      <c r="B45" s="80" t="inlineStr">
         <is>
           <t>2026-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="C45" s="79" t="inlineStr">
+      <c r="C45" s="80" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D45" s="79" t="inlineStr"/>
-      <c r="E45" s="79" t="inlineStr"/>
-      <c r="F45" s="79" t="inlineStr">
+      <c r="D45" s="80" t="inlineStr"/>
+      <c r="E45" s="80" t="inlineStr"/>
+      <c r="F45" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G45" s="79" t="inlineStr">
+      <c r="G45" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H45" s="80" t="n">
+      <c r="H45" s="81" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="79" t="inlineStr">
+      <c r="A46" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B46" s="79" t="inlineStr">
+      <c r="B46" s="80" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C46" s="79" t="inlineStr">
+      <c r="C46" s="80" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D46" s="79" t="inlineStr">
+      <c r="D46" s="80" t="inlineStr">
         <is>
           <t>NFS.1500</t>
         </is>
       </c>
-      <c r="E46" s="79" t="inlineStr">
+      <c r="E46" s="80" t="inlineStr">
         <is>
           <t>102432/1</t>
         </is>
       </c>
-      <c r="F46" s="79" t="inlineStr">
+      <c r="F46" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G46" s="79" t="inlineStr">
+      <c r="G46" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H46" s="80" t="n">
+      <c r="H46" s="81" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="79" t="inlineStr">
+      <c r="A47" s="80" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B47" s="79" t="inlineStr">
+      <c r="B47" s="80" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C47" s="79" t="inlineStr">
+      <c r="C47" s="80" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D47" s="79" t="inlineStr">
+      <c r="D47" s="80" t="inlineStr">
         <is>
           <t>NFS.1534</t>
         </is>
       </c>
-      <c r="E47" s="79" t="inlineStr">
+      <c r="E47" s="80" t="inlineStr">
         <is>
           <t>102434/1</t>
         </is>
       </c>
-      <c r="F47" s="79" t="inlineStr">
+      <c r="F47" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G47" s="79" t="inlineStr">
+      <c r="G47" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H47" s="80" t="n">
+      <c r="H47" s="81" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="79" t="inlineStr">
+      <c r="A48" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B48" s="79" t="inlineStr">
+      <c r="B48" s="80" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C48" s="79" t="inlineStr">
+      <c r="C48" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D48" s="79" t="inlineStr">
+      <c r="D48" s="80" t="inlineStr">
         <is>
           <t>FAT.8910315</t>
         </is>
       </c>
-      <c r="E48" s="79" t="inlineStr">
+      <c r="E48" s="80" t="inlineStr">
         <is>
           <t>105607/1</t>
         </is>
       </c>
-      <c r="F48" s="79" t="inlineStr">
+      <c r="F48" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G48" s="79" t="inlineStr">
+      <c r="G48" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H48" s="80" t="n">
+      <c r="H48" s="81" t="n">
         <v>11.99</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="79" t="inlineStr">
+      <c r="A49" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B49" s="79" t="inlineStr">
+      <c r="B49" s="80" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C49" s="79" t="inlineStr">
+      <c r="C49" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D49" s="79" t="inlineStr">
+      <c r="D49" s="80" t="inlineStr">
         <is>
           <t>FAT.13443658</t>
         </is>
       </c>
-      <c r="E49" s="79" t="inlineStr">
+      <c r="E49" s="80" t="inlineStr">
         <is>
           <t>105676/1</t>
         </is>
       </c>
-      <c r="F49" s="79" t="inlineStr">
+      <c r="F49" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G49" s="79" t="inlineStr">
+      <c r="G49" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H49" s="80" t="n">
+      <c r="H49" s="81" t="n">
         <v>557.63</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="79" t="inlineStr">
+      <c r="A50" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B50" s="79" t="inlineStr">
+      <c r="B50" s="80" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C50" s="79" t="inlineStr">
+      <c r="C50" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D50" s="79" t="inlineStr">
+      <c r="D50" s="80" t="inlineStr">
         <is>
           <t>FAT.13443664</t>
         </is>
       </c>
-      <c r="E50" s="79" t="inlineStr">
+      <c r="E50" s="80" t="inlineStr">
         <is>
           <t>105677/1</t>
         </is>
       </c>
-      <c r="F50" s="79" t="inlineStr">
+      <c r="F50" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G50" s="79" t="inlineStr">
+      <c r="G50" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H50" s="80" t="n">
+      <c r="H50" s="81" t="n">
         <v>132.09</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="79" t="inlineStr">
+      <c r="A51" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B51" s="79" t="inlineStr">
+      <c r="B51" s="80" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C51" s="79" t="inlineStr">
+      <c r="C51" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D51" s="79" t="inlineStr">
+      <c r="D51" s="80" t="inlineStr">
         <is>
           <t>FAT.13443112</t>
         </is>
       </c>
-      <c r="E51" s="79" t="inlineStr">
+      <c r="E51" s="80" t="inlineStr">
         <is>
           <t>105792/1</t>
         </is>
       </c>
-      <c r="F51" s="79" t="inlineStr">
+      <c r="F51" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G51" s="79" t="inlineStr">
+      <c r="G51" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H51" s="80" t="n">
+      <c r="H51" s="81" t="n">
         <v>20.23</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="79" t="inlineStr">
+      <c r="A52" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B52" s="79" t="inlineStr">
+      <c r="B52" s="80" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C52" s="79" t="inlineStr">
+      <c r="C52" s="80" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D52" s="79" t="inlineStr">
+      <c r="D52" s="80" t="inlineStr">
         <is>
           <t>NFS.363799</t>
         </is>
       </c>
-      <c r="E52" s="79" t="inlineStr">
+      <c r="E52" s="80" t="inlineStr">
         <is>
           <t>104634/1</t>
         </is>
       </c>
-      <c r="F52" s="79" t="inlineStr">
+      <c r="F52" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G52" s="79" t="inlineStr">
+      <c r="G52" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H52" s="80" t="n">
+      <c r="H52" s="81" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="79" t="inlineStr">
+      <c r="A53" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B53" s="79" t="inlineStr">
+      <c r="B53" s="80" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="C53" s="79" t="inlineStr">
+      <c r="C53" s="80" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D53" s="79" t="inlineStr">
+      <c r="D53" s="80" t="inlineStr">
         <is>
           <t>BOL.04.26</t>
         </is>
       </c>
-      <c r="E53" s="79" t="inlineStr">
+      <c r="E53" s="80" t="inlineStr">
         <is>
           <t>104820/1</t>
         </is>
       </c>
-      <c r="F53" s="79" t="inlineStr">
+      <c r="F53" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G53" s="79" t="inlineStr">
+      <c r="G53" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H53" s="80" t="n">
+      <c r="H53" s="81" t="n">
         <v>1024.76</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="79" t="inlineStr">
+      <c r="A54" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B54" s="79" t="inlineStr">
+      <c r="B54" s="80" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C54" s="79" t="inlineStr">
+      <c r="C54" s="80" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D54" s="79" t="inlineStr">
+      <c r="D54" s="80" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 29.04.26</t>
         </is>
       </c>
-      <c r="E54" s="79" t="inlineStr">
+      <c r="E54" s="80" t="inlineStr">
         <is>
           <t>106325/1</t>
         </is>
       </c>
-      <c r="F54" s="79" t="inlineStr">
+      <c r="F54" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G54" s="79" t="inlineStr">
+      <c r="G54" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H54" s="80" t="n">
+      <c r="H54" s="81" t="n">
         <v>21.76</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="79" t="inlineStr">
+      <c r="A55" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B55" s="79" t="inlineStr">
+      <c r="B55" s="80" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C55" s="79" t="inlineStr">
+      <c r="C55" s="80" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D55" s="79" t="inlineStr">
+      <c r="D55" s="80" t="inlineStr">
         <is>
           <t>FAT.CHATGPT 3 LIC</t>
         </is>
       </c>
-      <c r="E55" s="79" t="inlineStr">
+      <c r="E55" s="80" t="inlineStr">
         <is>
           <t>102137/1</t>
         </is>
       </c>
-      <c r="F55" s="79" t="inlineStr">
+      <c r="F55" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G55" s="79" t="inlineStr">
+      <c r="G55" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H55" s="80" t="n">
+      <c r="H55" s="81" t="n">
         <v>5393.88</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="79" t="inlineStr">
+      <c r="A56" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B56" s="79" t="inlineStr">
+      <c r="B56" s="80" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C56" s="79" t="inlineStr">
+      <c r="C56" s="80" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D56" s="79" t="inlineStr">
+      <c r="D56" s="80" t="inlineStr">
         <is>
           <t>BOL.28855</t>
         </is>
       </c>
-      <c r="E56" s="79" t="inlineStr">
+      <c r="E56" s="80" t="inlineStr">
         <is>
           <t>103694/1</t>
         </is>
       </c>
-      <c r="F56" s="79" t="inlineStr">
+      <c r="F56" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G56" s="79" t="inlineStr">
+      <c r="G56" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H56" s="80" t="n">
+      <c r="H56" s="81" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="79" t="inlineStr">
+      <c r="A57" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B57" s="79" t="inlineStr">
+      <c r="B57" s="80" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="C57" s="79" t="inlineStr">
+      <c r="C57" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D57" s="79" t="inlineStr">
+      <c r="D57" s="80" t="inlineStr">
         <is>
           <t>SAL.SAL 032026</t>
         </is>
       </c>
-      <c r="E57" s="79" t="inlineStr">
+      <c r="E57" s="80" t="inlineStr">
         <is>
           <t>103924/1</t>
         </is>
       </c>
-      <c r="F57" s="79" t="inlineStr">
+      <c r="F57" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G57" s="79" t="inlineStr">
+      <c r="G57" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H57" s="80" t="n">
+      <c r="H57" s="81" t="n">
         <v>1515</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="79" t="inlineStr">
+      <c r="A58" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B58" s="79" t="inlineStr">
+      <c r="B58" s="80" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="C58" s="79" t="inlineStr">
+      <c r="C58" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D58" s="79" t="inlineStr">
+      <c r="D58" s="80" t="inlineStr">
         <is>
           <t>SAL.vale 042026</t>
         </is>
       </c>
-      <c r="E58" s="79" t="inlineStr">
+      <c r="E58" s="80" t="inlineStr">
         <is>
           <t>105055/1</t>
         </is>
       </c>
-      <c r="F58" s="79" t="inlineStr">
+      <c r="F58" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G58" s="79" t="inlineStr">
+      <c r="G58" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H58" s="80" t="n">
+      <c r="H58" s="81" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="79" t="inlineStr">
+      <c r="A59" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B59" s="79" t="inlineStr">
+      <c r="B59" s="80" t="inlineStr">
         <is>
           <t>2026-04-20 00:00:00</t>
         </is>
       </c>
-      <c r="C59" s="79" t="inlineStr">
+      <c r="C59" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D59" s="79" t="inlineStr">
+      <c r="D59" s="80" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E59" s="79" t="inlineStr">
+      <c r="E59" s="80" t="inlineStr">
         <is>
           <t>113754/4</t>
         </is>
       </c>
-      <c r="F59" s="79" t="inlineStr">
+      <c r="F59" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G59" s="79" t="inlineStr">
+      <c r="G59" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H59" s="80" t="n">
+      <c r="H59" s="81" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="79" t="inlineStr">
+      <c r="A60" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B60" s="79" t="inlineStr">
+      <c r="B60" s="80" t="inlineStr">
         <is>
           <t>2026-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="C60" s="79" t="inlineStr">
+      <c r="C60" s="80" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D60" s="79" t="inlineStr"/>
-      <c r="E60" s="79" t="inlineStr"/>
-      <c r="F60" s="79" t="inlineStr">
+      <c r="D60" s="80" t="inlineStr"/>
+      <c r="E60" s="80" t="inlineStr"/>
+      <c r="F60" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G60" s="79" t="inlineStr">
+      <c r="G60" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H60" s="80" t="n">
+      <c r="H60" s="81" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="79" t="inlineStr">
+      <c r="A61" s="80" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B61" s="79" t="inlineStr">
+      <c r="B61" s="80" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="C61" s="79" t="inlineStr">
+      <c r="C61" s="80" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D61" s="79" t="inlineStr">
+      <c r="D61" s="80" t="inlineStr">
         <is>
           <t>NFS.1573</t>
         </is>
       </c>
-      <c r="E61" s="79" t="inlineStr">
+      <c r="E61" s="80" t="inlineStr">
         <is>
           <t>105411/1</t>
         </is>
       </c>
-      <c r="F61" s="79" t="inlineStr">
+      <c r="F61" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G61" s="79" t="inlineStr">
+      <c r="G61" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H61" s="80" t="n">
+      <c r="H61" s="81" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="79" t="inlineStr">
+      <c r="A62" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B62" s="79" t="inlineStr">
+      <c r="B62" s="80" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="C62" s="79" t="inlineStr">
+      <c r="C62" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D62" s="79" t="inlineStr">
+      <c r="D62" s="80" t="inlineStr">
         <is>
           <t>FAT.2ªvia Claro Abril</t>
         </is>
       </c>
-      <c r="E62" s="79" t="inlineStr">
+      <c r="E62" s="80" t="inlineStr">
         <is>
           <t>107340/1</t>
         </is>
       </c>
-      <c r="F62" s="79" t="inlineStr">
+      <c r="F62" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G62" s="79" t="inlineStr">
+      <c r="G62" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H62" s="80" t="n">
+      <c r="H62" s="81" t="n">
         <v>182.32</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="79" t="inlineStr">
+      <c r="A63" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B63" s="79" t="inlineStr">
+      <c r="B63" s="80" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C63" s="79" t="inlineStr">
+      <c r="C63" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D63" s="79" t="inlineStr">
+      <c r="D63" s="80" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E63" s="79" t="inlineStr">
+      <c r="E63" s="80" t="inlineStr">
         <is>
           <t>108218/1</t>
         </is>
       </c>
-      <c r="F63" s="79" t="inlineStr">
+      <c r="F63" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G63" s="79" t="inlineStr">
+      <c r="G63" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H63" s="80" t="n">
+      <c r="H63" s="81" t="n">
         <v>629.98</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="79" t="inlineStr">
+      <c r="A64" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B64" s="79" t="inlineStr">
+      <c r="B64" s="80" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C64" s="79" t="inlineStr">
+      <c r="C64" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D64" s="79" t="inlineStr">
+      <c r="D64" s="80" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E64" s="79" t="inlineStr">
+      <c r="E64" s="80" t="inlineStr">
         <is>
           <t>108218/2</t>
         </is>
       </c>
-      <c r="F64" s="79" t="inlineStr">
+      <c r="F64" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G64" s="79" t="inlineStr">
+      <c r="G64" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H64" s="80" t="n">
+      <c r="H64" s="81" t="n">
         <v>18.86</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="79" t="inlineStr">
+      <c r="A65" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B65" s="79" t="inlineStr">
+      <c r="B65" s="80" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C65" s="79" t="inlineStr">
+      <c r="C65" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D65" s="79" t="inlineStr">
+      <c r="D65" s="80" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E65" s="79" t="inlineStr">
+      <c r="E65" s="80" t="inlineStr">
         <is>
           <t>108218/3</t>
         </is>
       </c>
-      <c r="F65" s="79" t="inlineStr">
+      <c r="F65" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G65" s="79" t="inlineStr">
+      <c r="G65" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H65" s="80" t="n">
+      <c r="H65" s="81" t="n">
         <v>133.95</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="79" t="inlineStr">
+      <c r="A66" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B66" s="79" t="inlineStr">
+      <c r="B66" s="80" t="inlineStr">
         <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="C66" s="79" t="inlineStr">
+      <c r="C66" s="80" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D66" s="79" t="inlineStr">
+      <c r="D66" s="80" t="inlineStr">
         <is>
           <t>NFS.76</t>
         </is>
       </c>
-      <c r="E66" s="79" t="inlineStr">
+      <c r="E66" s="80" t="inlineStr">
         <is>
           <t>105987/1</t>
         </is>
       </c>
-      <c r="F66" s="79" t="inlineStr">
+      <c r="F66" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G66" s="79" t="inlineStr">
+      <c r="G66" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H66" s="80" t="n">
+      <c r="H66" s="81" t="n">
         <v>3723.62</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="79" t="inlineStr">
+      <c r="A67" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B67" s="79" t="inlineStr">
+      <c r="B67" s="80" t="inlineStr">
         <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="C67" s="79" t="inlineStr">
+      <c r="C67" s="80" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D67" s="79" t="inlineStr">
+      <c r="D67" s="80" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 11.05.26</t>
         </is>
       </c>
-      <c r="E67" s="79" t="inlineStr">
+      <c r="E67" s="80" t="inlineStr">
         <is>
           <t>107254/1</t>
         </is>
       </c>
-      <c r="F67" s="79" t="inlineStr">
+      <c r="F67" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G67" s="79" t="inlineStr">
+      <c r="G67" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H67" s="80" t="n">
+      <c r="H67" s="81" t="n">
         <v>74.81</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="79" t="inlineStr">
+      <c r="A68" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B68" s="79" t="inlineStr">
+      <c r="B68" s="80" t="inlineStr">
         <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="C68" s="79" t="inlineStr">
+      <c r="C68" s="80" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D68" s="79" t="inlineStr">
+      <c r="D68" s="80" t="inlineStr">
         <is>
           <t>NFS.5744</t>
         </is>
       </c>
-      <c r="E68" s="79" t="inlineStr">
+      <c r="E68" s="80" t="inlineStr">
         <is>
           <t>106664/1</t>
         </is>
       </c>
-      <c r="F68" s="79" t="inlineStr">
+      <c r="F68" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G68" s="79" t="inlineStr">
+      <c r="G68" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H68" s="80" t="n">
+      <c r="H68" s="81" t="n">
         <v>741.1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="79" t="inlineStr">
+      <c r="A69" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B69" s="79" t="inlineStr">
+      <c r="B69" s="80" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C69" s="79" t="inlineStr">
+      <c r="C69" s="80" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D69" s="79" t="inlineStr">
+      <c r="D69" s="80" t="inlineStr">
         <is>
           <t>BOL.29637</t>
         </is>
       </c>
-      <c r="E69" s="79" t="inlineStr">
+      <c r="E69" s="80" t="inlineStr">
         <is>
           <t>108040/1</t>
         </is>
       </c>
-      <c r="F69" s="79" t="inlineStr">
+      <c r="F69" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G69" s="79" t="inlineStr">
+      <c r="G69" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H69" s="80" t="n">
+      <c r="H69" s="81" t="n">
         <v>137.92</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="79" t="inlineStr">
+      <c r="A70" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B70" s="79" t="inlineStr">
+      <c r="B70" s="80" t="inlineStr">
         <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="C70" s="79" t="inlineStr">
+      <c r="C70" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D70" s="79" t="inlineStr">
+      <c r="D70" s="80" t="inlineStr">
         <is>
           <t>SAL.sal 042026</t>
         </is>
       </c>
-      <c r="E70" s="79" t="inlineStr">
+      <c r="E70" s="80" t="inlineStr">
         <is>
           <t>106947/1</t>
         </is>
       </c>
-      <c r="F70" s="79" t="inlineStr">
+      <c r="F70" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G70" s="79" t="inlineStr">
+      <c r="G70" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H70" s="80" t="n">
+      <c r="H70" s="81" t="n">
         <v>1483</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="79" t="inlineStr">
+      <c r="A71" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B71" s="79" t="inlineStr">
+      <c r="B71" s="80" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="C71" s="79" t="inlineStr">
+      <c r="C71" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D71" s="79" t="inlineStr">
+      <c r="D71" s="80" t="inlineStr">
         <is>
           <t>SAL.vale 052026</t>
         </is>
       </c>
-      <c r="E71" s="79" t="inlineStr">
+      <c r="E71" s="80" t="inlineStr">
         <is>
           <t>108156/1</t>
         </is>
       </c>
-      <c r="F71" s="79" t="inlineStr">
+      <c r="F71" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G71" s="79" t="inlineStr">
+      <c r="G71" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H71" s="80" t="n">
+      <c r="H71" s="81" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="79" t="inlineStr">
+      <c r="A72" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B72" s="79" t="inlineStr">
+      <c r="B72" s="80" t="inlineStr">
         <is>
           <t>2026-05-20 00:00:00</t>
         </is>
       </c>
-      <c r="C72" s="79" t="inlineStr">
+      <c r="C72" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D72" s="79" t="inlineStr">
+      <c r="D72" s="80" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E72" s="79" t="inlineStr">
+      <c r="E72" s="80" t="inlineStr">
         <is>
           <t>113754/5</t>
         </is>
       </c>
-      <c r="F72" s="79" t="inlineStr">
+      <c r="F72" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G72" s="79" t="inlineStr">
+      <c r="G72" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H72" s="80" t="n">
+      <c r="H72" s="81" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="79" t="inlineStr">
+      <c r="A73" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B73" s="79" t="inlineStr">
+      <c r="B73" s="80" t="inlineStr">
         <is>
           <t>2026-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="C73" s="79" t="inlineStr">
+      <c r="C73" s="80" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D73" s="79" t="inlineStr"/>
-      <c r="E73" s="79" t="inlineStr"/>
-      <c r="F73" s="79" t="inlineStr">
+      <c r="D73" s="80" t="inlineStr"/>
+      <c r="E73" s="80" t="inlineStr"/>
+      <c r="F73" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G73" s="79" t="inlineStr">
+      <c r="G73" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H73" s="80" t="n">
+      <c r="H73" s="81" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="79" t="inlineStr">
+      <c r="A74" s="80" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B74" s="79" t="inlineStr">
+      <c r="B74" s="80" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C74" s="79" t="inlineStr">
+      <c r="C74" s="80" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D74" s="79" t="inlineStr">
+      <c r="D74" s="80" t="inlineStr">
         <is>
           <t>NFS.1631</t>
         </is>
       </c>
-      <c r="E74" s="79" t="inlineStr">
+      <c r="E74" s="80" t="inlineStr">
         <is>
           <t>107973/1</t>
         </is>
       </c>
-      <c r="F74" s="79" t="inlineStr">
+      <c r="F74" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G74" s="79" t="inlineStr">
+      <c r="G74" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H74" s="80" t="n">
+      <c r="H74" s="81" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="79" t="inlineStr">
+      <c r="A75" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B75" s="79" t="inlineStr">
+      <c r="B75" s="80" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C75" s="79" t="inlineStr">
+      <c r="C75" s="80" t="inlineStr">
         <is>
           <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
         </is>
       </c>
-      <c r="D75" s="79" t="inlineStr">
+      <c r="D75" s="80" t="inlineStr">
         <is>
           <t>AV.1015392</t>
         </is>
       </c>
-      <c r="E75" s="79" t="inlineStr">
+      <c r="E75" s="80" t="inlineStr">
         <is>
           <t>108925/1</t>
         </is>
       </c>
-      <c r="F75" s="79" t="inlineStr">
+      <c r="F75" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G75" s="79" t="inlineStr">
+      <c r="G75" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H75" s="80" t="n">
+      <c r="H75" s="81" t="n">
         <v>183.6</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="79" t="inlineStr">
+      <c r="A76" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B76" s="79" t="inlineStr">
+      <c r="B76" s="80" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C76" s="79" t="inlineStr">
+      <c r="C76" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D76" s="79" t="inlineStr">
+      <c r="D76" s="80" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E76" s="79" t="inlineStr">
+      <c r="E76" s="80" t="inlineStr">
         <is>
           <t>111124/1</t>
         </is>
       </c>
-      <c r="F76" s="79" t="inlineStr">
+      <c r="F76" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G76" s="79" t="inlineStr">
+      <c r="G76" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H76" s="80" t="n">
+      <c r="H76" s="81" t="n">
         <v>720</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="79" t="inlineStr">
+      <c r="A77" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B77" s="79" t="inlineStr">
+      <c r="B77" s="80" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C77" s="79" t="inlineStr">
+      <c r="C77" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D77" s="79" t="inlineStr">
+      <c r="D77" s="80" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E77" s="79" t="inlineStr">
+      <c r="E77" s="80" t="inlineStr">
         <is>
           <t>111124/3</t>
         </is>
       </c>
-      <c r="F77" s="79" t="inlineStr">
+      <c r="F77" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G77" s="79" t="inlineStr">
+      <c r="G77" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H77" s="80" t="n">
+      <c r="H77" s="81" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="79" t="inlineStr">
+      <c r="A78" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B78" s="79" t="inlineStr">
+      <c r="B78" s="80" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C78" s="79" t="inlineStr">
+      <c r="C78" s="80" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D78" s="79" t="inlineStr">
+      <c r="D78" s="80" t="inlineStr">
         <is>
           <t>NFS.373725</t>
         </is>
       </c>
-      <c r="E78" s="79" t="inlineStr">
+      <c r="E78" s="80" t="inlineStr">
         <is>
           <t>110785/1</t>
         </is>
       </c>
-      <c r="F78" s="79" t="inlineStr">
+      <c r="F78" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G78" s="79" t="inlineStr">
+      <c r="G78" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H78" s="80" t="n">
+      <c r="H78" s="81" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="79" t="inlineStr">
+      <c r="A79" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B79" s="79" t="inlineStr">
+      <c r="B79" s="80" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C79" s="79" t="inlineStr">
+      <c r="C79" s="80" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D79" s="79" t="inlineStr">
+      <c r="D79" s="80" t="inlineStr">
         <is>
           <t>NFS.0036884701</t>
         </is>
       </c>
-      <c r="E79" s="79" t="inlineStr">
+      <c r="E79" s="80" t="inlineStr">
         <is>
           <t>109295/1</t>
         </is>
       </c>
-      <c r="F79" s="79" t="inlineStr">
+      <c r="F79" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G79" s="79" t="inlineStr">
+      <c r="G79" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H79" s="80" t="n">
+      <c r="H79" s="81" t="n">
         <v>84.81999999999999</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="79" t="inlineStr">
+      <c r="A80" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B80" s="79" t="inlineStr">
+      <c r="B80" s="80" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C80" s="79" t="inlineStr">
+      <c r="C80" s="80" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D80" s="79" t="inlineStr">
+      <c r="D80" s="80" t="inlineStr">
         <is>
           <t>NFS.78</t>
         </is>
       </c>
-      <c r="E80" s="79" t="inlineStr">
+      <c r="E80" s="80" t="inlineStr">
         <is>
           <t>108317/1</t>
         </is>
       </c>
-      <c r="F80" s="79" t="inlineStr">
+      <c r="F80" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G80" s="79" t="inlineStr">
+      <c r="G80" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H80" s="80" t="n">
+      <c r="H80" s="81" t="n">
         <v>6173.37</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="79" t="inlineStr">
+      <c r="A81" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B81" s="79" t="inlineStr">
+      <c r="B81" s="80" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="C81" s="79" t="inlineStr">
+      <c r="C81" s="80" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D81" s="79" t="inlineStr">
+      <c r="D81" s="80" t="inlineStr">
         <is>
           <t>NFS.5832</t>
         </is>
       </c>
-      <c r="E81" s="79" t="inlineStr">
+      <c r="E81" s="80" t="inlineStr">
         <is>
           <t>109227/1</t>
         </is>
       </c>
-      <c r="F81" s="79" t="inlineStr">
+      <c r="F81" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G81" s="79" t="inlineStr">
+      <c r="G81" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H81" s="80" t="n">
+      <c r="H81" s="81" t="n">
         <v>740.38</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="79" t="inlineStr">
+      <c r="A82" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B82" s="79" t="inlineStr">
+      <c r="B82" s="80" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C82" s="79" t="inlineStr">
+      <c r="C82" s="80" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D82" s="79" t="inlineStr">
+      <c r="D82" s="80" t="inlineStr">
         <is>
           <t>FAT.Vivo 04 2026</t>
         </is>
       </c>
-      <c r="E82" s="79" t="inlineStr">
+      <c r="E82" s="80" t="inlineStr">
         <is>
           <t>110752/1</t>
         </is>
       </c>
-      <c r="F82" s="79" t="inlineStr">
+      <c r="F82" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G82" s="79" t="inlineStr">
+      <c r="G82" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H82" s="80" t="n">
+      <c r="H82" s="81" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="79" t="inlineStr">
+      <c r="A83" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B83" s="79" t="inlineStr">
+      <c r="B83" s="80" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C83" s="79" t="inlineStr">
+      <c r="C83" s="80" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D83" s="79" t="inlineStr">
+      <c r="D83" s="80" t="inlineStr">
         <is>
           <t>FAT.Vivo 05 2026</t>
         </is>
       </c>
-      <c r="E83" s="79" t="inlineStr">
+      <c r="E83" s="80" t="inlineStr">
         <is>
           <t>110753/1</t>
         </is>
       </c>
-      <c r="F83" s="79" t="inlineStr">
+      <c r="F83" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G83" s="79" t="inlineStr">
+      <c r="G83" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H83" s="80" t="n">
+      <c r="H83" s="81" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="79" t="inlineStr">
+      <c r="A84" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B84" s="79" t="inlineStr">
+      <c r="B84" s="80" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C84" s="79" t="inlineStr">
+      <c r="C84" s="80" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D84" s="79" t="inlineStr">
+      <c r="D84" s="80" t="inlineStr">
         <is>
           <t>FAT.Vivo 06 2026</t>
         </is>
       </c>
-      <c r="E84" s="79" t="inlineStr">
+      <c r="E84" s="80" t="inlineStr">
         <is>
           <t>110754/1</t>
         </is>
       </c>
-      <c r="F84" s="79" t="inlineStr">
+      <c r="F84" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G84" s="79" t="inlineStr">
+      <c r="G84" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H84" s="80" t="n">
+      <c r="H84" s="81" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="79" t="inlineStr">
+      <c r="A85" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B85" s="79" t="inlineStr">
+      <c r="B85" s="80" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C85" s="79" t="inlineStr">
+      <c r="C85" s="80" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D85" s="79" t="inlineStr">
+      <c r="D85" s="80" t="inlineStr">
         <is>
           <t>BOL.1017717992</t>
         </is>
       </c>
-      <c r="E85" s="79" t="inlineStr">
+      <c r="E85" s="80" t="inlineStr">
         <is>
           <t>109298/1</t>
         </is>
       </c>
-      <c r="F85" s="79" t="inlineStr">
+      <c r="F85" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G85" s="79" t="inlineStr">
+      <c r="G85" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H85" s="80" t="n">
+      <c r="H85" s="81" t="n">
         <v>137.93</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="79" t="inlineStr">
+      <c r="A86" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B86" s="79" t="inlineStr">
+      <c r="B86" s="80" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C86" s="79" t="inlineStr">
+      <c r="C86" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D86" s="79" t="inlineStr">
+      <c r="D86" s="80" t="inlineStr">
         <is>
           <t>CX.27.05.26</t>
         </is>
       </c>
-      <c r="E86" s="79" t="inlineStr">
+      <c r="E86" s="80" t="inlineStr">
         <is>
           <t>108827/1</t>
         </is>
       </c>
-      <c r="F86" s="79" t="inlineStr">
+      <c r="F86" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G86" s="79" t="inlineStr">
+      <c r="G86" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H86" s="80" t="n">
+      <c r="H86" s="81" t="n">
         <v>184</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="79" t="inlineStr">
+      <c r="A87" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B87" s="79" t="inlineStr">
+      <c r="B87" s="80" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C87" s="79" t="inlineStr">
+      <c r="C87" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D87" s="79" t="inlineStr">
+      <c r="D87" s="80" t="inlineStr">
         <is>
           <t>SAL.1_ Ferias 1 VIn D 26</t>
         </is>
       </c>
-      <c r="E87" s="79" t="inlineStr">
+      <c r="E87" s="80" t="inlineStr">
         <is>
           <t>107780/1</t>
         </is>
       </c>
-      <c r="F87" s="79" t="inlineStr">
+      <c r="F87" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G87" s="79" t="inlineStr">
+      <c r="G87" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H87" s="80" t="n">
+      <c r="H87" s="81" t="n">
         <v>1101.12</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="79" t="inlineStr">
+      <c r="A88" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B88" s="79" t="inlineStr">
+      <c r="B88" s="80" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C88" s="79" t="inlineStr">
+      <c r="C88" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D88" s="79" t="inlineStr">
+      <c r="D88" s="80" t="inlineStr">
         <is>
           <t>SAL.sal 052026</t>
         </is>
       </c>
-      <c r="E88" s="79" t="inlineStr">
+      <c r="E88" s="80" t="inlineStr">
         <is>
           <t>109482/1</t>
         </is>
       </c>
-      <c r="F88" s="79" t="inlineStr">
+      <c r="F88" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G88" s="79" t="inlineStr">
+      <c r="G88" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H88" s="80" t="n">
+      <c r="H88" s="81" t="n">
         <v>1455</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="79" t="inlineStr">
+      <c r="A89" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B89" s="79" t="inlineStr">
+      <c r="B89" s="80" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C89" s="79" t="inlineStr">
+      <c r="C89" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D89" s="79" t="inlineStr">
+      <c r="D89" s="80" t="inlineStr">
         <is>
           <t>SAL.SALARIO06VINI</t>
         </is>
       </c>
-      <c r="E89" s="79" t="inlineStr">
+      <c r="E89" s="80" t="inlineStr">
         <is>
           <t>110700/1</t>
         </is>
       </c>
-      <c r="F89" s="79" t="inlineStr">
+      <c r="F89" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G89" s="79" t="inlineStr">
+      <c r="G89" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H89" s="80" t="n">
+      <c r="H89" s="81" t="n">
         <v>686</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="79" t="inlineStr">
+      <c r="A90" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B90" s="79" t="inlineStr">
+      <c r="B90" s="80" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="C90" s="79" t="inlineStr">
+      <c r="C90" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D90" s="79" t="inlineStr">
+      <c r="D90" s="80" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E90" s="79" t="inlineStr">
+      <c r="E90" s="80" t="inlineStr">
         <is>
           <t>113754/6</t>
         </is>
       </c>
-      <c r="F90" s="79" t="inlineStr">
+      <c r="F90" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G90" s="79" t="inlineStr">
+      <c r="G90" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H90" s="80" t="n">
+      <c r="H90" s="81" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="79" t="inlineStr">
+      <c r="A91" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B91" s="79" t="inlineStr">
+      <c r="B91" s="80" t="inlineStr">
         <is>
           <t>2026-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="C91" s="79" t="inlineStr">
+      <c r="C91" s="80" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D91" s="79" t="inlineStr"/>
-      <c r="E91" s="79" t="inlineStr"/>
-      <c r="F91" s="79" t="inlineStr">
+      <c r="D91" s="80" t="inlineStr"/>
+      <c r="E91" s="80" t="inlineStr"/>
+      <c r="F91" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G91" s="79" t="inlineStr">
+      <c r="G91" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H91" s="80" t="n">
+      <c r="H91" s="81" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="79" t="inlineStr">
+      <c r="A92" s="80" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B92" s="79" t="inlineStr">
+      <c r="B92" s="80" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C92" s="79" t="inlineStr">
+      <c r="C92" s="80" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D92" s="79" t="inlineStr">
+      <c r="D92" s="80" t="inlineStr">
         <is>
           <t>NFS.33</t>
         </is>
       </c>
-      <c r="E92" s="79" t="inlineStr">
+      <c r="E92" s="80" t="inlineStr">
         <is>
           <t>110902/1</t>
         </is>
       </c>
-      <c r="F92" s="79" t="inlineStr">
+      <c r="F92" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G92" s="79" t="inlineStr">
+      <c r="G92" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H92" s="80" t="n">
+      <c r="H92" s="81" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="79" t="inlineStr">
+      <c r="A93" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B93" s="79" t="inlineStr">
+      <c r="B93" s="80" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C93" s="79" t="inlineStr">
+      <c r="C93" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D93" s="79" t="inlineStr">
+      <c r="D93" s="80" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E93" s="79" t="inlineStr">
+      <c r="E93" s="80" t="inlineStr">
         <is>
           <t>113575/1</t>
         </is>
       </c>
-      <c r="F93" s="79" t="inlineStr">
+      <c r="F93" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G93" s="79" t="inlineStr">
+      <c r="G93" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H93" s="80" t="n">
+      <c r="H93" s="81" t="n">
         <v>20.39</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="79" t="inlineStr">
+      <c r="A94" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B94" s="79" t="inlineStr">
+      <c r="B94" s="80" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C94" s="79" t="inlineStr">
+      <c r="C94" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D94" s="79" t="inlineStr">
+      <c r="D94" s="80" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E94" s="79" t="inlineStr">
+      <c r="E94" s="80" t="inlineStr">
         <is>
           <t>113575/2</t>
         </is>
       </c>
-      <c r="F94" s="79" t="inlineStr">
+      <c r="F94" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G94" s="79" t="inlineStr">
+      <c r="G94" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H94" s="80" t="n">
+      <c r="H94" s="81" t="n">
         <v>133.73</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="79" t="inlineStr">
+      <c r="A95" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B95" s="79" t="inlineStr">
+      <c r="B95" s="80" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C95" s="79" t="inlineStr">
+      <c r="C95" s="80" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D95" s="79" t="inlineStr">
+      <c r="D95" s="80" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E95" s="79" t="inlineStr">
+      <c r="E95" s="80" t="inlineStr">
         <is>
           <t>113575/3</t>
         </is>
       </c>
-      <c r="F95" s="79" t="inlineStr">
+      <c r="F95" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G95" s="79" t="inlineStr">
+      <c r="G95" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H95" s="80" t="n">
+      <c r="H95" s="81" t="n">
         <v>825.28</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="79" t="inlineStr">
+      <c r="A96" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B96" s="79" t="inlineStr">
+      <c r="B96" s="80" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C96" s="79" t="inlineStr">
+      <c r="C96" s="80" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D96" s="79" t="inlineStr">
+      <c r="D96" s="80" t="inlineStr">
         <is>
           <t>NFS.377682</t>
         </is>
       </c>
-      <c r="E96" s="79" t="inlineStr">
+      <c r="E96" s="80" t="inlineStr">
         <is>
           <t>114092/1</t>
         </is>
       </c>
-      <c r="F96" s="79" t="inlineStr">
+      <c r="F96" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G96" s="79" t="inlineStr">
+      <c r="G96" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H96" s="80" t="n">
+      <c r="H96" s="81" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="79" t="inlineStr">
+      <c r="A97" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B97" s="79" t="inlineStr">
+      <c r="B97" s="80" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="C97" s="79" t="inlineStr">
+      <c r="C97" s="80" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D97" s="79" t="inlineStr">
+      <c r="D97" s="80" t="inlineStr">
         <is>
           <t>NFS.3</t>
         </is>
       </c>
-      <c r="E97" s="79" t="inlineStr">
+      <c r="E97" s="80" t="inlineStr">
         <is>
           <t>111371/1</t>
         </is>
       </c>
-      <c r="F97" s="79" t="inlineStr">
+      <c r="F97" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G97" s="79" t="inlineStr">
+      <c r="G97" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H97" s="80" t="n">
+      <c r="H97" s="81" t="n">
         <v>6300</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="79" t="inlineStr">
+      <c r="A98" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B98" s="79" t="inlineStr">
+      <c r="B98" s="80" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C98" s="79" t="inlineStr">
+      <c r="C98" s="80" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D98" s="79" t="inlineStr">
+      <c r="D98" s="80" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 07.26</t>
         </is>
       </c>
-      <c r="E98" s="79" t="inlineStr">
+      <c r="E98" s="80" t="inlineStr">
         <is>
           <t>113049/1</t>
         </is>
       </c>
-      <c r="F98" s="79" t="inlineStr">
+      <c r="F98" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G98" s="79" t="inlineStr">
+      <c r="G98" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H98" s="80" t="n">
+      <c r="H98" s="81" t="n">
         <v>1151.26</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="79" t="inlineStr">
+      <c r="A99" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B99" s="79" t="inlineStr">
+      <c r="B99" s="80" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C99" s="79" t="inlineStr">
+      <c r="C99" s="80" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D99" s="79" t="inlineStr">
+      <c r="D99" s="80" t="inlineStr">
         <is>
           <t>NFS.66</t>
         </is>
       </c>
-      <c r="E99" s="79" t="inlineStr">
+      <c r="E99" s="80" t="inlineStr">
         <is>
           <t>112107/1</t>
         </is>
       </c>
-      <c r="F99" s="79" t="inlineStr">
+      <c r="F99" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G99" s="79" t="inlineStr">
+      <c r="G99" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H99" s="80" t="n">
+      <c r="H99" s="81" t="n">
         <v>1037.38</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="79" t="inlineStr">
+      <c r="A100" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B100" s="79" t="inlineStr">
+      <c r="B100" s="80" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="C100" s="79" t="inlineStr">
+      <c r="C100" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D100" s="79" t="inlineStr">
+      <c r="D100" s="80" t="inlineStr">
         <is>
           <t>SAL.sal 0626</t>
         </is>
       </c>
-      <c r="E100" s="79" t="inlineStr">
+      <c r="E100" s="80" t="inlineStr">
         <is>
           <t>112402/1</t>
         </is>
       </c>
-      <c r="F100" s="79" t="inlineStr">
+      <c r="F100" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G100" s="79" t="inlineStr">
+      <c r="G100" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H100" s="80" t="n">
+      <c r="H100" s="81" t="n">
         <v>1225</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="79" t="inlineStr">
+      <c r="A101" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B101" s="79" t="inlineStr">
+      <c r="B101" s="80" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C101" s="79" t="inlineStr">
+      <c r="C101" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D101" s="79" t="inlineStr">
+      <c r="D101" s="80" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E101" s="79" t="inlineStr">
+      <c r="E101" s="80" t="inlineStr">
         <is>
           <t>113754/1</t>
         </is>
       </c>
-      <c r="F101" s="79" t="inlineStr">
+      <c r="F101" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G101" s="79" t="inlineStr">
+      <c r="G101" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H101" s="80" t="n">
+      <c r="H101" s="81" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="79" t="inlineStr">
+      <c r="A102" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B102" s="79" t="inlineStr">
+      <c r="B102" s="80" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C102" s="79" t="inlineStr">
+      <c r="C102" s="80" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D102" s="79" t="inlineStr">
+      <c r="D102" s="80" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E102" s="79" t="inlineStr">
+      <c r="E102" s="80" t="inlineStr">
         <is>
           <t>113754/7</t>
         </is>
       </c>
-      <c r="F102" s="79" t="inlineStr">
+      <c r="F102" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G102" s="79" t="inlineStr">
+      <c r="G102" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H102" s="80" t="n">
+      <c r="H102" s="81" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="79" t="inlineStr">
+      <c r="A103" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B103" s="79" t="inlineStr">
+      <c r="B103" s="80" t="inlineStr">
         <is>
           <t>2026-07-01 00:00:00</t>
         </is>
       </c>
-      <c r="C103" s="79" t="inlineStr">
+      <c r="C103" s="80" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D103" s="79" t="inlineStr"/>
-      <c r="E103" s="79" t="inlineStr"/>
-      <c r="F103" s="79" t="inlineStr">
+      <c r="D103" s="80" t="inlineStr"/>
+      <c r="E103" s="80" t="inlineStr"/>
+      <c r="F103" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G103" s="79" t="inlineStr">
+      <c r="G103" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H103" s="80" t="n">
+      <c r="H103" s="81" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="79" t="inlineStr">
+      <c r="A104" s="80" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B104" s="79" t="inlineStr">
+      <c r="B104" s="80" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C104" s="79" t="inlineStr">
+      <c r="C104" s="80" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D104" s="79" t="inlineStr">
+      <c r="D104" s="80" t="inlineStr">
         <is>
           <t>NFS.84</t>
         </is>
       </c>
-      <c r="E104" s="79" t="inlineStr">
+      <c r="E104" s="80" t="inlineStr">
         <is>
           <t>113583/1</t>
         </is>
       </c>
-      <c r="F104" s="79" t="inlineStr">
+      <c r="F104" s="80" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G104" s="79" t="inlineStr">
+      <c r="G104" s="80" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H104" s="80" t="n">
+      <c r="H104" s="81" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="105">
-      <c r="G105" s="81" t="inlineStr">
+      <c r="G105" s="82" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H105" s="82">
+      <c r="H105" s="83">
         <f>SUM(H5:H104)</f>
         <v/>
       </c>
@@ -10685,7 +10693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10878,17 +10886,17 @@
       </c>
       <c r="B9" s="62" t="inlineStr">
         <is>
-          <t>Realizado de jan a abr — A LANÇAR</t>
+          <t>Realizado de ago a dez — a lançar no decorrer do ano</t>
         </is>
       </c>
       <c r="C9" s="62" t="inlineStr">
         <is>
-          <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
+          <t>Jan a jul estão lançados. Ago a dez ficam em branco e serão preenchidos conforme os meses fecharem, com a extração do SIENGE.</t>
         </is>
       </c>
       <c r="D9" s="62" t="inlineStr">
         <is>
-          <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
+          <t>Enquanto isso, o mês de referência do Comparativo deve ficar no último mês fechado (hoje Jul/26) — assim o acumulado compara períodos iguais dos dois lados.</t>
         </is>
       </c>
       <c r="E9" s="62" t="inlineStr">
@@ -10896,63 +10904,63 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr">
-        <is>
-          <t>A LANÇAR</t>
+      <c r="F9" s="68" t="inlineStr">
+        <is>
+          <t>EM ANDAMENTO</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="64" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B10" s="65" t="inlineStr">
         <is>
-          <t>Despesas do TI — A LANÇAR</t>
+          <t>Despesas fora do orçamento identificadas no extrato</t>
         </is>
       </c>
       <c r="C10" s="65" t="inlineStr">
         <is>
-          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
+          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: J H Alves / Monitor Remoto (R$ 20.509) e um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama).</t>
         </is>
       </c>
       <c r="D10" s="65" t="inlineStr">
         <is>
-          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
+          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. Decidir na reunião quais entram no centro de custo da área — e, para os que entrarem, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
         </is>
       </c>
       <c r="E10" s="65" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F10" s="63" t="inlineStr">
-        <is>
-          <t>A LANÇAR</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F10" s="69" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B11" s="62" t="inlineStr">
         <is>
-          <t>Base de meses — reconciliada com a ficha original</t>
+          <t>Despesas do TI — A LANÇAR</t>
         </is>
       </c>
       <c r="C11" s="62" t="inlineStr">
         <is>
-          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
+          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
         </is>
       </c>
       <c r="D11" s="62" t="inlineStr">
         <is>
-          <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
+          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
         </is>
       </c>
       <c r="E11" s="62" t="inlineStr">
@@ -10960,132 +10968,132 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F11" s="68" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F11" s="63" t="inlineStr">
+        <is>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" s="65" t="inlineStr">
         <is>
-          <t>Origem do valor realizado</t>
+          <t>Base de meses — reconciliada com a ficha original</t>
         </is>
       </c>
       <c r="C12" s="65" t="inlineStr">
         <is>
-          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
+          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
         </is>
       </c>
       <c r="D12" s="65" t="inlineStr">
         <is>
-          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
+          <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
         </is>
       </c>
       <c r="E12" s="65" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
-        </is>
-      </c>
-      <c r="F12" s="66" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F12" s="70" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="61" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" s="62" t="inlineStr">
         <is>
-          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
+          <t>Origem do valor realizado — DEFINIDA: SIENGE</t>
         </is>
       </c>
       <c r="C13" s="62" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
+          <t>Será aberto um centro de custo próprio no SIENGE e todos os valores do realizado serão extraídos de lá. Nada será lançado manualmente. O extrato das abas 'Contas Pagas' já vem nesse formato.</t>
         </is>
       </c>
       <c r="D13" s="62" t="inlineStr">
         <is>
-          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
+          <t>O realizado passa a bater com a contabilidade por construção, que era o risco principal. Duas coisas a encaminhar: (1) o de-para entre credor do SIENGE e linha do orçamento — a coluna 'Já está no orçamento?' da aba de resumo é o rascunho dele; (2) definir se a extração sai por regime de caixa ou de competência, ver item 7.</t>
         </is>
       </c>
       <c r="E13" s="62" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F13" s="69" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F13" s="70" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B14" s="65" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
         </is>
       </c>
       <c r="C14" s="65" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
         </is>
       </c>
       <c r="D14" s="65" t="inlineStr">
         <is>
-          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
+          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E14" s="65" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F14" s="66" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F14" s="69" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" s="62" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
       <c r="C15" s="62" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
         </is>
       </c>
       <c r="D15" s="62" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
         </is>
       </c>
       <c r="E15" s="62" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F15" s="66" t="inlineStr">
@@ -11097,22 +11105,22 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" s="65" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
         </is>
       </c>
       <c r="C16" s="65" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
         </is>
       </c>
       <c r="D16" s="65" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
         </is>
       </c>
       <c r="E16" s="65" t="inlineStr">
@@ -11129,30 +11137,62 @@
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="61" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B17" s="62" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C17" s="62" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D17" s="62" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E17" s="62" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F17" s="66" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="64" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="B18" s="65" t="inlineStr">
         <is>
           <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C18" s="65" t="inlineStr">
         <is>
           <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
-      <c r="D17" s="62" t="inlineStr">
-        <is>
-          <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Vale conferir quais contratos pagam no mês seguinte e decidir se o comparativo passa para competência.</t>
-        </is>
-      </c>
-      <c r="E17" s="62" t="inlineStr">
+      <c r="D18" s="65" t="inlineStr">
+        <is>
+          <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Com a extração vindo do SIENGE, basta escolher o regime na hora de gerar o relatório: definir isso UMA vez e manter, para o histórico não misturar critérios.</t>
+        </is>
+      </c>
+      <c r="E18" s="65" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F17" s="67" t="inlineStr">
+      <c r="F18" s="67" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>
@@ -11203,60 +11243,60 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
-        <is>
-          <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
+      <c r="B5" s="72" t="inlineStr">
+        <is>
+          <t>Extraia do SIENGE o relatório do centro de custo do departamento, no mês que fechou. A fonte do realizado é o SIENGE — nada é digitado de cabeça.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
-        <is>
-          <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
+      <c r="B6" s="72" t="inlineStr">
+        <is>
+          <t>Lance na aba REALIZADO, nas células amarelas, o valor de cada linha do orçamento. Item sem gasto no mês: digite 0 — deixar em branco significa 'ainda não lancei'. Use a coluna 'Fonte do dado' para registrar de qual relatório o número saiu, com a data da extração.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="71" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="70" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="71" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="70" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -11271,60 +11311,60 @@
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="70" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="71" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="70" t="inlineStr">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="71" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="70" t="inlineStr">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="71" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="70" t="inlineStr">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="71" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -11339,36 +11379,36 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="70" t="inlineStr">
+      <c r="A19" s="71" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="71" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="70" t="inlineStr">
+      <c r="A20" s="71" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="71" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="70" t="inlineStr">
+      <c r="A21" s="71" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="71" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>
@@ -11527,86 +11567,86 @@
       <c r="J5" s="54" t="n">
         <v>6300</v>
       </c>
-      <c r="K5" s="72" t="n">
+      <c r="K5" s="73" t="n">
         <v>20508.55</v>
       </c>
-      <c r="L5" s="73" t="n"/>
+      <c r="L5" s="74" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="75" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C6" s="75" t="n">
+      <c r="C6" s="76" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="76" t="n">
+      <c r="D6" s="77" t="n">
         <v>2670.84</v>
       </c>
-      <c r="E6" s="76" t="n">
+      <c r="E6" s="77" t="n">
         <v>2986.04</v>
       </c>
-      <c r="F6" s="76" t="n">
+      <c r="F6" s="77" t="n">
         <v>2778.04</v>
       </c>
-      <c r="G6" s="76" t="n">
+      <c r="G6" s="77" t="n">
         <v>2751.04</v>
       </c>
-      <c r="H6" s="76" t="n">
+      <c r="H6" s="77" t="n">
         <v>2719.04</v>
       </c>
-      <c r="I6" s="76" t="n">
+      <c r="I6" s="77" t="n">
         <v>3633.16</v>
       </c>
-      <c r="J6" s="76" t="n">
+      <c r="J6" s="77" t="n">
         <v>2461.04</v>
       </c>
-      <c r="K6" s="77" t="n">
+      <c r="K6" s="78" t="n">
         <v>19999.2</v>
       </c>
-      <c r="L6" s="78" t="inlineStr">
+      <c r="L6" s="79" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius Di Franco</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="74" t="inlineStr">
+      <c r="A7" s="75" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C7" s="75" t="n">
+      <c r="C7" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="76" t="n"/>
-      <c r="E7" s="76" t="n">
+      <c r="D7" s="77" t="n"/>
+      <c r="E7" s="77" t="n">
         <v>234.46</v>
       </c>
-      <c r="F7" s="76" t="n">
+      <c r="F7" s="77" t="n">
         <v>321.76</v>
       </c>
-      <c r="G7" s="76" t="n">
+      <c r="G7" s="77" t="n">
         <v>5393.88</v>
       </c>
-      <c r="H7" s="76" t="n"/>
-      <c r="I7" s="76" t="n"/>
-      <c r="J7" s="76" t="n"/>
-      <c r="K7" s="77" t="n">
+      <c r="H7" s="77" t="n"/>
+      <c r="I7" s="77" t="n"/>
+      <c r="J7" s="77" t="n"/>
+      <c r="K7" s="78" t="n">
         <v>5950.1</v>
       </c>
-      <c r="L7" s="78" t="inlineStr">
+      <c r="L7" s="79" t="inlineStr">
         <is>
           <t>TI-D11 GPT</t>
         </is>
@@ -11645,10 +11685,10 @@
       <c r="J8" s="54" t="n">
         <v>979.4</v>
       </c>
-      <c r="K8" s="72" t="n">
+      <c r="K8" s="73" t="n">
         <v>5228.139999999999</v>
       </c>
-      <c r="L8" s="73" t="n"/>
+      <c r="L8" s="74" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="56" t="inlineStr">
@@ -11681,10 +11721,10 @@
       <c r="J9" s="54" t="n">
         <v>1151.26</v>
       </c>
-      <c r="K9" s="72" t="n">
+      <c r="K9" s="73" t="n">
         <v>3296.12</v>
       </c>
-      <c r="L9" s="73" t="n"/>
+      <c r="L9" s="74" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="56" t="inlineStr">
@@ -11715,48 +11755,48 @@
       <c r="J10" s="54" t="n">
         <v>1037.38</v>
       </c>
-      <c r="K10" s="72" t="n">
+      <c r="K10" s="73" t="n">
         <v>3242.61</v>
       </c>
-      <c r="L10" s="73" t="n"/>
+      <c r="L10" s="74" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="74" t="inlineStr">
+      <c r="A11" s="75" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="75" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C11" s="75" t="n">
+      <c r="C11" s="76" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="76" t="n"/>
-      <c r="E11" s="76" t="n">
+      <c r="D11" s="77" t="n"/>
+      <c r="E11" s="77" t="n">
         <v>485</v>
       </c>
-      <c r="F11" s="76" t="n">
+      <c r="F11" s="77" t="n">
         <v>485</v>
       </c>
-      <c r="G11" s="76" t="n">
+      <c r="G11" s="77" t="n">
         <v>485</v>
       </c>
-      <c r="H11" s="76" t="n">
+      <c r="H11" s="77" t="n">
         <v>485</v>
       </c>
-      <c r="I11" s="76" t="n">
+      <c r="I11" s="77" t="n">
         <v>485</v>
       </c>
-      <c r="J11" s="76" t="n">
+      <c r="J11" s="77" t="n">
         <v>485</v>
       </c>
-      <c r="K11" s="77" t="n">
+      <c r="K11" s="78" t="n">
         <v>2910</v>
       </c>
-      <c r="L11" s="78" t="inlineStr">
+      <c r="L11" s="79" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius (benefício)</t>
         </is>
@@ -11789,10 +11829,10 @@
       <c r="H12" s="54" t="n"/>
       <c r="I12" s="54" t="n"/>
       <c r="J12" s="54" t="n"/>
-      <c r="K12" s="72" t="n">
+      <c r="K12" s="73" t="n">
         <v>954.5500000000001</v>
       </c>
-      <c r="L12" s="73" t="n"/>
+      <c r="L12" s="74" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="56" t="inlineStr">
@@ -11825,10 +11865,10 @@
         <v>137.93</v>
       </c>
       <c r="J13" s="54" t="n"/>
-      <c r="K13" s="72" t="n">
+      <c r="K13" s="73" t="n">
         <v>827.49</v>
       </c>
-      <c r="L13" s="73" t="n"/>
+      <c r="L13" s="74" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="56" t="inlineStr">
@@ -11859,10 +11899,10 @@
         <v>554.58</v>
       </c>
       <c r="J14" s="54" t="n"/>
-      <c r="K14" s="72" t="n">
+      <c r="K14" s="73" t="n">
         <v>758.53</v>
       </c>
-      <c r="L14" s="73" t="n"/>
+      <c r="L14" s="74" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="56" t="inlineStr">
@@ -11899,10 +11939,10 @@
       <c r="J15" s="54" t="n">
         <v>82.5</v>
       </c>
-      <c r="K15" s="72" t="n">
+      <c r="K15" s="73" t="n">
         <v>690</v>
       </c>
-      <c r="L15" s="73" t="n"/>
+      <c r="L15" s="74" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
@@ -11935,10 +11975,10 @@
       <c r="J16" s="54" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="K16" s="72" t="n">
+      <c r="K16" s="73" t="n">
         <v>562.42</v>
       </c>
-      <c r="L16" s="73" t="n"/>
+      <c r="L16" s="74" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="56" t="inlineStr">
@@ -11963,10 +12003,10 @@
         <v>183.6</v>
       </c>
       <c r="J17" s="54" t="n"/>
-      <c r="K17" s="72" t="n">
+      <c r="K17" s="73" t="n">
         <v>183.6</v>
       </c>
-      <c r="L17" s="73" t="n"/>
+      <c r="L17" s="74" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="51" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -150,7 +150,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -214,17 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -259,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -403,16 +398,13 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -425,13 +417,13 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1935,3964 +1927,3964 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="80" t="inlineStr">
+      <c r="A5" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="80" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>09/01/2026</t>
         </is>
       </c>
-      <c r="C5" s="80" t="inlineStr">
+      <c r="C5" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D5" s="80" t="inlineStr">
+      <c r="D5" s="79" t="inlineStr">
         <is>
           <t>FAT.11.25</t>
         </is>
       </c>
-      <c r="E5" s="80" t="inlineStr">
+      <c r="E5" s="79" t="inlineStr">
         <is>
           <t>95941/1</t>
         </is>
       </c>
-      <c r="F5" s="80" t="inlineStr">
+      <c r="F5" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G5" s="80" t="inlineStr">
+      <c r="G5" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H5" s="81" t="n">
+      <c r="H5" s="80" t="n">
         <v>407.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="80" t="inlineStr">
+      <c r="A6" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B6" s="80" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C6" s="80" t="inlineStr">
+      <c r="C6" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D6" s="80" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>FAT.01.26</t>
         </is>
       </c>
-      <c r="E6" s="80" t="inlineStr">
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>97478/1</t>
         </is>
       </c>
-      <c r="F6" s="80" t="inlineStr">
+      <c r="F6" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G6" s="80" t="inlineStr">
+      <c r="G6" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H6" s="81" t="n">
+      <c r="H6" s="80" t="n">
         <v>390.95</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="80" t="inlineStr">
+      <c r="A7" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C7" s="80" t="inlineStr">
+      <c r="C7" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D7" s="80" t="inlineStr">
+      <c r="D7" s="79" t="inlineStr">
         <is>
           <t>FAT.184180933</t>
         </is>
       </c>
-      <c r="E7" s="80" t="inlineStr">
+      <c r="E7" s="79" t="inlineStr">
         <is>
           <t>97480/1</t>
         </is>
       </c>
-      <c r="F7" s="80" t="inlineStr">
+      <c r="F7" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G7" s="80" t="inlineStr">
+      <c r="G7" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H7" s="81" t="n">
+      <c r="H7" s="80" t="n">
         <v>123.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="80" t="inlineStr">
+      <c r="A8" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B8" s="80" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C8" s="80" t="inlineStr">
+      <c r="C8" s="79" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D8" s="80" t="inlineStr">
+      <c r="D8" s="79" t="inlineStr">
         <is>
           <t>NFS.347106</t>
         </is>
       </c>
-      <c r="E8" s="80" t="inlineStr">
+      <c r="E8" s="79" t="inlineStr">
         <is>
           <t>96534/1</t>
         </is>
       </c>
-      <c r="F8" s="80" t="inlineStr">
+      <c r="F8" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G8" s="80" t="inlineStr">
+      <c r="G8" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H8" s="81" t="n">
+      <c r="H8" s="80" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="80" t="inlineStr">
+      <c r="A9" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="C9" s="80" t="inlineStr">
+      <c r="C9" s="79" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D9" s="80" t="inlineStr">
+      <c r="D9" s="79" t="inlineStr">
         <is>
           <t>NFS.70</t>
         </is>
       </c>
-      <c r="E9" s="80" t="inlineStr">
+      <c r="E9" s="79" t="inlineStr">
         <is>
           <t>96602/1</t>
         </is>
       </c>
-      <c r="F9" s="80" t="inlineStr">
+      <c r="F9" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G9" s="80" t="inlineStr">
+      <c r="G9" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H9" s="81" t="n">
+      <c r="H9" s="80" t="n">
         <v>4311.56</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="80" t="inlineStr">
+      <c r="A10" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="C10" s="80" t="inlineStr">
+      <c r="C10" s="79" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D10" s="80" t="inlineStr">
+      <c r="D10" s="79" t="inlineStr">
         <is>
           <t>AV.LIC EMAILS 01.25</t>
         </is>
       </c>
-      <c r="E10" s="80" t="inlineStr">
+      <c r="E10" s="79" t="inlineStr">
         <is>
           <t>96014/1</t>
         </is>
       </c>
-      <c r="F10" s="80" t="inlineStr">
+      <c r="F10" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G10" s="80" t="inlineStr">
+      <c r="G10" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H10" s="81" t="n">
+      <c r="H10" s="80" t="n">
         <v>6.2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="80" t="inlineStr">
+      <c r="A11" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>25/01/2026</t>
         </is>
       </c>
-      <c r="C11" s="80" t="inlineStr">
+      <c r="C11" s="79" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D11" s="80" t="inlineStr">
+      <c r="D11" s="79" t="inlineStr">
         <is>
           <t>BOL.13.01</t>
         </is>
       </c>
-      <c r="E11" s="80" t="inlineStr">
+      <c r="E11" s="79" t="inlineStr">
         <is>
           <t>96623/1</t>
         </is>
       </c>
-      <c r="F11" s="80" t="inlineStr">
+      <c r="F11" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G11" s="80" t="inlineStr">
+      <c r="G11" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H11" s="81" t="n">
+      <c r="H11" s="80" t="n">
         <v>918.08</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="80" t="inlineStr">
+      <c r="A12" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C12" s="80" t="inlineStr">
+      <c r="C12" s="79" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D12" s="80" t="inlineStr">
+      <c r="D12" s="79" t="inlineStr">
         <is>
           <t>FAT.2682</t>
         </is>
       </c>
-      <c r="E12" s="80" t="inlineStr">
+      <c r="E12" s="79" t="inlineStr">
         <is>
           <t>96458/1</t>
         </is>
       </c>
-      <c r="F12" s="80" t="inlineStr">
+      <c r="F12" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G12" s="80" t="inlineStr">
+      <c r="G12" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H12" s="81" t="n">
+      <c r="H12" s="80" t="n">
         <v>723.75</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="80" t="inlineStr">
+      <c r="A13" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="C13" s="80" t="inlineStr">
+      <c r="C13" s="79" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D13" s="80" t="inlineStr">
+      <c r="D13" s="79" t="inlineStr">
         <is>
           <t>FAT.2011241340</t>
         </is>
       </c>
-      <c r="E13" s="80" t="inlineStr">
+      <c r="E13" s="79" t="inlineStr">
         <is>
           <t>96088/1</t>
         </is>
       </c>
-      <c r="F13" s="80" t="inlineStr">
+      <c r="F13" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G13" s="80" t="inlineStr">
+      <c r="G13" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H13" s="81" t="n">
+      <c r="H13" s="80" t="n">
         <v>51.63</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="80" t="inlineStr">
+      <c r="A14" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B14" s="80" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>22/01/2026</t>
         </is>
       </c>
-      <c r="C14" s="80" t="inlineStr">
+      <c r="C14" s="79" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D14" s="80" t="inlineStr">
+      <c r="D14" s="79" t="inlineStr">
         <is>
           <t>FAT.5664047504</t>
         </is>
       </c>
-      <c r="E14" s="80" t="inlineStr">
+      <c r="E14" s="79" t="inlineStr">
         <is>
           <t>96789/1</t>
         </is>
       </c>
-      <c r="F14" s="80" t="inlineStr">
+      <c r="F14" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G14" s="80" t="inlineStr">
+      <c r="G14" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H14" s="81" t="n">
+      <c r="H14" s="80" t="n">
         <v>331.42</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="80" t="inlineStr">
+      <c r="A15" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B15" s="80" t="inlineStr">
+      <c r="B15" s="79" t="inlineStr">
         <is>
           <t>26/01/2026</t>
         </is>
       </c>
-      <c r="C15" s="80" t="inlineStr">
+      <c r="C15" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D15" s="80" t="inlineStr">
+      <c r="D15" s="79" t="inlineStr">
         <is>
           <t>CX.16.01.26</t>
         </is>
       </c>
-      <c r="E15" s="80" t="inlineStr">
+      <c r="E15" s="79" t="inlineStr">
         <is>
           <t>97067/1</t>
         </is>
       </c>
-      <c r="F15" s="80" t="inlineStr">
+      <c r="F15" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G15" s="80" t="inlineStr">
+      <c r="G15" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H15" s="81" t="n">
+      <c r="H15" s="80" t="n">
         <v>39.84</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="80" t="inlineStr">
+      <c r="A16" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B16" s="80" t="inlineStr">
+      <c r="B16" s="79" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="C16" s="80" t="inlineStr">
+      <c r="C16" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D16" s="80" t="inlineStr">
+      <c r="D16" s="79" t="inlineStr">
         <is>
           <t>SAL.Sal_122025</t>
         </is>
       </c>
-      <c r="E16" s="80" t="inlineStr">
+      <c r="E16" s="79" t="inlineStr">
         <is>
           <t>96252/1</t>
         </is>
       </c>
-      <c r="F16" s="80" t="inlineStr">
+      <c r="F16" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G16" s="80" t="inlineStr">
+      <c r="G16" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H16" s="81" t="n">
+      <c r="H16" s="80" t="n">
         <v>1602</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="80" t="inlineStr">
+      <c r="A17" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B17" s="80" t="inlineStr">
+      <c r="B17" s="79" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="C17" s="80" t="inlineStr">
+      <c r="C17" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D17" s="80" t="inlineStr">
+      <c r="D17" s="79" t="inlineStr">
         <is>
           <t>SAL.VALE_ 012026</t>
         </is>
       </c>
-      <c r="E17" s="80" t="inlineStr">
+      <c r="E17" s="79" t="inlineStr">
         <is>
           <t>97269/1</t>
         </is>
       </c>
-      <c r="F17" s="80" t="inlineStr">
+      <c r="F17" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G17" s="80" t="inlineStr">
+      <c r="G17" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H17" s="81" t="n">
+      <c r="H17" s="80" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="80" t="inlineStr">
+      <c r="A18" s="79" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B18" s="80" t="inlineStr">
+      <c r="B18" s="79" t="inlineStr">
         <is>
           <t>27/01/2026</t>
         </is>
       </c>
-      <c r="C18" s="80" t="inlineStr">
+      <c r="C18" s="79" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D18" s="80" t="inlineStr">
+      <c r="D18" s="79" t="inlineStr">
         <is>
           <t>BOL.1</t>
         </is>
       </c>
-      <c r="E18" s="80" t="inlineStr">
+      <c r="E18" s="79" t="inlineStr">
         <is>
           <t>97204/1</t>
         </is>
       </c>
-      <c r="F18" s="80" t="inlineStr">
+      <c r="F18" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G18" s="80" t="inlineStr">
+      <c r="G18" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H18" s="81" t="n">
+      <c r="H18" s="80" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="80" t="inlineStr">
+      <c r="A19" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B19" s="80" t="inlineStr">
+      <c r="B19" s="79" t="inlineStr">
         <is>
           <t>04/02/2026</t>
         </is>
       </c>
-      <c r="C19" s="80" t="inlineStr">
+      <c r="C19" s="79" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D19" s="80" t="inlineStr">
+      <c r="D19" s="79" t="inlineStr">
         <is>
           <t>AV.04.02.26</t>
         </is>
       </c>
-      <c r="E19" s="80" t="inlineStr">
+      <c r="E19" s="79" t="inlineStr">
         <is>
           <t>98500/1</t>
         </is>
       </c>
-      <c r="F19" s="80" t="inlineStr">
+      <c r="F19" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G19" s="80" t="inlineStr">
+      <c r="G19" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H19" s="81" t="n">
+      <c r="H19" s="80" t="n">
         <v>26.67</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="80" t="inlineStr">
+      <c r="A20" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C20" s="80" t="inlineStr">
+      <c r="C20" s="79" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D20" s="80" t="inlineStr">
+      <c r="D20" s="79" t="inlineStr">
         <is>
           <t>AV.12.02.26 LCW</t>
         </is>
       </c>
-      <c r="E20" s="80" t="inlineStr">
+      <c r="E20" s="79" t="inlineStr">
         <is>
           <t>99336/1</t>
         </is>
       </c>
-      <c r="F20" s="80" t="inlineStr">
+      <c r="F20" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G20" s="80" t="inlineStr">
+      <c r="G20" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H20" s="81" t="n">
+      <c r="H20" s="80" t="n">
         <v>72.58</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="80" t="inlineStr">
+      <c r="A21" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B21" s="80" t="inlineStr">
+      <c r="B21" s="79" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C21" s="80" t="inlineStr">
+      <c r="C21" s="79" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D21" s="80" t="inlineStr">
+      <c r="D21" s="79" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E21" s="80" t="inlineStr">
+      <c r="E21" s="79" t="inlineStr">
         <is>
           <t>95104/2</t>
         </is>
       </c>
-      <c r="F21" s="80" t="inlineStr">
+      <c r="F21" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G21" s="80" t="inlineStr">
+      <c r="G21" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H21" s="81" t="n">
+      <c r="H21" s="80" t="n">
         <v>234.46</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="80" t="inlineStr">
+      <c r="A22" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B22" s="80" t="inlineStr">
+      <c r="B22" s="79" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C22" s="80" t="inlineStr">
+      <c r="C22" s="79" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D22" s="80" t="inlineStr">
+      <c r="D22" s="79" t="inlineStr">
         <is>
           <t>FAT.3575377</t>
         </is>
       </c>
-      <c r="E22" s="80" t="inlineStr">
+      <c r="E22" s="79" t="inlineStr">
         <is>
           <t>100172/1</t>
         </is>
       </c>
-      <c r="F22" s="80" t="inlineStr">
+      <c r="F22" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G22" s="80" t="inlineStr">
+      <c r="G22" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H22" s="81" t="n">
+      <c r="H22" s="80" t="n">
         <v>52.32</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="80" t="inlineStr">
+      <c r="A23" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B23" s="80" t="inlineStr">
+      <c r="B23" s="79" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C23" s="80" t="inlineStr">
+      <c r="C23" s="79" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D23" s="80" t="inlineStr">
+      <c r="D23" s="79" t="inlineStr">
         <is>
           <t>FAT.5290953</t>
         </is>
       </c>
-      <c r="E23" s="80" t="inlineStr">
+      <c r="E23" s="79" t="inlineStr">
         <is>
           <t>100173/1</t>
         </is>
       </c>
-      <c r="F23" s="80" t="inlineStr">
+      <c r="F23" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G23" s="80" t="inlineStr">
+      <c r="G23" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H23" s="81" t="n">
+      <c r="H23" s="80" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="80" t="inlineStr">
+      <c r="A24" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B24" s="80" t="inlineStr">
+      <c r="B24" s="79" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C24" s="80" t="inlineStr">
+      <c r="C24" s="79" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D24" s="80" t="inlineStr">
+      <c r="D24" s="79" t="inlineStr">
         <is>
           <t>BOL.141</t>
         </is>
       </c>
-      <c r="E24" s="80" t="inlineStr">
+      <c r="E24" s="79" t="inlineStr">
         <is>
           <t>99947/1</t>
         </is>
       </c>
-      <c r="F24" s="80" t="inlineStr">
+      <c r="F24" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G24" s="80" t="inlineStr">
+      <c r="G24" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H24" s="81" t="n">
+      <c r="H24" s="80" t="n">
         <v>338.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="80" t="inlineStr">
+      <c r="A25" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B25" s="80" t="inlineStr">
+      <c r="B25" s="79" t="inlineStr">
         <is>
           <t>13/02/2026</t>
         </is>
       </c>
-      <c r="C25" s="80" t="inlineStr">
+      <c r="C25" s="79" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D25" s="80" t="inlineStr">
+      <c r="D25" s="79" t="inlineStr">
         <is>
           <t>BOL.26449</t>
         </is>
       </c>
-      <c r="E25" s="80" t="inlineStr">
+      <c r="E25" s="79" t="inlineStr">
         <is>
           <t>99484/1</t>
         </is>
       </c>
-      <c r="F25" s="80" t="inlineStr">
+      <c r="F25" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G25" s="80" t="inlineStr">
+      <c r="G25" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H25" s="81" t="n">
+      <c r="H25" s="80" t="n">
         <v>137.94</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="80" t="inlineStr">
+      <c r="A26" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B26" s="80" t="inlineStr">
+      <c r="B26" s="79" t="inlineStr">
         <is>
           <t>19/02/2026</t>
         </is>
       </c>
-      <c r="C26" s="80" t="inlineStr">
+      <c r="C26" s="79" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D26" s="80" t="inlineStr">
+      <c r="D26" s="79" t="inlineStr">
         <is>
           <t>BOL.27256</t>
         </is>
       </c>
-      <c r="E26" s="80" t="inlineStr">
+      <c r="E26" s="79" t="inlineStr">
         <is>
           <t>99486/1</t>
         </is>
       </c>
-      <c r="F26" s="80" t="inlineStr">
+      <c r="F26" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G26" s="80" t="inlineStr">
+      <c r="G26" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H26" s="81" t="n">
+      <c r="H26" s="80" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="80" t="inlineStr">
+      <c r="A27" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B27" s="80" t="inlineStr">
+      <c r="B27" s="79" t="inlineStr">
         <is>
           <t>06/02/2026</t>
         </is>
       </c>
-      <c r="C27" s="80" t="inlineStr">
+      <c r="C27" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D27" s="80" t="inlineStr">
+      <c r="D27" s="79" t="inlineStr">
         <is>
           <t>SAL.SAL JANEIRO 2026</t>
         </is>
       </c>
-      <c r="E27" s="80" t="inlineStr">
+      <c r="E27" s="79" t="inlineStr">
         <is>
           <t>98811/1</t>
         </is>
       </c>
-      <c r="F27" s="80" t="inlineStr">
+      <c r="F27" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G27" s="80" t="inlineStr">
+      <c r="G27" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H27" s="81" t="n">
+      <c r="H27" s="80" t="n">
         <v>1750</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="80" t="inlineStr">
+      <c r="A28" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B28" s="80" t="inlineStr">
+      <c r="B28" s="79" t="inlineStr">
         <is>
           <t>20/02/2026</t>
         </is>
       </c>
-      <c r="C28" s="80" t="inlineStr">
+      <c r="C28" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D28" s="80" t="inlineStr">
+      <c r="D28" s="79" t="inlineStr">
         <is>
           <t>SAL.VALE FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E28" s="80" t="inlineStr">
+      <c r="E28" s="79" t="inlineStr">
         <is>
           <t>99890/1</t>
         </is>
       </c>
-      <c r="F28" s="80" t="inlineStr">
+      <c r="F28" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G28" s="80" t="inlineStr">
+      <c r="G28" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H28" s="81" t="n">
+      <c r="H28" s="80" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="80" t="inlineStr">
+      <c r="A29" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B29" s="80" t="inlineStr">
+      <c r="B29" s="79" t="inlineStr">
         <is>
           <t>2026-02-20 00:00:00</t>
         </is>
       </c>
-      <c r="C29" s="80" t="inlineStr">
+      <c r="C29" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D29" s="80" t="inlineStr">
+      <c r="D29" s="79" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E29" s="80" t="inlineStr">
+      <c r="E29" s="79" t="inlineStr">
         <is>
           <t>113754/2</t>
         </is>
       </c>
-      <c r="F29" s="80" t="inlineStr">
+      <c r="F29" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G29" s="80" t="inlineStr">
+      <c r="G29" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H29" s="81" t="n">
+      <c r="H29" s="80" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="80" t="inlineStr">
+      <c r="A30" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B30" s="80" t="inlineStr">
+      <c r="B30" s="79" t="inlineStr">
         <is>
           <t>2026-02-01 00:00:00</t>
         </is>
       </c>
-      <c r="C30" s="80" t="inlineStr">
+      <c r="C30" s="79" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D30" s="80" t="inlineStr"/>
-      <c r="E30" s="80" t="inlineStr"/>
-      <c r="F30" s="80" t="inlineStr">
+      <c r="D30" s="79" t="inlineStr"/>
+      <c r="E30" s="79" t="inlineStr"/>
+      <c r="F30" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G30" s="80" t="inlineStr">
+      <c r="G30" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H30" s="81" t="n">
+      <c r="H30" s="80" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="80" t="inlineStr">
+      <c r="A31" s="79" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B31" s="80" t="inlineStr">
+      <c r="B31" s="79" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C31" s="80" t="inlineStr">
+      <c r="C31" s="79" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D31" s="80" t="inlineStr">
+      <c r="D31" s="79" t="inlineStr">
         <is>
           <t>NFS.1430</t>
         </is>
       </c>
-      <c r="E31" s="80" t="inlineStr">
+      <c r="E31" s="79" t="inlineStr">
         <is>
           <t>99956/1</t>
         </is>
       </c>
-      <c r="F31" s="80" t="inlineStr">
+      <c r="F31" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G31" s="80" t="inlineStr">
+      <c r="G31" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H31" s="81" t="n">
+      <c r="H31" s="80" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="80" t="inlineStr">
+      <c r="A32" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B32" s="80" t="inlineStr">
+      <c r="B32" s="79" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C32" s="80" t="inlineStr">
+      <c r="C32" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D32" s="80" t="inlineStr">
+      <c r="D32" s="79" t="inlineStr">
         <is>
           <t>FAT.5042829</t>
         </is>
       </c>
-      <c r="E32" s="80" t="inlineStr">
+      <c r="E32" s="79" t="inlineStr">
         <is>
           <t>100503/1</t>
         </is>
       </c>
-      <c r="F32" s="80" t="inlineStr">
+      <c r="F32" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G32" s="80" t="inlineStr">
+      <c r="G32" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H32" s="81" t="n">
+      <c r="H32" s="80" t="n">
         <v>87.69</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="80" t="inlineStr">
+      <c r="A33" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B33" s="80" t="inlineStr">
+      <c r="B33" s="79" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C33" s="80" t="inlineStr">
+      <c r="C33" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D33" s="80" t="inlineStr">
+      <c r="D33" s="79" t="inlineStr">
         <is>
           <t>FAT.5042827</t>
         </is>
       </c>
-      <c r="E33" s="80" t="inlineStr">
+      <c r="E33" s="79" t="inlineStr">
         <is>
           <t>100504/1</t>
         </is>
       </c>
-      <c r="F33" s="80" t="inlineStr">
+      <c r="F33" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G33" s="80" t="inlineStr">
+      <c r="G33" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H33" s="81" t="n">
+      <c r="H33" s="80" t="n">
         <v>382.4</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="80" t="inlineStr">
+      <c r="A34" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B34" s="80" t="inlineStr">
+      <c r="B34" s="79" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="C34" s="80" t="inlineStr">
+      <c r="C34" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D34" s="80" t="inlineStr">
+      <c r="D34" s="79" t="inlineStr">
         <is>
           <t>FAT.8910508</t>
         </is>
       </c>
-      <c r="E34" s="80" t="inlineStr">
+      <c r="E34" s="79" t="inlineStr">
         <is>
           <t>102706/1</t>
         </is>
       </c>
-      <c r="F34" s="80" t="inlineStr">
+      <c r="F34" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G34" s="80" t="inlineStr">
+      <c r="G34" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H34" s="81" t="n">
+      <c r="H34" s="80" t="n">
         <v>429.49</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="80" t="inlineStr">
+      <c r="A35" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B35" s="80" t="inlineStr">
+      <c r="B35" s="79" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="C35" s="80" t="inlineStr">
+      <c r="C35" s="79" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D35" s="80" t="inlineStr">
+      <c r="D35" s="79" t="inlineStr">
         <is>
           <t>NFS.351653</t>
         </is>
       </c>
-      <c r="E35" s="80" t="inlineStr">
+      <c r="E35" s="79" t="inlineStr">
         <is>
           <t>100083/1</t>
         </is>
       </c>
-      <c r="F35" s="80" t="inlineStr">
+      <c r="F35" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G35" s="80" t="inlineStr">
+      <c r="G35" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H35" s="81" t="n">
+      <c r="H35" s="80" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="80" t="inlineStr">
+      <c r="A36" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B36" s="80" t="inlineStr">
+      <c r="B36" s="79" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="C36" s="80" t="inlineStr">
+      <c r="C36" s="79" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D36" s="80" t="inlineStr">
+      <c r="D36" s="79" t="inlineStr">
         <is>
           <t>NFS.359396</t>
         </is>
       </c>
-      <c r="E36" s="80" t="inlineStr">
+      <c r="E36" s="79" t="inlineStr">
         <is>
           <t>102608/1</t>
         </is>
       </c>
-      <c r="F36" s="80" t="inlineStr">
+      <c r="F36" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G36" s="80" t="inlineStr">
+      <c r="G36" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H36" s="81" t="n">
+      <c r="H36" s="80" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="80" t="inlineStr">
+      <c r="A37" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B37" s="80" t="inlineStr">
+      <c r="B37" s="79" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="C37" s="80" t="inlineStr">
+      <c r="C37" s="79" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D37" s="80" t="inlineStr">
+      <c r="D37" s="79" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E37" s="80" t="inlineStr">
+      <c r="E37" s="79" t="inlineStr">
         <is>
           <t>95104/3</t>
         </is>
       </c>
-      <c r="F37" s="80" t="inlineStr">
+      <c r="F37" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G37" s="80" t="inlineStr">
+      <c r="G37" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H37" s="81" t="n">
+      <c r="H37" s="80" t="n">
         <v>111.38</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="80" t="inlineStr">
+      <c r="A38" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B38" s="80" t="inlineStr">
+      <c r="B38" s="79" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C38" s="80" t="inlineStr">
+      <c r="C38" s="79" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D38" s="80" t="inlineStr">
+      <c r="D38" s="79" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E38" s="80" t="inlineStr">
+      <c r="E38" s="79" t="inlineStr">
         <is>
           <t>95104/4</t>
         </is>
       </c>
-      <c r="F38" s="80" t="inlineStr">
+      <c r="F38" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G38" s="80" t="inlineStr">
+      <c r="G38" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H38" s="81" t="n">
+      <c r="H38" s="80" t="n">
         <v>210.38</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="80" t="inlineStr">
+      <c r="A39" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B39" s="80" t="inlineStr">
+      <c r="B39" s="79" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="C39" s="80" t="inlineStr">
+      <c r="C39" s="79" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D39" s="80" t="inlineStr">
+      <c r="D39" s="79" t="inlineStr">
         <is>
           <t>FAT.2024588614</t>
         </is>
       </c>
-      <c r="E39" s="80" t="inlineStr">
+      <c r="E39" s="79" t="inlineStr">
         <is>
           <t>102316/1</t>
         </is>
       </c>
-      <c r="F39" s="80" t="inlineStr">
+      <c r="F39" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G39" s="80" t="inlineStr">
+      <c r="G39" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H39" s="81" t="n">
+      <c r="H39" s="80" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="80" t="inlineStr">
+      <c r="A40" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B40" s="80" t="inlineStr">
+      <c r="B40" s="79" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C40" s="80" t="inlineStr">
+      <c r="C40" s="79" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D40" s="80" t="inlineStr">
+      <c r="D40" s="79" t="inlineStr">
         <is>
           <t>BOL.5708173302</t>
         </is>
       </c>
-      <c r="E40" s="80" t="inlineStr">
+      <c r="E40" s="79" t="inlineStr">
         <is>
           <t>102057/1</t>
         </is>
       </c>
-      <c r="F40" s="80" t="inlineStr">
+      <c r="F40" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G40" s="80" t="inlineStr">
+      <c r="G40" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H40" s="81" t="n">
+      <c r="H40" s="80" t="n">
         <v>284.63</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="80" t="inlineStr">
+      <c r="A41" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B41" s="80" t="inlineStr">
+      <c r="B41" s="79" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="C41" s="80" t="inlineStr">
+      <c r="C41" s="79" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D41" s="80" t="inlineStr">
+      <c r="D41" s="79" t="inlineStr">
         <is>
           <t>BOL.28049</t>
         </is>
       </c>
-      <c r="E41" s="80" t="inlineStr">
+      <c r="E41" s="79" t="inlineStr">
         <is>
           <t>100887/1</t>
         </is>
       </c>
-      <c r="F41" s="80" t="inlineStr">
+      <c r="F41" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G41" s="80" t="inlineStr">
+      <c r="G41" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H41" s="81" t="n">
+      <c r="H41" s="80" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="80" t="inlineStr">
+      <c r="A42" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B42" s="80" t="inlineStr">
+      <c r="B42" s="79" t="inlineStr">
         <is>
           <t>06/03/2026</t>
         </is>
       </c>
-      <c r="C42" s="80" t="inlineStr">
+      <c r="C42" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D42" s="80" t="inlineStr">
+      <c r="D42" s="79" t="inlineStr">
         <is>
           <t>SAL.SAL FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E42" s="80" t="inlineStr">
+      <c r="E42" s="79" t="inlineStr">
         <is>
           <t>101276/1</t>
         </is>
       </c>
-      <c r="F42" s="80" t="inlineStr">
+      <c r="F42" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G42" s="80" t="inlineStr">
+      <c r="G42" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H42" s="81" t="n">
+      <c r="H42" s="80" t="n">
         <v>1542</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="80" t="inlineStr">
+      <c r="A43" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B43" s="80" t="inlineStr">
+      <c r="B43" s="79" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C43" s="80" t="inlineStr">
+      <c r="C43" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D43" s="80" t="inlineStr">
+      <c r="D43" s="79" t="inlineStr">
         <is>
           <t>SAL.VALE 032026</t>
         </is>
       </c>
-      <c r="E43" s="80" t="inlineStr">
+      <c r="E43" s="79" t="inlineStr">
         <is>
           <t>102295/1</t>
         </is>
       </c>
-      <c r="F43" s="80" t="inlineStr">
+      <c r="F43" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G43" s="80" t="inlineStr">
+      <c r="G43" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H43" s="81" t="n">
+      <c r="H43" s="80" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="80" t="inlineStr">
+      <c r="A44" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B44" s="80" t="inlineStr">
+      <c r="B44" s="79" t="inlineStr">
         <is>
           <t>2026-03-20 00:00:00</t>
         </is>
       </c>
-      <c r="C44" s="80" t="inlineStr">
+      <c r="C44" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D44" s="80" t="inlineStr">
+      <c r="D44" s="79" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E44" s="80" t="inlineStr">
+      <c r="E44" s="79" t="inlineStr">
         <is>
           <t>113754/3</t>
         </is>
       </c>
-      <c r="F44" s="80" t="inlineStr">
+      <c r="F44" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G44" s="80" t="inlineStr">
+      <c r="G44" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H44" s="81" t="n">
+      <c r="H44" s="80" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="80" t="inlineStr">
+      <c r="A45" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B45" s="80" t="inlineStr">
+      <c r="B45" s="79" t="inlineStr">
         <is>
           <t>2026-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="C45" s="80" t="inlineStr">
+      <c r="C45" s="79" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D45" s="80" t="inlineStr"/>
-      <c r="E45" s="80" t="inlineStr"/>
-      <c r="F45" s="80" t="inlineStr">
+      <c r="D45" s="79" t="inlineStr"/>
+      <c r="E45" s="79" t="inlineStr"/>
+      <c r="F45" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G45" s="80" t="inlineStr">
+      <c r="G45" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H45" s="81" t="n">
+      <c r="H45" s="80" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="80" t="inlineStr">
+      <c r="A46" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B46" s="80" t="inlineStr">
+      <c r="B46" s="79" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C46" s="80" t="inlineStr">
+      <c r="C46" s="79" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D46" s="80" t="inlineStr">
+      <c r="D46" s="79" t="inlineStr">
         <is>
           <t>NFS.1500</t>
         </is>
       </c>
-      <c r="E46" s="80" t="inlineStr">
+      <c r="E46" s="79" t="inlineStr">
         <is>
           <t>102432/1</t>
         </is>
       </c>
-      <c r="F46" s="80" t="inlineStr">
+      <c r="F46" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G46" s="80" t="inlineStr">
+      <c r="G46" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H46" s="81" t="n">
+      <c r="H46" s="80" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="80" t="inlineStr">
+      <c r="A47" s="79" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B47" s="80" t="inlineStr">
+      <c r="B47" s="79" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C47" s="80" t="inlineStr">
+      <c r="C47" s="79" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D47" s="80" t="inlineStr">
+      <c r="D47" s="79" t="inlineStr">
         <is>
           <t>NFS.1534</t>
         </is>
       </c>
-      <c r="E47" s="80" t="inlineStr">
+      <c r="E47" s="79" t="inlineStr">
         <is>
           <t>102434/1</t>
         </is>
       </c>
-      <c r="F47" s="80" t="inlineStr">
+      <c r="F47" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G47" s="80" t="inlineStr">
+      <c r="G47" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H47" s="81" t="n">
+      <c r="H47" s="80" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="80" t="inlineStr">
+      <c r="A48" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B48" s="80" t="inlineStr">
+      <c r="B48" s="79" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C48" s="80" t="inlineStr">
+      <c r="C48" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D48" s="80" t="inlineStr">
+      <c r="D48" s="79" t="inlineStr">
         <is>
           <t>FAT.8910315</t>
         </is>
       </c>
-      <c r="E48" s="80" t="inlineStr">
+      <c r="E48" s="79" t="inlineStr">
         <is>
           <t>105607/1</t>
         </is>
       </c>
-      <c r="F48" s="80" t="inlineStr">
+      <c r="F48" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G48" s="80" t="inlineStr">
+      <c r="G48" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H48" s="81" t="n">
+      <c r="H48" s="80" t="n">
         <v>11.99</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="80" t="inlineStr">
+      <c r="A49" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B49" s="80" t="inlineStr">
+      <c r="B49" s="79" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C49" s="80" t="inlineStr">
+      <c r="C49" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D49" s="80" t="inlineStr">
+      <c r="D49" s="79" t="inlineStr">
         <is>
           <t>FAT.13443658</t>
         </is>
       </c>
-      <c r="E49" s="80" t="inlineStr">
+      <c r="E49" s="79" t="inlineStr">
         <is>
           <t>105676/1</t>
         </is>
       </c>
-      <c r="F49" s="80" t="inlineStr">
+      <c r="F49" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G49" s="80" t="inlineStr">
+      <c r="G49" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H49" s="81" t="n">
+      <c r="H49" s="80" t="n">
         <v>557.63</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="80" t="inlineStr">
+      <c r="A50" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B50" s="80" t="inlineStr">
+      <c r="B50" s="79" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C50" s="80" t="inlineStr">
+      <c r="C50" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D50" s="80" t="inlineStr">
+      <c r="D50" s="79" t="inlineStr">
         <is>
           <t>FAT.13443664</t>
         </is>
       </c>
-      <c r="E50" s="80" t="inlineStr">
+      <c r="E50" s="79" t="inlineStr">
         <is>
           <t>105677/1</t>
         </is>
       </c>
-      <c r="F50" s="80" t="inlineStr">
+      <c r="F50" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G50" s="80" t="inlineStr">
+      <c r="G50" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H50" s="81" t="n">
+      <c r="H50" s="80" t="n">
         <v>132.09</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="80" t="inlineStr">
+      <c r="A51" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B51" s="80" t="inlineStr">
+      <c r="B51" s="79" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C51" s="80" t="inlineStr">
+      <c r="C51" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D51" s="80" t="inlineStr">
+      <c r="D51" s="79" t="inlineStr">
         <is>
           <t>FAT.13443112</t>
         </is>
       </c>
-      <c r="E51" s="80" t="inlineStr">
+      <c r="E51" s="79" t="inlineStr">
         <is>
           <t>105792/1</t>
         </is>
       </c>
-      <c r="F51" s="80" t="inlineStr">
+      <c r="F51" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G51" s="80" t="inlineStr">
+      <c r="G51" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H51" s="81" t="n">
+      <c r="H51" s="80" t="n">
         <v>20.23</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="80" t="inlineStr">
+      <c r="A52" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B52" s="80" t="inlineStr">
+      <c r="B52" s="79" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C52" s="80" t="inlineStr">
+      <c r="C52" s="79" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D52" s="80" t="inlineStr">
+      <c r="D52" s="79" t="inlineStr">
         <is>
           <t>NFS.363799</t>
         </is>
       </c>
-      <c r="E52" s="80" t="inlineStr">
+      <c r="E52" s="79" t="inlineStr">
         <is>
           <t>104634/1</t>
         </is>
       </c>
-      <c r="F52" s="80" t="inlineStr">
+      <c r="F52" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G52" s="80" t="inlineStr">
+      <c r="G52" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H52" s="81" t="n">
+      <c r="H52" s="80" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="80" t="inlineStr">
+      <c r="A53" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B53" s="80" t="inlineStr">
+      <c r="B53" s="79" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="C53" s="80" t="inlineStr">
+      <c r="C53" s="79" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D53" s="80" t="inlineStr">
+      <c r="D53" s="79" t="inlineStr">
         <is>
           <t>BOL.04.26</t>
         </is>
       </c>
-      <c r="E53" s="80" t="inlineStr">
+      <c r="E53" s="79" t="inlineStr">
         <is>
           <t>104820/1</t>
         </is>
       </c>
-      <c r="F53" s="80" t="inlineStr">
+      <c r="F53" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G53" s="80" t="inlineStr">
+      <c r="G53" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H53" s="81" t="n">
+      <c r="H53" s="80" t="n">
         <v>1024.76</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="80" t="inlineStr">
+      <c r="A54" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B54" s="80" t="inlineStr">
+      <c r="B54" s="79" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C54" s="80" t="inlineStr">
+      <c r="C54" s="79" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D54" s="80" t="inlineStr">
+      <c r="D54" s="79" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 29.04.26</t>
         </is>
       </c>
-      <c r="E54" s="80" t="inlineStr">
+      <c r="E54" s="79" t="inlineStr">
         <is>
           <t>106325/1</t>
         </is>
       </c>
-      <c r="F54" s="80" t="inlineStr">
+      <c r="F54" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G54" s="80" t="inlineStr">
+      <c r="G54" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H54" s="81" t="n">
+      <c r="H54" s="80" t="n">
         <v>21.76</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="80" t="inlineStr">
+      <c r="A55" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B55" s="80" t="inlineStr">
+      <c r="B55" s="79" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C55" s="80" t="inlineStr">
+      <c r="C55" s="79" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D55" s="80" t="inlineStr">
+      <c r="D55" s="79" t="inlineStr">
         <is>
           <t>FAT.CHATGPT 3 LIC</t>
         </is>
       </c>
-      <c r="E55" s="80" t="inlineStr">
+      <c r="E55" s="79" t="inlineStr">
         <is>
           <t>102137/1</t>
         </is>
       </c>
-      <c r="F55" s="80" t="inlineStr">
+      <c r="F55" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G55" s="80" t="inlineStr">
+      <c r="G55" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H55" s="81" t="n">
+      <c r="H55" s="80" t="n">
         <v>5393.88</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="80" t="inlineStr">
+      <c r="A56" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B56" s="80" t="inlineStr">
+      <c r="B56" s="79" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C56" s="80" t="inlineStr">
+      <c r="C56" s="79" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D56" s="80" t="inlineStr">
+      <c r="D56" s="79" t="inlineStr">
         <is>
           <t>BOL.28855</t>
         </is>
       </c>
-      <c r="E56" s="80" t="inlineStr">
+      <c r="E56" s="79" t="inlineStr">
         <is>
           <t>103694/1</t>
         </is>
       </c>
-      <c r="F56" s="80" t="inlineStr">
+      <c r="F56" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G56" s="80" t="inlineStr">
+      <c r="G56" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H56" s="81" t="n">
+      <c r="H56" s="80" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="80" t="inlineStr">
+      <c r="A57" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B57" s="80" t="inlineStr">
+      <c r="B57" s="79" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="C57" s="80" t="inlineStr">
+      <c r="C57" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D57" s="80" t="inlineStr">
+      <c r="D57" s="79" t="inlineStr">
         <is>
           <t>SAL.SAL 032026</t>
         </is>
       </c>
-      <c r="E57" s="80" t="inlineStr">
+      <c r="E57" s="79" t="inlineStr">
         <is>
           <t>103924/1</t>
         </is>
       </c>
-      <c r="F57" s="80" t="inlineStr">
+      <c r="F57" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G57" s="80" t="inlineStr">
+      <c r="G57" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H57" s="81" t="n">
+      <c r="H57" s="80" t="n">
         <v>1515</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="80" t="inlineStr">
+      <c r="A58" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B58" s="80" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="C58" s="80" t="inlineStr">
+      <c r="C58" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D58" s="80" t="inlineStr">
+      <c r="D58" s="79" t="inlineStr">
         <is>
           <t>SAL.vale 042026</t>
         </is>
       </c>
-      <c r="E58" s="80" t="inlineStr">
+      <c r="E58" s="79" t="inlineStr">
         <is>
           <t>105055/1</t>
         </is>
       </c>
-      <c r="F58" s="80" t="inlineStr">
+      <c r="F58" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G58" s="80" t="inlineStr">
+      <c r="G58" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H58" s="81" t="n">
+      <c r="H58" s="80" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="80" t="inlineStr">
+      <c r="A59" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B59" s="80" t="inlineStr">
+      <c r="B59" s="79" t="inlineStr">
         <is>
           <t>2026-04-20 00:00:00</t>
         </is>
       </c>
-      <c r="C59" s="80" t="inlineStr">
+      <c r="C59" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D59" s="80" t="inlineStr">
+      <c r="D59" s="79" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E59" s="80" t="inlineStr">
+      <c r="E59" s="79" t="inlineStr">
         <is>
           <t>113754/4</t>
         </is>
       </c>
-      <c r="F59" s="80" t="inlineStr">
+      <c r="F59" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G59" s="80" t="inlineStr">
+      <c r="G59" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H59" s="81" t="n">
+      <c r="H59" s="80" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="80" t="inlineStr">
+      <c r="A60" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B60" s="80" t="inlineStr">
+      <c r="B60" s="79" t="inlineStr">
         <is>
           <t>2026-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="C60" s="80" t="inlineStr">
+      <c r="C60" s="79" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D60" s="80" t="inlineStr"/>
-      <c r="E60" s="80" t="inlineStr"/>
-      <c r="F60" s="80" t="inlineStr">
+      <c r="D60" s="79" t="inlineStr"/>
+      <c r="E60" s="79" t="inlineStr"/>
+      <c r="F60" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G60" s="80" t="inlineStr">
+      <c r="G60" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H60" s="81" t="n">
+      <c r="H60" s="80" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="80" t="inlineStr">
+      <c r="A61" s="79" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B61" s="80" t="inlineStr">
+      <c r="B61" s="79" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="C61" s="80" t="inlineStr">
+      <c r="C61" s="79" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D61" s="80" t="inlineStr">
+      <c r="D61" s="79" t="inlineStr">
         <is>
           <t>NFS.1573</t>
         </is>
       </c>
-      <c r="E61" s="80" t="inlineStr">
+      <c r="E61" s="79" t="inlineStr">
         <is>
           <t>105411/1</t>
         </is>
       </c>
-      <c r="F61" s="80" t="inlineStr">
+      <c r="F61" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G61" s="80" t="inlineStr">
+      <c r="G61" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H61" s="81" t="n">
+      <c r="H61" s="80" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="80" t="inlineStr">
+      <c r="A62" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B62" s="80" t="inlineStr">
+      <c r="B62" s="79" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="C62" s="80" t="inlineStr">
+      <c r="C62" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D62" s="80" t="inlineStr">
+      <c r="D62" s="79" t="inlineStr">
         <is>
           <t>FAT.2ªvia Claro Abril</t>
         </is>
       </c>
-      <c r="E62" s="80" t="inlineStr">
+      <c r="E62" s="79" t="inlineStr">
         <is>
           <t>107340/1</t>
         </is>
       </c>
-      <c r="F62" s="80" t="inlineStr">
+      <c r="F62" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G62" s="80" t="inlineStr">
+      <c r="G62" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H62" s="81" t="n">
+      <c r="H62" s="80" t="n">
         <v>182.32</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="80" t="inlineStr">
+      <c r="A63" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B63" s="80" t="inlineStr">
+      <c r="B63" s="79" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C63" s="80" t="inlineStr">
+      <c r="C63" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D63" s="80" t="inlineStr">
+      <c r="D63" s="79" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E63" s="80" t="inlineStr">
+      <c r="E63" s="79" t="inlineStr">
         <is>
           <t>108218/1</t>
         </is>
       </c>
-      <c r="F63" s="80" t="inlineStr">
+      <c r="F63" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G63" s="80" t="inlineStr">
+      <c r="G63" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H63" s="81" t="n">
+      <c r="H63" s="80" t="n">
         <v>629.98</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="80" t="inlineStr">
+      <c r="A64" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B64" s="80" t="inlineStr">
+      <c r="B64" s="79" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C64" s="80" t="inlineStr">
+      <c r="C64" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D64" s="80" t="inlineStr">
+      <c r="D64" s="79" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E64" s="80" t="inlineStr">
+      <c r="E64" s="79" t="inlineStr">
         <is>
           <t>108218/2</t>
         </is>
       </c>
-      <c r="F64" s="80" t="inlineStr">
+      <c r="F64" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G64" s="80" t="inlineStr">
+      <c r="G64" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H64" s="81" t="n">
+      <c r="H64" s="80" t="n">
         <v>18.86</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="80" t="inlineStr">
+      <c r="A65" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B65" s="80" t="inlineStr">
+      <c r="B65" s="79" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C65" s="80" t="inlineStr">
+      <c r="C65" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D65" s="80" t="inlineStr">
+      <c r="D65" s="79" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E65" s="80" t="inlineStr">
+      <c r="E65" s="79" t="inlineStr">
         <is>
           <t>108218/3</t>
         </is>
       </c>
-      <c r="F65" s="80" t="inlineStr">
+      <c r="F65" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G65" s="80" t="inlineStr">
+      <c r="G65" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H65" s="81" t="n">
+      <c r="H65" s="80" t="n">
         <v>133.95</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="80" t="inlineStr">
+      <c r="A66" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B66" s="80" t="inlineStr">
+      <c r="B66" s="79" t="inlineStr">
         <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="C66" s="80" t="inlineStr">
+      <c r="C66" s="79" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D66" s="80" t="inlineStr">
+      <c r="D66" s="79" t="inlineStr">
         <is>
           <t>NFS.76</t>
         </is>
       </c>
-      <c r="E66" s="80" t="inlineStr">
+      <c r="E66" s="79" t="inlineStr">
         <is>
           <t>105987/1</t>
         </is>
       </c>
-      <c r="F66" s="80" t="inlineStr">
+      <c r="F66" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G66" s="80" t="inlineStr">
+      <c r="G66" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H66" s="81" t="n">
+      <c r="H66" s="80" t="n">
         <v>3723.62</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="80" t="inlineStr">
+      <c r="A67" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B67" s="80" t="inlineStr">
+      <c r="B67" s="79" t="inlineStr">
         <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="C67" s="80" t="inlineStr">
+      <c r="C67" s="79" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D67" s="80" t="inlineStr">
+      <c r="D67" s="79" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 11.05.26</t>
         </is>
       </c>
-      <c r="E67" s="80" t="inlineStr">
+      <c r="E67" s="79" t="inlineStr">
         <is>
           <t>107254/1</t>
         </is>
       </c>
-      <c r="F67" s="80" t="inlineStr">
+      <c r="F67" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G67" s="80" t="inlineStr">
+      <c r="G67" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H67" s="81" t="n">
+      <c r="H67" s="80" t="n">
         <v>74.81</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="80" t="inlineStr">
+      <c r="A68" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B68" s="80" t="inlineStr">
+      <c r="B68" s="79" t="inlineStr">
         <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="C68" s="80" t="inlineStr">
+      <c r="C68" s="79" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D68" s="80" t="inlineStr">
+      <c r="D68" s="79" t="inlineStr">
         <is>
           <t>NFS.5744</t>
         </is>
       </c>
-      <c r="E68" s="80" t="inlineStr">
+      <c r="E68" s="79" t="inlineStr">
         <is>
           <t>106664/1</t>
         </is>
       </c>
-      <c r="F68" s="80" t="inlineStr">
+      <c r="F68" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G68" s="80" t="inlineStr">
+      <c r="G68" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H68" s="81" t="n">
+      <c r="H68" s="80" t="n">
         <v>741.1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="80" t="inlineStr">
+      <c r="A69" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B69" s="80" t="inlineStr">
+      <c r="B69" s="79" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C69" s="80" t="inlineStr">
+      <c r="C69" s="79" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D69" s="80" t="inlineStr">
+      <c r="D69" s="79" t="inlineStr">
         <is>
           <t>BOL.29637</t>
         </is>
       </c>
-      <c r="E69" s="80" t="inlineStr">
+      <c r="E69" s="79" t="inlineStr">
         <is>
           <t>108040/1</t>
         </is>
       </c>
-      <c r="F69" s="80" t="inlineStr">
+      <c r="F69" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G69" s="80" t="inlineStr">
+      <c r="G69" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H69" s="81" t="n">
+      <c r="H69" s="80" t="n">
         <v>137.92</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="80" t="inlineStr">
+      <c r="A70" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B70" s="80" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="C70" s="80" t="inlineStr">
+      <c r="C70" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D70" s="80" t="inlineStr">
+      <c r="D70" s="79" t="inlineStr">
         <is>
           <t>SAL.sal 042026</t>
         </is>
       </c>
-      <c r="E70" s="80" t="inlineStr">
+      <c r="E70" s="79" t="inlineStr">
         <is>
           <t>106947/1</t>
         </is>
       </c>
-      <c r="F70" s="80" t="inlineStr">
+      <c r="F70" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G70" s="80" t="inlineStr">
+      <c r="G70" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H70" s="81" t="n">
+      <c r="H70" s="80" t="n">
         <v>1483</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="80" t="inlineStr">
+      <c r="A71" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B71" s="80" t="inlineStr">
+      <c r="B71" s="79" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="C71" s="80" t="inlineStr">
+      <c r="C71" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D71" s="80" t="inlineStr">
+      <c r="D71" s="79" t="inlineStr">
         <is>
           <t>SAL.vale 052026</t>
         </is>
       </c>
-      <c r="E71" s="80" t="inlineStr">
+      <c r="E71" s="79" t="inlineStr">
         <is>
           <t>108156/1</t>
         </is>
       </c>
-      <c r="F71" s="80" t="inlineStr">
+      <c r="F71" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G71" s="80" t="inlineStr">
+      <c r="G71" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H71" s="81" t="n">
+      <c r="H71" s="80" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="80" t="inlineStr">
+      <c r="A72" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B72" s="80" t="inlineStr">
+      <c r="B72" s="79" t="inlineStr">
         <is>
           <t>2026-05-20 00:00:00</t>
         </is>
       </c>
-      <c r="C72" s="80" t="inlineStr">
+      <c r="C72" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D72" s="80" t="inlineStr">
+      <c r="D72" s="79" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E72" s="80" t="inlineStr">
+      <c r="E72" s="79" t="inlineStr">
         <is>
           <t>113754/5</t>
         </is>
       </c>
-      <c r="F72" s="80" t="inlineStr">
+      <c r="F72" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G72" s="80" t="inlineStr">
+      <c r="G72" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H72" s="81" t="n">
+      <c r="H72" s="80" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="80" t="inlineStr">
+      <c r="A73" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B73" s="80" t="inlineStr">
+      <c r="B73" s="79" t="inlineStr">
         <is>
           <t>2026-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="C73" s="80" t="inlineStr">
+      <c r="C73" s="79" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D73" s="80" t="inlineStr"/>
-      <c r="E73" s="80" t="inlineStr"/>
-      <c r="F73" s="80" t="inlineStr">
+      <c r="D73" s="79" t="inlineStr"/>
+      <c r="E73" s="79" t="inlineStr"/>
+      <c r="F73" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G73" s="80" t="inlineStr">
+      <c r="G73" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H73" s="81" t="n">
+      <c r="H73" s="80" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="80" t="inlineStr">
+      <c r="A74" s="79" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B74" s="80" t="inlineStr">
+      <c r="B74" s="79" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C74" s="80" t="inlineStr">
+      <c r="C74" s="79" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D74" s="80" t="inlineStr">
+      <c r="D74" s="79" t="inlineStr">
         <is>
           <t>NFS.1631</t>
         </is>
       </c>
-      <c r="E74" s="80" t="inlineStr">
+      <c r="E74" s="79" t="inlineStr">
         <is>
           <t>107973/1</t>
         </is>
       </c>
-      <c r="F74" s="80" t="inlineStr">
+      <c r="F74" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G74" s="80" t="inlineStr">
+      <c r="G74" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H74" s="81" t="n">
+      <c r="H74" s="80" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="80" t="inlineStr">
+      <c r="A75" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B75" s="80" t="inlineStr">
+      <c r="B75" s="79" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C75" s="80" t="inlineStr">
+      <c r="C75" s="79" t="inlineStr">
         <is>
           <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
         </is>
       </c>
-      <c r="D75" s="80" t="inlineStr">
+      <c r="D75" s="79" t="inlineStr">
         <is>
           <t>AV.1015392</t>
         </is>
       </c>
-      <c r="E75" s="80" t="inlineStr">
+      <c r="E75" s="79" t="inlineStr">
         <is>
           <t>108925/1</t>
         </is>
       </c>
-      <c r="F75" s="80" t="inlineStr">
+      <c r="F75" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G75" s="80" t="inlineStr">
+      <c r="G75" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H75" s="81" t="n">
+      <c r="H75" s="80" t="n">
         <v>183.6</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="80" t="inlineStr">
+      <c r="A76" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B76" s="80" t="inlineStr">
+      <c r="B76" s="79" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C76" s="80" t="inlineStr">
+      <c r="C76" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D76" s="80" t="inlineStr">
+      <c r="D76" s="79" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E76" s="80" t="inlineStr">
+      <c r="E76" s="79" t="inlineStr">
         <is>
           <t>111124/1</t>
         </is>
       </c>
-      <c r="F76" s="80" t="inlineStr">
+      <c r="F76" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G76" s="80" t="inlineStr">
+      <c r="G76" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H76" s="81" t="n">
+      <c r="H76" s="80" t="n">
         <v>720</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="80" t="inlineStr">
+      <c r="A77" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B77" s="80" t="inlineStr">
+      <c r="B77" s="79" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C77" s="80" t="inlineStr">
+      <c r="C77" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D77" s="80" t="inlineStr">
+      <c r="D77" s="79" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E77" s="80" t="inlineStr">
+      <c r="E77" s="79" t="inlineStr">
         <is>
           <t>111124/3</t>
         </is>
       </c>
-      <c r="F77" s="80" t="inlineStr">
+      <c r="F77" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G77" s="80" t="inlineStr">
+      <c r="G77" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H77" s="81" t="n">
+      <c r="H77" s="80" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="80" t="inlineStr">
+      <c r="A78" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B78" s="80" t="inlineStr">
+      <c r="B78" s="79" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C78" s="80" t="inlineStr">
+      <c r="C78" s="79" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D78" s="80" t="inlineStr">
+      <c r="D78" s="79" t="inlineStr">
         <is>
           <t>NFS.373725</t>
         </is>
       </c>
-      <c r="E78" s="80" t="inlineStr">
+      <c r="E78" s="79" t="inlineStr">
         <is>
           <t>110785/1</t>
         </is>
       </c>
-      <c r="F78" s="80" t="inlineStr">
+      <c r="F78" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G78" s="80" t="inlineStr">
+      <c r="G78" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H78" s="81" t="n">
+      <c r="H78" s="80" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="80" t="inlineStr">
+      <c r="A79" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B79" s="80" t="inlineStr">
+      <c r="B79" s="79" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C79" s="80" t="inlineStr">
+      <c r="C79" s="79" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D79" s="80" t="inlineStr">
+      <c r="D79" s="79" t="inlineStr">
         <is>
           <t>NFS.0036884701</t>
         </is>
       </c>
-      <c r="E79" s="80" t="inlineStr">
+      <c r="E79" s="79" t="inlineStr">
         <is>
           <t>109295/1</t>
         </is>
       </c>
-      <c r="F79" s="80" t="inlineStr">
+      <c r="F79" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G79" s="80" t="inlineStr">
+      <c r="G79" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H79" s="81" t="n">
+      <c r="H79" s="80" t="n">
         <v>84.81999999999999</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="80" t="inlineStr">
+      <c r="A80" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B80" s="80" t="inlineStr">
+      <c r="B80" s="79" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C80" s="80" t="inlineStr">
+      <c r="C80" s="79" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D80" s="80" t="inlineStr">
+      <c r="D80" s="79" t="inlineStr">
         <is>
           <t>NFS.78</t>
         </is>
       </c>
-      <c r="E80" s="80" t="inlineStr">
+      <c r="E80" s="79" t="inlineStr">
         <is>
           <t>108317/1</t>
         </is>
       </c>
-      <c r="F80" s="80" t="inlineStr">
+      <c r="F80" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G80" s="80" t="inlineStr">
+      <c r="G80" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H80" s="81" t="n">
+      <c r="H80" s="80" t="n">
         <v>6173.37</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="80" t="inlineStr">
+      <c r="A81" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B81" s="80" t="inlineStr">
+      <c r="B81" s="79" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="C81" s="80" t="inlineStr">
+      <c r="C81" s="79" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D81" s="80" t="inlineStr">
+      <c r="D81" s="79" t="inlineStr">
         <is>
           <t>NFS.5832</t>
         </is>
       </c>
-      <c r="E81" s="80" t="inlineStr">
+      <c r="E81" s="79" t="inlineStr">
         <is>
           <t>109227/1</t>
         </is>
       </c>
-      <c r="F81" s="80" t="inlineStr">
+      <c r="F81" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G81" s="80" t="inlineStr">
+      <c r="G81" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H81" s="81" t="n">
+      <c r="H81" s="80" t="n">
         <v>740.38</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="80" t="inlineStr">
+      <c r="A82" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B82" s="80" t="inlineStr">
+      <c r="B82" s="79" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C82" s="80" t="inlineStr">
+      <c r="C82" s="79" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D82" s="80" t="inlineStr">
+      <c r="D82" s="79" t="inlineStr">
         <is>
           <t>FAT.Vivo 04 2026</t>
         </is>
       </c>
-      <c r="E82" s="80" t="inlineStr">
+      <c r="E82" s="79" t="inlineStr">
         <is>
           <t>110752/1</t>
         </is>
       </c>
-      <c r="F82" s="80" t="inlineStr">
+      <c r="F82" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G82" s="80" t="inlineStr">
+      <c r="G82" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H82" s="81" t="n">
+      <c r="H82" s="80" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="80" t="inlineStr">
+      <c r="A83" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B83" s="80" t="inlineStr">
+      <c r="B83" s="79" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C83" s="80" t="inlineStr">
+      <c r="C83" s="79" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D83" s="80" t="inlineStr">
+      <c r="D83" s="79" t="inlineStr">
         <is>
           <t>FAT.Vivo 05 2026</t>
         </is>
       </c>
-      <c r="E83" s="80" t="inlineStr">
+      <c r="E83" s="79" t="inlineStr">
         <is>
           <t>110753/1</t>
         </is>
       </c>
-      <c r="F83" s="80" t="inlineStr">
+      <c r="F83" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G83" s="80" t="inlineStr">
+      <c r="G83" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H83" s="81" t="n">
+      <c r="H83" s="80" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="80" t="inlineStr">
+      <c r="A84" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B84" s="80" t="inlineStr">
+      <c r="B84" s="79" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C84" s="80" t="inlineStr">
+      <c r="C84" s="79" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D84" s="80" t="inlineStr">
+      <c r="D84" s="79" t="inlineStr">
         <is>
           <t>FAT.Vivo 06 2026</t>
         </is>
       </c>
-      <c r="E84" s="80" t="inlineStr">
+      <c r="E84" s="79" t="inlineStr">
         <is>
           <t>110754/1</t>
         </is>
       </c>
-      <c r="F84" s="80" t="inlineStr">
+      <c r="F84" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G84" s="80" t="inlineStr">
+      <c r="G84" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H84" s="81" t="n">
+      <c r="H84" s="80" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="80" t="inlineStr">
+      <c r="A85" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B85" s="80" t="inlineStr">
+      <c r="B85" s="79" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C85" s="80" t="inlineStr">
+      <c r="C85" s="79" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D85" s="80" t="inlineStr">
+      <c r="D85" s="79" t="inlineStr">
         <is>
           <t>BOL.1017717992</t>
         </is>
       </c>
-      <c r="E85" s="80" t="inlineStr">
+      <c r="E85" s="79" t="inlineStr">
         <is>
           <t>109298/1</t>
         </is>
       </c>
-      <c r="F85" s="80" t="inlineStr">
+      <c r="F85" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G85" s="80" t="inlineStr">
+      <c r="G85" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H85" s="81" t="n">
+      <c r="H85" s="80" t="n">
         <v>137.93</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="80" t="inlineStr">
+      <c r="A86" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B86" s="80" t="inlineStr">
+      <c r="B86" s="79" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C86" s="80" t="inlineStr">
+      <c r="C86" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D86" s="80" t="inlineStr">
+      <c r="D86" s="79" t="inlineStr">
         <is>
           <t>CX.27.05.26</t>
         </is>
       </c>
-      <c r="E86" s="80" t="inlineStr">
+      <c r="E86" s="79" t="inlineStr">
         <is>
           <t>108827/1</t>
         </is>
       </c>
-      <c r="F86" s="80" t="inlineStr">
+      <c r="F86" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G86" s="80" t="inlineStr">
+      <c r="G86" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H86" s="81" t="n">
+      <c r="H86" s="80" t="n">
         <v>184</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="80" t="inlineStr">
+      <c r="A87" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B87" s="80" t="inlineStr">
+      <c r="B87" s="79" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C87" s="80" t="inlineStr">
+      <c r="C87" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D87" s="80" t="inlineStr">
+      <c r="D87" s="79" t="inlineStr">
         <is>
           <t>SAL.1_ Ferias 1 VIn D 26</t>
         </is>
       </c>
-      <c r="E87" s="80" t="inlineStr">
+      <c r="E87" s="79" t="inlineStr">
         <is>
           <t>107780/1</t>
         </is>
       </c>
-      <c r="F87" s="80" t="inlineStr">
+      <c r="F87" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G87" s="80" t="inlineStr">
+      <c r="G87" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H87" s="81" t="n">
+      <c r="H87" s="80" t="n">
         <v>1101.12</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="80" t="inlineStr">
+      <c r="A88" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B88" s="80" t="inlineStr">
+      <c r="B88" s="79" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C88" s="80" t="inlineStr">
+      <c r="C88" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D88" s="80" t="inlineStr">
+      <c r="D88" s="79" t="inlineStr">
         <is>
           <t>SAL.sal 052026</t>
         </is>
       </c>
-      <c r="E88" s="80" t="inlineStr">
+      <c r="E88" s="79" t="inlineStr">
         <is>
           <t>109482/1</t>
         </is>
       </c>
-      <c r="F88" s="80" t="inlineStr">
+      <c r="F88" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G88" s="80" t="inlineStr">
+      <c r="G88" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H88" s="81" t="n">
+      <c r="H88" s="80" t="n">
         <v>1455</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="80" t="inlineStr">
+      <c r="A89" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B89" s="80" t="inlineStr">
+      <c r="B89" s="79" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C89" s="80" t="inlineStr">
+      <c r="C89" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D89" s="80" t="inlineStr">
+      <c r="D89" s="79" t="inlineStr">
         <is>
           <t>SAL.SALARIO06VINI</t>
         </is>
       </c>
-      <c r="E89" s="80" t="inlineStr">
+      <c r="E89" s="79" t="inlineStr">
         <is>
           <t>110700/1</t>
         </is>
       </c>
-      <c r="F89" s="80" t="inlineStr">
+      <c r="F89" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G89" s="80" t="inlineStr">
+      <c r="G89" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H89" s="81" t="n">
+      <c r="H89" s="80" t="n">
         <v>686</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="80" t="inlineStr">
+      <c r="A90" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B90" s="80" t="inlineStr">
+      <c r="B90" s="79" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="C90" s="80" t="inlineStr">
+      <c r="C90" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D90" s="80" t="inlineStr">
+      <c r="D90" s="79" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E90" s="80" t="inlineStr">
+      <c r="E90" s="79" t="inlineStr">
         <is>
           <t>113754/6</t>
         </is>
       </c>
-      <c r="F90" s="80" t="inlineStr">
+      <c r="F90" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G90" s="80" t="inlineStr">
+      <c r="G90" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H90" s="81" t="n">
+      <c r="H90" s="80" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="80" t="inlineStr">
+      <c r="A91" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B91" s="80" t="inlineStr">
+      <c r="B91" s="79" t="inlineStr">
         <is>
           <t>2026-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="C91" s="80" t="inlineStr">
+      <c r="C91" s="79" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D91" s="80" t="inlineStr"/>
-      <c r="E91" s="80" t="inlineStr"/>
-      <c r="F91" s="80" t="inlineStr">
+      <c r="D91" s="79" t="inlineStr"/>
+      <c r="E91" s="79" t="inlineStr"/>
+      <c r="F91" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G91" s="80" t="inlineStr">
+      <c r="G91" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H91" s="81" t="n">
+      <c r="H91" s="80" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="80" t="inlineStr">
+      <c r="A92" s="79" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B92" s="80" t="inlineStr">
+      <c r="B92" s="79" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C92" s="80" t="inlineStr">
+      <c r="C92" s="79" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D92" s="80" t="inlineStr">
+      <c r="D92" s="79" t="inlineStr">
         <is>
           <t>NFS.33</t>
         </is>
       </c>
-      <c r="E92" s="80" t="inlineStr">
+      <c r="E92" s="79" t="inlineStr">
         <is>
           <t>110902/1</t>
         </is>
       </c>
-      <c r="F92" s="80" t="inlineStr">
+      <c r="F92" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G92" s="80" t="inlineStr">
+      <c r="G92" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H92" s="81" t="n">
+      <c r="H92" s="80" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="80" t="inlineStr">
+      <c r="A93" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B93" s="80" t="inlineStr">
+      <c r="B93" s="79" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C93" s="80" t="inlineStr">
+      <c r="C93" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D93" s="80" t="inlineStr">
+      <c r="D93" s="79" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E93" s="80" t="inlineStr">
+      <c r="E93" s="79" t="inlineStr">
         <is>
           <t>113575/1</t>
         </is>
       </c>
-      <c r="F93" s="80" t="inlineStr">
+      <c r="F93" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G93" s="80" t="inlineStr">
+      <c r="G93" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H93" s="81" t="n">
+      <c r="H93" s="80" t="n">
         <v>20.39</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="80" t="inlineStr">
+      <c r="A94" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B94" s="80" t="inlineStr">
+      <c r="B94" s="79" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C94" s="80" t="inlineStr">
+      <c r="C94" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D94" s="80" t="inlineStr">
+      <c r="D94" s="79" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E94" s="80" t="inlineStr">
+      <c r="E94" s="79" t="inlineStr">
         <is>
           <t>113575/2</t>
         </is>
       </c>
-      <c r="F94" s="80" t="inlineStr">
+      <c r="F94" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G94" s="80" t="inlineStr">
+      <c r="G94" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H94" s="81" t="n">
+      <c r="H94" s="80" t="n">
         <v>133.73</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="80" t="inlineStr">
+      <c r="A95" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B95" s="80" t="inlineStr">
+      <c r="B95" s="79" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C95" s="80" t="inlineStr">
+      <c r="C95" s="79" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D95" s="80" t="inlineStr">
+      <c r="D95" s="79" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E95" s="80" t="inlineStr">
+      <c r="E95" s="79" t="inlineStr">
         <is>
           <t>113575/3</t>
         </is>
       </c>
-      <c r="F95" s="80" t="inlineStr">
+      <c r="F95" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G95" s="80" t="inlineStr">
+      <c r="G95" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H95" s="81" t="n">
+      <c r="H95" s="80" t="n">
         <v>825.28</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="80" t="inlineStr">
+      <c r="A96" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B96" s="80" t="inlineStr">
+      <c r="B96" s="79" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C96" s="80" t="inlineStr">
+      <c r="C96" s="79" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D96" s="80" t="inlineStr">
+      <c r="D96" s="79" t="inlineStr">
         <is>
           <t>NFS.377682</t>
         </is>
       </c>
-      <c r="E96" s="80" t="inlineStr">
+      <c r="E96" s="79" t="inlineStr">
         <is>
           <t>114092/1</t>
         </is>
       </c>
-      <c r="F96" s="80" t="inlineStr">
+      <c r="F96" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G96" s="80" t="inlineStr">
+      <c r="G96" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H96" s="81" t="n">
+      <c r="H96" s="80" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="80" t="inlineStr">
+      <c r="A97" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B97" s="80" t="inlineStr">
+      <c r="B97" s="79" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="C97" s="80" t="inlineStr">
+      <c r="C97" s="79" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D97" s="80" t="inlineStr">
+      <c r="D97" s="79" t="inlineStr">
         <is>
           <t>NFS.3</t>
         </is>
       </c>
-      <c r="E97" s="80" t="inlineStr">
+      <c r="E97" s="79" t="inlineStr">
         <is>
           <t>111371/1</t>
         </is>
       </c>
-      <c r="F97" s="80" t="inlineStr">
+      <c r="F97" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G97" s="80" t="inlineStr">
+      <c r="G97" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H97" s="81" t="n">
+      <c r="H97" s="80" t="n">
         <v>6300</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="80" t="inlineStr">
+      <c r="A98" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B98" s="80" t="inlineStr">
+      <c r="B98" s="79" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C98" s="80" t="inlineStr">
+      <c r="C98" s="79" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D98" s="80" t="inlineStr">
+      <c r="D98" s="79" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 07.26</t>
         </is>
       </c>
-      <c r="E98" s="80" t="inlineStr">
+      <c r="E98" s="79" t="inlineStr">
         <is>
           <t>113049/1</t>
         </is>
       </c>
-      <c r="F98" s="80" t="inlineStr">
+      <c r="F98" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G98" s="80" t="inlineStr">
+      <c r="G98" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H98" s="81" t="n">
+      <c r="H98" s="80" t="n">
         <v>1151.26</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="80" t="inlineStr">
+      <c r="A99" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B99" s="80" t="inlineStr">
+      <c r="B99" s="79" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C99" s="80" t="inlineStr">
+      <c r="C99" s="79" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D99" s="80" t="inlineStr">
+      <c r="D99" s="79" t="inlineStr">
         <is>
           <t>NFS.66</t>
         </is>
       </c>
-      <c r="E99" s="80" t="inlineStr">
+      <c r="E99" s="79" t="inlineStr">
         <is>
           <t>112107/1</t>
         </is>
       </c>
-      <c r="F99" s="80" t="inlineStr">
+      <c r="F99" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G99" s="80" t="inlineStr">
+      <c r="G99" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H99" s="81" t="n">
+      <c r="H99" s="80" t="n">
         <v>1037.38</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="80" t="inlineStr">
+      <c r="A100" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B100" s="80" t="inlineStr">
+      <c r="B100" s="79" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="C100" s="80" t="inlineStr">
+      <c r="C100" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D100" s="80" t="inlineStr">
+      <c r="D100" s="79" t="inlineStr">
         <is>
           <t>SAL.sal 0626</t>
         </is>
       </c>
-      <c r="E100" s="80" t="inlineStr">
+      <c r="E100" s="79" t="inlineStr">
         <is>
           <t>112402/1</t>
         </is>
       </c>
-      <c r="F100" s="80" t="inlineStr">
+      <c r="F100" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G100" s="80" t="inlineStr">
+      <c r="G100" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H100" s="81" t="n">
+      <c r="H100" s="80" t="n">
         <v>1225</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="80" t="inlineStr">
+      <c r="A101" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B101" s="80" t="inlineStr">
+      <c r="B101" s="79" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C101" s="80" t="inlineStr">
+      <c r="C101" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D101" s="80" t="inlineStr">
+      <c r="D101" s="79" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E101" s="80" t="inlineStr">
+      <c r="E101" s="79" t="inlineStr">
         <is>
           <t>113754/1</t>
         </is>
       </c>
-      <c r="F101" s="80" t="inlineStr">
+      <c r="F101" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G101" s="80" t="inlineStr">
+      <c r="G101" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H101" s="81" t="n">
+      <c r="H101" s="80" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="80" t="inlineStr">
+      <c r="A102" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B102" s="80" t="inlineStr">
+      <c r="B102" s="79" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C102" s="80" t="inlineStr">
+      <c r="C102" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D102" s="80" t="inlineStr">
+      <c r="D102" s="79" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E102" s="80" t="inlineStr">
+      <c r="E102" s="79" t="inlineStr">
         <is>
           <t>113754/7</t>
         </is>
       </c>
-      <c r="F102" s="80" t="inlineStr">
+      <c r="F102" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G102" s="80" t="inlineStr">
+      <c r="G102" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H102" s="81" t="n">
+      <c r="H102" s="80" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="80" t="inlineStr">
+      <c r="A103" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B103" s="80" t="inlineStr">
+      <c r="B103" s="79" t="inlineStr">
         <is>
           <t>2026-07-01 00:00:00</t>
         </is>
       </c>
-      <c r="C103" s="80" t="inlineStr">
+      <c r="C103" s="79" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D103" s="80" t="inlineStr"/>
-      <c r="E103" s="80" t="inlineStr"/>
-      <c r="F103" s="80" t="inlineStr">
+      <c r="D103" s="79" t="inlineStr"/>
+      <c r="E103" s="79" t="inlineStr"/>
+      <c r="F103" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G103" s="80" t="inlineStr">
+      <c r="G103" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H103" s="81" t="n">
+      <c r="H103" s="80" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="80" t="inlineStr">
+      <c r="A104" s="79" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B104" s="80" t="inlineStr">
+      <c r="B104" s="79" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C104" s="80" t="inlineStr">
+      <c r="C104" s="79" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D104" s="80" t="inlineStr">
+      <c r="D104" s="79" t="inlineStr">
         <is>
           <t>NFS.84</t>
         </is>
       </c>
-      <c r="E104" s="80" t="inlineStr">
+      <c r="E104" s="79" t="inlineStr">
         <is>
           <t>113583/1</t>
         </is>
       </c>
-      <c r="F104" s="80" t="inlineStr">
+      <c r="F104" s="79" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G104" s="80" t="inlineStr">
+      <c r="G104" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H104" s="81" t="n">
+      <c r="H104" s="80" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="105">
-      <c r="G105" s="82" t="inlineStr">
+      <c r="G105" s="81" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H105" s="83">
+      <c r="H105" s="82">
         <f>SUM(H5:H104)</f>
         <v/>
       </c>
@@ -10854,7 +10846,7 @@
       </c>
       <c r="B8" s="65" t="inlineStr">
         <is>
-          <t>Planejado de jan a abr — CONFERIR</t>
+          <t>Planejado de jan a abr — conferido</t>
         </is>
       </c>
       <c r="C8" s="65" t="inlineStr">
@@ -10864,7 +10856,7 @@
       </c>
       <c r="D8" s="65" t="inlineStr">
         <is>
-          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
+          <t>Conferido e validado pela gestora: os valores replicados estão corretos, nenhum ajuste necessário.</t>
         </is>
       </c>
       <c r="E8" s="65" t="inlineStr">
@@ -10874,7 +10866,7 @@
       </c>
       <c r="F8" s="67" t="inlineStr">
         <is>
-          <t>CONFERIR</t>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
@@ -10904,9 +10896,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="68" t="inlineStr">
-        <is>
-          <t>EM ANDAMENTO</t>
+      <c r="F9" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10928,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F10" s="69" t="inlineStr">
+      <c r="F10" s="68" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -11000,7 +10992,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="70" t="inlineStr">
+      <c r="F12" s="67" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
@@ -11032,7 +11024,7 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F13" s="70" t="inlineStr">
+      <c r="F13" s="67" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
@@ -11064,7 +11056,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F14" s="69" t="inlineStr">
+      <c r="F14" s="68" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -11192,7 +11184,7 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F18" s="67" t="inlineStr">
+      <c r="F18" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>
@@ -11243,60 +11235,60 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="71" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="72" t="inlineStr">
+      <c r="B5" s="71" t="inlineStr">
         <is>
           <t>Extraia do SIENGE o relatório do centro de custo do departamento, no mês que fechou. A fonte do realizado é o SIENGE — nada é digitado de cabeça.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="71" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="72" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>Lance na aba REALIZADO, nas células amarelas, o valor de cada linha do orçamento. Item sem gasto no mês: digite 0 — deixar em branco significa 'ainda não lancei'. Use a coluna 'Fonte do dado' para registrar de qual relatório o número saiu, com a data da extração.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="71" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="72" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="72" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="71" t="inlineStr">
+      <c r="A9" s="70" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="72" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -11311,60 +11303,60 @@
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="72" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="71" t="inlineStr">
+      <c r="A13" s="70" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="72" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="71" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="72" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="71" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="72" t="inlineStr">
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="71" t="inlineStr">
+      <c r="A16" s="70" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="72" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -11379,36 +11371,36 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="71" t="inlineStr">
+      <c r="A19" s="70" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="72" t="inlineStr">
+      <c r="B19" s="71" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="71" t="inlineStr">
+      <c r="A20" s="70" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="72" t="inlineStr">
+      <c r="B20" s="71" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="71" t="inlineStr">
+      <c r="A21" s="70" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="72" t="inlineStr">
+      <c r="B21" s="71" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>
@@ -11567,86 +11559,86 @@
       <c r="J5" s="54" t="n">
         <v>6300</v>
       </c>
-      <c r="K5" s="73" t="n">
+      <c r="K5" s="72" t="n">
         <v>20508.55</v>
       </c>
-      <c r="L5" s="74" t="n"/>
+      <c r="L5" s="73" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="74" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C6" s="76" t="n">
+      <c r="C6" s="75" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="77" t="n">
+      <c r="D6" s="76" t="n">
         <v>2670.84</v>
       </c>
-      <c r="E6" s="77" t="n">
+      <c r="E6" s="76" t="n">
         <v>2986.04</v>
       </c>
-      <c r="F6" s="77" t="n">
+      <c r="F6" s="76" t="n">
         <v>2778.04</v>
       </c>
-      <c r="G6" s="77" t="n">
+      <c r="G6" s="76" t="n">
         <v>2751.04</v>
       </c>
-      <c r="H6" s="77" t="n">
+      <c r="H6" s="76" t="n">
         <v>2719.04</v>
       </c>
-      <c r="I6" s="77" t="n">
+      <c r="I6" s="76" t="n">
         <v>3633.16</v>
       </c>
-      <c r="J6" s="77" t="n">
+      <c r="J6" s="76" t="n">
         <v>2461.04</v>
       </c>
-      <c r="K6" s="78" t="n">
+      <c r="K6" s="77" t="n">
         <v>19999.2</v>
       </c>
-      <c r="L6" s="79" t="inlineStr">
+      <c r="L6" s="78" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius Di Franco</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="74" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C7" s="76" t="n">
+      <c r="C7" s="75" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="77" t="n"/>
-      <c r="E7" s="77" t="n">
+      <c r="D7" s="76" t="n"/>
+      <c r="E7" s="76" t="n">
         <v>234.46</v>
       </c>
-      <c r="F7" s="77" t="n">
+      <c r="F7" s="76" t="n">
         <v>321.76</v>
       </c>
-      <c r="G7" s="77" t="n">
+      <c r="G7" s="76" t="n">
         <v>5393.88</v>
       </c>
-      <c r="H7" s="77" t="n"/>
-      <c r="I7" s="77" t="n"/>
-      <c r="J7" s="77" t="n"/>
-      <c r="K7" s="78" t="n">
+      <c r="H7" s="76" t="n"/>
+      <c r="I7" s="76" t="n"/>
+      <c r="J7" s="76" t="n"/>
+      <c r="K7" s="77" t="n">
         <v>5950.1</v>
       </c>
-      <c r="L7" s="79" t="inlineStr">
+      <c r="L7" s="78" t="inlineStr">
         <is>
           <t>TI-D11 GPT</t>
         </is>
@@ -11685,10 +11677,10 @@
       <c r="J8" s="54" t="n">
         <v>979.4</v>
       </c>
-      <c r="K8" s="73" t="n">
+      <c r="K8" s="72" t="n">
         <v>5228.139999999999</v>
       </c>
-      <c r="L8" s="74" t="n"/>
+      <c r="L8" s="73" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="56" t="inlineStr">
@@ -11721,10 +11713,10 @@
       <c r="J9" s="54" t="n">
         <v>1151.26</v>
       </c>
-      <c r="K9" s="73" t="n">
+      <c r="K9" s="72" t="n">
         <v>3296.12</v>
       </c>
-      <c r="L9" s="74" t="n"/>
+      <c r="L9" s="73" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="56" t="inlineStr">
@@ -11755,48 +11747,48 @@
       <c r="J10" s="54" t="n">
         <v>1037.38</v>
       </c>
-      <c r="K10" s="73" t="n">
+      <c r="K10" s="72" t="n">
         <v>3242.61</v>
       </c>
-      <c r="L10" s="74" t="n"/>
+      <c r="L10" s="73" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="75" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="B11" s="75" t="inlineStr">
+      <c r="B11" s="74" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C11" s="76" t="n">
+      <c r="C11" s="75" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="77" t="n"/>
-      <c r="E11" s="77" t="n">
+      <c r="D11" s="76" t="n"/>
+      <c r="E11" s="76" t="n">
         <v>485</v>
       </c>
-      <c r="F11" s="77" t="n">
+      <c r="F11" s="76" t="n">
         <v>485</v>
       </c>
-      <c r="G11" s="77" t="n">
+      <c r="G11" s="76" t="n">
         <v>485</v>
       </c>
-      <c r="H11" s="77" t="n">
+      <c r="H11" s="76" t="n">
         <v>485</v>
       </c>
-      <c r="I11" s="77" t="n">
+      <c r="I11" s="76" t="n">
         <v>485</v>
       </c>
-      <c r="J11" s="77" t="n">
+      <c r="J11" s="76" t="n">
         <v>485</v>
       </c>
-      <c r="K11" s="78" t="n">
+      <c r="K11" s="77" t="n">
         <v>2910</v>
       </c>
-      <c r="L11" s="79" t="inlineStr">
+      <c r="L11" s="78" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius (benefício)</t>
         </is>
@@ -11829,10 +11821,10 @@
       <c r="H12" s="54" t="n"/>
       <c r="I12" s="54" t="n"/>
       <c r="J12" s="54" t="n"/>
-      <c r="K12" s="73" t="n">
+      <c r="K12" s="72" t="n">
         <v>954.5500000000001</v>
       </c>
-      <c r="L12" s="74" t="n"/>
+      <c r="L12" s="73" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="56" t="inlineStr">
@@ -11865,10 +11857,10 @@
         <v>137.93</v>
       </c>
       <c r="J13" s="54" t="n"/>
-      <c r="K13" s="73" t="n">
+      <c r="K13" s="72" t="n">
         <v>827.49</v>
       </c>
-      <c r="L13" s="74" t="n"/>
+      <c r="L13" s="73" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="56" t="inlineStr">
@@ -11899,10 +11891,10 @@
         <v>554.58</v>
       </c>
       <c r="J14" s="54" t="n"/>
-      <c r="K14" s="73" t="n">
+      <c r="K14" s="72" t="n">
         <v>758.53</v>
       </c>
-      <c r="L14" s="74" t="n"/>
+      <c r="L14" s="73" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="56" t="inlineStr">
@@ -11939,10 +11931,10 @@
       <c r="J15" s="54" t="n">
         <v>82.5</v>
       </c>
-      <c r="K15" s="73" t="n">
+      <c r="K15" s="72" t="n">
         <v>690</v>
       </c>
-      <c r="L15" s="74" t="n"/>
+      <c r="L15" s="73" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
@@ -11975,10 +11967,10 @@
       <c r="J16" s="54" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="K16" s="73" t="n">
+      <c r="K16" s="72" t="n">
         <v>562.42</v>
       </c>
-      <c r="L16" s="74" t="n"/>
+      <c r="L16" s="73" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="56" t="inlineStr">
@@ -12003,10 +11995,10 @@
         <v>183.6</v>
       </c>
       <c r="J17" s="54" t="n"/>
-      <c r="K17" s="73" t="n">
+      <c r="K17" s="72" t="n">
         <v>183.6</v>
       </c>
-      <c r="L17" s="74" t="n"/>
+      <c r="L17" s="73" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="51" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -8974,6 +8974,10 @@
       <c r="M5" s="49" t="n"/>
       <c r="N5" s="49" t="n"/>
       <c r="O5" s="49" t="n"/>
+      <c r="P5" s="49" t="n"/>
+      <c r="Q5" s="49" t="n"/>
+      <c r="R5" s="49" t="n"/>
+      <c r="S5" s="49" t="n"/>
       <c r="T5" s="45">
         <f>SUM(H5:S5)</f>
         <v/>
@@ -9036,6 +9040,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="49" t="n"/>
+      <c r="P6" s="49" t="n"/>
+      <c r="Q6" s="49" t="n"/>
+      <c r="R6" s="49" t="n"/>
+      <c r="S6" s="49" t="n"/>
       <c r="T6" s="45">
         <f>SUM(H6:S6)</f>
         <v/>
@@ -9102,6 +9110,10 @@
         <v>6300</v>
       </c>
       <c r="O7" s="49" t="n"/>
+      <c r="P7" s="49" t="n"/>
+      <c r="Q7" s="49" t="n"/>
+      <c r="R7" s="49" t="n"/>
+      <c r="S7" s="49" t="n"/>
       <c r="T7" s="45">
         <f>SUM(H7:S7)</f>
         <v/>
@@ -9154,6 +9166,10 @@
       <c r="M8" s="49" t="n"/>
       <c r="N8" s="49" t="n"/>
       <c r="O8" s="49" t="n"/>
+      <c r="P8" s="49" t="n"/>
+      <c r="Q8" s="49" t="n"/>
+      <c r="R8" s="49" t="n"/>
+      <c r="S8" s="49" t="n"/>
       <c r="T8" s="45">
         <f>SUM(H8:S8)</f>
         <v/>
@@ -9198,6 +9214,10 @@
       <c r="M9" s="49" t="n"/>
       <c r="N9" s="49" t="n"/>
       <c r="O9" s="49" t="n"/>
+      <c r="P9" s="49" t="n"/>
+      <c r="Q9" s="49" t="n"/>
+      <c r="R9" s="49" t="n"/>
+      <c r="S9" s="49" t="n"/>
       <c r="T9" s="45">
         <f>SUM(H9:S9)</f>
         <v/>
@@ -9242,6 +9262,10 @@
       <c r="M10" s="49" t="n"/>
       <c r="N10" s="49" t="n"/>
       <c r="O10" s="49" t="n"/>
+      <c r="P10" s="49" t="n"/>
+      <c r="Q10" s="49" t="n"/>
+      <c r="R10" s="49" t="n"/>
+      <c r="S10" s="49" t="n"/>
       <c r="T10" s="45">
         <f>SUM(H10:S10)</f>
         <v/>
@@ -9286,6 +9310,10 @@
       <c r="M11" s="49" t="n"/>
       <c r="N11" s="49" t="n"/>
       <c r="O11" s="49" t="n"/>
+      <c r="P11" s="49" t="n"/>
+      <c r="Q11" s="49" t="n"/>
+      <c r="R11" s="49" t="n"/>
+      <c r="S11" s="49" t="n"/>
       <c r="T11" s="45">
         <f>SUM(H11:S11)</f>
         <v/>
@@ -9330,6 +9358,10 @@
       <c r="M12" s="49" t="n"/>
       <c r="N12" s="49" t="n"/>
       <c r="O12" s="49" t="n"/>
+      <c r="P12" s="49" t="n"/>
+      <c r="Q12" s="49" t="n"/>
+      <c r="R12" s="49" t="n"/>
+      <c r="S12" s="49" t="n"/>
       <c r="T12" s="45">
         <f>SUM(H12:S12)</f>
         <v/>
@@ -9374,6 +9406,10 @@
       <c r="M13" s="49" t="n"/>
       <c r="N13" s="49" t="n"/>
       <c r="O13" s="49" t="n"/>
+      <c r="P13" s="49" t="n"/>
+      <c r="Q13" s="49" t="n"/>
+      <c r="R13" s="49" t="n"/>
+      <c r="S13" s="49" t="n"/>
       <c r="T13" s="45">
         <f>SUM(H13:S13)</f>
         <v/>
@@ -9418,6 +9454,10 @@
       <c r="M14" s="49" t="n"/>
       <c r="N14" s="49" t="n"/>
       <c r="O14" s="49" t="n"/>
+      <c r="P14" s="49" t="n"/>
+      <c r="Q14" s="49" t="n"/>
+      <c r="R14" s="49" t="n"/>
+      <c r="S14" s="49" t="n"/>
       <c r="T14" s="45">
         <f>SUM(H14:S14)</f>
         <v/>
@@ -9462,6 +9502,10 @@
       <c r="M15" s="49" t="n"/>
       <c r="N15" s="49" t="n"/>
       <c r="O15" s="49" t="n"/>
+      <c r="P15" s="49" t="n"/>
+      <c r="Q15" s="49" t="n"/>
+      <c r="R15" s="49" t="n"/>
+      <c r="S15" s="49" t="n"/>
       <c r="T15" s="45">
         <f>SUM(H15:S15)</f>
         <v/>
@@ -9506,6 +9550,10 @@
       <c r="M16" s="49" t="n"/>
       <c r="N16" s="49" t="n"/>
       <c r="O16" s="49" t="n"/>
+      <c r="P16" s="49" t="n"/>
+      <c r="Q16" s="49" t="n"/>
+      <c r="R16" s="49" t="n"/>
+      <c r="S16" s="49" t="n"/>
       <c r="T16" s="45">
         <f>SUM(H16:S16)</f>
         <v/>
@@ -9550,6 +9598,10 @@
       <c r="M17" s="49" t="n"/>
       <c r="N17" s="49" t="n"/>
       <c r="O17" s="49" t="n"/>
+      <c r="P17" s="49" t="n"/>
+      <c r="Q17" s="49" t="n"/>
+      <c r="R17" s="49" t="n"/>
+      <c r="S17" s="49" t="n"/>
       <c r="T17" s="45">
         <f>SUM(H17:S17)</f>
         <v/>
@@ -9594,6 +9646,10 @@
       <c r="M18" s="49" t="n"/>
       <c r="N18" s="49" t="n"/>
       <c r="O18" s="49" t="n"/>
+      <c r="P18" s="49" t="n"/>
+      <c r="Q18" s="49" t="n"/>
+      <c r="R18" s="49" t="n"/>
+      <c r="S18" s="49" t="n"/>
       <c r="T18" s="45">
         <f>SUM(H18:S18)</f>
         <v/>
@@ -9638,6 +9694,10 @@
       <c r="M19" s="49" t="n"/>
       <c r="N19" s="49" t="n"/>
       <c r="O19" s="49" t="n"/>
+      <c r="P19" s="49" t="n"/>
+      <c r="Q19" s="49" t="n"/>
+      <c r="R19" s="49" t="n"/>
+      <c r="S19" s="49" t="n"/>
       <c r="T19" s="45">
         <f>SUM(H19:S19)</f>
         <v/>
@@ -9682,6 +9742,10 @@
       <c r="M20" s="49" t="n"/>
       <c r="N20" s="49" t="n"/>
       <c r="O20" s="49" t="n"/>
+      <c r="P20" s="49" t="n"/>
+      <c r="Q20" s="49" t="n"/>
+      <c r="R20" s="49" t="n"/>
+      <c r="S20" s="49" t="n"/>
       <c r="T20" s="45">
         <f>SUM(H20:S20)</f>
         <v/>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -5905,7 +5905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7309,49 +7309,49 @@
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="42" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B31" s="42" t="n"/>
-      <c r="C31" s="42" t="n"/>
-      <c r="D31" s="42" t="n"/>
-      <c r="E31" s="42" t="n"/>
-      <c r="F31" s="43">
+      <c r="B32" s="42" t="n"/>
+      <c r="C32" s="42" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="43">
         <f>SUM(F6:F21)</f>
         <v/>
       </c>
-      <c r="G31" s="43">
+      <c r="G32" s="43">
         <f>SUM(G6:G21)</f>
         <v/>
       </c>
-      <c r="H31" s="43">
+      <c r="H32" s="43">
         <f>SUM(H6:H21)</f>
         <v/>
       </c>
-      <c r="I31" s="43">
+      <c r="I32" s="43">
         <f>SUM(I6:I21)</f>
         <v/>
       </c>
-      <c r="J31" s="43">
+      <c r="J32" s="43">
         <f>SUM(J6:J21)</f>
         <v/>
       </c>
-      <c r="K31" s="43">
+      <c r="K32" s="43">
         <f>SUM(K6:K21)</f>
         <v/>
       </c>
-      <c r="L31" s="44">
-        <f>IFERROR(K31/I31,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="44">
-        <f>IFERROR(J31/I31,"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="42" t="n"/>
+      <c r="L32" s="44">
+        <f>IFERROR(K32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="44">
+        <f>IFERROR(J32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="42" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:N21"/>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="D10" s="65" t="inlineStr">
         <is>
-          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. Decidir na reunião quais entram no centro de custo da área — e, para os que entrarem, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
+          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. ATENÇÃO: parte desses valores pode ser repasse ou custa reembolsável pelo cliente, e não custo da área — foi o caso da Dra. Michele (ver item P). Separar o que é custo antes de decidir. Para os que entrarem no centro de custo, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
         </is>
       </c>
       <c r="E10" s="65" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11230,17 +11230,17 @@
       </c>
       <c r="B18" s="65" t="inlineStr">
         <is>
-          <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
+          <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
       <c r="C18" s="65" t="inlineStr">
         <is>
-          <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
+          <t>Confirmado pela gestora: TODOS os PJs prestam o serviço e recebem no mês seguinte. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
       <c r="D18" s="65" t="inlineStr">
         <is>
-          <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Com a extração vindo do SIENGE, basta escolher o regime na hora de gerar o relatório: definir isso UMA vez e manter, para o histórico não misturar critérios.</t>
+          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios.</t>
         </is>
       </c>
       <c r="E18" s="65" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11235,12 +11235,12 @@
       </c>
       <c r="C18" s="65" t="inlineStr">
         <is>
-          <t>Confirmado pela gestora: TODOS os PJs prestam o serviço e recebem no mês seguinte. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
+          <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
       <c r="D18" s="65" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios.</t>
+          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
       <c r="E18" s="65" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -395,10 +395,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
+          <t>Consultor — orçado desde jan/26. As atividades só começaram em abr/26: a contratação foi segurada por três meses</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
@@ -7722,13 +7722,13 @@
         </is>
       </c>
       <c r="H7" s="37" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I7" s="37" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J7" s="37" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="K7" s="37" t="n">
         <v>10000</v>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="V7" s="50" t="inlineStr">
         <is>
-          <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
+          <t>Sem custo em jan–mar (contratação segurada). R$ 6.300/mês a partir de abr, contra R$ 10.000 orçados</t>
         </is>
       </c>
     </row>
@@ -10846,17 +10846,17 @@
       </c>
       <c r="B6" s="65" t="inlineStr">
         <is>
-          <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
+          <t>Jonathan — economia de R$ 44.800 até julho</t>
         </is>
       </c>
       <c r="C6" s="65" t="inlineStr">
         <is>
-          <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
+          <t>Orçado R$ 10.000/mês desde jan/26. A contratação foi segurada e as atividades só começaram em abr/26, a R$ 6.300/mês. Resultado: três meses sem custo (R$ 30.000) e quatro meses a R$ 3.700 abaixo do orçado (R$ 14.800).</t>
         </is>
       </c>
       <c r="D6" s="65" t="inlineStr">
         <is>
-          <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
+          <t>É de longe a maior economia das duas áreas: R$ 44.800 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Se o valor de R$ 6.300 se mantiver até dez, somam-se outros R$ 18.500 — total de R$ 63.300 no ano. Vale destacar na apresentação à diretoria.</t>
         </is>
       </c>
       <c r="E6" s="65" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F6" s="66" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
@@ -10896,7 +10896,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="66" t="inlineStr">
+      <c r="F7" s="67" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -10928,7 +10928,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F8" s="67" t="inlineStr">
+      <c r="F8" s="66" t="inlineStr">
         <is>
           <t>APLICADO</t>
         </is>
@@ -10960,7 +10960,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="67" t="inlineStr">
+      <c r="F9" s="66" t="inlineStr">
         <is>
           <t>APLICADO</t>
         </is>
@@ -11038,17 +11038,17 @@
       </c>
       <c r="B12" s="65" t="inlineStr">
         <is>
-          <t>Base de meses — reconciliada com a ficha original</t>
+          <t>Base de meses do TI — Jonathan corrigido para 12 meses</t>
         </is>
       </c>
       <c r="C12" s="65" t="inlineStr">
         <is>
-          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
+          <t>A ficha trazia os totais do TI digitados à mão: Vinicius e Elias em 12 meses (R$ 64.998,30 e R$ 12.780,00, ambos confirmados) e Jonathan em 9 meses (R$ 90.000). A gestora confirmou que o orçamento dele valia desde jan/26, ou seja, 12 meses — os R$ 90.000 da ficha não refletiam o orçamento aprovado.</t>
         </is>
       </c>
       <c r="D12" s="65" t="inlineStr">
         <is>
-          <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
+          <t>Equipe de TI passa de R$ 167.778,30 para R$ 197.778,30 (+R$ 30.000). Os R$ 167.778,30 da ficha continuam batendo com Vinicius e Elias, mas a linha do Jonathan estava subdimensionada em 3 meses.</t>
         </is>
       </c>
       <c r="E12" s="65" t="inlineStr">
@@ -11056,7 +11056,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="67" t="inlineStr">
+      <c r="F12" s="66" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
@@ -11088,7 +11088,7 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F13" s="67" t="inlineStr">
+      <c r="F13" s="66" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
@@ -11152,7 +11152,7 @@
           <t>Cristiane + Controladoria</t>
         </is>
       </c>
-      <c r="F15" s="66" t="inlineStr">
+      <c r="F15" s="67" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -11184,7 +11184,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F16" s="66" t="inlineStr">
+      <c r="F16" s="67" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -11216,7 +11216,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F17" s="66" t="inlineStr">
+      <c r="F17" s="67" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -8361,7 +8361,7 @@
       </c>
       <c r="E16" s="36" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas</t>
         </is>
       </c>
       <c r="F16" s="35" t="inlineStr"/>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="E17" s="36" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="E18" s="36" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F18" s="35" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="E19" s="36" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr"/>
@@ -11102,17 +11102,17 @@
       </c>
       <c r="B14" s="65" t="inlineStr">
         <is>
-          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
+          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
         </is>
       </c>
       <c r="C14" s="65" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
         </is>
       </c>
       <c r="D14" s="65" t="inlineStr">
         <is>
-          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
+          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E14" s="65" t="inlineStr">
@@ -11134,17 +11134,17 @@
       </c>
       <c r="B15" s="62" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>Rateio dos softwares corporativos e das IAs</t>
         </is>
       </c>
       <c r="C15" s="62" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
         </is>
       </c>
       <c r="D15" s="62" t="inlineStr">
         <is>
-          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
+          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
         </is>
       </c>
       <c r="E15" s="62" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -7931,7 +7931,7 @@
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
+          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR. Pagamentos reais de R$ 575/mês estão lançados no centro de custo Jurídico por engano (ver pendência Q)</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr"/>
@@ -10749,7 +10749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11097,91 +11097,91 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="64" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B14" s="65" t="inlineStr">
         <is>
-          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
+          <t>Adapta lançado no centro de custo errado — RECLASSIFICAR</t>
         </is>
       </c>
       <c r="C14" s="65" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
+          <t>Os pagamentos do Adapta (ADAPTA EDUCACAO LTDA, contrato 4134643529) estão no centro de custo Jurídico no SIENGE: R$ 575,00/mês de jan a mai e R$ 476,00 em jun, todos com vencimento dia 15. Total de R$ 3.351,00 em seis meses. Não é despesa do Jurídico — é ferramenta de IA, de uso transversal.</t>
         </is>
       </c>
       <c r="D14" s="65" t="inlineStr">
         <is>
-          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
+          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
         </is>
       </c>
       <c r="E14" s="65" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F14" s="68" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F14" s="63" t="inlineStr">
+        <is>
+          <t>RECLASSIFICAR</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B15" s="62" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos e das IAs</t>
+          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
         </is>
       </c>
       <c r="C15" s="62" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
         </is>
       </c>
       <c r="D15" s="62" t="inlineStr">
         <is>
-          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
+          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E15" s="62" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F15" s="67" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F15" s="68" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" s="65" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Rateio dos softwares corporativos e das IAs</t>
         </is>
       </c>
       <c r="C16" s="65" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
         </is>
       </c>
       <c r="D16" s="65" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
         </is>
       </c>
       <c r="E16" s="65" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F16" s="67" t="inlineStr">
@@ -11193,22 +11193,22 @@
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B17" s="62" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
         </is>
       </c>
       <c r="C17" s="62" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
         </is>
       </c>
       <c r="D17" s="62" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
         </is>
       </c>
       <c r="E17" s="62" t="inlineStr">
@@ -11225,30 +11225,62 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="64" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C18" s="65" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D18" s="65" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E18" s="65" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F18" s="67" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B18" s="65" t="inlineStr">
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C18" s="65" t="inlineStr">
+      <c r="C19" s="62" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D18" s="65" t="inlineStr">
+      <c r="D19" s="62" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E18" s="65" t="inlineStr">
+      <c r="E19" s="62" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F18" s="69" t="inlineStr">
+      <c r="F19" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11198,27 +11198,27 @@
       </c>
       <c r="B17" s="62" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Sala de Reunião — EXECUTAR, PAUSAR OU REPENSAR?</t>
         </is>
       </c>
       <c r="C17" s="62" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Projeto orçado em R$ 2.800/mês × 12 = R$ 33.600, classificado em Móveis e Utensílios, sem nenhum lançamento até jul/26. A gestora levanta que a sala já não comporta todas as pessoas, então investir na configuração atual pode não resolver o problema real. Três caminhos: executar como está, pausar, ou repensar a solução (outro espaço, formato híbrido, mais de uma sala).</t>
         </is>
       </c>
       <c r="D17" s="62" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer.</t>
         </is>
       </c>
       <c r="E17" s="62" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F17" s="67" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F17" s="68" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -10749,7 +10749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11225,62 +11225,94 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B18" s="65" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Notebooks — TI compra, mas não enxerga o saldo das áreas</t>
         </is>
       </c>
       <c r="C18" s="65" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Cada área tem a própria linha de orçamento para notebooks, mas é o TI que recebe a solicitação e executa a compra quando surge a necessidade. Hoje o TI não tem acompanhamento do orçamento das outras áreas, então aprova pedidos sem saber quanto resta em cada uma.</t>
         </is>
       </c>
       <c r="D18" s="65" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>O TI vira o executor de um estouro que não é dele e que ninguém percebe antes de acontecer — a área descobre no fechamento, quando já comprou. Proposta: o TI passa a acompanhar o saldo da rubrica de notebooks de cada área e avisa quando a solicitação for levar ao estouro, antes de comprar. Com o centro de custo no SIENGE, esse acompanhamento sai do mesmo relatório. Definir com a diretoria quem dá o aval quando o saldo acabar: a área solicitante, o TI ou a controladoria.</t>
         </is>
       </c>
       <c r="E18" s="65" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F18" s="67" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F18" s="68" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="61" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="62" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C19" s="62" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D19" s="62" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E19" s="62" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="64" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C20" s="65" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D19" s="62" t="inlineStr">
+      <c r="D20" s="65" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E19" s="62" t="inlineStr">
+      <c r="E20" s="65" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F19" s="69" t="inlineStr">
+      <c r="F20" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -10749,7 +10749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11257,22 +11257,22 @@
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B19" s="62" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Rubricas genéricas — detalhar no lançamento, não no orçamento</t>
         </is>
       </c>
       <c r="C19" s="62" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Rubricas como 'Peças de Manutenção' (R$ 9.720/ano) agrupam itens de naturezas diferentes: mouse, teclado, carregador, tela, carcaça. Sem detalhe, não dá para saber o que puxa o gasto. A alternativa de criar uma linha por item foi avaliada e descartada por ora.</t>
         </is>
       </c>
       <c r="D19" s="62" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>DECIDIDO: manter uma linha de orçamento e detalhar na DESCRIÇÃO do lançamento no SIENGE, com padrão fixo ('Peças – mouse', 'Peças – tela'). Motivos: (1) não há histórico — as despesas do TI ainda não têm lançamento, então orçar item a item seria estimativa sem base, e cada linha acusaria desvio pela divisão errada, não pelo gasto; (2) cinco linhas viram cinco lançamentos mensais para uma rubrica que é 11% das despesas da área; (3) o plano de contas é definido pela controladoria, então subitens no orçamento não mudariam a classificação contábil. Em jan/27, com seis meses de dados reais, reavaliar. Se separar, separar por NATUREZA (reposição x reparo), que é o que dá leitura gerencial, e não item a item. Mesmo critério vale para 'Equipamentos Eletrônicos Diversos' e demais rubricas genéricas.</t>
         </is>
       </c>
       <c r="E19" s="62" t="inlineStr">
@@ -11280,39 +11280,71 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F19" s="67" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F19" s="66" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="64" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C20" s="65" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D20" s="65" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E20" s="65" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F20" s="67" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="61" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B20" s="65" t="inlineStr">
+      <c r="B21" s="62" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C20" s="65" t="inlineStr">
+      <c r="C21" s="62" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D20" s="65" t="inlineStr">
+      <c r="D21" s="62" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E20" s="65" t="inlineStr">
+      <c r="E21" s="62" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F20" s="69" t="inlineStr">
+      <c r="F21" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>
@@ -11333,7 +11365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11426,134 +11458,156 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>COMO LER OS NÚMEROS</t>
+          <t>PADRÃO DE DESCRIÇÃO</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="70" t="inlineStr">
         <is>
-          <t>Desvio positivo (vermelho)</t>
+          <t>Rubricas genéricas</t>
         </is>
       </c>
       <c r="B12" s="71" t="inlineStr">
         <is>
-          <t>Gastou ACIMA do orçado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="70" t="inlineStr">
-        <is>
-          <t>Desvio negativo (verde)</t>
-        </is>
-      </c>
-      <c r="B13" s="71" t="inlineStr">
-        <is>
-          <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="70" t="inlineStr">
-        <is>
-          <t>Planejado acum.</t>
-        </is>
-      </c>
-      <c r="B14" s="71" t="inlineStr">
-        <is>
-          <t>Soma de maio até o mês selecionado.</t>
+          <t>Em linhas que agrupam itens variados (peças de manutenção, equipamentos diversos), detalhe o item na descrição do lançamento no SIENGE, sempre no mesmo padrão: 'Peças – mouse', 'Peças – tela'. O orçamento fica numa linha só e o detalhe sai por filtro quando precisar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="70" t="inlineStr">
         <is>
-          <t>% Executado</t>
+          <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
       <c r="B15" s="71" t="inlineStr">
         <is>
-          <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
+          <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="70" t="inlineStr">
         <is>
-          <t>Sem lançamento</t>
+          <t>Desvio negativo (verde)</t>
         </is>
       </c>
       <c r="B16" s="71" t="inlineStr">
         <is>
-          <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>REGRAS DA PLANILHA</t>
+          <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>Planejado acum.</t>
+        </is>
+      </c>
+      <c r="B17" s="71" t="inlineStr">
+        <is>
+          <t>Soma de maio até o mês selecionado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="70" t="inlineStr">
+        <is>
+          <t>% Executado</t>
+        </is>
+      </c>
+      <c r="B18" s="71" t="inlineStr">
+        <is>
+          <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="70" t="inlineStr">
         <is>
+          <t>Sem lançamento</t>
+        </is>
+      </c>
+      <c r="B19" s="71" t="inlineStr">
+        <is>
+          <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>REGRAS DA PLANILHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="70" t="inlineStr">
+        <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="71" t="inlineStr">
+      <c r="B22" s="71" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="70" t="inlineStr">
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="70" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="71" t="inlineStr">
+      <c r="B23" s="71" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="70" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="70" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="71" t="inlineStr">
+      <c r="B24" s="71" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B13:C13"/>
+  <mergeCells count="20">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -15,14 +15,16 @@
     <sheet name="Por Plano de Contas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Pendências" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Contas Pagas (resumo)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Contas Pagas (detalhe)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Controle de Equipamentos" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Contas Pagas (resumo)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Contas Pagas (detalhe)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -254,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -412,6 +414,21 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1857,6 +1874,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONTAS PAGAS — RESUMO POR CREDOR  (TI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Extrato do financeiro, centro de custo "T.I". ABA DE APOIO: o centro de custo destes itens ainda não foi decidido, então nada aqui entra no Planejado, no Realizado nem no Painel. A coluna final aponta o que provavelmente já está no orçamento — confira e remova as duplicidades à mão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>Credor</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Centro de Custo</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>Nº lanç.</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="inlineStr">
+        <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="F4" s="46" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="H4" s="46" t="inlineStr">
+        <is>
+          <t>Mai/26</t>
+        </is>
+      </c>
+      <c r="I4" s="46" t="inlineStr">
+        <is>
+          <t>Jun/26</t>
+        </is>
+      </c>
+      <c r="J4" s="46" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="K4" s="46" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L4" s="46" t="inlineStr">
+        <is>
+          <t>Já está no orçamento?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="56" t="inlineStr">
+        <is>
+          <t>J H ALVES - MONITOR REMOTO</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C5" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="54" t="n">
+        <v>4311.56</v>
+      </c>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n">
+        <v>3723.62</v>
+      </c>
+      <c r="I5" s="54" t="n">
+        <v>6173.37</v>
+      </c>
+      <c r="J5" s="54" t="n">
+        <v>6300</v>
+      </c>
+      <c r="K5" s="79" t="n">
+        <v>20508.55</v>
+      </c>
+      <c r="L5" s="80" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>VINICIUS DI FRANCO HEITOR</t>
+        </is>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C6" s="82" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="83" t="n">
+        <v>2670.84</v>
+      </c>
+      <c r="E6" s="83" t="n">
+        <v>2986.04</v>
+      </c>
+      <c r="F6" s="83" t="n">
+        <v>2778.04</v>
+      </c>
+      <c r="G6" s="83" t="n">
+        <v>2751.04</v>
+      </c>
+      <c r="H6" s="83" t="n">
+        <v>2719.04</v>
+      </c>
+      <c r="I6" s="83" t="n">
+        <v>3633.16</v>
+      </c>
+      <c r="J6" s="83" t="n">
+        <v>2461.04</v>
+      </c>
+      <c r="K6" s="84" t="n">
+        <v>19999.2</v>
+      </c>
+      <c r="L6" s="85" t="inlineStr">
+        <is>
+          <t>TI-E01 Vinicius Di Franco</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>OPENAI BRAZIL LIMITADA</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C7" s="82" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="83" t="n"/>
+      <c r="E7" s="83" t="n">
+        <v>234.46</v>
+      </c>
+      <c r="F7" s="83" t="n">
+        <v>321.76</v>
+      </c>
+      <c r="G7" s="83" t="n">
+        <v>5393.88</v>
+      </c>
+      <c r="H7" s="83" t="n"/>
+      <c r="I7" s="83" t="n"/>
+      <c r="J7" s="83" t="n"/>
+      <c r="K7" s="84" t="n">
+        <v>5950.1</v>
+      </c>
+      <c r="L7" s="85" t="inlineStr">
+        <is>
+          <t>TI-D11 GPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C8" s="53" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" s="54" t="n">
+        <v>922.1099999999999</v>
+      </c>
+      <c r="E8" s="54" t="n"/>
+      <c r="F8" s="54" t="n">
+        <v>899.5799999999999</v>
+      </c>
+      <c r="G8" s="54" t="n">
+        <v>721.9400000000001</v>
+      </c>
+      <c r="H8" s="54" t="n">
+        <v>965.1099999999999</v>
+      </c>
+      <c r="I8" s="54" t="n">
+        <v>740</v>
+      </c>
+      <c r="J8" s="54" t="n">
+        <v>979.4</v>
+      </c>
+      <c r="K8" s="79" t="n">
+        <v>5228.139999999999</v>
+      </c>
+      <c r="L8" s="80" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="54" t="n">
+        <v>924.2800000000001</v>
+      </c>
+      <c r="E9" s="54" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="F9" s="54" t="n"/>
+      <c r="G9" s="54" t="n">
+        <v>1046.52</v>
+      </c>
+      <c r="H9" s="54" t="n">
+        <v>74.81</v>
+      </c>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n">
+        <v>1151.26</v>
+      </c>
+      <c r="K9" s="79" t="n">
+        <v>3296.12</v>
+      </c>
+      <c r="L9" s="80" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="54" t="n">
+        <v>723.75</v>
+      </c>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="n">
+        <v>741.1</v>
+      </c>
+      <c r="I10" s="54" t="n">
+        <v>740.38</v>
+      </c>
+      <c r="J10" s="54" t="n">
+        <v>1037.38</v>
+      </c>
+      <c r="K10" s="79" t="n">
+        <v>3242.61</v>
+      </c>
+      <c r="L10" s="80" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>Vale Alimentação Vinicius</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C11" s="82" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="83" t="n"/>
+      <c r="E11" s="83" t="n">
+        <v>485</v>
+      </c>
+      <c r="F11" s="83" t="n">
+        <v>485</v>
+      </c>
+      <c r="G11" s="83" t="n">
+        <v>485</v>
+      </c>
+      <c r="H11" s="83" t="n">
+        <v>485</v>
+      </c>
+      <c r="I11" s="83" t="n">
+        <v>485</v>
+      </c>
+      <c r="J11" s="83" t="n">
+        <v>485</v>
+      </c>
+      <c r="K11" s="84" t="n">
+        <v>2910</v>
+      </c>
+      <c r="L11" s="85" t="inlineStr">
+        <is>
+          <t>TI-E01 Vinicius (benefício)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>TIM S A</t>
+        </is>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C12" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="54" t="n">
+        <v>331.42</v>
+      </c>
+      <c r="E12" s="54" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="F12" s="54" t="n">
+        <v>284.63</v>
+      </c>
+      <c r="G12" s="54" t="n"/>
+      <c r="H12" s="54" t="n"/>
+      <c r="I12" s="54" t="n"/>
+      <c r="J12" s="54" t="n"/>
+      <c r="K12" s="79" t="n">
+        <v>954.5500000000001</v>
+      </c>
+      <c r="L12" s="80" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
+        </is>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C13" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="54" t="n"/>
+      <c r="E13" s="54" t="n">
+        <v>275.84</v>
+      </c>
+      <c r="F13" s="54" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="G13" s="54" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="H13" s="54" t="n">
+        <v>137.92</v>
+      </c>
+      <c r="I13" s="54" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="J13" s="54" t="n"/>
+      <c r="K13" s="79" t="n">
+        <v>827.49</v>
+      </c>
+      <c r="L13" s="80" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>TELEFONICA BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C14" s="53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="54" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="E14" s="54" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="F14" s="54" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n">
+        <v>554.58</v>
+      </c>
+      <c r="J14" s="54" t="n"/>
+      <c r="K14" s="79" t="n">
+        <v>758.53</v>
+      </c>
+      <c r="L14" s="80" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>WEB MOBILE TELECOM LTDA</t>
+        </is>
+      </c>
+      <c r="B15" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C15" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="54" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E15" s="54" t="n">
+        <v>75</v>
+      </c>
+      <c r="F15" s="54" t="n">
+        <v>225</v>
+      </c>
+      <c r="G15" s="54" t="n">
+        <v>75</v>
+      </c>
+      <c r="H15" s="54" t="n">
+        <v>75</v>
+      </c>
+      <c r="I15" s="54" t="n">
+        <v>75</v>
+      </c>
+      <c r="J15" s="54" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="K15" s="79" t="n">
+        <v>690</v>
+      </c>
+      <c r="L15" s="80" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C16" s="53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="54" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E16" s="54" t="n"/>
+      <c r="F16" s="54" t="n">
+        <v>159.2</v>
+      </c>
+      <c r="G16" s="54" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="H16" s="54" t="n"/>
+      <c r="I16" s="54" t="n">
+        <v>164.42</v>
+      </c>
+      <c r="J16" s="54" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="K16" s="79" t="n">
+        <v>562.42</v>
+      </c>
+      <c r="L16" s="80" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>T.I</t>
+        </is>
+      </c>
+      <c r="C17" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="54" t="n"/>
+      <c r="F17" s="54" t="n"/>
+      <c r="G17" s="54" t="n"/>
+      <c r="H17" s="54" t="n"/>
+      <c r="I17" s="54" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="79" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="L17" s="80" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="n"/>
+      <c r="C18" s="51" t="n"/>
+      <c r="D18" s="52">
+        <f>SUM(D5:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="52">
+        <f>SUM(E5:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="52">
+        <f>SUM(F5:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="52">
+        <f>SUM(G5:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="52">
+        <f>SUM(H5:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="52">
+        <f>SUM(I5:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="52">
+        <f>SUM(J5:J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="52">
+        <f>SUM(K5:K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="51" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:L17"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1927,3964 +2565,3964 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="79" t="inlineStr">
+      <c r="A5" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="79" t="inlineStr">
+      <c r="B5" s="86" t="inlineStr">
         <is>
           <t>09/01/2026</t>
         </is>
       </c>
-      <c r="C5" s="79" t="inlineStr">
+      <c r="C5" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D5" s="79" t="inlineStr">
+      <c r="D5" s="86" t="inlineStr">
         <is>
           <t>FAT.11.25</t>
         </is>
       </c>
-      <c r="E5" s="79" t="inlineStr">
+      <c r="E5" s="86" t="inlineStr">
         <is>
           <t>95941/1</t>
         </is>
       </c>
-      <c r="F5" s="79" t="inlineStr">
+      <c r="F5" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G5" s="79" t="inlineStr">
+      <c r="G5" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H5" s="80" t="n">
+      <c r="H5" s="87" t="n">
         <v>407.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="79" t="inlineStr">
+      <c r="A6" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B6" s="79" t="inlineStr">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C6" s="79" t="inlineStr">
+      <c r="C6" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
+      <c r="D6" s="86" t="inlineStr">
         <is>
           <t>FAT.01.26</t>
         </is>
       </c>
-      <c r="E6" s="79" t="inlineStr">
+      <c r="E6" s="86" t="inlineStr">
         <is>
           <t>97478/1</t>
         </is>
       </c>
-      <c r="F6" s="79" t="inlineStr">
+      <c r="F6" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G6" s="79" t="inlineStr">
+      <c r="G6" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H6" s="80" t="n">
+      <c r="H6" s="87" t="n">
         <v>390.95</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="79" t="inlineStr">
+      <c r="A7" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B7" s="79" t="inlineStr">
+      <c r="B7" s="86" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C7" s="79" t="inlineStr">
+      <c r="C7" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D7" s="79" t="inlineStr">
+      <c r="D7" s="86" t="inlineStr">
         <is>
           <t>FAT.184180933</t>
         </is>
       </c>
-      <c r="E7" s="79" t="inlineStr">
+      <c r="E7" s="86" t="inlineStr">
         <is>
           <t>97480/1</t>
         </is>
       </c>
-      <c r="F7" s="79" t="inlineStr">
+      <c r="F7" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G7" s="79" t="inlineStr">
+      <c r="G7" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H7" s="80" t="n">
+      <c r="H7" s="87" t="n">
         <v>123.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="79" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="86" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C8" s="79" t="inlineStr">
+      <c r="C8" s="86" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D8" s="79" t="inlineStr">
+      <c r="D8" s="86" t="inlineStr">
         <is>
           <t>NFS.347106</t>
         </is>
       </c>
-      <c r="E8" s="79" t="inlineStr">
+      <c r="E8" s="86" t="inlineStr">
         <is>
           <t>96534/1</t>
         </is>
       </c>
-      <c r="F8" s="79" t="inlineStr">
+      <c r="F8" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G8" s="79" t="inlineStr">
+      <c r="G8" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H8" s="80" t="n">
+      <c r="H8" s="87" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="79" t="inlineStr">
+      <c r="A9" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="86" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="C9" s="79" t="inlineStr">
+      <c r="C9" s="86" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D9" s="79" t="inlineStr">
+      <c r="D9" s="86" t="inlineStr">
         <is>
           <t>NFS.70</t>
         </is>
       </c>
-      <c r="E9" s="79" t="inlineStr">
+      <c r="E9" s="86" t="inlineStr">
         <is>
           <t>96602/1</t>
         </is>
       </c>
-      <c r="F9" s="79" t="inlineStr">
+      <c r="F9" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G9" s="79" t="inlineStr">
+      <c r="G9" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H9" s="80" t="n">
+      <c r="H9" s="87" t="n">
         <v>4311.56</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="79" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B10" s="79" t="inlineStr">
+      <c r="B10" s="86" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="C10" s="79" t="inlineStr">
+      <c r="C10" s="86" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D10" s="79" t="inlineStr">
+      <c r="D10" s="86" t="inlineStr">
         <is>
           <t>AV.LIC EMAILS 01.25</t>
         </is>
       </c>
-      <c r="E10" s="79" t="inlineStr">
+      <c r="E10" s="86" t="inlineStr">
         <is>
           <t>96014/1</t>
         </is>
       </c>
-      <c r="F10" s="79" t="inlineStr">
+      <c r="F10" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G10" s="79" t="inlineStr">
+      <c r="G10" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H10" s="80" t="n">
+      <c r="H10" s="87" t="n">
         <v>6.2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="79" t="inlineStr">
+      <c r="A11" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B11" s="79" t="inlineStr">
+      <c r="B11" s="86" t="inlineStr">
         <is>
           <t>25/01/2026</t>
         </is>
       </c>
-      <c r="C11" s="79" t="inlineStr">
+      <c r="C11" s="86" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D11" s="79" t="inlineStr">
+      <c r="D11" s="86" t="inlineStr">
         <is>
           <t>BOL.13.01</t>
         </is>
       </c>
-      <c r="E11" s="79" t="inlineStr">
+      <c r="E11" s="86" t="inlineStr">
         <is>
           <t>96623/1</t>
         </is>
       </c>
-      <c r="F11" s="79" t="inlineStr">
+      <c r="F11" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G11" s="79" t="inlineStr">
+      <c r="G11" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H11" s="80" t="n">
+      <c r="H11" s="87" t="n">
         <v>918.08</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="79" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="86" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C12" s="79" t="inlineStr">
+      <c r="C12" s="86" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D12" s="79" t="inlineStr">
+      <c r="D12" s="86" t="inlineStr">
         <is>
           <t>FAT.2682</t>
         </is>
       </c>
-      <c r="E12" s="79" t="inlineStr">
+      <c r="E12" s="86" t="inlineStr">
         <is>
           <t>96458/1</t>
         </is>
       </c>
-      <c r="F12" s="79" t="inlineStr">
+      <c r="F12" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G12" s="79" t="inlineStr">
+      <c r="G12" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H12" s="80" t="n">
+      <c r="H12" s="87" t="n">
         <v>723.75</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="79" t="inlineStr">
+      <c r="A13" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B13" s="79" t="inlineStr">
+      <c r="B13" s="86" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="C13" s="79" t="inlineStr">
+      <c r="C13" s="86" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D13" s="79" t="inlineStr">
+      <c r="D13" s="86" t="inlineStr">
         <is>
           <t>FAT.2011241340</t>
         </is>
       </c>
-      <c r="E13" s="79" t="inlineStr">
+      <c r="E13" s="86" t="inlineStr">
         <is>
           <t>96088/1</t>
         </is>
       </c>
-      <c r="F13" s="79" t="inlineStr">
+      <c r="F13" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G13" s="79" t="inlineStr">
+      <c r="G13" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H13" s="80" t="n">
+      <c r="H13" s="87" t="n">
         <v>51.63</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="79" t="inlineStr">
+      <c r="A14" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="86" t="inlineStr">
         <is>
           <t>22/01/2026</t>
         </is>
       </c>
-      <c r="C14" s="79" t="inlineStr">
+      <c r="C14" s="86" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D14" s="79" t="inlineStr">
+      <c r="D14" s="86" t="inlineStr">
         <is>
           <t>FAT.5664047504</t>
         </is>
       </c>
-      <c r="E14" s="79" t="inlineStr">
+      <c r="E14" s="86" t="inlineStr">
         <is>
           <t>96789/1</t>
         </is>
       </c>
-      <c r="F14" s="79" t="inlineStr">
+      <c r="F14" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G14" s="79" t="inlineStr">
+      <c r="G14" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H14" s="80" t="n">
+      <c r="H14" s="87" t="n">
         <v>331.42</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="79" t="inlineStr">
+      <c r="A15" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="86" t="inlineStr">
         <is>
           <t>26/01/2026</t>
         </is>
       </c>
-      <c r="C15" s="79" t="inlineStr">
+      <c r="C15" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D15" s="79" t="inlineStr">
+      <c r="D15" s="86" t="inlineStr">
         <is>
           <t>CX.16.01.26</t>
         </is>
       </c>
-      <c r="E15" s="79" t="inlineStr">
+      <c r="E15" s="86" t="inlineStr">
         <is>
           <t>97067/1</t>
         </is>
       </c>
-      <c r="F15" s="79" t="inlineStr">
+      <c r="F15" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G15" s="79" t="inlineStr">
+      <c r="G15" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H15" s="80" t="n">
+      <c r="H15" s="87" t="n">
         <v>39.84</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="79" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="86" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="C16" s="79" t="inlineStr">
+      <c r="C16" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="D16" s="86" t="inlineStr">
         <is>
           <t>SAL.Sal_122025</t>
         </is>
       </c>
-      <c r="E16" s="79" t="inlineStr">
+      <c r="E16" s="86" t="inlineStr">
         <is>
           <t>96252/1</t>
         </is>
       </c>
-      <c r="F16" s="79" t="inlineStr">
+      <c r="F16" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G16" s="79" t="inlineStr">
+      <c r="G16" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H16" s="80" t="n">
+      <c r="H16" s="87" t="n">
         <v>1602</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="79" t="inlineStr">
+      <c r="A17" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B17" s="79" t="inlineStr">
+      <c r="B17" s="86" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="C17" s="79" t="inlineStr">
+      <c r="C17" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D17" s="79" t="inlineStr">
+      <c r="D17" s="86" t="inlineStr">
         <is>
           <t>SAL.VALE_ 012026</t>
         </is>
       </c>
-      <c r="E17" s="79" t="inlineStr">
+      <c r="E17" s="86" t="inlineStr">
         <is>
           <t>97269/1</t>
         </is>
       </c>
-      <c r="F17" s="79" t="inlineStr">
+      <c r="F17" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G17" s="79" t="inlineStr">
+      <c r="G17" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H17" s="80" t="n">
+      <c r="H17" s="87" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="79" t="inlineStr">
+      <c r="A18" s="86" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B18" s="79" t="inlineStr">
+      <c r="B18" s="86" t="inlineStr">
         <is>
           <t>27/01/2026</t>
         </is>
       </c>
-      <c r="C18" s="79" t="inlineStr">
+      <c r="C18" s="86" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D18" s="79" t="inlineStr">
+      <c r="D18" s="86" t="inlineStr">
         <is>
           <t>BOL.1</t>
         </is>
       </c>
-      <c r="E18" s="79" t="inlineStr">
+      <c r="E18" s="86" t="inlineStr">
         <is>
           <t>97204/1</t>
         </is>
       </c>
-      <c r="F18" s="79" t="inlineStr">
+      <c r="F18" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G18" s="79" t="inlineStr">
+      <c r="G18" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H18" s="80" t="n">
+      <c r="H18" s="87" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="79" t="inlineStr">
+      <c r="A19" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B19" s="79" t="inlineStr">
+      <c r="B19" s="86" t="inlineStr">
         <is>
           <t>04/02/2026</t>
         </is>
       </c>
-      <c r="C19" s="79" t="inlineStr">
+      <c r="C19" s="86" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D19" s="79" t="inlineStr">
+      <c r="D19" s="86" t="inlineStr">
         <is>
           <t>AV.04.02.26</t>
         </is>
       </c>
-      <c r="E19" s="79" t="inlineStr">
+      <c r="E19" s="86" t="inlineStr">
         <is>
           <t>98500/1</t>
         </is>
       </c>
-      <c r="F19" s="79" t="inlineStr">
+      <c r="F19" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G19" s="79" t="inlineStr">
+      <c r="G19" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H19" s="80" t="n">
+      <c r="H19" s="87" t="n">
         <v>26.67</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="79" t="inlineStr">
+      <c r="A20" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="86" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C20" s="79" t="inlineStr">
+      <c r="C20" s="86" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D20" s="79" t="inlineStr">
+      <c r="D20" s="86" t="inlineStr">
         <is>
           <t>AV.12.02.26 LCW</t>
         </is>
       </c>
-      <c r="E20" s="79" t="inlineStr">
+      <c r="E20" s="86" t="inlineStr">
         <is>
           <t>99336/1</t>
         </is>
       </c>
-      <c r="F20" s="79" t="inlineStr">
+      <c r="F20" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G20" s="79" t="inlineStr">
+      <c r="G20" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H20" s="80" t="n">
+      <c r="H20" s="87" t="n">
         <v>72.58</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="79" t="inlineStr">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B21" s="79" t="inlineStr">
+      <c r="B21" s="86" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C21" s="79" t="inlineStr">
+      <c r="C21" s="86" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D21" s="79" t="inlineStr">
+      <c r="D21" s="86" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E21" s="79" t="inlineStr">
+      <c r="E21" s="86" t="inlineStr">
         <is>
           <t>95104/2</t>
         </is>
       </c>
-      <c r="F21" s="79" t="inlineStr">
+      <c r="F21" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G21" s="79" t="inlineStr">
+      <c r="G21" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H21" s="80" t="n">
+      <c r="H21" s="87" t="n">
         <v>234.46</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="79" t="inlineStr">
+      <c r="A22" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B22" s="79" t="inlineStr">
+      <c r="B22" s="86" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C22" s="79" t="inlineStr">
+      <c r="C22" s="86" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D22" s="79" t="inlineStr">
+      <c r="D22" s="86" t="inlineStr">
         <is>
           <t>FAT.3575377</t>
         </is>
       </c>
-      <c r="E22" s="79" t="inlineStr">
+      <c r="E22" s="86" t="inlineStr">
         <is>
           <t>100172/1</t>
         </is>
       </c>
-      <c r="F22" s="79" t="inlineStr">
+      <c r="F22" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G22" s="79" t="inlineStr">
+      <c r="G22" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H22" s="80" t="n">
+      <c r="H22" s="87" t="n">
         <v>52.32</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="79" t="inlineStr">
+      <c r="A23" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B23" s="79" t="inlineStr">
+      <c r="B23" s="86" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C23" s="79" t="inlineStr">
+      <c r="C23" s="86" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D23" s="79" t="inlineStr">
+      <c r="D23" s="86" t="inlineStr">
         <is>
           <t>FAT.5290953</t>
         </is>
       </c>
-      <c r="E23" s="79" t="inlineStr">
+      <c r="E23" s="86" t="inlineStr">
         <is>
           <t>100173/1</t>
         </is>
       </c>
-      <c r="F23" s="79" t="inlineStr">
+      <c r="F23" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G23" s="79" t="inlineStr">
+      <c r="G23" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H23" s="80" t="n">
+      <c r="H23" s="87" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="79" t="inlineStr">
+      <c r="A24" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B24" s="79" t="inlineStr">
+      <c r="B24" s="86" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C24" s="79" t="inlineStr">
+      <c r="C24" s="86" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D24" s="79" t="inlineStr">
+      <c r="D24" s="86" t="inlineStr">
         <is>
           <t>BOL.141</t>
         </is>
       </c>
-      <c r="E24" s="79" t="inlineStr">
+      <c r="E24" s="86" t="inlineStr">
         <is>
           <t>99947/1</t>
         </is>
       </c>
-      <c r="F24" s="79" t="inlineStr">
+      <c r="F24" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G24" s="79" t="inlineStr">
+      <c r="G24" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H24" s="80" t="n">
+      <c r="H24" s="87" t="n">
         <v>338.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="79" t="inlineStr">
+      <c r="A25" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B25" s="79" t="inlineStr">
+      <c r="B25" s="86" t="inlineStr">
         <is>
           <t>13/02/2026</t>
         </is>
       </c>
-      <c r="C25" s="79" t="inlineStr">
+      <c r="C25" s="86" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D25" s="79" t="inlineStr">
+      <c r="D25" s="86" t="inlineStr">
         <is>
           <t>BOL.26449</t>
         </is>
       </c>
-      <c r="E25" s="79" t="inlineStr">
+      <c r="E25" s="86" t="inlineStr">
         <is>
           <t>99484/1</t>
         </is>
       </c>
-      <c r="F25" s="79" t="inlineStr">
+      <c r="F25" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G25" s="79" t="inlineStr">
+      <c r="G25" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H25" s="80" t="n">
+      <c r="H25" s="87" t="n">
         <v>137.94</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="79" t="inlineStr">
+      <c r="A26" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B26" s="79" t="inlineStr">
+      <c r="B26" s="86" t="inlineStr">
         <is>
           <t>19/02/2026</t>
         </is>
       </c>
-      <c r="C26" s="79" t="inlineStr">
+      <c r="C26" s="86" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D26" s="79" t="inlineStr">
+      <c r="D26" s="86" t="inlineStr">
         <is>
           <t>BOL.27256</t>
         </is>
       </c>
-      <c r="E26" s="79" t="inlineStr">
+      <c r="E26" s="86" t="inlineStr">
         <is>
           <t>99486/1</t>
         </is>
       </c>
-      <c r="F26" s="79" t="inlineStr">
+      <c r="F26" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G26" s="79" t="inlineStr">
+      <c r="G26" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H26" s="80" t="n">
+      <c r="H26" s="87" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="79" t="inlineStr">
+      <c r="A27" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B27" s="79" t="inlineStr">
+      <c r="B27" s="86" t="inlineStr">
         <is>
           <t>06/02/2026</t>
         </is>
       </c>
-      <c r="C27" s="79" t="inlineStr">
+      <c r="C27" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D27" s="79" t="inlineStr">
+      <c r="D27" s="86" t="inlineStr">
         <is>
           <t>SAL.SAL JANEIRO 2026</t>
         </is>
       </c>
-      <c r="E27" s="79" t="inlineStr">
+      <c r="E27" s="86" t="inlineStr">
         <is>
           <t>98811/1</t>
         </is>
       </c>
-      <c r="F27" s="79" t="inlineStr">
+      <c r="F27" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G27" s="79" t="inlineStr">
+      <c r="G27" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H27" s="80" t="n">
+      <c r="H27" s="87" t="n">
         <v>1750</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="79" t="inlineStr">
+      <c r="A28" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B28" s="79" t="inlineStr">
+      <c r="B28" s="86" t="inlineStr">
         <is>
           <t>20/02/2026</t>
         </is>
       </c>
-      <c r="C28" s="79" t="inlineStr">
+      <c r="C28" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D28" s="79" t="inlineStr">
+      <c r="D28" s="86" t="inlineStr">
         <is>
           <t>SAL.VALE FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E28" s="79" t="inlineStr">
+      <c r="E28" s="86" t="inlineStr">
         <is>
           <t>99890/1</t>
         </is>
       </c>
-      <c r="F28" s="79" t="inlineStr">
+      <c r="F28" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G28" s="79" t="inlineStr">
+      <c r="G28" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H28" s="80" t="n">
+      <c r="H28" s="87" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="79" t="inlineStr">
+      <c r="A29" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B29" s="79" t="inlineStr">
+      <c r="B29" s="86" t="inlineStr">
         <is>
           <t>2026-02-20 00:00:00</t>
         </is>
       </c>
-      <c r="C29" s="79" t="inlineStr">
+      <c r="C29" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D29" s="79" t="inlineStr">
+      <c r="D29" s="86" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E29" s="79" t="inlineStr">
+      <c r="E29" s="86" t="inlineStr">
         <is>
           <t>113754/2</t>
         </is>
       </c>
-      <c r="F29" s="79" t="inlineStr">
+      <c r="F29" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G29" s="79" t="inlineStr">
+      <c r="G29" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H29" s="80" t="n">
+      <c r="H29" s="87" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="79" t="inlineStr">
+      <c r="A30" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B30" s="79" t="inlineStr">
+      <c r="B30" s="86" t="inlineStr">
         <is>
           <t>2026-02-01 00:00:00</t>
         </is>
       </c>
-      <c r="C30" s="79" t="inlineStr">
+      <c r="C30" s="86" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D30" s="79" t="inlineStr"/>
-      <c r="E30" s="79" t="inlineStr"/>
-      <c r="F30" s="79" t="inlineStr">
+      <c r="D30" s="86" t="inlineStr"/>
+      <c r="E30" s="86" t="inlineStr"/>
+      <c r="F30" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G30" s="79" t="inlineStr">
+      <c r="G30" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H30" s="80" t="n">
+      <c r="H30" s="87" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="79" t="inlineStr">
+      <c r="A31" s="86" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B31" s="79" t="inlineStr">
+      <c r="B31" s="86" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C31" s="79" t="inlineStr">
+      <c r="C31" s="86" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D31" s="79" t="inlineStr">
+      <c r="D31" s="86" t="inlineStr">
         <is>
           <t>NFS.1430</t>
         </is>
       </c>
-      <c r="E31" s="79" t="inlineStr">
+      <c r="E31" s="86" t="inlineStr">
         <is>
           <t>99956/1</t>
         </is>
       </c>
-      <c r="F31" s="79" t="inlineStr">
+      <c r="F31" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G31" s="79" t="inlineStr">
+      <c r="G31" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H31" s="80" t="n">
+      <c r="H31" s="87" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="79" t="inlineStr">
+      <c r="A32" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B32" s="79" t="inlineStr">
+      <c r="B32" s="86" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C32" s="79" t="inlineStr">
+      <c r="C32" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D32" s="79" t="inlineStr">
+      <c r="D32" s="86" t="inlineStr">
         <is>
           <t>FAT.5042829</t>
         </is>
       </c>
-      <c r="E32" s="79" t="inlineStr">
+      <c r="E32" s="86" t="inlineStr">
         <is>
           <t>100503/1</t>
         </is>
       </c>
-      <c r="F32" s="79" t="inlineStr">
+      <c r="F32" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G32" s="79" t="inlineStr">
+      <c r="G32" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H32" s="80" t="n">
+      <c r="H32" s="87" t="n">
         <v>87.69</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="79" t="inlineStr">
+      <c r="A33" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B33" s="79" t="inlineStr">
+      <c r="B33" s="86" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C33" s="79" t="inlineStr">
+      <c r="C33" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D33" s="79" t="inlineStr">
+      <c r="D33" s="86" t="inlineStr">
         <is>
           <t>FAT.5042827</t>
         </is>
       </c>
-      <c r="E33" s="79" t="inlineStr">
+      <c r="E33" s="86" t="inlineStr">
         <is>
           <t>100504/1</t>
         </is>
       </c>
-      <c r="F33" s="79" t="inlineStr">
+      <c r="F33" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G33" s="79" t="inlineStr">
+      <c r="G33" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H33" s="80" t="n">
+      <c r="H33" s="87" t="n">
         <v>382.4</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="79" t="inlineStr">
+      <c r="A34" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B34" s="79" t="inlineStr">
+      <c r="B34" s="86" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="C34" s="79" t="inlineStr">
+      <c r="C34" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D34" s="79" t="inlineStr">
+      <c r="D34" s="86" t="inlineStr">
         <is>
           <t>FAT.8910508</t>
         </is>
       </c>
-      <c r="E34" s="79" t="inlineStr">
+      <c r="E34" s="86" t="inlineStr">
         <is>
           <t>102706/1</t>
         </is>
       </c>
-      <c r="F34" s="79" t="inlineStr">
+      <c r="F34" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G34" s="79" t="inlineStr">
+      <c r="G34" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H34" s="80" t="n">
+      <c r="H34" s="87" t="n">
         <v>429.49</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="79" t="inlineStr">
+      <c r="A35" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B35" s="79" t="inlineStr">
+      <c r="B35" s="86" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="C35" s="79" t="inlineStr">
+      <c r="C35" s="86" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D35" s="79" t="inlineStr">
+      <c r="D35" s="86" t="inlineStr">
         <is>
           <t>NFS.351653</t>
         </is>
       </c>
-      <c r="E35" s="79" t="inlineStr">
+      <c r="E35" s="86" t="inlineStr">
         <is>
           <t>100083/1</t>
         </is>
       </c>
-      <c r="F35" s="79" t="inlineStr">
+      <c r="F35" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G35" s="79" t="inlineStr">
+      <c r="G35" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H35" s="80" t="n">
+      <c r="H35" s="87" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="79" t="inlineStr">
+      <c r="A36" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B36" s="79" t="inlineStr">
+      <c r="B36" s="86" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="C36" s="79" t="inlineStr">
+      <c r="C36" s="86" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D36" s="79" t="inlineStr">
+      <c r="D36" s="86" t="inlineStr">
         <is>
           <t>NFS.359396</t>
         </is>
       </c>
-      <c r="E36" s="79" t="inlineStr">
+      <c r="E36" s="86" t="inlineStr">
         <is>
           <t>102608/1</t>
         </is>
       </c>
-      <c r="F36" s="79" t="inlineStr">
+      <c r="F36" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G36" s="79" t="inlineStr">
+      <c r="G36" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H36" s="80" t="n">
+      <c r="H36" s="87" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="79" t="inlineStr">
+      <c r="A37" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B37" s="79" t="inlineStr">
+      <c r="B37" s="86" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="C37" s="79" t="inlineStr">
+      <c r="C37" s="86" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D37" s="79" t="inlineStr">
+      <c r="D37" s="86" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E37" s="79" t="inlineStr">
+      <c r="E37" s="86" t="inlineStr">
         <is>
           <t>95104/3</t>
         </is>
       </c>
-      <c r="F37" s="79" t="inlineStr">
+      <c r="F37" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G37" s="79" t="inlineStr">
+      <c r="G37" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H37" s="80" t="n">
+      <c r="H37" s="87" t="n">
         <v>111.38</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="79" t="inlineStr">
+      <c r="A38" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B38" s="79" t="inlineStr">
+      <c r="B38" s="86" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C38" s="79" t="inlineStr">
+      <c r="C38" s="86" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D38" s="79" t="inlineStr">
+      <c r="D38" s="86" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E38" s="79" t="inlineStr">
+      <c r="E38" s="86" t="inlineStr">
         <is>
           <t>95104/4</t>
         </is>
       </c>
-      <c r="F38" s="79" t="inlineStr">
+      <c r="F38" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G38" s="79" t="inlineStr">
+      <c r="G38" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H38" s="80" t="n">
+      <c r="H38" s="87" t="n">
         <v>210.38</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="79" t="inlineStr">
+      <c r="A39" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B39" s="79" t="inlineStr">
+      <c r="B39" s="86" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="C39" s="79" t="inlineStr">
+      <c r="C39" s="86" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D39" s="79" t="inlineStr">
+      <c r="D39" s="86" t="inlineStr">
         <is>
           <t>FAT.2024588614</t>
         </is>
       </c>
-      <c r="E39" s="79" t="inlineStr">
+      <c r="E39" s="86" t="inlineStr">
         <is>
           <t>102316/1</t>
         </is>
       </c>
-      <c r="F39" s="79" t="inlineStr">
+      <c r="F39" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G39" s="79" t="inlineStr">
+      <c r="G39" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H39" s="80" t="n">
+      <c r="H39" s="87" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="79" t="inlineStr">
+      <c r="A40" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B40" s="79" t="inlineStr">
+      <c r="B40" s="86" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C40" s="79" t="inlineStr">
+      <c r="C40" s="86" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D40" s="79" t="inlineStr">
+      <c r="D40" s="86" t="inlineStr">
         <is>
           <t>BOL.5708173302</t>
         </is>
       </c>
-      <c r="E40" s="79" t="inlineStr">
+      <c r="E40" s="86" t="inlineStr">
         <is>
           <t>102057/1</t>
         </is>
       </c>
-      <c r="F40" s="79" t="inlineStr">
+      <c r="F40" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G40" s="79" t="inlineStr">
+      <c r="G40" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H40" s="80" t="n">
+      <c r="H40" s="87" t="n">
         <v>284.63</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="79" t="inlineStr">
+      <c r="A41" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B41" s="79" t="inlineStr">
+      <c r="B41" s="86" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="C41" s="79" t="inlineStr">
+      <c r="C41" s="86" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D41" s="79" t="inlineStr">
+      <c r="D41" s="86" t="inlineStr">
         <is>
           <t>BOL.28049</t>
         </is>
       </c>
-      <c r="E41" s="79" t="inlineStr">
+      <c r="E41" s="86" t="inlineStr">
         <is>
           <t>100887/1</t>
         </is>
       </c>
-      <c r="F41" s="79" t="inlineStr">
+      <c r="F41" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G41" s="79" t="inlineStr">
+      <c r="G41" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H41" s="80" t="n">
+      <c r="H41" s="87" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="79" t="inlineStr">
+      <c r="A42" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B42" s="79" t="inlineStr">
+      <c r="B42" s="86" t="inlineStr">
         <is>
           <t>06/03/2026</t>
         </is>
       </c>
-      <c r="C42" s="79" t="inlineStr">
+      <c r="C42" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D42" s="79" t="inlineStr">
+      <c r="D42" s="86" t="inlineStr">
         <is>
           <t>SAL.SAL FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E42" s="79" t="inlineStr">
+      <c r="E42" s="86" t="inlineStr">
         <is>
           <t>101276/1</t>
         </is>
       </c>
-      <c r="F42" s="79" t="inlineStr">
+      <c r="F42" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G42" s="79" t="inlineStr">
+      <c r="G42" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H42" s="80" t="n">
+      <c r="H42" s="87" t="n">
         <v>1542</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="79" t="inlineStr">
+      <c r="A43" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B43" s="79" t="inlineStr">
+      <c r="B43" s="86" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C43" s="79" t="inlineStr">
+      <c r="C43" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D43" s="79" t="inlineStr">
+      <c r="D43" s="86" t="inlineStr">
         <is>
           <t>SAL.VALE 032026</t>
         </is>
       </c>
-      <c r="E43" s="79" t="inlineStr">
+      <c r="E43" s="86" t="inlineStr">
         <is>
           <t>102295/1</t>
         </is>
       </c>
-      <c r="F43" s="79" t="inlineStr">
+      <c r="F43" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G43" s="79" t="inlineStr">
+      <c r="G43" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H43" s="80" t="n">
+      <c r="H43" s="87" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="79" t="inlineStr">
+      <c r="A44" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B44" s="79" t="inlineStr">
+      <c r="B44" s="86" t="inlineStr">
         <is>
           <t>2026-03-20 00:00:00</t>
         </is>
       </c>
-      <c r="C44" s="79" t="inlineStr">
+      <c r="C44" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D44" s="79" t="inlineStr">
+      <c r="D44" s="86" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E44" s="79" t="inlineStr">
+      <c r="E44" s="86" t="inlineStr">
         <is>
           <t>113754/3</t>
         </is>
       </c>
-      <c r="F44" s="79" t="inlineStr">
+      <c r="F44" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G44" s="79" t="inlineStr">
+      <c r="G44" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H44" s="80" t="n">
+      <c r="H44" s="87" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="79" t="inlineStr">
+      <c r="A45" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B45" s="79" t="inlineStr">
+      <c r="B45" s="86" t="inlineStr">
         <is>
           <t>2026-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="C45" s="79" t="inlineStr">
+      <c r="C45" s="86" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D45" s="79" t="inlineStr"/>
-      <c r="E45" s="79" t="inlineStr"/>
-      <c r="F45" s="79" t="inlineStr">
+      <c r="D45" s="86" t="inlineStr"/>
+      <c r="E45" s="86" t="inlineStr"/>
+      <c r="F45" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G45" s="79" t="inlineStr">
+      <c r="G45" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H45" s="80" t="n">
+      <c r="H45" s="87" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="79" t="inlineStr">
+      <c r="A46" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B46" s="79" t="inlineStr">
+      <c r="B46" s="86" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C46" s="79" t="inlineStr">
+      <c r="C46" s="86" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D46" s="79" t="inlineStr">
+      <c r="D46" s="86" t="inlineStr">
         <is>
           <t>NFS.1500</t>
         </is>
       </c>
-      <c r="E46" s="79" t="inlineStr">
+      <c r="E46" s="86" t="inlineStr">
         <is>
           <t>102432/1</t>
         </is>
       </c>
-      <c r="F46" s="79" t="inlineStr">
+      <c r="F46" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G46" s="79" t="inlineStr">
+      <c r="G46" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H46" s="80" t="n">
+      <c r="H46" s="87" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="79" t="inlineStr">
+      <c r="A47" s="86" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B47" s="79" t="inlineStr">
+      <c r="B47" s="86" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C47" s="79" t="inlineStr">
+      <c r="C47" s="86" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D47" s="79" t="inlineStr">
+      <c r="D47" s="86" t="inlineStr">
         <is>
           <t>NFS.1534</t>
         </is>
       </c>
-      <c r="E47" s="79" t="inlineStr">
+      <c r="E47" s="86" t="inlineStr">
         <is>
           <t>102434/1</t>
         </is>
       </c>
-      <c r="F47" s="79" t="inlineStr">
+      <c r="F47" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G47" s="79" t="inlineStr">
+      <c r="G47" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H47" s="80" t="n">
+      <c r="H47" s="87" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="79" t="inlineStr">
+      <c r="A48" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B48" s="79" t="inlineStr">
+      <c r="B48" s="86" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C48" s="79" t="inlineStr">
+      <c r="C48" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D48" s="79" t="inlineStr">
+      <c r="D48" s="86" t="inlineStr">
         <is>
           <t>FAT.8910315</t>
         </is>
       </c>
-      <c r="E48" s="79" t="inlineStr">
+      <c r="E48" s="86" t="inlineStr">
         <is>
           <t>105607/1</t>
         </is>
       </c>
-      <c r="F48" s="79" t="inlineStr">
+      <c r="F48" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G48" s="79" t="inlineStr">
+      <c r="G48" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H48" s="80" t="n">
+      <c r="H48" s="87" t="n">
         <v>11.99</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="79" t="inlineStr">
+      <c r="A49" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B49" s="79" t="inlineStr">
+      <c r="B49" s="86" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C49" s="79" t="inlineStr">
+      <c r="C49" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D49" s="79" t="inlineStr">
+      <c r="D49" s="86" t="inlineStr">
         <is>
           <t>FAT.13443658</t>
         </is>
       </c>
-      <c r="E49" s="79" t="inlineStr">
+      <c r="E49" s="86" t="inlineStr">
         <is>
           <t>105676/1</t>
         </is>
       </c>
-      <c r="F49" s="79" t="inlineStr">
+      <c r="F49" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G49" s="79" t="inlineStr">
+      <c r="G49" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H49" s="80" t="n">
+      <c r="H49" s="87" t="n">
         <v>557.63</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="79" t="inlineStr">
+      <c r="A50" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B50" s="79" t="inlineStr">
+      <c r="B50" s="86" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C50" s="79" t="inlineStr">
+      <c r="C50" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D50" s="79" t="inlineStr">
+      <c r="D50" s="86" t="inlineStr">
         <is>
           <t>FAT.13443664</t>
         </is>
       </c>
-      <c r="E50" s="79" t="inlineStr">
+      <c r="E50" s="86" t="inlineStr">
         <is>
           <t>105677/1</t>
         </is>
       </c>
-      <c r="F50" s="79" t="inlineStr">
+      <c r="F50" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G50" s="79" t="inlineStr">
+      <c r="G50" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H50" s="80" t="n">
+      <c r="H50" s="87" t="n">
         <v>132.09</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="79" t="inlineStr">
+      <c r="A51" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B51" s="79" t="inlineStr">
+      <c r="B51" s="86" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C51" s="79" t="inlineStr">
+      <c r="C51" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D51" s="79" t="inlineStr">
+      <c r="D51" s="86" t="inlineStr">
         <is>
           <t>FAT.13443112</t>
         </is>
       </c>
-      <c r="E51" s="79" t="inlineStr">
+      <c r="E51" s="86" t="inlineStr">
         <is>
           <t>105792/1</t>
         </is>
       </c>
-      <c r="F51" s="79" t="inlineStr">
+      <c r="F51" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G51" s="79" t="inlineStr">
+      <c r="G51" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H51" s="80" t="n">
+      <c r="H51" s="87" t="n">
         <v>20.23</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="79" t="inlineStr">
+      <c r="A52" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B52" s="79" t="inlineStr">
+      <c r="B52" s="86" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C52" s="79" t="inlineStr">
+      <c r="C52" s="86" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D52" s="79" t="inlineStr">
+      <c r="D52" s="86" t="inlineStr">
         <is>
           <t>NFS.363799</t>
         </is>
       </c>
-      <c r="E52" s="79" t="inlineStr">
+      <c r="E52" s="86" t="inlineStr">
         <is>
           <t>104634/1</t>
         </is>
       </c>
-      <c r="F52" s="79" t="inlineStr">
+      <c r="F52" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G52" s="79" t="inlineStr">
+      <c r="G52" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H52" s="80" t="n">
+      <c r="H52" s="87" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="79" t="inlineStr">
+      <c r="A53" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B53" s="79" t="inlineStr">
+      <c r="B53" s="86" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="C53" s="79" t="inlineStr">
+      <c r="C53" s="86" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D53" s="79" t="inlineStr">
+      <c r="D53" s="86" t="inlineStr">
         <is>
           <t>BOL.04.26</t>
         </is>
       </c>
-      <c r="E53" s="79" t="inlineStr">
+      <c r="E53" s="86" t="inlineStr">
         <is>
           <t>104820/1</t>
         </is>
       </c>
-      <c r="F53" s="79" t="inlineStr">
+      <c r="F53" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G53" s="79" t="inlineStr">
+      <c r="G53" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H53" s="80" t="n">
+      <c r="H53" s="87" t="n">
         <v>1024.76</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="79" t="inlineStr">
+      <c r="A54" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B54" s="79" t="inlineStr">
+      <c r="B54" s="86" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C54" s="79" t="inlineStr">
+      <c r="C54" s="86" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D54" s="79" t="inlineStr">
+      <c r="D54" s="86" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 29.04.26</t>
         </is>
       </c>
-      <c r="E54" s="79" t="inlineStr">
+      <c r="E54" s="86" t="inlineStr">
         <is>
           <t>106325/1</t>
         </is>
       </c>
-      <c r="F54" s="79" t="inlineStr">
+      <c r="F54" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G54" s="79" t="inlineStr">
+      <c r="G54" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H54" s="80" t="n">
+      <c r="H54" s="87" t="n">
         <v>21.76</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="79" t="inlineStr">
+      <c r="A55" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B55" s="79" t="inlineStr">
+      <c r="B55" s="86" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C55" s="79" t="inlineStr">
+      <c r="C55" s="86" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D55" s="79" t="inlineStr">
+      <c r="D55" s="86" t="inlineStr">
         <is>
           <t>FAT.CHATGPT 3 LIC</t>
         </is>
       </c>
-      <c r="E55" s="79" t="inlineStr">
+      <c r="E55" s="86" t="inlineStr">
         <is>
           <t>102137/1</t>
         </is>
       </c>
-      <c r="F55" s="79" t="inlineStr">
+      <c r="F55" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G55" s="79" t="inlineStr">
+      <c r="G55" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H55" s="80" t="n">
+      <c r="H55" s="87" t="n">
         <v>5393.88</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="79" t="inlineStr">
+      <c r="A56" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B56" s="79" t="inlineStr">
+      <c r="B56" s="86" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C56" s="79" t="inlineStr">
+      <c r="C56" s="86" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D56" s="79" t="inlineStr">
+      <c r="D56" s="86" t="inlineStr">
         <is>
           <t>BOL.28855</t>
         </is>
       </c>
-      <c r="E56" s="79" t="inlineStr">
+      <c r="E56" s="86" t="inlineStr">
         <is>
           <t>103694/1</t>
         </is>
       </c>
-      <c r="F56" s="79" t="inlineStr">
+      <c r="F56" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G56" s="79" t="inlineStr">
+      <c r="G56" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H56" s="80" t="n">
+      <c r="H56" s="87" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="79" t="inlineStr">
+      <c r="A57" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B57" s="79" t="inlineStr">
+      <c r="B57" s="86" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="C57" s="79" t="inlineStr">
+      <c r="C57" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D57" s="79" t="inlineStr">
+      <c r="D57" s="86" t="inlineStr">
         <is>
           <t>SAL.SAL 032026</t>
         </is>
       </c>
-      <c r="E57" s="79" t="inlineStr">
+      <c r="E57" s="86" t="inlineStr">
         <is>
           <t>103924/1</t>
         </is>
       </c>
-      <c r="F57" s="79" t="inlineStr">
+      <c r="F57" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G57" s="79" t="inlineStr">
+      <c r="G57" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H57" s="80" t="n">
+      <c r="H57" s="87" t="n">
         <v>1515</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="79" t="inlineStr">
+      <c r="A58" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B58" s="79" t="inlineStr">
+      <c r="B58" s="86" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="C58" s="79" t="inlineStr">
+      <c r="C58" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D58" s="79" t="inlineStr">
+      <c r="D58" s="86" t="inlineStr">
         <is>
           <t>SAL.vale 042026</t>
         </is>
       </c>
-      <c r="E58" s="79" t="inlineStr">
+      <c r="E58" s="86" t="inlineStr">
         <is>
           <t>105055/1</t>
         </is>
       </c>
-      <c r="F58" s="79" t="inlineStr">
+      <c r="F58" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G58" s="79" t="inlineStr">
+      <c r="G58" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H58" s="80" t="n">
+      <c r="H58" s="87" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="79" t="inlineStr">
+      <c r="A59" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B59" s="79" t="inlineStr">
+      <c r="B59" s="86" t="inlineStr">
         <is>
           <t>2026-04-20 00:00:00</t>
         </is>
       </c>
-      <c r="C59" s="79" t="inlineStr">
+      <c r="C59" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D59" s="79" t="inlineStr">
+      <c r="D59" s="86" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E59" s="79" t="inlineStr">
+      <c r="E59" s="86" t="inlineStr">
         <is>
           <t>113754/4</t>
         </is>
       </c>
-      <c r="F59" s="79" t="inlineStr">
+      <c r="F59" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G59" s="79" t="inlineStr">
+      <c r="G59" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H59" s="80" t="n">
+      <c r="H59" s="87" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="79" t="inlineStr">
+      <c r="A60" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B60" s="79" t="inlineStr">
+      <c r="B60" s="86" t="inlineStr">
         <is>
           <t>2026-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="C60" s="79" t="inlineStr">
+      <c r="C60" s="86" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D60" s="79" t="inlineStr"/>
-      <c r="E60" s="79" t="inlineStr"/>
-      <c r="F60" s="79" t="inlineStr">
+      <c r="D60" s="86" t="inlineStr"/>
+      <c r="E60" s="86" t="inlineStr"/>
+      <c r="F60" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G60" s="79" t="inlineStr">
+      <c r="G60" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H60" s="80" t="n">
+      <c r="H60" s="87" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="79" t="inlineStr">
+      <c r="A61" s="86" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B61" s="79" t="inlineStr">
+      <c r="B61" s="86" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="C61" s="79" t="inlineStr">
+      <c r="C61" s="86" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D61" s="79" t="inlineStr">
+      <c r="D61" s="86" t="inlineStr">
         <is>
           <t>NFS.1573</t>
         </is>
       </c>
-      <c r="E61" s="79" t="inlineStr">
+      <c r="E61" s="86" t="inlineStr">
         <is>
           <t>105411/1</t>
         </is>
       </c>
-      <c r="F61" s="79" t="inlineStr">
+      <c r="F61" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G61" s="79" t="inlineStr">
+      <c r="G61" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H61" s="80" t="n">
+      <c r="H61" s="87" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="79" t="inlineStr">
+      <c r="A62" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B62" s="79" t="inlineStr">
+      <c r="B62" s="86" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="C62" s="79" t="inlineStr">
+      <c r="C62" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D62" s="79" t="inlineStr">
+      <c r="D62" s="86" t="inlineStr">
         <is>
           <t>FAT.2ªvia Claro Abril</t>
         </is>
       </c>
-      <c r="E62" s="79" t="inlineStr">
+      <c r="E62" s="86" t="inlineStr">
         <is>
           <t>107340/1</t>
         </is>
       </c>
-      <c r="F62" s="79" t="inlineStr">
+      <c r="F62" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G62" s="79" t="inlineStr">
+      <c r="G62" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H62" s="80" t="n">
+      <c r="H62" s="87" t="n">
         <v>182.32</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="79" t="inlineStr">
+      <c r="A63" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B63" s="79" t="inlineStr">
+      <c r="B63" s="86" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C63" s="79" t="inlineStr">
+      <c r="C63" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D63" s="79" t="inlineStr">
+      <c r="D63" s="86" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E63" s="79" t="inlineStr">
+      <c r="E63" s="86" t="inlineStr">
         <is>
           <t>108218/1</t>
         </is>
       </c>
-      <c r="F63" s="79" t="inlineStr">
+      <c r="F63" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G63" s="79" t="inlineStr">
+      <c r="G63" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H63" s="80" t="n">
+      <c r="H63" s="87" t="n">
         <v>629.98</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="79" t="inlineStr">
+      <c r="A64" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B64" s="79" t="inlineStr">
+      <c r="B64" s="86" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C64" s="79" t="inlineStr">
+      <c r="C64" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D64" s="79" t="inlineStr">
+      <c r="D64" s="86" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E64" s="79" t="inlineStr">
+      <c r="E64" s="86" t="inlineStr">
         <is>
           <t>108218/2</t>
         </is>
       </c>
-      <c r="F64" s="79" t="inlineStr">
+      <c r="F64" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G64" s="79" t="inlineStr">
+      <c r="G64" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H64" s="80" t="n">
+      <c r="H64" s="87" t="n">
         <v>18.86</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="79" t="inlineStr">
+      <c r="A65" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B65" s="79" t="inlineStr">
+      <c r="B65" s="86" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C65" s="79" t="inlineStr">
+      <c r="C65" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D65" s="79" t="inlineStr">
+      <c r="D65" s="86" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E65" s="79" t="inlineStr">
+      <c r="E65" s="86" t="inlineStr">
         <is>
           <t>108218/3</t>
         </is>
       </c>
-      <c r="F65" s="79" t="inlineStr">
+      <c r="F65" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G65" s="79" t="inlineStr">
+      <c r="G65" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H65" s="80" t="n">
+      <c r="H65" s="87" t="n">
         <v>133.95</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="79" t="inlineStr">
+      <c r="A66" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B66" s="79" t="inlineStr">
+      <c r="B66" s="86" t="inlineStr">
         <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="C66" s="79" t="inlineStr">
+      <c r="C66" s="86" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D66" s="79" t="inlineStr">
+      <c r="D66" s="86" t="inlineStr">
         <is>
           <t>NFS.76</t>
         </is>
       </c>
-      <c r="E66" s="79" t="inlineStr">
+      <c r="E66" s="86" t="inlineStr">
         <is>
           <t>105987/1</t>
         </is>
       </c>
-      <c r="F66" s="79" t="inlineStr">
+      <c r="F66" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G66" s="79" t="inlineStr">
+      <c r="G66" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H66" s="80" t="n">
+      <c r="H66" s="87" t="n">
         <v>3723.62</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="79" t="inlineStr">
+      <c r="A67" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B67" s="79" t="inlineStr">
+      <c r="B67" s="86" t="inlineStr">
         <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="C67" s="79" t="inlineStr">
+      <c r="C67" s="86" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D67" s="79" t="inlineStr">
+      <c r="D67" s="86" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 11.05.26</t>
         </is>
       </c>
-      <c r="E67" s="79" t="inlineStr">
+      <c r="E67" s="86" t="inlineStr">
         <is>
           <t>107254/1</t>
         </is>
       </c>
-      <c r="F67" s="79" t="inlineStr">
+      <c r="F67" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G67" s="79" t="inlineStr">
+      <c r="G67" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H67" s="80" t="n">
+      <c r="H67" s="87" t="n">
         <v>74.81</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="79" t="inlineStr">
+      <c r="A68" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B68" s="79" t="inlineStr">
+      <c r="B68" s="86" t="inlineStr">
         <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="C68" s="79" t="inlineStr">
+      <c r="C68" s="86" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D68" s="79" t="inlineStr">
+      <c r="D68" s="86" t="inlineStr">
         <is>
           <t>NFS.5744</t>
         </is>
       </c>
-      <c r="E68" s="79" t="inlineStr">
+      <c r="E68" s="86" t="inlineStr">
         <is>
           <t>106664/1</t>
         </is>
       </c>
-      <c r="F68" s="79" t="inlineStr">
+      <c r="F68" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G68" s="79" t="inlineStr">
+      <c r="G68" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H68" s="80" t="n">
+      <c r="H68" s="87" t="n">
         <v>741.1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="79" t="inlineStr">
+      <c r="A69" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B69" s="79" t="inlineStr">
+      <c r="B69" s="86" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C69" s="79" t="inlineStr">
+      <c r="C69" s="86" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D69" s="79" t="inlineStr">
+      <c r="D69" s="86" t="inlineStr">
         <is>
           <t>BOL.29637</t>
         </is>
       </c>
-      <c r="E69" s="79" t="inlineStr">
+      <c r="E69" s="86" t="inlineStr">
         <is>
           <t>108040/1</t>
         </is>
       </c>
-      <c r="F69" s="79" t="inlineStr">
+      <c r="F69" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G69" s="79" t="inlineStr">
+      <c r="G69" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H69" s="80" t="n">
+      <c r="H69" s="87" t="n">
         <v>137.92</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="79" t="inlineStr">
+      <c r="A70" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B70" s="79" t="inlineStr">
+      <c r="B70" s="86" t="inlineStr">
         <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="C70" s="79" t="inlineStr">
+      <c r="C70" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D70" s="79" t="inlineStr">
+      <c r="D70" s="86" t="inlineStr">
         <is>
           <t>SAL.sal 042026</t>
         </is>
       </c>
-      <c r="E70" s="79" t="inlineStr">
+      <c r="E70" s="86" t="inlineStr">
         <is>
           <t>106947/1</t>
         </is>
       </c>
-      <c r="F70" s="79" t="inlineStr">
+      <c r="F70" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G70" s="79" t="inlineStr">
+      <c r="G70" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H70" s="80" t="n">
+      <c r="H70" s="87" t="n">
         <v>1483</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="79" t="inlineStr">
+      <c r="A71" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B71" s="79" t="inlineStr">
+      <c r="B71" s="86" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="C71" s="79" t="inlineStr">
+      <c r="C71" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D71" s="79" t="inlineStr">
+      <c r="D71" s="86" t="inlineStr">
         <is>
           <t>SAL.vale 052026</t>
         </is>
       </c>
-      <c r="E71" s="79" t="inlineStr">
+      <c r="E71" s="86" t="inlineStr">
         <is>
           <t>108156/1</t>
         </is>
       </c>
-      <c r="F71" s="79" t="inlineStr">
+      <c r="F71" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G71" s="79" t="inlineStr">
+      <c r="G71" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H71" s="80" t="n">
+      <c r="H71" s="87" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="79" t="inlineStr">
+      <c r="A72" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B72" s="79" t="inlineStr">
+      <c r="B72" s="86" t="inlineStr">
         <is>
           <t>2026-05-20 00:00:00</t>
         </is>
       </c>
-      <c r="C72" s="79" t="inlineStr">
+      <c r="C72" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D72" s="79" t="inlineStr">
+      <c r="D72" s="86" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E72" s="79" t="inlineStr">
+      <c r="E72" s="86" t="inlineStr">
         <is>
           <t>113754/5</t>
         </is>
       </c>
-      <c r="F72" s="79" t="inlineStr">
+      <c r="F72" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G72" s="79" t="inlineStr">
+      <c r="G72" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H72" s="80" t="n">
+      <c r="H72" s="87" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="79" t="inlineStr">
+      <c r="A73" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B73" s="79" t="inlineStr">
+      <c r="B73" s="86" t="inlineStr">
         <is>
           <t>2026-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="C73" s="79" t="inlineStr">
+      <c r="C73" s="86" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D73" s="79" t="inlineStr"/>
-      <c r="E73" s="79" t="inlineStr"/>
-      <c r="F73" s="79" t="inlineStr">
+      <c r="D73" s="86" t="inlineStr"/>
+      <c r="E73" s="86" t="inlineStr"/>
+      <c r="F73" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G73" s="79" t="inlineStr">
+      <c r="G73" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H73" s="80" t="n">
+      <c r="H73" s="87" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="79" t="inlineStr">
+      <c r="A74" s="86" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B74" s="79" t="inlineStr">
+      <c r="B74" s="86" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C74" s="79" t="inlineStr">
+      <c r="C74" s="86" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D74" s="79" t="inlineStr">
+      <c r="D74" s="86" t="inlineStr">
         <is>
           <t>NFS.1631</t>
         </is>
       </c>
-      <c r="E74" s="79" t="inlineStr">
+      <c r="E74" s="86" t="inlineStr">
         <is>
           <t>107973/1</t>
         </is>
       </c>
-      <c r="F74" s="79" t="inlineStr">
+      <c r="F74" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G74" s="79" t="inlineStr">
+      <c r="G74" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H74" s="80" t="n">
+      <c r="H74" s="87" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="79" t="inlineStr">
+      <c r="A75" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B75" s="79" t="inlineStr">
+      <c r="B75" s="86" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C75" s="79" t="inlineStr">
+      <c r="C75" s="86" t="inlineStr">
         <is>
           <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
         </is>
       </c>
-      <c r="D75" s="79" t="inlineStr">
+      <c r="D75" s="86" t="inlineStr">
         <is>
           <t>AV.1015392</t>
         </is>
       </c>
-      <c r="E75" s="79" t="inlineStr">
+      <c r="E75" s="86" t="inlineStr">
         <is>
           <t>108925/1</t>
         </is>
       </c>
-      <c r="F75" s="79" t="inlineStr">
+      <c r="F75" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G75" s="79" t="inlineStr">
+      <c r="G75" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H75" s="80" t="n">
+      <c r="H75" s="87" t="n">
         <v>183.6</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="79" t="inlineStr">
+      <c r="A76" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B76" s="79" t="inlineStr">
+      <c r="B76" s="86" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C76" s="79" t="inlineStr">
+      <c r="C76" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D76" s="79" t="inlineStr">
+      <c r="D76" s="86" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E76" s="79" t="inlineStr">
+      <c r="E76" s="86" t="inlineStr">
         <is>
           <t>111124/1</t>
         </is>
       </c>
-      <c r="F76" s="79" t="inlineStr">
+      <c r="F76" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G76" s="79" t="inlineStr">
+      <c r="G76" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H76" s="80" t="n">
+      <c r="H76" s="87" t="n">
         <v>720</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="79" t="inlineStr">
+      <c r="A77" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B77" s="79" t="inlineStr">
+      <c r="B77" s="86" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C77" s="79" t="inlineStr">
+      <c r="C77" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D77" s="79" t="inlineStr">
+      <c r="D77" s="86" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E77" s="79" t="inlineStr">
+      <c r="E77" s="86" t="inlineStr">
         <is>
           <t>111124/3</t>
         </is>
       </c>
-      <c r="F77" s="79" t="inlineStr">
+      <c r="F77" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G77" s="79" t="inlineStr">
+      <c r="G77" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H77" s="80" t="n">
+      <c r="H77" s="87" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="79" t="inlineStr">
+      <c r="A78" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B78" s="79" t="inlineStr">
+      <c r="B78" s="86" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C78" s="79" t="inlineStr">
+      <c r="C78" s="86" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D78" s="79" t="inlineStr">
+      <c r="D78" s="86" t="inlineStr">
         <is>
           <t>NFS.373725</t>
         </is>
       </c>
-      <c r="E78" s="79" t="inlineStr">
+      <c r="E78" s="86" t="inlineStr">
         <is>
           <t>110785/1</t>
         </is>
       </c>
-      <c r="F78" s="79" t="inlineStr">
+      <c r="F78" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G78" s="79" t="inlineStr">
+      <c r="G78" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H78" s="80" t="n">
+      <c r="H78" s="87" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="79" t="inlineStr">
+      <c r="A79" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B79" s="79" t="inlineStr">
+      <c r="B79" s="86" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C79" s="79" t="inlineStr">
+      <c r="C79" s="86" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D79" s="79" t="inlineStr">
+      <c r="D79" s="86" t="inlineStr">
         <is>
           <t>NFS.0036884701</t>
         </is>
       </c>
-      <c r="E79" s="79" t="inlineStr">
+      <c r="E79" s="86" t="inlineStr">
         <is>
           <t>109295/1</t>
         </is>
       </c>
-      <c r="F79" s="79" t="inlineStr">
+      <c r="F79" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G79" s="79" t="inlineStr">
+      <c r="G79" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H79" s="80" t="n">
+      <c r="H79" s="87" t="n">
         <v>84.81999999999999</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="79" t="inlineStr">
+      <c r="A80" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B80" s="79" t="inlineStr">
+      <c r="B80" s="86" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C80" s="79" t="inlineStr">
+      <c r="C80" s="86" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D80" s="79" t="inlineStr">
+      <c r="D80" s="86" t="inlineStr">
         <is>
           <t>NFS.78</t>
         </is>
       </c>
-      <c r="E80" s="79" t="inlineStr">
+      <c r="E80" s="86" t="inlineStr">
         <is>
           <t>108317/1</t>
         </is>
       </c>
-      <c r="F80" s="79" t="inlineStr">
+      <c r="F80" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G80" s="79" t="inlineStr">
+      <c r="G80" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H80" s="80" t="n">
+      <c r="H80" s="87" t="n">
         <v>6173.37</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="79" t="inlineStr">
+      <c r="A81" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B81" s="79" t="inlineStr">
+      <c r="B81" s="86" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="C81" s="79" t="inlineStr">
+      <c r="C81" s="86" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D81" s="79" t="inlineStr">
+      <c r="D81" s="86" t="inlineStr">
         <is>
           <t>NFS.5832</t>
         </is>
       </c>
-      <c r="E81" s="79" t="inlineStr">
+      <c r="E81" s="86" t="inlineStr">
         <is>
           <t>109227/1</t>
         </is>
       </c>
-      <c r="F81" s="79" t="inlineStr">
+      <c r="F81" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G81" s="79" t="inlineStr">
+      <c r="G81" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H81" s="80" t="n">
+      <c r="H81" s="87" t="n">
         <v>740.38</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="79" t="inlineStr">
+      <c r="A82" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B82" s="79" t="inlineStr">
+      <c r="B82" s="86" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C82" s="79" t="inlineStr">
+      <c r="C82" s="86" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D82" s="79" t="inlineStr">
+      <c r="D82" s="86" t="inlineStr">
         <is>
           <t>FAT.Vivo 04 2026</t>
         </is>
       </c>
-      <c r="E82" s="79" t="inlineStr">
+      <c r="E82" s="86" t="inlineStr">
         <is>
           <t>110752/1</t>
         </is>
       </c>
-      <c r="F82" s="79" t="inlineStr">
+      <c r="F82" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G82" s="79" t="inlineStr">
+      <c r="G82" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H82" s="80" t="n">
+      <c r="H82" s="87" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="79" t="inlineStr">
+      <c r="A83" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B83" s="79" t="inlineStr">
+      <c r="B83" s="86" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C83" s="79" t="inlineStr">
+      <c r="C83" s="86" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D83" s="79" t="inlineStr">
+      <c r="D83" s="86" t="inlineStr">
         <is>
           <t>FAT.Vivo 05 2026</t>
         </is>
       </c>
-      <c r="E83" s="79" t="inlineStr">
+      <c r="E83" s="86" t="inlineStr">
         <is>
           <t>110753/1</t>
         </is>
       </c>
-      <c r="F83" s="79" t="inlineStr">
+      <c r="F83" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G83" s="79" t="inlineStr">
+      <c r="G83" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H83" s="80" t="n">
+      <c r="H83" s="87" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="79" t="inlineStr">
+      <c r="A84" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B84" s="79" t="inlineStr">
+      <c r="B84" s="86" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C84" s="79" t="inlineStr">
+      <c r="C84" s="86" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D84" s="79" t="inlineStr">
+      <c r="D84" s="86" t="inlineStr">
         <is>
           <t>FAT.Vivo 06 2026</t>
         </is>
       </c>
-      <c r="E84" s="79" t="inlineStr">
+      <c r="E84" s="86" t="inlineStr">
         <is>
           <t>110754/1</t>
         </is>
       </c>
-      <c r="F84" s="79" t="inlineStr">
+      <c r="F84" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G84" s="79" t="inlineStr">
+      <c r="G84" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H84" s="80" t="n">
+      <c r="H84" s="87" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="79" t="inlineStr">
+      <c r="A85" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B85" s="79" t="inlineStr">
+      <c r="B85" s="86" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C85" s="79" t="inlineStr">
+      <c r="C85" s="86" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D85" s="79" t="inlineStr">
+      <c r="D85" s="86" t="inlineStr">
         <is>
           <t>BOL.1017717992</t>
         </is>
       </c>
-      <c r="E85" s="79" t="inlineStr">
+      <c r="E85" s="86" t="inlineStr">
         <is>
           <t>109298/1</t>
         </is>
       </c>
-      <c r="F85" s="79" t="inlineStr">
+      <c r="F85" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G85" s="79" t="inlineStr">
+      <c r="G85" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H85" s="80" t="n">
+      <c r="H85" s="87" t="n">
         <v>137.93</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="79" t="inlineStr">
+      <c r="A86" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B86" s="79" t="inlineStr">
+      <c r="B86" s="86" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C86" s="79" t="inlineStr">
+      <c r="C86" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D86" s="79" t="inlineStr">
+      <c r="D86" s="86" t="inlineStr">
         <is>
           <t>CX.27.05.26</t>
         </is>
       </c>
-      <c r="E86" s="79" t="inlineStr">
+      <c r="E86" s="86" t="inlineStr">
         <is>
           <t>108827/1</t>
         </is>
       </c>
-      <c r="F86" s="79" t="inlineStr">
+      <c r="F86" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G86" s="79" t="inlineStr">
+      <c r="G86" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H86" s="80" t="n">
+      <c r="H86" s="87" t="n">
         <v>184</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="79" t="inlineStr">
+      <c r="A87" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B87" s="79" t="inlineStr">
+      <c r="B87" s="86" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C87" s="79" t="inlineStr">
+      <c r="C87" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D87" s="79" t="inlineStr">
+      <c r="D87" s="86" t="inlineStr">
         <is>
           <t>SAL.1_ Ferias 1 VIn D 26</t>
         </is>
       </c>
-      <c r="E87" s="79" t="inlineStr">
+      <c r="E87" s="86" t="inlineStr">
         <is>
           <t>107780/1</t>
         </is>
       </c>
-      <c r="F87" s="79" t="inlineStr">
+      <c r="F87" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G87" s="79" t="inlineStr">
+      <c r="G87" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H87" s="80" t="n">
+      <c r="H87" s="87" t="n">
         <v>1101.12</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="79" t="inlineStr">
+      <c r="A88" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B88" s="79" t="inlineStr">
+      <c r="B88" s="86" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C88" s="79" t="inlineStr">
+      <c r="C88" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D88" s="79" t="inlineStr">
+      <c r="D88" s="86" t="inlineStr">
         <is>
           <t>SAL.sal 052026</t>
         </is>
       </c>
-      <c r="E88" s="79" t="inlineStr">
+      <c r="E88" s="86" t="inlineStr">
         <is>
           <t>109482/1</t>
         </is>
       </c>
-      <c r="F88" s="79" t="inlineStr">
+      <c r="F88" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G88" s="79" t="inlineStr">
+      <c r="G88" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H88" s="80" t="n">
+      <c r="H88" s="87" t="n">
         <v>1455</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="79" t="inlineStr">
+      <c r="A89" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B89" s="79" t="inlineStr">
+      <c r="B89" s="86" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C89" s="79" t="inlineStr">
+      <c r="C89" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D89" s="79" t="inlineStr">
+      <c r="D89" s="86" t="inlineStr">
         <is>
           <t>SAL.SALARIO06VINI</t>
         </is>
       </c>
-      <c r="E89" s="79" t="inlineStr">
+      <c r="E89" s="86" t="inlineStr">
         <is>
           <t>110700/1</t>
         </is>
       </c>
-      <c r="F89" s="79" t="inlineStr">
+      <c r="F89" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G89" s="79" t="inlineStr">
+      <c r="G89" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H89" s="80" t="n">
+      <c r="H89" s="87" t="n">
         <v>686</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="79" t="inlineStr">
+      <c r="A90" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B90" s="79" t="inlineStr">
+      <c r="B90" s="86" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="C90" s="79" t="inlineStr">
+      <c r="C90" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D90" s="79" t="inlineStr">
+      <c r="D90" s="86" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E90" s="79" t="inlineStr">
+      <c r="E90" s="86" t="inlineStr">
         <is>
           <t>113754/6</t>
         </is>
       </c>
-      <c r="F90" s="79" t="inlineStr">
+      <c r="F90" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G90" s="79" t="inlineStr">
+      <c r="G90" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H90" s="80" t="n">
+      <c r="H90" s="87" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="79" t="inlineStr">
+      <c r="A91" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B91" s="79" t="inlineStr">
+      <c r="B91" s="86" t="inlineStr">
         <is>
           <t>2026-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="C91" s="79" t="inlineStr">
+      <c r="C91" s="86" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D91" s="79" t="inlineStr"/>
-      <c r="E91" s="79" t="inlineStr"/>
-      <c r="F91" s="79" t="inlineStr">
+      <c r="D91" s="86" t="inlineStr"/>
+      <c r="E91" s="86" t="inlineStr"/>
+      <c r="F91" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G91" s="79" t="inlineStr">
+      <c r="G91" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H91" s="80" t="n">
+      <c r="H91" s="87" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="79" t="inlineStr">
+      <c r="A92" s="86" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B92" s="79" t="inlineStr">
+      <c r="B92" s="86" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C92" s="79" t="inlineStr">
+      <c r="C92" s="86" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D92" s="79" t="inlineStr">
+      <c r="D92" s="86" t="inlineStr">
         <is>
           <t>NFS.33</t>
         </is>
       </c>
-      <c r="E92" s="79" t="inlineStr">
+      <c r="E92" s="86" t="inlineStr">
         <is>
           <t>110902/1</t>
         </is>
       </c>
-      <c r="F92" s="79" t="inlineStr">
+      <c r="F92" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G92" s="79" t="inlineStr">
+      <c r="G92" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H92" s="80" t="n">
+      <c r="H92" s="87" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="79" t="inlineStr">
+      <c r="A93" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B93" s="79" t="inlineStr">
+      <c r="B93" s="86" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C93" s="79" t="inlineStr">
+      <c r="C93" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D93" s="79" t="inlineStr">
+      <c r="D93" s="86" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E93" s="79" t="inlineStr">
+      <c r="E93" s="86" t="inlineStr">
         <is>
           <t>113575/1</t>
         </is>
       </c>
-      <c r="F93" s="79" t="inlineStr">
+      <c r="F93" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G93" s="79" t="inlineStr">
+      <c r="G93" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H93" s="80" t="n">
+      <c r="H93" s="87" t="n">
         <v>20.39</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="79" t="inlineStr">
+      <c r="A94" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B94" s="79" t="inlineStr">
+      <c r="B94" s="86" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C94" s="79" t="inlineStr">
+      <c r="C94" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D94" s="79" t="inlineStr">
+      <c r="D94" s="86" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E94" s="79" t="inlineStr">
+      <c r="E94" s="86" t="inlineStr">
         <is>
           <t>113575/2</t>
         </is>
       </c>
-      <c r="F94" s="79" t="inlineStr">
+      <c r="F94" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G94" s="79" t="inlineStr">
+      <c r="G94" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H94" s="80" t="n">
+      <c r="H94" s="87" t="n">
         <v>133.73</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="79" t="inlineStr">
+      <c r="A95" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B95" s="79" t="inlineStr">
+      <c r="B95" s="86" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C95" s="79" t="inlineStr">
+      <c r="C95" s="86" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D95" s="79" t="inlineStr">
+      <c r="D95" s="86" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E95" s="79" t="inlineStr">
+      <c r="E95" s="86" t="inlineStr">
         <is>
           <t>113575/3</t>
         </is>
       </c>
-      <c r="F95" s="79" t="inlineStr">
+      <c r="F95" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G95" s="79" t="inlineStr">
+      <c r="G95" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H95" s="80" t="n">
+      <c r="H95" s="87" t="n">
         <v>825.28</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="79" t="inlineStr">
+      <c r="A96" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B96" s="79" t="inlineStr">
+      <c r="B96" s="86" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C96" s="79" t="inlineStr">
+      <c r="C96" s="86" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D96" s="79" t="inlineStr">
+      <c r="D96" s="86" t="inlineStr">
         <is>
           <t>NFS.377682</t>
         </is>
       </c>
-      <c r="E96" s="79" t="inlineStr">
+      <c r="E96" s="86" t="inlineStr">
         <is>
           <t>114092/1</t>
         </is>
       </c>
-      <c r="F96" s="79" t="inlineStr">
+      <c r="F96" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G96" s="79" t="inlineStr">
+      <c r="G96" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H96" s="80" t="n">
+      <c r="H96" s="87" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="79" t="inlineStr">
+      <c r="A97" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B97" s="79" t="inlineStr">
+      <c r="B97" s="86" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="C97" s="79" t="inlineStr">
+      <c r="C97" s="86" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D97" s="79" t="inlineStr">
+      <c r="D97" s="86" t="inlineStr">
         <is>
           <t>NFS.3</t>
         </is>
       </c>
-      <c r="E97" s="79" t="inlineStr">
+      <c r="E97" s="86" t="inlineStr">
         <is>
           <t>111371/1</t>
         </is>
       </c>
-      <c r="F97" s="79" t="inlineStr">
+      <c r="F97" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G97" s="79" t="inlineStr">
+      <c r="G97" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H97" s="80" t="n">
+      <c r="H97" s="87" t="n">
         <v>6300</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="79" t="inlineStr">
+      <c r="A98" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B98" s="79" t="inlineStr">
+      <c r="B98" s="86" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C98" s="79" t="inlineStr">
+      <c r="C98" s="86" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D98" s="79" t="inlineStr">
+      <c r="D98" s="86" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 07.26</t>
         </is>
       </c>
-      <c r="E98" s="79" t="inlineStr">
+      <c r="E98" s="86" t="inlineStr">
         <is>
           <t>113049/1</t>
         </is>
       </c>
-      <c r="F98" s="79" t="inlineStr">
+      <c r="F98" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G98" s="79" t="inlineStr">
+      <c r="G98" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H98" s="80" t="n">
+      <c r="H98" s="87" t="n">
         <v>1151.26</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="79" t="inlineStr">
+      <c r="A99" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B99" s="79" t="inlineStr">
+      <c r="B99" s="86" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C99" s="79" t="inlineStr">
+      <c r="C99" s="86" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D99" s="79" t="inlineStr">
+      <c r="D99" s="86" t="inlineStr">
         <is>
           <t>NFS.66</t>
         </is>
       </c>
-      <c r="E99" s="79" t="inlineStr">
+      <c r="E99" s="86" t="inlineStr">
         <is>
           <t>112107/1</t>
         </is>
       </c>
-      <c r="F99" s="79" t="inlineStr">
+      <c r="F99" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G99" s="79" t="inlineStr">
+      <c r="G99" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H99" s="80" t="n">
+      <c r="H99" s="87" t="n">
         <v>1037.38</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="79" t="inlineStr">
+      <c r="A100" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B100" s="79" t="inlineStr">
+      <c r="B100" s="86" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="C100" s="79" t="inlineStr">
+      <c r="C100" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D100" s="79" t="inlineStr">
+      <c r="D100" s="86" t="inlineStr">
         <is>
           <t>SAL.sal 0626</t>
         </is>
       </c>
-      <c r="E100" s="79" t="inlineStr">
+      <c r="E100" s="86" t="inlineStr">
         <is>
           <t>112402/1</t>
         </is>
       </c>
-      <c r="F100" s="79" t="inlineStr">
+      <c r="F100" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G100" s="79" t="inlineStr">
+      <c r="G100" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H100" s="80" t="n">
+      <c r="H100" s="87" t="n">
         <v>1225</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="79" t="inlineStr">
+      <c r="A101" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B101" s="79" t="inlineStr">
+      <c r="B101" s="86" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C101" s="79" t="inlineStr">
+      <c r="C101" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D101" s="79" t="inlineStr">
+      <c r="D101" s="86" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E101" s="79" t="inlineStr">
+      <c r="E101" s="86" t="inlineStr">
         <is>
           <t>113754/1</t>
         </is>
       </c>
-      <c r="F101" s="79" t="inlineStr">
+      <c r="F101" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G101" s="79" t="inlineStr">
+      <c r="G101" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H101" s="80" t="n">
+      <c r="H101" s="87" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="79" t="inlineStr">
+      <c r="A102" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B102" s="79" t="inlineStr">
+      <c r="B102" s="86" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C102" s="79" t="inlineStr">
+      <c r="C102" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D102" s="79" t="inlineStr">
+      <c r="D102" s="86" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E102" s="79" t="inlineStr">
+      <c r="E102" s="86" t="inlineStr">
         <is>
           <t>113754/7</t>
         </is>
       </c>
-      <c r="F102" s="79" t="inlineStr">
+      <c r="F102" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G102" s="79" t="inlineStr">
+      <c r="G102" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H102" s="80" t="n">
+      <c r="H102" s="87" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="79" t="inlineStr">
+      <c r="A103" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B103" s="79" t="inlineStr">
+      <c r="B103" s="86" t="inlineStr">
         <is>
           <t>2026-07-01 00:00:00</t>
         </is>
       </c>
-      <c r="C103" s="79" t="inlineStr">
+      <c r="C103" s="86" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D103" s="79" t="inlineStr"/>
-      <c r="E103" s="79" t="inlineStr"/>
-      <c r="F103" s="79" t="inlineStr">
+      <c r="D103" s="86" t="inlineStr"/>
+      <c r="E103" s="86" t="inlineStr"/>
+      <c r="F103" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G103" s="79" t="inlineStr">
+      <c r="G103" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H103" s="80" t="n">
+      <c r="H103" s="87" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="79" t="inlineStr">
+      <c r="A104" s="86" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B104" s="79" t="inlineStr">
+      <c r="B104" s="86" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C104" s="79" t="inlineStr">
+      <c r="C104" s="86" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D104" s="79" t="inlineStr">
+      <c r="D104" s="86" t="inlineStr">
         <is>
           <t>NFS.84</t>
         </is>
       </c>
-      <c r="E104" s="79" t="inlineStr">
+      <c r="E104" s="86" t="inlineStr">
         <is>
           <t>113583/1</t>
         </is>
       </c>
-      <c r="F104" s="79" t="inlineStr">
+      <c r="F104" s="86" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G104" s="79" t="inlineStr">
+      <c r="G104" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H104" s="80" t="n">
+      <c r="H104" s="87" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="105">
-      <c r="G105" s="81" t="inlineStr">
+      <c r="G105" s="88" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H105" s="82">
+      <c r="H105" s="89">
         <f>SUM(H5:H104)</f>
         <v/>
       </c>
@@ -10749,7 +11387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11289,22 +11927,22 @@
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B20" s="65" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Política de troca 1x1 e empréstimo — IMPLANTAR</t>
         </is>
       </c>
       <c r="C20" s="65" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Hoje não existe regra: o pedido chega e a compra é feita. A proposta é que para receber um item novo a pessoa entregue o que quebrou (troca 1x1), e que exista um equipamento reserva para empréstimo imediato, para ninguém ficar parado esperando. O reserva é COM FIO de propósito: mais barato e menos confortável que o definitivo, o que cria o incentivo natural para devolver e fechar a troca. A aba 'Controle de Equipamentos' já está pronta para o registro.</t>
         </is>
       </c>
       <c r="D20" s="65" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso — se uma área quebra três vezes mais que as outras, isso aparece. Encaminhar: (1) comunicar a regra às áreas; (2) montar o pequeno estoque de reserva; (3) definir quantos dias o empréstimo pode durar antes de virar 'Atrasado'; (4) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
         </is>
       </c>
       <c r="E20" s="65" t="inlineStr">
@@ -11314,37 +11952,69 @@
       </c>
       <c r="F20" s="67" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>IMPLANTAR</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="61" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="62" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C21" s="62" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D21" s="62" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E21" s="62" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F21" s="67" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="64" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="B22" s="65" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="C22" s="65" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D21" s="62" t="inlineStr">
+      <c r="D22" s="65" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E21" s="62" t="inlineStr">
+      <c r="E22" s="65" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F21" s="69" t="inlineStr">
+      <c r="F22" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>
@@ -11619,617 +12289,1119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CONTAS PAGAS — RESUMO POR CREDOR  (TI)</t>
+          <t>CONTROLE DE EQUIPAMENTOS — solicitações, troca 1x1 e empréstimos</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Extrato do financeiro, centro de custo "T.I". ABA DE APOIO: o centro de custo destes itens ainda não foi decidido, então nada aqui entra no Planejado, no Realizado nem no Painel. A coluna final aponta o que provavelmente já está no orçamento — confira e remova as duplicidades à mão.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="46" t="inlineStr">
-        <is>
-          <t>Credor</t>
-        </is>
-      </c>
-      <c r="B4" s="46" t="inlineStr">
-        <is>
-          <t>Centro de Custo</t>
-        </is>
-      </c>
-      <c r="C4" s="46" t="inlineStr">
-        <is>
-          <t>Nº lanç.</t>
-        </is>
-      </c>
-      <c r="D4" s="46" t="inlineStr">
-        <is>
-          <t>Jan/26</t>
-        </is>
-      </c>
-      <c r="E4" s="46" t="inlineStr">
-        <is>
-          <t>Fev/26</t>
-        </is>
-      </c>
-      <c r="F4" s="46" t="inlineStr">
-        <is>
-          <t>Mar/26</t>
-        </is>
-      </c>
-      <c r="G4" s="46" t="inlineStr">
-        <is>
-          <t>Abr/26</t>
-        </is>
-      </c>
-      <c r="H4" s="46" t="inlineStr">
-        <is>
-          <t>Mai/26</t>
-        </is>
-      </c>
-      <c r="I4" s="46" t="inlineStr">
-        <is>
-          <t>Jun/26</t>
-        </is>
-      </c>
-      <c r="J4" s="46" t="inlineStr">
-        <is>
-          <t>Jul/26</t>
-        </is>
-      </c>
-      <c r="K4" s="46" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L4" s="46" t="inlineStr">
-        <is>
-          <t>Já está no orçamento?</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="56" t="inlineStr">
-        <is>
-          <t>J H ALVES - MONITOR REMOTO</t>
-        </is>
-      </c>
-      <c r="B5" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C5" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="54" t="n">
-        <v>4311.56</v>
-      </c>
-      <c r="E5" s="54" t="n"/>
-      <c r="F5" s="54" t="n"/>
-      <c r="G5" s="54" t="n"/>
-      <c r="H5" s="54" t="n">
-        <v>3723.62</v>
-      </c>
-      <c r="I5" s="54" t="n">
-        <v>6173.37</v>
-      </c>
-      <c r="J5" s="54" t="n">
-        <v>6300</v>
-      </c>
-      <c r="K5" s="72" t="n">
-        <v>20508.55</v>
-      </c>
-      <c r="L5" s="73" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="74" t="inlineStr">
-        <is>
-          <t>VINICIUS DI FRANCO HEITOR</t>
-        </is>
-      </c>
-      <c r="B6" s="74" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C6" s="75" t="n">
-        <v>23</v>
-      </c>
-      <c r="D6" s="76" t="n">
-        <v>2670.84</v>
-      </c>
-      <c r="E6" s="76" t="n">
-        <v>2986.04</v>
-      </c>
-      <c r="F6" s="76" t="n">
-        <v>2778.04</v>
-      </c>
-      <c r="G6" s="76" t="n">
-        <v>2751.04</v>
-      </c>
-      <c r="H6" s="76" t="n">
-        <v>2719.04</v>
-      </c>
-      <c r="I6" s="76" t="n">
-        <v>3633.16</v>
-      </c>
-      <c r="J6" s="76" t="n">
-        <v>2461.04</v>
-      </c>
-      <c r="K6" s="77" t="n">
-        <v>19999.2</v>
-      </c>
-      <c r="L6" s="78" t="inlineStr">
-        <is>
-          <t>TI-E01 Vinicius Di Franco</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="74" t="inlineStr">
-        <is>
-          <t>OPENAI BRAZIL LIMITADA</t>
-        </is>
-      </c>
-      <c r="B7" s="74" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C7" s="75" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="76" t="n"/>
-      <c r="E7" s="76" t="n">
-        <v>234.46</v>
-      </c>
-      <c r="F7" s="76" t="n">
-        <v>321.76</v>
-      </c>
-      <c r="G7" s="76" t="n">
-        <v>5393.88</v>
-      </c>
-      <c r="H7" s="76" t="n"/>
-      <c r="I7" s="76" t="n"/>
-      <c r="J7" s="76" t="n"/>
-      <c r="K7" s="77" t="n">
-        <v>5950.1</v>
-      </c>
-      <c r="L7" s="78" t="inlineStr">
-        <is>
-          <t>TI-D11 GPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="56" t="inlineStr">
-        <is>
-          <t>CLARO S.A.</t>
-        </is>
-      </c>
-      <c r="B8" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="n">
-        <v>19</v>
-      </c>
-      <c r="D8" s="54" t="n">
-        <v>922.1099999999999</v>
-      </c>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="54" t="n">
-        <v>899.5799999999999</v>
-      </c>
-      <c r="G8" s="54" t="n">
-        <v>721.9400000000001</v>
-      </c>
-      <c r="H8" s="54" t="n">
-        <v>965.1099999999999</v>
-      </c>
-      <c r="I8" s="54" t="n">
-        <v>740</v>
-      </c>
-      <c r="J8" s="54" t="n">
-        <v>979.4</v>
-      </c>
-      <c r="K8" s="72" t="n">
-        <v>5228.139999999999</v>
-      </c>
-      <c r="L8" s="73" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="56" t="inlineStr">
-        <is>
-          <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
-        </is>
-      </c>
-      <c r="B9" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C9" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" s="54" t="n">
-        <v>924.2800000000001</v>
-      </c>
-      <c r="E9" s="54" t="n">
-        <v>99.25</v>
-      </c>
-      <c r="F9" s="54" t="n"/>
-      <c r="G9" s="54" t="n">
-        <v>1046.52</v>
-      </c>
-      <c r="H9" s="54" t="n">
-        <v>74.81</v>
-      </c>
-      <c r="I9" s="54" t="n"/>
-      <c r="J9" s="54" t="n">
-        <v>1151.26</v>
-      </c>
-      <c r="K9" s="72" t="n">
-        <v>3296.12</v>
-      </c>
-      <c r="L9" s="73" t="n"/>
+          <t>Registro operacional do TI. O SIENGE mostra o que foi PAGO; esta aba mostra o que foi PEDIDO — é no intervalo entre os dois que dá para avisar a área antes de estourar o saldo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>REGRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="72" t="inlineStr">
+        <is>
+          <t>Troca 1x1</t>
+        </is>
+      </c>
+      <c r="B5" s="73" t="inlineStr">
+        <is>
+          <t>Para receber um item novo, a pessoa entrega o que quebrou. O patrimônio devolvido é registrado na coluna própria.</t>
+        </is>
+      </c>
+      <c r="C5" s="74" t="n"/>
+      <c r="D5" s="74" t="n"/>
+      <c r="E5" s="74" t="n"/>
+      <c r="F5" s="74" t="n"/>
+      <c r="G5" s="74" t="n"/>
+      <c r="H5" s="74" t="n"/>
+      <c r="I5" s="74" t="n"/>
+      <c r="J5" s="74" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="72" t="inlineStr">
+        <is>
+          <t>Empréstimo</t>
+        </is>
+      </c>
+      <c r="B6" s="73" t="inlineStr">
+        <is>
+          <t>Quem está sem o equipamento sai com um reserva na hora, para não ficar parado. O reserva é COM FIO de propósito: mais barato e menos confortável que o definitivo, o que cria o incentivo para devolver e fechar a troca.</t>
+        </is>
+      </c>
+      <c r="C6" s="74" t="n"/>
+      <c r="D6" s="74" t="n"/>
+      <c r="E6" s="74" t="n"/>
+      <c r="F6" s="74" t="n"/>
+      <c r="G6" s="74" t="n"/>
+      <c r="H6" s="74" t="n"/>
+      <c r="I6" s="74" t="n"/>
+      <c r="J6" s="74" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="72" t="inlineStr">
+        <is>
+          <t>Sem devolução</t>
+        </is>
+      </c>
+      <c r="B7" s="73" t="inlineStr">
+        <is>
+          <t>Se a pessoa não entrega o item antigo, a solicitação fica 'Pendente devolução' e não vira compra até ser resolvida.</t>
+        </is>
+      </c>
+      <c r="C7" s="74" t="n"/>
+      <c r="D7" s="74" t="n"/>
+      <c r="E7" s="74" t="n"/>
+      <c r="F7" s="74" t="n"/>
+      <c r="G7" s="74" t="n"/>
+      <c r="H7" s="74" t="n"/>
+      <c r="I7" s="74" t="n"/>
+      <c r="J7" s="74" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="72" t="inlineStr">
+        <is>
+          <t>Aviso de saldo</t>
+        </is>
+      </c>
+      <c r="B8" s="73" t="inlineStr">
+        <is>
+          <t>Antes de aprovar, conferir o saldo da rubrica da área solicitante. Se a compra for levar ao estouro, avisar a área ANTES de comprar (pendência R).</t>
+        </is>
+      </c>
+      <c r="C8" s="74" t="n"/>
+      <c r="D8" s="74" t="n"/>
+      <c r="E8" s="74" t="n"/>
+      <c r="F8" s="74" t="n"/>
+      <c r="G8" s="74" t="n"/>
+      <c r="H8" s="74" t="n"/>
+      <c r="I8" s="74" t="n"/>
+      <c r="J8" s="74" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="56" t="inlineStr">
-        <is>
-          <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
-        </is>
-      </c>
-      <c r="B10" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C10" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="54" t="n">
-        <v>723.75</v>
-      </c>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="54" t="n"/>
-      <c r="G10" s="54" t="n"/>
-      <c r="H10" s="54" t="n">
-        <v>741.1</v>
-      </c>
-      <c r="I10" s="54" t="n">
-        <v>740.38</v>
-      </c>
-      <c r="J10" s="54" t="n">
-        <v>1037.38</v>
-      </c>
-      <c r="K10" s="72" t="n">
-        <v>3242.61</v>
-      </c>
-      <c r="L10" s="73" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="74" t="inlineStr">
-        <is>
-          <t>Vale Alimentação Vinicius</t>
-        </is>
-      </c>
-      <c r="B11" s="74" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C11" s="75" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="76" t="n"/>
-      <c r="E11" s="76" t="n">
-        <v>485</v>
-      </c>
-      <c r="F11" s="76" t="n">
-        <v>485</v>
-      </c>
-      <c r="G11" s="76" t="n">
-        <v>485</v>
-      </c>
-      <c r="H11" s="76" t="n">
-        <v>485</v>
-      </c>
-      <c r="I11" s="76" t="n">
-        <v>485</v>
-      </c>
-      <c r="J11" s="76" t="n">
-        <v>485</v>
-      </c>
-      <c r="K11" s="77" t="n">
-        <v>2910</v>
-      </c>
-      <c r="L11" s="78" t="inlineStr">
-        <is>
-          <t>TI-E01 Vinicius (benefício)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="56" t="inlineStr">
-        <is>
-          <t>TIM S A</t>
-        </is>
-      </c>
-      <c r="B12" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C12" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="54" t="n">
-        <v>331.42</v>
-      </c>
-      <c r="E12" s="54" t="n">
-        <v>338.5</v>
-      </c>
-      <c r="F12" s="54" t="n">
-        <v>284.63</v>
-      </c>
-      <c r="G12" s="54" t="n"/>
-      <c r="H12" s="54" t="n"/>
-      <c r="I12" s="54" t="n"/>
-      <c r="J12" s="54" t="n"/>
-      <c r="K12" s="72" t="n">
-        <v>954.5500000000001</v>
-      </c>
-      <c r="L12" s="73" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="56" t="inlineStr">
-        <is>
-          <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
-        </is>
-      </c>
-      <c r="B13" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C13" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="54" t="n"/>
-      <c r="E13" s="54" t="n">
-        <v>275.84</v>
-      </c>
-      <c r="F13" s="54" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="G13" s="54" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="H13" s="54" t="n">
-        <v>137.92</v>
-      </c>
-      <c r="I13" s="54" t="n">
-        <v>137.93</v>
-      </c>
-      <c r="J13" s="54" t="n"/>
-      <c r="K13" s="72" t="n">
-        <v>827.49</v>
-      </c>
-      <c r="L13" s="73" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="56" t="inlineStr">
-        <is>
-          <t>TELEFONICA BRASIL S.A.</t>
-        </is>
-      </c>
-      <c r="B14" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C14" s="53" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" s="54" t="n">
-        <v>51.63</v>
-      </c>
-      <c r="E14" s="54" t="n">
-        <v>102.32</v>
-      </c>
-      <c r="F14" s="54" t="n">
-        <v>50</v>
-      </c>
-      <c r="G14" s="54" t="n"/>
-      <c r="H14" s="54" t="n"/>
-      <c r="I14" s="54" t="n">
-        <v>554.58</v>
-      </c>
-      <c r="J14" s="54" t="n"/>
-      <c r="K14" s="72" t="n">
-        <v>758.53</v>
-      </c>
-      <c r="L14" s="73" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="56" t="inlineStr">
-        <is>
-          <t>WEB MOBILE TELECOM LTDA</t>
-        </is>
-      </c>
-      <c r="B15" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C15" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="54" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="E15" s="54" t="n">
-        <v>75</v>
-      </c>
-      <c r="F15" s="54" t="n">
-        <v>225</v>
-      </c>
-      <c r="G15" s="54" t="n">
-        <v>75</v>
-      </c>
-      <c r="H15" s="54" t="n">
-        <v>75</v>
-      </c>
-      <c r="I15" s="54" t="n">
-        <v>75</v>
-      </c>
-      <c r="J15" s="54" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="K15" s="72" t="n">
-        <v>690</v>
-      </c>
-      <c r="L15" s="73" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="56" t="inlineStr">
-        <is>
-          <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
-        </is>
-      </c>
-      <c r="B16" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C16" s="53" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" s="54" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="E16" s="54" t="n"/>
-      <c r="F16" s="54" t="n">
-        <v>159.2</v>
-      </c>
-      <c r="G16" s="54" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="H16" s="54" t="n"/>
-      <c r="I16" s="54" t="n">
-        <v>164.42</v>
-      </c>
-      <c r="J16" s="54" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="K16" s="72" t="n">
-        <v>562.42</v>
-      </c>
-      <c r="L16" s="73" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="56" t="inlineStr">
-        <is>
-          <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
-        </is>
-      </c>
-      <c r="B17" s="56" t="inlineStr">
-        <is>
-          <t>T.I</t>
-        </is>
-      </c>
-      <c r="C17" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="54" t="n"/>
-      <c r="E17" s="54" t="n"/>
-      <c r="F17" s="54" t="n"/>
-      <c r="G17" s="54" t="n"/>
-      <c r="H17" s="54" t="n"/>
-      <c r="I17" s="54" t="n">
-        <v>183.6</v>
-      </c>
-      <c r="J17" s="54" t="n"/>
-      <c r="K17" s="72" t="n">
-        <v>183.6</v>
-      </c>
-      <c r="L17" s="73" t="n"/>
+      <c r="A10" s="75" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÕES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Área solicitante</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Solicitante</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Devolveu o antigo?</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Patrimônio devolvido</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Valor estimado</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="76" t="n"/>
+      <c r="B12" s="76" t="n"/>
+      <c r="C12" s="76" t="n"/>
+      <c r="D12" s="76" t="n"/>
+      <c r="E12" s="76" t="n"/>
+      <c r="F12" s="76" t="n"/>
+      <c r="G12" s="76" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="76" t="n"/>
+      <c r="J12" s="76" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="76" t="n"/>
+      <c r="B13" s="76" t="n"/>
+      <c r="C13" s="76" t="n"/>
+      <c r="D13" s="76" t="n"/>
+      <c r="E13" s="76" t="n"/>
+      <c r="F13" s="76" t="n"/>
+      <c r="G13" s="76" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="76" t="n"/>
+      <c r="J13" s="76" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="76" t="n"/>
+      <c r="B14" s="76" t="n"/>
+      <c r="C14" s="76" t="n"/>
+      <c r="D14" s="76" t="n"/>
+      <c r="E14" s="76" t="n"/>
+      <c r="F14" s="76" t="n"/>
+      <c r="G14" s="76" t="n"/>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="76" t="n"/>
+      <c r="J14" s="76" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="76" t="n"/>
+      <c r="B15" s="76" t="n"/>
+      <c r="C15" s="76" t="n"/>
+      <c r="D15" s="76" t="n"/>
+      <c r="E15" s="76" t="n"/>
+      <c r="F15" s="76" t="n"/>
+      <c r="G15" s="76" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="76" t="n"/>
+      <c r="J15" s="76" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="76" t="n"/>
+      <c r="B16" s="76" t="n"/>
+      <c r="C16" s="76" t="n"/>
+      <c r="D16" s="76" t="n"/>
+      <c r="E16" s="76" t="n"/>
+      <c r="F16" s="76" t="n"/>
+      <c r="G16" s="76" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="76" t="n"/>
+      <c r="J16" s="76" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="76" t="n"/>
+      <c r="B17" s="76" t="n"/>
+      <c r="C17" s="76" t="n"/>
+      <c r="D17" s="76" t="n"/>
+      <c r="E17" s="76" t="n"/>
+      <c r="F17" s="76" t="n"/>
+      <c r="G17" s="76" t="n"/>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="76" t="n"/>
+      <c r="J17" s="76" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B18" s="51" t="n"/>
-      <c r="C18" s="51" t="n"/>
-      <c r="D18" s="52">
-        <f>SUM(D5:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="52">
-        <f>SUM(E5:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="52">
-        <f>SUM(F5:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="52">
-        <f>SUM(G5:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="52">
-        <f>SUM(H5:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="52">
-        <f>SUM(I5:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="52">
-        <f>SUM(J5:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="52">
-        <f>SUM(K5:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="51" t="n"/>
+      <c r="A18" s="76" t="n"/>
+      <c r="B18" s="76" t="n"/>
+      <c r="C18" s="76" t="n"/>
+      <c r="D18" s="76" t="n"/>
+      <c r="E18" s="76" t="n"/>
+      <c r="F18" s="76" t="n"/>
+      <c r="G18" s="76" t="n"/>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="76" t="n"/>
+      <c r="J18" s="76" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="76" t="n"/>
+      <c r="B19" s="76" t="n"/>
+      <c r="C19" s="76" t="n"/>
+      <c r="D19" s="76" t="n"/>
+      <c r="E19" s="76" t="n"/>
+      <c r="F19" s="76" t="n"/>
+      <c r="G19" s="76" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="76" t="n"/>
+      <c r="J19" s="76" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="76" t="n"/>
+      <c r="B20" s="76" t="n"/>
+      <c r="C20" s="76" t="n"/>
+      <c r="D20" s="76" t="n"/>
+      <c r="E20" s="76" t="n"/>
+      <c r="F20" s="76" t="n"/>
+      <c r="G20" s="76" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="76" t="n"/>
+      <c r="J20" s="76" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="76" t="n"/>
+      <c r="B21" s="76" t="n"/>
+      <c r="C21" s="76" t="n"/>
+      <c r="D21" s="76" t="n"/>
+      <c r="E21" s="76" t="n"/>
+      <c r="F21" s="76" t="n"/>
+      <c r="G21" s="76" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="76" t="n"/>
+      <c r="J21" s="76" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="76" t="n"/>
+      <c r="B22" s="76" t="n"/>
+      <c r="C22" s="76" t="n"/>
+      <c r="D22" s="76" t="n"/>
+      <c r="E22" s="76" t="n"/>
+      <c r="F22" s="76" t="n"/>
+      <c r="G22" s="76" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="76" t="n"/>
+      <c r="J22" s="76" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="76" t="n"/>
+      <c r="B23" s="76" t="n"/>
+      <c r="C23" s="76" t="n"/>
+      <c r="D23" s="76" t="n"/>
+      <c r="E23" s="76" t="n"/>
+      <c r="F23" s="76" t="n"/>
+      <c r="G23" s="76" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="76" t="n"/>
+      <c r="J23" s="76" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="76" t="n"/>
+      <c r="B24" s="76" t="n"/>
+      <c r="C24" s="76" t="n"/>
+      <c r="D24" s="76" t="n"/>
+      <c r="E24" s="76" t="n"/>
+      <c r="F24" s="76" t="n"/>
+      <c r="G24" s="76" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="76" t="n"/>
+      <c r="J24" s="76" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="76" t="n"/>
+      <c r="B25" s="76" t="n"/>
+      <c r="C25" s="76" t="n"/>
+      <c r="D25" s="76" t="n"/>
+      <c r="E25" s="76" t="n"/>
+      <c r="F25" s="76" t="n"/>
+      <c r="G25" s="76" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="76" t="n"/>
+      <c r="J25" s="76" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="76" t="n"/>
+      <c r="B26" s="76" t="n"/>
+      <c r="C26" s="76" t="n"/>
+      <c r="D26" s="76" t="n"/>
+      <c r="E26" s="76" t="n"/>
+      <c r="F26" s="76" t="n"/>
+      <c r="G26" s="76" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="76" t="n"/>
+      <c r="J26" s="76" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="76" t="n"/>
+      <c r="B27" s="76" t="n"/>
+      <c r="C27" s="76" t="n"/>
+      <c r="D27" s="76" t="n"/>
+      <c r="E27" s="76" t="n"/>
+      <c r="F27" s="76" t="n"/>
+      <c r="G27" s="76" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="76" t="n"/>
+      <c r="J27" s="76" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="76" t="n"/>
+      <c r="B28" s="76" t="n"/>
+      <c r="C28" s="76" t="n"/>
+      <c r="D28" s="76" t="n"/>
+      <c r="E28" s="76" t="n"/>
+      <c r="F28" s="76" t="n"/>
+      <c r="G28" s="76" t="n"/>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="76" t="n"/>
+      <c r="J28" s="76" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="76" t="n"/>
+      <c r="B29" s="76" t="n"/>
+      <c r="C29" s="76" t="n"/>
+      <c r="D29" s="76" t="n"/>
+      <c r="E29" s="76" t="n"/>
+      <c r="F29" s="76" t="n"/>
+      <c r="G29" s="76" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="76" t="n"/>
+      <c r="J29" s="76" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="76" t="n"/>
+      <c r="B30" s="76" t="n"/>
+      <c r="C30" s="76" t="n"/>
+      <c r="D30" s="76" t="n"/>
+      <c r="E30" s="76" t="n"/>
+      <c r="F30" s="76" t="n"/>
+      <c r="G30" s="76" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="76" t="n"/>
+      <c r="J30" s="76" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="76" t="n"/>
+      <c r="B31" s="76" t="n"/>
+      <c r="C31" s="76" t="n"/>
+      <c r="D31" s="76" t="n"/>
+      <c r="E31" s="76" t="n"/>
+      <c r="F31" s="76" t="n"/>
+      <c r="G31" s="76" t="n"/>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="76" t="n"/>
+      <c r="J31" s="76" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="76" t="n"/>
+      <c r="B32" s="76" t="n"/>
+      <c r="C32" s="76" t="n"/>
+      <c r="D32" s="76" t="n"/>
+      <c r="E32" s="76" t="n"/>
+      <c r="F32" s="76" t="n"/>
+      <c r="G32" s="76" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="76" t="n"/>
+      <c r="J32" s="76" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="76" t="n"/>
+      <c r="B33" s="76" t="n"/>
+      <c r="C33" s="76" t="n"/>
+      <c r="D33" s="76" t="n"/>
+      <c r="E33" s="76" t="n"/>
+      <c r="F33" s="76" t="n"/>
+      <c r="G33" s="76" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="76" t="n"/>
+      <c r="J33" s="76" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="76" t="n"/>
+      <c r="B34" s="76" t="n"/>
+      <c r="C34" s="76" t="n"/>
+      <c r="D34" s="76" t="n"/>
+      <c r="E34" s="76" t="n"/>
+      <c r="F34" s="76" t="n"/>
+      <c r="G34" s="76" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="76" t="n"/>
+      <c r="J34" s="76" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="76" t="n"/>
+      <c r="B35" s="76" t="n"/>
+      <c r="C35" s="76" t="n"/>
+      <c r="D35" s="76" t="n"/>
+      <c r="E35" s="76" t="n"/>
+      <c r="F35" s="76" t="n"/>
+      <c r="G35" s="76" t="n"/>
+      <c r="H35" s="49" t="n"/>
+      <c r="I35" s="76" t="n"/>
+      <c r="J35" s="76" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="76" t="n"/>
+      <c r="B36" s="76" t="n"/>
+      <c r="C36" s="76" t="n"/>
+      <c r="D36" s="76" t="n"/>
+      <c r="E36" s="76" t="n"/>
+      <c r="F36" s="76" t="n"/>
+      <c r="G36" s="76" t="n"/>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="76" t="n"/>
+      <c r="J36" s="76" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="76" t="n"/>
+      <c r="B37" s="76" t="n"/>
+      <c r="C37" s="76" t="n"/>
+      <c r="D37" s="76" t="n"/>
+      <c r="E37" s="76" t="n"/>
+      <c r="F37" s="76" t="n"/>
+      <c r="G37" s="76" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="76" t="n"/>
+      <c r="J37" s="76" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="76" t="n"/>
+      <c r="B38" s="76" t="n"/>
+      <c r="C38" s="76" t="n"/>
+      <c r="D38" s="76" t="n"/>
+      <c r="E38" s="76" t="n"/>
+      <c r="F38" s="76" t="n"/>
+      <c r="G38" s="76" t="n"/>
+      <c r="H38" s="49" t="n"/>
+      <c r="I38" s="76" t="n"/>
+      <c r="J38" s="76" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="76" t="n"/>
+      <c r="B39" s="76" t="n"/>
+      <c r="C39" s="76" t="n"/>
+      <c r="D39" s="76" t="n"/>
+      <c r="E39" s="76" t="n"/>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="49" t="n"/>
+      <c r="I39" s="76" t="n"/>
+      <c r="J39" s="76" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="76" t="n"/>
+      <c r="B40" s="76" t="n"/>
+      <c r="C40" s="76" t="n"/>
+      <c r="D40" s="76" t="n"/>
+      <c r="E40" s="76" t="n"/>
+      <c r="F40" s="76" t="n"/>
+      <c r="G40" s="76" t="n"/>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="76" t="n"/>
+      <c r="J40" s="76" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="76" t="n"/>
+      <c r="B41" s="76" t="n"/>
+      <c r="C41" s="76" t="n"/>
+      <c r="D41" s="76" t="n"/>
+      <c r="E41" s="76" t="n"/>
+      <c r="F41" s="76" t="n"/>
+      <c r="G41" s="76" t="n"/>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="76" t="n"/>
+      <c r="J41" s="76" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="76" t="n"/>
+      <c r="B42" s="76" t="n"/>
+      <c r="C42" s="76" t="n"/>
+      <c r="D42" s="76" t="n"/>
+      <c r="E42" s="76" t="n"/>
+      <c r="F42" s="76" t="n"/>
+      <c r="G42" s="76" t="n"/>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="76" t="n"/>
+      <c r="J42" s="76" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="76" t="n"/>
+      <c r="B43" s="76" t="n"/>
+      <c r="C43" s="76" t="n"/>
+      <c r="D43" s="76" t="n"/>
+      <c r="E43" s="76" t="n"/>
+      <c r="F43" s="76" t="n"/>
+      <c r="G43" s="76" t="n"/>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="76" t="n"/>
+      <c r="J43" s="76" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="76" t="n"/>
+      <c r="B44" s="76" t="n"/>
+      <c r="C44" s="76" t="n"/>
+      <c r="D44" s="76" t="n"/>
+      <c r="E44" s="76" t="n"/>
+      <c r="F44" s="76" t="n"/>
+      <c r="G44" s="76" t="n"/>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="76" t="n"/>
+      <c r="J44" s="76" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="76" t="n"/>
+      <c r="B45" s="76" t="n"/>
+      <c r="C45" s="76" t="n"/>
+      <c r="D45" s="76" t="n"/>
+      <c r="E45" s="76" t="n"/>
+      <c r="F45" s="76" t="n"/>
+      <c r="G45" s="76" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="76" t="n"/>
+      <c r="J45" s="76" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="76" t="n"/>
+      <c r="B46" s="76" t="n"/>
+      <c r="C46" s="76" t="n"/>
+      <c r="D46" s="76" t="n"/>
+      <c r="E46" s="76" t="n"/>
+      <c r="F46" s="76" t="n"/>
+      <c r="G46" s="76" t="n"/>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="76" t="n"/>
+      <c r="J46" s="76" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="76" t="n"/>
+      <c r="B47" s="76" t="n"/>
+      <c r="C47" s="76" t="n"/>
+      <c r="D47" s="76" t="n"/>
+      <c r="E47" s="76" t="n"/>
+      <c r="F47" s="76" t="n"/>
+      <c r="G47" s="76" t="n"/>
+      <c r="H47" s="49" t="n"/>
+      <c r="I47" s="76" t="n"/>
+      <c r="J47" s="76" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="76" t="n"/>
+      <c r="B48" s="76" t="n"/>
+      <c r="C48" s="76" t="n"/>
+      <c r="D48" s="76" t="n"/>
+      <c r="E48" s="76" t="n"/>
+      <c r="F48" s="76" t="n"/>
+      <c r="G48" s="76" t="n"/>
+      <c r="H48" s="49" t="n"/>
+      <c r="I48" s="76" t="n"/>
+      <c r="J48" s="76" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="76" t="n"/>
+      <c r="B49" s="76" t="n"/>
+      <c r="C49" s="76" t="n"/>
+      <c r="D49" s="76" t="n"/>
+      <c r="E49" s="76" t="n"/>
+      <c r="F49" s="76" t="n"/>
+      <c r="G49" s="76" t="n"/>
+      <c r="H49" s="49" t="n"/>
+      <c r="I49" s="76" t="n"/>
+      <c r="J49" s="76" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="76" t="n"/>
+      <c r="B50" s="76" t="n"/>
+      <c r="C50" s="76" t="n"/>
+      <c r="D50" s="76" t="n"/>
+      <c r="E50" s="76" t="n"/>
+      <c r="F50" s="76" t="n"/>
+      <c r="G50" s="76" t="n"/>
+      <c r="H50" s="49" t="n"/>
+      <c r="I50" s="76" t="n"/>
+      <c r="J50" s="76" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="76" t="n"/>
+      <c r="B51" s="76" t="n"/>
+      <c r="C51" s="76" t="n"/>
+      <c r="D51" s="76" t="n"/>
+      <c r="E51" s="76" t="n"/>
+      <c r="F51" s="76" t="n"/>
+      <c r="G51" s="76" t="n"/>
+      <c r="H51" s="49" t="n"/>
+      <c r="I51" s="76" t="n"/>
+      <c r="J51" s="76" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>EMPRÉSTIMOS (equipamento reserva)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="77" t="inlineStr">
+        <is>
+          <t>Item emprestado</t>
+        </is>
+      </c>
+      <c r="B54" s="77" t="inlineStr">
+        <is>
+          <t>Patrimônio</t>
+        </is>
+      </c>
+      <c r="C54" s="77" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="D54" s="77" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="E54" s="77" t="inlineStr">
+        <is>
+          <t>Saída em</t>
+        </is>
+      </c>
+      <c r="F54" s="77" t="inlineStr">
+        <is>
+          <t>Previsão de devolução</t>
+        </is>
+      </c>
+      <c r="G54" s="77" t="inlineStr">
+        <is>
+          <t>Devolvido em</t>
+        </is>
+      </c>
+      <c r="H54" s="77" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I54" s="77" t="inlineStr">
+        <is>
+          <t>Dias em posse</t>
+        </is>
+      </c>
+      <c r="J54" s="77" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="76" t="n"/>
+      <c r="B55" s="76" t="n"/>
+      <c r="C55" s="76" t="n"/>
+      <c r="D55" s="76" t="n"/>
+      <c r="E55" s="76" t="n"/>
+      <c r="F55" s="76" t="n"/>
+      <c r="G55" s="76" t="n"/>
+      <c r="H55" s="76" t="n"/>
+      <c r="I55" s="78">
+        <f>IF(E55="","",IF(G55="",TODAY()-E55,G55-E55))</f>
+        <v/>
+      </c>
+      <c r="J55" s="76" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="76" t="n"/>
+      <c r="B56" s="76" t="n"/>
+      <c r="C56" s="76" t="n"/>
+      <c r="D56" s="76" t="n"/>
+      <c r="E56" s="76" t="n"/>
+      <c r="F56" s="76" t="n"/>
+      <c r="G56" s="76" t="n"/>
+      <c r="H56" s="76" t="n"/>
+      <c r="I56" s="78">
+        <f>IF(E56="","",IF(G56="",TODAY()-E56,G56-E56))</f>
+        <v/>
+      </c>
+      <c r="J56" s="76" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="76" t="n"/>
+      <c r="B57" s="76" t="n"/>
+      <c r="C57" s="76" t="n"/>
+      <c r="D57" s="76" t="n"/>
+      <c r="E57" s="76" t="n"/>
+      <c r="F57" s="76" t="n"/>
+      <c r="G57" s="76" t="n"/>
+      <c r="H57" s="76" t="n"/>
+      <c r="I57" s="78">
+        <f>IF(E57="","",IF(G57="",TODAY()-E57,G57-E57))</f>
+        <v/>
+      </c>
+      <c r="J57" s="76" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="76" t="n"/>
+      <c r="B58" s="76" t="n"/>
+      <c r="C58" s="76" t="n"/>
+      <c r="D58" s="76" t="n"/>
+      <c r="E58" s="76" t="n"/>
+      <c r="F58" s="76" t="n"/>
+      <c r="G58" s="76" t="n"/>
+      <c r="H58" s="76" t="n"/>
+      <c r="I58" s="78">
+        <f>IF(E58="","",IF(G58="",TODAY()-E58,G58-E58))</f>
+        <v/>
+      </c>
+      <c r="J58" s="76" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="76" t="n"/>
+      <c r="B59" s="76" t="n"/>
+      <c r="C59" s="76" t="n"/>
+      <c r="D59" s="76" t="n"/>
+      <c r="E59" s="76" t="n"/>
+      <c r="F59" s="76" t="n"/>
+      <c r="G59" s="76" t="n"/>
+      <c r="H59" s="76" t="n"/>
+      <c r="I59" s="78">
+        <f>IF(E59="","",IF(G59="",TODAY()-E59,G59-E59))</f>
+        <v/>
+      </c>
+      <c r="J59" s="76" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="76" t="n"/>
+      <c r="B60" s="76" t="n"/>
+      <c r="C60" s="76" t="n"/>
+      <c r="D60" s="76" t="n"/>
+      <c r="E60" s="76" t="n"/>
+      <c r="F60" s="76" t="n"/>
+      <c r="G60" s="76" t="n"/>
+      <c r="H60" s="76" t="n"/>
+      <c r="I60" s="78">
+        <f>IF(E60="","",IF(G60="",TODAY()-E60,G60-E60))</f>
+        <v/>
+      </c>
+      <c r="J60" s="76" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="76" t="n"/>
+      <c r="B61" s="76" t="n"/>
+      <c r="C61" s="76" t="n"/>
+      <c r="D61" s="76" t="n"/>
+      <c r="E61" s="76" t="n"/>
+      <c r="F61" s="76" t="n"/>
+      <c r="G61" s="76" t="n"/>
+      <c r="H61" s="76" t="n"/>
+      <c r="I61" s="78">
+        <f>IF(E61="","",IF(G61="",TODAY()-E61,G61-E61))</f>
+        <v/>
+      </c>
+      <c r="J61" s="76" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="76" t="n"/>
+      <c r="B62" s="76" t="n"/>
+      <c r="C62" s="76" t="n"/>
+      <c r="D62" s="76" t="n"/>
+      <c r="E62" s="76" t="n"/>
+      <c r="F62" s="76" t="n"/>
+      <c r="G62" s="76" t="n"/>
+      <c r="H62" s="76" t="n"/>
+      <c r="I62" s="78">
+        <f>IF(E62="","",IF(G62="",TODAY()-E62,G62-E62))</f>
+        <v/>
+      </c>
+      <c r="J62" s="76" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="76" t="n"/>
+      <c r="B63" s="76" t="n"/>
+      <c r="C63" s="76" t="n"/>
+      <c r="D63" s="76" t="n"/>
+      <c r="E63" s="76" t="n"/>
+      <c r="F63" s="76" t="n"/>
+      <c r="G63" s="76" t="n"/>
+      <c r="H63" s="76" t="n"/>
+      <c r="I63" s="78">
+        <f>IF(E63="","",IF(G63="",TODAY()-E63,G63-E63))</f>
+        <v/>
+      </c>
+      <c r="J63" s="76" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="76" t="n"/>
+      <c r="B64" s="76" t="n"/>
+      <c r="C64" s="76" t="n"/>
+      <c r="D64" s="76" t="n"/>
+      <c r="E64" s="76" t="n"/>
+      <c r="F64" s="76" t="n"/>
+      <c r="G64" s="76" t="n"/>
+      <c r="H64" s="76" t="n"/>
+      <c r="I64" s="78">
+        <f>IF(E64="","",IF(G64="",TODAY()-E64,G64-E64))</f>
+        <v/>
+      </c>
+      <c r="J64" s="76" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="76" t="n"/>
+      <c r="B65" s="76" t="n"/>
+      <c r="C65" s="76" t="n"/>
+      <c r="D65" s="76" t="n"/>
+      <c r="E65" s="76" t="n"/>
+      <c r="F65" s="76" t="n"/>
+      <c r="G65" s="76" t="n"/>
+      <c r="H65" s="76" t="n"/>
+      <c r="I65" s="78">
+        <f>IF(E65="","",IF(G65="",TODAY()-E65,G65-E65))</f>
+        <v/>
+      </c>
+      <c r="J65" s="76" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="76" t="n"/>
+      <c r="B66" s="76" t="n"/>
+      <c r="C66" s="76" t="n"/>
+      <c r="D66" s="76" t="n"/>
+      <c r="E66" s="76" t="n"/>
+      <c r="F66" s="76" t="n"/>
+      <c r="G66" s="76" t="n"/>
+      <c r="H66" s="76" t="n"/>
+      <c r="I66" s="78">
+        <f>IF(E66="","",IF(G66="",TODAY()-E66,G66-E66))</f>
+        <v/>
+      </c>
+      <c r="J66" s="76" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="76" t="n"/>
+      <c r="B67" s="76" t="n"/>
+      <c r="C67" s="76" t="n"/>
+      <c r="D67" s="76" t="n"/>
+      <c r="E67" s="76" t="n"/>
+      <c r="F67" s="76" t="n"/>
+      <c r="G67" s="76" t="n"/>
+      <c r="H67" s="76" t="n"/>
+      <c r="I67" s="78">
+        <f>IF(E67="","",IF(G67="",TODAY()-E67,G67-E67))</f>
+        <v/>
+      </c>
+      <c r="J67" s="76" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="76" t="n"/>
+      <c r="B68" s="76" t="n"/>
+      <c r="C68" s="76" t="n"/>
+      <c r="D68" s="76" t="n"/>
+      <c r="E68" s="76" t="n"/>
+      <c r="F68" s="76" t="n"/>
+      <c r="G68" s="76" t="n"/>
+      <c r="H68" s="76" t="n"/>
+      <c r="I68" s="78">
+        <f>IF(E68="","",IF(G68="",TODAY()-E68,G68-E68))</f>
+        <v/>
+      </c>
+      <c r="J68" s="76" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="76" t="n"/>
+      <c r="B69" s="76" t="n"/>
+      <c r="C69" s="76" t="n"/>
+      <c r="D69" s="76" t="n"/>
+      <c r="E69" s="76" t="n"/>
+      <c r="F69" s="76" t="n"/>
+      <c r="G69" s="76" t="n"/>
+      <c r="H69" s="76" t="n"/>
+      <c r="I69" s="78">
+        <f>IF(E69="","",IF(G69="",TODAY()-E69,G69-E69))</f>
+        <v/>
+      </c>
+      <c r="J69" s="76" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="76" t="n"/>
+      <c r="B70" s="76" t="n"/>
+      <c r="C70" s="76" t="n"/>
+      <c r="D70" s="76" t="n"/>
+      <c r="E70" s="76" t="n"/>
+      <c r="F70" s="76" t="n"/>
+      <c r="G70" s="76" t="n"/>
+      <c r="H70" s="76" t="n"/>
+      <c r="I70" s="78">
+        <f>IF(E70="","",IF(G70="",TODAY()-E70,G70-E70))</f>
+        <v/>
+      </c>
+      <c r="J70" s="76" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="76" t="n"/>
+      <c r="B71" s="76" t="n"/>
+      <c r="C71" s="76" t="n"/>
+      <c r="D71" s="76" t="n"/>
+      <c r="E71" s="76" t="n"/>
+      <c r="F71" s="76" t="n"/>
+      <c r="G71" s="76" t="n"/>
+      <c r="H71" s="76" t="n"/>
+      <c r="I71" s="78">
+        <f>IF(E71="","",IF(G71="",TODAY()-E71,G71-E71))</f>
+        <v/>
+      </c>
+      <c r="J71" s="76" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="76" t="n"/>
+      <c r="B72" s="76" t="n"/>
+      <c r="C72" s="76" t="n"/>
+      <c r="D72" s="76" t="n"/>
+      <c r="E72" s="76" t="n"/>
+      <c r="F72" s="76" t="n"/>
+      <c r="G72" s="76" t="n"/>
+      <c r="H72" s="76" t="n"/>
+      <c r="I72" s="78">
+        <f>IF(E72="","",IF(G72="",TODAY()-E72,G72-E72))</f>
+        <v/>
+      </c>
+      <c r="J72" s="76" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="76" t="n"/>
+      <c r="B73" s="76" t="n"/>
+      <c r="C73" s="76" t="n"/>
+      <c r="D73" s="76" t="n"/>
+      <c r="E73" s="76" t="n"/>
+      <c r="F73" s="76" t="n"/>
+      <c r="G73" s="76" t="n"/>
+      <c r="H73" s="76" t="n"/>
+      <c r="I73" s="78">
+        <f>IF(E73="","",IF(G73="",TODAY()-E73,G73-E73))</f>
+        <v/>
+      </c>
+      <c r="J73" s="76" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="76" t="n"/>
+      <c r="B74" s="76" t="n"/>
+      <c r="C74" s="76" t="n"/>
+      <c r="D74" s="76" t="n"/>
+      <c r="E74" s="76" t="n"/>
+      <c r="F74" s="76" t="n"/>
+      <c r="G74" s="76" t="n"/>
+      <c r="H74" s="76" t="n"/>
+      <c r="I74" s="78">
+        <f>IF(E74="","",IF(G74="",TODAY()-E74,G74-E74))</f>
+        <v/>
+      </c>
+      <c r="J74" s="76" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="76" t="n"/>
+      <c r="B75" s="76" t="n"/>
+      <c r="C75" s="76" t="n"/>
+      <c r="D75" s="76" t="n"/>
+      <c r="E75" s="76" t="n"/>
+      <c r="F75" s="76" t="n"/>
+      <c r="G75" s="76" t="n"/>
+      <c r="H75" s="76" t="n"/>
+      <c r="I75" s="78">
+        <f>IF(E75="","",IF(G75="",TODAY()-E75,G75-E75))</f>
+        <v/>
+      </c>
+      <c r="J75" s="76" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="76" t="n"/>
+      <c r="B76" s="76" t="n"/>
+      <c r="C76" s="76" t="n"/>
+      <c r="D76" s="76" t="n"/>
+      <c r="E76" s="76" t="n"/>
+      <c r="F76" s="76" t="n"/>
+      <c r="G76" s="76" t="n"/>
+      <c r="H76" s="76" t="n"/>
+      <c r="I76" s="78">
+        <f>IF(E76="","",IF(G76="",TODAY()-E76,G76-E76))</f>
+        <v/>
+      </c>
+      <c r="J76" s="76" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="76" t="n"/>
+      <c r="B77" s="76" t="n"/>
+      <c r="C77" s="76" t="n"/>
+      <c r="D77" s="76" t="n"/>
+      <c r="E77" s="76" t="n"/>
+      <c r="F77" s="76" t="n"/>
+      <c r="G77" s="76" t="n"/>
+      <c r="H77" s="76" t="n"/>
+      <c r="I77" s="78">
+        <f>IF(E77="","",IF(G77="",TODAY()-E77,G77-E77))</f>
+        <v/>
+      </c>
+      <c r="J77" s="76" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="76" t="n"/>
+      <c r="B78" s="76" t="n"/>
+      <c r="C78" s="76" t="n"/>
+      <c r="D78" s="76" t="n"/>
+      <c r="E78" s="76" t="n"/>
+      <c r="F78" s="76" t="n"/>
+      <c r="G78" s="76" t="n"/>
+      <c r="H78" s="76" t="n"/>
+      <c r="I78" s="78">
+        <f>IF(E78="","",IF(G78="",TODAY()-E78,G78-E78))</f>
+        <v/>
+      </c>
+      <c r="J78" s="76" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="76" t="n"/>
+      <c r="B79" s="76" t="n"/>
+      <c r="C79" s="76" t="n"/>
+      <c r="D79" s="76" t="n"/>
+      <c r="E79" s="76" t="n"/>
+      <c r="F79" s="76" t="n"/>
+      <c r="G79" s="76" t="n"/>
+      <c r="H79" s="76" t="n"/>
+      <c r="I79" s="78">
+        <f>IF(E79="","",IF(G79="",TODAY()-E79,G79-E79))</f>
+        <v/>
+      </c>
+      <c r="J79" s="76" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L17"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+  <autoFilter ref="A11:J51"/>
+  <mergeCells count="9">
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="B6:J6"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="I12:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Aberta,Aguardando devolução,Aprovada,Comprada,Entregue,Negada"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F12:F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sim,Não,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H55:H79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Emprestado,Devolvido,Atrasado,Baixado"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11387,7 +11387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="D17" s="62" t="inlineStr">
         <is>
-          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer.</t>
+          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. SEPARAR OS ITENS: a descrição na ficha mistura infraestrutura de reunião (câmeras, microfones, cadeiras) com material de consumo e brindes (canetas, blocos personalizados, copos, cafeteira). O segundo grupo é papelaria e deveria estar no Administrativo, não no TI (item U).</t>
         </is>
       </c>
       <c r="E17" s="62" t="inlineStr">
@@ -11959,62 +11959,94 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B21" s="62" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Papelaria não é TI — manter no Administrativo</t>
         </is>
       </c>
       <c r="C21" s="62" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Recomendação registrada: o controle de papelaria (canetas, blocos, papel, copos) deve ficar no Administrativo/Facilities, não no TI. O TI controla equipamento porque há decisão TÉCNICA envolvida — se o notebook precisa de troca ou só de formatação, se a tela quebrou por defeito ou por queda. Não existe decisão técnica em caneta e bloco.</t>
         </is>
       </c>
       <c r="D21" s="62" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Três diferenças separam as duas coisas: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. Se papelaria estiver caindo no orçamento do TI por motivo histórico, é o mesmo caso do Adapta (item Q): classificação errada, corrigir na origem quando o centro de custo novo for aberto.</t>
         </is>
       </c>
       <c r="E21" s="62" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Administrativo</t>
         </is>
       </c>
       <c r="F21" s="67" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>RECOMENDAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="64" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="65" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C22" s="65" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D22" s="65" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E22" s="65" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F22" s="67" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="61" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B22" s="65" t="inlineStr">
+      <c r="B23" s="62" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C22" s="65" t="inlineStr">
+      <c r="C23" s="62" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D22" s="65" t="inlineStr">
+      <c r="D23" s="62" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E22" s="65" t="inlineStr">
+      <c r="E23" s="62" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F22" s="69" t="inlineStr">
+      <c r="F23" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -20,8 +20,8 @@
     <sheet name="Contas Pagas (detalhe)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$104</definedName>
@@ -211,12 +211,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1233,15 +1233,15 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$B$5:$B$20,"TI",Planejado!$C$5:$C$20,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$B$5:$B$21,"TI",Planejado!$C$5:$C$21,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1257,7 +1257,7 @@
         <v/>
       </c>
       <c r="I6" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$21,"&gt;0",Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$21,"?*",Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$22,"&gt;0",Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$22,"?*",Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1273,15 +1273,15 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$B$5:$B$20,"TI",Planejado!$C$5:$C$20,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$B$5:$B$21,"TI",Planejado!$C$5:$C$21,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1297,7 +1297,7 @@
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$21,"&gt;0",Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$21,"?*",Comparativo!$B$6:$B$21,"TI",Comparativo!$C$6:$C$21,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$22,"&gt;0",Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$22,"?*",Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1313,15 +1313,15 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="12">
@@ -1337,7 +1337,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$21,"&gt;0",Comparativo!$B$6:$B$21,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$21,"?*",Comparativo!$B$6:$B$21,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$22,"&gt;0",Comparativo!$B$6:$B$22,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$22,"?*",Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="17">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$21,"&lt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$22,"&lt;0")</f>
         <v/>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="17">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$21,"&gt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$22,"&gt;0")</f>
         <v/>
       </c>
       <c r="D13" s="18" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B14" s="19" t="n"/>
       <c r="C14" s="20">
-        <f>-SUM(Comparativo!$Q$6:$Q$21)</f>
+        <f>-SUM(Comparativo!$Q$6:$Q$22)</f>
         <v/>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B15" s="16" t="n"/>
       <c r="C15" s="17">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$21)/Comparativo!$D$3*12,"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$22)/Comparativo!$D$3*12,"")</f>
         <v/>
       </c>
       <c r="D15" s="18" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="22">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$21)/SUM(Comparativo!$S$6:$S$21),"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$22)/SUM(Comparativo!$S$6:$S$22),"")</f>
         <v/>
       </c>
       <c r="D16" s="18" t="inlineStr">
@@ -1515,23 +1515,23 @@
         <v>1</v>
       </c>
       <c r="B21" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="C21" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A21),Comparativo!$R$6:$R$21,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),""),"")</f>
         <v/>
       </c>
       <c r="G21" s="29">
@@ -1544,23 +1544,23 @@
         <v>2</v>
       </c>
       <c r="B22" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="C22" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="F22" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A22),Comparativo!$R$6:$R$21,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),""),"")</f>
         <v/>
       </c>
       <c r="G22" s="29">
@@ -1573,23 +1573,23 @@
         <v>3</v>
       </c>
       <c r="B23" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="C23" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="F23" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A23),Comparativo!$R$6:$R$21,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),""),"")</f>
         <v/>
       </c>
       <c r="G23" s="29">
@@ -1602,23 +1602,23 @@
         <v>4</v>
       </c>
       <c r="B24" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="C24" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="F24" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A24),Comparativo!$R$6:$R$21,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),""),"")</f>
         <v/>
       </c>
       <c r="G24" s="29">
@@ -1631,23 +1631,23 @@
         <v>5</v>
       </c>
       <c r="B25" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$R$6:$R$21,A25),Comparativo!$R$6:$R$21,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),""),"")</f>
         <v/>
       </c>
       <c r="G25" s="29">
@@ -1705,23 +1705,23 @@
         <v>1</v>
       </c>
       <c r="B30" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="C30" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="F30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A30),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="G30" s="29">
@@ -1734,23 +1734,23 @@
         <v>2</v>
       </c>
       <c r="B31" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="C31" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="F31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A31),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="G31" s="29">
@@ -1763,23 +1763,23 @@
         <v>3</v>
       </c>
       <c r="B32" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="C32" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="F32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A32),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="G32" s="29">
@@ -1792,23 +1792,23 @@
         <v>4</v>
       </c>
       <c r="B33" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="C33" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="F33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A33),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="G33" s="29">
@@ -1821,23 +1821,23 @@
         <v>5</v>
       </c>
       <c r="B34" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$21,MATCH(LARGE(Comparativo!$O$6:$O$21,A34),Comparativo!$O$6:$O$21,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="29">
@@ -6543,7 +6543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7947,57 +7947,135 @@
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="42" t="inlineStr">
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="35">
+        <f>Planejado!A21</f>
+        <v/>
+      </c>
+      <c r="B22" s="35">
+        <f>Planejado!B21</f>
+        <v/>
+      </c>
+      <c r="C22" s="35">
+        <f>Planejado!C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="36">
+        <f>Planejado!D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="35">
+        <f>Planejado!G21</f>
+        <v/>
+      </c>
+      <c r="F22" s="37">
+        <f>INDEX(Planejado!$H21:$S21,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G22" s="37">
+        <f>INDEX(Realizado!$H21:$S21,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H22" s="37">
+        <f>G22-F22</f>
+        <v/>
+      </c>
+      <c r="I22" s="37">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H21:$S21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="37">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H21:$S21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="37">
+        <f>J22-I22</f>
+        <v/>
+      </c>
+      <c r="L22" s="38">
+        <f>IFERROR(K22/I22,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="38">
+        <f>IFERROR(J22/I22,"")</f>
+        <v/>
+      </c>
+      <c r="N22" s="39">
+        <f>IF(P22=0,"Sem lançamento",IF(AND(I22=0,J22=0),"—",IF(I22=0,"Não orçado",IF(K22&gt;0.05*I22,"Acima do orçado",IF(K22&lt;-0.05*I22,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O22" s="34">
+        <f>IF(K22&gt;1,K22+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P22" s="40">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H21:$S21&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="41">
+        <f>IF(P22=0,"",K22)</f>
+        <v/>
+      </c>
+      <c r="R22" s="41">
+        <f>IF(AND(Q22&lt;&gt;"",Q22&lt;-1),-Q22+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S22" s="41">
+        <f>IF(Q22="","",I22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B32" s="42" t="n"/>
-      <c r="C32" s="42" t="n"/>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="42" t="n"/>
-      <c r="F32" s="43">
-        <f>SUM(F6:F21)</f>
-        <v/>
-      </c>
-      <c r="G32" s="43">
-        <f>SUM(G6:G21)</f>
-        <v/>
-      </c>
-      <c r="H32" s="43">
-        <f>SUM(H6:H21)</f>
-        <v/>
-      </c>
-      <c r="I32" s="43">
-        <f>SUM(I6:I21)</f>
-        <v/>
-      </c>
-      <c r="J32" s="43">
-        <f>SUM(J6:J21)</f>
-        <v/>
-      </c>
-      <c r="K32" s="43">
-        <f>SUM(K6:K21)</f>
-        <v/>
-      </c>
-      <c r="L32" s="44">
-        <f>IFERROR(K32/I32,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="44">
-        <f>IFERROR(J32/I32,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="42" t="n"/>
+      <c r="B33" s="42" t="n"/>
+      <c r="C33" s="42" t="n"/>
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="43">
+        <f>SUM(F6:F22)</f>
+        <v/>
+      </c>
+      <c r="G33" s="43">
+        <f>SUM(G6:G22)</f>
+        <v/>
+      </c>
+      <c r="H33" s="43">
+        <f>SUM(H6:H22)</f>
+        <v/>
+      </c>
+      <c r="I33" s="43">
+        <f>SUM(I6:I22)</f>
+        <v/>
+      </c>
+      <c r="J33" s="43">
+        <f>SUM(J6:J22)</f>
+        <v/>
+      </c>
+      <c r="K33" s="43">
+        <f>SUM(K6:K22)</f>
+        <v/>
+      </c>
+      <c r="L33" s="44">
+        <f>IFERROR(K33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="44">
+        <f>IFERROR(J33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="42" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N21"/>
+  <autoFilter ref="A5:N22"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H21">
+  <conditionalFormatting sqref="H6:H22">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -8005,7 +8083,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K21">
+  <conditionalFormatting sqref="K6:K22">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -8028,7 +8106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8269,7 +8347,7 @@
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>Suporte Técnico Terceirizado</t>
+          <t>Suporte Técnico Terceirizado — R$ 1.065/mês até ago/26; R$ 603,30 a partir de set/26 (renegociação)</t>
         </is>
       </c>
       <c r="F6" s="35" t="inlineStr">
@@ -8307,16 +8385,16 @@
         <v>1065</v>
       </c>
       <c r="P6" s="37" t="n">
-        <v>1065</v>
+        <v>603.3</v>
       </c>
       <c r="Q6" s="37" t="n">
-        <v>1065</v>
+        <v>603.3</v>
       </c>
       <c r="R6" s="37" t="n">
-        <v>1065</v>
+        <v>603.3</v>
       </c>
       <c r="S6" s="37" t="n">
-        <v>1065</v>
+        <v>603.3</v>
       </c>
       <c r="T6" s="45">
         <f>SUM(H6:S6)</f>
@@ -9271,7 +9349,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>TI-D09</t>
+          <t>TI-D14</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
@@ -9286,18 +9364,18 @@
       </c>
       <c r="D20" s="36" t="inlineStr">
         <is>
-          <t>Bonificação do time</t>
+          <t>AnyDesk</t>
         </is>
       </c>
       <c r="E20" s="36" t="inlineStr">
         <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+          <t>Licença de acesso remoto — contratação prevista, não constava na ficha. Valor e mês de início a definir. CONFERIR sobreposição com o serviço de monitoramento remoto já contratado (J H Alves)</t>
         </is>
       </c>
       <c r="F20" s="35" t="inlineStr"/>
       <c r="G20" s="35" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H20" s="37" t="n">
@@ -9322,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="37" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P20" s="37" t="n">
         <v>0</v>
@@ -9334,80 +9412,153 @@
         <v>0</v>
       </c>
       <c r="S20" s="37" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="T20" s="45">
         <f>SUM(H20:S20)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="42" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>TI-D09</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D21" s="36" t="inlineStr">
+        <is>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E21" s="36" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr"/>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="37" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="37" t="n">
+        <v>3600</v>
+      </c>
+      <c r="T21" s="45">
+        <f>SUM(H21:S21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B21" s="42" t="n"/>
-      <c r="C21" s="42" t="n"/>
-      <c r="D21" s="42" t="n"/>
-      <c r="E21" s="42" t="n"/>
-      <c r="F21" s="42" t="n"/>
-      <c r="G21" s="42" t="n"/>
-      <c r="H21" s="43">
-        <f>SUM(H5:H20)</f>
-        <v/>
-      </c>
-      <c r="I21" s="43">
-        <f>SUM(I5:I20)</f>
-        <v/>
-      </c>
-      <c r="J21" s="43">
-        <f>SUM(J5:J20)</f>
-        <v/>
-      </c>
-      <c r="K21" s="43">
-        <f>SUM(K5:K20)</f>
-        <v/>
-      </c>
-      <c r="L21" s="43">
-        <f>SUM(L5:L20)</f>
-        <v/>
-      </c>
-      <c r="M21" s="43">
-        <f>SUM(M5:M20)</f>
-        <v/>
-      </c>
-      <c r="N21" s="43">
-        <f>SUM(N5:N20)</f>
-        <v/>
-      </c>
-      <c r="O21" s="43">
-        <f>SUM(O5:O20)</f>
-        <v/>
-      </c>
-      <c r="P21" s="43">
-        <f>SUM(P5:P20)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="43">
-        <f>SUM(Q5:Q20)</f>
-        <v/>
-      </c>
-      <c r="R21" s="43">
-        <f>SUM(R5:R20)</f>
-        <v/>
-      </c>
-      <c r="S21" s="43">
-        <f>SUM(S5:S20)</f>
-        <v/>
-      </c>
-      <c r="T21" s="43">
-        <f>SUM(T5:T20)</f>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="43">
+        <f>SUM(H5:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="43">
+        <f>SUM(I5:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="43">
+        <f>SUM(J5:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="43">
+        <f>SUM(K5:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="43">
+        <f>SUM(L5:L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="43">
+        <f>SUM(M5:M21)</f>
+        <v/>
+      </c>
+      <c r="N22" s="43">
+        <f>SUM(N5:N21)</f>
+        <v/>
+      </c>
+      <c r="O22" s="43">
+        <f>SUM(O5:O21)</f>
+        <v/>
+      </c>
+      <c r="P22" s="43">
+        <f>SUM(P5:P21)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="43">
+        <f>SUM(Q5:Q21)</f>
+        <v/>
+      </c>
+      <c r="R22" s="43">
+        <f>SUM(R5:R21)</f>
+        <v/>
+      </c>
+      <c r="S22" s="43">
+        <f>SUM(S5:S21)</f>
+        <v/>
+      </c>
+      <c r="T22" s="43">
+        <f>SUM(T5:T21)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T20"/>
+  <autoFilter ref="A4:T21"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -9422,7 +9573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10391,72 +10542,120 @@
       <c r="U20" s="50" t="n"/>
       <c r="V20" s="50" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="51" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="47">
+        <f>Planejado!A21</f>
+        <v/>
+      </c>
+      <c r="B21" s="47">
+        <f>Planejado!B21</f>
+        <v/>
+      </c>
+      <c r="C21" s="47">
+        <f>Planejado!C21</f>
+        <v/>
+      </c>
+      <c r="D21" s="48">
+        <f>Planejado!D21</f>
+        <v/>
+      </c>
+      <c r="E21" s="48">
+        <f>Planejado!E21</f>
+        <v/>
+      </c>
+      <c r="F21" s="47">
+        <f>Planejado!F21</f>
+        <v/>
+      </c>
+      <c r="G21" s="47">
+        <f>Planejado!G21</f>
+        <v/>
+      </c>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="49" t="n"/>
+      <c r="K21" s="49" t="n"/>
+      <c r="L21" s="49" t="n"/>
+      <c r="M21" s="49" t="n"/>
+      <c r="N21" s="49" t="n"/>
+      <c r="O21" s="49" t="n"/>
+      <c r="P21" s="49" t="n"/>
+      <c r="Q21" s="49" t="n"/>
+      <c r="R21" s="49" t="n"/>
+      <c r="S21" s="49" t="n"/>
+      <c r="T21" s="45">
+        <f>SUM(H21:S21)</f>
+        <v/>
+      </c>
+      <c r="U21" s="50" t="n"/>
+      <c r="V21" s="50" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B21" s="51" t="n"/>
-      <c r="C21" s="51" t="n"/>
-      <c r="D21" s="51" t="n"/>
-      <c r="E21" s="51" t="n"/>
-      <c r="F21" s="51" t="n"/>
-      <c r="G21" s="51" t="n"/>
-      <c r="H21" s="52">
-        <f>SUM(H5:H20)</f>
-        <v/>
-      </c>
-      <c r="I21" s="52">
-        <f>SUM(I5:I20)</f>
-        <v/>
-      </c>
-      <c r="J21" s="52">
-        <f>SUM(J5:J20)</f>
-        <v/>
-      </c>
-      <c r="K21" s="52">
-        <f>SUM(K5:K20)</f>
-        <v/>
-      </c>
-      <c r="L21" s="52">
-        <f>SUM(L5:L20)</f>
-        <v/>
-      </c>
-      <c r="M21" s="52">
-        <f>SUM(M5:M20)</f>
-        <v/>
-      </c>
-      <c r="N21" s="52">
-        <f>SUM(N5:N20)</f>
-        <v/>
-      </c>
-      <c r="O21" s="52">
-        <f>SUM(O5:O20)</f>
-        <v/>
-      </c>
-      <c r="P21" s="52">
-        <f>SUM(P5:P20)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="52">
-        <f>SUM(Q5:Q20)</f>
-        <v/>
-      </c>
-      <c r="R21" s="52">
-        <f>SUM(R5:R20)</f>
-        <v/>
-      </c>
-      <c r="S21" s="52">
-        <f>SUM(S5:S20)</f>
-        <v/>
-      </c>
-      <c r="T21" s="52">
-        <f>SUM(T5:T20)</f>
-        <v/>
-      </c>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="51" t="n"/>
+      <c r="B22" s="51" t="n"/>
+      <c r="C22" s="51" t="n"/>
+      <c r="D22" s="51" t="n"/>
+      <c r="E22" s="51" t="n"/>
+      <c r="F22" s="51" t="n"/>
+      <c r="G22" s="51" t="n"/>
+      <c r="H22" s="52">
+        <f>SUM(H5:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="52">
+        <f>SUM(I5:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="52">
+        <f>SUM(J5:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="52">
+        <f>SUM(K5:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="52">
+        <f>SUM(L5:L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="52">
+        <f>SUM(M5:M21)</f>
+        <v/>
+      </c>
+      <c r="N22" s="52">
+        <f>SUM(N5:N21)</f>
+        <v/>
+      </c>
+      <c r="O22" s="52">
+        <f>SUM(O5:O21)</f>
+        <v/>
+      </c>
+      <c r="P22" s="52">
+        <f>SUM(P5:P21)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="52">
+        <f>SUM(Q5:Q21)</f>
+        <v/>
+      </c>
+      <c r="R22" s="52">
+        <f>SUM(R5:R21)</f>
+        <v/>
+      </c>
+      <c r="S22" s="52">
+        <f>SUM(S5:S21)</f>
+        <v/>
+      </c>
+      <c r="T22" s="52">
+        <f>SUM(T5:T21)</f>
+        <v/>
+      </c>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10549,11 +10748,11 @@
         </is>
       </c>
       <c r="B5" s="54">
-        <f>SUMIFS(Planejado!$H$5:$H$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C5" s="54">
-        <f>SUMIFS(Realizado!$H$5:$H$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D5" s="54">
@@ -10584,11 +10783,11 @@
         </is>
       </c>
       <c r="B6" s="37">
-        <f>SUMIFS(Planejado!$I$5:$I$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C6" s="37">
-        <f>SUMIFS(Realizado!$I$5:$I$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D6" s="37">
@@ -10619,11 +10818,11 @@
         </is>
       </c>
       <c r="B7" s="54">
-        <f>SUMIFS(Planejado!$J$5:$J$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C7" s="54">
-        <f>SUMIFS(Realizado!$J$5:$J$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D7" s="54">
@@ -10654,11 +10853,11 @@
         </is>
       </c>
       <c r="B8" s="37">
-        <f>SUMIFS(Planejado!$K$5:$K$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C8" s="37">
-        <f>SUMIFS(Realizado!$K$5:$K$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="37">
@@ -10689,11 +10888,11 @@
         </is>
       </c>
       <c r="B9" s="54">
-        <f>SUMIFS(Planejado!$L$5:$L$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C9" s="54">
-        <f>SUMIFS(Realizado!$L$5:$L$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D9" s="54">
@@ -10724,11 +10923,11 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>SUMIFS(Planejado!$M$5:$M$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C10" s="37">
-        <f>SUMIFS(Realizado!$M$5:$M$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D10" s="37">
@@ -10759,11 +10958,11 @@
         </is>
       </c>
       <c r="B11" s="54">
-        <f>SUMIFS(Planejado!$N$5:$N$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C11" s="54">
-        <f>SUMIFS(Realizado!$N$5:$N$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="54">
@@ -10794,11 +10993,11 @@
         </is>
       </c>
       <c r="B12" s="37">
-        <f>SUMIFS(Planejado!$O$5:$O$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C12" s="37">
-        <f>SUMIFS(Realizado!$O$5:$O$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D12" s="37">
@@ -10829,11 +11028,11 @@
         </is>
       </c>
       <c r="B13" s="54">
-        <f>SUMIFS(Planejado!$P$5:$P$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C13" s="54">
-        <f>SUMIFS(Realizado!$P$5:$P$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D13" s="54">
@@ -10864,11 +11063,11 @@
         </is>
       </c>
       <c r="B14" s="37">
-        <f>SUMIFS(Planejado!$Q$5:$Q$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C14" s="37">
-        <f>SUMIFS(Realizado!$Q$5:$Q$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D14" s="37">
@@ -10899,11 +11098,11 @@
         </is>
       </c>
       <c r="B15" s="54">
-        <f>SUMIFS(Planejado!$R$5:$R$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C15" s="54">
-        <f>SUMIFS(Realizado!$R$5:$R$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D15" s="54">
@@ -10934,11 +11133,11 @@
         </is>
       </c>
       <c r="B16" s="37">
-        <f>SUMIFS(Planejado!$S$5:$S$20,Planejado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$21,Planejado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="C16" s="37">
-        <f>SUMIFS(Realizado!$S$5:$S$20,Realizado!$B$5:$B$20,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$21,Realizado!$B$5:$B$21,"TI")</f>
         <v/>
       </c>
       <c r="D16" s="37">
@@ -11091,11 +11290,11 @@
         </is>
       </c>
       <c r="B5" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A5,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A5,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C5" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A5,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A5,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D5" s="54">
@@ -11115,7 +11314,7 @@
         <v/>
       </c>
       <c r="H5" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A5)</f>
         <v/>
       </c>
     </row>
@@ -11126,11 +11325,11 @@
         </is>
       </c>
       <c r="B6" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A6,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A6,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C6" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A6,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A6,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D6" s="37">
@@ -11150,7 +11349,7 @@
         <v/>
       </c>
       <c r="H6" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A6)</f>
         <v/>
       </c>
     </row>
@@ -11161,11 +11360,11 @@
         </is>
       </c>
       <c r="B7" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A7,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A7,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C7" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A7,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A7,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D7" s="54">
@@ -11185,7 +11384,7 @@
         <v/>
       </c>
       <c r="H7" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A7)</f>
         <v/>
       </c>
     </row>
@@ -11196,11 +11395,11 @@
         </is>
       </c>
       <c r="B8" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A8,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A8,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C8" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A8,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A8,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="37">
@@ -11220,7 +11419,7 @@
         <v/>
       </c>
       <c r="H8" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A8)</f>
         <v/>
       </c>
     </row>
@@ -11231,11 +11430,11 @@
         </is>
       </c>
       <c r="B9" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A9,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A9,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C9" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A9,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A9,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D9" s="54">
@@ -11255,7 +11454,7 @@
         <v/>
       </c>
       <c r="H9" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A9)</f>
         <v/>
       </c>
     </row>
@@ -11266,11 +11465,11 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A10,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A10,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C10" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A10,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A10,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D10" s="37">
@@ -11290,7 +11489,7 @@
         <v/>
       </c>
       <c r="H10" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A10)</f>
         <v/>
       </c>
     </row>
@@ -11301,11 +11500,11 @@
         </is>
       </c>
       <c r="B11" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$21,Comparativo!$E$6:$E$21,$A11,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A11,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C11" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$21,Comparativo!$E$6:$E$21,$A11,Comparativo!$B$6:$B$21,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A11,Comparativo!$B$6:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="54">
@@ -11325,7 +11524,7 @@
         <v/>
       </c>
       <c r="H11" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$20,Planejado!$G$5:$G$20,$A11)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A11)</f>
         <v/>
       </c>
     </row>
@@ -11387,7 +11586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11516,17 +11715,17 @@
       </c>
       <c r="B7" s="62" t="inlineStr">
         <is>
-          <t>Elias Benedito zerado nos três meses</t>
+          <t>Elias Benedito — sem custo até jul, renegociado para set</t>
         </is>
       </c>
       <c r="C7" s="62" t="inlineStr">
         <is>
-          <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
+          <t>Orçado R$ 1.065/mês, realizado R$ 0 de jan a jul — contrato ativo, mas sem acionamento no período (confirmado pela gestora). O pagamento passa a ocorrer agora, e a partir de set/26 o valor foi renegociado de R$ 1.065 para R$ 603,30.</t>
         </is>
       </c>
       <c r="D7" s="62" t="inlineStr">
         <is>
-          <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 12.780 a liberar no orçamento do ano.</t>
+          <t>Duas economias na mesma linha: R$ 7.455 pelos sete meses sem acionamento, e R$ 461,70/mês (43%) a partir de set pela renegociação — R$ 1.846,80 no ano. O planejado já reflete o valor novo de set a dez.</t>
         </is>
       </c>
       <c r="E7" s="62" t="inlineStr">
@@ -11534,9 +11733,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="67" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F7" s="66" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11829,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F10" s="68" t="inlineStr">
+      <c r="F10" s="67" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -11790,7 +11989,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F15" s="68" t="inlineStr">
+      <c r="F15" s="67" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -11822,7 +12021,7 @@
           <t>Cristiane + Controladoria</t>
         </is>
       </c>
-      <c r="F16" s="67" t="inlineStr">
+      <c r="F16" s="68" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -11854,7 +12053,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F17" s="68" t="inlineStr">
+      <c r="F17" s="67" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -11886,7 +12085,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F18" s="68" t="inlineStr">
+      <c r="F18" s="67" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -11950,7 +12149,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F20" s="67" t="inlineStr">
+      <c r="F20" s="68" t="inlineStr">
         <is>
           <t>IMPLANTAR</t>
         </is>
@@ -11982,7 +12181,7 @@
           <t>Cristiane + Administrativo</t>
         </is>
       </c>
-      <c r="F21" s="67" t="inlineStr">
+      <c r="F21" s="68" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO</t>
         </is>
@@ -11991,22 +12190,22 @@
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B22" s="65" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>AnyDesk — contratação prevista, definir valor</t>
         </is>
       </c>
       <c r="C22" s="65" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Licença de acesso remoto que será contratada e não constava na ficha. Linha criada com planejado zerado, à espera do valor e do mês de início.</t>
         </is>
       </c>
       <c r="D22" s="65" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>ATENÇÃO À SOBREPOSIÇÃO: o extrato mostra R$ 20.508,55 pagos a J H ALVES — MONITOR REMOTO de jan a jul, o maior fornecedor de despesa do TI e também fora do orçamento (item M). Se o AnyDesk cobre a mesma necessidade, é substituição e pode gerar economia; se é complementar, é custo novo somado a um custo que já não estava previsto. Esclarecer antes de contratar — é o mesmo padrão do Jusfy x Astrea, em que dois softwares de função parecida quase rodaram em paralelo.</t>
         </is>
       </c>
       <c r="E22" s="65" t="inlineStr">
@@ -12014,39 +12213,71 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F22" s="67" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F22" s="68" t="inlineStr">
+        <is>
+          <t>DEFINIR VALOR</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="61" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="62" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C23" s="62" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D23" s="62" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E23" s="62" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F23" s="68" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="64" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B23" s="62" t="inlineStr">
+      <c r="B24" s="65" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C23" s="62" t="inlineStr">
+      <c r="C24" s="65" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D23" s="62" t="inlineStr">
+      <c r="D24" s="65" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E23" s="62" t="inlineStr">
+      <c r="E24" s="65" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F23" s="69" t="inlineStr">
+      <c r="F24" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11586,7 +11586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12222,62 +12222,94 @@
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B23" s="62" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Vitor (diretoria) — Claude ou GPT? PERGUNTAR</t>
         </is>
       </c>
       <c r="C23" s="62" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Confirmar com o Vitor se ele seguirá usando o Claude, o GPT, ou os dois. Hoje as duas ferramentas estão contratadas e são de mesma finalidade — IA generalista —, então manter as duas para o mesmo usuário é redundância paga.</t>
         </is>
       </c>
       <c r="D23" s="62" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>É pré-requisito para fechar a meta do item L: não dá para dimensionar o orçamento de IA sem saber quantas licenças de cada ferramenta ficam de pé. Referência de custo: a OpenAI aparece no extrato com R$ 5.950,10 em sete meses, sendo R$ 5.394 só em abr/26. Levantar a mesma informação para os demais usuários, não só a diretoria — a decisão vale para todo mundo.</t>
         </is>
       </c>
       <c r="E23" s="62" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Vitor</t>
         </is>
       </c>
       <c r="F23" s="68" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>PERGUNTAR</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="64" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C24" s="65" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D24" s="65" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E24" s="65" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F24" s="68" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="61" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B24" s="65" t="inlineStr">
+      <c r="B25" s="62" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C24" s="65" t="inlineStr">
+      <c r="C25" s="62" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D24" s="65" t="inlineStr">
+      <c r="D25" s="62" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E24" s="65" t="inlineStr">
+      <c r="E25" s="62" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F24" s="69" t="inlineStr">
+      <c r="F25" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11586,7 +11586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12254,62 +12254,94 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B24" s="65" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Mapa de licenças de IA — quem usa o quê</t>
         </is>
       </c>
       <c r="C24" s="65" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Situação atual conhecida: a licença do GPT era da Thamar e hoje é usada em conjunto por Gil, Miguel e Thamar. Uma licença também foi cedida ao Financeiro. Falta o mapa completo — quem usa cada ferramenta, em qual área e sob qual login.</t>
         </is>
       </c>
       <c r="D24" s="65" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Duas consequências. ORÇAMENTO: uma licença usada pelo Financeiro é custo de outra área lançado no TI/Jurídico — é exatamente o caso que o rateio do item L precisa resolver, e sem o mapa não há como ratear. RISCO: contas de IA generalista são individuais, e o compartilhamento entre pessoas costuma contrariar os termos de uso do fornecedor, com risco de suspensão. Mais grave num escritório de advocacia: o histórico de conversas fica visível para todos que usam o mesmo login, então dados de um cliente podem ser vistos por quem não atua no caso — questão de sigilo profissional, não só de custo. Avaliar licenças individuais ou plano de equipe, que costuma sair mais barato por usuário e separa os históricos.</t>
         </is>
       </c>
       <c r="E24" s="65" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Vitor</t>
         </is>
       </c>
       <c r="F24" s="68" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>LEVANTAR</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="61" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="62" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C25" s="62" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D25" s="62" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E25" s="62" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F25" s="68" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="64" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B25" s="62" t="inlineStr">
+      <c r="B26" s="65" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C25" s="62" t="inlineStr">
+      <c r="C26" s="65" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D25" s="62" t="inlineStr">
+      <c r="D26" s="65" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E25" s="62" t="inlineStr">
+      <c r="E26" s="65" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F25" s="69" t="inlineStr">
+      <c r="F26" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -12291,17 +12291,17 @@
       </c>
       <c r="B25" s="62" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
         </is>
       </c>
       <c r="C25" s="62" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
         </is>
       </c>
       <c r="D25" s="62" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
         </is>
       </c>
       <c r="E25" s="62" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="F25" s="68" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>CONFIRMAR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11586,7 +11586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12286,22 +12286,22 @@
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B25" s="62" t="inlineStr">
         <is>
-          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
+          <t>Divisão de responsabilidades no acompanhamento</t>
         </is>
       </c>
       <c r="C25" s="62" t="inlineStr">
         <is>
-          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
+          <t>Definição de quem faz o quê no controle orçamentário do TI. Capacidades: Vinicius, analista, 173 h/mês a R$ 31,25/h de custo total; Jonathan, consultor/desenvolvedor, 3 dias por semana, 104 h/mês a R$ 60,58/h — o dobro. Cristiane na gestão.</t>
         </is>
       </c>
       <c r="D25" s="62" t="inlineStr">
         <is>
-          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
+          <t>VINICIUS (todo o recorrente): extração mensal do SIENGE e lançamento do realizado, controle de equipamentos (solicitações, empréstimos, troca 1x1), acompanhamento do saldo por área para avisar antes do estouro, conferência de faturas contra contrato. JONATHAN (pontual e técnico, nunca rotina): avaliar AnyDesk x Monitor Remoto, avaliar Claude x GPT e planos de equipe, e automatizar a extração do SIENGE — esta última é a que paga o custo dele, porque devolve tempo do analista todos os meses. CRISTIANE: negociação de contratos, rateio, o que entra e sai do orçamento, apresentação à diretoria. Critério: 104 h/mês é capacidade limitada, e cada hora do consultor em tarefa administrativa custa o dobro da mesma hora do analista. Se o Jonathan aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
         </is>
       </c>
       <c r="E25" s="62" t="inlineStr">
@@ -12309,39 +12309,71 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F25" s="68" t="inlineStr">
-        <is>
-          <t>CONFIRMAR</t>
+      <c r="F25" s="66" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="64" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="65" t="inlineStr">
+        <is>
+          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
+        </is>
+      </c>
+      <c r="C26" s="65" t="inlineStr">
+        <is>
+          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
+        </is>
+      </c>
+      <c r="D26" s="65" t="inlineStr">
+        <is>
+          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
+        </is>
+      </c>
+      <c r="E26" s="65" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F26" s="68" t="inlineStr">
+        <is>
+          <t>CONFIRMAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="61" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B26" s="65" t="inlineStr">
+      <c r="B27" s="62" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C26" s="65" t="inlineStr">
+      <c r="C27" s="62" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D26" s="65" t="inlineStr">
+      <c r="D27" s="62" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E26" s="65" t="inlineStr">
+      <c r="E27" s="62" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F26" s="69" t="inlineStr">
+      <c r="F27" s="69" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -211,17 +211,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -397,10 +397,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -430,10 +430,6 @@
     <xf numFmtId="1" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -441,6 +437,10 @@
     <xf numFmtId="164" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1968,114 +1968,118 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="79" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C5" s="53" t="n">
+      <c r="C5" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="54" t="n">
+      <c r="D5" s="81" t="n">
         <v>4311.56</v>
       </c>
-      <c r="E5" s="54" t="n"/>
-      <c r="F5" s="54" t="n"/>
-      <c r="G5" s="54" t="n"/>
-      <c r="H5" s="54" t="n">
+      <c r="E5" s="81" t="n"/>
+      <c r="F5" s="81" t="n"/>
+      <c r="G5" s="81" t="n"/>
+      <c r="H5" s="81" t="n">
         <v>3723.62</v>
       </c>
-      <c r="I5" s="54" t="n">
+      <c r="I5" s="81" t="n">
         <v>6173.37</v>
       </c>
-      <c r="J5" s="54" t="n">
+      <c r="J5" s="81" t="n">
         <v>6300</v>
       </c>
-      <c r="K5" s="79" t="n">
+      <c r="K5" s="82" t="n">
         <v>20508.55</v>
       </c>
-      <c r="L5" s="80" t="n"/>
+      <c r="L5" s="83" t="inlineStr">
+        <is>
+          <t>TI-E03 Jonathan (Monitor Remoto)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="79" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="B6" s="81" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C6" s="82" t="n">
+      <c r="C6" s="80" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="83" t="n">
+      <c r="D6" s="81" t="n">
         <v>2670.84</v>
       </c>
-      <c r="E6" s="83" t="n">
+      <c r="E6" s="81" t="n">
         <v>2986.04</v>
       </c>
-      <c r="F6" s="83" t="n">
+      <c r="F6" s="81" t="n">
         <v>2778.04</v>
       </c>
-      <c r="G6" s="83" t="n">
+      <c r="G6" s="81" t="n">
         <v>2751.04</v>
       </c>
-      <c r="H6" s="83" t="n">
+      <c r="H6" s="81" t="n">
         <v>2719.04</v>
       </c>
-      <c r="I6" s="83" t="n">
+      <c r="I6" s="81" t="n">
         <v>3633.16</v>
       </c>
-      <c r="J6" s="83" t="n">
+      <c r="J6" s="81" t="n">
         <v>2461.04</v>
       </c>
-      <c r="K6" s="84" t="n">
+      <c r="K6" s="82" t="n">
         <v>19999.2</v>
       </c>
-      <c r="L6" s="85" t="inlineStr">
+      <c r="L6" s="83" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius Di Franco</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="81" t="inlineStr">
+      <c r="A7" s="79" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="B7" s="81" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C7" s="82" t="n">
+      <c r="C7" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="83" t="n">
+      <c r="D7" s="81" t="n"/>
+      <c r="E7" s="81" t="n">
         <v>234.46</v>
       </c>
-      <c r="F7" s="83" t="n">
+      <c r="F7" s="81" t="n">
         <v>321.76</v>
       </c>
-      <c r="G7" s="83" t="n">
+      <c r="G7" s="81" t="n">
         <v>5393.88</v>
       </c>
-      <c r="H7" s="83" t="n"/>
-      <c r="I7" s="83" t="n"/>
-      <c r="J7" s="83" t="n"/>
-      <c r="K7" s="84" t="n">
+      <c r="H7" s="81" t="n"/>
+      <c r="I7" s="81" t="n"/>
+      <c r="J7" s="81" t="n"/>
+      <c r="K7" s="82" t="n">
         <v>5950.1</v>
       </c>
-      <c r="L7" s="85" t="inlineStr">
+      <c r="L7" s="83" t="inlineStr">
         <is>
           <t>TI-D11 GPT</t>
         </is>
@@ -2114,10 +2118,10 @@
       <c r="J8" s="54" t="n">
         <v>979.4</v>
       </c>
-      <c r="K8" s="79" t="n">
+      <c r="K8" s="84" t="n">
         <v>5228.139999999999</v>
       </c>
-      <c r="L8" s="80" t="n"/>
+      <c r="L8" s="85" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="56" t="inlineStr">
@@ -2150,10 +2154,10 @@
       <c r="J9" s="54" t="n">
         <v>1151.26</v>
       </c>
-      <c r="K9" s="79" t="n">
+      <c r="K9" s="84" t="n">
         <v>3296.12</v>
       </c>
-      <c r="L9" s="80" t="n"/>
+      <c r="L9" s="85" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="56" t="inlineStr">
@@ -2184,48 +2188,48 @@
       <c r="J10" s="54" t="n">
         <v>1037.38</v>
       </c>
-      <c r="K10" s="79" t="n">
+      <c r="K10" s="84" t="n">
         <v>3242.61</v>
       </c>
-      <c r="L10" s="80" t="n"/>
+      <c r="L10" s="85" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="81" t="inlineStr">
+      <c r="A11" s="79" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="B11" s="81" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C11" s="82" t="n">
+      <c r="C11" s="80" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="83" t="n"/>
-      <c r="E11" s="83" t="n">
+      <c r="D11" s="81" t="n"/>
+      <c r="E11" s="81" t="n">
         <v>485</v>
       </c>
-      <c r="F11" s="83" t="n">
+      <c r="F11" s="81" t="n">
         <v>485</v>
       </c>
-      <c r="G11" s="83" t="n">
+      <c r="G11" s="81" t="n">
         <v>485</v>
       </c>
-      <c r="H11" s="83" t="n">
+      <c r="H11" s="81" t="n">
         <v>485</v>
       </c>
-      <c r="I11" s="83" t="n">
+      <c r="I11" s="81" t="n">
         <v>485</v>
       </c>
-      <c r="J11" s="83" t="n">
+      <c r="J11" s="81" t="n">
         <v>485</v>
       </c>
-      <c r="K11" s="84" t="n">
+      <c r="K11" s="82" t="n">
         <v>2910</v>
       </c>
-      <c r="L11" s="85" t="inlineStr">
+      <c r="L11" s="83" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius (benefício)</t>
         </is>
@@ -2258,10 +2262,10 @@
       <c r="H12" s="54" t="n"/>
       <c r="I12" s="54" t="n"/>
       <c r="J12" s="54" t="n"/>
-      <c r="K12" s="79" t="n">
+      <c r="K12" s="84" t="n">
         <v>954.5500000000001</v>
       </c>
-      <c r="L12" s="80" t="n"/>
+      <c r="L12" s="85" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="56" t="inlineStr">
@@ -2294,10 +2298,10 @@
         <v>137.93</v>
       </c>
       <c r="J13" s="54" t="n"/>
-      <c r="K13" s="79" t="n">
+      <c r="K13" s="84" t="n">
         <v>827.49</v>
       </c>
-      <c r="L13" s="80" t="n"/>
+      <c r="L13" s="85" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="56" t="inlineStr">
@@ -2328,10 +2332,10 @@
         <v>554.58</v>
       </c>
       <c r="J14" s="54" t="n"/>
-      <c r="K14" s="79" t="n">
+      <c r="K14" s="84" t="n">
         <v>758.53</v>
       </c>
-      <c r="L14" s="80" t="n"/>
+      <c r="L14" s="85" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="56" t="inlineStr">
@@ -2368,10 +2372,10 @@
       <c r="J15" s="54" t="n">
         <v>82.5</v>
       </c>
-      <c r="K15" s="79" t="n">
+      <c r="K15" s="84" t="n">
         <v>690</v>
       </c>
-      <c r="L15" s="80" t="n"/>
+      <c r="L15" s="85" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
@@ -2404,10 +2408,10 @@
       <c r="J16" s="54" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="K16" s="79" t="n">
+      <c r="K16" s="84" t="n">
         <v>562.42</v>
       </c>
-      <c r="L16" s="80" t="n"/>
+      <c r="L16" s="85" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="56" t="inlineStr">
@@ -2432,10 +2436,10 @@
         <v>183.6</v>
       </c>
       <c r="J17" s="54" t="n"/>
-      <c r="K17" s="79" t="n">
+      <c r="K17" s="84" t="n">
         <v>183.6</v>
       </c>
-      <c r="L17" s="80" t="n"/>
+      <c r="L17" s="85" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="51" t="inlineStr">
@@ -9878,7 +9882,7 @@
         <v/>
       </c>
       <c r="H7" s="49" t="n">
-        <v>0</v>
+        <v>4311.56</v>
       </c>
       <c r="I7" s="49" t="n">
         <v>0</v>
@@ -9887,13 +9891,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="49" t="n">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="L7" s="49" t="n">
-        <v>6300</v>
+        <v>3723.62</v>
       </c>
       <c r="M7" s="49" t="n">
-        <v>6300</v>
+        <v>6173.37</v>
       </c>
       <c r="N7" s="49" t="n">
         <v>6300</v>
@@ -9909,12 +9913,12 @@
       </c>
       <c r="U7" s="50" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Extrato do financeiro</t>
         </is>
       </c>
       <c r="V7" s="50" t="inlineStr">
         <is>
-          <t>Sem custo em jan–mar (contratação segurada). R$ 6.300/mês a partir de abr, contra R$ 10.000 orçados</t>
+          <t>Credor 'J H ALVES - MONITOR REMOTO'. Pagamentos: 19/01 NFS.70 R$ 4.311,56; 01/05 NFS.76 R$ 3.723,62; 01/06 NFS.78 R$ 6.173,37; 01/07 NFS.3 R$ 6.300,00. Sem pagamento em fev, mar e abr</t>
         </is>
       </c>
     </row>
@@ -11683,17 +11687,17 @@
       </c>
       <c r="B6" s="65" t="inlineStr">
         <is>
-          <t>Jonathan — economia de R$ 44.800 até julho</t>
+          <t>Jonathan — economia de R$ 49.491 até julho</t>
         </is>
       </c>
       <c r="C6" s="65" t="inlineStr">
         <is>
-          <t>Orçado R$ 10.000/mês desde jan/26. A contratação foi segurada e as atividades só começaram em abr/26, a R$ 6.300/mês. Resultado: três meses sem custo (R$ 30.000) e quatro meses a R$ 3.700 abaixo do orçado (R$ 14.800).</t>
+          <t>Orçado R$ 10.000/mês desde jan/26. A contratação foi segurada e o serviço só começou depois, chegando a R$ 6.300/mês. Realizado pelo extrato, no credor 'J H ALVES — MONITOR REMOTO': R$ 4.311,56 em jan, nada em fev, mar e abr, e R$ 3.723,62, R$ 6.173,37 e R$ 6.300,00 em mai, jun e jul. Total de R$ 20.508,55 contra R$ 70.000 orçados.</t>
         </is>
       </c>
       <c r="D6" s="65" t="inlineStr">
         <is>
-          <t>É de longe a maior economia das duas áreas: R$ 44.800 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Se o valor de R$ 6.300 se mantiver até dez, somam-se outros R$ 18.500 — total de R$ 63.300 no ano. Vale destacar na apresentação à diretoria.</t>
+          <t>É de longe a maior economia das duas áreas: R$ 49.491,45 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Vale destacar na apresentação. DOIS PONTOS A ESCLARECER: (1) o pagamento de R$ 4.311,56 em 19/01 é anterior ao início das atividades — provavelmente serviço de dez/2025 recebido no mês seguinte, confirmar; (2) mai e jun saíram abaixo de R$ 6.300 (R$ 3.723,62 e R$ 6.173,37), verificar se foi proporcional por dias trabalhados.</t>
         </is>
       </c>
       <c r="E6" s="65" t="inlineStr">
@@ -11703,7 +11707,7 @@
       </c>
       <c r="F6" s="66" t="inlineStr">
         <is>
-          <t>RESOLVIDO</t>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11737,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="66" t="inlineStr">
+      <c r="F7" s="67" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
@@ -11765,7 +11769,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F8" s="66" t="inlineStr">
+      <c r="F8" s="67" t="inlineStr">
         <is>
           <t>APLICADO</t>
         </is>
@@ -11797,7 +11801,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="66" t="inlineStr">
+      <c r="F9" s="67" t="inlineStr">
         <is>
           <t>APLICADO</t>
         </is>
@@ -11816,7 +11820,7 @@
       </c>
       <c r="C10" s="65" t="inlineStr">
         <is>
-          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: J H Alves / Monitor Remoto (R$ 20.509) e um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama).</t>
+          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama). O 'J H Alves — Monitor Remoto' NÃO entra nesta lista: é o Jonathan, que já tem linha no orçamento (TI-E03).</t>
         </is>
       </c>
       <c r="D10" s="65" t="inlineStr">
@@ -11829,7 +11833,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F10" s="67" t="inlineStr">
+      <c r="F10" s="68" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -11893,7 +11897,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="66" t="inlineStr">
+      <c r="F12" s="67" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
@@ -11925,7 +11929,7 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F13" s="66" t="inlineStr">
+      <c r="F13" s="67" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
@@ -11989,7 +11993,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F15" s="67" t="inlineStr">
+      <c r="F15" s="68" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -12021,7 +12025,7 @@
           <t>Cristiane + Controladoria</t>
         </is>
       </c>
-      <c r="F16" s="68" t="inlineStr">
+      <c r="F16" s="69" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -12053,7 +12057,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F17" s="67" t="inlineStr">
+      <c r="F17" s="68" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -12085,7 +12089,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F18" s="67" t="inlineStr">
+      <c r="F18" s="68" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -12117,7 +12121,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F19" s="66" t="inlineStr">
+      <c r="F19" s="67" t="inlineStr">
         <is>
           <t>APLICADO</t>
         </is>
@@ -12149,7 +12153,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F20" s="68" t="inlineStr">
+      <c r="F20" s="69" t="inlineStr">
         <is>
           <t>IMPLANTAR</t>
         </is>
@@ -12181,7 +12185,7 @@
           <t>Cristiane + Administrativo</t>
         </is>
       </c>
-      <c r="F21" s="68" t="inlineStr">
+      <c r="F21" s="69" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO</t>
         </is>
@@ -12205,7 +12209,7 @@
       </c>
       <c r="D22" s="65" t="inlineStr">
         <is>
-          <t>ATENÇÃO À SOBREPOSIÇÃO: o extrato mostra R$ 20.508,55 pagos a J H ALVES — MONITOR REMOTO de jan a jul, o maior fornecedor de despesa do TI e também fora do orçamento (item M). Se o AnyDesk cobre a mesma necessidade, é substituição e pode gerar economia; se é complementar, é custo novo somado a um custo que já não estava previsto. Esclarecer antes de contratar — é o mesmo padrão do Jusfy x Astrea, em que dois softwares de função parecida quase rodaram em paralelo.</t>
+          <t>Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. O AnyDesk é contratação nova e sem substituto atual. Definir valor e mês para a linha entrar no orçamento — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
         </is>
       </c>
       <c r="E22" s="65" t="inlineStr">
@@ -12213,7 +12217,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F22" s="68" t="inlineStr">
+      <c r="F22" s="69" t="inlineStr">
         <is>
           <t>DEFINIR VALOR</t>
         </is>
@@ -12245,7 +12249,7 @@
           <t>Cristiane + Vitor</t>
         </is>
       </c>
-      <c r="F23" s="68" t="inlineStr">
+      <c r="F23" s="69" t="inlineStr">
         <is>
           <t>PERGUNTAR</t>
         </is>
@@ -12277,7 +12281,7 @@
           <t>Cristiane + Vitor</t>
         </is>
       </c>
-      <c r="F24" s="68" t="inlineStr">
+      <c r="F24" s="69" t="inlineStr">
         <is>
           <t>LEVANTAR</t>
         </is>
@@ -12309,7 +12313,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F25" s="66" t="inlineStr">
+      <c r="F25" s="67" t="inlineStr">
         <is>
           <t>APLICADO</t>
         </is>
@@ -12341,7 +12345,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F26" s="68" t="inlineStr">
+      <c r="F26" s="69" t="inlineStr">
         <is>
           <t>CONFIRMAR</t>
         </is>
@@ -12373,7 +12377,7 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F27" s="69" t="inlineStr">
+      <c r="F27" s="66" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -20,8 +20,8 @@
     <sheet name="Contas Pagas (detalhe)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$104</definedName>
@@ -1233,15 +1233,15 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$B$5:$B$21,"TI",Planejado!$C$5:$C$21,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$B$5:$B$22,"TI",Planejado!$C$5:$C$22,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$B$6:$B$23,"TI",Comparativo!$C$6:$C$23,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$B$6:$B$23,"TI",Comparativo!$C$6:$C$23,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1257,7 +1257,7 @@
         <v/>
       </c>
       <c r="I6" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$22,"&gt;0",Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$22,"?*",Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$23,"&gt;0",Comparativo!$B$6:$B$23,"TI",Comparativo!$C$6:$C$23,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$23,"?*",Comparativo!$B$6:$B$23,"TI",Comparativo!$C$6:$C$23,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1273,15 +1273,15 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$B$5:$B$21,"TI",Planejado!$C$5:$C$21,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$B$5:$B$22,"TI",Planejado!$C$5:$C$22,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$B$6:$B$23,"TI",Comparativo!$C$6:$C$23,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$B$6:$B$23,"TI",Comparativo!$C$6:$C$23,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1297,7 +1297,7 @@
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$22,"&gt;0",Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$22,"?*",Comparativo!$B$6:$B$22,"TI",Comparativo!$C$6:$C$22,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$23,"&gt;0",Comparativo!$B$6:$B$23,"TI",Comparativo!$C$6:$C$23,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$23,"?*",Comparativo!$B$6:$B$23,"TI",Comparativo!$C$6:$C$23,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1313,15 +1313,15 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="12">
@@ -1337,7 +1337,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$22,"&gt;0",Comparativo!$B$6:$B$22,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$22,"?*",Comparativo!$B$6:$B$22,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$23,"&gt;0",Comparativo!$B$6:$B$23,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$23,"?*",Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="17">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$22,"&lt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$23,"&lt;0")</f>
         <v/>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="17">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$22,"&gt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$23,"&gt;0")</f>
         <v/>
       </c>
       <c r="D13" s="18" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B14" s="19" t="n"/>
       <c r="C14" s="20">
-        <f>-SUM(Comparativo!$Q$6:$Q$22)</f>
+        <f>-SUM(Comparativo!$Q$6:$Q$23)</f>
         <v/>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B15" s="16" t="n"/>
       <c r="C15" s="17">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$22)/Comparativo!$D$3*12,"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$23)/Comparativo!$D$3*12,"")</f>
         <v/>
       </c>
       <c r="D15" s="18" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="22">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$22)/SUM(Comparativo!$S$6:$S$22),"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$23)/SUM(Comparativo!$S$6:$S$23),"")</f>
         <v/>
       </c>
       <c r="D16" s="18" t="inlineStr">
@@ -1515,23 +1515,23 @@
         <v>1</v>
       </c>
       <c r="B21" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A21),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="C21" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A21),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A21),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A21),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A21),Comparativo!$R$6:$R$22,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A21),Comparativo!$R$6:$R$23,0)),""),"")</f>
         <v/>
       </c>
       <c r="G21" s="29">
@@ -1544,23 +1544,23 @@
         <v>2</v>
       </c>
       <c r="B22" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A22),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="C22" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A22),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A22),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A22),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="F22" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A22),Comparativo!$R$6:$R$22,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A22),Comparativo!$R$6:$R$23,0)),""),"")</f>
         <v/>
       </c>
       <c r="G22" s="29">
@@ -1573,23 +1573,23 @@
         <v>3</v>
       </c>
       <c r="B23" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A23),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="C23" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A23),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A23),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A23),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="F23" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A23),Comparativo!$R$6:$R$22,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A23),Comparativo!$R$6:$R$23,0)),""),"")</f>
         <v/>
       </c>
       <c r="G23" s="29">
@@ -1602,23 +1602,23 @@
         <v>4</v>
       </c>
       <c r="B24" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A24),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="C24" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A24),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A24),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A24),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="F24" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A24),Comparativo!$R$6:$R$22,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A24),Comparativo!$R$6:$R$23,0)),""),"")</f>
         <v/>
       </c>
       <c r="G24" s="29">
@@ -1631,23 +1631,23 @@
         <v>5</v>
       </c>
       <c r="B25" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A25),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A25),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A25),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A25),Comparativo!$R$6:$R$23,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="28">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$R$6:$R$22,A25),Comparativo!$R$6:$R$22,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$R$6:$R$23,A25),Comparativo!$R$6:$R$23,0)),""),"")</f>
         <v/>
       </c>
       <c r="G25" s="29">
@@ -1705,23 +1705,23 @@
         <v>1</v>
       </c>
       <c r="B30" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A30),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="C30" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A30),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A30),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A30),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="F30" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A30),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A30),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="G30" s="29">
@@ -1734,23 +1734,23 @@
         <v>2</v>
       </c>
       <c r="B31" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A31),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="C31" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A31),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A31),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A31),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="F31" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A31),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A31),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="G31" s="29">
@@ -1763,23 +1763,23 @@
         <v>3</v>
       </c>
       <c r="B32" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A32),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="C32" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A32),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A32),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A32),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="F32" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A32),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A32),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="G32" s="29">
@@ -1792,23 +1792,23 @@
         <v>4</v>
       </c>
       <c r="B33" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A33),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="C33" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A33),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A33),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A33),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="F33" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A33),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A33),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="G33" s="29">
@@ -1821,23 +1821,23 @@
         <v>5</v>
       </c>
       <c r="B34" s="26">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A34),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="26">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A34),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A34),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A34),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="27">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$22,MATCH(LARGE(Comparativo!$O$6:$O$22,A34),Comparativo!$O$6:$O$22,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$23,MATCH(LARGE(Comparativo!$O$6:$O$23,A34),Comparativo!$O$6:$O$23,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="29">
@@ -6547,7 +6547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8029,57 +8029,135 @@
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="42" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="35">
+        <f>Planejado!A22</f>
+        <v/>
+      </c>
+      <c r="B23" s="35">
+        <f>Planejado!B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="35">
+        <f>Planejado!C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="36">
+        <f>Planejado!D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="35">
+        <f>Planejado!G22</f>
+        <v/>
+      </c>
+      <c r="F23" s="37">
+        <f>INDEX(Planejado!$H22:$S22,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G23" s="37">
+        <f>INDEX(Realizado!$H22:$S22,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H23" s="37">
+        <f>G23-F23</f>
+        <v/>
+      </c>
+      <c r="I23" s="37">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H22:$S22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="37">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H22:$S22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="37">
+        <f>J23-I23</f>
+        <v/>
+      </c>
+      <c r="L23" s="38">
+        <f>IFERROR(K23/I23,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="38">
+        <f>IFERROR(J23/I23,"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="39">
+        <f>IF(P23=0,"Sem lançamento",IF(AND(I23=0,J23=0),"—",IF(I23=0,"Não orçado",IF(K23&gt;0.05*I23,"Acima do orçado",IF(K23&lt;-0.05*I23,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O23" s="34">
+        <f>IF(K23&gt;1,K23+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="40">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H22:$S22&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="41">
+        <f>IF(P23=0,"",K23)</f>
+        <v/>
+      </c>
+      <c r="R23" s="41">
+        <f>IF(AND(Q23&lt;&gt;"",Q23&lt;-1),-Q23+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S23" s="41">
+        <f>IF(Q23="","",I23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B33" s="42" t="n"/>
-      <c r="C33" s="42" t="n"/>
-      <c r="D33" s="42" t="n"/>
-      <c r="E33" s="42" t="n"/>
-      <c r="F33" s="43">
-        <f>SUM(F6:F22)</f>
-        <v/>
-      </c>
-      <c r="G33" s="43">
-        <f>SUM(G6:G22)</f>
-        <v/>
-      </c>
-      <c r="H33" s="43">
-        <f>SUM(H6:H22)</f>
-        <v/>
-      </c>
-      <c r="I33" s="43">
-        <f>SUM(I6:I22)</f>
-        <v/>
-      </c>
-      <c r="J33" s="43">
-        <f>SUM(J6:J22)</f>
-        <v/>
-      </c>
-      <c r="K33" s="43">
-        <f>SUM(K6:K22)</f>
-        <v/>
-      </c>
-      <c r="L33" s="44">
-        <f>IFERROR(K33/I33,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="44">
-        <f>IFERROR(J33/I33,"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="42" t="n"/>
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="42" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="43">
+        <f>SUM(F6:F23)</f>
+        <v/>
+      </c>
+      <c r="G34" s="43">
+        <f>SUM(G6:G23)</f>
+        <v/>
+      </c>
+      <c r="H34" s="43">
+        <f>SUM(H6:H23)</f>
+        <v/>
+      </c>
+      <c r="I34" s="43">
+        <f>SUM(I6:I23)</f>
+        <v/>
+      </c>
+      <c r="J34" s="43">
+        <f>SUM(J6:J23)</f>
+        <v/>
+      </c>
+      <c r="K34" s="43">
+        <f>SUM(K6:K23)</f>
+        <v/>
+      </c>
+      <c r="L34" s="44">
+        <f>IFERROR(K34/I34,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="44">
+        <f>IFERROR(J34/I34,"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="42" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N22"/>
+  <autoFilter ref="A5:N23"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H22">
+  <conditionalFormatting sqref="H6:H23">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -8087,7 +8165,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K22">
+  <conditionalFormatting sqref="K6:K23">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -8110,7 +8188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8274,7 +8352,7 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
+          <t>Analista Administrativo — suporte ao usuário, rotina administrativa do orçamento e apoio operacional ao desenvolvimento conduzido pelo consultor. Orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
@@ -8423,12 +8501,12 @@
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Jonathan — consultor (desde abr/26)</t>
         </is>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>Consultor — orçado desde jan/26. As atividades só começaram em abr/26: a contratação foi segurada por três meses</t>
+          <t>Consultor/desenvolvedor, 3 dias por semana (104 h/mês) desde abr/26. Orçado em R$ 10.000/mês desde jan/26; a contratação foi segurada por três meses. Credor no SIENGE: J H ALVES — MONITOR REMOTO</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
@@ -8485,7 +8563,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>TI-D01</t>
+          <t>TI-E04</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
@@ -8495,60 +8573,64 @@
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
-          <t>Peças de Manutenção</t>
+          <t>Monitor Remoto — serviços esporádicos (até mar/26)</t>
         </is>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
-        </is>
-      </c>
-      <c r="F8" s="35" t="inlineStr"/>
+          <t>Mesmo prestador do TI-E03, em vínculo anterior: serviços esporádicos prestados de fora, encerrados quando ele passou a atuar como consultor fixo em abr/26. Não constava na ficha de orçamento</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos Diversos</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="I8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="J8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="K8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="L8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="M8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="N8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="O8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="P8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="R8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="S8" s="37" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="T8" s="45">
         <f>SUM(H8:S8)</f>
@@ -8558,7 +8640,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>TI-D02</t>
+          <t>TI-D01</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
@@ -8573,55 +8655,55 @@
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>Backup em Nuvem</t>
+          <t>Peças de Manutenção</t>
         </is>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
+          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr"/>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
       <c r="H9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="I9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="J9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="K9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="L9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="M9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="N9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="O9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="P9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="Q9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="R9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="S9" s="37" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="T9" s="45">
         <f>SUM(H9:S9)</f>
@@ -8631,7 +8713,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>TI-D03</t>
+          <t>TI-D02</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
@@ -8646,12 +8728,12 @@
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
-          <t>Inteligência Artificial (Adapta)</t>
+          <t>Backup em Nuvem</t>
         </is>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR. Pagamentos reais de R$ 575/mês estão lançados no centro de custo Jurídico por engano (ver pendência Q)</t>
+          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr"/>
@@ -8661,40 +8743,40 @@
         </is>
       </c>
       <c r="H10" s="37" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="I10" s="37" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="J10" s="37" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="K10" s="37" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="L10" s="37" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="M10" s="37" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="N10" s="37" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="O10" s="37" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="P10" s="37" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="Q10" s="37" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="R10" s="37" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="S10" s="37" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="T10" s="45">
         <f>SUM(H10:S10)</f>
@@ -8704,7 +8786,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>TI-D04</t>
+          <t>TI-D03</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
@@ -8719,12 +8801,12 @@
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>Antivírus</t>
+          <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
+          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR. Pagamentos reais de R$ 575/mês estão lançados no centro de custo Jurídico por engano (ver pendência Q)</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr"/>
@@ -8734,40 +8816,40 @@
         </is>
       </c>
       <c r="H11" s="37" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="I11" s="37" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="J11" s="37" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="K11" s="37" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="L11" s="37" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="M11" s="37" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="N11" s="37" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="O11" s="37" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="P11" s="37" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="Q11" s="37" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="R11" s="37" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="S11" s="37" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="T11" s="45">
         <f>SUM(H11:S11)</f>
@@ -8777,7 +8859,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>TI-D05</t>
+          <t>TI-D04</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
@@ -8792,12 +8874,12 @@
       </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>Pacote Office 365</t>
+          <t>Antivírus</t>
         </is>
       </c>
       <c r="E12" s="36" t="inlineStr">
         <is>
-          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
+          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F12" s="35" t="inlineStr"/>
@@ -8807,40 +8889,40 @@
         </is>
       </c>
       <c r="H12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="I12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="J12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="K12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="L12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="M12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="N12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="O12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="P12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="Q12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="R12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="S12" s="37" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="T12" s="45">
         <f>SUM(H12:S12)</f>
@@ -8850,7 +8932,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>TI-D06</t>
+          <t>TI-D05</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
@@ -8865,55 +8947,55 @@
       </c>
       <c r="D13" s="36" t="inlineStr">
         <is>
-          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+          <t>Pacote Office 365</t>
         </is>
       </c>
       <c r="E13" s="36" t="inlineStr">
         <is>
-          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr"/>
       <c r="G13" s="35" t="inlineStr">
         <is>
-          <t>Móveis e Utensílios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="I13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="J13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="K13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="L13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="M13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="N13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="O13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="P13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="Q13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="R13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="S13" s="37" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="T13" s="45">
         <f>SUM(H13:S13)</f>
@@ -8923,7 +9005,7 @@
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>TI-D07</t>
+          <t>TI-D06</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
@@ -8938,51 +9020,55 @@
       </c>
       <c r="D14" s="36" t="inlineStr">
         <is>
-          <t>Cursos e Treinamentos</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="inlineStr"/>
+          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+        </is>
+      </c>
+      <c r="E14" s="36" t="inlineStr">
+        <is>
+          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+        </is>
+      </c>
       <c r="F14" s="35" t="inlineStr"/>
       <c r="G14" s="35" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Móveis e Utensílios</t>
         </is>
       </c>
       <c r="H14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="I14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="J14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="K14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="L14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="M14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="N14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="O14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="P14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="Q14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="R14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="S14" s="37" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="T14" s="45">
         <f>SUM(H14:S14)</f>
@@ -8992,7 +9078,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>TI-D08</t>
+          <t>TI-D07</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
@@ -9007,51 +9093,51 @@
       </c>
       <c r="D15" s="36" t="inlineStr">
         <is>
-          <t>Aplicativo de Gravação de Reunião</t>
+          <t>Cursos e Treinamentos</t>
         </is>
       </c>
       <c r="E15" s="36" t="inlineStr"/>
       <c r="F15" s="35" t="inlineStr"/>
       <c r="G15" s="35" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="J15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="K15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="M15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="N15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="O15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="P15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="Q15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="R15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="S15" s="37" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="T15" s="45">
         <f>SUM(H15:S15)</f>
@@ -9061,7 +9147,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>TI-D10</t>
+          <t>TI-D08</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
@@ -9076,14 +9162,10 @@
       </c>
       <c r="D16" s="36" t="inlineStr">
         <is>
-          <t>Claude</t>
-        </is>
-      </c>
-      <c r="E16" s="36" t="inlineStr">
-        <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas</t>
-        </is>
-      </c>
+          <t>Aplicativo de Gravação de Reunião</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr"/>
       <c r="F16" s="35" t="inlineStr"/>
       <c r="G16" s="35" t="inlineStr">
         <is>
@@ -9091,40 +9173,40 @@
         </is>
       </c>
       <c r="H16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="I16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="J16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="K16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="M16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="N16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="O16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="P16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="Q16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="R16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="S16" s="37" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="T16" s="45">
         <f>SUM(H16:S16)</f>
@@ -9134,7 +9216,7 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>TI-D11</t>
+          <t>TI-D10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
@@ -9149,7 +9231,7 @@
       </c>
       <c r="D17" s="36" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="E17" s="36" t="inlineStr">
@@ -9207,7 +9289,7 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>TI-D12</t>
+          <t>TI-D11</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
@@ -9222,12 +9304,12 @@
       </c>
       <c r="D18" s="36" t="inlineStr">
         <is>
-          <t>Adapta One</t>
+          <t>GPT</t>
         </is>
       </c>
       <c r="E18" s="36" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas</t>
         </is>
       </c>
       <c r="F18" s="35" t="inlineStr"/>
@@ -9280,7 +9362,7 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>TI-D13</t>
+          <t>TI-D12</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
@@ -9295,12 +9377,12 @@
       </c>
       <c r="D19" s="36" t="inlineStr">
         <is>
-          <t>Adapta Skip</t>
+          <t>Adapta One</t>
         </is>
       </c>
       <c r="E19" s="36" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr"/>
@@ -9353,7 +9435,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>TI-D14</t>
+          <t>TI-D13</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
@@ -9368,12 +9450,12 @@
       </c>
       <c r="D20" s="36" t="inlineStr">
         <is>
-          <t>AnyDesk</t>
+          <t>Adapta Skip</t>
         </is>
       </c>
       <c r="E20" s="36" t="inlineStr">
         <is>
-          <t>Licença de acesso remoto — contratação prevista, não constava na ficha. Valor e mês de início a definir. CONFERIR sobreposição com o serviço de monitoramento remoto já contratado (J H Alves)</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F20" s="35" t="inlineStr"/>
@@ -9426,7 +9508,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>TI-D09</t>
+          <t>TI-D14</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
@@ -9441,18 +9523,18 @@
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
-          <t>Bonificação do time</t>
+          <t>AnyDesk</t>
         </is>
       </c>
       <c r="E21" s="36" t="inlineStr">
         <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+          <t>Licença de acesso remoto — contratação prevista, não constava na ficha. Valor e mês de início a definir. CONFERIR sobreposição com o serviço de monitoramento remoto já contratado (J H Alves)</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr"/>
       <c r="G21" s="35" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H21" s="37" t="n">
@@ -9477,7 +9559,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="37" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P21" s="37" t="n">
         <v>0</v>
@@ -9489,80 +9571,153 @@
         <v>0</v>
       </c>
       <c r="S21" s="37" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="T21" s="45">
         <f>SUM(H21:S21)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="42" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>TI-D09</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
+        <is>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr"/>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="37" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="37" t="n">
+        <v>3600</v>
+      </c>
+      <c r="T22" s="45">
+        <f>SUM(H22:S22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B22" s="42" t="n"/>
-      <c r="C22" s="42" t="n"/>
-      <c r="D22" s="42" t="n"/>
-      <c r="E22" s="42" t="n"/>
-      <c r="F22" s="42" t="n"/>
-      <c r="G22" s="42" t="n"/>
-      <c r="H22" s="43">
-        <f>SUM(H5:H21)</f>
-        <v/>
-      </c>
-      <c r="I22" s="43">
-        <f>SUM(I5:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="43">
-        <f>SUM(J5:J21)</f>
-        <v/>
-      </c>
-      <c r="K22" s="43">
-        <f>SUM(K5:K21)</f>
-        <v/>
-      </c>
-      <c r="L22" s="43">
-        <f>SUM(L5:L21)</f>
-        <v/>
-      </c>
-      <c r="M22" s="43">
-        <f>SUM(M5:M21)</f>
-        <v/>
-      </c>
-      <c r="N22" s="43">
-        <f>SUM(N5:N21)</f>
-        <v/>
-      </c>
-      <c r="O22" s="43">
-        <f>SUM(O5:O21)</f>
-        <v/>
-      </c>
-      <c r="P22" s="43">
-        <f>SUM(P5:P21)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="43">
-        <f>SUM(Q5:Q21)</f>
-        <v/>
-      </c>
-      <c r="R22" s="43">
-        <f>SUM(R5:R21)</f>
-        <v/>
-      </c>
-      <c r="S22" s="43">
-        <f>SUM(S5:S21)</f>
-        <v/>
-      </c>
-      <c r="T22" s="43">
-        <f>SUM(T5:T21)</f>
+      <c r="B23" s="42" t="n"/>
+      <c r="C23" s="42" t="n"/>
+      <c r="D23" s="42" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="42" t="n"/>
+      <c r="H23" s="43">
+        <f>SUM(H5:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="43">
+        <f>SUM(I5:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="43">
+        <f>SUM(J5:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="43">
+        <f>SUM(K5:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="43">
+        <f>SUM(L5:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="43">
+        <f>SUM(M5:M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="43">
+        <f>SUM(N5:N22)</f>
+        <v/>
+      </c>
+      <c r="O23" s="43">
+        <f>SUM(O5:O22)</f>
+        <v/>
+      </c>
+      <c r="P23" s="43">
+        <f>SUM(P5:P22)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="43">
+        <f>SUM(Q5:Q22)</f>
+        <v/>
+      </c>
+      <c r="R23" s="43">
+        <f>SUM(R5:R22)</f>
+        <v/>
+      </c>
+      <c r="S23" s="43">
+        <f>SUM(S5:S22)</f>
+        <v/>
+      </c>
+      <c r="T23" s="43">
+        <f>SUM(T5:T22)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T21"/>
+  <autoFilter ref="A4:T22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -9577,7 +9732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9882,7 +10037,7 @@
         <v/>
       </c>
       <c r="H7" s="49" t="n">
-        <v>4311.56</v>
+        <v>0</v>
       </c>
       <c r="I7" s="49" t="n">
         <v>0</v>
@@ -9918,7 +10073,7 @@
       </c>
       <c r="V7" s="50" t="inlineStr">
         <is>
-          <t>Credor 'J H ALVES - MONITOR REMOTO'. Pagamentos: 19/01 NFS.70 R$ 4.311,56; 01/05 NFS.76 R$ 3.723,62; 01/06 NFS.78 R$ 6.173,37; 01/07 NFS.3 R$ 6.300,00. Sem pagamento em fev, mar e abr</t>
+          <t>01/05 NFS.76 R$ 3.723,62; 01/06 NFS.78 R$ 6.173,37; 01/07 NFS.3 R$ 6.300,00. Sem pagamento em jan–abr: contratação segurada</t>
         </is>
       </c>
     </row>
@@ -9951,24 +10106,56 @@
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="49" t="n"/>
-      <c r="I8" s="49" t="n"/>
-      <c r="J8" s="49" t="n"/>
-      <c r="K8" s="49" t="n"/>
-      <c r="L8" s="49" t="n"/>
-      <c r="M8" s="49" t="n"/>
-      <c r="N8" s="49" t="n"/>
-      <c r="O8" s="49" t="n"/>
-      <c r="P8" s="49" t="n"/>
-      <c r="Q8" s="49" t="n"/>
-      <c r="R8" s="49" t="n"/>
-      <c r="S8" s="49" t="n"/>
+      <c r="H8" s="49" t="n">
+        <v>4311.56</v>
+      </c>
+      <c r="I8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="T8" s="45">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
-      <c r="U8" s="50" t="n"/>
-      <c r="V8" s="50" t="n"/>
+      <c r="U8" s="50" t="inlineStr">
+        <is>
+          <t>Extrato do financeiro</t>
+        </is>
+      </c>
+      <c r="V8" s="50" t="inlineStr">
+        <is>
+          <t>19/01 NFS.70 R$ 4.311,56 — serviço esporádico, provavelmente referente a dez/25. Vínculo encerrado com a entrada como consultor fixo</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="47">
@@ -10594,72 +10781,120 @@
       <c r="U21" s="50" t="n"/>
       <c r="V21" s="50" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="47">
+        <f>Planejado!A22</f>
+        <v/>
+      </c>
+      <c r="B22" s="47">
+        <f>Planejado!B22</f>
+        <v/>
+      </c>
+      <c r="C22" s="47">
+        <f>Planejado!C22</f>
+        <v/>
+      </c>
+      <c r="D22" s="48">
+        <f>Planejado!D22</f>
+        <v/>
+      </c>
+      <c r="E22" s="48">
+        <f>Planejado!E22</f>
+        <v/>
+      </c>
+      <c r="F22" s="47">
+        <f>Planejado!F22</f>
+        <v/>
+      </c>
+      <c r="G22" s="47">
+        <f>Planejado!G22</f>
+        <v/>
+      </c>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="49" t="n"/>
+      <c r="K22" s="49" t="n"/>
+      <c r="L22" s="49" t="n"/>
+      <c r="M22" s="49" t="n"/>
+      <c r="N22" s="49" t="n"/>
+      <c r="O22" s="49" t="n"/>
+      <c r="P22" s="49" t="n"/>
+      <c r="Q22" s="49" t="n"/>
+      <c r="R22" s="49" t="n"/>
+      <c r="S22" s="49" t="n"/>
+      <c r="T22" s="45">
+        <f>SUM(H22:S22)</f>
+        <v/>
+      </c>
+      <c r="U22" s="50" t="n"/>
+      <c r="V22" s="50" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B22" s="51" t="n"/>
-      <c r="C22" s="51" t="n"/>
-      <c r="D22" s="51" t="n"/>
-      <c r="E22" s="51" t="n"/>
-      <c r="F22" s="51" t="n"/>
-      <c r="G22" s="51" t="n"/>
-      <c r="H22" s="52">
-        <f>SUM(H5:H21)</f>
-        <v/>
-      </c>
-      <c r="I22" s="52">
-        <f>SUM(I5:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="52">
-        <f>SUM(J5:J21)</f>
-        <v/>
-      </c>
-      <c r="K22" s="52">
-        <f>SUM(K5:K21)</f>
-        <v/>
-      </c>
-      <c r="L22" s="52">
-        <f>SUM(L5:L21)</f>
-        <v/>
-      </c>
-      <c r="M22" s="52">
-        <f>SUM(M5:M21)</f>
-        <v/>
-      </c>
-      <c r="N22" s="52">
-        <f>SUM(N5:N21)</f>
-        <v/>
-      </c>
-      <c r="O22" s="52">
-        <f>SUM(O5:O21)</f>
-        <v/>
-      </c>
-      <c r="P22" s="52">
-        <f>SUM(P5:P21)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="52">
-        <f>SUM(Q5:Q21)</f>
-        <v/>
-      </c>
-      <c r="R22" s="52">
-        <f>SUM(R5:R21)</f>
-        <v/>
-      </c>
-      <c r="S22" s="52">
-        <f>SUM(S5:S21)</f>
-        <v/>
-      </c>
-      <c r="T22" s="52">
-        <f>SUM(T5:T21)</f>
-        <v/>
-      </c>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="51" t="n"/>
+      <c r="B23" s="51" t="n"/>
+      <c r="C23" s="51" t="n"/>
+      <c r="D23" s="51" t="n"/>
+      <c r="E23" s="51" t="n"/>
+      <c r="F23" s="51" t="n"/>
+      <c r="G23" s="51" t="n"/>
+      <c r="H23" s="52">
+        <f>SUM(H5:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="52">
+        <f>SUM(I5:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="52">
+        <f>SUM(J5:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="52">
+        <f>SUM(K5:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="52">
+        <f>SUM(L5:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="52">
+        <f>SUM(M5:M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="52">
+        <f>SUM(N5:N22)</f>
+        <v/>
+      </c>
+      <c r="O23" s="52">
+        <f>SUM(O5:O22)</f>
+        <v/>
+      </c>
+      <c r="P23" s="52">
+        <f>SUM(P5:P22)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="52">
+        <f>SUM(Q5:Q22)</f>
+        <v/>
+      </c>
+      <c r="R23" s="52">
+        <f>SUM(R5:R22)</f>
+        <v/>
+      </c>
+      <c r="S23" s="52">
+        <f>SUM(S5:S22)</f>
+        <v/>
+      </c>
+      <c r="T23" s="52">
+        <f>SUM(T5:T22)</f>
+        <v/>
+      </c>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10752,11 +10987,11 @@
         </is>
       </c>
       <c r="B5" s="54">
-        <f>SUMIFS(Planejado!$H$5:$H$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C5" s="54">
-        <f>SUMIFS(Realizado!$H$5:$H$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D5" s="54">
@@ -10787,11 +11022,11 @@
         </is>
       </c>
       <c r="B6" s="37">
-        <f>SUMIFS(Planejado!$I$5:$I$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C6" s="37">
-        <f>SUMIFS(Realizado!$I$5:$I$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D6" s="37">
@@ -10822,11 +11057,11 @@
         </is>
       </c>
       <c r="B7" s="54">
-        <f>SUMIFS(Planejado!$J$5:$J$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C7" s="54">
-        <f>SUMIFS(Realizado!$J$5:$J$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D7" s="54">
@@ -10857,11 +11092,11 @@
         </is>
       </c>
       <c r="B8" s="37">
-        <f>SUMIFS(Planejado!$K$5:$K$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C8" s="37">
-        <f>SUMIFS(Realizado!$K$5:$K$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="37">
@@ -10892,11 +11127,11 @@
         </is>
       </c>
       <c r="B9" s="54">
-        <f>SUMIFS(Planejado!$L$5:$L$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C9" s="54">
-        <f>SUMIFS(Realizado!$L$5:$L$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D9" s="54">
@@ -10927,11 +11162,11 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>SUMIFS(Planejado!$M$5:$M$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C10" s="37">
-        <f>SUMIFS(Realizado!$M$5:$M$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D10" s="37">
@@ -10962,11 +11197,11 @@
         </is>
       </c>
       <c r="B11" s="54">
-        <f>SUMIFS(Planejado!$N$5:$N$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C11" s="54">
-        <f>SUMIFS(Realizado!$N$5:$N$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="54">
@@ -10997,11 +11232,11 @@
         </is>
       </c>
       <c r="B12" s="37">
-        <f>SUMIFS(Planejado!$O$5:$O$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C12" s="37">
-        <f>SUMIFS(Realizado!$O$5:$O$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D12" s="37">
@@ -11032,11 +11267,11 @@
         </is>
       </c>
       <c r="B13" s="54">
-        <f>SUMIFS(Planejado!$P$5:$P$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C13" s="54">
-        <f>SUMIFS(Realizado!$P$5:$P$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D13" s="54">
@@ -11067,11 +11302,11 @@
         </is>
       </c>
       <c r="B14" s="37">
-        <f>SUMIFS(Planejado!$Q$5:$Q$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C14" s="37">
-        <f>SUMIFS(Realizado!$Q$5:$Q$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D14" s="37">
@@ -11102,11 +11337,11 @@
         </is>
       </c>
       <c r="B15" s="54">
-        <f>SUMIFS(Planejado!$R$5:$R$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C15" s="54">
-        <f>SUMIFS(Realizado!$R$5:$R$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D15" s="54">
@@ -11137,11 +11372,11 @@
         </is>
       </c>
       <c r="B16" s="37">
-        <f>SUMIFS(Planejado!$S$5:$S$21,Planejado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$22,Planejado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="C16" s="37">
-        <f>SUMIFS(Realizado!$S$5:$S$21,Realizado!$B$5:$B$21,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$22,Realizado!$B$5:$B$22,"TI")</f>
         <v/>
       </c>
       <c r="D16" s="37">
@@ -11294,11 +11529,11 @@
         </is>
       </c>
       <c r="B5" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A5,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$E$6:$E$23,$A5,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="C5" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A5,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$E$6:$E$23,$A5,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="D5" s="54">
@@ -11318,7 +11553,7 @@
         <v/>
       </c>
       <c r="H5" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$G$5:$G$22,$A5)</f>
         <v/>
       </c>
     </row>
@@ -11329,11 +11564,11 @@
         </is>
       </c>
       <c r="B6" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A6,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$E$6:$E$23,$A6,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="C6" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A6,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$E$6:$E$23,$A6,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="D6" s="37">
@@ -11353,7 +11588,7 @@
         <v/>
       </c>
       <c r="H6" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$G$5:$G$22,$A6)</f>
         <v/>
       </c>
     </row>
@@ -11364,11 +11599,11 @@
         </is>
       </c>
       <c r="B7" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A7,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$E$6:$E$23,$A7,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="C7" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A7,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$E$6:$E$23,$A7,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="D7" s="54">
@@ -11388,7 +11623,7 @@
         <v/>
       </c>
       <c r="H7" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$G$5:$G$22,$A7)</f>
         <v/>
       </c>
     </row>
@@ -11399,11 +11634,11 @@
         </is>
       </c>
       <c r="B8" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A8,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$E$6:$E$23,$A8,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="C8" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A8,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$E$6:$E$23,$A8,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="D8" s="37">
@@ -11423,7 +11658,7 @@
         <v/>
       </c>
       <c r="H8" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$G$5:$G$22,$A8)</f>
         <v/>
       </c>
     </row>
@@ -11434,11 +11669,11 @@
         </is>
       </c>
       <c r="B9" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A9,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$E$6:$E$23,$A9,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="C9" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A9,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$E$6:$E$23,$A9,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="D9" s="54">
@@ -11458,7 +11693,7 @@
         <v/>
       </c>
       <c r="H9" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$G$5:$G$22,$A9)</f>
         <v/>
       </c>
     </row>
@@ -11469,11 +11704,11 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A10,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$E$6:$E$23,$A10,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="C10" s="37">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A10,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$E$6:$E$23,$A10,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="D10" s="37">
@@ -11493,7 +11728,7 @@
         <v/>
       </c>
       <c r="H10" s="37">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$G$5:$G$22,$A10)</f>
         <v/>
       </c>
     </row>
@@ -11504,11 +11739,11 @@
         </is>
       </c>
       <c r="B11" s="54">
-        <f>SUMIFS(Comparativo!$I$6:$I$22,Comparativo!$E$6:$E$22,$A11,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$23,Comparativo!$E$6:$E$23,$A11,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="C11" s="54">
-        <f>SUMIFS(Comparativo!$J$6:$J$22,Comparativo!$E$6:$E$22,$A11,Comparativo!$B$6:$B$22,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$23,Comparativo!$E$6:$E$23,$A11,Comparativo!$B$6:$B$23,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="54">
@@ -11528,7 +11763,7 @@
         <v/>
       </c>
       <c r="H11" s="54">
-        <f>SUMIFS(Planejado!$T$5:$T$21,Planejado!$G$5:$G$21,$A11)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$22,Planejado!$G$5:$G$22,$A11)</f>
         <v/>
       </c>
     </row>
@@ -11590,7 +11825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11687,17 +11922,17 @@
       </c>
       <c r="B6" s="65" t="inlineStr">
         <is>
-          <t>Jonathan — economia de R$ 49.491 até julho</t>
+          <t>Jonathan — economia de R$ 53.803 até julho</t>
         </is>
       </c>
       <c r="C6" s="65" t="inlineStr">
         <is>
-          <t>Orçado R$ 10.000/mês desde jan/26. A contratação foi segurada e o serviço só começou depois, chegando a R$ 6.300/mês. Realizado pelo extrato, no credor 'J H ALVES — MONITOR REMOTO': R$ 4.311,56 em jan, nada em fev, mar e abr, e R$ 3.723,62, R$ 6.173,37 e R$ 6.300,00 em mai, jun e jul. Total de R$ 20.508,55 contra R$ 70.000 orçados.</t>
+          <t>Orçado R$ 10.000/mês desde jan/26, com a contratação segurada até abr/26, quando ele passou a atuar como consultor fixo, 3 dias por semana. Realizado de R$ 16.196,99 em jan–jul (pagamentos de mai, jun e jul) contra R$ 70.000 orçados. O vínculo anterior, de serviços esporádicos prestados de fora, foi separado na linha TI-E04.</t>
         </is>
       </c>
       <c r="D6" s="65" t="inlineStr">
         <is>
-          <t>É de longe a maior economia das duas áreas: R$ 49.491,45 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Vale destacar na apresentação. DOIS PONTOS A ESCLARECER: (1) o pagamento de R$ 4.311,56 em 19/01 é anterior ao início das atividades — provavelmente serviço de dez/2025 recebido no mês seguinte, confirmar; (2) mai e jun saíram abaixo de R$ 6.300 (R$ 3.723,62 e R$ 6.173,37), verificar se foi proporcional por dias trabalhados.</t>
+          <t>É de longe a maior economia das duas áreas: R$ 53.803,01 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Vale destacar na apresentação. A CONFERIR: mai e jun saíram abaixo de R$ 6.300 (R$ 3.723,62 e R$ 6.173,37) — verificar se foi proporcional aos dias trabalhados no início do contrato.</t>
         </is>
       </c>
       <c r="E6" s="65" t="inlineStr">
@@ -11714,22 +11949,22 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="61" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B7" s="62" t="inlineStr">
         <is>
-          <t>Elias Benedito — sem custo até jul, renegociado para set</t>
+          <t>Serviços esporádicos do Monitor Remoto — fora do orçamento</t>
         </is>
       </c>
       <c r="C7" s="62" t="inlineStr">
         <is>
-          <t>Orçado R$ 1.065/mês, realizado R$ 0 de jan a jul — contrato ativo, mas sem acionamento no período (confirmado pela gestora). O pagamento passa a ocorrer agora, e a partir de set/26 o valor foi renegociado de R$ 1.065 para R$ 603,30.</t>
+          <t>Antes de entrar como consultor fixo, o mesmo prestador atendia de fora, em serviços esporádicos. Consta um pagamento de R$ 4.311,56 em 19/01/26 (NFS.70), provavelmente referente a dez/25 pelo regime de caixa. Esse vínculo não estava na ficha de orçamento e foi encerrado em abr/26.</t>
         </is>
       </c>
       <c r="D7" s="62" t="inlineStr">
         <is>
-          <t>Duas economias na mesma linha: R$ 7.455 pelos sete meses sem acionamento, e R$ 461,70/mês (43%) a partir de set pela renegociação — R$ 1.846,80 no ano. O planejado já reflete o valor novo de set a dez.</t>
+          <t>Linha TI-E04 criada com planejado zero, então o valor aparece como 'Não orçado'. Como o vínculo acabou, não haverá novos lançamentos — a linha existe para o histórico não se misturar com a consultoria fixa. Confirmar se houve pagamento esporádico em fev e mar que não caiu no centro de custo do TI.</t>
         </is>
       </c>
       <c r="E7" s="62" t="inlineStr">
@@ -11737,31 +11972,31 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="67" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F7" s="66" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="64" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B8" s="65" t="inlineStr">
         <is>
-          <t>Planejado de jan a abr — conferido</t>
+          <t>Elias Benedito — sem custo até jul, renegociado para set</t>
         </is>
       </c>
       <c r="C8" s="65" t="inlineStr">
         <is>
-          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
+          <t>Orçado R$ 1.065/mês, realizado R$ 0 de jan a jul — contrato ativo, mas sem acionamento no período (confirmado pela gestora). O pagamento passa a ocorrer agora, e a partir de set/26 o valor foi renegociado de R$ 1.065 para R$ 603,30.</t>
         </is>
       </c>
       <c r="D8" s="65" t="inlineStr">
         <is>
-          <t>Conferido e validado pela gestora: os valores replicados estão corretos, nenhum ajuste necessário.</t>
+          <t>Duas economias na mesma linha: R$ 7.455 pelos sete meses sem acionamento, e R$ 461,70/mês (43%) a partir de set pela renegociação — R$ 1.846,80 no ano. O planejado já reflete o valor novo de set a dez.</t>
         </is>
       </c>
       <c r="E8" s="65" t="inlineStr">
@@ -11771,29 +12006,29 @@
       </c>
       <c r="F8" s="67" t="inlineStr">
         <is>
-          <t>APLICADO</t>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="61" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B9" s="62" t="inlineStr">
         <is>
-          <t>Realizado de ago a dez — a lançar no decorrer do ano</t>
+          <t>Planejado de jan a abr — conferido</t>
         </is>
       </c>
       <c r="C9" s="62" t="inlineStr">
         <is>
-          <t>Jan a jul estão lançados. Ago a dez ficam em branco e serão preenchidos conforme os meses fecharem, com a extração do SIENGE.</t>
+          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
         </is>
       </c>
       <c r="D9" s="62" t="inlineStr">
         <is>
-          <t>Enquanto isso, o mês de referência do Comparativo deve ficar no último mês fechado (hoje Jul/26) — assim o acumulado compara períodos iguais dos dois lados.</t>
+          <t>Conferido e validado pela gestora: os valores replicados estão corretos, nenhum ajuste necessário.</t>
         </is>
       </c>
       <c r="E9" s="62" t="inlineStr">
@@ -11810,86 +12045,86 @@
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B10" s="65" t="inlineStr">
         <is>
-          <t>Despesas fora do orçamento identificadas no extrato</t>
+          <t>Realizado de ago a dez — a lançar no decorrer do ano</t>
         </is>
       </c>
       <c r="C10" s="65" t="inlineStr">
         <is>
-          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama). O 'J H Alves — Monitor Remoto' NÃO entra nesta lista: é o Jonathan, que já tem linha no orçamento (TI-E03).</t>
+          <t>Jan a jul estão lançados. Ago a dez ficam em branco e serão preenchidos conforme os meses fecharem, com a extração do SIENGE.</t>
         </is>
       </c>
       <c r="D10" s="65" t="inlineStr">
         <is>
-          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. ATENÇÃO: parte desses valores pode ser repasse ou custa reembolsável pelo cliente, e não custo da área — foi o caso da Dra. Michele (ver item P). Separar o que é custo antes de decidir. Para os que entrarem no centro de custo, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
+          <t>Enquanto isso, o mês de referência do Comparativo deve ficar no último mês fechado (hoje Jul/26) — assim o acumulado compara períodos iguais dos dois lados.</t>
         </is>
       </c>
       <c r="E10" s="65" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F10" s="68" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F10" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="61" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B11" s="62" t="inlineStr">
         <is>
-          <t>Despesas do TI — A LANÇAR</t>
+          <t>Despesas fora do orçamento identificadas no extrato</t>
         </is>
       </c>
       <c r="C11" s="62" t="inlineStr">
         <is>
-          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
+          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama). O 'J H Alves — Monitor Remoto' NÃO entra nesta lista: é o Jonathan, que já tem linha no orçamento (TI-E03).</t>
         </is>
       </c>
       <c r="D11" s="62" t="inlineStr">
         <is>
-          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
+          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. ATENÇÃO: parte desses valores pode ser repasse ou custa reembolsável pelo cliente, e não custo da área — foi o caso da Dra. Michele (ver item P). Separar o que é custo antes de decidir. Para os que entrarem no centro de custo, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
         </is>
       </c>
       <c r="E11" s="62" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F11" s="63" t="inlineStr">
-        <is>
-          <t>A LANÇAR</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F11" s="68" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B12" s="65" t="inlineStr">
         <is>
-          <t>Base de meses do TI — Jonathan corrigido para 12 meses</t>
+          <t>Despesas do TI — A LANÇAR</t>
         </is>
       </c>
       <c r="C12" s="65" t="inlineStr">
         <is>
-          <t>A ficha trazia os totais do TI digitados à mão: Vinicius e Elias em 12 meses (R$ 64.998,30 e R$ 12.780,00, ambos confirmados) e Jonathan em 9 meses (R$ 90.000). A gestora confirmou que o orçamento dele valia desde jan/26, ou seja, 12 meses — os R$ 90.000 da ficha não refletiam o orçamento aprovado.</t>
+          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
         </is>
       </c>
       <c r="D12" s="65" t="inlineStr">
         <is>
-          <t>Equipe de TI passa de R$ 167.778,30 para R$ 197.778,30 (+R$ 30.000). Os R$ 167.778,30 da ficha continuam batendo com Vinicius e Elias, mas a linha do Jonathan estava subdimensionada em 3 meses.</t>
+          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
         </is>
       </c>
       <c r="E12" s="65" t="inlineStr">
@@ -11897,36 +12132,36 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="67" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F12" s="63" t="inlineStr">
+        <is>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" s="62" t="inlineStr">
         <is>
-          <t>Origem do valor realizado — DEFINIDA: SIENGE</t>
+          <t>Base de meses do TI — Jonathan corrigido para 12 meses</t>
         </is>
       </c>
       <c r="C13" s="62" t="inlineStr">
         <is>
-          <t>Será aberto um centro de custo próprio no SIENGE e todos os valores do realizado serão extraídos de lá. Nada será lançado manualmente. O extrato das abas 'Contas Pagas' já vem nesse formato.</t>
+          <t>A ficha trazia os totais do TI digitados à mão: Vinicius e Elias em 12 meses (R$ 64.998,30 e R$ 12.780,00, ambos confirmados) e Jonathan em 9 meses (R$ 90.000). A gestora confirmou que o orçamento dele valia desde jan/26, ou seja, 12 meses — os R$ 90.000 da ficha não refletiam o orçamento aprovado.</t>
         </is>
       </c>
       <c r="D13" s="62" t="inlineStr">
         <is>
-          <t>O realizado passa a bater com a contabilidade por construção, que era o risco principal. Duas coisas a encaminhar: (1) o de-para entre credor do SIENGE e linha do orçamento — a coluna 'Já está no orçamento?' da aba de resumo é o rascunho dele; (2) definir se a extração sai por regime de caixa ou de competência, ver item 7.</t>
+          <t>Equipe de TI passa de R$ 167.778,30 para R$ 197.778,30 (+R$ 30.000). Os R$ 167.778,30 da ficha continuam batendo com Vinicius e Elias, mas a linha do Jonathan estava subdimensionada em 3 meses.</t>
         </is>
       </c>
       <c r="E13" s="62" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F13" s="67" t="inlineStr">
@@ -11938,22 +12173,22 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="64" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B14" s="65" t="inlineStr">
         <is>
-          <t>Adapta lançado no centro de custo errado — RECLASSIFICAR</t>
+          <t>Origem do valor realizado — DEFINIDA: SIENGE</t>
         </is>
       </c>
       <c r="C14" s="65" t="inlineStr">
         <is>
-          <t>Os pagamentos do Adapta (ADAPTA EDUCACAO LTDA, contrato 4134643529) estão no centro de custo Jurídico no SIENGE: R$ 575,00/mês de jan a mai e R$ 476,00 em jun, todos com vencimento dia 15. Total de R$ 3.351,00 em seis meses. Não é despesa do Jurídico — é ferramenta de IA, de uso transversal.</t>
+          <t>Será aberto um centro de custo próprio no SIENGE e todos os valores do realizado serão extraídos de lá. Nada será lançado manualmente. O extrato das abas 'Contas Pagas' já vem nesse formato.</t>
         </is>
       </c>
       <c r="D14" s="65" t="inlineStr">
         <is>
-          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
+          <t>O realizado passa a bater com a contabilidade por construção, que era o risco principal. Duas coisas a encaminhar: (1) o de-para entre credor do SIENGE e linha do orçamento — a coluna 'Já está no orçamento?' da aba de resumo é o rascunho dele; (2) definir se a extração sai por regime de caixa ou de competência, ver item 7.</t>
         </is>
       </c>
       <c r="E14" s="65" t="inlineStr">
@@ -11961,127 +12196,127 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F14" s="63" t="inlineStr">
-        <is>
-          <t>RECLASSIFICAR</t>
+      <c r="F14" s="67" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="61" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B15" s="62" t="inlineStr">
         <is>
-          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
+          <t>Adapta lançado no centro de custo errado — RECLASSIFICAR</t>
         </is>
       </c>
       <c r="C15" s="62" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
+          <t>Os pagamentos do Adapta (ADAPTA EDUCACAO LTDA, contrato 4134643529) estão no centro de custo Jurídico no SIENGE: R$ 575,00/mês de jan a mai e R$ 476,00 em jun, todos com vencimento dia 15. Total de R$ 3.351,00 em seis meses. Não é despesa do Jurídico — é ferramenta de IA, de uso transversal.</t>
         </is>
       </c>
       <c r="D15" s="62" t="inlineStr">
         <is>
-          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
+          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
         </is>
       </c>
       <c r="E15" s="62" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F15" s="68" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F15" s="63" t="inlineStr">
+        <is>
+          <t>RECLASSIFICAR</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B16" s="65" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos e das IAs</t>
+          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
         </is>
       </c>
       <c r="C16" s="65" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
         </is>
       </c>
       <c r="D16" s="65" t="inlineStr">
         <is>
-          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
+          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E16" s="65" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F16" s="69" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F16" s="68" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" s="62" t="inlineStr">
         <is>
-          <t>Sala de Reunião — EXECUTAR, PAUSAR OU REPENSAR?</t>
+          <t>Rateio dos softwares corporativos e das IAs</t>
         </is>
       </c>
       <c r="C17" s="62" t="inlineStr">
         <is>
-          <t>Projeto orçado em R$ 2.800/mês × 12 = R$ 33.600, classificado em Móveis e Utensílios, sem nenhum lançamento até jul/26. A gestora levanta que a sala já não comporta todas as pessoas, então investir na configuração atual pode não resolver o problema real. Três caminhos: executar como está, pausar, ou repensar a solução (outro espaço, formato híbrido, mais de uma sala).</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
         </is>
       </c>
       <c r="D17" s="62" t="inlineStr">
         <is>
-          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. SEPARAR OS ITENS: a descrição na ficha mistura infraestrutura de reunião (câmeras, microfones, cadeiras) com material de consumo e brindes (canetas, blocos personalizados, copos, cafeteira). O segundo grupo é papelaria e deveria estar no Administrativo, não no TI (item U).</t>
+          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
         </is>
       </c>
       <c r="E17" s="62" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F17" s="68" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Controladoria</t>
+        </is>
+      </c>
+      <c r="F17" s="69" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="64" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" s="65" t="inlineStr">
         <is>
-          <t>Notebooks — TI compra, mas não enxerga o saldo das áreas</t>
+          <t>Sala de Reunião — EXECUTAR, PAUSAR OU REPENSAR?</t>
         </is>
       </c>
       <c r="C18" s="65" t="inlineStr">
         <is>
-          <t>Cada área tem a própria linha de orçamento para notebooks, mas é o TI que recebe a solicitação e executa a compra quando surge a necessidade. Hoje o TI não tem acompanhamento do orçamento das outras áreas, então aprova pedidos sem saber quanto resta em cada uma.</t>
+          <t>Projeto orçado em R$ 2.800/mês × 12 = R$ 33.600, classificado em Móveis e Utensílios, sem nenhum lançamento até jul/26. A gestora levanta que a sala já não comporta todas as pessoas, então investir na configuração atual pode não resolver o problema real. Três caminhos: executar como está, pausar, ou repensar a solução (outro espaço, formato híbrido, mais de uma sala).</t>
         </is>
       </c>
       <c r="D18" s="65" t="inlineStr">
         <is>
-          <t>O TI vira o executor de um estouro que não é dele e que ninguém percebe antes de acontecer — a área descobre no fechamento, quando já comprou. Proposta: o TI passa a acompanhar o saldo da rubrica de notebooks de cada área e avisa quando a solicitação for levar ao estouro, antes de comprar. Com o centro de custo no SIENGE, esse acompanhamento sai do mesmo relatório. Definir com a diretoria quem dá o aval quando o saldo acabar: a área solicitante, o TI ou a controladoria.</t>
+          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. SEPARAR OS ITENS: a descrição na ficha mistura infraestrutura de reunião (câmeras, microfones, cadeiras) com material de consumo e brindes (canetas, blocos personalizados, copos, cafeteira). O segundo grupo é papelaria e deveria estar no Administrativo, não no TI (item U).</t>
         </is>
       </c>
       <c r="E18" s="65" t="inlineStr">
@@ -12098,54 +12333,54 @@
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="61" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B19" s="62" t="inlineStr">
         <is>
-          <t>Rubricas genéricas — detalhar no lançamento, não no orçamento</t>
+          <t>Notebooks — TI compra, mas não enxerga o saldo das áreas</t>
         </is>
       </c>
       <c r="C19" s="62" t="inlineStr">
         <is>
-          <t>Rubricas como 'Peças de Manutenção' (R$ 9.720/ano) agrupam itens de naturezas diferentes: mouse, teclado, carregador, tela, carcaça. Sem detalhe, não dá para saber o que puxa o gasto. A alternativa de criar uma linha por item foi avaliada e descartada por ora.</t>
+          <t>Cada área tem a própria linha de orçamento para notebooks, mas é o TI que recebe a solicitação e executa a compra quando surge a necessidade. Hoje o TI não tem acompanhamento do orçamento das outras áreas, então aprova pedidos sem saber quanto resta em cada uma.</t>
         </is>
       </c>
       <c r="D19" s="62" t="inlineStr">
         <is>
-          <t>DECIDIDO: manter uma linha de orçamento e detalhar na DESCRIÇÃO do lançamento no SIENGE, com padrão fixo ('Peças – mouse', 'Peças – tela'). Motivos: (1) não há histórico — as despesas do TI ainda não têm lançamento, então orçar item a item seria estimativa sem base, e cada linha acusaria desvio pela divisão errada, não pelo gasto; (2) cinco linhas viram cinco lançamentos mensais para uma rubrica que é 11% das despesas da área; (3) o plano de contas é definido pela controladoria, então subitens no orçamento não mudariam a classificação contábil. Em jan/27, com seis meses de dados reais, reavaliar. Se separar, separar por NATUREZA (reposição x reparo), que é o que dá leitura gerencial, e não item a item. Mesmo critério vale para 'Equipamentos Eletrônicos Diversos' e demais rubricas genéricas.</t>
+          <t>O TI vira o executor de um estouro que não é dele e que ninguém percebe antes de acontecer — a área descobre no fechamento, quando já comprou. Proposta: o TI passa a acompanhar o saldo da rubrica de notebooks de cada área e avisa quando a solicitação for levar ao estouro, antes de comprar. Com o centro de custo no SIENGE, esse acompanhamento sai do mesmo relatório. Definir com a diretoria quem dá o aval quando o saldo acabar: a área solicitante, o TI ou a controladoria.</t>
         </is>
       </c>
       <c r="E19" s="62" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F19" s="67" t="inlineStr">
-        <is>
-          <t>APLICADO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F19" s="68" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="64" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B20" s="65" t="inlineStr">
         <is>
-          <t>Política de troca 1x1 e empréstimo — IMPLANTAR</t>
+          <t>Rubricas genéricas — detalhar no lançamento, não no orçamento</t>
         </is>
       </c>
       <c r="C20" s="65" t="inlineStr">
         <is>
-          <t>Hoje não existe regra: o pedido chega e a compra é feita. A proposta é que para receber um item novo a pessoa entregue o que quebrou (troca 1x1), e que exista um equipamento reserva para empréstimo imediato, para ninguém ficar parado esperando. O reserva é COM FIO de propósito: mais barato e menos confortável que o definitivo, o que cria o incentivo natural para devolver e fechar a troca. A aba 'Controle de Equipamentos' já está pronta para o registro.</t>
+          <t>Rubricas como 'Peças de Manutenção' (R$ 9.720/ano) agrupam itens de naturezas diferentes: mouse, teclado, carregador, tela, carcaça. Sem detalhe, não dá para saber o que puxa o gasto. A alternativa de criar uma linha por item foi avaliada e descartada por ora.</t>
         </is>
       </c>
       <c r="D20" s="65" t="inlineStr">
         <is>
-          <t>Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso — se uma área quebra três vezes mais que as outras, isso aparece. Encaminhar: (1) comunicar a regra às áreas; (2) montar o pequeno estoque de reserva; (3) definir quantos dias o empréstimo pode durar antes de virar 'Atrasado'; (4) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
+          <t>DECIDIDO: manter uma linha de orçamento e detalhar na DESCRIÇÃO do lançamento no SIENGE, com padrão fixo ('Peças – mouse', 'Peças – tela'). Motivos: (1) não há histórico — as despesas do TI ainda não têm lançamento, então orçar item a item seria estimativa sem base, e cada linha acusaria desvio pela divisão errada, não pelo gasto; (2) cinco linhas viram cinco lançamentos mensais para uma rubrica que é 11% das despesas da área; (3) o plano de contas é definido pela controladoria, então subitens no orçamento não mudariam a classificação contábil. Em jan/27, com seis meses de dados reais, reavaliar. Se separar, separar por NATUREZA (reposição x reparo), que é o que dá leitura gerencial, e não item a item. Mesmo critério vale para 'Equipamentos Eletrônicos Diversos' e demais rubricas genéricas.</t>
         </is>
       </c>
       <c r="E20" s="65" t="inlineStr">
@@ -12153,127 +12388,127 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F20" s="69" t="inlineStr">
-        <is>
-          <t>IMPLANTAR</t>
+      <c r="F20" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="61" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B21" s="62" t="inlineStr">
         <is>
-          <t>Papelaria não é TI — manter no Administrativo</t>
+          <t>Política de troca 1x1 e empréstimo — IMPLANTAR</t>
         </is>
       </c>
       <c r="C21" s="62" t="inlineStr">
         <is>
-          <t>Recomendação registrada: o controle de papelaria (canetas, blocos, papel, copos) deve ficar no Administrativo/Facilities, não no TI. O TI controla equipamento porque há decisão TÉCNICA envolvida — se o notebook precisa de troca ou só de formatação, se a tela quebrou por defeito ou por queda. Não existe decisão técnica em caneta e bloco.</t>
+          <t>Hoje não existe regra: o pedido chega e a compra é feita. A proposta é que para receber um item novo a pessoa entregue o que quebrou (troca 1x1), e que exista um equipamento reserva para empréstimo imediato, para ninguém ficar parado esperando. O reserva é COM FIO de propósito: mais barato e menos confortável que o definitivo, o que cria o incentivo natural para devolver e fechar a troca. A aba 'Controle de Equipamentos' já está pronta para o registro.</t>
         </is>
       </c>
       <c r="D21" s="62" t="inlineStr">
         <is>
-          <t>Três diferenças separam as duas coisas: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. Se papelaria estiver caindo no orçamento do TI por motivo histórico, é o mesmo caso do Adapta (item Q): classificação errada, corrigir na origem quando o centro de custo novo for aberto.</t>
+          <t>Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso — se uma área quebra três vezes mais que as outras, isso aparece. Encaminhar: (1) comunicar a regra às áreas; (2) montar o pequeno estoque de reserva; (3) definir quantos dias o empréstimo pode durar antes de virar 'Atrasado'; (4) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
         </is>
       </c>
       <c r="E21" s="62" t="inlineStr">
         <is>
-          <t>Cristiane + Administrativo</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F21" s="69" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO</t>
+          <t>IMPLANTAR</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="64" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B22" s="65" t="inlineStr">
         <is>
-          <t>AnyDesk — contratação prevista, definir valor</t>
+          <t>Papelaria não é TI — manter no Administrativo</t>
         </is>
       </c>
       <c r="C22" s="65" t="inlineStr">
         <is>
-          <t>Licença de acesso remoto que será contratada e não constava na ficha. Linha criada com planejado zerado, à espera do valor e do mês de início.</t>
+          <t>Recomendação registrada: o controle de papelaria (canetas, blocos, papel, copos) deve ficar no Administrativo/Facilities, não no TI. O TI controla equipamento porque há decisão TÉCNICA envolvida — se o notebook precisa de troca ou só de formatação, se a tela quebrou por defeito ou por queda. Não existe decisão técnica em caneta e bloco.</t>
         </is>
       </c>
       <c r="D22" s="65" t="inlineStr">
         <is>
-          <t>Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. O AnyDesk é contratação nova e sem substituto atual. Definir valor e mês para a linha entrar no orçamento — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
+          <t>Três diferenças separam as duas coisas: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. Se papelaria estiver caindo no orçamento do TI por motivo histórico, é o mesmo caso do Adapta (item Q): classificação errada, corrigir na origem quando o centro de custo novo for aberto.</t>
         </is>
       </c>
       <c r="E22" s="65" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Administrativo</t>
         </is>
       </c>
       <c r="F22" s="69" t="inlineStr">
         <is>
-          <t>DEFINIR VALOR</t>
+          <t>RECOMENDAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="61" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B23" s="62" t="inlineStr">
         <is>
-          <t>Vitor (diretoria) — Claude ou GPT? PERGUNTAR</t>
+          <t>AnyDesk — contratação prevista, definir valor</t>
         </is>
       </c>
       <c r="C23" s="62" t="inlineStr">
         <is>
-          <t>Confirmar com o Vitor se ele seguirá usando o Claude, o GPT, ou os dois. Hoje as duas ferramentas estão contratadas e são de mesma finalidade — IA generalista —, então manter as duas para o mesmo usuário é redundância paga.</t>
+          <t>Licença de acesso remoto que será contratada e não constava na ficha. Linha criada com planejado zerado, à espera do valor e do mês de início.</t>
         </is>
       </c>
       <c r="D23" s="62" t="inlineStr">
         <is>
-          <t>É pré-requisito para fechar a meta do item L: não dá para dimensionar o orçamento de IA sem saber quantas licenças de cada ferramenta ficam de pé. Referência de custo: a OpenAI aparece no extrato com R$ 5.950,10 em sete meses, sendo R$ 5.394 só em abr/26. Levantar a mesma informação para os demais usuários, não só a diretoria — a decisão vale para todo mundo.</t>
+          <t>Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. O AnyDesk é contratação nova e sem substituto atual. Definir valor e mês para a linha entrar no orçamento — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
         </is>
       </c>
       <c r="E23" s="62" t="inlineStr">
         <is>
-          <t>Cristiane + Vitor</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F23" s="69" t="inlineStr">
         <is>
-          <t>PERGUNTAR</t>
+          <t>DEFINIR VALOR</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B24" s="65" t="inlineStr">
         <is>
-          <t>Mapa de licenças de IA — quem usa o quê</t>
+          <t>Vitor (diretoria) — Claude ou GPT? PERGUNTAR</t>
         </is>
       </c>
       <c r="C24" s="65" t="inlineStr">
         <is>
-          <t>Situação atual conhecida: a licença do GPT era da Thamar e hoje é usada em conjunto por Gil, Miguel e Thamar. Uma licença também foi cedida ao Financeiro. Falta o mapa completo — quem usa cada ferramenta, em qual área e sob qual login.</t>
+          <t>Confirmar com o Vitor se ele seguirá usando o Claude, o GPT, ou os dois. Hoje as duas ferramentas estão contratadas e são de mesma finalidade — IA generalista —, então manter as duas para o mesmo usuário é redundância paga.</t>
         </is>
       </c>
       <c r="D24" s="65" t="inlineStr">
         <is>
-          <t>Duas consequências. ORÇAMENTO: uma licença usada pelo Financeiro é custo de outra área lançado no TI/Jurídico — é exatamente o caso que o rateio do item L precisa resolver, e sem o mapa não há como ratear. RISCO: contas de IA generalista são individuais, e o compartilhamento entre pessoas costuma contrariar os termos de uso do fornecedor, com risco de suspensão. Mais grave num escritório de advocacia: o histórico de conversas fica visível para todos que usam o mesmo login, então dados de um cliente podem ser vistos por quem não atua no caso — questão de sigilo profissional, não só de custo. Avaliar licenças individuais ou plano de equipe, que costuma sair mais barato por usuário e separa os históricos.</t>
+          <t>É pré-requisito para fechar a meta do item L: não dá para dimensionar o orçamento de IA sem saber quantas licenças de cada ferramenta ficam de pé. Referência de custo: a OpenAI aparece no extrato com R$ 5.950,10 em sete meses, sendo R$ 5.394 só em abr/26. Levantar a mesma informação para os demais usuários, não só a diretoria — a decisão vale para todo mundo.</t>
         </is>
       </c>
       <c r="E24" s="65" t="inlineStr">
@@ -12283,61 +12518,61 @@
       </c>
       <c r="F24" s="69" t="inlineStr">
         <is>
-          <t>LEVANTAR</t>
+          <t>PERGUNTAR</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="61" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B25" s="62" t="inlineStr">
         <is>
-          <t>Divisão de responsabilidades no acompanhamento</t>
+          <t>Mapa de licenças de IA — quem usa o quê</t>
         </is>
       </c>
       <c r="C25" s="62" t="inlineStr">
         <is>
-          <t>Definição de quem faz o quê no controle orçamentário do TI. Capacidades: Vinicius, analista, 173 h/mês a R$ 31,25/h de custo total; Jonathan, consultor/desenvolvedor, 3 dias por semana, 104 h/mês a R$ 60,58/h — o dobro. Cristiane na gestão.</t>
+          <t>Situação atual conhecida: a licença do GPT era da Thamar e hoje é usada em conjunto por Gil, Miguel e Thamar. Uma licença também foi cedida ao Financeiro. Falta o mapa completo — quem usa cada ferramenta, em qual área e sob qual login.</t>
         </is>
       </c>
       <c r="D25" s="62" t="inlineStr">
         <is>
-          <t>VINICIUS (todo o recorrente): extração mensal do SIENGE e lançamento do realizado, controle de equipamentos (solicitações, empréstimos, troca 1x1), acompanhamento do saldo por área para avisar antes do estouro, conferência de faturas contra contrato. JONATHAN (pontual e técnico, nunca rotina): avaliar AnyDesk x Monitor Remoto, avaliar Claude x GPT e planos de equipe, e automatizar a extração do SIENGE — esta última é a que paga o custo dele, porque devolve tempo do analista todos os meses. CRISTIANE: negociação de contratos, rateio, o que entra e sai do orçamento, apresentação à diretoria. Critério: 104 h/mês é capacidade limitada, e cada hora do consultor em tarefa administrativa custa o dobro da mesma hora do analista. Se o Jonathan aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
+          <t>Duas consequências. ORÇAMENTO: uma licença usada pelo Financeiro é custo de outra área lançado no TI/Jurídico — é exatamente o caso que o rateio do item L precisa resolver, e sem o mapa não há como ratear. RISCO: contas de IA generalista são individuais, e o compartilhamento entre pessoas costuma contrariar os termos de uso do fornecedor, com risco de suspensão. Mais grave num escritório de advocacia: o histórico de conversas fica visível para todos que usam o mesmo login, então dados de um cliente podem ser vistos por quem não atua no caso — questão de sigilo profissional, não só de custo. Avaliar licenças individuais ou plano de equipe, que costuma sair mais barato por usuário e separa os históricos.</t>
         </is>
       </c>
       <c r="E25" s="62" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F25" s="67" t="inlineStr">
-        <is>
-          <t>APLICADO</t>
+          <t>Cristiane + Vitor</t>
+        </is>
+      </c>
+      <c r="F25" s="69" t="inlineStr">
+        <is>
+          <t>LEVANTAR</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B26" s="65" t="inlineStr">
         <is>
-          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
+          <t>Divisão de responsabilidades no acompanhamento</t>
         </is>
       </c>
       <c r="C26" s="65" t="inlineStr">
         <is>
-          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
+          <t>Definição de quem faz o quê no controle orçamentário do TI. Capacidades: Vinicius, analista, 173 h/mês a R$ 31,25/h de custo total; Jonathan, consultor/desenvolvedor, 3 dias por semana, 104 h/mês a R$ 60,58/h — o dobro. Cristiane na gestão.</t>
         </is>
       </c>
       <c r="D26" s="65" t="inlineStr">
         <is>
-          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
+          <t>VINICIUS (suporte + recorrente + apoio ao desenvolvimento): suporte ao usuário; extração mensal do SIENGE e lançamento do realizado; controle de equipamentos (solicitações, empréstimos, troca 1x1); acompanhamento do saldo por área para avisar antes do estouro; conferência de faturas contra contrato; e apoio operacional ao Jonathan no que o desenvolvimento exigir. Esse apoio é o que multiplica as 104 h/mês do consultor: cada tarefa operacional que sai das mãos dele por R$ 31,25/h é uma hora de R$ 60,58 liberada para o que só ele faz. JONATHAN (pontual e técnico, nunca rotina): avaliar AnyDesk x Monitor Remoto, avaliar Claude x GPT e planos de equipe, e automatizar a extração do SIENGE — esta última é a que paga o custo dele, porque devolve tempo do analista todos os meses. CRISTIANE: negociação de contratos, rateio, o que entra e sai do orçamento, apresentação à diretoria. Critério: 104 h/mês é capacidade limitada, e cada hora do consultor em tarefa administrativa custa o dobro da mesma hora do analista. Se o Jonathan aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
         </is>
       </c>
       <c r="E26" s="65" t="inlineStr">
@@ -12345,39 +12580,71 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F26" s="69" t="inlineStr">
-        <is>
-          <t>CONFIRMAR</t>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="61" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="62" t="inlineStr">
+        <is>
+          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
+        </is>
+      </c>
+      <c r="C27" s="62" t="inlineStr">
+        <is>
+          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
+        </is>
+      </c>
+      <c r="D27" s="62" t="inlineStr">
+        <is>
+          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
+        </is>
+      </c>
+      <c r="E27" s="62" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F27" s="69" t="inlineStr">
+        <is>
+          <t>CONFIRMAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="64" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="62" t="inlineStr">
+      <c r="B28" s="65" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C27" s="62" t="inlineStr">
+      <c r="C28" s="65" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D27" s="62" t="inlineStr">
+      <c r="D28" s="65" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E27" s="62" t="inlineStr">
+      <c r="E28" s="65" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F27" s="66" t="inlineStr">
+      <c r="F28" s="66" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -15,16 +15,17 @@
     <sheet name="Por Plano de Contas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Pendências" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Controle de Equipamentos" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Contas Pagas (resumo)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Contas Pagas (detalhe)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Papéis e Responsabilidades" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Controle de Equipamentos" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Contas Pagas (resumo)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Contas Pagas (detalhe)" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -256,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -415,14 +416,35 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1874,6 +1896,1129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLE DE EQUIPAMENTOS — solicitações, troca 1x1 e empréstimos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Registro operacional do TI. O SIENGE mostra o que foi PAGO; esta aba mostra o que foi PEDIDO — é no intervalo entre os dois que dá para avisar a área antes de estourar o saldo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>REGRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>Troca 1x1</t>
+        </is>
+      </c>
+      <c r="B5" s="78" t="inlineStr">
+        <is>
+          <t>Para receber um item novo, a pessoa entrega o que quebrou. O patrimônio devolvido é registrado na coluna própria.</t>
+        </is>
+      </c>
+      <c r="C5" s="79" t="n"/>
+      <c r="D5" s="79" t="n"/>
+      <c r="E5" s="79" t="n"/>
+      <c r="F5" s="79" t="n"/>
+      <c r="G5" s="79" t="n"/>
+      <c r="H5" s="79" t="n"/>
+      <c r="I5" s="79" t="n"/>
+      <c r="J5" s="79" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="82" t="inlineStr">
+        <is>
+          <t>Empréstimo</t>
+        </is>
+      </c>
+      <c r="B6" s="78" t="inlineStr">
+        <is>
+          <t>Quem está sem o equipamento sai com um reserva na hora, para não ficar parado. O reserva é COM FIO de propósito: mais barato e menos confortável que o definitivo, o que cria o incentivo para devolver e fechar a troca.</t>
+        </is>
+      </c>
+      <c r="C6" s="79" t="n"/>
+      <c r="D6" s="79" t="n"/>
+      <c r="E6" s="79" t="n"/>
+      <c r="F6" s="79" t="n"/>
+      <c r="G6" s="79" t="n"/>
+      <c r="H6" s="79" t="n"/>
+      <c r="I6" s="79" t="n"/>
+      <c r="J6" s="79" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>Sem devolução</t>
+        </is>
+      </c>
+      <c r="B7" s="78" t="inlineStr">
+        <is>
+          <t>Se a pessoa não entrega o item antigo, a solicitação fica 'Pendente devolução' e não vira compra até ser resolvida.</t>
+        </is>
+      </c>
+      <c r="C7" s="79" t="n"/>
+      <c r="D7" s="79" t="n"/>
+      <c r="E7" s="79" t="n"/>
+      <c r="F7" s="79" t="n"/>
+      <c r="G7" s="79" t="n"/>
+      <c r="H7" s="79" t="n"/>
+      <c r="I7" s="79" t="n"/>
+      <c r="J7" s="79" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="82" t="inlineStr">
+        <is>
+          <t>Aviso de saldo</t>
+        </is>
+      </c>
+      <c r="B8" s="78" t="inlineStr">
+        <is>
+          <t>Antes de aprovar, conferir o saldo da rubrica da área solicitante. Se a compra for levar ao estouro, avisar a área ANTES de comprar (pendência R).</t>
+        </is>
+      </c>
+      <c r="C8" s="79" t="n"/>
+      <c r="D8" s="79" t="n"/>
+      <c r="E8" s="79" t="n"/>
+      <c r="F8" s="79" t="n"/>
+      <c r="G8" s="79" t="n"/>
+      <c r="H8" s="79" t="n"/>
+      <c r="I8" s="79" t="n"/>
+      <c r="J8" s="79" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="76" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÕES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Área solicitante</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Solicitante</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Devolveu o antigo?</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Patrimônio devolvido</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Valor estimado</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="83" t="n"/>
+      <c r="B12" s="83" t="n"/>
+      <c r="C12" s="83" t="n"/>
+      <c r="D12" s="83" t="n"/>
+      <c r="E12" s="83" t="n"/>
+      <c r="F12" s="83" t="n"/>
+      <c r="G12" s="83" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="83" t="n"/>
+      <c r="J12" s="83" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="83" t="n"/>
+      <c r="B13" s="83" t="n"/>
+      <c r="C13" s="83" t="n"/>
+      <c r="D13" s="83" t="n"/>
+      <c r="E13" s="83" t="n"/>
+      <c r="F13" s="83" t="n"/>
+      <c r="G13" s="83" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="83" t="n"/>
+      <c r="J13" s="83" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="83" t="n"/>
+      <c r="B14" s="83" t="n"/>
+      <c r="C14" s="83" t="n"/>
+      <c r="D14" s="83" t="n"/>
+      <c r="E14" s="83" t="n"/>
+      <c r="F14" s="83" t="n"/>
+      <c r="G14" s="83" t="n"/>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="83" t="n"/>
+      <c r="J14" s="83" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="83" t="n"/>
+      <c r="B15" s="83" t="n"/>
+      <c r="C15" s="83" t="n"/>
+      <c r="D15" s="83" t="n"/>
+      <c r="E15" s="83" t="n"/>
+      <c r="F15" s="83" t="n"/>
+      <c r="G15" s="83" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="83" t="n"/>
+      <c r="J15" s="83" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="83" t="n"/>
+      <c r="B16" s="83" t="n"/>
+      <c r="C16" s="83" t="n"/>
+      <c r="D16" s="83" t="n"/>
+      <c r="E16" s="83" t="n"/>
+      <c r="F16" s="83" t="n"/>
+      <c r="G16" s="83" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="83" t="n"/>
+      <c r="J16" s="83" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="83" t="n"/>
+      <c r="B17" s="83" t="n"/>
+      <c r="C17" s="83" t="n"/>
+      <c r="D17" s="83" t="n"/>
+      <c r="E17" s="83" t="n"/>
+      <c r="F17" s="83" t="n"/>
+      <c r="G17" s="83" t="n"/>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="83" t="n"/>
+      <c r="J17" s="83" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="83" t="n"/>
+      <c r="B18" s="83" t="n"/>
+      <c r="C18" s="83" t="n"/>
+      <c r="D18" s="83" t="n"/>
+      <c r="E18" s="83" t="n"/>
+      <c r="F18" s="83" t="n"/>
+      <c r="G18" s="83" t="n"/>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="83" t="n"/>
+      <c r="J18" s="83" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="83" t="n"/>
+      <c r="B19" s="83" t="n"/>
+      <c r="C19" s="83" t="n"/>
+      <c r="D19" s="83" t="n"/>
+      <c r="E19" s="83" t="n"/>
+      <c r="F19" s="83" t="n"/>
+      <c r="G19" s="83" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="83" t="n"/>
+      <c r="J19" s="83" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="83" t="n"/>
+      <c r="B20" s="83" t="n"/>
+      <c r="C20" s="83" t="n"/>
+      <c r="D20" s="83" t="n"/>
+      <c r="E20" s="83" t="n"/>
+      <c r="F20" s="83" t="n"/>
+      <c r="G20" s="83" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="83" t="n"/>
+      <c r="J20" s="83" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="83" t="n"/>
+      <c r="B21" s="83" t="n"/>
+      <c r="C21" s="83" t="n"/>
+      <c r="D21" s="83" t="n"/>
+      <c r="E21" s="83" t="n"/>
+      <c r="F21" s="83" t="n"/>
+      <c r="G21" s="83" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="83" t="n"/>
+      <c r="J21" s="83" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="83" t="n"/>
+      <c r="B22" s="83" t="n"/>
+      <c r="C22" s="83" t="n"/>
+      <c r="D22" s="83" t="n"/>
+      <c r="E22" s="83" t="n"/>
+      <c r="F22" s="83" t="n"/>
+      <c r="G22" s="83" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="83" t="n"/>
+      <c r="J22" s="83" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="83" t="n"/>
+      <c r="B23" s="83" t="n"/>
+      <c r="C23" s="83" t="n"/>
+      <c r="D23" s="83" t="n"/>
+      <c r="E23" s="83" t="n"/>
+      <c r="F23" s="83" t="n"/>
+      <c r="G23" s="83" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="83" t="n"/>
+      <c r="J23" s="83" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="83" t="n"/>
+      <c r="B24" s="83" t="n"/>
+      <c r="C24" s="83" t="n"/>
+      <c r="D24" s="83" t="n"/>
+      <c r="E24" s="83" t="n"/>
+      <c r="F24" s="83" t="n"/>
+      <c r="G24" s="83" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="83" t="n"/>
+      <c r="J24" s="83" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="83" t="n"/>
+      <c r="B25" s="83" t="n"/>
+      <c r="C25" s="83" t="n"/>
+      <c r="D25" s="83" t="n"/>
+      <c r="E25" s="83" t="n"/>
+      <c r="F25" s="83" t="n"/>
+      <c r="G25" s="83" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="83" t="n"/>
+      <c r="J25" s="83" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="83" t="n"/>
+      <c r="B26" s="83" t="n"/>
+      <c r="C26" s="83" t="n"/>
+      <c r="D26" s="83" t="n"/>
+      <c r="E26" s="83" t="n"/>
+      <c r="F26" s="83" t="n"/>
+      <c r="G26" s="83" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="83" t="n"/>
+      <c r="J26" s="83" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="83" t="n"/>
+      <c r="B27" s="83" t="n"/>
+      <c r="C27" s="83" t="n"/>
+      <c r="D27" s="83" t="n"/>
+      <c r="E27" s="83" t="n"/>
+      <c r="F27" s="83" t="n"/>
+      <c r="G27" s="83" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="83" t="n"/>
+      <c r="J27" s="83" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="83" t="n"/>
+      <c r="B28" s="83" t="n"/>
+      <c r="C28" s="83" t="n"/>
+      <c r="D28" s="83" t="n"/>
+      <c r="E28" s="83" t="n"/>
+      <c r="F28" s="83" t="n"/>
+      <c r="G28" s="83" t="n"/>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="83" t="n"/>
+      <c r="J28" s="83" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="83" t="n"/>
+      <c r="B29" s="83" t="n"/>
+      <c r="C29" s="83" t="n"/>
+      <c r="D29" s="83" t="n"/>
+      <c r="E29" s="83" t="n"/>
+      <c r="F29" s="83" t="n"/>
+      <c r="G29" s="83" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="83" t="n"/>
+      <c r="J29" s="83" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="83" t="n"/>
+      <c r="B30" s="83" t="n"/>
+      <c r="C30" s="83" t="n"/>
+      <c r="D30" s="83" t="n"/>
+      <c r="E30" s="83" t="n"/>
+      <c r="F30" s="83" t="n"/>
+      <c r="G30" s="83" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="83" t="n"/>
+      <c r="J30" s="83" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="83" t="n"/>
+      <c r="B31" s="83" t="n"/>
+      <c r="C31" s="83" t="n"/>
+      <c r="D31" s="83" t="n"/>
+      <c r="E31" s="83" t="n"/>
+      <c r="F31" s="83" t="n"/>
+      <c r="G31" s="83" t="n"/>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="83" t="n"/>
+      <c r="J31" s="83" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="83" t="n"/>
+      <c r="B32" s="83" t="n"/>
+      <c r="C32" s="83" t="n"/>
+      <c r="D32" s="83" t="n"/>
+      <c r="E32" s="83" t="n"/>
+      <c r="F32" s="83" t="n"/>
+      <c r="G32" s="83" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="83" t="n"/>
+      <c r="J32" s="83" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="83" t="n"/>
+      <c r="B33" s="83" t="n"/>
+      <c r="C33" s="83" t="n"/>
+      <c r="D33" s="83" t="n"/>
+      <c r="E33" s="83" t="n"/>
+      <c r="F33" s="83" t="n"/>
+      <c r="G33" s="83" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="83" t="n"/>
+      <c r="J33" s="83" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="83" t="n"/>
+      <c r="B34" s="83" t="n"/>
+      <c r="C34" s="83" t="n"/>
+      <c r="D34" s="83" t="n"/>
+      <c r="E34" s="83" t="n"/>
+      <c r="F34" s="83" t="n"/>
+      <c r="G34" s="83" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="83" t="n"/>
+      <c r="J34" s="83" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="83" t="n"/>
+      <c r="B35" s="83" t="n"/>
+      <c r="C35" s="83" t="n"/>
+      <c r="D35" s="83" t="n"/>
+      <c r="E35" s="83" t="n"/>
+      <c r="F35" s="83" t="n"/>
+      <c r="G35" s="83" t="n"/>
+      <c r="H35" s="49" t="n"/>
+      <c r="I35" s="83" t="n"/>
+      <c r="J35" s="83" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="83" t="n"/>
+      <c r="B36" s="83" t="n"/>
+      <c r="C36" s="83" t="n"/>
+      <c r="D36" s="83" t="n"/>
+      <c r="E36" s="83" t="n"/>
+      <c r="F36" s="83" t="n"/>
+      <c r="G36" s="83" t="n"/>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="83" t="n"/>
+      <c r="J36" s="83" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="83" t="n"/>
+      <c r="B37" s="83" t="n"/>
+      <c r="C37" s="83" t="n"/>
+      <c r="D37" s="83" t="n"/>
+      <c r="E37" s="83" t="n"/>
+      <c r="F37" s="83" t="n"/>
+      <c r="G37" s="83" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="83" t="n"/>
+      <c r="J37" s="83" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="83" t="n"/>
+      <c r="B38" s="83" t="n"/>
+      <c r="C38" s="83" t="n"/>
+      <c r="D38" s="83" t="n"/>
+      <c r="E38" s="83" t="n"/>
+      <c r="F38" s="83" t="n"/>
+      <c r="G38" s="83" t="n"/>
+      <c r="H38" s="49" t="n"/>
+      <c r="I38" s="83" t="n"/>
+      <c r="J38" s="83" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="83" t="n"/>
+      <c r="B39" s="83" t="n"/>
+      <c r="C39" s="83" t="n"/>
+      <c r="D39" s="83" t="n"/>
+      <c r="E39" s="83" t="n"/>
+      <c r="F39" s="83" t="n"/>
+      <c r="G39" s="83" t="n"/>
+      <c r="H39" s="49" t="n"/>
+      <c r="I39" s="83" t="n"/>
+      <c r="J39" s="83" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="83" t="n"/>
+      <c r="B40" s="83" t="n"/>
+      <c r="C40" s="83" t="n"/>
+      <c r="D40" s="83" t="n"/>
+      <c r="E40" s="83" t="n"/>
+      <c r="F40" s="83" t="n"/>
+      <c r="G40" s="83" t="n"/>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="83" t="n"/>
+      <c r="J40" s="83" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="83" t="n"/>
+      <c r="B41" s="83" t="n"/>
+      <c r="C41" s="83" t="n"/>
+      <c r="D41" s="83" t="n"/>
+      <c r="E41" s="83" t="n"/>
+      <c r="F41" s="83" t="n"/>
+      <c r="G41" s="83" t="n"/>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="83" t="n"/>
+      <c r="J41" s="83" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="83" t="n"/>
+      <c r="B42" s="83" t="n"/>
+      <c r="C42" s="83" t="n"/>
+      <c r="D42" s="83" t="n"/>
+      <c r="E42" s="83" t="n"/>
+      <c r="F42" s="83" t="n"/>
+      <c r="G42" s="83" t="n"/>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="83" t="n"/>
+      <c r="J42" s="83" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="83" t="n"/>
+      <c r="B43" s="83" t="n"/>
+      <c r="C43" s="83" t="n"/>
+      <c r="D43" s="83" t="n"/>
+      <c r="E43" s="83" t="n"/>
+      <c r="F43" s="83" t="n"/>
+      <c r="G43" s="83" t="n"/>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="83" t="n"/>
+      <c r="J43" s="83" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="83" t="n"/>
+      <c r="B44" s="83" t="n"/>
+      <c r="C44" s="83" t="n"/>
+      <c r="D44" s="83" t="n"/>
+      <c r="E44" s="83" t="n"/>
+      <c r="F44" s="83" t="n"/>
+      <c r="G44" s="83" t="n"/>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="83" t="n"/>
+      <c r="J44" s="83" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="83" t="n"/>
+      <c r="B45" s="83" t="n"/>
+      <c r="C45" s="83" t="n"/>
+      <c r="D45" s="83" t="n"/>
+      <c r="E45" s="83" t="n"/>
+      <c r="F45" s="83" t="n"/>
+      <c r="G45" s="83" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="83" t="n"/>
+      <c r="J45" s="83" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="83" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="G46" s="83" t="n"/>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="83" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="G47" s="83" t="n"/>
+      <c r="H47" s="49" t="n"/>
+      <c r="I47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="83" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="G48" s="83" t="n"/>
+      <c r="H48" s="49" t="n"/>
+      <c r="I48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="83" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="G49" s="83" t="n"/>
+      <c r="H49" s="49" t="n"/>
+      <c r="I49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="83" t="n"/>
+      <c r="B50" s="83" t="n"/>
+      <c r="C50" s="83" t="n"/>
+      <c r="D50" s="83" t="n"/>
+      <c r="E50" s="83" t="n"/>
+      <c r="F50" s="83" t="n"/>
+      <c r="G50" s="83" t="n"/>
+      <c r="H50" s="49" t="n"/>
+      <c r="I50" s="83" t="n"/>
+      <c r="J50" s="83" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="83" t="n"/>
+      <c r="B51" s="83" t="n"/>
+      <c r="C51" s="83" t="n"/>
+      <c r="D51" s="83" t="n"/>
+      <c r="E51" s="83" t="n"/>
+      <c r="F51" s="83" t="n"/>
+      <c r="G51" s="83" t="n"/>
+      <c r="H51" s="49" t="n"/>
+      <c r="I51" s="83" t="n"/>
+      <c r="J51" s="83" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>EMPRÉSTIMOS (equipamento reserva)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="84" t="inlineStr">
+        <is>
+          <t>Item emprestado</t>
+        </is>
+      </c>
+      <c r="B54" s="84" t="inlineStr">
+        <is>
+          <t>Patrimônio</t>
+        </is>
+      </c>
+      <c r="C54" s="84" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="D54" s="84" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="E54" s="84" t="inlineStr">
+        <is>
+          <t>Saída em</t>
+        </is>
+      </c>
+      <c r="F54" s="84" t="inlineStr">
+        <is>
+          <t>Previsão de devolução</t>
+        </is>
+      </c>
+      <c r="G54" s="84" t="inlineStr">
+        <is>
+          <t>Devolvido em</t>
+        </is>
+      </c>
+      <c r="H54" s="84" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I54" s="84" t="inlineStr">
+        <is>
+          <t>Dias em posse</t>
+        </is>
+      </c>
+      <c r="J54" s="84" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="83" t="n"/>
+      <c r="B55" s="83" t="n"/>
+      <c r="C55" s="83" t="n"/>
+      <c r="D55" s="83" t="n"/>
+      <c r="E55" s="83" t="n"/>
+      <c r="F55" s="83" t="n"/>
+      <c r="G55" s="83" t="n"/>
+      <c r="H55" s="83" t="n"/>
+      <c r="I55" s="85">
+        <f>IF(E55="","",IF(G55="",TODAY()-E55,G55-E55))</f>
+        <v/>
+      </c>
+      <c r="J55" s="83" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="83" t="n"/>
+      <c r="B56" s="83" t="n"/>
+      <c r="C56" s="83" t="n"/>
+      <c r="D56" s="83" t="n"/>
+      <c r="E56" s="83" t="n"/>
+      <c r="F56" s="83" t="n"/>
+      <c r="G56" s="83" t="n"/>
+      <c r="H56" s="83" t="n"/>
+      <c r="I56" s="85">
+        <f>IF(E56="","",IF(G56="",TODAY()-E56,G56-E56))</f>
+        <v/>
+      </c>
+      <c r="J56" s="83" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="83" t="n"/>
+      <c r="B57" s="83" t="n"/>
+      <c r="C57" s="83" t="n"/>
+      <c r="D57" s="83" t="n"/>
+      <c r="E57" s="83" t="n"/>
+      <c r="F57" s="83" t="n"/>
+      <c r="G57" s="83" t="n"/>
+      <c r="H57" s="83" t="n"/>
+      <c r="I57" s="85">
+        <f>IF(E57="","",IF(G57="",TODAY()-E57,G57-E57))</f>
+        <v/>
+      </c>
+      <c r="J57" s="83" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="83" t="n"/>
+      <c r="B58" s="83" t="n"/>
+      <c r="C58" s="83" t="n"/>
+      <c r="D58" s="83" t="n"/>
+      <c r="E58" s="83" t="n"/>
+      <c r="F58" s="83" t="n"/>
+      <c r="G58" s="83" t="n"/>
+      <c r="H58" s="83" t="n"/>
+      <c r="I58" s="85">
+        <f>IF(E58="","",IF(G58="",TODAY()-E58,G58-E58))</f>
+        <v/>
+      </c>
+      <c r="J58" s="83" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="83" t="n"/>
+      <c r="B59" s="83" t="n"/>
+      <c r="C59" s="83" t="n"/>
+      <c r="D59" s="83" t="n"/>
+      <c r="E59" s="83" t="n"/>
+      <c r="F59" s="83" t="n"/>
+      <c r="G59" s="83" t="n"/>
+      <c r="H59" s="83" t="n"/>
+      <c r="I59" s="85">
+        <f>IF(E59="","",IF(G59="",TODAY()-E59,G59-E59))</f>
+        <v/>
+      </c>
+      <c r="J59" s="83" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="83" t="n"/>
+      <c r="B60" s="83" t="n"/>
+      <c r="C60" s="83" t="n"/>
+      <c r="D60" s="83" t="n"/>
+      <c r="E60" s="83" t="n"/>
+      <c r="F60" s="83" t="n"/>
+      <c r="G60" s="83" t="n"/>
+      <c r="H60" s="83" t="n"/>
+      <c r="I60" s="85">
+        <f>IF(E60="","",IF(G60="",TODAY()-E60,G60-E60))</f>
+        <v/>
+      </c>
+      <c r="J60" s="83" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="83" t="n"/>
+      <c r="B61" s="83" t="n"/>
+      <c r="C61" s="83" t="n"/>
+      <c r="D61" s="83" t="n"/>
+      <c r="E61" s="83" t="n"/>
+      <c r="F61" s="83" t="n"/>
+      <c r="G61" s="83" t="n"/>
+      <c r="H61" s="83" t="n"/>
+      <c r="I61" s="85">
+        <f>IF(E61="","",IF(G61="",TODAY()-E61,G61-E61))</f>
+        <v/>
+      </c>
+      <c r="J61" s="83" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="83" t="n"/>
+      <c r="B62" s="83" t="n"/>
+      <c r="C62" s="83" t="n"/>
+      <c r="D62" s="83" t="n"/>
+      <c r="E62" s="83" t="n"/>
+      <c r="F62" s="83" t="n"/>
+      <c r="G62" s="83" t="n"/>
+      <c r="H62" s="83" t="n"/>
+      <c r="I62" s="85">
+        <f>IF(E62="","",IF(G62="",TODAY()-E62,G62-E62))</f>
+        <v/>
+      </c>
+      <c r="J62" s="83" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="83" t="n"/>
+      <c r="B63" s="83" t="n"/>
+      <c r="C63" s="83" t="n"/>
+      <c r="D63" s="83" t="n"/>
+      <c r="E63" s="83" t="n"/>
+      <c r="F63" s="83" t="n"/>
+      <c r="G63" s="83" t="n"/>
+      <c r="H63" s="83" t="n"/>
+      <c r="I63" s="85">
+        <f>IF(E63="","",IF(G63="",TODAY()-E63,G63-E63))</f>
+        <v/>
+      </c>
+      <c r="J63" s="83" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="83" t="n"/>
+      <c r="B64" s="83" t="n"/>
+      <c r="C64" s="83" t="n"/>
+      <c r="D64" s="83" t="n"/>
+      <c r="E64" s="83" t="n"/>
+      <c r="F64" s="83" t="n"/>
+      <c r="G64" s="83" t="n"/>
+      <c r="H64" s="83" t="n"/>
+      <c r="I64" s="85">
+        <f>IF(E64="","",IF(G64="",TODAY()-E64,G64-E64))</f>
+        <v/>
+      </c>
+      <c r="J64" s="83" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="83" t="n"/>
+      <c r="B65" s="83" t="n"/>
+      <c r="C65" s="83" t="n"/>
+      <c r="D65" s="83" t="n"/>
+      <c r="E65" s="83" t="n"/>
+      <c r="F65" s="83" t="n"/>
+      <c r="G65" s="83" t="n"/>
+      <c r="H65" s="83" t="n"/>
+      <c r="I65" s="85">
+        <f>IF(E65="","",IF(G65="",TODAY()-E65,G65-E65))</f>
+        <v/>
+      </c>
+      <c r="J65" s="83" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="83" t="n"/>
+      <c r="B66" s="83" t="n"/>
+      <c r="C66" s="83" t="n"/>
+      <c r="D66" s="83" t="n"/>
+      <c r="E66" s="83" t="n"/>
+      <c r="F66" s="83" t="n"/>
+      <c r="G66" s="83" t="n"/>
+      <c r="H66" s="83" t="n"/>
+      <c r="I66" s="85">
+        <f>IF(E66="","",IF(G66="",TODAY()-E66,G66-E66))</f>
+        <v/>
+      </c>
+      <c r="J66" s="83" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="83" t="n"/>
+      <c r="B67" s="83" t="n"/>
+      <c r="C67" s="83" t="n"/>
+      <c r="D67" s="83" t="n"/>
+      <c r="E67" s="83" t="n"/>
+      <c r="F67" s="83" t="n"/>
+      <c r="G67" s="83" t="n"/>
+      <c r="H67" s="83" t="n"/>
+      <c r="I67" s="85">
+        <f>IF(E67="","",IF(G67="",TODAY()-E67,G67-E67))</f>
+        <v/>
+      </c>
+      <c r="J67" s="83" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="83" t="n"/>
+      <c r="B68" s="83" t="n"/>
+      <c r="C68" s="83" t="n"/>
+      <c r="D68" s="83" t="n"/>
+      <c r="E68" s="83" t="n"/>
+      <c r="F68" s="83" t="n"/>
+      <c r="G68" s="83" t="n"/>
+      <c r="H68" s="83" t="n"/>
+      <c r="I68" s="85">
+        <f>IF(E68="","",IF(G68="",TODAY()-E68,G68-E68))</f>
+        <v/>
+      </c>
+      <c r="J68" s="83" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="83" t="n"/>
+      <c r="B69" s="83" t="n"/>
+      <c r="C69" s="83" t="n"/>
+      <c r="D69" s="83" t="n"/>
+      <c r="E69" s="83" t="n"/>
+      <c r="F69" s="83" t="n"/>
+      <c r="G69" s="83" t="n"/>
+      <c r="H69" s="83" t="n"/>
+      <c r="I69" s="85">
+        <f>IF(E69="","",IF(G69="",TODAY()-E69,G69-E69))</f>
+        <v/>
+      </c>
+      <c r="J69" s="83" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="83" t="n"/>
+      <c r="B70" s="83" t="n"/>
+      <c r="C70" s="83" t="n"/>
+      <c r="D70" s="83" t="n"/>
+      <c r="E70" s="83" t="n"/>
+      <c r="F70" s="83" t="n"/>
+      <c r="G70" s="83" t="n"/>
+      <c r="H70" s="83" t="n"/>
+      <c r="I70" s="85">
+        <f>IF(E70="","",IF(G70="",TODAY()-E70,G70-E70))</f>
+        <v/>
+      </c>
+      <c r="J70" s="83" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="83" t="n"/>
+      <c r="B71" s="83" t="n"/>
+      <c r="C71" s="83" t="n"/>
+      <c r="D71" s="83" t="n"/>
+      <c r="E71" s="83" t="n"/>
+      <c r="F71" s="83" t="n"/>
+      <c r="G71" s="83" t="n"/>
+      <c r="H71" s="83" t="n"/>
+      <c r="I71" s="85">
+        <f>IF(E71="","",IF(G71="",TODAY()-E71,G71-E71))</f>
+        <v/>
+      </c>
+      <c r="J71" s="83" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="83" t="n"/>
+      <c r="B72" s="83" t="n"/>
+      <c r="C72" s="83" t="n"/>
+      <c r="D72" s="83" t="n"/>
+      <c r="E72" s="83" t="n"/>
+      <c r="F72" s="83" t="n"/>
+      <c r="G72" s="83" t="n"/>
+      <c r="H72" s="83" t="n"/>
+      <c r="I72" s="85">
+        <f>IF(E72="","",IF(G72="",TODAY()-E72,G72-E72))</f>
+        <v/>
+      </c>
+      <c r="J72" s="83" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="83" t="n"/>
+      <c r="B73" s="83" t="n"/>
+      <c r="C73" s="83" t="n"/>
+      <c r="D73" s="83" t="n"/>
+      <c r="E73" s="83" t="n"/>
+      <c r="F73" s="83" t="n"/>
+      <c r="G73" s="83" t="n"/>
+      <c r="H73" s="83" t="n"/>
+      <c r="I73" s="85">
+        <f>IF(E73="","",IF(G73="",TODAY()-E73,G73-E73))</f>
+        <v/>
+      </c>
+      <c r="J73" s="83" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="83" t="n"/>
+      <c r="B74" s="83" t="n"/>
+      <c r="C74" s="83" t="n"/>
+      <c r="D74" s="83" t="n"/>
+      <c r="E74" s="83" t="n"/>
+      <c r="F74" s="83" t="n"/>
+      <c r="G74" s="83" t="n"/>
+      <c r="H74" s="83" t="n"/>
+      <c r="I74" s="85">
+        <f>IF(E74="","",IF(G74="",TODAY()-E74,G74-E74))</f>
+        <v/>
+      </c>
+      <c r="J74" s="83" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="83" t="n"/>
+      <c r="B75" s="83" t="n"/>
+      <c r="C75" s="83" t="n"/>
+      <c r="D75" s="83" t="n"/>
+      <c r="E75" s="83" t="n"/>
+      <c r="F75" s="83" t="n"/>
+      <c r="G75" s="83" t="n"/>
+      <c r="H75" s="83" t="n"/>
+      <c r="I75" s="85">
+        <f>IF(E75="","",IF(G75="",TODAY()-E75,G75-E75))</f>
+        <v/>
+      </c>
+      <c r="J75" s="83" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="83" t="n"/>
+      <c r="B76" s="83" t="n"/>
+      <c r="C76" s="83" t="n"/>
+      <c r="D76" s="83" t="n"/>
+      <c r="E76" s="83" t="n"/>
+      <c r="F76" s="83" t="n"/>
+      <c r="G76" s="83" t="n"/>
+      <c r="H76" s="83" t="n"/>
+      <c r="I76" s="85">
+        <f>IF(E76="","",IF(G76="",TODAY()-E76,G76-E76))</f>
+        <v/>
+      </c>
+      <c r="J76" s="83" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="83" t="n"/>
+      <c r="B77" s="83" t="n"/>
+      <c r="C77" s="83" t="n"/>
+      <c r="D77" s="83" t="n"/>
+      <c r="E77" s="83" t="n"/>
+      <c r="F77" s="83" t="n"/>
+      <c r="G77" s="83" t="n"/>
+      <c r="H77" s="83" t="n"/>
+      <c r="I77" s="85">
+        <f>IF(E77="","",IF(G77="",TODAY()-E77,G77-E77))</f>
+        <v/>
+      </c>
+      <c r="J77" s="83" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="83" t="n"/>
+      <c r="B78" s="83" t="n"/>
+      <c r="C78" s="83" t="n"/>
+      <c r="D78" s="83" t="n"/>
+      <c r="E78" s="83" t="n"/>
+      <c r="F78" s="83" t="n"/>
+      <c r="G78" s="83" t="n"/>
+      <c r="H78" s="83" t="n"/>
+      <c r="I78" s="85">
+        <f>IF(E78="","",IF(G78="",TODAY()-E78,G78-E78))</f>
+        <v/>
+      </c>
+      <c r="J78" s="83" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="83" t="n"/>
+      <c r="B79" s="83" t="n"/>
+      <c r="C79" s="83" t="n"/>
+      <c r="D79" s="83" t="n"/>
+      <c r="E79" s="83" t="n"/>
+      <c r="F79" s="83" t="n"/>
+      <c r="G79" s="83" t="n"/>
+      <c r="H79" s="83" t="n"/>
+      <c r="I79" s="85">
+        <f>IF(E79="","",IF(G79="",TODAY()-E79,G79-E79))</f>
+        <v/>
+      </c>
+      <c r="J79" s="83" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A11:J51"/>
+  <mergeCells count="9">
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="B6:J6"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="I12:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Aberta,Aguardando devolução,Aprovada,Comprada,Entregue,Negada"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F12:F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sim,Não,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H55:H79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Emprestado,Devolvido,Atrasado,Baixado"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1968,118 +3113,118 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="79" t="inlineStr">
+      <c r="A5" s="86" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="B5" s="79" t="inlineStr">
+      <c r="B5" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C5" s="80" t="n">
+      <c r="C5" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="81" t="n">
+      <c r="D5" s="88" t="n">
         <v>4311.56</v>
       </c>
-      <c r="E5" s="81" t="n"/>
-      <c r="F5" s="81" t="n"/>
-      <c r="G5" s="81" t="n"/>
-      <c r="H5" s="81" t="n">
+      <c r="E5" s="88" t="n"/>
+      <c r="F5" s="88" t="n"/>
+      <c r="G5" s="88" t="n"/>
+      <c r="H5" s="88" t="n">
         <v>3723.62</v>
       </c>
-      <c r="I5" s="81" t="n">
+      <c r="I5" s="88" t="n">
         <v>6173.37</v>
       </c>
-      <c r="J5" s="81" t="n">
+      <c r="J5" s="88" t="n">
         <v>6300</v>
       </c>
-      <c r="K5" s="82" t="n">
+      <c r="K5" s="89" t="n">
         <v>20508.55</v>
       </c>
-      <c r="L5" s="83" t="inlineStr">
+      <c r="L5" s="90" t="inlineStr">
         <is>
           <t>TI-E03 Jonathan (Monitor Remoto)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="79" t="inlineStr">
+      <c r="A6" s="86" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="B6" s="79" t="inlineStr">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C6" s="80" t="n">
+      <c r="C6" s="87" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="81" t="n">
+      <c r="D6" s="88" t="n">
         <v>2670.84</v>
       </c>
-      <c r="E6" s="81" t="n">
+      <c r="E6" s="88" t="n">
         <v>2986.04</v>
       </c>
-      <c r="F6" s="81" t="n">
+      <c r="F6" s="88" t="n">
         <v>2778.04</v>
       </c>
-      <c r="G6" s="81" t="n">
+      <c r="G6" s="88" t="n">
         <v>2751.04</v>
       </c>
-      <c r="H6" s="81" t="n">
+      <c r="H6" s="88" t="n">
         <v>2719.04</v>
       </c>
-      <c r="I6" s="81" t="n">
+      <c r="I6" s="88" t="n">
         <v>3633.16</v>
       </c>
-      <c r="J6" s="81" t="n">
+      <c r="J6" s="88" t="n">
         <v>2461.04</v>
       </c>
-      <c r="K6" s="82" t="n">
+      <c r="K6" s="89" t="n">
         <v>19999.2</v>
       </c>
-      <c r="L6" s="83" t="inlineStr">
+      <c r="L6" s="90" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius Di Franco</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="79" t="inlineStr">
+      <c r="A7" s="86" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="B7" s="79" t="inlineStr">
+      <c r="B7" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C7" s="80" t="n">
+      <c r="C7" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="81" t="n"/>
-      <c r="E7" s="81" t="n">
+      <c r="D7" s="88" t="n"/>
+      <c r="E7" s="88" t="n">
         <v>234.46</v>
       </c>
-      <c r="F7" s="81" t="n">
+      <c r="F7" s="88" t="n">
         <v>321.76</v>
       </c>
-      <c r="G7" s="81" t="n">
+      <c r="G7" s="88" t="n">
         <v>5393.88</v>
       </c>
-      <c r="H7" s="81" t="n"/>
-      <c r="I7" s="81" t="n"/>
-      <c r="J7" s="81" t="n"/>
-      <c r="K7" s="82" t="n">
+      <c r="H7" s="88" t="n"/>
+      <c r="I7" s="88" t="n"/>
+      <c r="J7" s="88" t="n"/>
+      <c r="K7" s="89" t="n">
         <v>5950.1</v>
       </c>
-      <c r="L7" s="83" t="inlineStr">
+      <c r="L7" s="90" t="inlineStr">
         <is>
           <t>TI-D11 GPT</t>
         </is>
@@ -2118,10 +3263,10 @@
       <c r="J8" s="54" t="n">
         <v>979.4</v>
       </c>
-      <c r="K8" s="84" t="n">
+      <c r="K8" s="91" t="n">
         <v>5228.139999999999</v>
       </c>
-      <c r="L8" s="85" t="n"/>
+      <c r="L8" s="92" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="56" t="inlineStr">
@@ -2154,10 +3299,10 @@
       <c r="J9" s="54" t="n">
         <v>1151.26</v>
       </c>
-      <c r="K9" s="84" t="n">
+      <c r="K9" s="91" t="n">
         <v>3296.12</v>
       </c>
-      <c r="L9" s="85" t="n"/>
+      <c r="L9" s="92" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="56" t="inlineStr">
@@ -2188,48 +3333,48 @@
       <c r="J10" s="54" t="n">
         <v>1037.38</v>
       </c>
-      <c r="K10" s="84" t="n">
+      <c r="K10" s="91" t="n">
         <v>3242.61</v>
       </c>
-      <c r="L10" s="85" t="n"/>
+      <c r="L10" s="92" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="79" t="inlineStr">
+      <c r="A11" s="86" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="B11" s="79" t="inlineStr">
+      <c r="B11" s="86" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C11" s="80" t="n">
+      <c r="C11" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="81" t="n"/>
-      <c r="E11" s="81" t="n">
+      <c r="D11" s="88" t="n"/>
+      <c r="E11" s="88" t="n">
         <v>485</v>
       </c>
-      <c r="F11" s="81" t="n">
+      <c r="F11" s="88" t="n">
         <v>485</v>
       </c>
-      <c r="G11" s="81" t="n">
+      <c r="G11" s="88" t="n">
         <v>485</v>
       </c>
-      <c r="H11" s="81" t="n">
+      <c r="H11" s="88" t="n">
         <v>485</v>
       </c>
-      <c r="I11" s="81" t="n">
+      <c r="I11" s="88" t="n">
         <v>485</v>
       </c>
-      <c r="J11" s="81" t="n">
+      <c r="J11" s="88" t="n">
         <v>485</v>
       </c>
-      <c r="K11" s="82" t="n">
+      <c r="K11" s="89" t="n">
         <v>2910</v>
       </c>
-      <c r="L11" s="83" t="inlineStr">
+      <c r="L11" s="90" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius (benefício)</t>
         </is>
@@ -2262,10 +3407,10 @@
       <c r="H12" s="54" t="n"/>
       <c r="I12" s="54" t="n"/>
       <c r="J12" s="54" t="n"/>
-      <c r="K12" s="84" t="n">
+      <c r="K12" s="91" t="n">
         <v>954.5500000000001</v>
       </c>
-      <c r="L12" s="85" t="n"/>
+      <c r="L12" s="92" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="56" t="inlineStr">
@@ -2298,10 +3443,10 @@
         <v>137.93</v>
       </c>
       <c r="J13" s="54" t="n"/>
-      <c r="K13" s="84" t="n">
+      <c r="K13" s="91" t="n">
         <v>827.49</v>
       </c>
-      <c r="L13" s="85" t="n"/>
+      <c r="L13" s="92" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="56" t="inlineStr">
@@ -2332,10 +3477,10 @@
         <v>554.58</v>
       </c>
       <c r="J14" s="54" t="n"/>
-      <c r="K14" s="84" t="n">
+      <c r="K14" s="91" t="n">
         <v>758.53</v>
       </c>
-      <c r="L14" s="85" t="n"/>
+      <c r="L14" s="92" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="56" t="inlineStr">
@@ -2372,10 +3517,10 @@
       <c r="J15" s="54" t="n">
         <v>82.5</v>
       </c>
-      <c r="K15" s="84" t="n">
+      <c r="K15" s="91" t="n">
         <v>690</v>
       </c>
-      <c r="L15" s="85" t="n"/>
+      <c r="L15" s="92" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
@@ -2408,10 +3553,10 @@
       <c r="J16" s="54" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="K16" s="84" t="n">
+      <c r="K16" s="91" t="n">
         <v>562.42</v>
       </c>
-      <c r="L16" s="85" t="n"/>
+      <c r="L16" s="92" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="56" t="inlineStr">
@@ -2436,10 +3581,10 @@
         <v>183.6</v>
       </c>
       <c r="J17" s="54" t="n"/>
-      <c r="K17" s="84" t="n">
+      <c r="K17" s="91" t="n">
         <v>183.6</v>
       </c>
-      <c r="L17" s="85" t="n"/>
+      <c r="L17" s="92" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="51" t="inlineStr">
@@ -2493,7 +3638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2569,3964 +3714,3964 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="93" t="inlineStr">
         <is>
           <t>09/01/2026</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D5" s="86" t="inlineStr">
+      <c r="D5" s="93" t="inlineStr">
         <is>
           <t>FAT.11.25</t>
         </is>
       </c>
-      <c r="E5" s="86" t="inlineStr">
+      <c r="E5" s="93" t="inlineStr">
         <is>
           <t>95941/1</t>
         </is>
       </c>
-      <c r="F5" s="86" t="inlineStr">
+      <c r="F5" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G5" s="86" t="inlineStr">
+      <c r="G5" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H5" s="87" t="n">
+      <c r="H5" s="94" t="n">
         <v>407.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="86" t="inlineStr">
+      <c r="A6" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B6" s="86" t="inlineStr">
+      <c r="B6" s="93" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C6" s="86" t="inlineStr">
+      <c r="C6" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D6" s="86" t="inlineStr">
+      <c r="D6" s="93" t="inlineStr">
         <is>
           <t>FAT.01.26</t>
         </is>
       </c>
-      <c r="E6" s="86" t="inlineStr">
+      <c r="E6" s="93" t="inlineStr">
         <is>
           <t>97478/1</t>
         </is>
       </c>
-      <c r="F6" s="86" t="inlineStr">
+      <c r="F6" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G6" s="86" t="inlineStr">
+      <c r="G6" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H6" s="87" t="n">
+      <c r="H6" s="94" t="n">
         <v>390.95</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="86" t="inlineStr">
+      <c r="A7" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B7" s="86" t="inlineStr">
+      <c r="B7" s="93" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C7" s="86" t="inlineStr">
+      <c r="C7" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D7" s="86" t="inlineStr">
+      <c r="D7" s="93" t="inlineStr">
         <is>
           <t>FAT.184180933</t>
         </is>
       </c>
-      <c r="E7" s="86" t="inlineStr">
+      <c r="E7" s="93" t="inlineStr">
         <is>
           <t>97480/1</t>
         </is>
       </c>
-      <c r="F7" s="86" t="inlineStr">
+      <c r="F7" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G7" s="86" t="inlineStr">
+      <c r="G7" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H7" s="87" t="n">
+      <c r="H7" s="94" t="n">
         <v>123.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="86" t="inlineStr">
+      <c r="A8" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B8" s="86" t="inlineStr">
+      <c r="B8" s="93" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C8" s="86" t="inlineStr">
+      <c r="C8" s="93" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D8" s="86" t="inlineStr">
+      <c r="D8" s="93" t="inlineStr">
         <is>
           <t>NFS.347106</t>
         </is>
       </c>
-      <c r="E8" s="86" t="inlineStr">
+      <c r="E8" s="93" t="inlineStr">
         <is>
           <t>96534/1</t>
         </is>
       </c>
-      <c r="F8" s="86" t="inlineStr">
+      <c r="F8" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G8" s="86" t="inlineStr">
+      <c r="G8" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H8" s="87" t="n">
+      <c r="H8" s="94" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="86" t="inlineStr">
+      <c r="A9" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B9" s="86" t="inlineStr">
+      <c r="B9" s="93" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="C9" s="86" t="inlineStr">
+      <c r="C9" s="93" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D9" s="86" t="inlineStr">
+      <c r="D9" s="93" t="inlineStr">
         <is>
           <t>NFS.70</t>
         </is>
       </c>
-      <c r="E9" s="86" t="inlineStr">
+      <c r="E9" s="93" t="inlineStr">
         <is>
           <t>96602/1</t>
         </is>
       </c>
-      <c r="F9" s="86" t="inlineStr">
+      <c r="F9" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G9" s="86" t="inlineStr">
+      <c r="G9" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H9" s="87" t="n">
+      <c r="H9" s="94" t="n">
         <v>4311.56</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="86" t="inlineStr">
+      <c r="A10" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B10" s="86" t="inlineStr">
+      <c r="B10" s="93" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="C10" s="86" t="inlineStr">
+      <c r="C10" s="93" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D10" s="86" t="inlineStr">
+      <c r="D10" s="93" t="inlineStr">
         <is>
           <t>AV.LIC EMAILS 01.25</t>
         </is>
       </c>
-      <c r="E10" s="86" t="inlineStr">
+      <c r="E10" s="93" t="inlineStr">
         <is>
           <t>96014/1</t>
         </is>
       </c>
-      <c r="F10" s="86" t="inlineStr">
+      <c r="F10" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G10" s="86" t="inlineStr">
+      <c r="G10" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H10" s="87" t="n">
+      <c r="H10" s="94" t="n">
         <v>6.2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="86" t="inlineStr">
+      <c r="A11" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B11" s="86" t="inlineStr">
+      <c r="B11" s="93" t="inlineStr">
         <is>
           <t>25/01/2026</t>
         </is>
       </c>
-      <c r="C11" s="86" t="inlineStr">
+      <c r="C11" s="93" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D11" s="86" t="inlineStr">
+      <c r="D11" s="93" t="inlineStr">
         <is>
           <t>BOL.13.01</t>
         </is>
       </c>
-      <c r="E11" s="86" t="inlineStr">
+      <c r="E11" s="93" t="inlineStr">
         <is>
           <t>96623/1</t>
         </is>
       </c>
-      <c r="F11" s="86" t="inlineStr">
+      <c r="F11" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G11" s="86" t="inlineStr">
+      <c r="G11" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H11" s="87" t="n">
+      <c r="H11" s="94" t="n">
         <v>918.08</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="86" t="inlineStr">
+      <c r="A12" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B12" s="86" t="inlineStr">
+      <c r="B12" s="93" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C12" s="86" t="inlineStr">
+      <c r="C12" s="93" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D12" s="86" t="inlineStr">
+      <c r="D12" s="93" t="inlineStr">
         <is>
           <t>FAT.2682</t>
         </is>
       </c>
-      <c r="E12" s="86" t="inlineStr">
+      <c r="E12" s="93" t="inlineStr">
         <is>
           <t>96458/1</t>
         </is>
       </c>
-      <c r="F12" s="86" t="inlineStr">
+      <c r="F12" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G12" s="86" t="inlineStr">
+      <c r="G12" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H12" s="87" t="n">
+      <c r="H12" s="94" t="n">
         <v>723.75</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="86" t="inlineStr">
+      <c r="A13" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B13" s="86" t="inlineStr">
+      <c r="B13" s="93" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="C13" s="86" t="inlineStr">
+      <c r="C13" s="93" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D13" s="86" t="inlineStr">
+      <c r="D13" s="93" t="inlineStr">
         <is>
           <t>FAT.2011241340</t>
         </is>
       </c>
-      <c r="E13" s="86" t="inlineStr">
+      <c r="E13" s="93" t="inlineStr">
         <is>
           <t>96088/1</t>
         </is>
       </c>
-      <c r="F13" s="86" t="inlineStr">
+      <c r="F13" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G13" s="86" t="inlineStr">
+      <c r="G13" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H13" s="87" t="n">
+      <c r="H13" s="94" t="n">
         <v>51.63</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="86" t="inlineStr">
+      <c r="A14" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B14" s="86" t="inlineStr">
+      <c r="B14" s="93" t="inlineStr">
         <is>
           <t>22/01/2026</t>
         </is>
       </c>
-      <c r="C14" s="86" t="inlineStr">
+      <c r="C14" s="93" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D14" s="86" t="inlineStr">
+      <c r="D14" s="93" t="inlineStr">
         <is>
           <t>FAT.5664047504</t>
         </is>
       </c>
-      <c r="E14" s="86" t="inlineStr">
+      <c r="E14" s="93" t="inlineStr">
         <is>
           <t>96789/1</t>
         </is>
       </c>
-      <c r="F14" s="86" t="inlineStr">
+      <c r="F14" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G14" s="86" t="inlineStr">
+      <c r="G14" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H14" s="87" t="n">
+      <c r="H14" s="94" t="n">
         <v>331.42</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="86" t="inlineStr">
+      <c r="A15" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B15" s="86" t="inlineStr">
+      <c r="B15" s="93" t="inlineStr">
         <is>
           <t>26/01/2026</t>
         </is>
       </c>
-      <c r="C15" s="86" t="inlineStr">
+      <c r="C15" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D15" s="86" t="inlineStr">
+      <c r="D15" s="93" t="inlineStr">
         <is>
           <t>CX.16.01.26</t>
         </is>
       </c>
-      <c r="E15" s="86" t="inlineStr">
+      <c r="E15" s="93" t="inlineStr">
         <is>
           <t>97067/1</t>
         </is>
       </c>
-      <c r="F15" s="86" t="inlineStr">
+      <c r="F15" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G15" s="86" t="inlineStr">
+      <c r="G15" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H15" s="87" t="n">
+      <c r="H15" s="94" t="n">
         <v>39.84</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="86" t="inlineStr">
+      <c r="A16" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B16" s="86" t="inlineStr">
+      <c r="B16" s="93" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="C16" s="86" t="inlineStr">
+      <c r="C16" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D16" s="86" t="inlineStr">
+      <c r="D16" s="93" t="inlineStr">
         <is>
           <t>SAL.Sal_122025</t>
         </is>
       </c>
-      <c r="E16" s="86" t="inlineStr">
+      <c r="E16" s="93" t="inlineStr">
         <is>
           <t>96252/1</t>
         </is>
       </c>
-      <c r="F16" s="86" t="inlineStr">
+      <c r="F16" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G16" s="86" t="inlineStr">
+      <c r="G16" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H16" s="87" t="n">
+      <c r="H16" s="94" t="n">
         <v>1602</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="86" t="inlineStr">
+      <c r="A17" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B17" s="86" t="inlineStr">
+      <c r="B17" s="93" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="C17" s="86" t="inlineStr">
+      <c r="C17" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D17" s="86" t="inlineStr">
+      <c r="D17" s="93" t="inlineStr">
         <is>
           <t>SAL.VALE_ 012026</t>
         </is>
       </c>
-      <c r="E17" s="86" t="inlineStr">
+      <c r="E17" s="93" t="inlineStr">
         <is>
           <t>97269/1</t>
         </is>
       </c>
-      <c r="F17" s="86" t="inlineStr">
+      <c r="F17" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G17" s="86" t="inlineStr">
+      <c r="G17" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H17" s="87" t="n">
+      <c r="H17" s="94" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="86" t="inlineStr">
+      <c r="A18" s="93" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B18" s="86" t="inlineStr">
+      <c r="B18" s="93" t="inlineStr">
         <is>
           <t>27/01/2026</t>
         </is>
       </c>
-      <c r="C18" s="86" t="inlineStr">
+      <c r="C18" s="93" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D18" s="86" t="inlineStr">
+      <c r="D18" s="93" t="inlineStr">
         <is>
           <t>BOL.1</t>
         </is>
       </c>
-      <c r="E18" s="86" t="inlineStr">
+      <c r="E18" s="93" t="inlineStr">
         <is>
           <t>97204/1</t>
         </is>
       </c>
-      <c r="F18" s="86" t="inlineStr">
+      <c r="F18" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G18" s="86" t="inlineStr">
+      <c r="G18" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H18" s="87" t="n">
+      <c r="H18" s="94" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="86" t="inlineStr">
+      <c r="A19" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B19" s="86" t="inlineStr">
+      <c r="B19" s="93" t="inlineStr">
         <is>
           <t>04/02/2026</t>
         </is>
       </c>
-      <c r="C19" s="86" t="inlineStr">
+      <c r="C19" s="93" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D19" s="86" t="inlineStr">
+      <c r="D19" s="93" t="inlineStr">
         <is>
           <t>AV.04.02.26</t>
         </is>
       </c>
-      <c r="E19" s="86" t="inlineStr">
+      <c r="E19" s="93" t="inlineStr">
         <is>
           <t>98500/1</t>
         </is>
       </c>
-      <c r="F19" s="86" t="inlineStr">
+      <c r="F19" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G19" s="86" t="inlineStr">
+      <c r="G19" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H19" s="87" t="n">
+      <c r="H19" s="94" t="n">
         <v>26.67</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="86" t="inlineStr">
+      <c r="A20" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B20" s="86" t="inlineStr">
+      <c r="B20" s="93" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C20" s="86" t="inlineStr">
+      <c r="C20" s="93" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D20" s="86" t="inlineStr">
+      <c r="D20" s="93" t="inlineStr">
         <is>
           <t>AV.12.02.26 LCW</t>
         </is>
       </c>
-      <c r="E20" s="86" t="inlineStr">
+      <c r="E20" s="93" t="inlineStr">
         <is>
           <t>99336/1</t>
         </is>
       </c>
-      <c r="F20" s="86" t="inlineStr">
+      <c r="F20" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G20" s="86" t="inlineStr">
+      <c r="G20" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H20" s="87" t="n">
+      <c r="H20" s="94" t="n">
         <v>72.58</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="86" t="inlineStr">
+      <c r="A21" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B21" s="86" t="inlineStr">
+      <c r="B21" s="93" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C21" s="86" t="inlineStr">
+      <c r="C21" s="93" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D21" s="86" t="inlineStr">
+      <c r="D21" s="93" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E21" s="86" t="inlineStr">
+      <c r="E21" s="93" t="inlineStr">
         <is>
           <t>95104/2</t>
         </is>
       </c>
-      <c r="F21" s="86" t="inlineStr">
+      <c r="F21" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G21" s="86" t="inlineStr">
+      <c r="G21" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H21" s="87" t="n">
+      <c r="H21" s="94" t="n">
         <v>234.46</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="86" t="inlineStr">
+      <c r="A22" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B22" s="86" t="inlineStr">
+      <c r="B22" s="93" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C22" s="86" t="inlineStr">
+      <c r="C22" s="93" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D22" s="86" t="inlineStr">
+      <c r="D22" s="93" t="inlineStr">
         <is>
           <t>FAT.3575377</t>
         </is>
       </c>
-      <c r="E22" s="86" t="inlineStr">
+      <c r="E22" s="93" t="inlineStr">
         <is>
           <t>100172/1</t>
         </is>
       </c>
-      <c r="F22" s="86" t="inlineStr">
+      <c r="F22" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G22" s="86" t="inlineStr">
+      <c r="G22" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H22" s="87" t="n">
+      <c r="H22" s="94" t="n">
         <v>52.32</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="86" t="inlineStr">
+      <c r="A23" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B23" s="86" t="inlineStr">
+      <c r="B23" s="93" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C23" s="86" t="inlineStr">
+      <c r="C23" s="93" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D23" s="86" t="inlineStr">
+      <c r="D23" s="93" t="inlineStr">
         <is>
           <t>FAT.5290953</t>
         </is>
       </c>
-      <c r="E23" s="86" t="inlineStr">
+      <c r="E23" s="93" t="inlineStr">
         <is>
           <t>100173/1</t>
         </is>
       </c>
-      <c r="F23" s="86" t="inlineStr">
+      <c r="F23" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G23" s="86" t="inlineStr">
+      <c r="G23" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H23" s="87" t="n">
+      <c r="H23" s="94" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="86" t="inlineStr">
+      <c r="A24" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B24" s="86" t="inlineStr">
+      <c r="B24" s="93" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C24" s="86" t="inlineStr">
+      <c r="C24" s="93" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D24" s="86" t="inlineStr">
+      <c r="D24" s="93" t="inlineStr">
         <is>
           <t>BOL.141</t>
         </is>
       </c>
-      <c r="E24" s="86" t="inlineStr">
+      <c r="E24" s="93" t="inlineStr">
         <is>
           <t>99947/1</t>
         </is>
       </c>
-      <c r="F24" s="86" t="inlineStr">
+      <c r="F24" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G24" s="86" t="inlineStr">
+      <c r="G24" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H24" s="87" t="n">
+      <c r="H24" s="94" t="n">
         <v>338.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="86" t="inlineStr">
+      <c r="A25" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B25" s="86" t="inlineStr">
+      <c r="B25" s="93" t="inlineStr">
         <is>
           <t>13/02/2026</t>
         </is>
       </c>
-      <c r="C25" s="86" t="inlineStr">
+      <c r="C25" s="93" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D25" s="86" t="inlineStr">
+      <c r="D25" s="93" t="inlineStr">
         <is>
           <t>BOL.26449</t>
         </is>
       </c>
-      <c r="E25" s="86" t="inlineStr">
+      <c r="E25" s="93" t="inlineStr">
         <is>
           <t>99484/1</t>
         </is>
       </c>
-      <c r="F25" s="86" t="inlineStr">
+      <c r="F25" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G25" s="86" t="inlineStr">
+      <c r="G25" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H25" s="87" t="n">
+      <c r="H25" s="94" t="n">
         <v>137.94</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="86" t="inlineStr">
+      <c r="A26" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B26" s="86" t="inlineStr">
+      <c r="B26" s="93" t="inlineStr">
         <is>
           <t>19/02/2026</t>
         </is>
       </c>
-      <c r="C26" s="86" t="inlineStr">
+      <c r="C26" s="93" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D26" s="86" t="inlineStr">
+      <c r="D26" s="93" t="inlineStr">
         <is>
           <t>BOL.27256</t>
         </is>
       </c>
-      <c r="E26" s="86" t="inlineStr">
+      <c r="E26" s="93" t="inlineStr">
         <is>
           <t>99486/1</t>
         </is>
       </c>
-      <c r="F26" s="86" t="inlineStr">
+      <c r="F26" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G26" s="86" t="inlineStr">
+      <c r="G26" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H26" s="87" t="n">
+      <c r="H26" s="94" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="86" t="inlineStr">
+      <c r="A27" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B27" s="86" t="inlineStr">
+      <c r="B27" s="93" t="inlineStr">
         <is>
           <t>06/02/2026</t>
         </is>
       </c>
-      <c r="C27" s="86" t="inlineStr">
+      <c r="C27" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D27" s="86" t="inlineStr">
+      <c r="D27" s="93" t="inlineStr">
         <is>
           <t>SAL.SAL JANEIRO 2026</t>
         </is>
       </c>
-      <c r="E27" s="86" t="inlineStr">
+      <c r="E27" s="93" t="inlineStr">
         <is>
           <t>98811/1</t>
         </is>
       </c>
-      <c r="F27" s="86" t="inlineStr">
+      <c r="F27" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G27" s="86" t="inlineStr">
+      <c r="G27" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H27" s="87" t="n">
+      <c r="H27" s="94" t="n">
         <v>1750</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="86" t="inlineStr">
+      <c r="A28" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B28" s="86" t="inlineStr">
+      <c r="B28" s="93" t="inlineStr">
         <is>
           <t>20/02/2026</t>
         </is>
       </c>
-      <c r="C28" s="86" t="inlineStr">
+      <c r="C28" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D28" s="86" t="inlineStr">
+      <c r="D28" s="93" t="inlineStr">
         <is>
           <t>SAL.VALE FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E28" s="86" t="inlineStr">
+      <c r="E28" s="93" t="inlineStr">
         <is>
           <t>99890/1</t>
         </is>
       </c>
-      <c r="F28" s="86" t="inlineStr">
+      <c r="F28" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G28" s="86" t="inlineStr">
+      <c r="G28" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H28" s="87" t="n">
+      <c r="H28" s="94" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="86" t="inlineStr">
+      <c r="A29" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B29" s="86" t="inlineStr">
+      <c r="B29" s="93" t="inlineStr">
         <is>
           <t>2026-02-20 00:00:00</t>
         </is>
       </c>
-      <c r="C29" s="86" t="inlineStr">
+      <c r="C29" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D29" s="86" t="inlineStr">
+      <c r="D29" s="93" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E29" s="86" t="inlineStr">
+      <c r="E29" s="93" t="inlineStr">
         <is>
           <t>113754/2</t>
         </is>
       </c>
-      <c r="F29" s="86" t="inlineStr">
+      <c r="F29" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G29" s="86" t="inlineStr">
+      <c r="G29" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H29" s="87" t="n">
+      <c r="H29" s="94" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="86" t="inlineStr">
+      <c r="A30" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B30" s="86" t="inlineStr">
+      <c r="B30" s="93" t="inlineStr">
         <is>
           <t>2026-02-01 00:00:00</t>
         </is>
       </c>
-      <c r="C30" s="86" t="inlineStr">
+      <c r="C30" s="93" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D30" s="86" t="inlineStr"/>
-      <c r="E30" s="86" t="inlineStr"/>
-      <c r="F30" s="86" t="inlineStr">
+      <c r="D30" s="93" t="inlineStr"/>
+      <c r="E30" s="93" t="inlineStr"/>
+      <c r="F30" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G30" s="86" t="inlineStr">
+      <c r="G30" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H30" s="87" t="n">
+      <c r="H30" s="94" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="86" t="inlineStr">
+      <c r="A31" s="93" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B31" s="86" t="inlineStr">
+      <c r="B31" s="93" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C31" s="86" t="inlineStr">
+      <c r="C31" s="93" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D31" s="86" t="inlineStr">
+      <c r="D31" s="93" t="inlineStr">
         <is>
           <t>NFS.1430</t>
         </is>
       </c>
-      <c r="E31" s="86" t="inlineStr">
+      <c r="E31" s="93" t="inlineStr">
         <is>
           <t>99956/1</t>
         </is>
       </c>
-      <c r="F31" s="86" t="inlineStr">
+      <c r="F31" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G31" s="86" t="inlineStr">
+      <c r="G31" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H31" s="87" t="n">
+      <c r="H31" s="94" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="86" t="inlineStr">
+      <c r="A32" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B32" s="86" t="inlineStr">
+      <c r="B32" s="93" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C32" s="86" t="inlineStr">
+      <c r="C32" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D32" s="86" t="inlineStr">
+      <c r="D32" s="93" t="inlineStr">
         <is>
           <t>FAT.5042829</t>
         </is>
       </c>
-      <c r="E32" s="86" t="inlineStr">
+      <c r="E32" s="93" t="inlineStr">
         <is>
           <t>100503/1</t>
         </is>
       </c>
-      <c r="F32" s="86" t="inlineStr">
+      <c r="F32" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G32" s="86" t="inlineStr">
+      <c r="G32" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H32" s="87" t="n">
+      <c r="H32" s="94" t="n">
         <v>87.69</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="86" t="inlineStr">
+      <c r="A33" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B33" s="86" t="inlineStr">
+      <c r="B33" s="93" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C33" s="86" t="inlineStr">
+      <c r="C33" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D33" s="86" t="inlineStr">
+      <c r="D33" s="93" t="inlineStr">
         <is>
           <t>FAT.5042827</t>
         </is>
       </c>
-      <c r="E33" s="86" t="inlineStr">
+      <c r="E33" s="93" t="inlineStr">
         <is>
           <t>100504/1</t>
         </is>
       </c>
-      <c r="F33" s="86" t="inlineStr">
+      <c r="F33" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G33" s="86" t="inlineStr">
+      <c r="G33" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H33" s="87" t="n">
+      <c r="H33" s="94" t="n">
         <v>382.4</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="86" t="inlineStr">
+      <c r="A34" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B34" s="86" t="inlineStr">
+      <c r="B34" s="93" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="C34" s="86" t="inlineStr">
+      <c r="C34" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D34" s="86" t="inlineStr">
+      <c r="D34" s="93" t="inlineStr">
         <is>
           <t>FAT.8910508</t>
         </is>
       </c>
-      <c r="E34" s="86" t="inlineStr">
+      <c r="E34" s="93" t="inlineStr">
         <is>
           <t>102706/1</t>
         </is>
       </c>
-      <c r="F34" s="86" t="inlineStr">
+      <c r="F34" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G34" s="86" t="inlineStr">
+      <c r="G34" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H34" s="87" t="n">
+      <c r="H34" s="94" t="n">
         <v>429.49</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="86" t="inlineStr">
+      <c r="A35" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B35" s="86" t="inlineStr">
+      <c r="B35" s="93" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="C35" s="86" t="inlineStr">
+      <c r="C35" s="93" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D35" s="86" t="inlineStr">
+      <c r="D35" s="93" t="inlineStr">
         <is>
           <t>NFS.351653</t>
         </is>
       </c>
-      <c r="E35" s="86" t="inlineStr">
+      <c r="E35" s="93" t="inlineStr">
         <is>
           <t>100083/1</t>
         </is>
       </c>
-      <c r="F35" s="86" t="inlineStr">
+      <c r="F35" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G35" s="86" t="inlineStr">
+      <c r="G35" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H35" s="87" t="n">
+      <c r="H35" s="94" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="86" t="inlineStr">
+      <c r="A36" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B36" s="86" t="inlineStr">
+      <c r="B36" s="93" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="C36" s="86" t="inlineStr">
+      <c r="C36" s="93" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D36" s="86" t="inlineStr">
+      <c r="D36" s="93" t="inlineStr">
         <is>
           <t>NFS.359396</t>
         </is>
       </c>
-      <c r="E36" s="86" t="inlineStr">
+      <c r="E36" s="93" t="inlineStr">
         <is>
           <t>102608/1</t>
         </is>
       </c>
-      <c r="F36" s="86" t="inlineStr">
+      <c r="F36" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G36" s="86" t="inlineStr">
+      <c r="G36" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H36" s="87" t="n">
+      <c r="H36" s="94" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="86" t="inlineStr">
+      <c r="A37" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B37" s="86" t="inlineStr">
+      <c r="B37" s="93" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="C37" s="86" t="inlineStr">
+      <c r="C37" s="93" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D37" s="86" t="inlineStr">
+      <c r="D37" s="93" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E37" s="86" t="inlineStr">
+      <c r="E37" s="93" t="inlineStr">
         <is>
           <t>95104/3</t>
         </is>
       </c>
-      <c r="F37" s="86" t="inlineStr">
+      <c r="F37" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G37" s="86" t="inlineStr">
+      <c r="G37" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H37" s="87" t="n">
+      <c r="H37" s="94" t="n">
         <v>111.38</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="86" t="inlineStr">
+      <c r="A38" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B38" s="86" t="inlineStr">
+      <c r="B38" s="93" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C38" s="86" t="inlineStr">
+      <c r="C38" s="93" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D38" s="86" t="inlineStr">
+      <c r="D38" s="93" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E38" s="86" t="inlineStr">
+      <c r="E38" s="93" t="inlineStr">
         <is>
           <t>95104/4</t>
         </is>
       </c>
-      <c r="F38" s="86" t="inlineStr">
+      <c r="F38" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G38" s="86" t="inlineStr">
+      <c r="G38" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H38" s="87" t="n">
+      <c r="H38" s="94" t="n">
         <v>210.38</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="86" t="inlineStr">
+      <c r="A39" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B39" s="86" t="inlineStr">
+      <c r="B39" s="93" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="C39" s="86" t="inlineStr">
+      <c r="C39" s="93" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D39" s="86" t="inlineStr">
+      <c r="D39" s="93" t="inlineStr">
         <is>
           <t>FAT.2024588614</t>
         </is>
       </c>
-      <c r="E39" s="86" t="inlineStr">
+      <c r="E39" s="93" t="inlineStr">
         <is>
           <t>102316/1</t>
         </is>
       </c>
-      <c r="F39" s="86" t="inlineStr">
+      <c r="F39" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G39" s="86" t="inlineStr">
+      <c r="G39" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H39" s="87" t="n">
+      <c r="H39" s="94" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="86" t="inlineStr">
+      <c r="A40" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B40" s="86" t="inlineStr">
+      <c r="B40" s="93" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C40" s="86" t="inlineStr">
+      <c r="C40" s="93" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D40" s="86" t="inlineStr">
+      <c r="D40" s="93" t="inlineStr">
         <is>
           <t>BOL.5708173302</t>
         </is>
       </c>
-      <c r="E40" s="86" t="inlineStr">
+      <c r="E40" s="93" t="inlineStr">
         <is>
           <t>102057/1</t>
         </is>
       </c>
-      <c r="F40" s="86" t="inlineStr">
+      <c r="F40" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G40" s="86" t="inlineStr">
+      <c r="G40" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H40" s="87" t="n">
+      <c r="H40" s="94" t="n">
         <v>284.63</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="86" t="inlineStr">
+      <c r="A41" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B41" s="86" t="inlineStr">
+      <c r="B41" s="93" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="C41" s="86" t="inlineStr">
+      <c r="C41" s="93" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D41" s="86" t="inlineStr">
+      <c r="D41" s="93" t="inlineStr">
         <is>
           <t>BOL.28049</t>
         </is>
       </c>
-      <c r="E41" s="86" t="inlineStr">
+      <c r="E41" s="93" t="inlineStr">
         <is>
           <t>100887/1</t>
         </is>
       </c>
-      <c r="F41" s="86" t="inlineStr">
+      <c r="F41" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G41" s="86" t="inlineStr">
+      <c r="G41" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H41" s="87" t="n">
+      <c r="H41" s="94" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="86" t="inlineStr">
+      <c r="A42" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B42" s="86" t="inlineStr">
+      <c r="B42" s="93" t="inlineStr">
         <is>
           <t>06/03/2026</t>
         </is>
       </c>
-      <c r="C42" s="86" t="inlineStr">
+      <c r="C42" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D42" s="86" t="inlineStr">
+      <c r="D42" s="93" t="inlineStr">
         <is>
           <t>SAL.SAL FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E42" s="86" t="inlineStr">
+      <c r="E42" s="93" t="inlineStr">
         <is>
           <t>101276/1</t>
         </is>
       </c>
-      <c r="F42" s="86" t="inlineStr">
+      <c r="F42" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G42" s="86" t="inlineStr">
+      <c r="G42" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H42" s="87" t="n">
+      <c r="H42" s="94" t="n">
         <v>1542</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="86" t="inlineStr">
+      <c r="A43" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B43" s="86" t="inlineStr">
+      <c r="B43" s="93" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C43" s="86" t="inlineStr">
+      <c r="C43" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D43" s="86" t="inlineStr">
+      <c r="D43" s="93" t="inlineStr">
         <is>
           <t>SAL.VALE 032026</t>
         </is>
       </c>
-      <c r="E43" s="86" t="inlineStr">
+      <c r="E43" s="93" t="inlineStr">
         <is>
           <t>102295/1</t>
         </is>
       </c>
-      <c r="F43" s="86" t="inlineStr">
+      <c r="F43" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G43" s="86" t="inlineStr">
+      <c r="G43" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H43" s="87" t="n">
+      <c r="H43" s="94" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="86" t="inlineStr">
+      <c r="A44" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B44" s="86" t="inlineStr">
+      <c r="B44" s="93" t="inlineStr">
         <is>
           <t>2026-03-20 00:00:00</t>
         </is>
       </c>
-      <c r="C44" s="86" t="inlineStr">
+      <c r="C44" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D44" s="86" t="inlineStr">
+      <c r="D44" s="93" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E44" s="86" t="inlineStr">
+      <c r="E44" s="93" t="inlineStr">
         <is>
           <t>113754/3</t>
         </is>
       </c>
-      <c r="F44" s="86" t="inlineStr">
+      <c r="F44" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G44" s="86" t="inlineStr">
+      <c r="G44" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H44" s="87" t="n">
+      <c r="H44" s="94" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="86" t="inlineStr">
+      <c r="A45" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B45" s="86" t="inlineStr">
+      <c r="B45" s="93" t="inlineStr">
         <is>
           <t>2026-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="C45" s="86" t="inlineStr">
+      <c r="C45" s="93" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D45" s="86" t="inlineStr"/>
-      <c r="E45" s="86" t="inlineStr"/>
-      <c r="F45" s="86" t="inlineStr">
+      <c r="D45" s="93" t="inlineStr"/>
+      <c r="E45" s="93" t="inlineStr"/>
+      <c r="F45" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G45" s="86" t="inlineStr">
+      <c r="G45" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H45" s="87" t="n">
+      <c r="H45" s="94" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="86" t="inlineStr">
+      <c r="A46" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B46" s="86" t="inlineStr">
+      <c r="B46" s="93" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C46" s="86" t="inlineStr">
+      <c r="C46" s="93" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D46" s="86" t="inlineStr">
+      <c r="D46" s="93" t="inlineStr">
         <is>
           <t>NFS.1500</t>
         </is>
       </c>
-      <c r="E46" s="86" t="inlineStr">
+      <c r="E46" s="93" t="inlineStr">
         <is>
           <t>102432/1</t>
         </is>
       </c>
-      <c r="F46" s="86" t="inlineStr">
+      <c r="F46" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G46" s="86" t="inlineStr">
+      <c r="G46" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H46" s="87" t="n">
+      <c r="H46" s="94" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="86" t="inlineStr">
+      <c r="A47" s="93" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B47" s="86" t="inlineStr">
+      <c r="B47" s="93" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C47" s="86" t="inlineStr">
+      <c r="C47" s="93" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D47" s="86" t="inlineStr">
+      <c r="D47" s="93" t="inlineStr">
         <is>
           <t>NFS.1534</t>
         </is>
       </c>
-      <c r="E47" s="86" t="inlineStr">
+      <c r="E47" s="93" t="inlineStr">
         <is>
           <t>102434/1</t>
         </is>
       </c>
-      <c r="F47" s="86" t="inlineStr">
+      <c r="F47" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G47" s="86" t="inlineStr">
+      <c r="G47" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H47" s="87" t="n">
+      <c r="H47" s="94" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="86" t="inlineStr">
+      <c r="A48" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B48" s="86" t="inlineStr">
+      <c r="B48" s="93" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C48" s="86" t="inlineStr">
+      <c r="C48" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D48" s="86" t="inlineStr">
+      <c r="D48" s="93" t="inlineStr">
         <is>
           <t>FAT.8910315</t>
         </is>
       </c>
-      <c r="E48" s="86" t="inlineStr">
+      <c r="E48" s="93" t="inlineStr">
         <is>
           <t>105607/1</t>
         </is>
       </c>
-      <c r="F48" s="86" t="inlineStr">
+      <c r="F48" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G48" s="86" t="inlineStr">
+      <c r="G48" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H48" s="87" t="n">
+      <c r="H48" s="94" t="n">
         <v>11.99</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="86" t="inlineStr">
+      <c r="A49" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B49" s="86" t="inlineStr">
+      <c r="B49" s="93" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C49" s="86" t="inlineStr">
+      <c r="C49" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D49" s="86" t="inlineStr">
+      <c r="D49" s="93" t="inlineStr">
         <is>
           <t>FAT.13443658</t>
         </is>
       </c>
-      <c r="E49" s="86" t="inlineStr">
+      <c r="E49" s="93" t="inlineStr">
         <is>
           <t>105676/1</t>
         </is>
       </c>
-      <c r="F49" s="86" t="inlineStr">
+      <c r="F49" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G49" s="86" t="inlineStr">
+      <c r="G49" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H49" s="87" t="n">
+      <c r="H49" s="94" t="n">
         <v>557.63</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="86" t="inlineStr">
+      <c r="A50" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B50" s="86" t="inlineStr">
+      <c r="B50" s="93" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C50" s="86" t="inlineStr">
+      <c r="C50" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D50" s="86" t="inlineStr">
+      <c r="D50" s="93" t="inlineStr">
         <is>
           <t>FAT.13443664</t>
         </is>
       </c>
-      <c r="E50" s="86" t="inlineStr">
+      <c r="E50" s="93" t="inlineStr">
         <is>
           <t>105677/1</t>
         </is>
       </c>
-      <c r="F50" s="86" t="inlineStr">
+      <c r="F50" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G50" s="86" t="inlineStr">
+      <c r="G50" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H50" s="87" t="n">
+      <c r="H50" s="94" t="n">
         <v>132.09</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="86" t="inlineStr">
+      <c r="A51" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B51" s="86" t="inlineStr">
+      <c r="B51" s="93" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C51" s="86" t="inlineStr">
+      <c r="C51" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D51" s="86" t="inlineStr">
+      <c r="D51" s="93" t="inlineStr">
         <is>
           <t>FAT.13443112</t>
         </is>
       </c>
-      <c r="E51" s="86" t="inlineStr">
+      <c r="E51" s="93" t="inlineStr">
         <is>
           <t>105792/1</t>
         </is>
       </c>
-      <c r="F51" s="86" t="inlineStr">
+      <c r="F51" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G51" s="86" t="inlineStr">
+      <c r="G51" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H51" s="87" t="n">
+      <c r="H51" s="94" t="n">
         <v>20.23</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="86" t="inlineStr">
+      <c r="A52" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B52" s="86" t="inlineStr">
+      <c r="B52" s="93" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C52" s="86" t="inlineStr">
+      <c r="C52" s="93" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D52" s="86" t="inlineStr">
+      <c r="D52" s="93" t="inlineStr">
         <is>
           <t>NFS.363799</t>
         </is>
       </c>
-      <c r="E52" s="86" t="inlineStr">
+      <c r="E52" s="93" t="inlineStr">
         <is>
           <t>104634/1</t>
         </is>
       </c>
-      <c r="F52" s="86" t="inlineStr">
+      <c r="F52" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G52" s="86" t="inlineStr">
+      <c r="G52" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H52" s="87" t="n">
+      <c r="H52" s="94" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="86" t="inlineStr">
+      <c r="A53" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B53" s="86" t="inlineStr">
+      <c r="B53" s="93" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="C53" s="86" t="inlineStr">
+      <c r="C53" s="93" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D53" s="86" t="inlineStr">
+      <c r="D53" s="93" t="inlineStr">
         <is>
           <t>BOL.04.26</t>
         </is>
       </c>
-      <c r="E53" s="86" t="inlineStr">
+      <c r="E53" s="93" t="inlineStr">
         <is>
           <t>104820/1</t>
         </is>
       </c>
-      <c r="F53" s="86" t="inlineStr">
+      <c r="F53" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G53" s="86" t="inlineStr">
+      <c r="G53" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H53" s="87" t="n">
+      <c r="H53" s="94" t="n">
         <v>1024.76</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="86" t="inlineStr">
+      <c r="A54" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B54" s="86" t="inlineStr">
+      <c r="B54" s="93" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C54" s="86" t="inlineStr">
+      <c r="C54" s="93" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D54" s="86" t="inlineStr">
+      <c r="D54" s="93" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 29.04.26</t>
         </is>
       </c>
-      <c r="E54" s="86" t="inlineStr">
+      <c r="E54" s="93" t="inlineStr">
         <is>
           <t>106325/1</t>
         </is>
       </c>
-      <c r="F54" s="86" t="inlineStr">
+      <c r="F54" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G54" s="86" t="inlineStr">
+      <c r="G54" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H54" s="87" t="n">
+      <c r="H54" s="94" t="n">
         <v>21.76</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="86" t="inlineStr">
+      <c r="A55" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B55" s="86" t="inlineStr">
+      <c r="B55" s="93" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C55" s="86" t="inlineStr">
+      <c r="C55" s="93" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D55" s="86" t="inlineStr">
+      <c r="D55" s="93" t="inlineStr">
         <is>
           <t>FAT.CHATGPT 3 LIC</t>
         </is>
       </c>
-      <c r="E55" s="86" t="inlineStr">
+      <c r="E55" s="93" t="inlineStr">
         <is>
           <t>102137/1</t>
         </is>
       </c>
-      <c r="F55" s="86" t="inlineStr">
+      <c r="F55" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G55" s="86" t="inlineStr">
+      <c r="G55" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H55" s="87" t="n">
+      <c r="H55" s="94" t="n">
         <v>5393.88</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="86" t="inlineStr">
+      <c r="A56" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B56" s="86" t="inlineStr">
+      <c r="B56" s="93" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C56" s="86" t="inlineStr">
+      <c r="C56" s="93" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D56" s="86" t="inlineStr">
+      <c r="D56" s="93" t="inlineStr">
         <is>
           <t>BOL.28855</t>
         </is>
       </c>
-      <c r="E56" s="86" t="inlineStr">
+      <c r="E56" s="93" t="inlineStr">
         <is>
           <t>103694/1</t>
         </is>
       </c>
-      <c r="F56" s="86" t="inlineStr">
+      <c r="F56" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G56" s="86" t="inlineStr">
+      <c r="G56" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H56" s="87" t="n">
+      <c r="H56" s="94" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="86" t="inlineStr">
+      <c r="A57" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B57" s="86" t="inlineStr">
+      <c r="B57" s="93" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="C57" s="86" t="inlineStr">
+      <c r="C57" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D57" s="86" t="inlineStr">
+      <c r="D57" s="93" t="inlineStr">
         <is>
           <t>SAL.SAL 032026</t>
         </is>
       </c>
-      <c r="E57" s="86" t="inlineStr">
+      <c r="E57" s="93" t="inlineStr">
         <is>
           <t>103924/1</t>
         </is>
       </c>
-      <c r="F57" s="86" t="inlineStr">
+      <c r="F57" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G57" s="86" t="inlineStr">
+      <c r="G57" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H57" s="87" t="n">
+      <c r="H57" s="94" t="n">
         <v>1515</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="86" t="inlineStr">
+      <c r="A58" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B58" s="86" t="inlineStr">
+      <c r="B58" s="93" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="C58" s="86" t="inlineStr">
+      <c r="C58" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D58" s="86" t="inlineStr">
+      <c r="D58" s="93" t="inlineStr">
         <is>
           <t>SAL.vale 042026</t>
         </is>
       </c>
-      <c r="E58" s="86" t="inlineStr">
+      <c r="E58" s="93" t="inlineStr">
         <is>
           <t>105055/1</t>
         </is>
       </c>
-      <c r="F58" s="86" t="inlineStr">
+      <c r="F58" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G58" s="86" t="inlineStr">
+      <c r="G58" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H58" s="87" t="n">
+      <c r="H58" s="94" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="86" t="inlineStr">
+      <c r="A59" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B59" s="86" t="inlineStr">
+      <c r="B59" s="93" t="inlineStr">
         <is>
           <t>2026-04-20 00:00:00</t>
         </is>
       </c>
-      <c r="C59" s="86" t="inlineStr">
+      <c r="C59" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D59" s="86" t="inlineStr">
+      <c r="D59" s="93" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E59" s="86" t="inlineStr">
+      <c r="E59" s="93" t="inlineStr">
         <is>
           <t>113754/4</t>
         </is>
       </c>
-      <c r="F59" s="86" t="inlineStr">
+      <c r="F59" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G59" s="86" t="inlineStr">
+      <c r="G59" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H59" s="87" t="n">
+      <c r="H59" s="94" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="86" t="inlineStr">
+      <c r="A60" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B60" s="86" t="inlineStr">
+      <c r="B60" s="93" t="inlineStr">
         <is>
           <t>2026-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="C60" s="86" t="inlineStr">
+      <c r="C60" s="93" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D60" s="86" t="inlineStr"/>
-      <c r="E60" s="86" t="inlineStr"/>
-      <c r="F60" s="86" t="inlineStr">
+      <c r="D60" s="93" t="inlineStr"/>
+      <c r="E60" s="93" t="inlineStr"/>
+      <c r="F60" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G60" s="86" t="inlineStr">
+      <c r="G60" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H60" s="87" t="n">
+      <c r="H60" s="94" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="86" t="inlineStr">
+      <c r="A61" s="93" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B61" s="86" t="inlineStr">
+      <c r="B61" s="93" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="C61" s="86" t="inlineStr">
+      <c r="C61" s="93" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D61" s="86" t="inlineStr">
+      <c r="D61" s="93" t="inlineStr">
         <is>
           <t>NFS.1573</t>
         </is>
       </c>
-      <c r="E61" s="86" t="inlineStr">
+      <c r="E61" s="93" t="inlineStr">
         <is>
           <t>105411/1</t>
         </is>
       </c>
-      <c r="F61" s="86" t="inlineStr">
+      <c r="F61" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G61" s="86" t="inlineStr">
+      <c r="G61" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H61" s="87" t="n">
+      <c r="H61" s="94" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="86" t="inlineStr">
+      <c r="A62" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B62" s="86" t="inlineStr">
+      <c r="B62" s="93" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="C62" s="86" t="inlineStr">
+      <c r="C62" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D62" s="86" t="inlineStr">
+      <c r="D62" s="93" t="inlineStr">
         <is>
           <t>FAT.2ªvia Claro Abril</t>
         </is>
       </c>
-      <c r="E62" s="86" t="inlineStr">
+      <c r="E62" s="93" t="inlineStr">
         <is>
           <t>107340/1</t>
         </is>
       </c>
-      <c r="F62" s="86" t="inlineStr">
+      <c r="F62" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G62" s="86" t="inlineStr">
+      <c r="G62" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H62" s="87" t="n">
+      <c r="H62" s="94" t="n">
         <v>182.32</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="86" t="inlineStr">
+      <c r="A63" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B63" s="86" t="inlineStr">
+      <c r="B63" s="93" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C63" s="86" t="inlineStr">
+      <c r="C63" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D63" s="86" t="inlineStr">
+      <c r="D63" s="93" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E63" s="86" t="inlineStr">
+      <c r="E63" s="93" t="inlineStr">
         <is>
           <t>108218/1</t>
         </is>
       </c>
-      <c r="F63" s="86" t="inlineStr">
+      <c r="F63" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G63" s="86" t="inlineStr">
+      <c r="G63" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H63" s="87" t="n">
+      <c r="H63" s="94" t="n">
         <v>629.98</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="86" t="inlineStr">
+      <c r="A64" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B64" s="86" t="inlineStr">
+      <c r="B64" s="93" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C64" s="86" t="inlineStr">
+      <c r="C64" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D64" s="86" t="inlineStr">
+      <c r="D64" s="93" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E64" s="86" t="inlineStr">
+      <c r="E64" s="93" t="inlineStr">
         <is>
           <t>108218/2</t>
         </is>
       </c>
-      <c r="F64" s="86" t="inlineStr">
+      <c r="F64" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G64" s="86" t="inlineStr">
+      <c r="G64" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H64" s="87" t="n">
+      <c r="H64" s="94" t="n">
         <v>18.86</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="86" t="inlineStr">
+      <c r="A65" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B65" s="86" t="inlineStr">
+      <c r="B65" s="93" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C65" s="86" t="inlineStr">
+      <c r="C65" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D65" s="86" t="inlineStr">
+      <c r="D65" s="93" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E65" s="86" t="inlineStr">
+      <c r="E65" s="93" t="inlineStr">
         <is>
           <t>108218/3</t>
         </is>
       </c>
-      <c r="F65" s="86" t="inlineStr">
+      <c r="F65" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G65" s="86" t="inlineStr">
+      <c r="G65" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H65" s="87" t="n">
+      <c r="H65" s="94" t="n">
         <v>133.95</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="86" t="inlineStr">
+      <c r="A66" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B66" s="86" t="inlineStr">
+      <c r="B66" s="93" t="inlineStr">
         <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="C66" s="86" t="inlineStr">
+      <c r="C66" s="93" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D66" s="86" t="inlineStr">
+      <c r="D66" s="93" t="inlineStr">
         <is>
           <t>NFS.76</t>
         </is>
       </c>
-      <c r="E66" s="86" t="inlineStr">
+      <c r="E66" s="93" t="inlineStr">
         <is>
           <t>105987/1</t>
         </is>
       </c>
-      <c r="F66" s="86" t="inlineStr">
+      <c r="F66" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G66" s="86" t="inlineStr">
+      <c r="G66" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H66" s="87" t="n">
+      <c r="H66" s="94" t="n">
         <v>3723.62</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="86" t="inlineStr">
+      <c r="A67" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B67" s="86" t="inlineStr">
+      <c r="B67" s="93" t="inlineStr">
         <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="C67" s="86" t="inlineStr">
+      <c r="C67" s="93" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D67" s="86" t="inlineStr">
+      <c r="D67" s="93" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 11.05.26</t>
         </is>
       </c>
-      <c r="E67" s="86" t="inlineStr">
+      <c r="E67" s="93" t="inlineStr">
         <is>
           <t>107254/1</t>
         </is>
       </c>
-      <c r="F67" s="86" t="inlineStr">
+      <c r="F67" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G67" s="86" t="inlineStr">
+      <c r="G67" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H67" s="87" t="n">
+      <c r="H67" s="94" t="n">
         <v>74.81</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="86" t="inlineStr">
+      <c r="A68" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B68" s="86" t="inlineStr">
+      <c r="B68" s="93" t="inlineStr">
         <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="C68" s="86" t="inlineStr">
+      <c r="C68" s="93" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D68" s="86" t="inlineStr">
+      <c r="D68" s="93" t="inlineStr">
         <is>
           <t>NFS.5744</t>
         </is>
       </c>
-      <c r="E68" s="86" t="inlineStr">
+      <c r="E68" s="93" t="inlineStr">
         <is>
           <t>106664/1</t>
         </is>
       </c>
-      <c r="F68" s="86" t="inlineStr">
+      <c r="F68" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G68" s="86" t="inlineStr">
+      <c r="G68" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H68" s="87" t="n">
+      <c r="H68" s="94" t="n">
         <v>741.1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="86" t="inlineStr">
+      <c r="A69" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B69" s="86" t="inlineStr">
+      <c r="B69" s="93" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C69" s="86" t="inlineStr">
+      <c r="C69" s="93" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D69" s="86" t="inlineStr">
+      <c r="D69" s="93" t="inlineStr">
         <is>
           <t>BOL.29637</t>
         </is>
       </c>
-      <c r="E69" s="86" t="inlineStr">
+      <c r="E69" s="93" t="inlineStr">
         <is>
           <t>108040/1</t>
         </is>
       </c>
-      <c r="F69" s="86" t="inlineStr">
+      <c r="F69" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G69" s="86" t="inlineStr">
+      <c r="G69" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H69" s="87" t="n">
+      <c r="H69" s="94" t="n">
         <v>137.92</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="86" t="inlineStr">
+      <c r="A70" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B70" s="86" t="inlineStr">
+      <c r="B70" s="93" t="inlineStr">
         <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="C70" s="86" t="inlineStr">
+      <c r="C70" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D70" s="86" t="inlineStr">
+      <c r="D70" s="93" t="inlineStr">
         <is>
           <t>SAL.sal 042026</t>
         </is>
       </c>
-      <c r="E70" s="86" t="inlineStr">
+      <c r="E70" s="93" t="inlineStr">
         <is>
           <t>106947/1</t>
         </is>
       </c>
-      <c r="F70" s="86" t="inlineStr">
+      <c r="F70" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G70" s="86" t="inlineStr">
+      <c r="G70" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H70" s="87" t="n">
+      <c r="H70" s="94" t="n">
         <v>1483</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="86" t="inlineStr">
+      <c r="A71" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B71" s="86" t="inlineStr">
+      <c r="B71" s="93" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="C71" s="86" t="inlineStr">
+      <c r="C71" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D71" s="86" t="inlineStr">
+      <c r="D71" s="93" t="inlineStr">
         <is>
           <t>SAL.vale 052026</t>
         </is>
       </c>
-      <c r="E71" s="86" t="inlineStr">
+      <c r="E71" s="93" t="inlineStr">
         <is>
           <t>108156/1</t>
         </is>
       </c>
-      <c r="F71" s="86" t="inlineStr">
+      <c r="F71" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G71" s="86" t="inlineStr">
+      <c r="G71" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H71" s="87" t="n">
+      <c r="H71" s="94" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="86" t="inlineStr">
+      <c r="A72" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B72" s="86" t="inlineStr">
+      <c r="B72" s="93" t="inlineStr">
         <is>
           <t>2026-05-20 00:00:00</t>
         </is>
       </c>
-      <c r="C72" s="86" t="inlineStr">
+      <c r="C72" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D72" s="86" t="inlineStr">
+      <c r="D72" s="93" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E72" s="86" t="inlineStr">
+      <c r="E72" s="93" t="inlineStr">
         <is>
           <t>113754/5</t>
         </is>
       </c>
-      <c r="F72" s="86" t="inlineStr">
+      <c r="F72" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G72" s="86" t="inlineStr">
+      <c r="G72" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H72" s="87" t="n">
+      <c r="H72" s="94" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="86" t="inlineStr">
+      <c r="A73" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B73" s="86" t="inlineStr">
+      <c r="B73" s="93" t="inlineStr">
         <is>
           <t>2026-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="C73" s="86" t="inlineStr">
+      <c r="C73" s="93" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D73" s="86" t="inlineStr"/>
-      <c r="E73" s="86" t="inlineStr"/>
-      <c r="F73" s="86" t="inlineStr">
+      <c r="D73" s="93" t="inlineStr"/>
+      <c r="E73" s="93" t="inlineStr"/>
+      <c r="F73" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G73" s="86" t="inlineStr">
+      <c r="G73" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H73" s="87" t="n">
+      <c r="H73" s="94" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="86" t="inlineStr">
+      <c r="A74" s="93" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B74" s="86" t="inlineStr">
+      <c r="B74" s="93" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C74" s="86" t="inlineStr">
+      <c r="C74" s="93" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D74" s="86" t="inlineStr">
+      <c r="D74" s="93" t="inlineStr">
         <is>
           <t>NFS.1631</t>
         </is>
       </c>
-      <c r="E74" s="86" t="inlineStr">
+      <c r="E74" s="93" t="inlineStr">
         <is>
           <t>107973/1</t>
         </is>
       </c>
-      <c r="F74" s="86" t="inlineStr">
+      <c r="F74" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G74" s="86" t="inlineStr">
+      <c r="G74" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H74" s="87" t="n">
+      <c r="H74" s="94" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="86" t="inlineStr">
+      <c r="A75" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B75" s="86" t="inlineStr">
+      <c r="B75" s="93" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C75" s="86" t="inlineStr">
+      <c r="C75" s="93" t="inlineStr">
         <is>
           <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
         </is>
       </c>
-      <c r="D75" s="86" t="inlineStr">
+      <c r="D75" s="93" t="inlineStr">
         <is>
           <t>AV.1015392</t>
         </is>
       </c>
-      <c r="E75" s="86" t="inlineStr">
+      <c r="E75" s="93" t="inlineStr">
         <is>
           <t>108925/1</t>
         </is>
       </c>
-      <c r="F75" s="86" t="inlineStr">
+      <c r="F75" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G75" s="86" t="inlineStr">
+      <c r="G75" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H75" s="87" t="n">
+      <c r="H75" s="94" t="n">
         <v>183.6</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="86" t="inlineStr">
+      <c r="A76" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B76" s="86" t="inlineStr">
+      <c r="B76" s="93" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C76" s="86" t="inlineStr">
+      <c r="C76" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D76" s="86" t="inlineStr">
+      <c r="D76" s="93" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E76" s="86" t="inlineStr">
+      <c r="E76" s="93" t="inlineStr">
         <is>
           <t>111124/1</t>
         </is>
       </c>
-      <c r="F76" s="86" t="inlineStr">
+      <c r="F76" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G76" s="86" t="inlineStr">
+      <c r="G76" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H76" s="87" t="n">
+      <c r="H76" s="94" t="n">
         <v>720</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="86" t="inlineStr">
+      <c r="A77" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B77" s="86" t="inlineStr">
+      <c r="B77" s="93" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C77" s="86" t="inlineStr">
+      <c r="C77" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D77" s="86" t="inlineStr">
+      <c r="D77" s="93" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E77" s="86" t="inlineStr">
+      <c r="E77" s="93" t="inlineStr">
         <is>
           <t>111124/3</t>
         </is>
       </c>
-      <c r="F77" s="86" t="inlineStr">
+      <c r="F77" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G77" s="86" t="inlineStr">
+      <c r="G77" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H77" s="87" t="n">
+      <c r="H77" s="94" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="86" t="inlineStr">
+      <c r="A78" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B78" s="86" t="inlineStr">
+      <c r="B78" s="93" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C78" s="86" t="inlineStr">
+      <c r="C78" s="93" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D78" s="86" t="inlineStr">
+      <c r="D78" s="93" t="inlineStr">
         <is>
           <t>NFS.373725</t>
         </is>
       </c>
-      <c r="E78" s="86" t="inlineStr">
+      <c r="E78" s="93" t="inlineStr">
         <is>
           <t>110785/1</t>
         </is>
       </c>
-      <c r="F78" s="86" t="inlineStr">
+      <c r="F78" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G78" s="86" t="inlineStr">
+      <c r="G78" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H78" s="87" t="n">
+      <c r="H78" s="94" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="86" t="inlineStr">
+      <c r="A79" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B79" s="86" t="inlineStr">
+      <c r="B79" s="93" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C79" s="86" t="inlineStr">
+      <c r="C79" s="93" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D79" s="86" t="inlineStr">
+      <c r="D79" s="93" t="inlineStr">
         <is>
           <t>NFS.0036884701</t>
         </is>
       </c>
-      <c r="E79" s="86" t="inlineStr">
+      <c r="E79" s="93" t="inlineStr">
         <is>
           <t>109295/1</t>
         </is>
       </c>
-      <c r="F79" s="86" t="inlineStr">
+      <c r="F79" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G79" s="86" t="inlineStr">
+      <c r="G79" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H79" s="87" t="n">
+      <c r="H79" s="94" t="n">
         <v>84.81999999999999</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="86" t="inlineStr">
+      <c r="A80" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B80" s="86" t="inlineStr">
+      <c r="B80" s="93" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C80" s="86" t="inlineStr">
+      <c r="C80" s="93" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D80" s="86" t="inlineStr">
+      <c r="D80" s="93" t="inlineStr">
         <is>
           <t>NFS.78</t>
         </is>
       </c>
-      <c r="E80" s="86" t="inlineStr">
+      <c r="E80" s="93" t="inlineStr">
         <is>
           <t>108317/1</t>
         </is>
       </c>
-      <c r="F80" s="86" t="inlineStr">
+      <c r="F80" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G80" s="86" t="inlineStr">
+      <c r="G80" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H80" s="87" t="n">
+      <c r="H80" s="94" t="n">
         <v>6173.37</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="86" t="inlineStr">
+      <c r="A81" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B81" s="86" t="inlineStr">
+      <c r="B81" s="93" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="C81" s="86" t="inlineStr">
+      <c r="C81" s="93" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D81" s="86" t="inlineStr">
+      <c r="D81" s="93" t="inlineStr">
         <is>
           <t>NFS.5832</t>
         </is>
       </c>
-      <c r="E81" s="86" t="inlineStr">
+      <c r="E81" s="93" t="inlineStr">
         <is>
           <t>109227/1</t>
         </is>
       </c>
-      <c r="F81" s="86" t="inlineStr">
+      <c r="F81" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G81" s="86" t="inlineStr">
+      <c r="G81" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H81" s="87" t="n">
+      <c r="H81" s="94" t="n">
         <v>740.38</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="86" t="inlineStr">
+      <c r="A82" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B82" s="86" t="inlineStr">
+      <c r="B82" s="93" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C82" s="86" t="inlineStr">
+      <c r="C82" s="93" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D82" s="86" t="inlineStr">
+      <c r="D82" s="93" t="inlineStr">
         <is>
           <t>FAT.Vivo 04 2026</t>
         </is>
       </c>
-      <c r="E82" s="86" t="inlineStr">
+      <c r="E82" s="93" t="inlineStr">
         <is>
           <t>110752/1</t>
         </is>
       </c>
-      <c r="F82" s="86" t="inlineStr">
+      <c r="F82" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G82" s="86" t="inlineStr">
+      <c r="G82" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H82" s="87" t="n">
+      <c r="H82" s="94" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="86" t="inlineStr">
+      <c r="A83" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B83" s="86" t="inlineStr">
+      <c r="B83" s="93" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C83" s="86" t="inlineStr">
+      <c r="C83" s="93" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D83" s="86" t="inlineStr">
+      <c r="D83" s="93" t="inlineStr">
         <is>
           <t>FAT.Vivo 05 2026</t>
         </is>
       </c>
-      <c r="E83" s="86" t="inlineStr">
+      <c r="E83" s="93" t="inlineStr">
         <is>
           <t>110753/1</t>
         </is>
       </c>
-      <c r="F83" s="86" t="inlineStr">
+      <c r="F83" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G83" s="86" t="inlineStr">
+      <c r="G83" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H83" s="87" t="n">
+      <c r="H83" s="94" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="86" t="inlineStr">
+      <c r="A84" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B84" s="86" t="inlineStr">
+      <c r="B84" s="93" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C84" s="86" t="inlineStr">
+      <c r="C84" s="93" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D84" s="86" t="inlineStr">
+      <c r="D84" s="93" t="inlineStr">
         <is>
           <t>FAT.Vivo 06 2026</t>
         </is>
       </c>
-      <c r="E84" s="86" t="inlineStr">
+      <c r="E84" s="93" t="inlineStr">
         <is>
           <t>110754/1</t>
         </is>
       </c>
-      <c r="F84" s="86" t="inlineStr">
+      <c r="F84" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G84" s="86" t="inlineStr">
+      <c r="G84" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H84" s="87" t="n">
+      <c r="H84" s="94" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="86" t="inlineStr">
+      <c r="A85" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B85" s="86" t="inlineStr">
+      <c r="B85" s="93" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C85" s="86" t="inlineStr">
+      <c r="C85" s="93" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D85" s="86" t="inlineStr">
+      <c r="D85" s="93" t="inlineStr">
         <is>
           <t>BOL.1017717992</t>
         </is>
       </c>
-      <c r="E85" s="86" t="inlineStr">
+      <c r="E85" s="93" t="inlineStr">
         <is>
           <t>109298/1</t>
         </is>
       </c>
-      <c r="F85" s="86" t="inlineStr">
+      <c r="F85" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G85" s="86" t="inlineStr">
+      <c r="G85" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H85" s="87" t="n">
+      <c r="H85" s="94" t="n">
         <v>137.93</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="86" t="inlineStr">
+      <c r="A86" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B86" s="86" t="inlineStr">
+      <c r="B86" s="93" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C86" s="86" t="inlineStr">
+      <c r="C86" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D86" s="86" t="inlineStr">
+      <c r="D86" s="93" t="inlineStr">
         <is>
           <t>CX.27.05.26</t>
         </is>
       </c>
-      <c r="E86" s="86" t="inlineStr">
+      <c r="E86" s="93" t="inlineStr">
         <is>
           <t>108827/1</t>
         </is>
       </c>
-      <c r="F86" s="86" t="inlineStr">
+      <c r="F86" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G86" s="86" t="inlineStr">
+      <c r="G86" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H86" s="87" t="n">
+      <c r="H86" s="94" t="n">
         <v>184</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="86" t="inlineStr">
+      <c r="A87" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B87" s="86" t="inlineStr">
+      <c r="B87" s="93" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C87" s="86" t="inlineStr">
+      <c r="C87" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D87" s="86" t="inlineStr">
+      <c r="D87" s="93" t="inlineStr">
         <is>
           <t>SAL.1_ Ferias 1 VIn D 26</t>
         </is>
       </c>
-      <c r="E87" s="86" t="inlineStr">
+      <c r="E87" s="93" t="inlineStr">
         <is>
           <t>107780/1</t>
         </is>
       </c>
-      <c r="F87" s="86" t="inlineStr">
+      <c r="F87" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G87" s="86" t="inlineStr">
+      <c r="G87" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H87" s="87" t="n">
+      <c r="H87" s="94" t="n">
         <v>1101.12</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="86" t="inlineStr">
+      <c r="A88" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B88" s="86" t="inlineStr">
+      <c r="B88" s="93" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C88" s="86" t="inlineStr">
+      <c r="C88" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D88" s="86" t="inlineStr">
+      <c r="D88" s="93" t="inlineStr">
         <is>
           <t>SAL.sal 052026</t>
         </is>
       </c>
-      <c r="E88" s="86" t="inlineStr">
+      <c r="E88" s="93" t="inlineStr">
         <is>
           <t>109482/1</t>
         </is>
       </c>
-      <c r="F88" s="86" t="inlineStr">
+      <c r="F88" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G88" s="86" t="inlineStr">
+      <c r="G88" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H88" s="87" t="n">
+      <c r="H88" s="94" t="n">
         <v>1455</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="86" t="inlineStr">
+      <c r="A89" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B89" s="86" t="inlineStr">
+      <c r="B89" s="93" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C89" s="86" t="inlineStr">
+      <c r="C89" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D89" s="86" t="inlineStr">
+      <c r="D89" s="93" t="inlineStr">
         <is>
           <t>SAL.SALARIO06VINI</t>
         </is>
       </c>
-      <c r="E89" s="86" t="inlineStr">
+      <c r="E89" s="93" t="inlineStr">
         <is>
           <t>110700/1</t>
         </is>
       </c>
-      <c r="F89" s="86" t="inlineStr">
+      <c r="F89" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G89" s="86" t="inlineStr">
+      <c r="G89" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H89" s="87" t="n">
+      <c r="H89" s="94" t="n">
         <v>686</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="86" t="inlineStr">
+      <c r="A90" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B90" s="86" t="inlineStr">
+      <c r="B90" s="93" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="C90" s="86" t="inlineStr">
+      <c r="C90" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D90" s="86" t="inlineStr">
+      <c r="D90" s="93" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E90" s="86" t="inlineStr">
+      <c r="E90" s="93" t="inlineStr">
         <is>
           <t>113754/6</t>
         </is>
       </c>
-      <c r="F90" s="86" t="inlineStr">
+      <c r="F90" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G90" s="86" t="inlineStr">
+      <c r="G90" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H90" s="87" t="n">
+      <c r="H90" s="94" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="86" t="inlineStr">
+      <c r="A91" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B91" s="86" t="inlineStr">
+      <c r="B91" s="93" t="inlineStr">
         <is>
           <t>2026-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="C91" s="86" t="inlineStr">
+      <c r="C91" s="93" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D91" s="86" t="inlineStr"/>
-      <c r="E91" s="86" t="inlineStr"/>
-      <c r="F91" s="86" t="inlineStr">
+      <c r="D91" s="93" t="inlineStr"/>
+      <c r="E91" s="93" t="inlineStr"/>
+      <c r="F91" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G91" s="86" t="inlineStr">
+      <c r="G91" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H91" s="87" t="n">
+      <c r="H91" s="94" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="86" t="inlineStr">
+      <c r="A92" s="93" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B92" s="86" t="inlineStr">
+      <c r="B92" s="93" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C92" s="86" t="inlineStr">
+      <c r="C92" s="93" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D92" s="86" t="inlineStr">
+      <c r="D92" s="93" t="inlineStr">
         <is>
           <t>NFS.33</t>
         </is>
       </c>
-      <c r="E92" s="86" t="inlineStr">
+      <c r="E92" s="93" t="inlineStr">
         <is>
           <t>110902/1</t>
         </is>
       </c>
-      <c r="F92" s="86" t="inlineStr">
+      <c r="F92" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G92" s="86" t="inlineStr">
+      <c r="G92" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H92" s="87" t="n">
+      <c r="H92" s="94" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="86" t="inlineStr">
+      <c r="A93" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B93" s="86" t="inlineStr">
+      <c r="B93" s="93" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C93" s="86" t="inlineStr">
+      <c r="C93" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D93" s="86" t="inlineStr">
+      <c r="D93" s="93" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E93" s="86" t="inlineStr">
+      <c r="E93" s="93" t="inlineStr">
         <is>
           <t>113575/1</t>
         </is>
       </c>
-      <c r="F93" s="86" t="inlineStr">
+      <c r="F93" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G93" s="86" t="inlineStr">
+      <c r="G93" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H93" s="87" t="n">
+      <c r="H93" s="94" t="n">
         <v>20.39</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="86" t="inlineStr">
+      <c r="A94" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B94" s="86" t="inlineStr">
+      <c r="B94" s="93" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C94" s="86" t="inlineStr">
+      <c r="C94" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D94" s="86" t="inlineStr">
+      <c r="D94" s="93" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E94" s="86" t="inlineStr">
+      <c r="E94" s="93" t="inlineStr">
         <is>
           <t>113575/2</t>
         </is>
       </c>
-      <c r="F94" s="86" t="inlineStr">
+      <c r="F94" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G94" s="86" t="inlineStr">
+      <c r="G94" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H94" s="87" t="n">
+      <c r="H94" s="94" t="n">
         <v>133.73</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="86" t="inlineStr">
+      <c r="A95" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B95" s="86" t="inlineStr">
+      <c r="B95" s="93" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C95" s="86" t="inlineStr">
+      <c r="C95" s="93" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D95" s="86" t="inlineStr">
+      <c r="D95" s="93" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E95" s="86" t="inlineStr">
+      <c r="E95" s="93" t="inlineStr">
         <is>
           <t>113575/3</t>
         </is>
       </c>
-      <c r="F95" s="86" t="inlineStr">
+      <c r="F95" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G95" s="86" t="inlineStr">
+      <c r="G95" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H95" s="87" t="n">
+      <c r="H95" s="94" t="n">
         <v>825.28</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="86" t="inlineStr">
+      <c r="A96" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B96" s="86" t="inlineStr">
+      <c r="B96" s="93" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C96" s="86" t="inlineStr">
+      <c r="C96" s="93" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D96" s="86" t="inlineStr">
+      <c r="D96" s="93" t="inlineStr">
         <is>
           <t>NFS.377682</t>
         </is>
       </c>
-      <c r="E96" s="86" t="inlineStr">
+      <c r="E96" s="93" t="inlineStr">
         <is>
           <t>114092/1</t>
         </is>
       </c>
-      <c r="F96" s="86" t="inlineStr">
+      <c r="F96" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G96" s="86" t="inlineStr">
+      <c r="G96" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H96" s="87" t="n">
+      <c r="H96" s="94" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="86" t="inlineStr">
+      <c r="A97" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B97" s="86" t="inlineStr">
+      <c r="B97" s="93" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="C97" s="86" t="inlineStr">
+      <c r="C97" s="93" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D97" s="86" t="inlineStr">
+      <c r="D97" s="93" t="inlineStr">
         <is>
           <t>NFS.3</t>
         </is>
       </c>
-      <c r="E97" s="86" t="inlineStr">
+      <c r="E97" s="93" t="inlineStr">
         <is>
           <t>111371/1</t>
         </is>
       </c>
-      <c r="F97" s="86" t="inlineStr">
+      <c r="F97" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G97" s="86" t="inlineStr">
+      <c r="G97" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H97" s="87" t="n">
+      <c r="H97" s="94" t="n">
         <v>6300</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="86" t="inlineStr">
+      <c r="A98" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B98" s="86" t="inlineStr">
+      <c r="B98" s="93" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C98" s="86" t="inlineStr">
+      <c r="C98" s="93" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D98" s="86" t="inlineStr">
+      <c r="D98" s="93" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 07.26</t>
         </is>
       </c>
-      <c r="E98" s="86" t="inlineStr">
+      <c r="E98" s="93" t="inlineStr">
         <is>
           <t>113049/1</t>
         </is>
       </c>
-      <c r="F98" s="86" t="inlineStr">
+      <c r="F98" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G98" s="86" t="inlineStr">
+      <c r="G98" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H98" s="87" t="n">
+      <c r="H98" s="94" t="n">
         <v>1151.26</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="86" t="inlineStr">
+      <c r="A99" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B99" s="86" t="inlineStr">
+      <c r="B99" s="93" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C99" s="86" t="inlineStr">
+      <c r="C99" s="93" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D99" s="86" t="inlineStr">
+      <c r="D99" s="93" t="inlineStr">
         <is>
           <t>NFS.66</t>
         </is>
       </c>
-      <c r="E99" s="86" t="inlineStr">
+      <c r="E99" s="93" t="inlineStr">
         <is>
           <t>112107/1</t>
         </is>
       </c>
-      <c r="F99" s="86" t="inlineStr">
+      <c r="F99" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G99" s="86" t="inlineStr">
+      <c r="G99" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H99" s="87" t="n">
+      <c r="H99" s="94" t="n">
         <v>1037.38</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="86" t="inlineStr">
+      <c r="A100" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B100" s="86" t="inlineStr">
+      <c r="B100" s="93" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="C100" s="86" t="inlineStr">
+      <c r="C100" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D100" s="86" t="inlineStr">
+      <c r="D100" s="93" t="inlineStr">
         <is>
           <t>SAL.sal 0626</t>
         </is>
       </c>
-      <c r="E100" s="86" t="inlineStr">
+      <c r="E100" s="93" t="inlineStr">
         <is>
           <t>112402/1</t>
         </is>
       </c>
-      <c r="F100" s="86" t="inlineStr">
+      <c r="F100" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G100" s="86" t="inlineStr">
+      <c r="G100" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H100" s="87" t="n">
+      <c r="H100" s="94" t="n">
         <v>1225</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="86" t="inlineStr">
+      <c r="A101" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B101" s="86" t="inlineStr">
+      <c r="B101" s="93" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C101" s="86" t="inlineStr">
+      <c r="C101" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D101" s="86" t="inlineStr">
+      <c r="D101" s="93" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E101" s="86" t="inlineStr">
+      <c r="E101" s="93" t="inlineStr">
         <is>
           <t>113754/1</t>
         </is>
       </c>
-      <c r="F101" s="86" t="inlineStr">
+      <c r="F101" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G101" s="86" t="inlineStr">
+      <c r="G101" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H101" s="87" t="n">
+      <c r="H101" s="94" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="86" t="inlineStr">
+      <c r="A102" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B102" s="86" t="inlineStr">
+      <c r="B102" s="93" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C102" s="86" t="inlineStr">
+      <c r="C102" s="93" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D102" s="86" t="inlineStr">
+      <c r="D102" s="93" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E102" s="86" t="inlineStr">
+      <c r="E102" s="93" t="inlineStr">
         <is>
           <t>113754/7</t>
         </is>
       </c>
-      <c r="F102" s="86" t="inlineStr">
+      <c r="F102" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G102" s="86" t="inlineStr">
+      <c r="G102" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H102" s="87" t="n">
+      <c r="H102" s="94" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="86" t="inlineStr">
+      <c r="A103" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B103" s="86" t="inlineStr">
+      <c r="B103" s="93" t="inlineStr">
         <is>
           <t>2026-07-01 00:00:00</t>
         </is>
       </c>
-      <c r="C103" s="86" t="inlineStr">
+      <c r="C103" s="93" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D103" s="86" t="inlineStr"/>
-      <c r="E103" s="86" t="inlineStr"/>
-      <c r="F103" s="86" t="inlineStr">
+      <c r="D103" s="93" t="inlineStr"/>
+      <c r="E103" s="93" t="inlineStr"/>
+      <c r="F103" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G103" s="86" t="inlineStr">
+      <c r="G103" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H103" s="87" t="n">
+      <c r="H103" s="94" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="86" t="inlineStr">
+      <c r="A104" s="93" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B104" s="86" t="inlineStr">
+      <c r="B104" s="93" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C104" s="86" t="inlineStr">
+      <c r="C104" s="93" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D104" s="86" t="inlineStr">
+      <c r="D104" s="93" t="inlineStr">
         <is>
           <t>NFS.84</t>
         </is>
       </c>
-      <c r="E104" s="86" t="inlineStr">
+      <c r="E104" s="93" t="inlineStr">
         <is>
           <t>113583/1</t>
         </is>
       </c>
-      <c r="F104" s="86" t="inlineStr">
+      <c r="F104" s="93" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G104" s="86" t="inlineStr">
+      <c r="G104" s="93" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H104" s="87" t="n">
+      <c r="H104" s="94" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="105">
-      <c r="G105" s="88" t="inlineStr">
+      <c r="G105" s="95" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H105" s="89">
+      <c r="H105" s="96">
         <f>SUM(H5:H104)</f>
         <v/>
       </c>
@@ -12919,1119 +14064,502 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CONTROLE DE EQUIPAMENTOS — solicitações, troca 1x1 e empréstimos</t>
+          <t>PAPÉIS E RESPONSABILIDADES — equipe de TI</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Registro operacional do TI. O SIENGE mostra o que foi PAGO; esta aba mostra o que foi PEDIDO — é no intervalo entre os dois que dá para avisar a área antes de estourar o saldo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>REGRAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>Quem faz o quê no acompanhamento orçamentário e na operação. O critério é custo por hora: tarefa recorrente vai para quem custa menos, e a capacidade cara fica reservada para o que só ela resolve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Função</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Vínculo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Capacidade</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Custo/hora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="72" t="inlineStr">
         <is>
-          <t>Troca 1x1</t>
+          <t>Cristiane Rabelo</t>
         </is>
       </c>
       <c r="B5" s="73" t="inlineStr">
         <is>
-          <t>Para receber um item novo, a pessoa entrega o que quebrou. O patrimônio devolvido é registrado na coluna própria.</t>
-        </is>
-      </c>
-      <c r="C5" s="74" t="n"/>
-      <c r="D5" s="74" t="n"/>
-      <c r="E5" s="74" t="n"/>
-      <c r="F5" s="74" t="n"/>
-      <c r="G5" s="74" t="n"/>
-      <c r="H5" s="74" t="n"/>
-      <c r="I5" s="74" t="n"/>
-      <c r="J5" s="74" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Gestora de TI e Jurídico</t>
+        </is>
+      </c>
+      <c r="C5" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="75" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="72" t="inlineStr">
         <is>
-          <t>Empréstimo</t>
+          <t>Vinicius Di Franco</t>
         </is>
       </c>
       <c r="B6" s="73" t="inlineStr">
         <is>
-          <t>Quem está sem o equipamento sai com um reserva na hora, para não ficar parado. O reserva é COM FIO de propósito: mais barato e menos confortável que o definitivo, o que cria o incentivo para devolver e fechar a troca.</t>
-        </is>
-      </c>
-      <c r="C6" s="74" t="n"/>
-      <c r="D6" s="74" t="n"/>
-      <c r="E6" s="74" t="n"/>
-      <c r="F6" s="74" t="n"/>
-      <c r="G6" s="74" t="n"/>
-      <c r="H6" s="74" t="n"/>
-      <c r="I6" s="74" t="n"/>
-      <c r="J6" s="74" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>Analista Administrativo</t>
+        </is>
+      </c>
+      <c r="C6" s="74" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="D6" s="74" t="inlineStr">
+        <is>
+          <t>173 h/mês (5x8h)</t>
+        </is>
+      </c>
+      <c r="E6" s="75" t="n">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="72" t="inlineStr">
         <is>
-          <t>Sem devolução</t>
+          <t>Jonathan (J H Alves)</t>
         </is>
       </c>
       <c r="B7" s="73" t="inlineStr">
         <is>
-          <t>Se a pessoa não entrega o item antigo, a solicitação fica 'Pendente devolução' e não vira compra até ser resolvida.</t>
-        </is>
-      </c>
-      <c r="C7" s="74" t="n"/>
-      <c r="D7" s="74" t="n"/>
-      <c r="E7" s="74" t="n"/>
-      <c r="F7" s="74" t="n"/>
-      <c r="G7" s="74" t="n"/>
-      <c r="H7" s="74" t="n"/>
-      <c r="I7" s="74" t="n"/>
-      <c r="J7" s="74" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>Consultor / Desenvolvedor</t>
+        </is>
+      </c>
+      <c r="C7" s="74" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D7" s="74" t="inlineStr">
+        <is>
+          <t>104 h/mês (3x8h)</t>
+        </is>
+      </c>
+      <c r="E7" s="75" t="n">
+        <v>60.58</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="72" t="inlineStr">
         <is>
-          <t>Aviso de saldo</t>
+          <t>Elias Benedito</t>
         </is>
       </c>
       <c r="B8" s="73" t="inlineStr">
         <is>
-          <t>Antes de aprovar, conferir o saldo da rubrica da área solicitante. Se a compra for levar ao estouro, avisar a área ANTES de comprar (pendência R).</t>
-        </is>
-      </c>
-      <c r="C8" s="74" t="n"/>
-      <c r="D8" s="74" t="n"/>
-      <c r="E8" s="74" t="n"/>
-      <c r="F8" s="74" t="n"/>
-      <c r="G8" s="74" t="n"/>
-      <c r="H8" s="74" t="n"/>
-      <c r="I8" s="74" t="n"/>
-      <c r="J8" s="74" t="n"/>
+          <t>Suporte Técnico Terceirizado</t>
+        </is>
+      </c>
+      <c r="C8" s="74" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D8" s="74" t="inlineStr">
+        <is>
+          <t>Sob demanda</t>
+        </is>
+      </c>
+      <c r="E8" s="75" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="75" t="inlineStr">
-        <is>
-          <t>SOLICITAÇÕES</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Área solicitante</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Solicitante</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Devolveu o antigo?</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Patrimônio devolvido</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Valor estimado</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Observações</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="76" t="n"/>
-      <c r="B12" s="76" t="n"/>
-      <c r="C12" s="76" t="n"/>
-      <c r="D12" s="76" t="n"/>
-      <c r="E12" s="76" t="n"/>
-      <c r="F12" s="76" t="n"/>
-      <c r="G12" s="76" t="n"/>
-      <c r="H12" s="49" t="n"/>
-      <c r="I12" s="76" t="n"/>
-      <c r="J12" s="76" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="76" t="n"/>
-      <c r="B13" s="76" t="n"/>
-      <c r="C13" s="76" t="n"/>
-      <c r="D13" s="76" t="n"/>
-      <c r="E13" s="76" t="n"/>
-      <c r="F13" s="76" t="n"/>
-      <c r="G13" s="76" t="n"/>
-      <c r="H13" s="49" t="n"/>
-      <c r="I13" s="76" t="n"/>
-      <c r="J13" s="76" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="76" t="n"/>
-      <c r="B14" s="76" t="n"/>
-      <c r="C14" s="76" t="n"/>
-      <c r="D14" s="76" t="n"/>
-      <c r="E14" s="76" t="n"/>
-      <c r="F14" s="76" t="n"/>
-      <c r="G14" s="76" t="n"/>
-      <c r="H14" s="49" t="n"/>
-      <c r="I14" s="76" t="n"/>
-      <c r="J14" s="76" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="76" t="n"/>
-      <c r="B15" s="76" t="n"/>
-      <c r="C15" s="76" t="n"/>
-      <c r="D15" s="76" t="n"/>
-      <c r="E15" s="76" t="n"/>
-      <c r="F15" s="76" t="n"/>
-      <c r="G15" s="76" t="n"/>
-      <c r="H15" s="49" t="n"/>
-      <c r="I15" s="76" t="n"/>
-      <c r="J15" s="76" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="76" t="n"/>
-      <c r="B16" s="76" t="n"/>
-      <c r="C16" s="76" t="n"/>
-      <c r="D16" s="76" t="n"/>
-      <c r="E16" s="76" t="n"/>
-      <c r="F16" s="76" t="n"/>
-      <c r="G16" s="76" t="n"/>
-      <c r="H16" s="49" t="n"/>
-      <c r="I16" s="76" t="n"/>
-      <c r="J16" s="76" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="76" t="n"/>
-      <c r="B17" s="76" t="n"/>
-      <c r="C17" s="76" t="n"/>
-      <c r="D17" s="76" t="n"/>
-      <c r="E17" s="76" t="n"/>
-      <c r="F17" s="76" t="n"/>
-      <c r="G17" s="76" t="n"/>
-      <c r="H17" s="49" t="n"/>
-      <c r="I17" s="76" t="n"/>
-      <c r="J17" s="76" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="76" t="n"/>
-      <c r="B18" s="76" t="n"/>
-      <c r="C18" s="76" t="n"/>
-      <c r="D18" s="76" t="n"/>
-      <c r="E18" s="76" t="n"/>
-      <c r="F18" s="76" t="n"/>
-      <c r="G18" s="76" t="n"/>
-      <c r="H18" s="49" t="n"/>
-      <c r="I18" s="76" t="n"/>
-      <c r="J18" s="76" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="76" t="n"/>
-      <c r="B19" s="76" t="n"/>
-      <c r="C19" s="76" t="n"/>
-      <c r="D19" s="76" t="n"/>
-      <c r="E19" s="76" t="n"/>
-      <c r="F19" s="76" t="n"/>
-      <c r="G19" s="76" t="n"/>
-      <c r="H19" s="49" t="n"/>
-      <c r="I19" s="76" t="n"/>
-      <c r="J19" s="76" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="76" t="n"/>
-      <c r="B20" s="76" t="n"/>
-      <c r="C20" s="76" t="n"/>
-      <c r="D20" s="76" t="n"/>
-      <c r="E20" s="76" t="n"/>
-      <c r="F20" s="76" t="n"/>
-      <c r="G20" s="76" t="n"/>
-      <c r="H20" s="49" t="n"/>
-      <c r="I20" s="76" t="n"/>
-      <c r="J20" s="76" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="76" t="n"/>
-      <c r="B21" s="76" t="n"/>
-      <c r="C21" s="76" t="n"/>
-      <c r="D21" s="76" t="n"/>
-      <c r="E21" s="76" t="n"/>
-      <c r="F21" s="76" t="n"/>
-      <c r="G21" s="76" t="n"/>
-      <c r="H21" s="49" t="n"/>
-      <c r="I21" s="76" t="n"/>
-      <c r="J21" s="76" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="76" t="n"/>
-      <c r="B22" s="76" t="n"/>
-      <c r="C22" s="76" t="n"/>
-      <c r="D22" s="76" t="n"/>
-      <c r="E22" s="76" t="n"/>
-      <c r="F22" s="76" t="n"/>
-      <c r="G22" s="76" t="n"/>
-      <c r="H22" s="49" t="n"/>
-      <c r="I22" s="76" t="n"/>
-      <c r="J22" s="76" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="76" t="n"/>
-      <c r="B23" s="76" t="n"/>
-      <c r="C23" s="76" t="n"/>
-      <c r="D23" s="76" t="n"/>
-      <c r="E23" s="76" t="n"/>
-      <c r="F23" s="76" t="n"/>
-      <c r="G23" s="76" t="n"/>
-      <c r="H23" s="49" t="n"/>
-      <c r="I23" s="76" t="n"/>
-      <c r="J23" s="76" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="76" t="n"/>
-      <c r="B24" s="76" t="n"/>
-      <c r="C24" s="76" t="n"/>
-      <c r="D24" s="76" t="n"/>
-      <c r="E24" s="76" t="n"/>
-      <c r="F24" s="76" t="n"/>
-      <c r="G24" s="76" t="n"/>
-      <c r="H24" s="49" t="n"/>
-      <c r="I24" s="76" t="n"/>
-      <c r="J24" s="76" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="76" t="n"/>
-      <c r="B25" s="76" t="n"/>
-      <c r="C25" s="76" t="n"/>
-      <c r="D25" s="76" t="n"/>
-      <c r="E25" s="76" t="n"/>
-      <c r="F25" s="76" t="n"/>
-      <c r="G25" s="76" t="n"/>
-      <c r="H25" s="49" t="n"/>
-      <c r="I25" s="76" t="n"/>
-      <c r="J25" s="76" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="76" t="n"/>
-      <c r="B26" s="76" t="n"/>
-      <c r="C26" s="76" t="n"/>
-      <c r="D26" s="76" t="n"/>
-      <c r="E26" s="76" t="n"/>
-      <c r="F26" s="76" t="n"/>
-      <c r="G26" s="76" t="n"/>
-      <c r="H26" s="49" t="n"/>
-      <c r="I26" s="76" t="n"/>
-      <c r="J26" s="76" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="76" t="n"/>
-      <c r="B27" s="76" t="n"/>
-      <c r="C27" s="76" t="n"/>
-      <c r="D27" s="76" t="n"/>
-      <c r="E27" s="76" t="n"/>
-      <c r="F27" s="76" t="n"/>
-      <c r="G27" s="76" t="n"/>
-      <c r="H27" s="49" t="n"/>
-      <c r="I27" s="76" t="n"/>
-      <c r="J27" s="76" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="76" t="n"/>
-      <c r="B28" s="76" t="n"/>
-      <c r="C28" s="76" t="n"/>
-      <c r="D28" s="76" t="n"/>
-      <c r="E28" s="76" t="n"/>
-      <c r="F28" s="76" t="n"/>
-      <c r="G28" s="76" t="n"/>
-      <c r="H28" s="49" t="n"/>
-      <c r="I28" s="76" t="n"/>
-      <c r="J28" s="76" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="76" t="n"/>
-      <c r="B29" s="76" t="n"/>
-      <c r="C29" s="76" t="n"/>
-      <c r="D29" s="76" t="n"/>
-      <c r="E29" s="76" t="n"/>
-      <c r="F29" s="76" t="n"/>
-      <c r="G29" s="76" t="n"/>
-      <c r="H29" s="49" t="n"/>
-      <c r="I29" s="76" t="n"/>
-      <c r="J29" s="76" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="76" t="n"/>
-      <c r="B30" s="76" t="n"/>
-      <c r="C30" s="76" t="n"/>
-      <c r="D30" s="76" t="n"/>
-      <c r="E30" s="76" t="n"/>
-      <c r="F30" s="76" t="n"/>
-      <c r="G30" s="76" t="n"/>
-      <c r="H30" s="49" t="n"/>
-      <c r="I30" s="76" t="n"/>
-      <c r="J30" s="76" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="76" t="n"/>
-      <c r="B31" s="76" t="n"/>
-      <c r="C31" s="76" t="n"/>
-      <c r="D31" s="76" t="n"/>
-      <c r="E31" s="76" t="n"/>
-      <c r="F31" s="76" t="n"/>
-      <c r="G31" s="76" t="n"/>
-      <c r="H31" s="49" t="n"/>
-      <c r="I31" s="76" t="n"/>
-      <c r="J31" s="76" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="76" t="n"/>
-      <c r="B32" s="76" t="n"/>
-      <c r="C32" s="76" t="n"/>
-      <c r="D32" s="76" t="n"/>
-      <c r="E32" s="76" t="n"/>
-      <c r="F32" s="76" t="n"/>
-      <c r="G32" s="76" t="n"/>
-      <c r="H32" s="49" t="n"/>
-      <c r="I32" s="76" t="n"/>
-      <c r="J32" s="76" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="76" t="n"/>
-      <c r="B33" s="76" t="n"/>
-      <c r="C33" s="76" t="n"/>
-      <c r="D33" s="76" t="n"/>
-      <c r="E33" s="76" t="n"/>
-      <c r="F33" s="76" t="n"/>
-      <c r="G33" s="76" t="n"/>
-      <c r="H33" s="49" t="n"/>
-      <c r="I33" s="76" t="n"/>
-      <c r="J33" s="76" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="76" t="n"/>
-      <c r="B34" s="76" t="n"/>
-      <c r="C34" s="76" t="n"/>
-      <c r="D34" s="76" t="n"/>
-      <c r="E34" s="76" t="n"/>
-      <c r="F34" s="76" t="n"/>
-      <c r="G34" s="76" t="n"/>
-      <c r="H34" s="49" t="n"/>
-      <c r="I34" s="76" t="n"/>
-      <c r="J34" s="76" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="76" t="n"/>
-      <c r="B35" s="76" t="n"/>
-      <c r="C35" s="76" t="n"/>
-      <c r="D35" s="76" t="n"/>
-      <c r="E35" s="76" t="n"/>
-      <c r="F35" s="76" t="n"/>
-      <c r="G35" s="76" t="n"/>
-      <c r="H35" s="49" t="n"/>
-      <c r="I35" s="76" t="n"/>
-      <c r="J35" s="76" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="76" t="n"/>
-      <c r="B36" s="76" t="n"/>
-      <c r="C36" s="76" t="n"/>
-      <c r="D36" s="76" t="n"/>
-      <c r="E36" s="76" t="n"/>
-      <c r="F36" s="76" t="n"/>
-      <c r="G36" s="76" t="n"/>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="76" t="n"/>
-      <c r="J36" s="76" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="76" t="n"/>
-      <c r="B37" s="76" t="n"/>
-      <c r="C37" s="76" t="n"/>
-      <c r="D37" s="76" t="n"/>
-      <c r="E37" s="76" t="n"/>
-      <c r="F37" s="76" t="n"/>
-      <c r="G37" s="76" t="n"/>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="76" t="n"/>
-      <c r="J37" s="76" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="76" t="n"/>
-      <c r="B38" s="76" t="n"/>
-      <c r="C38" s="76" t="n"/>
-      <c r="D38" s="76" t="n"/>
-      <c r="E38" s="76" t="n"/>
-      <c r="F38" s="76" t="n"/>
-      <c r="G38" s="76" t="n"/>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="76" t="n"/>
-      <c r="J38" s="76" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="76" t="n"/>
-      <c r="B39" s="76" t="n"/>
-      <c r="C39" s="76" t="n"/>
-      <c r="D39" s="76" t="n"/>
-      <c r="E39" s="76" t="n"/>
-      <c r="F39" s="76" t="n"/>
-      <c r="G39" s="76" t="n"/>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="76" t="n"/>
-      <c r="J39" s="76" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="76" t="n"/>
-      <c r="B40" s="76" t="n"/>
-      <c r="C40" s="76" t="n"/>
-      <c r="D40" s="76" t="n"/>
-      <c r="E40" s="76" t="n"/>
-      <c r="F40" s="76" t="n"/>
-      <c r="G40" s="76" t="n"/>
-      <c r="H40" s="49" t="n"/>
-      <c r="I40" s="76" t="n"/>
-      <c r="J40" s="76" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="76" t="n"/>
-      <c r="B41" s="76" t="n"/>
-      <c r="C41" s="76" t="n"/>
-      <c r="D41" s="76" t="n"/>
-      <c r="E41" s="76" t="n"/>
-      <c r="F41" s="76" t="n"/>
-      <c r="G41" s="76" t="n"/>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="76" t="n"/>
-      <c r="J41" s="76" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="76" t="n"/>
-      <c r="B42" s="76" t="n"/>
-      <c r="C42" s="76" t="n"/>
-      <c r="D42" s="76" t="n"/>
-      <c r="E42" s="76" t="n"/>
-      <c r="F42" s="76" t="n"/>
-      <c r="G42" s="76" t="n"/>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="76" t="n"/>
-      <c r="J42" s="76" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="76" t="n"/>
-      <c r="B43" s="76" t="n"/>
-      <c r="C43" s="76" t="n"/>
-      <c r="D43" s="76" t="n"/>
-      <c r="E43" s="76" t="n"/>
-      <c r="F43" s="76" t="n"/>
-      <c r="G43" s="76" t="n"/>
-      <c r="H43" s="49" t="n"/>
-      <c r="I43" s="76" t="n"/>
-      <c r="J43" s="76" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="76" t="n"/>
-      <c r="B44" s="76" t="n"/>
-      <c r="C44" s="76" t="n"/>
-      <c r="D44" s="76" t="n"/>
-      <c r="E44" s="76" t="n"/>
-      <c r="F44" s="76" t="n"/>
-      <c r="G44" s="76" t="n"/>
-      <c r="H44" s="49" t="n"/>
-      <c r="I44" s="76" t="n"/>
-      <c r="J44" s="76" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="76" t="n"/>
-      <c r="B45" s="76" t="n"/>
-      <c r="C45" s="76" t="n"/>
-      <c r="D45" s="76" t="n"/>
-      <c r="E45" s="76" t="n"/>
-      <c r="F45" s="76" t="n"/>
-      <c r="G45" s="76" t="n"/>
-      <c r="H45" s="49" t="n"/>
-      <c r="I45" s="76" t="n"/>
-      <c r="J45" s="76" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="76" t="n"/>
-      <c r="B46" s="76" t="n"/>
-      <c r="C46" s="76" t="n"/>
-      <c r="D46" s="76" t="n"/>
-      <c r="E46" s="76" t="n"/>
-      <c r="F46" s="76" t="n"/>
-      <c r="G46" s="76" t="n"/>
-      <c r="H46" s="49" t="n"/>
-      <c r="I46" s="76" t="n"/>
-      <c r="J46" s="76" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="76" t="n"/>
-      <c r="B47" s="76" t="n"/>
-      <c r="C47" s="76" t="n"/>
-      <c r="D47" s="76" t="n"/>
-      <c r="E47" s="76" t="n"/>
-      <c r="F47" s="76" t="n"/>
-      <c r="G47" s="76" t="n"/>
-      <c r="H47" s="49" t="n"/>
-      <c r="I47" s="76" t="n"/>
-      <c r="J47" s="76" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="76" t="n"/>
-      <c r="B48" s="76" t="n"/>
-      <c r="C48" s="76" t="n"/>
-      <c r="D48" s="76" t="n"/>
-      <c r="E48" s="76" t="n"/>
-      <c r="F48" s="76" t="n"/>
-      <c r="G48" s="76" t="n"/>
-      <c r="H48" s="49" t="n"/>
-      <c r="I48" s="76" t="n"/>
-      <c r="J48" s="76" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="76" t="n"/>
-      <c r="B49" s="76" t="n"/>
-      <c r="C49" s="76" t="n"/>
-      <c r="D49" s="76" t="n"/>
-      <c r="E49" s="76" t="n"/>
-      <c r="F49" s="76" t="n"/>
-      <c r="G49" s="76" t="n"/>
-      <c r="H49" s="49" t="n"/>
-      <c r="I49" s="76" t="n"/>
-      <c r="J49" s="76" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="76" t="n"/>
-      <c r="B50" s="76" t="n"/>
-      <c r="C50" s="76" t="n"/>
-      <c r="D50" s="76" t="n"/>
-      <c r="E50" s="76" t="n"/>
-      <c r="F50" s="76" t="n"/>
-      <c r="G50" s="76" t="n"/>
-      <c r="H50" s="49" t="n"/>
-      <c r="I50" s="76" t="n"/>
-      <c r="J50" s="76" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="76" t="n"/>
-      <c r="B51" s="76" t="n"/>
-      <c r="C51" s="76" t="n"/>
-      <c r="D51" s="76" t="n"/>
-      <c r="E51" s="76" t="n"/>
-      <c r="F51" s="76" t="n"/>
-      <c r="G51" s="76" t="n"/>
-      <c r="H51" s="49" t="n"/>
-      <c r="I51" s="76" t="n"/>
-      <c r="J51" s="76" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>EMPRÉSTIMOS (equipamento reserva)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="77" t="inlineStr">
-        <is>
-          <t>Item emprestado</t>
-        </is>
-      </c>
-      <c r="B54" s="77" t="inlineStr">
-        <is>
-          <t>Patrimônio</t>
-        </is>
-      </c>
-      <c r="C54" s="77" t="inlineStr">
-        <is>
-          <t>Área</t>
-        </is>
-      </c>
-      <c r="D54" s="77" t="inlineStr">
-        <is>
-          <t>Pessoa</t>
-        </is>
-      </c>
-      <c r="E54" s="77" t="inlineStr">
-        <is>
-          <t>Saída em</t>
-        </is>
-      </c>
-      <c r="F54" s="77" t="inlineStr">
-        <is>
-          <t>Previsão de devolução</t>
-        </is>
-      </c>
-      <c r="G54" s="77" t="inlineStr">
-        <is>
-          <t>Devolvido em</t>
-        </is>
-      </c>
-      <c r="H54" s="77" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I54" s="77" t="inlineStr">
-        <is>
-          <t>Dias em posse</t>
-        </is>
-      </c>
-      <c r="J54" s="77" t="inlineStr">
-        <is>
-          <t>Observações</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="76" t="n"/>
-      <c r="B55" s="76" t="n"/>
-      <c r="C55" s="76" t="n"/>
-      <c r="D55" s="76" t="n"/>
-      <c r="E55" s="76" t="n"/>
-      <c r="F55" s="76" t="n"/>
-      <c r="G55" s="76" t="n"/>
-      <c r="H55" s="76" t="n"/>
-      <c r="I55" s="78">
-        <f>IF(E55="","",IF(G55="",TODAY()-E55,G55-E55))</f>
-        <v/>
-      </c>
-      <c r="J55" s="76" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="76" t="n"/>
-      <c r="B56" s="76" t="n"/>
-      <c r="C56" s="76" t="n"/>
-      <c r="D56" s="76" t="n"/>
-      <c r="E56" s="76" t="n"/>
-      <c r="F56" s="76" t="n"/>
-      <c r="G56" s="76" t="n"/>
-      <c r="H56" s="76" t="n"/>
-      <c r="I56" s="78">
-        <f>IF(E56="","",IF(G56="",TODAY()-E56,G56-E56))</f>
-        <v/>
-      </c>
-      <c r="J56" s="76" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="76" t="n"/>
-      <c r="B57" s="76" t="n"/>
-      <c r="C57" s="76" t="n"/>
-      <c r="D57" s="76" t="n"/>
-      <c r="E57" s="76" t="n"/>
-      <c r="F57" s="76" t="n"/>
-      <c r="G57" s="76" t="n"/>
-      <c r="H57" s="76" t="n"/>
-      <c r="I57" s="78">
-        <f>IF(E57="","",IF(G57="",TODAY()-E57,G57-E57))</f>
-        <v/>
-      </c>
-      <c r="J57" s="76" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="76" t="n"/>
-      <c r="B58" s="76" t="n"/>
-      <c r="C58" s="76" t="n"/>
-      <c r="D58" s="76" t="n"/>
-      <c r="E58" s="76" t="n"/>
-      <c r="F58" s="76" t="n"/>
-      <c r="G58" s="76" t="n"/>
-      <c r="H58" s="76" t="n"/>
-      <c r="I58" s="78">
-        <f>IF(E58="","",IF(G58="",TODAY()-E58,G58-E58))</f>
-        <v/>
-      </c>
-      <c r="J58" s="76" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="76" t="n"/>
-      <c r="B59" s="76" t="n"/>
-      <c r="C59" s="76" t="n"/>
-      <c r="D59" s="76" t="n"/>
-      <c r="E59" s="76" t="n"/>
-      <c r="F59" s="76" t="n"/>
-      <c r="G59" s="76" t="n"/>
-      <c r="H59" s="76" t="n"/>
-      <c r="I59" s="78">
-        <f>IF(E59="","",IF(G59="",TODAY()-E59,G59-E59))</f>
-        <v/>
-      </c>
-      <c r="J59" s="76" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="76" t="n"/>
-      <c r="B60" s="76" t="n"/>
-      <c r="C60" s="76" t="n"/>
-      <c r="D60" s="76" t="n"/>
-      <c r="E60" s="76" t="n"/>
-      <c r="F60" s="76" t="n"/>
-      <c r="G60" s="76" t="n"/>
-      <c r="H60" s="76" t="n"/>
-      <c r="I60" s="78">
-        <f>IF(E60="","",IF(G60="",TODAY()-E60,G60-E60))</f>
-        <v/>
-      </c>
-      <c r="J60" s="76" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="76" t="n"/>
-      <c r="B61" s="76" t="n"/>
-      <c r="C61" s="76" t="n"/>
-      <c r="D61" s="76" t="n"/>
-      <c r="E61" s="76" t="n"/>
-      <c r="F61" s="76" t="n"/>
-      <c r="G61" s="76" t="n"/>
-      <c r="H61" s="76" t="n"/>
-      <c r="I61" s="78">
-        <f>IF(E61="","",IF(G61="",TODAY()-E61,G61-E61))</f>
-        <v/>
-      </c>
-      <c r="J61" s="76" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="76" t="n"/>
-      <c r="B62" s="76" t="n"/>
-      <c r="C62" s="76" t="n"/>
-      <c r="D62" s="76" t="n"/>
-      <c r="E62" s="76" t="n"/>
-      <c r="F62" s="76" t="n"/>
-      <c r="G62" s="76" t="n"/>
-      <c r="H62" s="76" t="n"/>
-      <c r="I62" s="78">
-        <f>IF(E62="","",IF(G62="",TODAY()-E62,G62-E62))</f>
-        <v/>
-      </c>
-      <c r="J62" s="76" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="76" t="n"/>
-      <c r="B63" s="76" t="n"/>
-      <c r="C63" s="76" t="n"/>
-      <c r="D63" s="76" t="n"/>
-      <c r="E63" s="76" t="n"/>
-      <c r="F63" s="76" t="n"/>
-      <c r="G63" s="76" t="n"/>
-      <c r="H63" s="76" t="n"/>
-      <c r="I63" s="78">
-        <f>IF(E63="","",IF(G63="",TODAY()-E63,G63-E63))</f>
-        <v/>
-      </c>
-      <c r="J63" s="76" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="76" t="n"/>
-      <c r="B64" s="76" t="n"/>
-      <c r="C64" s="76" t="n"/>
-      <c r="D64" s="76" t="n"/>
-      <c r="E64" s="76" t="n"/>
-      <c r="F64" s="76" t="n"/>
-      <c r="G64" s="76" t="n"/>
-      <c r="H64" s="76" t="n"/>
-      <c r="I64" s="78">
-        <f>IF(E64="","",IF(G64="",TODAY()-E64,G64-E64))</f>
-        <v/>
-      </c>
-      <c r="J64" s="76" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="76" t="n"/>
-      <c r="B65" s="76" t="n"/>
-      <c r="C65" s="76" t="n"/>
-      <c r="D65" s="76" t="n"/>
-      <c r="E65" s="76" t="n"/>
-      <c r="F65" s="76" t="n"/>
-      <c r="G65" s="76" t="n"/>
-      <c r="H65" s="76" t="n"/>
-      <c r="I65" s="78">
-        <f>IF(E65="","",IF(G65="",TODAY()-E65,G65-E65))</f>
-        <v/>
-      </c>
-      <c r="J65" s="76" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="76" t="n"/>
-      <c r="B66" s="76" t="n"/>
-      <c r="C66" s="76" t="n"/>
-      <c r="D66" s="76" t="n"/>
-      <c r="E66" s="76" t="n"/>
-      <c r="F66" s="76" t="n"/>
-      <c r="G66" s="76" t="n"/>
-      <c r="H66" s="76" t="n"/>
-      <c r="I66" s="78">
-        <f>IF(E66="","",IF(G66="",TODAY()-E66,G66-E66))</f>
-        <v/>
-      </c>
-      <c r="J66" s="76" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="76" t="n"/>
-      <c r="B67" s="76" t="n"/>
-      <c r="C67" s="76" t="n"/>
-      <c r="D67" s="76" t="n"/>
-      <c r="E67" s="76" t="n"/>
-      <c r="F67" s="76" t="n"/>
-      <c r="G67" s="76" t="n"/>
-      <c r="H67" s="76" t="n"/>
-      <c r="I67" s="78">
-        <f>IF(E67="","",IF(G67="",TODAY()-E67,G67-E67))</f>
-        <v/>
-      </c>
-      <c r="J67" s="76" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="76" t="n"/>
-      <c r="B68" s="76" t="n"/>
-      <c r="C68" s="76" t="n"/>
-      <c r="D68" s="76" t="n"/>
-      <c r="E68" s="76" t="n"/>
-      <c r="F68" s="76" t="n"/>
-      <c r="G68" s="76" t="n"/>
-      <c r="H68" s="76" t="n"/>
-      <c r="I68" s="78">
-        <f>IF(E68="","",IF(G68="",TODAY()-E68,G68-E68))</f>
-        <v/>
-      </c>
-      <c r="J68" s="76" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="76" t="n"/>
-      <c r="B69" s="76" t="n"/>
-      <c r="C69" s="76" t="n"/>
-      <c r="D69" s="76" t="n"/>
-      <c r="E69" s="76" t="n"/>
-      <c r="F69" s="76" t="n"/>
-      <c r="G69" s="76" t="n"/>
-      <c r="H69" s="76" t="n"/>
-      <c r="I69" s="78">
-        <f>IF(E69="","",IF(G69="",TODAY()-E69,G69-E69))</f>
-        <v/>
-      </c>
-      <c r="J69" s="76" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="76" t="n"/>
-      <c r="B70" s="76" t="n"/>
-      <c r="C70" s="76" t="n"/>
-      <c r="D70" s="76" t="n"/>
-      <c r="E70" s="76" t="n"/>
-      <c r="F70" s="76" t="n"/>
-      <c r="G70" s="76" t="n"/>
-      <c r="H70" s="76" t="n"/>
-      <c r="I70" s="78">
-        <f>IF(E70="","",IF(G70="",TODAY()-E70,G70-E70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="76" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="76" t="n"/>
-      <c r="B71" s="76" t="n"/>
-      <c r="C71" s="76" t="n"/>
-      <c r="D71" s="76" t="n"/>
-      <c r="E71" s="76" t="n"/>
-      <c r="F71" s="76" t="n"/>
-      <c r="G71" s="76" t="n"/>
-      <c r="H71" s="76" t="n"/>
-      <c r="I71" s="78">
-        <f>IF(E71="","",IF(G71="",TODAY()-E71,G71-E71))</f>
-        <v/>
-      </c>
-      <c r="J71" s="76" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="76" t="n"/>
-      <c r="B72" s="76" t="n"/>
-      <c r="C72" s="76" t="n"/>
-      <c r="D72" s="76" t="n"/>
-      <c r="E72" s="76" t="n"/>
-      <c r="F72" s="76" t="n"/>
-      <c r="G72" s="76" t="n"/>
-      <c r="H72" s="76" t="n"/>
-      <c r="I72" s="78">
-        <f>IF(E72="","",IF(G72="",TODAY()-E72,G72-E72))</f>
-        <v/>
-      </c>
-      <c r="J72" s="76" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="76" t="n"/>
-      <c r="B73" s="76" t="n"/>
-      <c r="C73" s="76" t="n"/>
-      <c r="D73" s="76" t="n"/>
-      <c r="E73" s="76" t="n"/>
-      <c r="F73" s="76" t="n"/>
-      <c r="G73" s="76" t="n"/>
-      <c r="H73" s="76" t="n"/>
-      <c r="I73" s="78">
-        <f>IF(E73="","",IF(G73="",TODAY()-E73,G73-E73))</f>
-        <v/>
-      </c>
-      <c r="J73" s="76" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="76" t="n"/>
-      <c r="B74" s="76" t="n"/>
-      <c r="C74" s="76" t="n"/>
-      <c r="D74" s="76" t="n"/>
-      <c r="E74" s="76" t="n"/>
-      <c r="F74" s="76" t="n"/>
-      <c r="G74" s="76" t="n"/>
-      <c r="H74" s="76" t="n"/>
-      <c r="I74" s="78">
-        <f>IF(E74="","",IF(G74="",TODAY()-E74,G74-E74))</f>
-        <v/>
-      </c>
-      <c r="J74" s="76" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="76" t="n"/>
-      <c r="B75" s="76" t="n"/>
-      <c r="C75" s="76" t="n"/>
-      <c r="D75" s="76" t="n"/>
-      <c r="E75" s="76" t="n"/>
-      <c r="F75" s="76" t="n"/>
-      <c r="G75" s="76" t="n"/>
-      <c r="H75" s="76" t="n"/>
-      <c r="I75" s="78">
-        <f>IF(E75="","",IF(G75="",TODAY()-E75,G75-E75))</f>
-        <v/>
-      </c>
-      <c r="J75" s="76" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="76" t="n"/>
-      <c r="B76" s="76" t="n"/>
-      <c r="C76" s="76" t="n"/>
-      <c r="D76" s="76" t="n"/>
-      <c r="E76" s="76" t="n"/>
-      <c r="F76" s="76" t="n"/>
-      <c r="G76" s="76" t="n"/>
-      <c r="H76" s="76" t="n"/>
-      <c r="I76" s="78">
-        <f>IF(E76="","",IF(G76="",TODAY()-E76,G76-E76))</f>
-        <v/>
-      </c>
-      <c r="J76" s="76" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="76" t="n"/>
-      <c r="B77" s="76" t="n"/>
-      <c r="C77" s="76" t="n"/>
-      <c r="D77" s="76" t="n"/>
-      <c r="E77" s="76" t="n"/>
-      <c r="F77" s="76" t="n"/>
-      <c r="G77" s="76" t="n"/>
-      <c r="H77" s="76" t="n"/>
-      <c r="I77" s="78">
-        <f>IF(E77="","",IF(G77="",TODAY()-E77,G77-E77))</f>
-        <v/>
-      </c>
-      <c r="J77" s="76" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="76" t="n"/>
-      <c r="B78" s="76" t="n"/>
-      <c r="C78" s="76" t="n"/>
-      <c r="D78" s="76" t="n"/>
-      <c r="E78" s="76" t="n"/>
-      <c r="F78" s="76" t="n"/>
-      <c r="G78" s="76" t="n"/>
-      <c r="H78" s="76" t="n"/>
-      <c r="I78" s="78">
-        <f>IF(E78="","",IF(G78="",TODAY()-E78,G78-E78))</f>
-        <v/>
-      </c>
-      <c r="J78" s="76" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="76" t="n"/>
-      <c r="B79" s="76" t="n"/>
-      <c r="C79" s="76" t="n"/>
-      <c r="D79" s="76" t="n"/>
-      <c r="E79" s="76" t="n"/>
-      <c r="F79" s="76" t="n"/>
-      <c r="G79" s="76" t="n"/>
-      <c r="H79" s="76" t="n"/>
-      <c r="I79" s="78">
-        <f>IF(E79="","",IF(G79="",TODAY()-E79,G79-E79))</f>
-        <v/>
-      </c>
-      <c r="J79" s="76" t="n"/>
+      <c r="A10" s="76" t="inlineStr">
+        <is>
+          <t>CRISTIANE — decisão, negociação e representação</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="77" t="inlineStr">
+        <is>
+          <t>Negociação de contratos</t>
+        </is>
+      </c>
+      <c r="B11" s="78" t="inlineStr">
+        <is>
+          <t>Fechar valor e condições com fornecedores e prestadores. É o que gerou as economias do ano: Jonathan de R$ 10.000 para R$ 6.300 e Elias de R$ 1.065 para R$ 603,30 (43% de redução).</t>
+        </is>
+      </c>
+      <c r="C11" s="79" t="n"/>
+      <c r="D11" s="79" t="n"/>
+      <c r="E11" s="79" t="n"/>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="77" t="inlineStr">
+        <is>
+          <t>O que entra e sai do orçamento</t>
+        </is>
+      </c>
+      <c r="B12" s="78" t="inlineStr">
+        <is>
+          <t>Aprovar inclusão de linha nova, cancelamento e revisão de valor. Exemplos do período: cancelamento do Astrea, inclusão da Dra. Michele, decisão sobre a sala de reunião.</t>
+        </is>
+      </c>
+      <c r="C12" s="79" t="n"/>
+      <c r="D12" s="79" t="n"/>
+      <c r="E12" s="79" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="77" t="inlineStr">
+        <is>
+          <t>Rateio e centro de custo</t>
+        </is>
+      </c>
+      <c r="B13" s="78" t="inlineStr">
+        <is>
+          <t>Definir com a controladoria o que é do TI e o que é corporativo — softwares de uso transversal, ferramentas de IA, reclassificações.</t>
+        </is>
+      </c>
+      <c r="C13" s="79" t="n"/>
+      <c r="D13" s="79" t="n"/>
+      <c r="E13" s="79" t="n"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="77" t="inlineStr">
+        <is>
+          <t>Apresentação à diretoria</t>
+        </is>
+      </c>
+      <c r="B14" s="78" t="inlineStr">
+        <is>
+          <t>Levar o Painel, defender os números e as pautas em aberto. Responder por desvio e por economia.</t>
+        </is>
+      </c>
+      <c r="C14" s="79" t="n"/>
+      <c r="D14" s="79" t="n"/>
+      <c r="E14" s="79" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="77" t="inlineStr">
+        <is>
+          <t>Aprovação de compra acima do saldo</t>
+        </is>
+      </c>
+      <c r="B15" s="78" t="inlineStr">
+        <is>
+          <t>Quando a solicitação de uma área levar ao estouro, decidir com a diretoria se aprova ou segura.</t>
+        </is>
+      </c>
+      <c r="C15" s="79" t="n"/>
+      <c r="D15" s="79" t="n"/>
+      <c r="E15" s="79" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>VINICIUS — suporte, rotina e apoio ao desenvolvimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="77" t="inlineStr">
+        <is>
+          <t>Suporte ao usuário</t>
+        </is>
+      </c>
+      <c r="B18" s="78" t="inlineStr">
+        <is>
+          <t>Atendimento do dia a dia às áreas: equipamento, acesso, software.</t>
+        </is>
+      </c>
+      <c r="C18" s="79" t="n"/>
+      <c r="D18" s="79" t="n"/>
+      <c r="E18" s="79" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="77" t="inlineStr">
+        <is>
+          <t>Fechamento mensal do orçamento</t>
+        </is>
+      </c>
+      <c r="B19" s="78" t="inlineStr">
+        <is>
+          <t>Extrair o relatório do centro de custo no SIENGE e lançar o realizado na aba Realizado, preenchendo a coluna Fonte do dado com a data da extração. Item sem gasto no mês recebe 0, não fica em branco.</t>
+        </is>
+      </c>
+      <c r="C19" s="79" t="n"/>
+      <c r="D19" s="79" t="n"/>
+      <c r="E19" s="79" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="77" t="inlineStr">
+        <is>
+          <t>Controle de equipamentos</t>
+        </is>
+      </c>
+      <c r="B20" s="78" t="inlineStr">
+        <is>
+          <t>Registrar solicitações e empréstimos na aba própria, cobrar a devolução do item quebrado na troca 1x1 e controlar o estoque reserva.</t>
+        </is>
+      </c>
+      <c r="C20" s="79" t="n"/>
+      <c r="D20" s="79" t="n"/>
+      <c r="E20" s="79" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="77" t="inlineStr">
+        <is>
+          <t>Saldo por área</t>
+        </is>
+      </c>
+      <c r="B21" s="78" t="inlineStr">
+        <is>
+          <t>Acompanhar quanto resta na rubrica de cada área e avisar ANTES de comprar quando a solicitação for levar ao estouro.</t>
+        </is>
+      </c>
+      <c r="C21" s="79" t="n"/>
+      <c r="D21" s="79" t="n"/>
+      <c r="E21" s="79" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="77" t="inlineStr">
+        <is>
+          <t>Conferência de faturas</t>
+        </is>
+      </c>
+      <c r="B22" s="78" t="inlineStr">
+        <is>
+          <t>Bater o valor cobrado contra o contrato. Foi assim que apareceram o Jusbrasil 30% acima e o Astrea a 5x o orçado.</t>
+        </is>
+      </c>
+      <c r="C22" s="79" t="n"/>
+      <c r="D22" s="79" t="n"/>
+      <c r="E22" s="79" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="77" t="inlineStr">
+        <is>
+          <t>Padrão de descrição no SIENGE</t>
+        </is>
+      </c>
+      <c r="B23" s="78" t="inlineStr">
+        <is>
+          <t>Em rubricas genéricas, detalhar o item na descrição do lançamento ('Peças – mouse', 'Peças – tela'), para a análise sair por filtro.</t>
+        </is>
+      </c>
+      <c r="C23" s="79" t="n"/>
+      <c r="D23" s="79" t="n"/>
+      <c r="E23" s="79" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="77" t="inlineStr">
+        <is>
+          <t>Apoio operacional ao desenvolvimento</t>
+        </is>
+      </c>
+      <c r="B24" s="78" t="inlineStr">
+        <is>
+          <t>Assumir as tarefas operacionais do que o Jonathan conduz. Cada hora que sai das mãos dele a R$ 31,25 libera uma hora de R$ 60,58 — é o que multiplica a capacidade limitada do consultor.</t>
+        </is>
+      </c>
+      <c r="C24" s="79" t="n"/>
+      <c r="D24" s="79" t="n"/>
+      <c r="E24" s="79" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>JONATHAN — técnico e pontual, nunca rotina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="77" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="B27" s="78" t="inlineStr">
+        <is>
+          <t>O trabalho de projeto para o qual foi contratado, 3 dias por semana.</t>
+        </is>
+      </c>
+      <c r="C27" s="79" t="n"/>
+      <c r="D27" s="79" t="n"/>
+      <c r="E27" s="79" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="77" t="inlineStr">
+        <is>
+          <t>Automatizar a extração do SIENGE</t>
+        </is>
+      </c>
+      <c r="B28" s="78" t="inlineStr">
+        <is>
+          <t>Entrega de maior retorno: gasta algumas horas uma vez e devolve tempo do analista todo mês.</t>
+        </is>
+      </c>
+      <c r="C28" s="79" t="n"/>
+      <c r="D28" s="79" t="n"/>
+      <c r="E28" s="79" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="77" t="inlineStr">
+        <is>
+          <t>Avaliar AnyDesk</t>
+        </is>
+      </c>
+      <c r="B29" s="78" t="inlineStr">
+        <is>
+          <t>Definir necessidade, plano e valor da licença de acesso remoto.</t>
+        </is>
+      </c>
+      <c r="C29" s="79" t="n"/>
+      <c r="D29" s="79" t="n"/>
+      <c r="E29" s="79" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="77" t="inlineStr">
+        <is>
+          <t>Avaliar Claude x GPT e planos de equipe</t>
+        </is>
+      </c>
+      <c r="B30" s="78" t="inlineStr">
+        <is>
+          <t>Subsidiar a decisão do Vitor e resolver o compartilhamento de login, que hoje expõe histórico de cliente entre usuários.</t>
+        </is>
+      </c>
+      <c r="C30" s="79" t="n"/>
+      <c r="D30" s="79" t="n"/>
+      <c r="E30" s="79" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="77" t="inlineStr">
+        <is>
+          <t>Investigar o consumo de API</t>
+        </is>
+      </c>
+      <c r="B31" s="78" t="inlineStr">
+        <is>
+          <t>O gasto da OpenAI saltou de R$ 322 em mar para R$ 5.394 em abr, padrão de consumo por uso. Configurar limite rígido de gasto e definir quem pode gerar chave.</t>
+        </is>
+      </c>
+      <c r="C31" s="79" t="n"/>
+      <c r="D31" s="79" t="n"/>
+      <c r="E31" s="79" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="77" t="inlineStr">
+        <is>
+          <t>NÃO fazer</t>
+        </is>
+      </c>
+      <c r="B32" s="78" t="inlineStr">
+        <is>
+          <t>Rotina administrativa, lançamento de planilha, controle de estoque. São 104 h/mês a R$ 60,58 — se ele aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
+        </is>
+      </c>
+      <c r="C32" s="79" t="n"/>
+      <c r="D32" s="79" t="n"/>
+      <c r="E32" s="79" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="80" t="inlineStr">
+        <is>
+          <t>ELIAS — suporte técnico sob demanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="77" t="inlineStr">
+        <is>
+          <t>Acionamento pontual</t>
+        </is>
+      </c>
+      <c r="B35" s="78" t="inlineStr">
+        <is>
+          <t>Contrato ativo, acionado conforme a necessidade. Sem acionamento de jan a jul/26. Valor renegociado de R$ 1.065 para R$ 603,30 a partir de set/26.</t>
+        </is>
+      </c>
+      <c r="C35" s="79" t="n"/>
+      <c r="D35" s="79" t="n"/>
+      <c r="E35" s="79" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="81" t="inlineStr">
+        <is>
+          <t>CRITÉRIO: a hora do consultor custa o dobro da hora do analista, e são só 104 por mês. Tarefa recorrente vai para quem custa menos; capacidade cara fica reservada para o que só ela resolve. Consultor em rotina administrativa é o recurso mais caro na tarefa mais barata.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A11:J51"/>
-  <mergeCells count="9">
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="B6:J6"/>
+  <mergeCells count="26">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B28:E28"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="I12:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Aberta,Aguardando devolução,Aprovada,Comprada,Entregue,Negada"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F12:F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Sim,Não,Não se aplica"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H55:H79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Emprestado,Devolvido,Atrasado,Baixado"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,6 +142,11 @@
     <font>
       <b val="1"/>
       <color rgb="001E6B3A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
       <sz val="9"/>
     </font>
     <font>
@@ -257,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -413,7 +418,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -438,6 +443,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -458,11 +466,11 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1933,7 +1941,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="82" t="inlineStr">
+      <c r="A5" s="83" t="inlineStr">
         <is>
           <t>Troca 1x1</t>
         </is>
@@ -1953,7 +1961,7 @@
       <c r="J5" s="79" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>Empréstimo</t>
         </is>
@@ -1973,7 +1981,7 @@
       <c r="J6" s="79" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="83" t="inlineStr">
         <is>
           <t>Sem devolução</t>
         </is>
@@ -1993,7 +2001,7 @@
       <c r="J7" s="79" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="83" t="inlineStr">
         <is>
           <t>Aviso de saldo</t>
         </is>
@@ -2072,484 +2080,484 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="83" t="n"/>
-      <c r="B12" s="83" t="n"/>
-      <c r="C12" s="83" t="n"/>
-      <c r="D12" s="83" t="n"/>
-      <c r="E12" s="83" t="n"/>
-      <c r="F12" s="83" t="n"/>
-      <c r="G12" s="83" t="n"/>
+      <c r="A12" s="84" t="n"/>
+      <c r="B12" s="84" t="n"/>
+      <c r="C12" s="84" t="n"/>
+      <c r="D12" s="84" t="n"/>
+      <c r="E12" s="84" t="n"/>
+      <c r="F12" s="84" t="n"/>
+      <c r="G12" s="84" t="n"/>
       <c r="H12" s="49" t="n"/>
-      <c r="I12" s="83" t="n"/>
-      <c r="J12" s="83" t="n"/>
+      <c r="I12" s="84" t="n"/>
+      <c r="J12" s="84" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="83" t="n"/>
-      <c r="B13" s="83" t="n"/>
-      <c r="C13" s="83" t="n"/>
-      <c r="D13" s="83" t="n"/>
-      <c r="E13" s="83" t="n"/>
-      <c r="F13" s="83" t="n"/>
-      <c r="G13" s="83" t="n"/>
+      <c r="A13" s="84" t="n"/>
+      <c r="B13" s="84" t="n"/>
+      <c r="C13" s="84" t="n"/>
+      <c r="D13" s="84" t="n"/>
+      <c r="E13" s="84" t="n"/>
+      <c r="F13" s="84" t="n"/>
+      <c r="G13" s="84" t="n"/>
       <c r="H13" s="49" t="n"/>
-      <c r="I13" s="83" t="n"/>
-      <c r="J13" s="83" t="n"/>
+      <c r="I13" s="84" t="n"/>
+      <c r="J13" s="84" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="83" t="n"/>
-      <c r="B14" s="83" t="n"/>
-      <c r="C14" s="83" t="n"/>
-      <c r="D14" s="83" t="n"/>
-      <c r="E14" s="83" t="n"/>
-      <c r="F14" s="83" t="n"/>
-      <c r="G14" s="83" t="n"/>
+      <c r="A14" s="84" t="n"/>
+      <c r="B14" s="84" t="n"/>
+      <c r="C14" s="84" t="n"/>
+      <c r="D14" s="84" t="n"/>
+      <c r="E14" s="84" t="n"/>
+      <c r="F14" s="84" t="n"/>
+      <c r="G14" s="84" t="n"/>
       <c r="H14" s="49" t="n"/>
-      <c r="I14" s="83" t="n"/>
-      <c r="J14" s="83" t="n"/>
+      <c r="I14" s="84" t="n"/>
+      <c r="J14" s="84" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="83" t="n"/>
-      <c r="B15" s="83" t="n"/>
-      <c r="C15" s="83" t="n"/>
-      <c r="D15" s="83" t="n"/>
-      <c r="E15" s="83" t="n"/>
-      <c r="F15" s="83" t="n"/>
-      <c r="G15" s="83" t="n"/>
+      <c r="A15" s="84" t="n"/>
+      <c r="B15" s="84" t="n"/>
+      <c r="C15" s="84" t="n"/>
+      <c r="D15" s="84" t="n"/>
+      <c r="E15" s="84" t="n"/>
+      <c r="F15" s="84" t="n"/>
+      <c r="G15" s="84" t="n"/>
       <c r="H15" s="49" t="n"/>
-      <c r="I15" s="83" t="n"/>
-      <c r="J15" s="83" t="n"/>
+      <c r="I15" s="84" t="n"/>
+      <c r="J15" s="84" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="83" t="n"/>
-      <c r="B16" s="83" t="n"/>
-      <c r="C16" s="83" t="n"/>
-      <c r="D16" s="83" t="n"/>
-      <c r="E16" s="83" t="n"/>
-      <c r="F16" s="83" t="n"/>
-      <c r="G16" s="83" t="n"/>
+      <c r="A16" s="84" t="n"/>
+      <c r="B16" s="84" t="n"/>
+      <c r="C16" s="84" t="n"/>
+      <c r="D16" s="84" t="n"/>
+      <c r="E16" s="84" t="n"/>
+      <c r="F16" s="84" t="n"/>
+      <c r="G16" s="84" t="n"/>
       <c r="H16" s="49" t="n"/>
-      <c r="I16" s="83" t="n"/>
-      <c r="J16" s="83" t="n"/>
+      <c r="I16" s="84" t="n"/>
+      <c r="J16" s="84" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="83" t="n"/>
-      <c r="B17" s="83" t="n"/>
-      <c r="C17" s="83" t="n"/>
-      <c r="D17" s="83" t="n"/>
-      <c r="E17" s="83" t="n"/>
-      <c r="F17" s="83" t="n"/>
-      <c r="G17" s="83" t="n"/>
+      <c r="A17" s="84" t="n"/>
+      <c r="B17" s="84" t="n"/>
+      <c r="C17" s="84" t="n"/>
+      <c r="D17" s="84" t="n"/>
+      <c r="E17" s="84" t="n"/>
+      <c r="F17" s="84" t="n"/>
+      <c r="G17" s="84" t="n"/>
       <c r="H17" s="49" t="n"/>
-      <c r="I17" s="83" t="n"/>
-      <c r="J17" s="83" t="n"/>
+      <c r="I17" s="84" t="n"/>
+      <c r="J17" s="84" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="83" t="n"/>
-      <c r="B18" s="83" t="n"/>
-      <c r="C18" s="83" t="n"/>
-      <c r="D18" s="83" t="n"/>
-      <c r="E18" s="83" t="n"/>
-      <c r="F18" s="83" t="n"/>
-      <c r="G18" s="83" t="n"/>
+      <c r="A18" s="84" t="n"/>
+      <c r="B18" s="84" t="n"/>
+      <c r="C18" s="84" t="n"/>
+      <c r="D18" s="84" t="n"/>
+      <c r="E18" s="84" t="n"/>
+      <c r="F18" s="84" t="n"/>
+      <c r="G18" s="84" t="n"/>
       <c r="H18" s="49" t="n"/>
-      <c r="I18" s="83" t="n"/>
-      <c r="J18" s="83" t="n"/>
+      <c r="I18" s="84" t="n"/>
+      <c r="J18" s="84" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="83" t="n"/>
-      <c r="B19" s="83" t="n"/>
-      <c r="C19" s="83" t="n"/>
-      <c r="D19" s="83" t="n"/>
-      <c r="E19" s="83" t="n"/>
-      <c r="F19" s="83" t="n"/>
-      <c r="G19" s="83" t="n"/>
+      <c r="A19" s="84" t="n"/>
+      <c r="B19" s="84" t="n"/>
+      <c r="C19" s="84" t="n"/>
+      <c r="D19" s="84" t="n"/>
+      <c r="E19" s="84" t="n"/>
+      <c r="F19" s="84" t="n"/>
+      <c r="G19" s="84" t="n"/>
       <c r="H19" s="49" t="n"/>
-      <c r="I19" s="83" t="n"/>
-      <c r="J19" s="83" t="n"/>
+      <c r="I19" s="84" t="n"/>
+      <c r="J19" s="84" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="83" t="n"/>
-      <c r="B20" s="83" t="n"/>
-      <c r="C20" s="83" t="n"/>
-      <c r="D20" s="83" t="n"/>
-      <c r="E20" s="83" t="n"/>
-      <c r="F20" s="83" t="n"/>
-      <c r="G20" s="83" t="n"/>
+      <c r="A20" s="84" t="n"/>
+      <c r="B20" s="84" t="n"/>
+      <c r="C20" s="84" t="n"/>
+      <c r="D20" s="84" t="n"/>
+      <c r="E20" s="84" t="n"/>
+      <c r="F20" s="84" t="n"/>
+      <c r="G20" s="84" t="n"/>
       <c r="H20" s="49" t="n"/>
-      <c r="I20" s="83" t="n"/>
-      <c r="J20" s="83" t="n"/>
+      <c r="I20" s="84" t="n"/>
+      <c r="J20" s="84" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="83" t="n"/>
-      <c r="B21" s="83" t="n"/>
-      <c r="C21" s="83" t="n"/>
-      <c r="D21" s="83" t="n"/>
-      <c r="E21" s="83" t="n"/>
-      <c r="F21" s="83" t="n"/>
-      <c r="G21" s="83" t="n"/>
+      <c r="A21" s="84" t="n"/>
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="84" t="n"/>
+      <c r="D21" s="84" t="n"/>
+      <c r="E21" s="84" t="n"/>
+      <c r="F21" s="84" t="n"/>
+      <c r="G21" s="84" t="n"/>
       <c r="H21" s="49" t="n"/>
-      <c r="I21" s="83" t="n"/>
-      <c r="J21" s="83" t="n"/>
+      <c r="I21" s="84" t="n"/>
+      <c r="J21" s="84" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="83" t="n"/>
-      <c r="B22" s="83" t="n"/>
-      <c r="C22" s="83" t="n"/>
-      <c r="D22" s="83" t="n"/>
-      <c r="E22" s="83" t="n"/>
-      <c r="F22" s="83" t="n"/>
-      <c r="G22" s="83" t="n"/>
+      <c r="A22" s="84" t="n"/>
+      <c r="B22" s="84" t="n"/>
+      <c r="C22" s="84" t="n"/>
+      <c r="D22" s="84" t="n"/>
+      <c r="E22" s="84" t="n"/>
+      <c r="F22" s="84" t="n"/>
+      <c r="G22" s="84" t="n"/>
       <c r="H22" s="49" t="n"/>
-      <c r="I22" s="83" t="n"/>
-      <c r="J22" s="83" t="n"/>
+      <c r="I22" s="84" t="n"/>
+      <c r="J22" s="84" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="83" t="n"/>
-      <c r="B23" s="83" t="n"/>
-      <c r="C23" s="83" t="n"/>
-      <c r="D23" s="83" t="n"/>
-      <c r="E23" s="83" t="n"/>
-      <c r="F23" s="83" t="n"/>
-      <c r="G23" s="83" t="n"/>
+      <c r="A23" s="84" t="n"/>
+      <c r="B23" s="84" t="n"/>
+      <c r="C23" s="84" t="n"/>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="84" t="n"/>
+      <c r="F23" s="84" t="n"/>
+      <c r="G23" s="84" t="n"/>
       <c r="H23" s="49" t="n"/>
-      <c r="I23" s="83" t="n"/>
-      <c r="J23" s="83" t="n"/>
+      <c r="I23" s="84" t="n"/>
+      <c r="J23" s="84" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="83" t="n"/>
-      <c r="B24" s="83" t="n"/>
-      <c r="C24" s="83" t="n"/>
-      <c r="D24" s="83" t="n"/>
-      <c r="E24" s="83" t="n"/>
-      <c r="F24" s="83" t="n"/>
-      <c r="G24" s="83" t="n"/>
+      <c r="A24" s="84" t="n"/>
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="84" t="n"/>
+      <c r="D24" s="84" t="n"/>
+      <c r="E24" s="84" t="n"/>
+      <c r="F24" s="84" t="n"/>
+      <c r="G24" s="84" t="n"/>
       <c r="H24" s="49" t="n"/>
-      <c r="I24" s="83" t="n"/>
-      <c r="J24" s="83" t="n"/>
+      <c r="I24" s="84" t="n"/>
+      <c r="J24" s="84" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="83" t="n"/>
-      <c r="B25" s="83" t="n"/>
-      <c r="C25" s="83" t="n"/>
-      <c r="D25" s="83" t="n"/>
-      <c r="E25" s="83" t="n"/>
-      <c r="F25" s="83" t="n"/>
-      <c r="G25" s="83" t="n"/>
+      <c r="A25" s="84" t="n"/>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
       <c r="H25" s="49" t="n"/>
-      <c r="I25" s="83" t="n"/>
-      <c r="J25" s="83" t="n"/>
+      <c r="I25" s="84" t="n"/>
+      <c r="J25" s="84" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="83" t="n"/>
-      <c r="B26" s="83" t="n"/>
-      <c r="C26" s="83" t="n"/>
-      <c r="D26" s="83" t="n"/>
-      <c r="E26" s="83" t="n"/>
-      <c r="F26" s="83" t="n"/>
-      <c r="G26" s="83" t="n"/>
+      <c r="A26" s="84" t="n"/>
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="84" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="84" t="n"/>
+      <c r="F26" s="84" t="n"/>
+      <c r="G26" s="84" t="n"/>
       <c r="H26" s="49" t="n"/>
-      <c r="I26" s="83" t="n"/>
-      <c r="J26" s="83" t="n"/>
+      <c r="I26" s="84" t="n"/>
+      <c r="J26" s="84" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="83" t="n"/>
-      <c r="B27" s="83" t="n"/>
-      <c r="C27" s="83" t="n"/>
-      <c r="D27" s="83" t="n"/>
-      <c r="E27" s="83" t="n"/>
-      <c r="F27" s="83" t="n"/>
-      <c r="G27" s="83" t="n"/>
+      <c r="A27" s="84" t="n"/>
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="84" t="n"/>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="84" t="n"/>
+      <c r="F27" s="84" t="n"/>
+      <c r="G27" s="84" t="n"/>
       <c r="H27" s="49" t="n"/>
-      <c r="I27" s="83" t="n"/>
-      <c r="J27" s="83" t="n"/>
+      <c r="I27" s="84" t="n"/>
+      <c r="J27" s="84" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="83" t="n"/>
-      <c r="B28" s="83" t="n"/>
-      <c r="C28" s="83" t="n"/>
-      <c r="D28" s="83" t="n"/>
-      <c r="E28" s="83" t="n"/>
-      <c r="F28" s="83" t="n"/>
-      <c r="G28" s="83" t="n"/>
+      <c r="A28" s="84" t="n"/>
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="84" t="n"/>
       <c r="H28" s="49" t="n"/>
-      <c r="I28" s="83" t="n"/>
-      <c r="J28" s="83" t="n"/>
+      <c r="I28" s="84" t="n"/>
+      <c r="J28" s="84" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="83" t="n"/>
-      <c r="B29" s="83" t="n"/>
-      <c r="C29" s="83" t="n"/>
-      <c r="D29" s="83" t="n"/>
-      <c r="E29" s="83" t="n"/>
-      <c r="F29" s="83" t="n"/>
-      <c r="G29" s="83" t="n"/>
+      <c r="A29" s="84" t="n"/>
+      <c r="B29" s="84" t="n"/>
+      <c r="C29" s="84" t="n"/>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="84" t="n"/>
+      <c r="F29" s="84" t="n"/>
+      <c r="G29" s="84" t="n"/>
       <c r="H29" s="49" t="n"/>
-      <c r="I29" s="83" t="n"/>
-      <c r="J29" s="83" t="n"/>
+      <c r="I29" s="84" t="n"/>
+      <c r="J29" s="84" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="83" t="n"/>
-      <c r="B30" s="83" t="n"/>
-      <c r="C30" s="83" t="n"/>
-      <c r="D30" s="83" t="n"/>
-      <c r="E30" s="83" t="n"/>
-      <c r="F30" s="83" t="n"/>
-      <c r="G30" s="83" t="n"/>
+      <c r="A30" s="84" t="n"/>
+      <c r="B30" s="84" t="n"/>
+      <c r="C30" s="84" t="n"/>
+      <c r="D30" s="84" t="n"/>
+      <c r="E30" s="84" t="n"/>
+      <c r="F30" s="84" t="n"/>
+      <c r="G30" s="84" t="n"/>
       <c r="H30" s="49" t="n"/>
-      <c r="I30" s="83" t="n"/>
-      <c r="J30" s="83" t="n"/>
+      <c r="I30" s="84" t="n"/>
+      <c r="J30" s="84" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="83" t="n"/>
-      <c r="B31" s="83" t="n"/>
-      <c r="C31" s="83" t="n"/>
-      <c r="D31" s="83" t="n"/>
-      <c r="E31" s="83" t="n"/>
-      <c r="F31" s="83" t="n"/>
-      <c r="G31" s="83" t="n"/>
+      <c r="A31" s="84" t="n"/>
+      <c r="B31" s="84" t="n"/>
+      <c r="C31" s="84" t="n"/>
+      <c r="D31" s="84" t="n"/>
+      <c r="E31" s="84" t="n"/>
+      <c r="F31" s="84" t="n"/>
+      <c r="G31" s="84" t="n"/>
       <c r="H31" s="49" t="n"/>
-      <c r="I31" s="83" t="n"/>
-      <c r="J31" s="83" t="n"/>
+      <c r="I31" s="84" t="n"/>
+      <c r="J31" s="84" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="83" t="n"/>
-      <c r="B32" s="83" t="n"/>
-      <c r="C32" s="83" t="n"/>
-      <c r="D32" s="83" t="n"/>
-      <c r="E32" s="83" t="n"/>
-      <c r="F32" s="83" t="n"/>
-      <c r="G32" s="83" t="n"/>
+      <c r="A32" s="84" t="n"/>
+      <c r="B32" s="84" t="n"/>
+      <c r="C32" s="84" t="n"/>
+      <c r="D32" s="84" t="n"/>
+      <c r="E32" s="84" t="n"/>
+      <c r="F32" s="84" t="n"/>
+      <c r="G32" s="84" t="n"/>
       <c r="H32" s="49" t="n"/>
-      <c r="I32" s="83" t="n"/>
-      <c r="J32" s="83" t="n"/>
+      <c r="I32" s="84" t="n"/>
+      <c r="J32" s="84" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="83" t="n"/>
-      <c r="B33" s="83" t="n"/>
-      <c r="C33" s="83" t="n"/>
-      <c r="D33" s="83" t="n"/>
-      <c r="E33" s="83" t="n"/>
-      <c r="F33" s="83" t="n"/>
-      <c r="G33" s="83" t="n"/>
+      <c r="A33" s="84" t="n"/>
+      <c r="B33" s="84" t="n"/>
+      <c r="C33" s="84" t="n"/>
+      <c r="D33" s="84" t="n"/>
+      <c r="E33" s="84" t="n"/>
+      <c r="F33" s="84" t="n"/>
+      <c r="G33" s="84" t="n"/>
       <c r="H33" s="49" t="n"/>
-      <c r="I33" s="83" t="n"/>
-      <c r="J33" s="83" t="n"/>
+      <c r="I33" s="84" t="n"/>
+      <c r="J33" s="84" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="83" t="n"/>
-      <c r="B34" s="83" t="n"/>
-      <c r="C34" s="83" t="n"/>
-      <c r="D34" s="83" t="n"/>
-      <c r="E34" s="83" t="n"/>
-      <c r="F34" s="83" t="n"/>
-      <c r="G34" s="83" t="n"/>
+      <c r="A34" s="84" t="n"/>
+      <c r="B34" s="84" t="n"/>
+      <c r="C34" s="84" t="n"/>
+      <c r="D34" s="84" t="n"/>
+      <c r="E34" s="84" t="n"/>
+      <c r="F34" s="84" t="n"/>
+      <c r="G34" s="84" t="n"/>
       <c r="H34" s="49" t="n"/>
-      <c r="I34" s="83" t="n"/>
-      <c r="J34" s="83" t="n"/>
+      <c r="I34" s="84" t="n"/>
+      <c r="J34" s="84" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="83" t="n"/>
-      <c r="B35" s="83" t="n"/>
-      <c r="C35" s="83" t="n"/>
-      <c r="D35" s="83" t="n"/>
-      <c r="E35" s="83" t="n"/>
-      <c r="F35" s="83" t="n"/>
-      <c r="G35" s="83" t="n"/>
+      <c r="A35" s="84" t="n"/>
+      <c r="B35" s="84" t="n"/>
+      <c r="C35" s="84" t="n"/>
+      <c r="D35" s="84" t="n"/>
+      <c r="E35" s="84" t="n"/>
+      <c r="F35" s="84" t="n"/>
+      <c r="G35" s="84" t="n"/>
       <c r="H35" s="49" t="n"/>
-      <c r="I35" s="83" t="n"/>
-      <c r="J35" s="83" t="n"/>
+      <c r="I35" s="84" t="n"/>
+      <c r="J35" s="84" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="83" t="n"/>
-      <c r="B36" s="83" t="n"/>
-      <c r="C36" s="83" t="n"/>
-      <c r="D36" s="83" t="n"/>
-      <c r="E36" s="83" t="n"/>
-      <c r="F36" s="83" t="n"/>
-      <c r="G36" s="83" t="n"/>
+      <c r="A36" s="84" t="n"/>
+      <c r="B36" s="84" t="n"/>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
       <c r="H36" s="49" t="n"/>
-      <c r="I36" s="83" t="n"/>
-      <c r="J36" s="83" t="n"/>
+      <c r="I36" s="84" t="n"/>
+      <c r="J36" s="84" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="83" t="n"/>
-      <c r="B37" s="83" t="n"/>
-      <c r="C37" s="83" t="n"/>
-      <c r="D37" s="83" t="n"/>
-      <c r="E37" s="83" t="n"/>
-      <c r="F37" s="83" t="n"/>
-      <c r="G37" s="83" t="n"/>
+      <c r="A37" s="84" t="n"/>
+      <c r="B37" s="84" t="n"/>
+      <c r="C37" s="84" t="n"/>
+      <c r="D37" s="84" t="n"/>
+      <c r="E37" s="84" t="n"/>
+      <c r="F37" s="84" t="n"/>
+      <c r="G37" s="84" t="n"/>
       <c r="H37" s="49" t="n"/>
-      <c r="I37" s="83" t="n"/>
-      <c r="J37" s="83" t="n"/>
+      <c r="I37" s="84" t="n"/>
+      <c r="J37" s="84" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="83" t="n"/>
-      <c r="B38" s="83" t="n"/>
-      <c r="C38" s="83" t="n"/>
-      <c r="D38" s="83" t="n"/>
-      <c r="E38" s="83" t="n"/>
-      <c r="F38" s="83" t="n"/>
-      <c r="G38" s="83" t="n"/>
+      <c r="A38" s="84" t="n"/>
+      <c r="B38" s="84" t="n"/>
+      <c r="C38" s="84" t="n"/>
+      <c r="D38" s="84" t="n"/>
+      <c r="E38" s="84" t="n"/>
+      <c r="F38" s="84" t="n"/>
+      <c r="G38" s="84" t="n"/>
       <c r="H38" s="49" t="n"/>
-      <c r="I38" s="83" t="n"/>
-      <c r="J38" s="83" t="n"/>
+      <c r="I38" s="84" t="n"/>
+      <c r="J38" s="84" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="83" t="n"/>
-      <c r="B39" s="83" t="n"/>
-      <c r="C39" s="83" t="n"/>
-      <c r="D39" s="83" t="n"/>
-      <c r="E39" s="83" t="n"/>
-      <c r="F39" s="83" t="n"/>
-      <c r="G39" s="83" t="n"/>
+      <c r="A39" s="84" t="n"/>
+      <c r="B39" s="84" t="n"/>
+      <c r="C39" s="84" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
+      <c r="G39" s="84" t="n"/>
       <c r="H39" s="49" t="n"/>
-      <c r="I39" s="83" t="n"/>
-      <c r="J39" s="83" t="n"/>
+      <c r="I39" s="84" t="n"/>
+      <c r="J39" s="84" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="83" t="n"/>
-      <c r="B40" s="83" t="n"/>
-      <c r="C40" s="83" t="n"/>
-      <c r="D40" s="83" t="n"/>
-      <c r="E40" s="83" t="n"/>
-      <c r="F40" s="83" t="n"/>
-      <c r="G40" s="83" t="n"/>
+      <c r="A40" s="84" t="n"/>
+      <c r="B40" s="84" t="n"/>
+      <c r="C40" s="84" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
+      <c r="G40" s="84" t="n"/>
       <c r="H40" s="49" t="n"/>
-      <c r="I40" s="83" t="n"/>
-      <c r="J40" s="83" t="n"/>
+      <c r="I40" s="84" t="n"/>
+      <c r="J40" s="84" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="83" t="n"/>
-      <c r="B41" s="83" t="n"/>
-      <c r="C41" s="83" t="n"/>
-      <c r="D41" s="83" t="n"/>
-      <c r="E41" s="83" t="n"/>
-      <c r="F41" s="83" t="n"/>
-      <c r="G41" s="83" t="n"/>
+      <c r="A41" s="84" t="n"/>
+      <c r="B41" s="84" t="n"/>
+      <c r="C41" s="84" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="84" t="n"/>
+      <c r="G41" s="84" t="n"/>
       <c r="H41" s="49" t="n"/>
-      <c r="I41" s="83" t="n"/>
-      <c r="J41" s="83" t="n"/>
+      <c r="I41" s="84" t="n"/>
+      <c r="J41" s="84" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="83" t="n"/>
-      <c r="B42" s="83" t="n"/>
-      <c r="C42" s="83" t="n"/>
-      <c r="D42" s="83" t="n"/>
-      <c r="E42" s="83" t="n"/>
-      <c r="F42" s="83" t="n"/>
-      <c r="G42" s="83" t="n"/>
+      <c r="A42" s="84" t="n"/>
+      <c r="B42" s="84" t="n"/>
+      <c r="C42" s="84" t="n"/>
+      <c r="D42" s="84" t="n"/>
+      <c r="E42" s="84" t="n"/>
+      <c r="F42" s="84" t="n"/>
+      <c r="G42" s="84" t="n"/>
       <c r="H42" s="49" t="n"/>
-      <c r="I42" s="83" t="n"/>
-      <c r="J42" s="83" t="n"/>
+      <c r="I42" s="84" t="n"/>
+      <c r="J42" s="84" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="83" t="n"/>
-      <c r="B43" s="83" t="n"/>
-      <c r="C43" s="83" t="n"/>
-      <c r="D43" s="83" t="n"/>
-      <c r="E43" s="83" t="n"/>
-      <c r="F43" s="83" t="n"/>
-      <c r="G43" s="83" t="n"/>
+      <c r="A43" s="84" t="n"/>
+      <c r="B43" s="84" t="n"/>
+      <c r="C43" s="84" t="n"/>
+      <c r="D43" s="84" t="n"/>
+      <c r="E43" s="84" t="n"/>
+      <c r="F43" s="84" t="n"/>
+      <c r="G43" s="84" t="n"/>
       <c r="H43" s="49" t="n"/>
-      <c r="I43" s="83" t="n"/>
-      <c r="J43" s="83" t="n"/>
+      <c r="I43" s="84" t="n"/>
+      <c r="J43" s="84" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="83" t="n"/>
-      <c r="B44" s="83" t="n"/>
-      <c r="C44" s="83" t="n"/>
-      <c r="D44" s="83" t="n"/>
-      <c r="E44" s="83" t="n"/>
-      <c r="F44" s="83" t="n"/>
-      <c r="G44" s="83" t="n"/>
+      <c r="A44" s="84" t="n"/>
+      <c r="B44" s="84" t="n"/>
+      <c r="C44" s="84" t="n"/>
+      <c r="D44" s="84" t="n"/>
+      <c r="E44" s="84" t="n"/>
+      <c r="F44" s="84" t="n"/>
+      <c r="G44" s="84" t="n"/>
       <c r="H44" s="49" t="n"/>
-      <c r="I44" s="83" t="n"/>
-      <c r="J44" s="83" t="n"/>
+      <c r="I44" s="84" t="n"/>
+      <c r="J44" s="84" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="83" t="n"/>
-      <c r="B45" s="83" t="n"/>
-      <c r="C45" s="83" t="n"/>
-      <c r="D45" s="83" t="n"/>
-      <c r="E45" s="83" t="n"/>
-      <c r="F45" s="83" t="n"/>
-      <c r="G45" s="83" t="n"/>
+      <c r="A45" s="84" t="n"/>
+      <c r="B45" s="84" t="n"/>
+      <c r="C45" s="84" t="n"/>
+      <c r="D45" s="84" t="n"/>
+      <c r="E45" s="84" t="n"/>
+      <c r="F45" s="84" t="n"/>
+      <c r="G45" s="84" t="n"/>
       <c r="H45" s="49" t="n"/>
-      <c r="I45" s="83" t="n"/>
-      <c r="J45" s="83" t="n"/>
+      <c r="I45" s="84" t="n"/>
+      <c r="J45" s="84" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="83" t="n"/>
-      <c r="B46" s="83" t="n"/>
-      <c r="C46" s="83" t="n"/>
-      <c r="D46" s="83" t="n"/>
-      <c r="E46" s="83" t="n"/>
-      <c r="F46" s="83" t="n"/>
-      <c r="G46" s="83" t="n"/>
+      <c r="A46" s="84" t="n"/>
+      <c r="B46" s="84" t="n"/>
+      <c r="C46" s="84" t="n"/>
+      <c r="D46" s="84" t="n"/>
+      <c r="E46" s="84" t="n"/>
+      <c r="F46" s="84" t="n"/>
+      <c r="G46" s="84" t="n"/>
       <c r="H46" s="49" t="n"/>
-      <c r="I46" s="83" t="n"/>
-      <c r="J46" s="83" t="n"/>
+      <c r="I46" s="84" t="n"/>
+      <c r="J46" s="84" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="83" t="n"/>
-      <c r="B47" s="83" t="n"/>
-      <c r="C47" s="83" t="n"/>
-      <c r="D47" s="83" t="n"/>
-      <c r="E47" s="83" t="n"/>
-      <c r="F47" s="83" t="n"/>
-      <c r="G47" s="83" t="n"/>
+      <c r="A47" s="84" t="n"/>
+      <c r="B47" s="84" t="n"/>
+      <c r="C47" s="84" t="n"/>
+      <c r="D47" s="84" t="n"/>
+      <c r="E47" s="84" t="n"/>
+      <c r="F47" s="84" t="n"/>
+      <c r="G47" s="84" t="n"/>
       <c r="H47" s="49" t="n"/>
-      <c r="I47" s="83" t="n"/>
-      <c r="J47" s="83" t="n"/>
+      <c r="I47" s="84" t="n"/>
+      <c r="J47" s="84" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="83" t="n"/>
-      <c r="B48" s="83" t="n"/>
-      <c r="C48" s="83" t="n"/>
-      <c r="D48" s="83" t="n"/>
-      <c r="E48" s="83" t="n"/>
-      <c r="F48" s="83" t="n"/>
-      <c r="G48" s="83" t="n"/>
+      <c r="A48" s="84" t="n"/>
+      <c r="B48" s="84" t="n"/>
+      <c r="C48" s="84" t="n"/>
+      <c r="D48" s="84" t="n"/>
+      <c r="E48" s="84" t="n"/>
+      <c r="F48" s="84" t="n"/>
+      <c r="G48" s="84" t="n"/>
       <c r="H48" s="49" t="n"/>
-      <c r="I48" s="83" t="n"/>
-      <c r="J48" s="83" t="n"/>
+      <c r="I48" s="84" t="n"/>
+      <c r="J48" s="84" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="83" t="n"/>
-      <c r="B49" s="83" t="n"/>
-      <c r="C49" s="83" t="n"/>
-      <c r="D49" s="83" t="n"/>
-      <c r="E49" s="83" t="n"/>
-      <c r="F49" s="83" t="n"/>
-      <c r="G49" s="83" t="n"/>
+      <c r="A49" s="84" t="n"/>
+      <c r="B49" s="84" t="n"/>
+      <c r="C49" s="84" t="n"/>
+      <c r="D49" s="84" t="n"/>
+      <c r="E49" s="84" t="n"/>
+      <c r="F49" s="84" t="n"/>
+      <c r="G49" s="84" t="n"/>
       <c r="H49" s="49" t="n"/>
-      <c r="I49" s="83" t="n"/>
-      <c r="J49" s="83" t="n"/>
+      <c r="I49" s="84" t="n"/>
+      <c r="J49" s="84" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="83" t="n"/>
-      <c r="B50" s="83" t="n"/>
-      <c r="C50" s="83" t="n"/>
-      <c r="D50" s="83" t="n"/>
-      <c r="E50" s="83" t="n"/>
-      <c r="F50" s="83" t="n"/>
-      <c r="G50" s="83" t="n"/>
+      <c r="A50" s="84" t="n"/>
+      <c r="B50" s="84" t="n"/>
+      <c r="C50" s="84" t="n"/>
+      <c r="D50" s="84" t="n"/>
+      <c r="E50" s="84" t="n"/>
+      <c r="F50" s="84" t="n"/>
+      <c r="G50" s="84" t="n"/>
       <c r="H50" s="49" t="n"/>
-      <c r="I50" s="83" t="n"/>
-      <c r="J50" s="83" t="n"/>
+      <c r="I50" s="84" t="n"/>
+      <c r="J50" s="84" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="83" t="n"/>
-      <c r="B51" s="83" t="n"/>
-      <c r="C51" s="83" t="n"/>
-      <c r="D51" s="83" t="n"/>
-      <c r="E51" s="83" t="n"/>
-      <c r="F51" s="83" t="n"/>
-      <c r="G51" s="83" t="n"/>
+      <c r="A51" s="84" t="n"/>
+      <c r="B51" s="84" t="n"/>
+      <c r="C51" s="84" t="n"/>
+      <c r="D51" s="84" t="n"/>
+      <c r="E51" s="84" t="n"/>
+      <c r="F51" s="84" t="n"/>
+      <c r="G51" s="84" t="n"/>
       <c r="H51" s="49" t="n"/>
-      <c r="I51" s="83" t="n"/>
-      <c r="J51" s="83" t="n"/>
+      <c r="I51" s="84" t="n"/>
+      <c r="J51" s="84" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
@@ -2559,431 +2567,431 @@
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="84" t="inlineStr">
+      <c r="A54" s="85" t="inlineStr">
         <is>
           <t>Item emprestado</t>
         </is>
       </c>
-      <c r="B54" s="84" t="inlineStr">
+      <c r="B54" s="85" t="inlineStr">
         <is>
           <t>Patrimônio</t>
         </is>
       </c>
-      <c r="C54" s="84" t="inlineStr">
+      <c r="C54" s="85" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="D54" s="84" t="inlineStr">
+      <c r="D54" s="85" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="E54" s="84" t="inlineStr">
+      <c r="E54" s="85" t="inlineStr">
         <is>
           <t>Saída em</t>
         </is>
       </c>
-      <c r="F54" s="84" t="inlineStr">
+      <c r="F54" s="85" t="inlineStr">
         <is>
           <t>Previsão de devolução</t>
         </is>
       </c>
-      <c r="G54" s="84" t="inlineStr">
+      <c r="G54" s="85" t="inlineStr">
         <is>
           <t>Devolvido em</t>
         </is>
       </c>
-      <c r="H54" s="84" t="inlineStr">
+      <c r="H54" s="85" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I54" s="84" t="inlineStr">
+      <c r="I54" s="85" t="inlineStr">
         <is>
           <t>Dias em posse</t>
         </is>
       </c>
-      <c r="J54" s="84" t="inlineStr">
+      <c r="J54" s="85" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="83" t="n"/>
-      <c r="B55" s="83" t="n"/>
-      <c r="C55" s="83" t="n"/>
-      <c r="D55" s="83" t="n"/>
-      <c r="E55" s="83" t="n"/>
-      <c r="F55" s="83" t="n"/>
-      <c r="G55" s="83" t="n"/>
-      <c r="H55" s="83" t="n"/>
-      <c r="I55" s="85">
+      <c r="A55" s="84" t="n"/>
+      <c r="B55" s="84" t="n"/>
+      <c r="C55" s="84" t="n"/>
+      <c r="D55" s="84" t="n"/>
+      <c r="E55" s="84" t="n"/>
+      <c r="F55" s="84" t="n"/>
+      <c r="G55" s="84" t="n"/>
+      <c r="H55" s="84" t="n"/>
+      <c r="I55" s="86">
         <f>IF(E55="","",IF(G55="",TODAY()-E55,G55-E55))</f>
         <v/>
       </c>
-      <c r="J55" s="83" t="n"/>
+      <c r="J55" s="84" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="83" t="n"/>
-      <c r="B56" s="83" t="n"/>
-      <c r="C56" s="83" t="n"/>
-      <c r="D56" s="83" t="n"/>
-      <c r="E56" s="83" t="n"/>
-      <c r="F56" s="83" t="n"/>
-      <c r="G56" s="83" t="n"/>
-      <c r="H56" s="83" t="n"/>
-      <c r="I56" s="85">
+      <c r="A56" s="84" t="n"/>
+      <c r="B56" s="84" t="n"/>
+      <c r="C56" s="84" t="n"/>
+      <c r="D56" s="84" t="n"/>
+      <c r="E56" s="84" t="n"/>
+      <c r="F56" s="84" t="n"/>
+      <c r="G56" s="84" t="n"/>
+      <c r="H56" s="84" t="n"/>
+      <c r="I56" s="86">
         <f>IF(E56="","",IF(G56="",TODAY()-E56,G56-E56))</f>
         <v/>
       </c>
-      <c r="J56" s="83" t="n"/>
+      <c r="J56" s="84" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="83" t="n"/>
-      <c r="B57" s="83" t="n"/>
-      <c r="C57" s="83" t="n"/>
-      <c r="D57" s="83" t="n"/>
-      <c r="E57" s="83" t="n"/>
-      <c r="F57" s="83" t="n"/>
-      <c r="G57" s="83" t="n"/>
-      <c r="H57" s="83" t="n"/>
-      <c r="I57" s="85">
+      <c r="A57" s="84" t="n"/>
+      <c r="B57" s="84" t="n"/>
+      <c r="C57" s="84" t="n"/>
+      <c r="D57" s="84" t="n"/>
+      <c r="E57" s="84" t="n"/>
+      <c r="F57" s="84" t="n"/>
+      <c r="G57" s="84" t="n"/>
+      <c r="H57" s="84" t="n"/>
+      <c r="I57" s="86">
         <f>IF(E57="","",IF(G57="",TODAY()-E57,G57-E57))</f>
         <v/>
       </c>
-      <c r="J57" s="83" t="n"/>
+      <c r="J57" s="84" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="83" t="n"/>
-      <c r="B58" s="83" t="n"/>
-      <c r="C58" s="83" t="n"/>
-      <c r="D58" s="83" t="n"/>
-      <c r="E58" s="83" t="n"/>
-      <c r="F58" s="83" t="n"/>
-      <c r="G58" s="83" t="n"/>
-      <c r="H58" s="83" t="n"/>
-      <c r="I58" s="85">
+      <c r="A58" s="84" t="n"/>
+      <c r="B58" s="84" t="n"/>
+      <c r="C58" s="84" t="n"/>
+      <c r="D58" s="84" t="n"/>
+      <c r="E58" s="84" t="n"/>
+      <c r="F58" s="84" t="n"/>
+      <c r="G58" s="84" t="n"/>
+      <c r="H58" s="84" t="n"/>
+      <c r="I58" s="86">
         <f>IF(E58="","",IF(G58="",TODAY()-E58,G58-E58))</f>
         <v/>
       </c>
-      <c r="J58" s="83" t="n"/>
+      <c r="J58" s="84" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="83" t="n"/>
-      <c r="B59" s="83" t="n"/>
-      <c r="C59" s="83" t="n"/>
-      <c r="D59" s="83" t="n"/>
-      <c r="E59" s="83" t="n"/>
-      <c r="F59" s="83" t="n"/>
-      <c r="G59" s="83" t="n"/>
-      <c r="H59" s="83" t="n"/>
-      <c r="I59" s="85">
+      <c r="A59" s="84" t="n"/>
+      <c r="B59" s="84" t="n"/>
+      <c r="C59" s="84" t="n"/>
+      <c r="D59" s="84" t="n"/>
+      <c r="E59" s="84" t="n"/>
+      <c r="F59" s="84" t="n"/>
+      <c r="G59" s="84" t="n"/>
+      <c r="H59" s="84" t="n"/>
+      <c r="I59" s="86">
         <f>IF(E59="","",IF(G59="",TODAY()-E59,G59-E59))</f>
         <v/>
       </c>
-      <c r="J59" s="83" t="n"/>
+      <c r="J59" s="84" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="83" t="n"/>
-      <c r="B60" s="83" t="n"/>
-      <c r="C60" s="83" t="n"/>
-      <c r="D60" s="83" t="n"/>
-      <c r="E60" s="83" t="n"/>
-      <c r="F60" s="83" t="n"/>
-      <c r="G60" s="83" t="n"/>
-      <c r="H60" s="83" t="n"/>
-      <c r="I60" s="85">
+      <c r="A60" s="84" t="n"/>
+      <c r="B60" s="84" t="n"/>
+      <c r="C60" s="84" t="n"/>
+      <c r="D60" s="84" t="n"/>
+      <c r="E60" s="84" t="n"/>
+      <c r="F60" s="84" t="n"/>
+      <c r="G60" s="84" t="n"/>
+      <c r="H60" s="84" t="n"/>
+      <c r="I60" s="86">
         <f>IF(E60="","",IF(G60="",TODAY()-E60,G60-E60))</f>
         <v/>
       </c>
-      <c r="J60" s="83" t="n"/>
+      <c r="J60" s="84" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="83" t="n"/>
-      <c r="B61" s="83" t="n"/>
-      <c r="C61" s="83" t="n"/>
-      <c r="D61" s="83" t="n"/>
-      <c r="E61" s="83" t="n"/>
-      <c r="F61" s="83" t="n"/>
-      <c r="G61" s="83" t="n"/>
-      <c r="H61" s="83" t="n"/>
-      <c r="I61" s="85">
+      <c r="A61" s="84" t="n"/>
+      <c r="B61" s="84" t="n"/>
+      <c r="C61" s="84" t="n"/>
+      <c r="D61" s="84" t="n"/>
+      <c r="E61" s="84" t="n"/>
+      <c r="F61" s="84" t="n"/>
+      <c r="G61" s="84" t="n"/>
+      <c r="H61" s="84" t="n"/>
+      <c r="I61" s="86">
         <f>IF(E61="","",IF(G61="",TODAY()-E61,G61-E61))</f>
         <v/>
       </c>
-      <c r="J61" s="83" t="n"/>
+      <c r="J61" s="84" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="83" t="n"/>
-      <c r="B62" s="83" t="n"/>
-      <c r="C62" s="83" t="n"/>
-      <c r="D62" s="83" t="n"/>
-      <c r="E62" s="83" t="n"/>
-      <c r="F62" s="83" t="n"/>
-      <c r="G62" s="83" t="n"/>
-      <c r="H62" s="83" t="n"/>
-      <c r="I62" s="85">
+      <c r="A62" s="84" t="n"/>
+      <c r="B62" s="84" t="n"/>
+      <c r="C62" s="84" t="n"/>
+      <c r="D62" s="84" t="n"/>
+      <c r="E62" s="84" t="n"/>
+      <c r="F62" s="84" t="n"/>
+      <c r="G62" s="84" t="n"/>
+      <c r="H62" s="84" t="n"/>
+      <c r="I62" s="86">
         <f>IF(E62="","",IF(G62="",TODAY()-E62,G62-E62))</f>
         <v/>
       </c>
-      <c r="J62" s="83" t="n"/>
+      <c r="J62" s="84" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="83" t="n"/>
-      <c r="B63" s="83" t="n"/>
-      <c r="C63" s="83" t="n"/>
-      <c r="D63" s="83" t="n"/>
-      <c r="E63" s="83" t="n"/>
-      <c r="F63" s="83" t="n"/>
-      <c r="G63" s="83" t="n"/>
-      <c r="H63" s="83" t="n"/>
-      <c r="I63" s="85">
+      <c r="A63" s="84" t="n"/>
+      <c r="B63" s="84" t="n"/>
+      <c r="C63" s="84" t="n"/>
+      <c r="D63" s="84" t="n"/>
+      <c r="E63" s="84" t="n"/>
+      <c r="F63" s="84" t="n"/>
+      <c r="G63" s="84" t="n"/>
+      <c r="H63" s="84" t="n"/>
+      <c r="I63" s="86">
         <f>IF(E63="","",IF(G63="",TODAY()-E63,G63-E63))</f>
         <v/>
       </c>
-      <c r="J63" s="83" t="n"/>
+      <c r="J63" s="84" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="83" t="n"/>
-      <c r="B64" s="83" t="n"/>
-      <c r="C64" s="83" t="n"/>
-      <c r="D64" s="83" t="n"/>
-      <c r="E64" s="83" t="n"/>
-      <c r="F64" s="83" t="n"/>
-      <c r="G64" s="83" t="n"/>
-      <c r="H64" s="83" t="n"/>
-      <c r="I64" s="85">
+      <c r="A64" s="84" t="n"/>
+      <c r="B64" s="84" t="n"/>
+      <c r="C64" s="84" t="n"/>
+      <c r="D64" s="84" t="n"/>
+      <c r="E64" s="84" t="n"/>
+      <c r="F64" s="84" t="n"/>
+      <c r="G64" s="84" t="n"/>
+      <c r="H64" s="84" t="n"/>
+      <c r="I64" s="86">
         <f>IF(E64="","",IF(G64="",TODAY()-E64,G64-E64))</f>
         <v/>
       </c>
-      <c r="J64" s="83" t="n"/>
+      <c r="J64" s="84" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="83" t="n"/>
-      <c r="B65" s="83" t="n"/>
-      <c r="C65" s="83" t="n"/>
-      <c r="D65" s="83" t="n"/>
-      <c r="E65" s="83" t="n"/>
-      <c r="F65" s="83" t="n"/>
-      <c r="G65" s="83" t="n"/>
-      <c r="H65" s="83" t="n"/>
-      <c r="I65" s="85">
+      <c r="A65" s="84" t="n"/>
+      <c r="B65" s="84" t="n"/>
+      <c r="C65" s="84" t="n"/>
+      <c r="D65" s="84" t="n"/>
+      <c r="E65" s="84" t="n"/>
+      <c r="F65" s="84" t="n"/>
+      <c r="G65" s="84" t="n"/>
+      <c r="H65" s="84" t="n"/>
+      <c r="I65" s="86">
         <f>IF(E65="","",IF(G65="",TODAY()-E65,G65-E65))</f>
         <v/>
       </c>
-      <c r="J65" s="83" t="n"/>
+      <c r="J65" s="84" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="83" t="n"/>
-      <c r="B66" s="83" t="n"/>
-      <c r="C66" s="83" t="n"/>
-      <c r="D66" s="83" t="n"/>
-      <c r="E66" s="83" t="n"/>
-      <c r="F66" s="83" t="n"/>
-      <c r="G66" s="83" t="n"/>
-      <c r="H66" s="83" t="n"/>
-      <c r="I66" s="85">
+      <c r="A66" s="84" t="n"/>
+      <c r="B66" s="84" t="n"/>
+      <c r="C66" s="84" t="n"/>
+      <c r="D66" s="84" t="n"/>
+      <c r="E66" s="84" t="n"/>
+      <c r="F66" s="84" t="n"/>
+      <c r="G66" s="84" t="n"/>
+      <c r="H66" s="84" t="n"/>
+      <c r="I66" s="86">
         <f>IF(E66="","",IF(G66="",TODAY()-E66,G66-E66))</f>
         <v/>
       </c>
-      <c r="J66" s="83" t="n"/>
+      <c r="J66" s="84" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="83" t="n"/>
-      <c r="B67" s="83" t="n"/>
-      <c r="C67" s="83" t="n"/>
-      <c r="D67" s="83" t="n"/>
-      <c r="E67" s="83" t="n"/>
-      <c r="F67" s="83" t="n"/>
-      <c r="G67" s="83" t="n"/>
-      <c r="H67" s="83" t="n"/>
-      <c r="I67" s="85">
+      <c r="A67" s="84" t="n"/>
+      <c r="B67" s="84" t="n"/>
+      <c r="C67" s="84" t="n"/>
+      <c r="D67" s="84" t="n"/>
+      <c r="E67" s="84" t="n"/>
+      <c r="F67" s="84" t="n"/>
+      <c r="G67" s="84" t="n"/>
+      <c r="H67" s="84" t="n"/>
+      <c r="I67" s="86">
         <f>IF(E67="","",IF(G67="",TODAY()-E67,G67-E67))</f>
         <v/>
       </c>
-      <c r="J67" s="83" t="n"/>
+      <c r="J67" s="84" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="83" t="n"/>
-      <c r="B68" s="83" t="n"/>
-      <c r="C68" s="83" t="n"/>
-      <c r="D68" s="83" t="n"/>
-      <c r="E68" s="83" t="n"/>
-      <c r="F68" s="83" t="n"/>
-      <c r="G68" s="83" t="n"/>
-      <c r="H68" s="83" t="n"/>
-      <c r="I68" s="85">
+      <c r="A68" s="84" t="n"/>
+      <c r="B68" s="84" t="n"/>
+      <c r="C68" s="84" t="n"/>
+      <c r="D68" s="84" t="n"/>
+      <c r="E68" s="84" t="n"/>
+      <c r="F68" s="84" t="n"/>
+      <c r="G68" s="84" t="n"/>
+      <c r="H68" s="84" t="n"/>
+      <c r="I68" s="86">
         <f>IF(E68="","",IF(G68="",TODAY()-E68,G68-E68))</f>
         <v/>
       </c>
-      <c r="J68" s="83" t="n"/>
+      <c r="J68" s="84" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="83" t="n"/>
-      <c r="B69" s="83" t="n"/>
-      <c r="C69" s="83" t="n"/>
-      <c r="D69" s="83" t="n"/>
-      <c r="E69" s="83" t="n"/>
-      <c r="F69" s="83" t="n"/>
-      <c r="G69" s="83" t="n"/>
-      <c r="H69" s="83" t="n"/>
-      <c r="I69" s="85">
+      <c r="A69" s="84" t="n"/>
+      <c r="B69" s="84" t="n"/>
+      <c r="C69" s="84" t="n"/>
+      <c r="D69" s="84" t="n"/>
+      <c r="E69" s="84" t="n"/>
+      <c r="F69" s="84" t="n"/>
+      <c r="G69" s="84" t="n"/>
+      <c r="H69" s="84" t="n"/>
+      <c r="I69" s="86">
         <f>IF(E69="","",IF(G69="",TODAY()-E69,G69-E69))</f>
         <v/>
       </c>
-      <c r="J69" s="83" t="n"/>
+      <c r="J69" s="84" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="83" t="n"/>
-      <c r="B70" s="83" t="n"/>
-      <c r="C70" s="83" t="n"/>
-      <c r="D70" s="83" t="n"/>
-      <c r="E70" s="83" t="n"/>
-      <c r="F70" s="83" t="n"/>
-      <c r="G70" s="83" t="n"/>
-      <c r="H70" s="83" t="n"/>
-      <c r="I70" s="85">
+      <c r="A70" s="84" t="n"/>
+      <c r="B70" s="84" t="n"/>
+      <c r="C70" s="84" t="n"/>
+      <c r="D70" s="84" t="n"/>
+      <c r="E70" s="84" t="n"/>
+      <c r="F70" s="84" t="n"/>
+      <c r="G70" s="84" t="n"/>
+      <c r="H70" s="84" t="n"/>
+      <c r="I70" s="86">
         <f>IF(E70="","",IF(G70="",TODAY()-E70,G70-E70))</f>
         <v/>
       </c>
-      <c r="J70" s="83" t="n"/>
+      <c r="J70" s="84" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="83" t="n"/>
-      <c r="B71" s="83" t="n"/>
-      <c r="C71" s="83" t="n"/>
-      <c r="D71" s="83" t="n"/>
-      <c r="E71" s="83" t="n"/>
-      <c r="F71" s="83" t="n"/>
-      <c r="G71" s="83" t="n"/>
-      <c r="H71" s="83" t="n"/>
-      <c r="I71" s="85">
+      <c r="A71" s="84" t="n"/>
+      <c r="B71" s="84" t="n"/>
+      <c r="C71" s="84" t="n"/>
+      <c r="D71" s="84" t="n"/>
+      <c r="E71" s="84" t="n"/>
+      <c r="F71" s="84" t="n"/>
+      <c r="G71" s="84" t="n"/>
+      <c r="H71" s="84" t="n"/>
+      <c r="I71" s="86">
         <f>IF(E71="","",IF(G71="",TODAY()-E71,G71-E71))</f>
         <v/>
       </c>
-      <c r="J71" s="83" t="n"/>
+      <c r="J71" s="84" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="83" t="n"/>
-      <c r="B72" s="83" t="n"/>
-      <c r="C72" s="83" t="n"/>
-      <c r="D72" s="83" t="n"/>
-      <c r="E72" s="83" t="n"/>
-      <c r="F72" s="83" t="n"/>
-      <c r="G72" s="83" t="n"/>
-      <c r="H72" s="83" t="n"/>
-      <c r="I72" s="85">
+      <c r="A72" s="84" t="n"/>
+      <c r="B72" s="84" t="n"/>
+      <c r="C72" s="84" t="n"/>
+      <c r="D72" s="84" t="n"/>
+      <c r="E72" s="84" t="n"/>
+      <c r="F72" s="84" t="n"/>
+      <c r="G72" s="84" t="n"/>
+      <c r="H72" s="84" t="n"/>
+      <c r="I72" s="86">
         <f>IF(E72="","",IF(G72="",TODAY()-E72,G72-E72))</f>
         <v/>
       </c>
-      <c r="J72" s="83" t="n"/>
+      <c r="J72" s="84" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="83" t="n"/>
-      <c r="B73" s="83" t="n"/>
-      <c r="C73" s="83" t="n"/>
-      <c r="D73" s="83" t="n"/>
-      <c r="E73" s="83" t="n"/>
-      <c r="F73" s="83" t="n"/>
-      <c r="G73" s="83" t="n"/>
-      <c r="H73" s="83" t="n"/>
-      <c r="I73" s="85">
+      <c r="A73" s="84" t="n"/>
+      <c r="B73" s="84" t="n"/>
+      <c r="C73" s="84" t="n"/>
+      <c r="D73" s="84" t="n"/>
+      <c r="E73" s="84" t="n"/>
+      <c r="F73" s="84" t="n"/>
+      <c r="G73" s="84" t="n"/>
+      <c r="H73" s="84" t="n"/>
+      <c r="I73" s="86">
         <f>IF(E73="","",IF(G73="",TODAY()-E73,G73-E73))</f>
         <v/>
       </c>
-      <c r="J73" s="83" t="n"/>
+      <c r="J73" s="84" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="83" t="n"/>
-      <c r="B74" s="83" t="n"/>
-      <c r="C74" s="83" t="n"/>
-      <c r="D74" s="83" t="n"/>
-      <c r="E74" s="83" t="n"/>
-      <c r="F74" s="83" t="n"/>
-      <c r="G74" s="83" t="n"/>
-      <c r="H74" s="83" t="n"/>
-      <c r="I74" s="85">
+      <c r="A74" s="84" t="n"/>
+      <c r="B74" s="84" t="n"/>
+      <c r="C74" s="84" t="n"/>
+      <c r="D74" s="84" t="n"/>
+      <c r="E74" s="84" t="n"/>
+      <c r="F74" s="84" t="n"/>
+      <c r="G74" s="84" t="n"/>
+      <c r="H74" s="84" t="n"/>
+      <c r="I74" s="86">
         <f>IF(E74="","",IF(G74="",TODAY()-E74,G74-E74))</f>
         <v/>
       </c>
-      <c r="J74" s="83" t="n"/>
+      <c r="J74" s="84" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="83" t="n"/>
-      <c r="B75" s="83" t="n"/>
-      <c r="C75" s="83" t="n"/>
-      <c r="D75" s="83" t="n"/>
-      <c r="E75" s="83" t="n"/>
-      <c r="F75" s="83" t="n"/>
-      <c r="G75" s="83" t="n"/>
-      <c r="H75" s="83" t="n"/>
-      <c r="I75" s="85">
+      <c r="A75" s="84" t="n"/>
+      <c r="B75" s="84" t="n"/>
+      <c r="C75" s="84" t="n"/>
+      <c r="D75" s="84" t="n"/>
+      <c r="E75" s="84" t="n"/>
+      <c r="F75" s="84" t="n"/>
+      <c r="G75" s="84" t="n"/>
+      <c r="H75" s="84" t="n"/>
+      <c r="I75" s="86">
         <f>IF(E75="","",IF(G75="",TODAY()-E75,G75-E75))</f>
         <v/>
       </c>
-      <c r="J75" s="83" t="n"/>
+      <c r="J75" s="84" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="83" t="n"/>
-      <c r="B76" s="83" t="n"/>
-      <c r="C76" s="83" t="n"/>
-      <c r="D76" s="83" t="n"/>
-      <c r="E76" s="83" t="n"/>
-      <c r="F76" s="83" t="n"/>
-      <c r="G76" s="83" t="n"/>
-      <c r="H76" s="83" t="n"/>
-      <c r="I76" s="85">
+      <c r="A76" s="84" t="n"/>
+      <c r="B76" s="84" t="n"/>
+      <c r="C76" s="84" t="n"/>
+      <c r="D76" s="84" t="n"/>
+      <c r="E76" s="84" t="n"/>
+      <c r="F76" s="84" t="n"/>
+      <c r="G76" s="84" t="n"/>
+      <c r="H76" s="84" t="n"/>
+      <c r="I76" s="86">
         <f>IF(E76="","",IF(G76="",TODAY()-E76,G76-E76))</f>
         <v/>
       </c>
-      <c r="J76" s="83" t="n"/>
+      <c r="J76" s="84" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="83" t="n"/>
-      <c r="B77" s="83" t="n"/>
-      <c r="C77" s="83" t="n"/>
-      <c r="D77" s="83" t="n"/>
-      <c r="E77" s="83" t="n"/>
-      <c r="F77" s="83" t="n"/>
-      <c r="G77" s="83" t="n"/>
-      <c r="H77" s="83" t="n"/>
-      <c r="I77" s="85">
+      <c r="A77" s="84" t="n"/>
+      <c r="B77" s="84" t="n"/>
+      <c r="C77" s="84" t="n"/>
+      <c r="D77" s="84" t="n"/>
+      <c r="E77" s="84" t="n"/>
+      <c r="F77" s="84" t="n"/>
+      <c r="G77" s="84" t="n"/>
+      <c r="H77" s="84" t="n"/>
+      <c r="I77" s="86">
         <f>IF(E77="","",IF(G77="",TODAY()-E77,G77-E77))</f>
         <v/>
       </c>
-      <c r="J77" s="83" t="n"/>
+      <c r="J77" s="84" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="83" t="n"/>
-      <c r="B78" s="83" t="n"/>
-      <c r="C78" s="83" t="n"/>
-      <c r="D78" s="83" t="n"/>
-      <c r="E78" s="83" t="n"/>
-      <c r="F78" s="83" t="n"/>
-      <c r="G78" s="83" t="n"/>
-      <c r="H78" s="83" t="n"/>
-      <c r="I78" s="85">
+      <c r="A78" s="84" t="n"/>
+      <c r="B78" s="84" t="n"/>
+      <c r="C78" s="84" t="n"/>
+      <c r="D78" s="84" t="n"/>
+      <c r="E78" s="84" t="n"/>
+      <c r="F78" s="84" t="n"/>
+      <c r="G78" s="84" t="n"/>
+      <c r="H78" s="84" t="n"/>
+      <c r="I78" s="86">
         <f>IF(E78="","",IF(G78="",TODAY()-E78,G78-E78))</f>
         <v/>
       </c>
-      <c r="J78" s="83" t="n"/>
+      <c r="J78" s="84" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="83" t="n"/>
-      <c r="B79" s="83" t="n"/>
-      <c r="C79" s="83" t="n"/>
-      <c r="D79" s="83" t="n"/>
-      <c r="E79" s="83" t="n"/>
-      <c r="F79" s="83" t="n"/>
-      <c r="G79" s="83" t="n"/>
-      <c r="H79" s="83" t="n"/>
-      <c r="I79" s="85">
+      <c r="A79" s="84" t="n"/>
+      <c r="B79" s="84" t="n"/>
+      <c r="C79" s="84" t="n"/>
+      <c r="D79" s="84" t="n"/>
+      <c r="E79" s="84" t="n"/>
+      <c r="F79" s="84" t="n"/>
+      <c r="G79" s="84" t="n"/>
+      <c r="H79" s="84" t="n"/>
+      <c r="I79" s="86">
         <f>IF(E79="","",IF(G79="",TODAY()-E79,G79-E79))</f>
         <v/>
       </c>
-      <c r="J79" s="83" t="n"/>
+      <c r="J79" s="84" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A11:J51"/>
@@ -3113,118 +3121,118 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="87" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="87" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C5" s="87" t="n">
+      <c r="C5" s="88" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="88" t="n">
+      <c r="D5" s="89" t="n">
         <v>4311.56</v>
       </c>
-      <c r="E5" s="88" t="n"/>
-      <c r="F5" s="88" t="n"/>
-      <c r="G5" s="88" t="n"/>
-      <c r="H5" s="88" t="n">
+      <c r="E5" s="89" t="n"/>
+      <c r="F5" s="89" t="n"/>
+      <c r="G5" s="89" t="n"/>
+      <c r="H5" s="89" t="n">
         <v>3723.62</v>
       </c>
-      <c r="I5" s="88" t="n">
+      <c r="I5" s="89" t="n">
         <v>6173.37</v>
       </c>
-      <c r="J5" s="88" t="n">
+      <c r="J5" s="89" t="n">
         <v>6300</v>
       </c>
-      <c r="K5" s="89" t="n">
+      <c r="K5" s="90" t="n">
         <v>20508.55</v>
       </c>
-      <c r="L5" s="90" t="inlineStr">
+      <c r="L5" s="91" t="inlineStr">
         <is>
           <t>TI-E03 Jonathan (Monitor Remoto)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="86" t="inlineStr">
+      <c r="A6" s="87" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="B6" s="86" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C6" s="87" t="n">
+      <c r="C6" s="88" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="88" t="n">
+      <c r="D6" s="89" t="n">
         <v>2670.84</v>
       </c>
-      <c r="E6" s="88" t="n">
+      <c r="E6" s="89" t="n">
         <v>2986.04</v>
       </c>
-      <c r="F6" s="88" t="n">
+      <c r="F6" s="89" t="n">
         <v>2778.04</v>
       </c>
-      <c r="G6" s="88" t="n">
+      <c r="G6" s="89" t="n">
         <v>2751.04</v>
       </c>
-      <c r="H6" s="88" t="n">
+      <c r="H6" s="89" t="n">
         <v>2719.04</v>
       </c>
-      <c r="I6" s="88" t="n">
+      <c r="I6" s="89" t="n">
         <v>3633.16</v>
       </c>
-      <c r="J6" s="88" t="n">
+      <c r="J6" s="89" t="n">
         <v>2461.04</v>
       </c>
-      <c r="K6" s="89" t="n">
+      <c r="K6" s="90" t="n">
         <v>19999.2</v>
       </c>
-      <c r="L6" s="90" t="inlineStr">
+      <c r="L6" s="91" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius Di Franco</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="86" t="inlineStr">
+      <c r="A7" s="87" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="B7" s="86" t="inlineStr">
+      <c r="B7" s="87" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C7" s="87" t="n">
+      <c r="C7" s="88" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="88" t="n"/>
-      <c r="E7" s="88" t="n">
+      <c r="D7" s="89" t="n"/>
+      <c r="E7" s="89" t="n">
         <v>234.46</v>
       </c>
-      <c r="F7" s="88" t="n">
+      <c r="F7" s="89" t="n">
         <v>321.76</v>
       </c>
-      <c r="G7" s="88" t="n">
+      <c r="G7" s="89" t="n">
         <v>5393.88</v>
       </c>
-      <c r="H7" s="88" t="n"/>
-      <c r="I7" s="88" t="n"/>
-      <c r="J7" s="88" t="n"/>
-      <c r="K7" s="89" t="n">
+      <c r="H7" s="89" t="n"/>
+      <c r="I7" s="89" t="n"/>
+      <c r="J7" s="89" t="n"/>
+      <c r="K7" s="90" t="n">
         <v>5950.1</v>
       </c>
-      <c r="L7" s="90" t="inlineStr">
+      <c r="L7" s="91" t="inlineStr">
         <is>
           <t>TI-D11 GPT</t>
         </is>
@@ -3263,10 +3271,10 @@
       <c r="J8" s="54" t="n">
         <v>979.4</v>
       </c>
-      <c r="K8" s="91" t="n">
+      <c r="K8" s="92" t="n">
         <v>5228.139999999999</v>
       </c>
-      <c r="L8" s="92" t="n"/>
+      <c r="L8" s="93" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="56" t="inlineStr">
@@ -3299,10 +3307,10 @@
       <c r="J9" s="54" t="n">
         <v>1151.26</v>
       </c>
-      <c r="K9" s="91" t="n">
+      <c r="K9" s="92" t="n">
         <v>3296.12</v>
       </c>
-      <c r="L9" s="92" t="n"/>
+      <c r="L9" s="93" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="56" t="inlineStr">
@@ -3333,48 +3341,48 @@
       <c r="J10" s="54" t="n">
         <v>1037.38</v>
       </c>
-      <c r="K10" s="91" t="n">
+      <c r="K10" s="92" t="n">
         <v>3242.61</v>
       </c>
-      <c r="L10" s="92" t="n"/>
+      <c r="L10" s="93" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="86" t="inlineStr">
+      <c r="A11" s="87" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="B11" s="86" t="inlineStr">
+      <c r="B11" s="87" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C11" s="87" t="n">
+      <c r="C11" s="88" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="88" t="n"/>
-      <c r="E11" s="88" t="n">
+      <c r="D11" s="89" t="n"/>
+      <c r="E11" s="89" t="n">
         <v>485</v>
       </c>
-      <c r="F11" s="88" t="n">
+      <c r="F11" s="89" t="n">
         <v>485</v>
       </c>
-      <c r="G11" s="88" t="n">
+      <c r="G11" s="89" t="n">
         <v>485</v>
       </c>
-      <c r="H11" s="88" t="n">
+      <c r="H11" s="89" t="n">
         <v>485</v>
       </c>
-      <c r="I11" s="88" t="n">
+      <c r="I11" s="89" t="n">
         <v>485</v>
       </c>
-      <c r="J11" s="88" t="n">
+      <c r="J11" s="89" t="n">
         <v>485</v>
       </c>
-      <c r="K11" s="89" t="n">
+      <c r="K11" s="90" t="n">
         <v>2910</v>
       </c>
-      <c r="L11" s="90" t="inlineStr">
+      <c r="L11" s="91" t="inlineStr">
         <is>
           <t>TI-E01 Vinicius (benefício)</t>
         </is>
@@ -3407,10 +3415,10 @@
       <c r="H12" s="54" t="n"/>
       <c r="I12" s="54" t="n"/>
       <c r="J12" s="54" t="n"/>
-      <c r="K12" s="91" t="n">
+      <c r="K12" s="92" t="n">
         <v>954.5500000000001</v>
       </c>
-      <c r="L12" s="92" t="n"/>
+      <c r="L12" s="93" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="56" t="inlineStr">
@@ -3443,10 +3451,10 @@
         <v>137.93</v>
       </c>
       <c r="J13" s="54" t="n"/>
-      <c r="K13" s="91" t="n">
+      <c r="K13" s="92" t="n">
         <v>827.49</v>
       </c>
-      <c r="L13" s="92" t="n"/>
+      <c r="L13" s="93" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="56" t="inlineStr">
@@ -3477,10 +3485,10 @@
         <v>554.58</v>
       </c>
       <c r="J14" s="54" t="n"/>
-      <c r="K14" s="91" t="n">
+      <c r="K14" s="92" t="n">
         <v>758.53</v>
       </c>
-      <c r="L14" s="92" t="n"/>
+      <c r="L14" s="93" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="56" t="inlineStr">
@@ -3517,10 +3525,10 @@
       <c r="J15" s="54" t="n">
         <v>82.5</v>
       </c>
-      <c r="K15" s="91" t="n">
+      <c r="K15" s="92" t="n">
         <v>690</v>
       </c>
-      <c r="L15" s="92" t="n"/>
+      <c r="L15" s="93" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
@@ -3553,10 +3561,10 @@
       <c r="J16" s="54" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="K16" s="91" t="n">
+      <c r="K16" s="92" t="n">
         <v>562.42</v>
       </c>
-      <c r="L16" s="92" t="n"/>
+      <c r="L16" s="93" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="56" t="inlineStr">
@@ -3581,10 +3589,10 @@
         <v>183.6</v>
       </c>
       <c r="J17" s="54" t="n"/>
-      <c r="K17" s="91" t="n">
+      <c r="K17" s="92" t="n">
         <v>183.6</v>
       </c>
-      <c r="L17" s="92" t="n"/>
+      <c r="L17" s="93" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="51" t="inlineStr">
@@ -3714,3964 +3722,3964 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="93" t="inlineStr">
+      <c r="A5" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="94" t="inlineStr">
         <is>
           <t>09/01/2026</t>
         </is>
       </c>
-      <c r="C5" s="93" t="inlineStr">
+      <c r="C5" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D5" s="93" t="inlineStr">
+      <c r="D5" s="94" t="inlineStr">
         <is>
           <t>FAT.11.25</t>
         </is>
       </c>
-      <c r="E5" s="93" t="inlineStr">
+      <c r="E5" s="94" t="inlineStr">
         <is>
           <t>95941/1</t>
         </is>
       </c>
-      <c r="F5" s="93" t="inlineStr">
+      <c r="F5" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G5" s="93" t="inlineStr">
+      <c r="G5" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H5" s="94" t="n">
+      <c r="H5" s="95" t="n">
         <v>407.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="93" t="inlineStr">
+      <c r="A6" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B6" s="93" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C6" s="93" t="inlineStr">
+      <c r="C6" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D6" s="93" t="inlineStr">
+      <c r="D6" s="94" t="inlineStr">
         <is>
           <t>FAT.01.26</t>
         </is>
       </c>
-      <c r="E6" s="93" t="inlineStr">
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>97478/1</t>
         </is>
       </c>
-      <c r="F6" s="93" t="inlineStr">
+      <c r="F6" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G6" s="93" t="inlineStr">
+      <c r="G6" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H6" s="94" t="n">
+      <c r="H6" s="95" t="n">
         <v>390.95</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="93" t="inlineStr">
+      <c r="A7" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="94" t="inlineStr">
         <is>
           <t>28/01/2026</t>
         </is>
       </c>
-      <c r="C7" s="93" t="inlineStr">
+      <c r="C7" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D7" s="93" t="inlineStr">
+      <c r="D7" s="94" t="inlineStr">
         <is>
           <t>FAT.184180933</t>
         </is>
       </c>
-      <c r="E7" s="93" t="inlineStr">
+      <c r="E7" s="94" t="inlineStr">
         <is>
           <t>97480/1</t>
         </is>
       </c>
-      <c r="F7" s="93" t="inlineStr">
+      <c r="F7" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G7" s="93" t="inlineStr">
+      <c r="G7" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H7" s="94" t="n">
+      <c r="H7" s="95" t="n">
         <v>123.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="93" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B8" s="93" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C8" s="93" t="inlineStr">
+      <c r="C8" s="94" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D8" s="93" t="inlineStr">
+      <c r="D8" s="94" t="inlineStr">
         <is>
           <t>NFS.347106</t>
         </is>
       </c>
-      <c r="E8" s="93" t="inlineStr">
+      <c r="E8" s="94" t="inlineStr">
         <is>
           <t>96534/1</t>
         </is>
       </c>
-      <c r="F8" s="93" t="inlineStr">
+      <c r="F8" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G8" s="93" t="inlineStr">
+      <c r="G8" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H8" s="94" t="n">
+      <c r="H8" s="95" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="93" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="94" t="inlineStr">
         <is>
           <t>19/01/2026</t>
         </is>
       </c>
-      <c r="C9" s="93" t="inlineStr">
+      <c r="C9" s="94" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D9" s="93" t="inlineStr">
+      <c r="D9" s="94" t="inlineStr">
         <is>
           <t>NFS.70</t>
         </is>
       </c>
-      <c r="E9" s="93" t="inlineStr">
+      <c r="E9" s="94" t="inlineStr">
         <is>
           <t>96602/1</t>
         </is>
       </c>
-      <c r="F9" s="93" t="inlineStr">
+      <c r="F9" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G9" s="93" t="inlineStr">
+      <c r="G9" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H9" s="94" t="n">
+      <c r="H9" s="95" t="n">
         <v>4311.56</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="93" t="inlineStr">
+      <c r="A10" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B10" s="93" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="C10" s="93" t="inlineStr">
+      <c r="C10" s="94" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D10" s="93" t="inlineStr">
+      <c r="D10" s="94" t="inlineStr">
         <is>
           <t>AV.LIC EMAILS 01.25</t>
         </is>
       </c>
-      <c r="E10" s="93" t="inlineStr">
+      <c r="E10" s="94" t="inlineStr">
         <is>
           <t>96014/1</t>
         </is>
       </c>
-      <c r="F10" s="93" t="inlineStr">
+      <c r="F10" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G10" s="93" t="inlineStr">
+      <c r="G10" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H10" s="94" t="n">
+      <c r="H10" s="95" t="n">
         <v>6.2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="93" t="inlineStr">
+      <c r="A11" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="94" t="inlineStr">
         <is>
           <t>25/01/2026</t>
         </is>
       </c>
-      <c r="C11" s="93" t="inlineStr">
+      <c r="C11" s="94" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D11" s="93" t="inlineStr">
+      <c r="D11" s="94" t="inlineStr">
         <is>
           <t>BOL.13.01</t>
         </is>
       </c>
-      <c r="E11" s="93" t="inlineStr">
+      <c r="E11" s="94" t="inlineStr">
         <is>
           <t>96623/1</t>
         </is>
       </c>
-      <c r="F11" s="93" t="inlineStr">
+      <c r="F11" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G11" s="93" t="inlineStr">
+      <c r="G11" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H11" s="94" t="n">
+      <c r="H11" s="95" t="n">
         <v>918.08</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="93" t="inlineStr">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B12" s="93" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>30/01/2026</t>
         </is>
       </c>
-      <c r="C12" s="93" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D12" s="93" t="inlineStr">
+      <c r="D12" s="94" t="inlineStr">
         <is>
           <t>FAT.2682</t>
         </is>
       </c>
-      <c r="E12" s="93" t="inlineStr">
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>96458/1</t>
         </is>
       </c>
-      <c r="F12" s="93" t="inlineStr">
+      <c r="F12" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G12" s="93" t="inlineStr">
+      <c r="G12" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H12" s="94" t="n">
+      <c r="H12" s="95" t="n">
         <v>723.75</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="93" t="inlineStr">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="94" t="inlineStr">
         <is>
           <t>12/01/2026</t>
         </is>
       </c>
-      <c r="C13" s="93" t="inlineStr">
+      <c r="C13" s="94" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D13" s="93" t="inlineStr">
+      <c r="D13" s="94" t="inlineStr">
         <is>
           <t>FAT.2011241340</t>
         </is>
       </c>
-      <c r="E13" s="93" t="inlineStr">
+      <c r="E13" s="94" t="inlineStr">
         <is>
           <t>96088/1</t>
         </is>
       </c>
-      <c r="F13" s="93" t="inlineStr">
+      <c r="F13" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G13" s="93" t="inlineStr">
+      <c r="G13" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H13" s="94" t="n">
+      <c r="H13" s="95" t="n">
         <v>51.63</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="93" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B14" s="93" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>22/01/2026</t>
         </is>
       </c>
-      <c r="C14" s="93" t="inlineStr">
+      <c r="C14" s="94" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D14" s="93" t="inlineStr">
+      <c r="D14" s="94" t="inlineStr">
         <is>
           <t>FAT.5664047504</t>
         </is>
       </c>
-      <c r="E14" s="93" t="inlineStr">
+      <c r="E14" s="94" t="inlineStr">
         <is>
           <t>96789/1</t>
         </is>
       </c>
-      <c r="F14" s="93" t="inlineStr">
+      <c r="F14" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G14" s="93" t="inlineStr">
+      <c r="G14" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H14" s="94" t="n">
+      <c r="H14" s="95" t="n">
         <v>331.42</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="93" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="94" t="inlineStr">
         <is>
           <t>26/01/2026</t>
         </is>
       </c>
-      <c r="C15" s="93" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D15" s="93" t="inlineStr">
+      <c r="D15" s="94" t="inlineStr">
         <is>
           <t>CX.16.01.26</t>
         </is>
       </c>
-      <c r="E15" s="93" t="inlineStr">
+      <c r="E15" s="94" t="inlineStr">
         <is>
           <t>97067/1</t>
         </is>
       </c>
-      <c r="F15" s="93" t="inlineStr">
+      <c r="F15" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G15" s="93" t="inlineStr">
+      <c r="G15" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H15" s="94" t="n">
+      <c r="H15" s="95" t="n">
         <v>39.84</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="93" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B16" s="93" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="C16" s="93" t="inlineStr">
+      <c r="C16" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D16" s="93" t="inlineStr">
+      <c r="D16" s="94" t="inlineStr">
         <is>
           <t>SAL.Sal_122025</t>
         </is>
       </c>
-      <c r="E16" s="93" t="inlineStr">
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>96252/1</t>
         </is>
       </c>
-      <c r="F16" s="93" t="inlineStr">
+      <c r="F16" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G16" s="93" t="inlineStr">
+      <c r="G16" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H16" s="94" t="n">
+      <c r="H16" s="95" t="n">
         <v>1602</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="93" t="inlineStr">
+      <c r="A17" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="94" t="inlineStr">
         <is>
           <t>20/01/2026</t>
         </is>
       </c>
-      <c r="C17" s="93" t="inlineStr">
+      <c r="C17" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D17" s="93" t="inlineStr">
+      <c r="D17" s="94" t="inlineStr">
         <is>
           <t>SAL.VALE_ 012026</t>
         </is>
       </c>
-      <c r="E17" s="93" t="inlineStr">
+      <c r="E17" s="94" t="inlineStr">
         <is>
           <t>97269/1</t>
         </is>
       </c>
-      <c r="F17" s="93" t="inlineStr">
+      <c r="F17" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G17" s="93" t="inlineStr">
+      <c r="G17" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H17" s="94" t="n">
+      <c r="H17" s="95" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="93" t="inlineStr">
+      <c r="A18" s="94" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>27/01/2026</t>
         </is>
       </c>
-      <c r="C18" s="93" t="inlineStr">
+      <c r="C18" s="94" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D18" s="93" t="inlineStr">
+      <c r="D18" s="94" t="inlineStr">
         <is>
           <t>BOL.1</t>
         </is>
       </c>
-      <c r="E18" s="93" t="inlineStr">
+      <c r="E18" s="94" t="inlineStr">
         <is>
           <t>97204/1</t>
         </is>
       </c>
-      <c r="F18" s="93" t="inlineStr">
+      <c r="F18" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G18" s="93" t="inlineStr">
+      <c r="G18" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H18" s="94" t="n">
+      <c r="H18" s="95" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="93" t="inlineStr">
+      <c r="A19" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B19" s="93" t="inlineStr">
+      <c r="B19" s="94" t="inlineStr">
         <is>
           <t>04/02/2026</t>
         </is>
       </c>
-      <c r="C19" s="93" t="inlineStr">
+      <c r="C19" s="94" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D19" s="93" t="inlineStr">
+      <c r="D19" s="94" t="inlineStr">
         <is>
           <t>AV.04.02.26</t>
         </is>
       </c>
-      <c r="E19" s="93" t="inlineStr">
+      <c r="E19" s="94" t="inlineStr">
         <is>
           <t>98500/1</t>
         </is>
       </c>
-      <c r="F19" s="93" t="inlineStr">
+      <c r="F19" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G19" s="93" t="inlineStr">
+      <c r="G19" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H19" s="94" t="n">
+      <c r="H19" s="95" t="n">
         <v>26.67</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="93" t="inlineStr">
+      <c r="A20" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B20" s="93" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C20" s="93" t="inlineStr">
+      <c r="C20" s="94" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D20" s="93" t="inlineStr">
+      <c r="D20" s="94" t="inlineStr">
         <is>
           <t>AV.12.02.26 LCW</t>
         </is>
       </c>
-      <c r="E20" s="93" t="inlineStr">
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>99336/1</t>
         </is>
       </c>
-      <c r="F20" s="93" t="inlineStr">
+      <c r="F20" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G20" s="93" t="inlineStr">
+      <c r="G20" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H20" s="94" t="n">
+      <c r="H20" s="95" t="n">
         <v>72.58</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="93" t="inlineStr">
+      <c r="A21" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B21" s="94" t="inlineStr">
         <is>
           <t>15/02/2026</t>
         </is>
       </c>
-      <c r="C21" s="93" t="inlineStr">
+      <c r="C21" s="94" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D21" s="93" t="inlineStr">
+      <c r="D21" s="94" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E21" s="93" t="inlineStr">
+      <c r="E21" s="94" t="inlineStr">
         <is>
           <t>95104/2</t>
         </is>
       </c>
-      <c r="F21" s="93" t="inlineStr">
+      <c r="F21" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G21" s="93" t="inlineStr">
+      <c r="G21" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H21" s="94" t="n">
+      <c r="H21" s="95" t="n">
         <v>234.46</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="93" t="inlineStr">
+      <c r="A22" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C22" s="93" t="inlineStr">
+      <c r="C22" s="94" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D22" s="93" t="inlineStr">
+      <c r="D22" s="94" t="inlineStr">
         <is>
           <t>FAT.3575377</t>
         </is>
       </c>
-      <c r="E22" s="93" t="inlineStr">
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>100172/1</t>
         </is>
       </c>
-      <c r="F22" s="93" t="inlineStr">
+      <c r="F22" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G22" s="93" t="inlineStr">
+      <c r="G22" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H22" s="94" t="n">
+      <c r="H22" s="95" t="n">
         <v>52.32</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="93" t="inlineStr">
+      <c r="A23" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B23" s="93" t="inlineStr">
+      <c r="B23" s="94" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="C23" s="93" t="inlineStr">
+      <c r="C23" s="94" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D23" s="93" t="inlineStr">
+      <c r="D23" s="94" t="inlineStr">
         <is>
           <t>FAT.5290953</t>
         </is>
       </c>
-      <c r="E23" s="93" t="inlineStr">
+      <c r="E23" s="94" t="inlineStr">
         <is>
           <t>100173/1</t>
         </is>
       </c>
-      <c r="F23" s="93" t="inlineStr">
+      <c r="F23" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G23" s="93" t="inlineStr">
+      <c r="G23" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H23" s="94" t="n">
+      <c r="H23" s="95" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="93" t="inlineStr">
+      <c r="A24" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B24" s="93" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C24" s="93" t="inlineStr">
+      <c r="C24" s="94" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D24" s="93" t="inlineStr">
+      <c r="D24" s="94" t="inlineStr">
         <is>
           <t>BOL.141</t>
         </is>
       </c>
-      <c r="E24" s="93" t="inlineStr">
+      <c r="E24" s="94" t="inlineStr">
         <is>
           <t>99947/1</t>
         </is>
       </c>
-      <c r="F24" s="93" t="inlineStr">
+      <c r="F24" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G24" s="93" t="inlineStr">
+      <c r="G24" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H24" s="94" t="n">
+      <c r="H24" s="95" t="n">
         <v>338.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="93" t="inlineStr">
+      <c r="A25" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B25" s="93" t="inlineStr">
+      <c r="B25" s="94" t="inlineStr">
         <is>
           <t>13/02/2026</t>
         </is>
       </c>
-      <c r="C25" s="93" t="inlineStr">
+      <c r="C25" s="94" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D25" s="93" t="inlineStr">
+      <c r="D25" s="94" t="inlineStr">
         <is>
           <t>BOL.26449</t>
         </is>
       </c>
-      <c r="E25" s="93" t="inlineStr">
+      <c r="E25" s="94" t="inlineStr">
         <is>
           <t>99484/1</t>
         </is>
       </c>
-      <c r="F25" s="93" t="inlineStr">
+      <c r="F25" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G25" s="93" t="inlineStr">
+      <c r="G25" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H25" s="94" t="n">
+      <c r="H25" s="95" t="n">
         <v>137.94</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="93" t="inlineStr">
+      <c r="A26" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
         <is>
           <t>19/02/2026</t>
         </is>
       </c>
-      <c r="C26" s="93" t="inlineStr">
+      <c r="C26" s="94" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D26" s="93" t="inlineStr">
+      <c r="D26" s="94" t="inlineStr">
         <is>
           <t>BOL.27256</t>
         </is>
       </c>
-      <c r="E26" s="93" t="inlineStr">
+      <c r="E26" s="94" t="inlineStr">
         <is>
           <t>99486/1</t>
         </is>
       </c>
-      <c r="F26" s="93" t="inlineStr">
+      <c r="F26" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G26" s="93" t="inlineStr">
+      <c r="G26" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H26" s="94" t="n">
+      <c r="H26" s="95" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="93" t="inlineStr">
+      <c r="A27" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B27" s="93" t="inlineStr">
+      <c r="B27" s="94" t="inlineStr">
         <is>
           <t>06/02/2026</t>
         </is>
       </c>
-      <c r="C27" s="93" t="inlineStr">
+      <c r="C27" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D27" s="93" t="inlineStr">
+      <c r="D27" s="94" t="inlineStr">
         <is>
           <t>SAL.SAL JANEIRO 2026</t>
         </is>
       </c>
-      <c r="E27" s="93" t="inlineStr">
+      <c r="E27" s="94" t="inlineStr">
         <is>
           <t>98811/1</t>
         </is>
       </c>
-      <c r="F27" s="93" t="inlineStr">
+      <c r="F27" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G27" s="93" t="inlineStr">
+      <c r="G27" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H27" s="94" t="n">
+      <c r="H27" s="95" t="n">
         <v>1750</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="93" t="inlineStr">
+      <c r="A28" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B28" s="93" t="inlineStr">
+      <c r="B28" s="94" t="inlineStr">
         <is>
           <t>20/02/2026</t>
         </is>
       </c>
-      <c r="C28" s="93" t="inlineStr">
+      <c r="C28" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D28" s="93" t="inlineStr">
+      <c r="D28" s="94" t="inlineStr">
         <is>
           <t>SAL.VALE FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E28" s="93" t="inlineStr">
+      <c r="E28" s="94" t="inlineStr">
         <is>
           <t>99890/1</t>
         </is>
       </c>
-      <c r="F28" s="93" t="inlineStr">
+      <c r="F28" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G28" s="93" t="inlineStr">
+      <c r="G28" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H28" s="94" t="n">
+      <c r="H28" s="95" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="93" t="inlineStr">
+      <c r="A29" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B29" s="93" t="inlineStr">
+      <c r="B29" s="94" t="inlineStr">
         <is>
           <t>2026-02-20 00:00:00</t>
         </is>
       </c>
-      <c r="C29" s="93" t="inlineStr">
+      <c r="C29" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D29" s="93" t="inlineStr">
+      <c r="D29" s="94" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E29" s="93" t="inlineStr">
+      <c r="E29" s="94" t="inlineStr">
         <is>
           <t>113754/2</t>
         </is>
       </c>
-      <c r="F29" s="93" t="inlineStr">
+      <c r="F29" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G29" s="93" t="inlineStr">
+      <c r="G29" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H29" s="94" t="n">
+      <c r="H29" s="95" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="93" t="inlineStr">
+      <c r="A30" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B30" s="93" t="inlineStr">
+      <c r="B30" s="94" t="inlineStr">
         <is>
           <t>2026-02-01 00:00:00</t>
         </is>
       </c>
-      <c r="C30" s="93" t="inlineStr">
+      <c r="C30" s="94" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D30" s="93" t="inlineStr"/>
-      <c r="E30" s="93" t="inlineStr"/>
-      <c r="F30" s="93" t="inlineStr">
+      <c r="D30" s="94" t="inlineStr"/>
+      <c r="E30" s="94" t="inlineStr"/>
+      <c r="F30" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G30" s="93" t="inlineStr">
+      <c r="G30" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H30" s="94" t="n">
+      <c r="H30" s="95" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="93" t="inlineStr">
+      <c r="A31" s="94" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B31" s="93" t="inlineStr">
+      <c r="B31" s="94" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="C31" s="93" t="inlineStr">
+      <c r="C31" s="94" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D31" s="93" t="inlineStr">
+      <c r="D31" s="94" t="inlineStr">
         <is>
           <t>NFS.1430</t>
         </is>
       </c>
-      <c r="E31" s="93" t="inlineStr">
+      <c r="E31" s="94" t="inlineStr">
         <is>
           <t>99956/1</t>
         </is>
       </c>
-      <c r="F31" s="93" t="inlineStr">
+      <c r="F31" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G31" s="93" t="inlineStr">
+      <c r="G31" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H31" s="94" t="n">
+      <c r="H31" s="95" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="93" t="inlineStr">
+      <c r="A32" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B32" s="93" t="inlineStr">
+      <c r="B32" s="94" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C32" s="93" t="inlineStr">
+      <c r="C32" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D32" s="93" t="inlineStr">
+      <c r="D32" s="94" t="inlineStr">
         <is>
           <t>FAT.5042829</t>
         </is>
       </c>
-      <c r="E32" s="93" t="inlineStr">
+      <c r="E32" s="94" t="inlineStr">
         <is>
           <t>100503/1</t>
         </is>
       </c>
-      <c r="F32" s="93" t="inlineStr">
+      <c r="F32" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G32" s="93" t="inlineStr">
+      <c r="G32" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H32" s="94" t="n">
+      <c r="H32" s="95" t="n">
         <v>87.69</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="93" t="inlineStr">
+      <c r="A33" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B33" s="93" t="inlineStr">
+      <c r="B33" s="94" t="inlineStr">
         <is>
           <t>05/03/2026</t>
         </is>
       </c>
-      <c r="C33" s="93" t="inlineStr">
+      <c r="C33" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D33" s="93" t="inlineStr">
+      <c r="D33" s="94" t="inlineStr">
         <is>
           <t>FAT.5042827</t>
         </is>
       </c>
-      <c r="E33" s="93" t="inlineStr">
+      <c r="E33" s="94" t="inlineStr">
         <is>
           <t>100504/1</t>
         </is>
       </c>
-      <c r="F33" s="93" t="inlineStr">
+      <c r="F33" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G33" s="93" t="inlineStr">
+      <c r="G33" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H33" s="94" t="n">
+      <c r="H33" s="95" t="n">
         <v>382.4</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="93" t="inlineStr">
+      <c r="A34" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B34" s="93" t="inlineStr">
+      <c r="B34" s="94" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="C34" s="93" t="inlineStr">
+      <c r="C34" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D34" s="93" t="inlineStr">
+      <c r="D34" s="94" t="inlineStr">
         <is>
           <t>FAT.8910508</t>
         </is>
       </c>
-      <c r="E34" s="93" t="inlineStr">
+      <c r="E34" s="94" t="inlineStr">
         <is>
           <t>102706/1</t>
         </is>
       </c>
-      <c r="F34" s="93" t="inlineStr">
+      <c r="F34" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G34" s="93" t="inlineStr">
+      <c r="G34" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H34" s="94" t="n">
+      <c r="H34" s="95" t="n">
         <v>429.49</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="93" t="inlineStr">
+      <c r="A35" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B35" s="93" t="inlineStr">
+      <c r="B35" s="94" t="inlineStr">
         <is>
           <t>02/03/2026</t>
         </is>
       </c>
-      <c r="C35" s="93" t="inlineStr">
+      <c r="C35" s="94" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D35" s="93" t="inlineStr">
+      <c r="D35" s="94" t="inlineStr">
         <is>
           <t>NFS.351653</t>
         </is>
       </c>
-      <c r="E35" s="93" t="inlineStr">
+      <c r="E35" s="94" t="inlineStr">
         <is>
           <t>100083/1</t>
         </is>
       </c>
-      <c r="F35" s="93" t="inlineStr">
+      <c r="F35" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G35" s="93" t="inlineStr">
+      <c r="G35" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H35" s="94" t="n">
+      <c r="H35" s="95" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="93" t="inlineStr">
+      <c r="A36" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B36" s="93" t="inlineStr">
+      <c r="B36" s="94" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="C36" s="93" t="inlineStr">
+      <c r="C36" s="94" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D36" s="93" t="inlineStr">
+      <c r="D36" s="94" t="inlineStr">
         <is>
           <t>NFS.359396</t>
         </is>
       </c>
-      <c r="E36" s="93" t="inlineStr">
+      <c r="E36" s="94" t="inlineStr">
         <is>
           <t>102608/1</t>
         </is>
       </c>
-      <c r="F36" s="93" t="inlineStr">
+      <c r="F36" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G36" s="93" t="inlineStr">
+      <c r="G36" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H36" s="94" t="n">
+      <c r="H36" s="95" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="93" t="inlineStr">
+      <c r="A37" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B37" s="93" t="inlineStr">
+      <c r="B37" s="94" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="C37" s="93" t="inlineStr">
+      <c r="C37" s="94" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D37" s="93" t="inlineStr">
+      <c r="D37" s="94" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E37" s="93" t="inlineStr">
+      <c r="E37" s="94" t="inlineStr">
         <is>
           <t>95104/3</t>
         </is>
       </c>
-      <c r="F37" s="93" t="inlineStr">
+      <c r="F37" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G37" s="93" t="inlineStr">
+      <c r="G37" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H37" s="94" t="n">
+      <c r="H37" s="95" t="n">
         <v>111.38</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="93" t="inlineStr">
+      <c r="A38" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B38" s="93" t="inlineStr">
+      <c r="B38" s="94" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C38" s="93" t="inlineStr">
+      <c r="C38" s="94" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D38" s="93" t="inlineStr">
+      <c r="D38" s="94" t="inlineStr">
         <is>
           <t>AV.CHATGPT JUR 2026</t>
         </is>
       </c>
-      <c r="E38" s="93" t="inlineStr">
+      <c r="E38" s="94" t="inlineStr">
         <is>
           <t>95104/4</t>
         </is>
       </c>
-      <c r="F38" s="93" t="inlineStr">
+      <c r="F38" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G38" s="93" t="inlineStr">
+      <c r="G38" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H38" s="94" t="n">
+      <c r="H38" s="95" t="n">
         <v>210.38</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="93" t="inlineStr">
+      <c r="A39" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B39" s="93" t="inlineStr">
+      <c r="B39" s="94" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="C39" s="93" t="inlineStr">
+      <c r="C39" s="94" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D39" s="93" t="inlineStr">
+      <c r="D39" s="94" t="inlineStr">
         <is>
           <t>FAT.2024588614</t>
         </is>
       </c>
-      <c r="E39" s="93" t="inlineStr">
+      <c r="E39" s="94" t="inlineStr">
         <is>
           <t>102316/1</t>
         </is>
       </c>
-      <c r="F39" s="93" t="inlineStr">
+      <c r="F39" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G39" s="93" t="inlineStr">
+      <c r="G39" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H39" s="94" t="n">
+      <c r="H39" s="95" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="93" t="inlineStr">
+      <c r="A40" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B40" s="93" t="inlineStr">
+      <c r="B40" s="94" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C40" s="93" t="inlineStr">
+      <c r="C40" s="94" t="inlineStr">
         <is>
           <t>TIM S A</t>
         </is>
       </c>
-      <c r="D40" s="93" t="inlineStr">
+      <c r="D40" s="94" t="inlineStr">
         <is>
           <t>BOL.5708173302</t>
         </is>
       </c>
-      <c r="E40" s="93" t="inlineStr">
+      <c r="E40" s="94" t="inlineStr">
         <is>
           <t>102057/1</t>
         </is>
       </c>
-      <c r="F40" s="93" t="inlineStr">
+      <c r="F40" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G40" s="93" t="inlineStr">
+      <c r="G40" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H40" s="94" t="n">
+      <c r="H40" s="95" t="n">
         <v>284.63</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="93" t="inlineStr">
+      <c r="A41" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B41" s="93" t="inlineStr">
+      <c r="B41" s="94" t="inlineStr">
         <is>
           <t>15/03/2026</t>
         </is>
       </c>
-      <c r="C41" s="93" t="inlineStr">
+      <c r="C41" s="94" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D41" s="93" t="inlineStr">
+      <c r="D41" s="94" t="inlineStr">
         <is>
           <t>BOL.28049</t>
         </is>
       </c>
-      <c r="E41" s="93" t="inlineStr">
+      <c r="E41" s="94" t="inlineStr">
         <is>
           <t>100887/1</t>
         </is>
       </c>
-      <c r="F41" s="93" t="inlineStr">
+      <c r="F41" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G41" s="93" t="inlineStr">
+      <c r="G41" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H41" s="94" t="n">
+      <c r="H41" s="95" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="93" t="inlineStr">
+      <c r="A42" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
+      <c r="B42" s="94" t="inlineStr">
         <is>
           <t>06/03/2026</t>
         </is>
       </c>
-      <c r="C42" s="93" t="inlineStr">
+      <c r="C42" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D42" s="93" t="inlineStr">
+      <c r="D42" s="94" t="inlineStr">
         <is>
           <t>SAL.SAL FEVEREIRO 26</t>
         </is>
       </c>
-      <c r="E42" s="93" t="inlineStr">
+      <c r="E42" s="94" t="inlineStr">
         <is>
           <t>101276/1</t>
         </is>
       </c>
-      <c r="F42" s="93" t="inlineStr">
+      <c r="F42" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G42" s="93" t="inlineStr">
+      <c r="G42" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H42" s="94" t="n">
+      <c r="H42" s="95" t="n">
         <v>1542</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="93" t="inlineStr">
+      <c r="A43" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B43" s="93" t="inlineStr">
+      <c r="B43" s="94" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="C43" s="93" t="inlineStr">
+      <c r="C43" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D43" s="93" t="inlineStr">
+      <c r="D43" s="94" t="inlineStr">
         <is>
           <t>SAL.VALE 032026</t>
         </is>
       </c>
-      <c r="E43" s="93" t="inlineStr">
+      <c r="E43" s="94" t="inlineStr">
         <is>
           <t>102295/1</t>
         </is>
       </c>
-      <c r="F43" s="93" t="inlineStr">
+      <c r="F43" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G43" s="93" t="inlineStr">
+      <c r="G43" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H43" s="94" t="n">
+      <c r="H43" s="95" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="93" t="inlineStr">
+      <c r="A44" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B44" s="93" t="inlineStr">
+      <c r="B44" s="94" t="inlineStr">
         <is>
           <t>2026-03-20 00:00:00</t>
         </is>
       </c>
-      <c r="C44" s="93" t="inlineStr">
+      <c r="C44" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D44" s="93" t="inlineStr">
+      <c r="D44" s="94" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E44" s="93" t="inlineStr">
+      <c r="E44" s="94" t="inlineStr">
         <is>
           <t>113754/3</t>
         </is>
       </c>
-      <c r="F44" s="93" t="inlineStr">
+      <c r="F44" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G44" s="93" t="inlineStr">
+      <c r="G44" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H44" s="94" t="n">
+      <c r="H44" s="95" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="93" t="inlineStr">
+      <c r="A45" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B45" s="93" t="inlineStr">
+      <c r="B45" s="94" t="inlineStr">
         <is>
           <t>2026-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="C45" s="93" t="inlineStr">
+      <c r="C45" s="94" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D45" s="93" t="inlineStr"/>
-      <c r="E45" s="93" t="inlineStr"/>
-      <c r="F45" s="93" t="inlineStr">
+      <c r="D45" s="94" t="inlineStr"/>
+      <c r="E45" s="94" t="inlineStr"/>
+      <c r="F45" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G45" s="93" t="inlineStr">
+      <c r="G45" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H45" s="94" t="n">
+      <c r="H45" s="95" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="93" t="inlineStr">
+      <c r="A46" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B46" s="93" t="inlineStr">
+      <c r="B46" s="94" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C46" s="93" t="inlineStr">
+      <c r="C46" s="94" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D46" s="93" t="inlineStr">
+      <c r="D46" s="94" t="inlineStr">
         <is>
           <t>NFS.1500</t>
         </is>
       </c>
-      <c r="E46" s="93" t="inlineStr">
+      <c r="E46" s="94" t="inlineStr">
         <is>
           <t>102432/1</t>
         </is>
       </c>
-      <c r="F46" s="93" t="inlineStr">
+      <c r="F46" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G46" s="93" t="inlineStr">
+      <c r="G46" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H46" s="94" t="n">
+      <c r="H46" s="95" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="93" t="inlineStr">
+      <c r="A47" s="94" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B47" s="93" t="inlineStr">
+      <c r="B47" s="94" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="C47" s="93" t="inlineStr">
+      <c r="C47" s="94" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D47" s="93" t="inlineStr">
+      <c r="D47" s="94" t="inlineStr">
         <is>
           <t>NFS.1534</t>
         </is>
       </c>
-      <c r="E47" s="93" t="inlineStr">
+      <c r="E47" s="94" t="inlineStr">
         <is>
           <t>102434/1</t>
         </is>
       </c>
-      <c r="F47" s="93" t="inlineStr">
+      <c r="F47" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G47" s="93" t="inlineStr">
+      <c r="G47" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H47" s="94" t="n">
+      <c r="H47" s="95" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="93" t="inlineStr">
+      <c r="A48" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B48" s="93" t="inlineStr">
+      <c r="B48" s="94" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C48" s="93" t="inlineStr">
+      <c r="C48" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D48" s="93" t="inlineStr">
+      <c r="D48" s="94" t="inlineStr">
         <is>
           <t>FAT.8910315</t>
         </is>
       </c>
-      <c r="E48" s="93" t="inlineStr">
+      <c r="E48" s="94" t="inlineStr">
         <is>
           <t>105607/1</t>
         </is>
       </c>
-      <c r="F48" s="93" t="inlineStr">
+      <c r="F48" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G48" s="93" t="inlineStr">
+      <c r="G48" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H48" s="94" t="n">
+      <c r="H48" s="95" t="n">
         <v>11.99</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="93" t="inlineStr">
+      <c r="A49" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B49" s="93" t="inlineStr">
+      <c r="B49" s="94" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C49" s="93" t="inlineStr">
+      <c r="C49" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D49" s="93" t="inlineStr">
+      <c r="D49" s="94" t="inlineStr">
         <is>
           <t>FAT.13443658</t>
         </is>
       </c>
-      <c r="E49" s="93" t="inlineStr">
+      <c r="E49" s="94" t="inlineStr">
         <is>
           <t>105676/1</t>
         </is>
       </c>
-      <c r="F49" s="93" t="inlineStr">
+      <c r="F49" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G49" s="93" t="inlineStr">
+      <c r="G49" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H49" s="94" t="n">
+      <c r="H49" s="95" t="n">
         <v>557.63</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="93" t="inlineStr">
+      <c r="A50" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B50" s="93" t="inlineStr">
+      <c r="B50" s="94" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="C50" s="93" t="inlineStr">
+      <c r="C50" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D50" s="93" t="inlineStr">
+      <c r="D50" s="94" t="inlineStr">
         <is>
           <t>FAT.13443664</t>
         </is>
       </c>
-      <c r="E50" s="93" t="inlineStr">
+      <c r="E50" s="94" t="inlineStr">
         <is>
           <t>105677/1</t>
         </is>
       </c>
-      <c r="F50" s="93" t="inlineStr">
+      <c r="F50" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G50" s="93" t="inlineStr">
+      <c r="G50" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H50" s="94" t="n">
+      <c r="H50" s="95" t="n">
         <v>132.09</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="93" t="inlineStr">
+      <c r="A51" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B51" s="93" t="inlineStr">
+      <c r="B51" s="94" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C51" s="93" t="inlineStr">
+      <c r="C51" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D51" s="93" t="inlineStr">
+      <c r="D51" s="94" t="inlineStr">
         <is>
           <t>FAT.13443112</t>
         </is>
       </c>
-      <c r="E51" s="93" t="inlineStr">
+      <c r="E51" s="94" t="inlineStr">
         <is>
           <t>105792/1</t>
         </is>
       </c>
-      <c r="F51" s="93" t="inlineStr">
+      <c r="F51" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G51" s="93" t="inlineStr">
+      <c r="G51" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H51" s="94" t="n">
+      <c r="H51" s="95" t="n">
         <v>20.23</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="93" t="inlineStr">
+      <c r="A52" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B52" s="93" t="inlineStr">
+      <c r="B52" s="94" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C52" s="93" t="inlineStr">
+      <c r="C52" s="94" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D52" s="93" t="inlineStr">
+      <c r="D52" s="94" t="inlineStr">
         <is>
           <t>NFS.363799</t>
         </is>
       </c>
-      <c r="E52" s="93" t="inlineStr">
+      <c r="E52" s="94" t="inlineStr">
         <is>
           <t>104634/1</t>
         </is>
       </c>
-      <c r="F52" s="93" t="inlineStr">
+      <c r="F52" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G52" s="93" t="inlineStr">
+      <c r="G52" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H52" s="94" t="n">
+      <c r="H52" s="95" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="93" t="inlineStr">
+      <c r="A53" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B53" s="93" t="inlineStr">
+      <c r="B53" s="94" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="C53" s="93" t="inlineStr">
+      <c r="C53" s="94" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D53" s="93" t="inlineStr">
+      <c r="D53" s="94" t="inlineStr">
         <is>
           <t>BOL.04.26</t>
         </is>
       </c>
-      <c r="E53" s="93" t="inlineStr">
+      <c r="E53" s="94" t="inlineStr">
         <is>
           <t>104820/1</t>
         </is>
       </c>
-      <c r="F53" s="93" t="inlineStr">
+      <c r="F53" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G53" s="93" t="inlineStr">
+      <c r="G53" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H53" s="94" t="n">
+      <c r="H53" s="95" t="n">
         <v>1024.76</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="93" t="inlineStr">
+      <c r="A54" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B54" s="93" t="inlineStr">
+      <c r="B54" s="94" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="C54" s="93" t="inlineStr">
+      <c r="C54" s="94" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D54" s="93" t="inlineStr">
+      <c r="D54" s="94" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 29.04.26</t>
         </is>
       </c>
-      <c r="E54" s="93" t="inlineStr">
+      <c r="E54" s="94" t="inlineStr">
         <is>
           <t>106325/1</t>
         </is>
       </c>
-      <c r="F54" s="93" t="inlineStr">
+      <c r="F54" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G54" s="93" t="inlineStr">
+      <c r="G54" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H54" s="94" t="n">
+      <c r="H54" s="95" t="n">
         <v>21.76</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="93" t="inlineStr">
+      <c r="A55" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B55" s="93" t="inlineStr">
+      <c r="B55" s="94" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C55" s="93" t="inlineStr">
+      <c r="C55" s="94" t="inlineStr">
         <is>
           <t>OPENAI BRAZIL LIMITADA</t>
         </is>
       </c>
-      <c r="D55" s="93" t="inlineStr">
+      <c r="D55" s="94" t="inlineStr">
         <is>
           <t>FAT.CHATGPT 3 LIC</t>
         </is>
       </c>
-      <c r="E55" s="93" t="inlineStr">
+      <c r="E55" s="94" t="inlineStr">
         <is>
           <t>102137/1</t>
         </is>
       </c>
-      <c r="F55" s="93" t="inlineStr">
+      <c r="F55" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G55" s="93" t="inlineStr">
+      <c r="G55" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H55" s="94" t="n">
+      <c r="H55" s="95" t="n">
         <v>5393.88</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="93" t="inlineStr">
+      <c r="A56" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B56" s="93" t="inlineStr">
+      <c r="B56" s="94" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="C56" s="93" t="inlineStr">
+      <c r="C56" s="94" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D56" s="93" t="inlineStr">
+      <c r="D56" s="94" t="inlineStr">
         <is>
           <t>BOL.28855</t>
         </is>
       </c>
-      <c r="E56" s="93" t="inlineStr">
+      <c r="E56" s="94" t="inlineStr">
         <is>
           <t>103694/1</t>
         </is>
       </c>
-      <c r="F56" s="93" t="inlineStr">
+      <c r="F56" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G56" s="93" t="inlineStr">
+      <c r="G56" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H56" s="94" t="n">
+      <c r="H56" s="95" t="n">
         <v>137.9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="93" t="inlineStr">
+      <c r="A57" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B57" s="93" t="inlineStr">
+      <c r="B57" s="94" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="C57" s="93" t="inlineStr">
+      <c r="C57" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D57" s="93" t="inlineStr">
+      <c r="D57" s="94" t="inlineStr">
         <is>
           <t>SAL.SAL 032026</t>
         </is>
       </c>
-      <c r="E57" s="93" t="inlineStr">
+      <c r="E57" s="94" t="inlineStr">
         <is>
           <t>103924/1</t>
         </is>
       </c>
-      <c r="F57" s="93" t="inlineStr">
+      <c r="F57" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G57" s="93" t="inlineStr">
+      <c r="G57" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H57" s="94" t="n">
+      <c r="H57" s="95" t="n">
         <v>1515</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="93" t="inlineStr">
+      <c r="A58" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B58" s="93" t="inlineStr">
+      <c r="B58" s="94" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="C58" s="93" t="inlineStr">
+      <c r="C58" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D58" s="93" t="inlineStr">
+      <c r="D58" s="94" t="inlineStr">
         <is>
           <t>SAL.vale 042026</t>
         </is>
       </c>
-      <c r="E58" s="93" t="inlineStr">
+      <c r="E58" s="94" t="inlineStr">
         <is>
           <t>105055/1</t>
         </is>
       </c>
-      <c r="F58" s="93" t="inlineStr">
+      <c r="F58" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G58" s="93" t="inlineStr">
+      <c r="G58" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H58" s="94" t="n">
+      <c r="H58" s="95" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="93" t="inlineStr">
+      <c r="A59" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B59" s="93" t="inlineStr">
+      <c r="B59" s="94" t="inlineStr">
         <is>
           <t>2026-04-20 00:00:00</t>
         </is>
       </c>
-      <c r="C59" s="93" t="inlineStr">
+      <c r="C59" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D59" s="93" t="inlineStr">
+      <c r="D59" s="94" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E59" s="93" t="inlineStr">
+      <c r="E59" s="94" t="inlineStr">
         <is>
           <t>113754/4</t>
         </is>
       </c>
-      <c r="F59" s="93" t="inlineStr">
+      <c r="F59" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G59" s="93" t="inlineStr">
+      <c r="G59" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H59" s="94" t="n">
+      <c r="H59" s="95" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="93" t="inlineStr">
+      <c r="A60" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B60" s="93" t="inlineStr">
+      <c r="B60" s="94" t="inlineStr">
         <is>
           <t>2026-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="C60" s="93" t="inlineStr">
+      <c r="C60" s="94" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D60" s="93" t="inlineStr"/>
-      <c r="E60" s="93" t="inlineStr"/>
-      <c r="F60" s="93" t="inlineStr">
+      <c r="D60" s="94" t="inlineStr"/>
+      <c r="E60" s="94" t="inlineStr"/>
+      <c r="F60" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G60" s="93" t="inlineStr">
+      <c r="G60" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H60" s="94" t="n">
+      <c r="H60" s="95" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="93" t="inlineStr">
+      <c r="A61" s="94" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B61" s="93" t="inlineStr">
+      <c r="B61" s="94" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="C61" s="93" t="inlineStr">
+      <c r="C61" s="94" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D61" s="93" t="inlineStr">
+      <c r="D61" s="94" t="inlineStr">
         <is>
           <t>NFS.1573</t>
         </is>
       </c>
-      <c r="E61" s="93" t="inlineStr">
+      <c r="E61" s="94" t="inlineStr">
         <is>
           <t>105411/1</t>
         </is>
       </c>
-      <c r="F61" s="93" t="inlineStr">
+      <c r="F61" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G61" s="93" t="inlineStr">
+      <c r="G61" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H61" s="94" t="n">
+      <c r="H61" s="95" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="93" t="inlineStr">
+      <c r="A62" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B62" s="93" t="inlineStr">
+      <c r="B62" s="94" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="C62" s="93" t="inlineStr">
+      <c r="C62" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D62" s="93" t="inlineStr">
+      <c r="D62" s="94" t="inlineStr">
         <is>
           <t>FAT.2ªvia Claro Abril</t>
         </is>
       </c>
-      <c r="E62" s="93" t="inlineStr">
+      <c r="E62" s="94" t="inlineStr">
         <is>
           <t>107340/1</t>
         </is>
       </c>
-      <c r="F62" s="93" t="inlineStr">
+      <c r="F62" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G62" s="93" t="inlineStr">
+      <c r="G62" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H62" s="94" t="n">
+      <c r="H62" s="95" t="n">
         <v>182.32</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="93" t="inlineStr">
+      <c r="A63" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B63" s="93" t="inlineStr">
+      <c r="B63" s="94" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C63" s="93" t="inlineStr">
+      <c r="C63" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D63" s="93" t="inlineStr">
+      <c r="D63" s="94" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E63" s="93" t="inlineStr">
+      <c r="E63" s="94" t="inlineStr">
         <is>
           <t>108218/1</t>
         </is>
       </c>
-      <c r="F63" s="93" t="inlineStr">
+      <c r="F63" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G63" s="93" t="inlineStr">
+      <c r="G63" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H63" s="94" t="n">
+      <c r="H63" s="95" t="n">
         <v>629.98</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="93" t="inlineStr">
+      <c r="A64" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B64" s="93" t="inlineStr">
+      <c r="B64" s="94" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C64" s="93" t="inlineStr">
+      <c r="C64" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D64" s="93" t="inlineStr">
+      <c r="D64" s="94" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E64" s="93" t="inlineStr">
+      <c r="E64" s="94" t="inlineStr">
         <is>
           <t>108218/2</t>
         </is>
       </c>
-      <c r="F64" s="93" t="inlineStr">
+      <c r="F64" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G64" s="93" t="inlineStr">
+      <c r="G64" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H64" s="94" t="n">
+      <c r="H64" s="95" t="n">
         <v>18.86</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="93" t="inlineStr">
+      <c r="A65" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B65" s="93" t="inlineStr">
+      <c r="B65" s="94" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="C65" s="93" t="inlineStr">
+      <c r="C65" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D65" s="93" t="inlineStr">
+      <c r="D65" s="94" t="inlineStr">
         <is>
           <t>FAT.17483469</t>
         </is>
       </c>
-      <c r="E65" s="93" t="inlineStr">
+      <c r="E65" s="94" t="inlineStr">
         <is>
           <t>108218/3</t>
         </is>
       </c>
-      <c r="F65" s="93" t="inlineStr">
+      <c r="F65" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G65" s="93" t="inlineStr">
+      <c r="G65" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H65" s="94" t="n">
+      <c r="H65" s="95" t="n">
         <v>133.95</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="93" t="inlineStr">
+      <c r="A66" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B66" s="93" t="inlineStr">
+      <c r="B66" s="94" t="inlineStr">
         <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="C66" s="93" t="inlineStr">
+      <c r="C66" s="94" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D66" s="93" t="inlineStr">
+      <c r="D66" s="94" t="inlineStr">
         <is>
           <t>NFS.76</t>
         </is>
       </c>
-      <c r="E66" s="93" t="inlineStr">
+      <c r="E66" s="94" t="inlineStr">
         <is>
           <t>105987/1</t>
         </is>
       </c>
-      <c r="F66" s="93" t="inlineStr">
+      <c r="F66" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G66" s="93" t="inlineStr">
+      <c r="G66" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H66" s="94" t="n">
+      <c r="H66" s="95" t="n">
         <v>3723.62</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="93" t="inlineStr">
+      <c r="A67" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B67" s="93" t="inlineStr">
+      <c r="B67" s="94" t="inlineStr">
         <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="C67" s="93" t="inlineStr">
+      <c r="C67" s="94" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D67" s="93" t="inlineStr">
+      <c r="D67" s="94" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 11.05.26</t>
         </is>
       </c>
-      <c r="E67" s="93" t="inlineStr">
+      <c r="E67" s="94" t="inlineStr">
         <is>
           <t>107254/1</t>
         </is>
       </c>
-      <c r="F67" s="93" t="inlineStr">
+      <c r="F67" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G67" s="93" t="inlineStr">
+      <c r="G67" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H67" s="94" t="n">
+      <c r="H67" s="95" t="n">
         <v>74.81</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="93" t="inlineStr">
+      <c r="A68" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B68" s="93" t="inlineStr">
+      <c r="B68" s="94" t="inlineStr">
         <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="C68" s="93" t="inlineStr">
+      <c r="C68" s="94" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D68" s="93" t="inlineStr">
+      <c r="D68" s="94" t="inlineStr">
         <is>
           <t>NFS.5744</t>
         </is>
       </c>
-      <c r="E68" s="93" t="inlineStr">
+      <c r="E68" s="94" t="inlineStr">
         <is>
           <t>106664/1</t>
         </is>
       </c>
-      <c r="F68" s="93" t="inlineStr">
+      <c r="F68" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G68" s="93" t="inlineStr">
+      <c r="G68" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H68" s="94" t="n">
+      <c r="H68" s="95" t="n">
         <v>741.1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="93" t="inlineStr">
+      <c r="A69" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B69" s="93" t="inlineStr">
+      <c r="B69" s="94" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C69" s="93" t="inlineStr">
+      <c r="C69" s="94" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D69" s="93" t="inlineStr">
+      <c r="D69" s="94" t="inlineStr">
         <is>
           <t>BOL.29637</t>
         </is>
       </c>
-      <c r="E69" s="93" t="inlineStr">
+      <c r="E69" s="94" t="inlineStr">
         <is>
           <t>108040/1</t>
         </is>
       </c>
-      <c r="F69" s="93" t="inlineStr">
+      <c r="F69" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G69" s="93" t="inlineStr">
+      <c r="G69" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H69" s="94" t="n">
+      <c r="H69" s="95" t="n">
         <v>137.92</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="93" t="inlineStr">
+      <c r="A70" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B70" s="93" t="inlineStr">
+      <c r="B70" s="94" t="inlineStr">
         <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="C70" s="93" t="inlineStr">
+      <c r="C70" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D70" s="93" t="inlineStr">
+      <c r="D70" s="94" t="inlineStr">
         <is>
           <t>SAL.sal 042026</t>
         </is>
       </c>
-      <c r="E70" s="93" t="inlineStr">
+      <c r="E70" s="94" t="inlineStr">
         <is>
           <t>106947/1</t>
         </is>
       </c>
-      <c r="F70" s="93" t="inlineStr">
+      <c r="F70" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G70" s="93" t="inlineStr">
+      <c r="G70" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H70" s="94" t="n">
+      <c r="H70" s="95" t="n">
         <v>1483</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="93" t="inlineStr">
+      <c r="A71" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B71" s="93" t="inlineStr">
+      <c r="B71" s="94" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="C71" s="93" t="inlineStr">
+      <c r="C71" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D71" s="93" t="inlineStr">
+      <c r="D71" s="94" t="inlineStr">
         <is>
           <t>SAL.vale 052026</t>
         </is>
       </c>
-      <c r="E71" s="93" t="inlineStr">
+      <c r="E71" s="94" t="inlineStr">
         <is>
           <t>108156/1</t>
         </is>
       </c>
-      <c r="F71" s="93" t="inlineStr">
+      <c r="F71" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G71" s="93" t="inlineStr">
+      <c r="G71" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H71" s="94" t="n">
+      <c r="H71" s="95" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="93" t="inlineStr">
+      <c r="A72" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B72" s="93" t="inlineStr">
+      <c r="B72" s="94" t="inlineStr">
         <is>
           <t>2026-05-20 00:00:00</t>
         </is>
       </c>
-      <c r="C72" s="93" t="inlineStr">
+      <c r="C72" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D72" s="93" t="inlineStr">
+      <c r="D72" s="94" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E72" s="93" t="inlineStr">
+      <c r="E72" s="94" t="inlineStr">
         <is>
           <t>113754/5</t>
         </is>
       </c>
-      <c r="F72" s="93" t="inlineStr">
+      <c r="F72" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G72" s="93" t="inlineStr">
+      <c r="G72" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H72" s="94" t="n">
+      <c r="H72" s="95" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="93" t="inlineStr">
+      <c r="A73" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B73" s="93" t="inlineStr">
+      <c r="B73" s="94" t="inlineStr">
         <is>
           <t>2026-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="C73" s="93" t="inlineStr">
+      <c r="C73" s="94" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D73" s="93" t="inlineStr"/>
-      <c r="E73" s="93" t="inlineStr"/>
-      <c r="F73" s="93" t="inlineStr">
+      <c r="D73" s="94" t="inlineStr"/>
+      <c r="E73" s="94" t="inlineStr"/>
+      <c r="F73" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G73" s="93" t="inlineStr">
+      <c r="G73" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H73" s="94" t="n">
+      <c r="H73" s="95" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="93" t="inlineStr">
+      <c r="A74" s="94" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B74" s="93" t="inlineStr">
+      <c r="B74" s="94" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="C74" s="93" t="inlineStr">
+      <c r="C74" s="94" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D74" s="93" t="inlineStr">
+      <c r="D74" s="94" t="inlineStr">
         <is>
           <t>NFS.1631</t>
         </is>
       </c>
-      <c r="E74" s="93" t="inlineStr">
+      <c r="E74" s="94" t="inlineStr">
         <is>
           <t>107973/1</t>
         </is>
       </c>
-      <c r="F74" s="93" t="inlineStr">
+      <c r="F74" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G74" s="93" t="inlineStr">
+      <c r="G74" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H74" s="94" t="n">
+      <c r="H74" s="95" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="93" t="inlineStr">
+      <c r="A75" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B75" s="93" t="inlineStr">
+      <c r="B75" s="94" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C75" s="93" t="inlineStr">
+      <c r="C75" s="94" t="inlineStr">
         <is>
           <t>ALFAMA PROCESSAMENTO DE DADOS LTDA</t>
         </is>
       </c>
-      <c r="D75" s="93" t="inlineStr">
+      <c r="D75" s="94" t="inlineStr">
         <is>
           <t>AV.1015392</t>
         </is>
       </c>
-      <c r="E75" s="93" t="inlineStr">
+      <c r="E75" s="94" t="inlineStr">
         <is>
           <t>108925/1</t>
         </is>
       </c>
-      <c r="F75" s="93" t="inlineStr">
+      <c r="F75" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G75" s="93" t="inlineStr">
+      <c r="G75" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H75" s="94" t="n">
+      <c r="H75" s="95" t="n">
         <v>183.6</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="93" t="inlineStr">
+      <c r="A76" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B76" s="93" t="inlineStr">
+      <c r="B76" s="94" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C76" s="93" t="inlineStr">
+      <c r="C76" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D76" s="93" t="inlineStr">
+      <c r="D76" s="94" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E76" s="93" t="inlineStr">
+      <c r="E76" s="94" t="inlineStr">
         <is>
           <t>111124/1</t>
         </is>
       </c>
-      <c r="F76" s="93" t="inlineStr">
+      <c r="F76" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G76" s="93" t="inlineStr">
+      <c r="G76" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H76" s="94" t="n">
+      <c r="H76" s="95" t="n">
         <v>720</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="93" t="inlineStr">
+      <c r="A77" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B77" s="93" t="inlineStr">
+      <c r="B77" s="94" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C77" s="93" t="inlineStr">
+      <c r="C77" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D77" s="93" t="inlineStr">
+      <c r="D77" s="94" t="inlineStr">
         <is>
           <t>FAT.21882309</t>
         </is>
       </c>
-      <c r="E77" s="93" t="inlineStr">
+      <c r="E77" s="94" t="inlineStr">
         <is>
           <t>111124/3</t>
         </is>
       </c>
-      <c r="F77" s="93" t="inlineStr">
+      <c r="F77" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G77" s="93" t="inlineStr">
+      <c r="G77" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H77" s="94" t="n">
+      <c r="H77" s="95" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="93" t="inlineStr">
+      <c r="A78" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B78" s="93" t="inlineStr">
+      <c r="B78" s="94" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C78" s="93" t="inlineStr">
+      <c r="C78" s="94" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D78" s="93" t="inlineStr">
+      <c r="D78" s="94" t="inlineStr">
         <is>
           <t>NFS.373725</t>
         </is>
       </c>
-      <c r="E78" s="93" t="inlineStr">
+      <c r="E78" s="94" t="inlineStr">
         <is>
           <t>110785/1</t>
         </is>
       </c>
-      <c r="F78" s="93" t="inlineStr">
+      <c r="F78" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G78" s="93" t="inlineStr">
+      <c r="G78" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H78" s="94" t="n">
+      <c r="H78" s="95" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="93" t="inlineStr">
+      <c r="A79" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B79" s="93" t="inlineStr">
+      <c r="B79" s="94" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C79" s="93" t="inlineStr">
+      <c r="C79" s="94" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D79" s="93" t="inlineStr">
+      <c r="D79" s="94" t="inlineStr">
         <is>
           <t>NFS.0036884701</t>
         </is>
       </c>
-      <c r="E79" s="93" t="inlineStr">
+      <c r="E79" s="94" t="inlineStr">
         <is>
           <t>109295/1</t>
         </is>
       </c>
-      <c r="F79" s="93" t="inlineStr">
+      <c r="F79" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G79" s="93" t="inlineStr">
+      <c r="G79" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H79" s="94" t="n">
+      <c r="H79" s="95" t="n">
         <v>84.81999999999999</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="93" t="inlineStr">
+      <c r="A80" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B80" s="93" t="inlineStr">
+      <c r="B80" s="94" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="C80" s="93" t="inlineStr">
+      <c r="C80" s="94" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D80" s="93" t="inlineStr">
+      <c r="D80" s="94" t="inlineStr">
         <is>
           <t>NFS.78</t>
         </is>
       </c>
-      <c r="E80" s="93" t="inlineStr">
+      <c r="E80" s="94" t="inlineStr">
         <is>
           <t>108317/1</t>
         </is>
       </c>
-      <c r="F80" s="93" t="inlineStr">
+      <c r="F80" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G80" s="93" t="inlineStr">
+      <c r="G80" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H80" s="94" t="n">
+      <c r="H80" s="95" t="n">
         <v>6173.37</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="93" t="inlineStr">
+      <c r="A81" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B81" s="93" t="inlineStr">
+      <c r="B81" s="94" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="C81" s="93" t="inlineStr">
+      <c r="C81" s="94" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D81" s="93" t="inlineStr">
+      <c r="D81" s="94" t="inlineStr">
         <is>
           <t>NFS.5832</t>
         </is>
       </c>
-      <c r="E81" s="93" t="inlineStr">
+      <c r="E81" s="94" t="inlineStr">
         <is>
           <t>109227/1</t>
         </is>
       </c>
-      <c r="F81" s="93" t="inlineStr">
+      <c r="F81" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G81" s="93" t="inlineStr">
+      <c r="G81" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H81" s="94" t="n">
+      <c r="H81" s="95" t="n">
         <v>740.38</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="93" t="inlineStr">
+      <c r="A82" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B82" s="93" t="inlineStr">
+      <c r="B82" s="94" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C82" s="93" t="inlineStr">
+      <c r="C82" s="94" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D82" s="93" t="inlineStr">
+      <c r="D82" s="94" t="inlineStr">
         <is>
           <t>FAT.Vivo 04 2026</t>
         </is>
       </c>
-      <c r="E82" s="93" t="inlineStr">
+      <c r="E82" s="94" t="inlineStr">
         <is>
           <t>110752/1</t>
         </is>
       </c>
-      <c r="F82" s="93" t="inlineStr">
+      <c r="F82" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G82" s="93" t="inlineStr">
+      <c r="G82" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H82" s="94" t="n">
+      <c r="H82" s="95" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="93" t="inlineStr">
+      <c r="A83" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B83" s="93" t="inlineStr">
+      <c r="B83" s="94" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C83" s="93" t="inlineStr">
+      <c r="C83" s="94" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D83" s="93" t="inlineStr">
+      <c r="D83" s="94" t="inlineStr">
         <is>
           <t>FAT.Vivo 05 2026</t>
         </is>
       </c>
-      <c r="E83" s="93" t="inlineStr">
+      <c r="E83" s="94" t="inlineStr">
         <is>
           <t>110753/1</t>
         </is>
       </c>
-      <c r="F83" s="93" t="inlineStr">
+      <c r="F83" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G83" s="93" t="inlineStr">
+      <c r="G83" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H83" s="94" t="n">
+      <c r="H83" s="95" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="93" t="inlineStr">
+      <c r="A84" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B84" s="93" t="inlineStr">
+      <c r="B84" s="94" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C84" s="93" t="inlineStr">
+      <c r="C84" s="94" t="inlineStr">
         <is>
           <t>TELEFONICA BRASIL S.A.</t>
         </is>
       </c>
-      <c r="D84" s="93" t="inlineStr">
+      <c r="D84" s="94" t="inlineStr">
         <is>
           <t>FAT.Vivo 06 2026</t>
         </is>
       </c>
-      <c r="E84" s="93" t="inlineStr">
+      <c r="E84" s="94" t="inlineStr">
         <is>
           <t>110754/1</t>
         </is>
       </c>
-      <c r="F84" s="93" t="inlineStr">
+      <c r="F84" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G84" s="93" t="inlineStr">
+      <c r="G84" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H84" s="94" t="n">
+      <c r="H84" s="95" t="n">
         <v>184.86</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="93" t="inlineStr">
+      <c r="A85" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B85" s="93" t="inlineStr">
+      <c r="B85" s="94" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C85" s="93" t="inlineStr">
+      <c r="C85" s="94" t="inlineStr">
         <is>
           <t>VC1 SOLUCOES EM TECNOLOGIA EIRELI</t>
         </is>
       </c>
-      <c r="D85" s="93" t="inlineStr">
+      <c r="D85" s="94" t="inlineStr">
         <is>
           <t>BOL.1017717992</t>
         </is>
       </c>
-      <c r="E85" s="93" t="inlineStr">
+      <c r="E85" s="94" t="inlineStr">
         <is>
           <t>109298/1</t>
         </is>
       </c>
-      <c r="F85" s="93" t="inlineStr">
+      <c r="F85" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G85" s="93" t="inlineStr">
+      <c r="G85" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H85" s="94" t="n">
+      <c r="H85" s="95" t="n">
         <v>137.93</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="93" t="inlineStr">
+      <c r="A86" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B86" s="93" t="inlineStr">
+      <c r="B86" s="94" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C86" s="93" t="inlineStr">
+      <c r="C86" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D86" s="93" t="inlineStr">
+      <c r="D86" s="94" t="inlineStr">
         <is>
           <t>CX.27.05.26</t>
         </is>
       </c>
-      <c r="E86" s="93" t="inlineStr">
+      <c r="E86" s="94" t="inlineStr">
         <is>
           <t>108827/1</t>
         </is>
       </c>
-      <c r="F86" s="93" t="inlineStr">
+      <c r="F86" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G86" s="93" t="inlineStr">
+      <c r="G86" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H86" s="94" t="n">
+      <c r="H86" s="95" t="n">
         <v>184</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="93" t="inlineStr">
+      <c r="A87" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B87" s="93" t="inlineStr">
+      <c r="B87" s="94" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="C87" s="93" t="inlineStr">
+      <c r="C87" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D87" s="93" t="inlineStr">
+      <c r="D87" s="94" t="inlineStr">
         <is>
           <t>SAL.1_ Ferias 1 VIn D 26</t>
         </is>
       </c>
-      <c r="E87" s="93" t="inlineStr">
+      <c r="E87" s="94" t="inlineStr">
         <is>
           <t>107780/1</t>
         </is>
       </c>
-      <c r="F87" s="93" t="inlineStr">
+      <c r="F87" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G87" s="93" t="inlineStr">
+      <c r="G87" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H87" s="94" t="n">
+      <c r="H87" s="95" t="n">
         <v>1101.12</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="93" t="inlineStr">
+      <c r="A88" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B88" s="93" t="inlineStr">
+      <c r="B88" s="94" t="inlineStr">
         <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="C88" s="93" t="inlineStr">
+      <c r="C88" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D88" s="93" t="inlineStr">
+      <c r="D88" s="94" t="inlineStr">
         <is>
           <t>SAL.sal 052026</t>
         </is>
       </c>
-      <c r="E88" s="93" t="inlineStr">
+      <c r="E88" s="94" t="inlineStr">
         <is>
           <t>109482/1</t>
         </is>
       </c>
-      <c r="F88" s="93" t="inlineStr">
+      <c r="F88" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G88" s="93" t="inlineStr">
+      <c r="G88" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H88" s="94" t="n">
+      <c r="H88" s="95" t="n">
         <v>1455</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="93" t="inlineStr">
+      <c r="A89" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B89" s="93" t="inlineStr">
+      <c r="B89" s="94" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C89" s="93" t="inlineStr">
+      <c r="C89" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D89" s="93" t="inlineStr">
+      <c r="D89" s="94" t="inlineStr">
         <is>
           <t>SAL.SALARIO06VINI</t>
         </is>
       </c>
-      <c r="E89" s="93" t="inlineStr">
+      <c r="E89" s="94" t="inlineStr">
         <is>
           <t>110700/1</t>
         </is>
       </c>
-      <c r="F89" s="93" t="inlineStr">
+      <c r="F89" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G89" s="93" t="inlineStr">
+      <c r="G89" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H89" s="94" t="n">
+      <c r="H89" s="95" t="n">
         <v>686</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="93" t="inlineStr">
+      <c r="A90" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B90" s="93" t="inlineStr">
+      <c r="B90" s="94" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
-      <c r="C90" s="93" t="inlineStr">
+      <c r="C90" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D90" s="93" t="inlineStr">
+      <c r="D90" s="94" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E90" s="93" t="inlineStr">
+      <c r="E90" s="94" t="inlineStr">
         <is>
           <t>113754/6</t>
         </is>
       </c>
-      <c r="F90" s="93" t="inlineStr">
+      <c r="F90" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G90" s="93" t="inlineStr">
+      <c r="G90" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H90" s="94" t="n">
+      <c r="H90" s="95" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="93" t="inlineStr">
+      <c r="A91" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B91" s="93" t="inlineStr">
+      <c r="B91" s="94" t="inlineStr">
         <is>
           <t>2026-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="C91" s="93" t="inlineStr">
+      <c r="C91" s="94" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D91" s="93" t="inlineStr"/>
-      <c r="E91" s="93" t="inlineStr"/>
-      <c r="F91" s="93" t="inlineStr">
+      <c r="D91" s="94" t="inlineStr"/>
+      <c r="E91" s="94" t="inlineStr"/>
+      <c r="F91" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G91" s="93" t="inlineStr">
+      <c r="G91" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H91" s="94" t="n">
+      <c r="H91" s="95" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="93" t="inlineStr">
+      <c r="A92" s="94" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B92" s="93" t="inlineStr">
+      <c r="B92" s="94" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C92" s="93" t="inlineStr">
+      <c r="C92" s="94" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D92" s="93" t="inlineStr">
+      <c r="D92" s="94" t="inlineStr">
         <is>
           <t>NFS.33</t>
         </is>
       </c>
-      <c r="E92" s="93" t="inlineStr">
+      <c r="E92" s="94" t="inlineStr">
         <is>
           <t>110902/1</t>
         </is>
       </c>
-      <c r="F92" s="93" t="inlineStr">
+      <c r="F92" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G92" s="93" t="inlineStr">
+      <c r="G92" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H92" s="94" t="n">
+      <c r="H92" s="95" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="93" t="inlineStr">
+      <c r="A93" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B93" s="93" t="inlineStr">
+      <c r="B93" s="94" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C93" s="93" t="inlineStr">
+      <c r="C93" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D93" s="93" t="inlineStr">
+      <c r="D93" s="94" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E93" s="93" t="inlineStr">
+      <c r="E93" s="94" t="inlineStr">
         <is>
           <t>113575/1</t>
         </is>
       </c>
-      <c r="F93" s="93" t="inlineStr">
+      <c r="F93" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G93" s="93" t="inlineStr">
+      <c r="G93" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H93" s="94" t="n">
+      <c r="H93" s="95" t="n">
         <v>20.39</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="93" t="inlineStr">
+      <c r="A94" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B94" s="93" t="inlineStr">
+      <c r="B94" s="94" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C94" s="93" t="inlineStr">
+      <c r="C94" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D94" s="93" t="inlineStr">
+      <c r="D94" s="94" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E94" s="93" t="inlineStr">
+      <c r="E94" s="94" t="inlineStr">
         <is>
           <t>113575/2</t>
         </is>
       </c>
-      <c r="F94" s="93" t="inlineStr">
+      <c r="F94" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G94" s="93" t="inlineStr">
+      <c r="G94" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H94" s="94" t="n">
+      <c r="H94" s="95" t="n">
         <v>133.73</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="93" t="inlineStr">
+      <c r="A95" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B95" s="93" t="inlineStr">
+      <c r="B95" s="94" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C95" s="93" t="inlineStr">
+      <c r="C95" s="94" t="inlineStr">
         <is>
           <t>CLARO S.A.</t>
         </is>
       </c>
-      <c r="D95" s="93" t="inlineStr">
+      <c r="D95" s="94" t="inlineStr">
         <is>
           <t>FAT.Claro 07.26</t>
         </is>
       </c>
-      <c r="E95" s="93" t="inlineStr">
+      <c r="E95" s="94" t="inlineStr">
         <is>
           <t>113575/3</t>
         </is>
       </c>
-      <c r="F95" s="93" t="inlineStr">
+      <c r="F95" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G95" s="93" t="inlineStr">
+      <c r="G95" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H95" s="94" t="n">
+      <c r="H95" s="95" t="n">
         <v>825.28</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="93" t="inlineStr">
+      <c r="A96" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B96" s="93" t="inlineStr">
+      <c r="B96" s="94" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C96" s="93" t="inlineStr">
+      <c r="C96" s="94" t="inlineStr">
         <is>
           <t>INTELBRAS S.A. INDUSTRIA DE TELECOMUNICACAO ELETRONICA BRASILEIRA</t>
         </is>
       </c>
-      <c r="D96" s="93" t="inlineStr">
+      <c r="D96" s="94" t="inlineStr">
         <is>
           <t>NFS.377682</t>
         </is>
       </c>
-      <c r="E96" s="93" t="inlineStr">
+      <c r="E96" s="94" t="inlineStr">
         <is>
           <t>114092/1</t>
         </is>
       </c>
-      <c r="F96" s="93" t="inlineStr">
+      <c r="F96" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G96" s="93" t="inlineStr">
+      <c r="G96" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H96" s="94" t="n">
+      <c r="H96" s="95" t="n">
         <v>79.59999999999999</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="93" t="inlineStr">
+      <c r="A97" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B97" s="93" t="inlineStr">
+      <c r="B97" s="94" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="C97" s="93" t="inlineStr">
+      <c r="C97" s="94" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="D97" s="93" t="inlineStr">
+      <c r="D97" s="94" t="inlineStr">
         <is>
           <t>NFS.3</t>
         </is>
       </c>
-      <c r="E97" s="93" t="inlineStr">
+      <c r="E97" s="94" t="inlineStr">
         <is>
           <t>111371/1</t>
         </is>
       </c>
-      <c r="F97" s="93" t="inlineStr">
+      <c r="F97" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G97" s="93" t="inlineStr">
+      <c r="G97" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H97" s="94" t="n">
+      <c r="H97" s="95" t="n">
         <v>6300</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="93" t="inlineStr">
+      <c r="A98" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B98" s="93" t="inlineStr">
+      <c r="B98" s="94" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C98" s="93" t="inlineStr">
+      <c r="C98" s="94" t="inlineStr">
         <is>
           <t>LOCAWEB SERVICOS DE INTERNET S/A</t>
         </is>
       </c>
-      <c r="D98" s="93" t="inlineStr">
+      <c r="D98" s="94" t="inlineStr">
         <is>
           <t>BOL.LOCAWEB 07.26</t>
         </is>
       </c>
-      <c r="E98" s="93" t="inlineStr">
+      <c r="E98" s="94" t="inlineStr">
         <is>
           <t>113049/1</t>
         </is>
       </c>
-      <c r="F98" s="93" t="inlineStr">
+      <c r="F98" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G98" s="93" t="inlineStr">
+      <c r="G98" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H98" s="94" t="n">
+      <c r="H98" s="95" t="n">
         <v>1151.26</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="93" t="inlineStr">
+      <c r="A99" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B99" s="93" t="inlineStr">
+      <c r="B99" s="94" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="C99" s="93" t="inlineStr">
+      <c r="C99" s="94" t="inlineStr">
         <is>
           <t>SABHA INTELIGENCIA EM TECNOLOGIA LTDA</t>
         </is>
       </c>
-      <c r="D99" s="93" t="inlineStr">
+      <c r="D99" s="94" t="inlineStr">
         <is>
           <t>NFS.66</t>
         </is>
       </c>
-      <c r="E99" s="93" t="inlineStr">
+      <c r="E99" s="94" t="inlineStr">
         <is>
           <t>112107/1</t>
         </is>
       </c>
-      <c r="F99" s="93" t="inlineStr">
+      <c r="F99" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G99" s="93" t="inlineStr">
+      <c r="G99" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H99" s="94" t="n">
+      <c r="H99" s="95" t="n">
         <v>1037.38</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="93" t="inlineStr">
+      <c r="A100" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B100" s="93" t="inlineStr">
+      <c r="B100" s="94" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="C100" s="93" t="inlineStr">
+      <c r="C100" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D100" s="93" t="inlineStr">
+      <c r="D100" s="94" t="inlineStr">
         <is>
           <t>SAL.sal 0626</t>
         </is>
       </c>
-      <c r="E100" s="93" t="inlineStr">
+      <c r="E100" s="94" t="inlineStr">
         <is>
           <t>112402/1</t>
         </is>
       </c>
-      <c r="F100" s="93" t="inlineStr">
+      <c r="F100" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G100" s="93" t="inlineStr">
+      <c r="G100" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H100" s="94" t="n">
+      <c r="H100" s="95" t="n">
         <v>1225</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="93" t="inlineStr">
+      <c r="A101" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B101" s="93" t="inlineStr">
+      <c r="B101" s="94" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C101" s="93" t="inlineStr">
+      <c r="C101" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D101" s="93" t="inlineStr">
+      <c r="D101" s="94" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E101" s="93" t="inlineStr">
+      <c r="E101" s="94" t="inlineStr">
         <is>
           <t>113754/1</t>
         </is>
       </c>
-      <c r="F101" s="93" t="inlineStr">
+      <c r="F101" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G101" s="93" t="inlineStr">
+      <c r="G101" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H101" s="94" t="n">
+      <c r="H101" s="95" t="n">
         <v>1029</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="93" t="inlineStr">
+      <c r="A102" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B102" s="93" t="inlineStr">
+      <c r="B102" s="94" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="C102" s="93" t="inlineStr">
+      <c r="C102" s="94" t="inlineStr">
         <is>
           <t>VINICIUS DI FRANCO HEITOR</t>
         </is>
       </c>
-      <c r="D102" s="93" t="inlineStr">
+      <c r="D102" s="94" t="inlineStr">
         <is>
           <t>FGTS/INSS</t>
         </is>
       </c>
-      <c r="E102" s="93" t="inlineStr">
+      <c r="E102" s="94" t="inlineStr">
         <is>
           <t>113754/7</t>
         </is>
       </c>
-      <c r="F102" s="93" t="inlineStr">
+      <c r="F102" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G102" s="93" t="inlineStr">
+      <c r="G102" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H102" s="94" t="n">
+      <c r="H102" s="95" t="n">
         <v>207.04</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="93" t="inlineStr">
+      <c r="A103" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B103" s="93" t="inlineStr">
+      <c r="B103" s="94" t="inlineStr">
         <is>
           <t>2026-07-01 00:00:00</t>
         </is>
       </c>
-      <c r="C103" s="93" t="inlineStr">
+      <c r="C103" s="94" t="inlineStr">
         <is>
           <t>Vale Alimentação Vinicius</t>
         </is>
       </c>
-      <c r="D103" s="93" t="inlineStr"/>
-      <c r="E103" s="93" t="inlineStr"/>
-      <c r="F103" s="93" t="inlineStr">
+      <c r="D103" s="94" t="inlineStr"/>
+      <c r="E103" s="94" t="inlineStr"/>
+      <c r="F103" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G103" s="93" t="inlineStr">
+      <c r="G103" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H103" s="94" t="n">
+      <c r="H103" s="95" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="93" t="inlineStr">
+      <c r="A104" s="94" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B104" s="93" t="inlineStr">
+      <c r="B104" s="94" t="inlineStr">
         <is>
           <t>25/07/2026</t>
         </is>
       </c>
-      <c r="C104" s="93" t="inlineStr">
+      <c r="C104" s="94" t="inlineStr">
         <is>
           <t>WEB MOBILE TELECOM LTDA</t>
         </is>
       </c>
-      <c r="D104" s="93" t="inlineStr">
+      <c r="D104" s="94" t="inlineStr">
         <is>
           <t>NFS.84</t>
         </is>
       </c>
-      <c r="E104" s="93" t="inlineStr">
+      <c r="E104" s="94" t="inlineStr">
         <is>
           <t>113583/1</t>
         </is>
       </c>
-      <c r="F104" s="93" t="inlineStr">
+      <c r="F104" s="94" t="inlineStr">
         <is>
           <t>Tetus</t>
         </is>
       </c>
-      <c r="G104" s="93" t="inlineStr">
+      <c r="G104" s="94" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="H104" s="94" t="n">
+      <c r="H104" s="95" t="n">
         <v>82.5</v>
       </c>
     </row>
     <row r="105">
-      <c r="G105" s="95" t="inlineStr">
+      <c r="G105" s="96" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H105" s="96">
+      <c r="H105" s="97">
         <f>SUM(H5:H104)</f>
         <v/>
       </c>
@@ -14064,7 +14072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -14214,49 +14222,41 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="76" t="inlineStr">
         <is>
-          <t>CRISTIANE — decisão, negociação e representação</t>
+          <t>CRISTIANE — gestora de TI e Jurídico</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="77" t="inlineStr">
         <is>
-          <t>Negociação de contratos</t>
+          <t>ESCOPO</t>
         </is>
       </c>
       <c r="B11" s="78" t="inlineStr">
         <is>
-          <t>Fechar valor e condições com fornecedores e prestadores. É o que gerou as economias do ano: Jonathan de R$ 10.000 para R$ 6.300 e Elias de R$ 1.065 para R$ 603,30 (43% de redução).</t>
+          <t>Responde pelas duas áreas: TI (R$ 284.971,50 orçados em 2026) e Jurídico (R$ 324.730,42), num total de R$ 609.701,92. Equipe direta de sete pessoas entre CLT e PJ.</t>
         </is>
       </c>
       <c r="C11" s="79" t="n"/>
       <c r="D11" s="79" t="n"/>
       <c r="E11" s="79" t="n"/>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="77" t="inlineStr">
-        <is>
-          <t>O que entra e sai do orçamento</t>
-        </is>
-      </c>
-      <c r="B12" s="78" t="inlineStr">
-        <is>
-          <t>Aprovar inclusão de linha nova, cancelamento e revisão de valor. Exemplos do período: cancelamento do Astrea, inclusão da Dra. Michele, decisão sobre a sala de reunião.</t>
-        </is>
-      </c>
-      <c r="C12" s="79" t="n"/>
-      <c r="D12" s="79" t="n"/>
-      <c r="E12" s="79" t="n"/>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="80" t="inlineStr">
+        <is>
+          <t>— ORÇAMENTO —</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="77" t="inlineStr">
         <is>
-          <t>Rateio e centro de custo</t>
+          <t>Montar e revisar o orçamento</t>
         </is>
       </c>
       <c r="B13" s="78" t="inlineStr">
         <is>
-          <t>Definir com a controladoria o que é do TI e o que é corporativo — softwares de uso transversal, ferramentas de IA, reclassificações.</t>
+          <t>Definir as linhas do ano, os valores e a base de meses de cada contrato. Revisar quando houver reajuste, entrada ou saída — como o aumento da Thamar, o do Vinicius e a inclusão da Dra. Michele.</t>
         </is>
       </c>
       <c r="C13" s="79" t="n"/>
@@ -14266,12 +14266,12 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="77" t="inlineStr">
         <is>
-          <t>Apresentação à diretoria</t>
+          <t>Aprovar o que entra e sai</t>
         </is>
       </c>
       <c r="B14" s="78" t="inlineStr">
         <is>
-          <t>Levar o Painel, defender os números e as pautas em aberto. Responder por desvio e por economia.</t>
+          <t>Nenhuma linha nova ou cancelamento sem passar por ela. Exemplos do período: cancelamento do Astrea, criação das linhas de IA, entrada do AnyDesk, decisão sobre a sala de reunião.</t>
         </is>
       </c>
       <c r="C14" s="79" t="n"/>
@@ -14281,34 +14281,49 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="77" t="inlineStr">
         <is>
-          <t>Aprovação de compra acima do saldo</t>
+          <t>Validar o fechamento mensal</t>
         </is>
       </c>
       <c r="B15" s="78" t="inlineStr">
         <is>
-          <t>Quando a solicitação de uma área levar ao estouro, decidir com a diretoria se aprova ou segura.</t>
+          <t>Conferir o que o analista lançou antes de o número virar informação oficial. Olhar a coluna 'Linhas lançadas' do Painel: desvio negativo em linha não lançada é ausência de dado, não economia.</t>
         </is>
       </c>
       <c r="C15" s="79" t="n"/>
       <c r="D15" s="79" t="n"/>
       <c r="E15" s="79" t="n"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>VINICIUS — suporte, rotina e apoio ao desenvolvimento</t>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="77" t="inlineStr">
+        <is>
+          <t>Responder pelo desvio</t>
+        </is>
+      </c>
+      <c r="B16" s="78" t="inlineStr">
+        <is>
+          <t>Explicar cada estouro e cada economia — o que foi decisão de gestão, o que foi erro de origem do orçamento e o que é só falta de lançamento.</t>
+        </is>
+      </c>
+      <c r="C16" s="79" t="n"/>
+      <c r="D16" s="79" t="n"/>
+      <c r="E16" s="79" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="80" t="inlineStr">
+        <is>
+          <t>— CONTRATOS E FORNECEDORES —</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="77" t="inlineStr">
         <is>
-          <t>Suporte ao usuário</t>
+          <t>Negociar valor e condições</t>
         </is>
       </c>
       <c r="B18" s="78" t="inlineStr">
         <is>
-          <t>Atendimento do dia a dia às áreas: equipamento, acesso, software.</t>
+          <t>É o que gerou as economias do ano: Jonathan de R$ 10.000 para R$ 6.300 e Elias de R$ 1.065 para R$ 603,30, 43% de redução. Só a negociação responde por boa parte dos R$ 56.946 economizados no TI.</t>
         </is>
       </c>
       <c r="C18" s="79" t="n"/>
@@ -14318,12 +14333,12 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="77" t="inlineStr">
         <is>
-          <t>Fechamento mensal do orçamento</t>
+          <t>Decidir contratar, manter ou cancelar</t>
         </is>
       </c>
       <c r="B19" s="78" t="inlineStr">
         <is>
-          <t>Extrair o relatório do centro de custo no SIENGE e lançar o realizado na aba Realizado, preenchendo a coluna Fonte do dado com a data da extração. Item sem gasto no mês recebe 0, não fica em branco.</t>
+          <t>Avaliar necessidade real antes de assinar e cortar o que não entrega. No período: Jusfy cancelado antes de iniciar, Astrea em cancelamento, contratação do Jonathan segurada por três meses.</t>
         </is>
       </c>
       <c r="C19" s="79" t="n"/>
@@ -14333,42 +14348,34 @@
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="77" t="inlineStr">
         <is>
-          <t>Controle de equipamentos</t>
+          <t>Controlar prazos de renovação</t>
         </is>
       </c>
       <c r="B20" s="78" t="inlineStr">
         <is>
-          <t>Registrar solicitações e empréstimos na aba própria, cobrar a devolução do item quebrado na troca 1x1 e controlar o estoque reserva.</t>
+          <t>Contratos anuais renovam sozinhos. O Astrea cobra em cartão e o ciclo vira em 01/11 — se o cancelamento não estiver confirmado até lá, entra anuidade de cerca de R$ 7.400 sem previsão orçamentária.</t>
         </is>
       </c>
       <c r="C20" s="79" t="n"/>
       <c r="D20" s="79" t="n"/>
       <c r="E20" s="79" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="77" t="inlineStr">
-        <is>
-          <t>Saldo por área</t>
-        </is>
-      </c>
-      <c r="B21" s="78" t="inlineStr">
-        <is>
-          <t>Acompanhar quanto resta na rubrica de cada área e avisar ANTES de comprar quando a solicitação for levar ao estouro.</t>
-        </is>
-      </c>
-      <c r="C21" s="79" t="n"/>
-      <c r="D21" s="79" t="n"/>
-      <c r="E21" s="79" t="n"/>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>— PESSOAS —</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="77" t="inlineStr">
         <is>
-          <t>Conferência de faturas</t>
+          <t>Dimensionar a equipe</t>
         </is>
       </c>
       <c r="B22" s="78" t="inlineStr">
         <is>
-          <t>Bater o valor cobrado contra o contrato. Foi assim que apareceram o Jusbrasil 30% acima e o Astrea a 5x o orçado.</t>
+          <t>Definir quem é CLT, quem é PJ, quantas horas e com que escopo. Decidir quando segurar uma contratação, como fez de jan a mar com o consultor.</t>
         </is>
       </c>
       <c r="C22" s="79" t="n"/>
@@ -14378,12 +14385,12 @@
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="77" t="inlineStr">
         <is>
-          <t>Padrão de descrição no SIENGE</t>
+          <t>Alocar o trabalho por custo</t>
         </is>
       </c>
       <c r="B23" s="78" t="inlineStr">
         <is>
-          <t>Em rubricas genéricas, detalhar o item na descrição do lançamento ('Peças – mouse', 'Peças – tela'), para a análise sair por filtro.</t>
+          <t>Manter a rotina com o analista e a capacidade cara reservada para o que só ela resolve. A hora do consultor custa o dobro e são só 104 por mês.</t>
         </is>
       </c>
       <c r="C23" s="79" t="n"/>
@@ -14393,34 +14400,49 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="77" t="inlineStr">
         <is>
-          <t>Apoio operacional ao desenvolvimento</t>
+          <t>Reajustes e bonificações</t>
         </is>
       </c>
       <c r="B24" s="78" t="inlineStr">
         <is>
-          <t>Assumir as tarefas operacionais do que o Jonathan conduz. Cada hora que sai das mãos dele a R$ 31,25 libera uma hora de R$ 60,58 — é o que multiplica a capacidade limitada do consultor.</t>
+          <t>Aprovar aumentos e decidir sobre as bonificações previstas em ago e dez, que somam R$ 29.160,60 nas duas áreas.</t>
         </is>
       </c>
       <c r="C24" s="79" t="n"/>
       <c r="D24" s="79" t="n"/>
       <c r="E24" s="79" t="n"/>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>JONATHAN — técnico e pontual, nunca rotina</t>
-        </is>
-      </c>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>— POLÍTICAS E GOVERNANÇA —</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="77" t="inlineStr">
+        <is>
+          <t>Definir regras de uso</t>
+        </is>
+      </c>
+      <c r="B26" s="78" t="inlineStr">
+        <is>
+          <t>Troca 1x1 de equipamento, estoque reserva para empréstimo, quem pode gerar chave de API, quem tem licença de IA e sob qual login.</t>
+        </is>
+      </c>
+      <c r="C26" s="79" t="n"/>
+      <c r="D26" s="79" t="n"/>
+      <c r="E26" s="79" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="77" t="inlineStr">
         <is>
-          <t>Desenvolvimento</t>
+          <t>Rateio e centro de custo</t>
         </is>
       </c>
       <c r="B27" s="78" t="inlineStr">
         <is>
-          <t>O trabalho de projeto para o qual foi contratado, 3 dias por semana.</t>
+          <t>Definir com a controladoria o que é do TI e o que é corporativo: oito linhas de uso transversal estão marcadas como RATEIO A DEFINIR, e o Adapta está classificado na área errada.</t>
         </is>
       </c>
       <c r="C27" s="79" t="n"/>
@@ -14430,42 +14452,34 @@
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="77" t="inlineStr">
         <is>
-          <t>Automatizar a extração do SIENGE</t>
+          <t>Zelar pelo sigilo</t>
         </is>
       </c>
       <c r="B28" s="78" t="inlineStr">
         <is>
-          <t>Entrega de maior retorno: gasta algumas horas uma vez e devolve tempo do analista todo mês.</t>
+          <t>Num escritório de advocacia, licença de IA compartilhada expõe o histórico de um cliente a quem não atua no caso. É risco de sigilo profissional, não só de custo.</t>
         </is>
       </c>
       <c r="C28" s="79" t="n"/>
       <c r="D28" s="79" t="n"/>
       <c r="E28" s="79" t="n"/>
     </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="77" t="inlineStr">
-        <is>
-          <t>Avaliar AnyDesk</t>
-        </is>
-      </c>
-      <c r="B29" s="78" t="inlineStr">
-        <is>
-          <t>Definir necessidade, plano e valor da licença de acesso remoto.</t>
-        </is>
-      </c>
-      <c r="C29" s="79" t="n"/>
-      <c r="D29" s="79" t="n"/>
-      <c r="E29" s="79" t="n"/>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="80" t="inlineStr">
+        <is>
+          <t>— RELACIONAMENTO —</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="77" t="inlineStr">
         <is>
-          <t>Avaliar Claude x GPT e planos de equipe</t>
+          <t>Diretoria</t>
         </is>
       </c>
       <c r="B30" s="78" t="inlineStr">
         <is>
-          <t>Subsidiar a decisão do Vitor e resolver o compartilhamento de login, que hoje expõe histórico de cliente entre usuários.</t>
+          <t>Apresentar o Painel, defender os números e levar as pautas em aberto. Hoje são seis: sala de reunião, meta das IAs, notebooks, despesas fora do orçamento, reclassificação do Adapta e erro de origem do Astrea.</t>
         </is>
       </c>
       <c r="C30" s="79" t="n"/>
@@ -14475,12 +14489,12 @@
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="77" t="inlineStr">
         <is>
-          <t>Investigar o consumo de API</t>
+          <t>Financeiro e controladoria</t>
         </is>
       </c>
       <c r="B31" s="78" t="inlineStr">
         <is>
-          <t>O gasto da OpenAI saltou de R$ 322 em mar para R$ 5.394 em abr, padrão de consumo por uso. Configurar limite rígido de gasto e definir quem pode gerar chave.</t>
+          <t>Abertura do centro de custo no SIENGE, escolha do regime (competência ou caixa), reclassificações e separação entre custo e repasse.</t>
         </is>
       </c>
       <c r="C31" s="79" t="n"/>
@@ -14490,74 +14504,316 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="77" t="inlineStr">
         <is>
-          <t>NÃO fazer</t>
+          <t>RH e Administrativo</t>
         </is>
       </c>
       <c r="B32" s="78" t="inlineStr">
         <is>
-          <t>Rotina administrativa, lançamento de planilha, controle de estoque. São 104 h/mês a R$ 60,58 — se ele aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
+          <t>Custo total dos CLT para o comparativo, e o que sai do TI por não ser dele — papelaria e treinamento corporativo.</t>
         </is>
       </c>
       <c r="C32" s="79" t="n"/>
       <c r="D32" s="79" t="n"/>
       <c r="E32" s="79" t="n"/>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="80" t="inlineStr">
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="77" t="inlineStr">
+        <is>
+          <t>Outras áreas</t>
+        </is>
+      </c>
+      <c r="B33" s="78" t="inlineStr">
+        <is>
+          <t>Avisar antes do estouro quando uma solicitação de equipamento passar do saldo da rubrica delas.</t>
+        </is>
+      </c>
+      <c r="C33" s="79" t="n"/>
+      <c r="D33" s="79" t="n"/>
+      <c r="E33" s="79" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>VINICIUS — suporte, rotina e apoio ao desenvolvimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="77" t="inlineStr">
+        <is>
+          <t>Suporte ao usuário</t>
+        </is>
+      </c>
+      <c r="B36" s="78" t="inlineStr">
+        <is>
+          <t>Atendimento do dia a dia às áreas: equipamento, acesso, software.</t>
+        </is>
+      </c>
+      <c r="C36" s="79" t="n"/>
+      <c r="D36" s="79" t="n"/>
+      <c r="E36" s="79" t="n"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="77" t="inlineStr">
+        <is>
+          <t>Fechamento mensal do orçamento</t>
+        </is>
+      </c>
+      <c r="B37" s="78" t="inlineStr">
+        <is>
+          <t>Extrair o relatório do centro de custo no SIENGE e lançar o realizado na aba Realizado, preenchendo a coluna Fonte do dado com a data da extração. Item sem gasto no mês recebe 0, não fica em branco.</t>
+        </is>
+      </c>
+      <c r="C37" s="79" t="n"/>
+      <c r="D37" s="79" t="n"/>
+      <c r="E37" s="79" t="n"/>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="77" t="inlineStr">
+        <is>
+          <t>Controle de equipamentos</t>
+        </is>
+      </c>
+      <c r="B38" s="78" t="inlineStr">
+        <is>
+          <t>Registrar solicitações e empréstimos na aba própria, cobrar a devolução do item quebrado na troca 1x1 e controlar o estoque reserva.</t>
+        </is>
+      </c>
+      <c r="C38" s="79" t="n"/>
+      <c r="D38" s="79" t="n"/>
+      <c r="E38" s="79" t="n"/>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="77" t="inlineStr">
+        <is>
+          <t>Saldo por área</t>
+        </is>
+      </c>
+      <c r="B39" s="78" t="inlineStr">
+        <is>
+          <t>Acompanhar quanto resta na rubrica de cada área e avisar ANTES de comprar quando a solicitação for levar ao estouro.</t>
+        </is>
+      </c>
+      <c r="C39" s="79" t="n"/>
+      <c r="D39" s="79" t="n"/>
+      <c r="E39" s="79" t="n"/>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="77" t="inlineStr">
+        <is>
+          <t>Conferência de faturas</t>
+        </is>
+      </c>
+      <c r="B40" s="78" t="inlineStr">
+        <is>
+          <t>Bater o valor cobrado contra o contrato. Foi assim que apareceram o Jusbrasil 30% acima e o Astrea a 5x o orçado.</t>
+        </is>
+      </c>
+      <c r="C40" s="79" t="n"/>
+      <c r="D40" s="79" t="n"/>
+      <c r="E40" s="79" t="n"/>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="77" t="inlineStr">
+        <is>
+          <t>Padrão de descrição no SIENGE</t>
+        </is>
+      </c>
+      <c r="B41" s="78" t="inlineStr">
+        <is>
+          <t>Em rubricas genéricas, detalhar o item na descrição do lançamento ('Peças – mouse', 'Peças – tela'), para a análise sair por filtro.</t>
+        </is>
+      </c>
+      <c r="C41" s="79" t="n"/>
+      <c r="D41" s="79" t="n"/>
+      <c r="E41" s="79" t="n"/>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="77" t="inlineStr">
+        <is>
+          <t>Apoio operacional ao desenvolvimento</t>
+        </is>
+      </c>
+      <c r="B42" s="78" t="inlineStr">
+        <is>
+          <t>Assumir as tarefas operacionais do que o Jonathan conduz. Cada hora que sai das mãos dele a R$ 31,25 libera uma hora de R$ 60,58 — é o que multiplica a capacidade limitada do consultor.</t>
+        </is>
+      </c>
+      <c r="C42" s="79" t="n"/>
+      <c r="D42" s="79" t="n"/>
+      <c r="E42" s="79" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>JONATHAN — técnico e pontual, nunca rotina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="77" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="B45" s="78" t="inlineStr">
+        <is>
+          <t>O trabalho de projeto para o qual foi contratado, 3 dias por semana.</t>
+        </is>
+      </c>
+      <c r="C45" s="79" t="n"/>
+      <c r="D45" s="79" t="n"/>
+      <c r="E45" s="79" t="n"/>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="77" t="inlineStr">
+        <is>
+          <t>Automatizar a extração do SIENGE</t>
+        </is>
+      </c>
+      <c r="B46" s="78" t="inlineStr">
+        <is>
+          <t>Entrega de maior retorno: gasta algumas horas uma vez e devolve tempo do analista todo mês.</t>
+        </is>
+      </c>
+      <c r="C46" s="79" t="n"/>
+      <c r="D46" s="79" t="n"/>
+      <c r="E46" s="79" t="n"/>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="77" t="inlineStr">
+        <is>
+          <t>Avaliar AnyDesk</t>
+        </is>
+      </c>
+      <c r="B47" s="78" t="inlineStr">
+        <is>
+          <t>Definir necessidade, plano e valor da licença de acesso remoto.</t>
+        </is>
+      </c>
+      <c r="C47" s="79" t="n"/>
+      <c r="D47" s="79" t="n"/>
+      <c r="E47" s="79" t="n"/>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="77" t="inlineStr">
+        <is>
+          <t>Avaliar Claude x GPT e planos de equipe</t>
+        </is>
+      </c>
+      <c r="B48" s="78" t="inlineStr">
+        <is>
+          <t>Subsidiar a decisão do Vitor e resolver o compartilhamento de login, que hoje expõe histórico de cliente entre usuários.</t>
+        </is>
+      </c>
+      <c r="C48" s="79" t="n"/>
+      <c r="D48" s="79" t="n"/>
+      <c r="E48" s="79" t="n"/>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="77" t="inlineStr">
+        <is>
+          <t>Investigar o consumo de API</t>
+        </is>
+      </c>
+      <c r="B49" s="78" t="inlineStr">
+        <is>
+          <t>O gasto da OpenAI saltou de R$ 322 em mar para R$ 5.394 em abr, padrão de consumo por uso. Configurar limite rígido de gasto e definir quem pode gerar chave.</t>
+        </is>
+      </c>
+      <c r="C49" s="79" t="n"/>
+      <c r="D49" s="79" t="n"/>
+      <c r="E49" s="79" t="n"/>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="77" t="inlineStr">
+        <is>
+          <t>NÃO fazer</t>
+        </is>
+      </c>
+      <c r="B50" s="78" t="inlineStr">
+        <is>
+          <t>Rotina administrativa, lançamento de planilha, controle de estoque. São 104 h/mês a R$ 60,58 — se ele aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
+        </is>
+      </c>
+      <c r="C50" s="79" t="n"/>
+      <c r="D50" s="79" t="n"/>
+      <c r="E50" s="79" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="81" t="inlineStr">
         <is>
           <t>ELIAS — suporte técnico sob demanda</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="77" t="inlineStr">
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="77" t="inlineStr">
         <is>
           <t>Acionamento pontual</t>
         </is>
       </c>
-      <c r="B35" s="78" t="inlineStr">
+      <c r="B53" s="78" t="inlineStr">
         <is>
           <t>Contrato ativo, acionado conforme a necessidade. Sem acionamento de jan a jul/26. Valor renegociado de R$ 1.065 para R$ 603,30 a partir de set/26.</t>
         </is>
       </c>
-      <c r="C35" s="79" t="n"/>
-      <c r="D35" s="79" t="n"/>
-      <c r="E35" s="79" t="n"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="81" t="inlineStr">
+      <c r="C53" s="79" t="n"/>
+      <c r="D53" s="79" t="n"/>
+      <c r="E53" s="79" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="82" t="inlineStr">
         <is>
           <t>CRITÉRIO: a hora do consultor custa o dobro da hora do analista, e são só 104 por mês. Tarefa recorrente vai para quem custa menos; capacidade cara fica reservada para o que só ela resolve. Consultor em rotina administrativa é o recurso mais caro na tarefa mais barata.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A34:E34"/>
+  <mergeCells count="44">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B49:E49"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B33:E33"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B46:E46"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="B31:E31"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B39:E39"/>
     <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B42:E42"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11915,13 +11915,27 @@
         <f>Planejado!G21</f>
         <v/>
       </c>
-      <c r="H21" s="49" t="n"/>
-      <c r="I21" s="49" t="n"/>
-      <c r="J21" s="49" t="n"/>
-      <c r="K21" s="49" t="n"/>
-      <c r="L21" s="49" t="n"/>
-      <c r="M21" s="49" t="n"/>
-      <c r="N21" s="49" t="n"/>
+      <c r="H21" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="O21" s="49" t="n"/>
       <c r="P21" s="49" t="n"/>
       <c r="Q21" s="49" t="n"/>
@@ -11931,8 +11945,16 @@
         <f>SUM(H21:S21)</f>
         <v/>
       </c>
-      <c r="U21" s="50" t="n"/>
-      <c r="V21" s="50" t="n"/>
+      <c r="U21" s="50" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="V21" s="50" t="inlineStr">
+        <is>
+          <t>Ainda não contratado — sem custo até jul/26</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="47">
@@ -13629,7 +13651,7 @@
       </c>
       <c r="D23" s="62" t="inlineStr">
         <is>
-          <t>Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. O AnyDesk é contratação nova e sem substituto atual. Definir valor e mês para a linha entrar no orçamento — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
+          <t>Ainda não contratado — realizado zerado até jul/26, e não falta de lançamento. Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. É contratação nova, sem substituto atual. Definir valor e mês antes de assinar — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
         </is>
       </c>
       <c r="E23" s="62" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -10173,12 +10173,12 @@
       </c>
       <c r="D14" s="36" t="inlineStr">
         <is>
-          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+          <t>Projeto Sala de Reunião — itens funcionais</t>
         </is>
       </c>
       <c r="E14" s="36" t="inlineStr">
         <is>
-          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+          <t>Câmeras, microfones e cadeiras. DECIDIDO executar só o funcional; cafeteira, copos, canetas e blocos personalizados saem para o Administrativo. Valor a rever quando vier a quebra entre funcional e consumo</t>
         </is>
       </c>
       <c r="F14" s="35" t="inlineStr"/>
@@ -13481,27 +13481,27 @@
       </c>
       <c r="B18" s="65" t="inlineStr">
         <is>
-          <t>Sala de Reunião — EXECUTAR, PAUSAR OU REPENSAR?</t>
+          <t>Sala de Reunião — DECIDIDO: executar só o funcional</t>
         </is>
       </c>
       <c r="C18" s="65" t="inlineStr">
         <is>
-          <t>Projeto orçado em R$ 2.800/mês × 12 = R$ 33.600, classificado em Móveis e Utensílios, sem nenhum lançamento até jul/26. A gestora levanta que a sala já não comporta todas as pessoas, então investir na configuração atual pode não resolver o problema real. Três caminhos: executar como está, pausar, ou repensar a solução (outro espaço, formato híbrido, mais de uma sala).</t>
+          <t>DECISÃO DA GESTORA: mexer somente no que for funcional. Entram os itens de infraestrutura de reunião — câmeras, microfones e cadeiras. Ficam de fora cafeteira, copos, canetas e blocos personalizados, que são consumo e brinde, pertencem ao Administrativo (item U) e não resolvem o problema da sala. O orçamento atual é de R$ 2.800/mês, R$ 33.600 no ano, sem nenhum lançamento até jul/26.</t>
         </is>
       </c>
       <c r="D18" s="65" t="inlineStr">
         <is>
-          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. SEPARAR OS ITENS: a descrição na ficha mistura infraestrutura de reunião (câmeras, microfones, cadeiras) com material de consumo e brindes (canetas, blocos personalizados, copos, cafeteira). O segundo grupo é papelaria e deveria estar no Administrativo, não no TI (item U).</t>
+          <t>FALTA A QUEBRA DO VALOR: quanto dos R$ 33.600 é funcional e quanto é consumo. Só com isso dá para ajustar a linha e liberar a diferença. Levantar orçamento dos itens funcionais antes de comprar. Definir também se é compra pontual ou parcelada — hoje está diluída linearmente em 12 meses, e se for compra única o desvio vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. Segue de pé a observação da gestora de que a sala já não comporta todas as pessoas: o funcional melhora a qualidade da reunião, não a capacidade — se o problema de espaço precisar de solução, é projeto à parte.</t>
         </is>
       </c>
       <c r="E18" s="65" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F18" s="68" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F18" s="69" t="inlineStr">
+        <is>
+          <t>QUEBRAR VALOR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Controle de Equipamentos'!$A$12:$J$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$104</definedName>
   </definedNames>
@@ -1904,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1983,12 +1983,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="83" t="inlineStr">
         <is>
-          <t>Sem devolução</t>
+          <t>Prazo: 7 dias</t>
         </is>
       </c>
       <c r="B7" s="78" t="inlineStr">
         <is>
-          <t>Se a pessoa não entrega o item antigo, a solicitação fica 'Pendente devolução' e não vira compra até ser resolvida.</t>
+          <t>O empréstimo vale por 7 dias corridos. Passou disso, o status vira 'Atrasado' e o TI cobra a devolução. A coluna 'Dias em posse' calcula sozinha a partir da data de saída.</t>
         </is>
       </c>
       <c r="C7" s="79" t="n"/>
@@ -2003,12 +2003,12 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="83" t="inlineStr">
         <is>
-          <t>Aviso de saldo</t>
+          <t>Sem devolução</t>
         </is>
       </c>
       <c r="B8" s="78" t="inlineStr">
         <is>
-          <t>Antes de aprovar, conferir o saldo da rubrica da área solicitante. Se a compra for levar ao estouro, avisar a área ANTES de comprar (pendência R).</t>
+          <t>Se a pessoa não entrega o item antigo, a solicitação fica 'Pendente devolução' e não vira compra até ser resolvida.</t>
         </is>
       </c>
       <c r="C8" s="79" t="n"/>
@@ -2020,76 +2020,84 @@
       <c r="I8" s="79" t="n"/>
       <c r="J8" s="79" t="n"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="76" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="83" t="inlineStr">
+        <is>
+          <t>Aviso de saldo</t>
+        </is>
+      </c>
+      <c r="B9" s="78" t="inlineStr">
+        <is>
+          <t>Antes de aprovar, conferir o saldo da rubrica da área solicitante. Se a compra for levar ao estouro, avisar a área ANTES de comprar (pendência R).</t>
+        </is>
+      </c>
+      <c r="C9" s="79" t="n"/>
+      <c r="D9" s="79" t="n"/>
+      <c r="E9" s="79" t="n"/>
+      <c r="F9" s="79" t="n"/>
+      <c r="G9" s="79" t="n"/>
+      <c r="H9" s="79" t="n"/>
+      <c r="I9" s="79" t="n"/>
+      <c r="J9" s="79" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="76" t="inlineStr">
         <is>
           <t>SOLICITAÇÕES</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Área solicitante</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Solicitante</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Devolveu o antigo?</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Patrimônio devolvido</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Valor estimado</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="84" t="n"/>
-      <c r="B12" s="84" t="n"/>
-      <c r="C12" s="84" t="n"/>
-      <c r="D12" s="84" t="n"/>
-      <c r="E12" s="84" t="n"/>
-      <c r="F12" s="84" t="n"/>
-      <c r="G12" s="84" t="n"/>
-      <c r="H12" s="49" t="n"/>
-      <c r="I12" s="84" t="n"/>
-      <c r="J12" s="84" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="84" t="n"/>
@@ -2559,79 +2567,76 @@
       <c r="I51" s="84" t="n"/>
       <c r="J51" s="84" t="n"/>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="84" t="n"/>
+      <c r="B52" s="84" t="n"/>
+      <c r="C52" s="84" t="n"/>
+      <c r="D52" s="84" t="n"/>
+      <c r="E52" s="84" t="n"/>
+      <c r="F52" s="84" t="n"/>
+      <c r="G52" s="84" t="n"/>
+      <c r="H52" s="49" t="n"/>
+      <c r="I52" s="84" t="n"/>
+      <c r="J52" s="84" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
         <is>
           <t>EMPRÉSTIMOS (equipamento reserva)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="85" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="85" t="inlineStr">
         <is>
           <t>Item emprestado</t>
         </is>
       </c>
-      <c r="B54" s="85" t="inlineStr">
+      <c r="B55" s="85" t="inlineStr">
         <is>
           <t>Patrimônio</t>
         </is>
       </c>
-      <c r="C54" s="85" t="inlineStr">
+      <c r="C55" s="85" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="D54" s="85" t="inlineStr">
+      <c r="D55" s="85" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="E54" s="85" t="inlineStr">
+      <c r="E55" s="85" t="inlineStr">
         <is>
           <t>Saída em</t>
         </is>
       </c>
-      <c r="F54" s="85" t="inlineStr">
+      <c r="F55" s="85" t="inlineStr">
         <is>
           <t>Previsão de devolução</t>
         </is>
       </c>
-      <c r="G54" s="85" t="inlineStr">
+      <c r="G55" s="85" t="inlineStr">
         <is>
           <t>Devolvido em</t>
         </is>
       </c>
-      <c r="H54" s="85" t="inlineStr">
+      <c r="H55" s="85" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I54" s="85" t="inlineStr">
-        <is>
-          <t>Dias em posse</t>
-        </is>
-      </c>
-      <c r="J54" s="85" t="inlineStr">
+      <c r="I55" s="85" t="inlineStr">
+        <is>
+          <t>Dias em posse (limite: 7)</t>
+        </is>
+      </c>
+      <c r="J55" s="85" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="84" t="n"/>
-      <c r="B55" s="84" t="n"/>
-      <c r="C55" s="84" t="n"/>
-      <c r="D55" s="84" t="n"/>
-      <c r="E55" s="84" t="n"/>
-      <c r="F55" s="84" t="n"/>
-      <c r="G55" s="84" t="n"/>
-      <c r="H55" s="84" t="n"/>
-      <c r="I55" s="86">
-        <f>IF(E55="","",IF(G55="",TODAY()-E55,G55-E55))</f>
-        <v/>
-      </c>
-      <c r="J55" s="84" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="84" t="n"/>
@@ -2993,27 +2998,48 @@
       </c>
       <c r="J79" s="84" t="n"/>
     </row>
+    <row r="80">
+      <c r="A80" s="84" t="n"/>
+      <c r="B80" s="84" t="n"/>
+      <c r="C80" s="84" t="n"/>
+      <c r="D80" s="84" t="n"/>
+      <c r="E80" s="84" t="n"/>
+      <c r="F80" s="84" t="n"/>
+      <c r="G80" s="84" t="n"/>
+      <c r="H80" s="84" t="n"/>
+      <c r="I80" s="86">
+        <f>IF(E80="","",IF(G80="",TODAY()-E80,G80-E80))</f>
+        <v/>
+      </c>
+      <c r="J80" s="84" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:J51"/>
-  <mergeCells count="9">
+  <autoFilter ref="A12:J52"/>
+  <mergeCells count="10">
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B5:J5"/>
-    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="B9:J9"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A10:J10"/>
     <mergeCell ref="B6:J6"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
+  <conditionalFormatting sqref="I56:I80">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="I12:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I13:I52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aberta,Aguardando devolução,Aprovada,Comprada,Entregue,Negada"</formula1>
     </dataValidation>
-    <dataValidation sqref="F12:F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F13:F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não,Não se aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="H55:H79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H56:H80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Emprestado,Devolvido,Atrasado,Baixado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13587,17 +13613,17 @@
       </c>
       <c r="D21" s="62" t="inlineStr">
         <is>
-          <t>Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso — se uma área quebra três vezes mais que as outras, isso aparece. Encaminhar: (1) comunicar a regra às áreas; (2) montar o pequeno estoque de reserva; (3) definir quantos dias o empréstimo pode durar antes de virar 'Atrasado'; (4) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
+          <t>APROVADA pela gestora, com prazo de empréstimo de 7 DIAS CORRIDOS — passou disso, vira 'Atrasado' e o TI cobra a devolução. A aba de controle já destaca em vermelho quem passar do prazo. Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso: se uma área quebra três vezes mais que as outras, isso aparece. Falta encaminhar: (1) comunicar a regra e o prazo às áreas; (2) montar o estoque de reserva com fio; (3) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
         </is>
       </c>
       <c r="E21" s="62" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Vinicius</t>
         </is>
       </c>
       <c r="F21" s="69" t="inlineStr">
         <is>
-          <t>IMPLANTAR</t>
+          <t>APROVADA</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -13421,7 +13421,7 @@
       </c>
       <c r="D15" s="62" t="inlineStr">
         <is>
-          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
+          <t>DECIDIDO: solicitar a reclassificação contábil ao financeiro agora, sem esperar a abertura do centro de custo novo. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado ao mesmo tempo. O que pedir ao financeiro: reclassificar os seis lançamentos do contrato 4134643529 (jan a jun/26) do centro de custo Jurídico para o de TI, e ajustar a classificação dos próximos para não repetir. Depois de reclassificado, aplicar o rateio do item L, já que é ferramenta de uso transversal. Quando o centro de custo novo abrir, conferir se a classificação nasceu certa.</t>
         </is>
       </c>
       <c r="E15" s="62" t="inlineStr">
@@ -13429,9 +13429,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F15" s="63" t="inlineStr">
-        <is>
-          <t>RECLASSIFICAR</t>
+      <c r="F15" s="69" t="inlineStr">
+        <is>
+          <t>SOLICITADA</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -13645,7 +13645,7 @@
       </c>
       <c r="D22" s="65" t="inlineStr">
         <is>
-          <t>Três diferenças separam as duas coisas: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. Se papelaria estiver caindo no orçamento do TI por motivo histórico, é o mesmo caso do Adapta (item Q): classificação errada, corrigir na origem quando o centro de custo novo for aberto.</t>
+          <t>CONFIRMADO pela gestora: papelaria fica no Administrativo. Três diferenças sustentam a separação: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. A VERIFICAR: se hoje há papelaria caindo no orçamento ou no centro de custo do TI por motivo histórico. Se houver, entra no mesmo pedido de reclassificação do Adapta (item Q). Vale conferir também os itens de consumo que estavam no projeto da sala de reunião — cafeteira, copos, canetas e blocos personalizados —, que por esta decisão saem do TI.</t>
         </is>
       </c>
       <c r="E22" s="65" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="F22" s="69" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO</t>
+          <t>CONFIRMADA</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>Jul/26</t>
+          <t>Jun/26</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
@@ -11163,9 +11163,7 @@
       <c r="M6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" s="49" t="n"/>
       <c r="O6" s="49" t="n"/>
       <c r="P6" s="49" t="n"/>
       <c r="Q6" s="49" t="n"/>
@@ -11177,7 +11175,7 @@
       </c>
       <c r="U6" s="50" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V6" s="50" t="inlineStr">
@@ -11225,17 +11223,15 @@
         <v>0</v>
       </c>
       <c r="K7" s="49" t="n">
-        <v>0</v>
+        <v>3723.62</v>
       </c>
       <c r="L7" s="49" t="n">
-        <v>3723.62</v>
+        <v>6173.37</v>
       </c>
       <c r="M7" s="49" t="n">
-        <v>6173.37</v>
-      </c>
-      <c r="N7" s="49" t="n">
         <v>6300</v>
       </c>
+      <c r="N7" s="49" t="n"/>
       <c r="O7" s="49" t="n"/>
       <c r="P7" s="49" t="n"/>
       <c r="Q7" s="49" t="n"/>
@@ -11252,7 +11248,7 @@
       </c>
       <c r="V7" s="50" t="inlineStr">
         <is>
-          <t>01/05 NFS.76 R$ 3.723,62; 01/06 NFS.78 R$ 6.173,37; 01/07 NFS.3 R$ 6.300,00. Sem pagamento em jan–abr: contratação segurada</t>
+          <t>Serviço de abr, mai e jun (pagos em 01/05, 01/06 e 01/07). Zero em jan–mar: contratação segurada — bate com a entrada em abr</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11282,7 @@
         <v/>
       </c>
       <c r="H8" s="49" t="n">
-        <v>4311.56</v>
+        <v>0</v>
       </c>
       <c r="I8" s="49" t="n">
         <v>0</v>
@@ -11332,7 +11328,7 @@
       </c>
       <c r="V8" s="50" t="inlineStr">
         <is>
-          <t>19/01 NFS.70 R$ 4.311,56 — serviço esporádico, provavelmente referente a dez/25. Vínculo encerrado com a entrada como consultor fixo</t>
+          <t>Zero no exercício: o pagamento de R$ 4.311,56 em 19/01 (NFS.70) era serviço de dez/25 e, por competência, não pertence a 2026. Vínculo encerrado com a entrada como consultor fixo</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11969,7 @@
       </c>
       <c r="U21" s="50" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V21" s="50" t="inlineStr">
@@ -13827,17 +13823,17 @@
       </c>
       <c r="B28" s="65" t="inlineStr">
         <is>
-          <t>Competência x caixa — DECIDIR O REGIME</t>
+          <t>Competência x caixa — DECIDIDO: COMPETÊNCIA</t>
         </is>
       </c>
       <c r="C28" s="65" t="inlineStr">
         <is>
-          <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
+          <t>Todos os PJs prestam no mês e recebem no seguinte — Miguel, Thamar e Dra. Michele no Jurídico; Elias e Jonathan no TI. O realizado foi convertido para COMPETÊNCIA: os valores dos PJs foram deslocados um mês para trás em relação à data de pagamento. O que foi pago em jan/26 era serviço de dez/25 e saiu do exercício.</t>
         </is>
       </c>
       <c r="D28" s="65" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
+          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. A CONFERIR: os CLT (Geovanna e Vinicius) NÃO foram deslocados. Se a folha for paga no mês seguinte, como é usual, eles também precisam deslocar. E na Thamar, confirmar se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
         </is>
       </c>
       <c r="E28" s="65" t="inlineStr">
@@ -13845,9 +13841,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F28" s="66" t="inlineStr">
-        <is>
-          <t>DECIDIR</t>
+      <c r="F28" s="67" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -11955,9 +11955,7 @@
       <c r="M21" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" s="49" t="n"/>
       <c r="O21" s="49" t="n"/>
       <c r="P21" s="49" t="n"/>
       <c r="Q21" s="49" t="n"/>
@@ -13833,7 +13831,7 @@
       </c>
       <c r="D28" s="65" t="inlineStr">
         <is>
-          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. A CONFERIR: os CLT (Geovanna e Vinicius) NÃO foram deslocados. Se a folha for paga no mês seguinte, como é usual, eles também precisam deslocar. E na Thamar, confirmar se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
+          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. Os CLT (Geovanna e Vinicius) seguem a mesma regra, confirmado pela gestora: folha paga no mês seguinte, também deslocados. A CONFERIR apenas na Thamar: se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
         </is>
       </c>
       <c r="E28" s="65" t="inlineStr">

--- a/orcamento/Orcamento_TI_2026.xlsx
+++ b/orcamento/Orcamento_TI_2026.xlsx
@@ -10199,12 +10199,12 @@
       </c>
       <c r="D14" s="36" t="inlineStr">
         <is>
-          <t>Projeto Sala de Reunião — itens funcionais</t>
+          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
         </is>
       </c>
       <c r="E14" s="36" t="inlineStr">
         <is>
-          <t>Câmeras, microfones e cadeiras. DECIDIDO executar só o funcional; cafeteira, copos, canetas e blocos personalizados saem para o Administrativo. Valor a rever quando vier a quebra entre funcional e consumo</t>
+          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc. APROVADO no escopo completo. Definir se é compra pontual ou parcelada — hoje está diluída linearmente em 12 meses</t>
         </is>
       </c>
       <c r="F14" s="35" t="inlineStr"/>
@@ -13501,17 +13501,17 @@
       </c>
       <c r="B18" s="65" t="inlineStr">
         <is>
-          <t>Sala de Reunião — DECIDIDO: executar só o funcional</t>
+          <t>Sala de Reunião — DECIDIDO: executar o projeto completo</t>
         </is>
       </c>
       <c r="C18" s="65" t="inlineStr">
         <is>
-          <t>DECISÃO DA GESTORA: mexer somente no que for funcional. Entram os itens de infraestrutura de reunião — câmeras, microfones e cadeiras. Ficam de fora cafeteira, copos, canetas e blocos personalizados, que são consumo e brinde, pertencem ao Administrativo (item U) e não resolvem o problema da sala. O orçamento atual é de R$ 2.800/mês, R$ 33.600 no ano, sem nenhum lançamento até jul/26.</t>
+          <t>DECISÃO DA GESTORA: executar como está, no escopo original. Entram tanto os itens de infraestrutura (câmeras, microfones, cadeiras) quanto os de consumo e ambientação (cafeteira, copos, canetas e blocos personalizados). Orçamento mantido em R$ 2.800/mês, R$ 33.600 no ano, sem nenhum lançamento até jun/26. Revoga a decisão anterior de executar só o funcional.</t>
         </is>
       </c>
       <c r="D18" s="65" t="inlineStr">
         <is>
-          <t>FALTA A QUEBRA DO VALOR: quanto dos R$ 33.600 é funcional e quanto é consumo. Só com isso dá para ajustar a linha e liberar a diferença. Levantar orçamento dos itens funcionais antes de comprar. Definir também se é compra pontual ou parcelada — hoje está diluída linearmente em 12 meses, e se for compra única o desvio vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. Segue de pé a observação da gestora de que a sala já não comporta todas as pessoas: o funcional melhora a qualidade da reunião, não a capacidade — se o problema de espaço precisar de solução, é projeto à parte.</t>
+          <t>É a maior despesa isolada do TI e 38% do que a área tem orçado em despesas, então o mês em que a compra ocorrer vai dominar o comparativo. DEFINIR: se é compra pontual ou parcelada. Hoje está diluída linearmente em 12 meses — se for compra única, o desvio vai acusar economia falsa todo mês até a compra e um pico no mês em que ela acontecer; nesse caso vale concentrar o planejado no mês previsto. OBSERVAR: os itens de consumo e brinde deste projeto são a exceção à decisão do item U, que tirou papelaria do TI — aqui ficam por serem parte de um projeto de ambientação, não reposição de material de escritório. E a ressalva da própria gestora continua de pé: o projeto melhora a qualidade da reunião, não a capacidade da sala. Se o espaço não comporta todas as pessoas, isso segue verdade depois da compra.</t>
         </is>
       </c>
       <c r="E18" s="65" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="F18" s="69" t="inlineStr">
         <is>
-          <t>QUEBRAR VALOR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
